--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENRJ.MI</t>
+          <t>ENRG.PA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CECE.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1232,8 +1232,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>1</v>
+      <c r="A14" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1256,31 +1256,31 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>104.78</v>
+        <v>257.975</v>
       </c>
       <c r="H14" t="n">
-        <v>104.042</v>
+        <v>253.3442</v>
       </c>
       <c r="I14" t="n">
-        <v>102.4304</v>
+        <v>230.3964</v>
       </c>
       <c r="J14" t="n">
-        <v>57.2</v>
+        <v>53.4</v>
       </c>
       <c r="K14" t="n">
-        <v>25.6</v>
+        <v>7.3</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1625</v>
-      </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>L1 BUY (5/5)</t>
+        <v>-2.4656</v>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PAFR.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1604,22 +1604,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6.79</v>
+        <v>7.419</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6095</v>
+        <v>7.3129</v>
       </c>
       <c r="I20" t="n">
-        <v>6.6312</v>
+        <v>6.9057</v>
       </c>
       <c r="J20" t="n">
-        <v>62.4</v>
+        <v>57.1</v>
       </c>
       <c r="K20" t="n">
-        <v>18.2</v>
+        <v>30.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0515</v>
+        <v>-0.0317</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EMQA.MI</t>
+          <t>EGEE.DE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1836,22 +1836,22 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>65.33</v>
+        <v>5963.5</v>
       </c>
       <c r="H24" t="n">
-        <v>63.9134</v>
+        <v>5799.7546</v>
       </c>
       <c r="I24" t="n">
-        <v>63.9156</v>
+        <v>4758.1534</v>
       </c>
       <c r="J24" t="n">
-        <v>61.7</v>
+        <v>54.4</v>
       </c>
       <c r="K24" t="n">
-        <v>18.8</v>
+        <v>10.3</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4318</v>
+        <v>-97.5719</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMJP.MI</t>
+          <t>CJ1.PA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1928,8 +1928,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>3</v>
+      <c r="A26" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1969,14 +1969,14 @@
       <c r="L26" t="n">
         <v>0.2534</v>
       </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AAUS.MI</t>
+          <t>LYPU.DE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2184,22 +2184,22 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>436.16</v>
+        <v>2479.5</v>
       </c>
       <c r="H30" t="n">
-        <v>423.9476</v>
+        <v>2398.2214</v>
       </c>
       <c r="I30" t="n">
-        <v>423.7632</v>
+        <v>2081.951</v>
       </c>
       <c r="J30" t="n">
-        <v>71</v>
+        <v>57.1</v>
       </c>
       <c r="K30" t="n">
-        <v>24.9</v>
+        <v>11.9</v>
       </c>
       <c r="L30" t="n">
-        <v>2.3344</v>
+        <v>-19.8327</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SD3E.MI</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EAEJ.MI</t>
+          <t>AZEH.DE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AWAT.MI</t>
+          <t>WATC.SW</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AWAT.MI</t>
+          <t>WAT.PA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2706,22 +2706,22 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>63.76</v>
+        <v>2161.75</v>
       </c>
       <c r="H39" t="n">
-        <v>62.3375</v>
+        <v>2070.7854</v>
       </c>
       <c r="I39" t="n">
-        <v>62.345</v>
+        <v>1663.2564</v>
       </c>
       <c r="J39" t="n">
-        <v>62.1</v>
+        <v>55.8</v>
       </c>
       <c r="K39" t="n">
-        <v>19</v>
+        <v>12.3</v>
       </c>
       <c r="L39" t="n">
-        <v>0.426</v>
+        <v>-34.4316</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2740,8 +2740,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>2</v>
+      <c r="A40" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2764,31 +2764,31 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>66.59999999999999</v>
+        <v>4.318</v>
       </c>
       <c r="H40" t="n">
-        <v>65.20740000000001</v>
+        <v>6.0109</v>
       </c>
       <c r="I40" t="n">
-        <v>65.3232</v>
+        <v>15.1466</v>
       </c>
       <c r="J40" t="n">
-        <v>61.3</v>
+        <v>45.4</v>
       </c>
       <c r="K40" t="n">
-        <v>18.7</v>
+        <v>9.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.7793</v>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -2996,22 +2996,22 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>176.74</v>
+        <v>442.4755</v>
       </c>
       <c r="H44" t="n">
-        <v>172.7139</v>
+        <v>427.4077</v>
       </c>
       <c r="I44" t="n">
-        <v>170.5344</v>
+        <v>378.4935</v>
       </c>
       <c r="J44" t="n">
-        <v>70.8</v>
+        <v>55.7</v>
       </c>
       <c r="K44" t="n">
-        <v>30.2</v>
+        <v>9.6</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8333</v>
+        <v>-3.0072</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3146,8 +3146,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
-        <v>3</v>
+      <c r="A47" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3187,14 +3187,14 @@
       <c r="L47" t="n">
         <v>-0.955</v>
       </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PREU.MI</t>
+          <t>LWCE.PA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EAEU.MI</t>
+          <t>EUEE.DE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UIMU.MI</t>
+          <t>MFDD.MI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>QFEU.MI</t>
+          <t>QCEU.PA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBES.MI</t>
+          <t>FMI.MI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PAZE.MI</t>
+          <t>EPAB.PA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MEMU.MI</t>
+          <t>CMU.PA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4132,8 +4132,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>2</v>
+      <c r="A64" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4156,31 +4156,31 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>411.58</v>
+        <v>237.2</v>
       </c>
       <c r="H64" t="n">
-        <v>409.1595</v>
+        <v>238.5414</v>
       </c>
       <c r="I64" t="n">
-        <v>410.6092</v>
+        <v>266.4454</v>
       </c>
       <c r="J64" t="n">
-        <v>55.1</v>
+        <v>47.7</v>
       </c>
       <c r="K64" t="n">
-        <v>17.9</v>
+        <v>8.4</v>
       </c>
       <c r="L64" t="n">
-        <v>1.2223</v>
-      </c>
-      <c r="M64" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>2.8977</v>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4248,8 +4248,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>1</v>
+      <c r="A66" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4272,31 +4272,31 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>4.85</v>
+        <v>4.3305</v>
       </c>
       <c r="H66" t="n">
-        <v>4.8027</v>
+        <v>4.2799</v>
       </c>
       <c r="I66" t="n">
-        <v>4.8002</v>
+        <v>4.2752</v>
       </c>
       <c r="J66" t="n">
-        <v>64.59999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="K66" t="n">
-        <v>24.5</v>
+        <v>6.1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="M66" s="1" t="inlineStr">
-        <is>
-          <t>L1 BUY (5/5)</t>
+        <v>0.0139</v>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4330,22 +4330,22 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>203.58</v>
+        <v>354.35</v>
       </c>
       <c r="H67" t="n">
-        <v>198.4826</v>
+        <v>343.7271</v>
       </c>
       <c r="I67" t="n">
-        <v>199.0398</v>
+        <v>313.427</v>
       </c>
       <c r="J67" t="n">
-        <v>63.7</v>
+        <v>55.7</v>
       </c>
       <c r="K67" t="n">
-        <v>23.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>1.3773</v>
+        <v>-1.9145</v>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -4968,22 +4968,22 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>5.15</v>
+        <v>12</v>
       </c>
       <c r="H78" t="n">
-        <v>5.1391</v>
+        <v>12.1352</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1558</v>
+        <v>11.0472</v>
       </c>
       <c r="J78" t="n">
-        <v>53.8</v>
+        <v>50.2</v>
       </c>
       <c r="K78" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0051</v>
+        <v>-0.0963</v>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5026,22 +5026,22 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>5.47</v>
+        <v>2828</v>
       </c>
       <c r="H79" t="n">
-        <v>5.4141</v>
+        <v>2753.1811</v>
       </c>
       <c r="I79" t="n">
-        <v>5.4432</v>
+        <v>2352.7483</v>
       </c>
       <c r="J79" t="n">
-        <v>59</v>
+        <v>55.4</v>
       </c>
       <c r="K79" t="n">
-        <v>18</v>
+        <v>10.3</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0193</v>
+        <v>-31.1544</v>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WENA.MI</t>
+          <t>WOEE.AS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -5200,22 +5200,22 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.77</v>
+        <v>3.11</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8127</v>
+        <v>2.8871</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8102</v>
+        <v>2.2077</v>
       </c>
       <c r="J82" t="n">
-        <v>36.3</v>
+        <v>56.5</v>
       </c>
       <c r="K82" t="n">
-        <v>18</v>
+        <v>16.8</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.0109</v>
+        <v>-0.0269</v>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EXEM.MI</t>
+          <t>WEXU.DE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EAEG.MI</t>
+          <t>EGRI.PA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AFHY.MI</t>
+          <t>AHYE.PA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GGRN.MI</t>
+          <t>CB3.PA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ECBX.MI</t>
+          <t>CBEF.MI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -6708,22 +6708,22 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>21.15</v>
+        <v>5.0855</v>
       </c>
       <c r="H108" t="n">
-        <v>21.1723</v>
+        <v>5.5709</v>
       </c>
       <c r="I108" t="n">
-        <v>21.1848</v>
+        <v>8.2729</v>
       </c>
       <c r="J108" t="n">
-        <v>47.6</v>
+        <v>45.5</v>
       </c>
       <c r="K108" t="n">
-        <v>14.4</v>
+        <v>9.4</v>
       </c>
       <c r="L108" t="n">
-        <v>-0.0016</v>
+        <v>0.2116</v>
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WENA.MI</t>
+          <t>WOEH.MI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BTP1.MI</t>
+          <t>BTP13.MI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>X1GA.MI</t>
+          <t>MA35.PA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>X1GA.MI</t>
+          <t>AM3A.PA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>UFRH.MI</t>
+          <t>AFRN.PA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -7380,8 +7380,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>2</v>
+      <c r="A120" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -7404,31 +7404,31 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>5.07</v>
+        <v>5.0283</v>
       </c>
       <c r="H120" t="n">
-        <v>5.0675</v>
+        <v>5.0295</v>
       </c>
       <c r="I120" t="n">
-        <v>5.0628</v>
+        <v>5.0358</v>
       </c>
       <c r="J120" t="n">
-        <v>99.8</v>
+        <v>45.3</v>
       </c>
       <c r="K120" t="n">
-        <v>95.8</v>
+        <v>9.9</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.0005</v>
+      </c>
+      <c r="M120" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -7438,8 +7438,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
-        <v>3</v>
+      <c r="A121" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -7479,14 +7479,14 @@
       <c r="L121" t="n">
         <v>-0.0759</v>
       </c>
-      <c r="M121" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+      <c r="M121" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>X1GA.MI</t>
+          <t>MA13.PA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LFIN.MI</t>
+          <t>FINSW.MI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>UFRH.MI</t>
+          <t>AFLT.PA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -8192,8 +8192,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>2</v>
+      <c r="A134" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -8216,31 +8216,31 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>15.47</v>
+        <v>6.354</v>
       </c>
       <c r="H134" t="n">
-        <v>15.4573</v>
+        <v>6.5967</v>
       </c>
       <c r="I134" t="n">
-        <v>15.4462</v>
+        <v>7.977</v>
       </c>
       <c r="J134" t="n">
-        <v>100</v>
+        <v>45.6</v>
       </c>
       <c r="K134" t="n">
-        <v>100</v>
+        <v>9.4</v>
       </c>
       <c r="L134" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="M134" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.1191</v>
+      </c>
+      <c r="M134" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>X006.MI</t>
+          <t>C3M.PA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EONA.MI</t>
+          <t>CSH.PA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -8448,22 +8448,22 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>20.73</v>
+        <v>19.194</v>
       </c>
       <c r="H138" t="n">
-        <v>20.7477</v>
+        <v>19.7582</v>
       </c>
       <c r="I138" t="n">
-        <v>21.141</v>
+        <v>20.2935</v>
       </c>
       <c r="J138" t="n">
-        <v>47.7</v>
+        <v>32.3</v>
       </c>
       <c r="K138" t="n">
-        <v>17.7</v>
+        <v>27.4</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0601</v>
+        <v>-0.0717</v>
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DAXE.MI</t>
+          <t>LYY7.DE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -8714,8 +8714,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n">
-        <v>3</v>
+      <c r="A143" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -8755,14 +8755,14 @@
       <c r="L143" t="n">
         <v>0.074</v>
       </c>
-      <c r="M143" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+      <c r="M143" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EMGB.MI</t>
+          <t>EMBHI.MI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EMGB.MI</t>
+          <t>AGEB.PA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>USEA.MI</t>
+          <t>USEH.MI</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -9028,22 +9028,22 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>149.33</v>
+        <v>148.37</v>
       </c>
       <c r="H148" t="n">
-        <v>150.4255</v>
+        <v>148.6929</v>
       </c>
       <c r="I148" t="n">
-        <v>151.2204</v>
+        <v>149.6427</v>
       </c>
       <c r="J148" t="n">
-        <v>37.6</v>
+        <v>43.6</v>
       </c>
       <c r="K148" t="n">
-        <v>17.6</v>
+        <v>22.4</v>
       </c>
       <c r="L148" t="n">
-        <v>-0.2021</v>
+        <v>-0.001</v>
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EMGB.MI</t>
+          <t>LEMB.L</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>UCBP.MI</t>
+          <t>USIH.PA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>UCBE.MI</t>
+          <t>PRAP.SW</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>UCBP.MI</t>
+          <t>USIG.L</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>UCBP.MI</t>
+          <t>USIC.L</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>USCP.MI</t>
+          <t>USRIH.MI</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>USCP.MI</t>
+          <t>WEBD.DE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>USEX.MI</t>
+          <t>LESA.DE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>USEA.MI</t>
+          <t>USEE.AS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>USES.MI</t>
+          <t>SADU.PA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10048,8 +10048,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="n">
-        <v>3</v>
+      <c r="A166" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -10089,14 +10089,14 @@
       <c r="L166" t="n">
         <v>-0.3903</v>
       </c>
-      <c r="M166" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+      <c r="M166" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -10478,22 +10478,22 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>15.39</v>
+        <v>15.878</v>
       </c>
       <c r="H173" t="n">
-        <v>15.0577</v>
+        <v>15.2079</v>
       </c>
       <c r="I173" t="n">
-        <v>15.0326</v>
+        <v>14.3084</v>
       </c>
       <c r="J173" t="n">
-        <v>64.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K173" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="L173" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="M173" s="4" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MILS.MI</t>
+          <t>GENY.L</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ROAI.MI</t>
+          <t>GOAI.PA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -11000,22 +11000,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>16.16</v>
+        <v>22.6</v>
       </c>
       <c r="H182" t="n">
-        <v>15.7244</v>
+        <v>21.7023</v>
       </c>
       <c r="I182" t="n">
-        <v>15.6592</v>
+        <v>19.3749</v>
       </c>
       <c r="J182" t="n">
-        <v>65.7</v>
+        <v>64</v>
       </c>
       <c r="K182" t="n">
-        <v>20.4</v>
+        <v>25.9</v>
       </c>
       <c r="L182" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -11282,7 +11282,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -11310,31 +11310,31 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>646.38</v>
+        <v>795.67</v>
       </c>
       <c r="H187" t="n">
-        <v>625.5232</v>
+        <v>781.3156</v>
       </c>
       <c r="I187" t="n">
-        <v>619.323</v>
+        <v>728.8896</v>
       </c>
       <c r="J187" t="n">
-        <v>77.2</v>
+        <v>59.7</v>
       </c>
       <c r="K187" t="n">
-        <v>27.4</v>
+        <v>20.5</v>
       </c>
       <c r="L187" t="n">
-        <v>3.4834</v>
-      </c>
-      <c r="M187" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>-2.8646</v>
+      </c>
+      <c r="M187" s="1" t="inlineStr">
+        <is>
+          <t>L1 BUY (5/5)</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -11533,8 +11533,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
-        <v>2</v>
+      <c r="A191" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -11562,31 +11562,31 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>164.86</v>
+        <v>42.125</v>
       </c>
       <c r="H191" t="n">
-        <v>154.0188</v>
+        <v>43.5879</v>
       </c>
       <c r="I191" t="n">
-        <v>151.6332</v>
+        <v>59.4245</v>
       </c>
       <c r="J191" t="n">
-        <v>79.7</v>
+        <v>47.5</v>
       </c>
       <c r="K191" t="n">
-        <v>26.8</v>
+        <v>7.3</v>
       </c>
       <c r="L191" t="n">
-        <v>1.7035</v>
-      </c>
-      <c r="M191" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>1.5795</v>
+      </c>
+      <c r="M191" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -11814,22 +11814,22 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>121.96</v>
+        <v>4.4735</v>
       </c>
       <c r="H195" t="n">
-        <v>123.0848</v>
+        <v>7.7948</v>
       </c>
       <c r="I195" t="n">
-        <v>123.7056</v>
+        <v>26.0084</v>
       </c>
       <c r="J195" t="n">
-        <v>35.6</v>
+        <v>45.4</v>
       </c>
       <c r="K195" t="n">
-        <v>19.2</v>
+        <v>9.6</v>
       </c>
       <c r="L195" t="n">
-        <v>-0.1891</v>
+        <v>1.5434</v>
       </c>
       <c r="M195" s="6" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03</t>
+          <t>2026-05-21 22:20</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O196"/>
+  <dimension ref="A1:O215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11910,6 +11910,747 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>3</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>CNYA.L</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>iShares MSCI China A UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Asia - Emergente</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>6.2525</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>3</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>NDIA.L</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>iShares MSCI India UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Asia - Emergente</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>8.555</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>3</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>WSML.L</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>iShares MSCI World Small Cap UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Globale / All-World</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>10.042</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>3</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>VHYL.L</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World High Div Yield UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Globale / All-World</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>66.56999999999999</v>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>3</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>GGRP.L</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>WisdomTree Global Quality Dividend Growth UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Globale / All-World</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>2990</v>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>3</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>HEAL.L</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>iShares Healthcare Innovation UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Settoriale - Salute</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>3</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>HLTH.DE</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR (Acc)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Settoriale - Salute</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Francoforte</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>3</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>EQQQ.L</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Invesco EQQQ NASDAQ-100 UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Settoriale - Tecnologia</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>53152</v>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>3</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>WTEC.L</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SPDR MSCI World Technology UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Settoriale - Tecnologia</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>256.86</v>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>3</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>IWMO.L</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Momentum Factor UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Globale / All-World</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>112.91</v>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>3</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>IWQU.L</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Globale / All-World</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>3</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>MVOL.L</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Globale / All-World</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>3</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>IGIL.L</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>iShares Global Inflation Linked Govt Bond UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Obbligazionari - Inflation Linked</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>165.99</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>3</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>LTAM.L</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>iShares MSCI EM Latin America UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>America Latina e Centrale</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>1588.5</v>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>3</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>CSKR.L</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>iShares MSCI Korea UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Asia - Emergente</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>497.45</v>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>3</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AGGG.L</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>iShares Core Global Aggregate Bond UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Obbligazionari - Globali</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>3</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>IBTS.L</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>iShares $ Treasury Bond 1-3yr UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Obbligazionari - Governativi USD</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>3</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>EMVL.L</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>iShares Edge MSCI EM Min Vol Factor UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Asia - Emergente</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>3</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CI2.PA</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Amundi MSCI India UCITS ETF Swap EUR (Acc)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Asia - Emergente</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Parigi</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>776.274</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:10</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O215"/>
+  <dimension ref="A1:O230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11947,7 +11947,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11986,7 +11985,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -12025,7 +12023,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -12064,7 +12061,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -12103,7 +12099,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -12142,7 +12137,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -12181,7 +12175,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -12220,7 +12213,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -12259,7 +12251,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12298,7 +12289,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12337,7 +12327,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12376,7 +12365,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12415,7 +12403,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12454,7 +12441,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12493,7 +12479,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12532,7 +12517,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12571,7 +12555,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12610,7 +12593,6 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12649,7 +12631,491 @@
           <t>2026-05-22 01:10</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>3</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>IWSZ.L</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>iShares MSCI World Mid-Cap Equal Weight UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Azionario Mid Cap</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>IE00BP3QZD73</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>3</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>IS3T.DE</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>iShares MSCI World Mid-Cap Equal Weight UCITS ETF EUR</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Azionario Mid Cap</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Francoforte</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>IE00BP3QZD73</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>3</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>EMID.L</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>iShares MSCI Europe Mid Cap UCITS ETF EUR (Dist)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Azionario Mid Cap</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>3</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>IUSF.L</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>iShares MSCI USA Mid-Cap Equal Weight UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Azionario Mid Cap</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>3</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>IUSZ.L</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>iShares MSCI USA Mid-Cap Equal Weight UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Azionario Mid Cap</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>3</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>AIGI.L</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>WisdomTree Industrial Metals ETC (Al+Cu+Zn+Ni+Pb)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>GB00B15KYG56</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>3</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>COPA.L</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>WisdomTree Copper ETC</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>GB00B15KXQ89</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>3</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ALUM.L</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>WisdomTree Aluminium ETC</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>3</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ZINC.L</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>WisdomTree Zinc ETC</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>3</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>MINE.L</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>iShares Copper Miners UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>IE00063FT9K6</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>3</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>BATG.L</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>3</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>IPRV.L</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>iShares Listed Private Equity UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>IE00B1TXHL60</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>3</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>IPRV.AS</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>iShares Listed Private Equity UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>IE00B1TXHL60</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>3</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>XLPE.L</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Xtrackers LPX Private Equity Swap UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>3</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>XLPE.MI</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Xtrackers LPX Private Equity Swap UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7219,7 +7219,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -7264,14 +7264,14 @@
       <c r="L108" t="n">
         <v>0.0013</v>
       </c>
-      <c r="M108" s="1" t="inlineStr">
-        <is>
-          <t>L1 BUY (6/6)</t>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 13:06</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -11783,22 +11783,22 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>362.75</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="H180" t="n">
-        <v>345.7242</v>
+        <v>62.6522</v>
       </c>
       <c r="I180" t="n">
-        <v>337.8794</v>
+        <v>58.2662</v>
       </c>
       <c r="J180" t="n">
-        <v>79</v>
+        <v>72.3</v>
       </c>
       <c r="K180" t="n">
-        <v>32.9</v>
+        <v>44.4</v>
       </c>
       <c r="L180" t="n">
-        <v>2.1498</v>
+        <v>0.0555</v>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-05-22 12:24</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12639,7 +12639,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="K199" t="n">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L199" t="n">
         <v>-0.002</v>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -12949,8 +12949,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
-        <v>3</v>
+      <c r="A200" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -12977,14 +12977,32 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="M200" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+      <c r="G200" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="H200" t="n">
+        <v>99.0094</v>
+      </c>
+      <c r="I200" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="J200" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="K200" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="M200" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-05-22 12:19</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -13035,7 +13053,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="K201" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="L201" t="n">
         <v>-0.2042</v>
@@ -13047,7 +13065,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -13098,7 +13116,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="K202" t="n">
-        <v>29.9</v>
+        <v>31.4</v>
       </c>
       <c r="L202" t="n">
         <v>-0.094</v>
@@ -13110,7 +13128,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-05-22 12:13</t>
+          <t>2026-05-22 12:28</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,7 +545,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOR.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TUR.MI</t>
+          <t>TUR.PA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BRES.MI</t>
+          <t>LBRE.DE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GRC.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BRA.MI</t>
+          <t>RIO.PA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BRES.MI</t>
+          <t>CHM.PA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ENRG.MI</t>
+          <t>CWE.PA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENER.MI</t>
+          <t>NRJ.PA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CEC.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TELE.MI</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EMXC.MI</t>
+          <t>EMXC.L</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UTIL.MI</t>
+          <t>UTI.MI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TPXH.MI</t>
+          <t>JPN.PA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TPXH.MI</t>
+          <t>TPXH.PA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>LGQM.DE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AEEM.MI</t>
+          <t>AEMD.DE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AEEM.MI</t>
+          <t>AEME.PA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TPXH.MI</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BNK.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AMEG.MI</t>
+          <t>AMEG.L</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CJ1.MI</t>
+          <t>CJ1.PA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AASI.MI</t>
+          <t>AEJ.PA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CRB.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AASI.MI</t>
+          <t>EMAD.L</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VLUE.MI</t>
+          <t>CV9.PA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BNKE.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AASI.MI</t>
+          <t>APX.PA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WAT.MI</t>
+          <t>WAT.PA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CI2.MI</t>
+          <t>LIGS.DE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FOOD.MI</t>
+          <t>LFOD.DE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EMSR.MI</t>
+          <t>EMSRI.PA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EMES.MI</t>
+          <t>SADM.DE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EPRE.MI</t>
+          <t>EPRE.PA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CN1.MI</t>
+          <t>CN1.PA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CEM.MI</t>
+          <t>MMS.PA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CV9.MI</t>
+          <t>VAL.PA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CEU.MI</t>
+          <t>MEU.PA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CEU.MI</t>
+          <t>CEU2.PA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FMI.MI</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LWCE.MI</t>
+          <t>LWCE.PA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EUPA.MI</t>
+          <t>CEUG.DE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RS2K.MI</t>
+          <t>RS2K.PA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EUPA.MI</t>
+          <t>ESGH.PA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EUPA.MI</t>
+          <t>ESGE.PA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HLT.MI</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MFDD.MI</t>
+          <t>MFDD.L</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QCEU.MI</t>
+          <t>QCEU.PA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CHIP.MI</t>
+          <t>CHIP.SW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FMI.MI</t>
+          <t>FMI.PA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MSE.MI</t>
+          <t>MSE.PA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CMU.MI</t>
+          <t>CMU.PA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CD9.MI</t>
+          <t>DJE.PA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WINC.MI</t>
+          <t>WINC.AS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CG9.MI</t>
+          <t>LGWT.DE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EUPA.MI</t>
+          <t>EUSRI.PA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EPRA.MI</t>
+          <t>MWO.PA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CC1.MI</t>
+          <t>CNAL.L</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EUPA.MI</t>
+          <t>EDSRI.MI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ACWE.MI</t>
+          <t>ACWI.PA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EMI.MI</t>
+          <t>EMI.DE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UINC.MI</t>
+          <t>INCI.AS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WOEE.MI</t>
+          <t>WOEE.AS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WHEA.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>X15E.MI</t>
+          <t>MTE.PA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IFLX.MI</t>
+          <t>IFLX.DE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>IWDA.L</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ECRP.MI</t>
+          <t>CC4.PA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CW8.MI</t>
+          <t>WLDH.PA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ECRP.MI</t>
+          <t>ECRP.PA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CC1.MI</t>
+          <t>CC1.PA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>X710.MI</t>
+          <t>MTDD.DE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>X1G.MI</t>
+          <t>X1G.PA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ECRP.MI</t>
+          <t>CRPX.L</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EGRI.MI</t>
+          <t>EGRI.PA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>X57E.MI</t>
+          <t>X57E.DE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CW8.MI</t>
+          <t>CW8.PA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CW8.MI</t>
+          <t>WLD.PA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AHYE.MI</t>
+          <t>AHYE.PA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GOVA.MI</t>
+          <t>10AL.DE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GGOV.MI</t>
+          <t>EAH.DE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CW8.MI</t>
+          <t>WLDC.PA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CB3.MI</t>
+          <t>CB3.PA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GAGG.MI</t>
+          <t>CLIM.PA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CORP.MI</t>
+          <t>EBBB.PA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CBEF.MI</t>
+          <t>CNB.PA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GHYA.MI</t>
+          <t>GHYU.L</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ELCR.MI</t>
+          <t>ELCR.PA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>500H.MI</t>
+          <t>S500.PA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GOVA.MI</t>
+          <t>EGOV.PA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>X35E.MI</t>
+          <t>EGV5.DE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>X15E.MI</t>
+          <t>E15G.DE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MA35.MI</t>
+          <t>MA35.PA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AM3A.MI</t>
+          <t>AM3A.PA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EFRN.MI</t>
+          <t>EFRN.DE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>USYH.MI</t>
+          <t>LYXE.DE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>X1G.MI</t>
+          <t>X13G.PA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MWRD.MI</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>X13E.MI</t>
+          <t>MTA.PA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MA13.MI</t>
+          <t>MA13.PA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>STHY.MI</t>
+          <t>YIEL.L</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ECRP.MI</t>
+          <t>ECR3.DE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>USYH.MI</t>
+          <t>USHY.L</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FINSW.MI</t>
+          <t>FINSW.PA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>C40.MI</t>
+          <t>CACC.PA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LWCR.MI</t>
+          <t>LWCR.DE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AFLT.MI</t>
+          <t>AFLT.PA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ERNA.MI</t>
+          <t>YCSH.DE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>C3M.MI</t>
+          <t>C3M.PA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CSH.MI</t>
+          <t>CSH.PA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>AGGH.MI</t>
+          <t>GAGG.PA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CORP.MI</t>
+          <t>UBBB.PA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EPRE.MI</t>
+          <t>EPRE.L</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CRB.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>USYH.MI</t>
+          <t>UHYC.L</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AGEB.MI</t>
+          <t>AGEB.PA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>500H.MI</t>
+          <t>500H.PA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LEMB.MI</t>
+          <t>LEMB.L</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>500H.MI</t>
+          <t>500.PA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>USIH.MI</t>
+          <t>USIH.PA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PRAP.MI</t>
+          <t>PRAP.SW</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GGOV.MI</t>
+          <t>GOVH.PA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>USIG.MI</t>
+          <t>USIG.L</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GGOV.MI</t>
+          <t>GGOV.PA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>USIC.MI</t>
+          <t>USIC.L</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CC1.MI</t>
+          <t>LHKG.DE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CC1.MI</t>
+          <t>ASI.PA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>USEE.MI</t>
+          <t>USEE.AS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SADU.MI</t>
+          <t>SADU.PA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CATH.MI</t>
+          <t>WLSC.PA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>INDI.MI</t>
+          <t>INR.PA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>INS.MI</t>
+          <t>LIRU.DE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>INDI.MI</t>
+          <t>CI2.PA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GLUX.MI</t>
+          <t>GLUX.PA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>UST.MI</t>
+          <t>NDXH.PA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>UST.MI</t>
+          <t>UST.PA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DTEC.MI</t>
+          <t>UNIC.L</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>UST.MI</t>
+          <t>UST.PA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>UST.MI</t>
+          <t>ANX.PA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FOOD.MI</t>
+          <t>LTVL.DE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GENY.MI</t>
+          <t>GENY.L</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GOAI.MI</t>
+          <t>GOAI.PA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>INDO.MI</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>WTEC.MI</t>
+          <t>TNOW.PA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DIGE.MI</t>
+          <t>DIGE.L</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>DEFS.PA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PHAU.MI</t>
+          <t>PHAU.L</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PHAG.MI</t>
+          <t>PHAG.L</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>VWRA.L</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IWDP.MI</t>
+          <t>IASP.SW</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IPRP.MI</t>
+          <t>IWDP.SW</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>INRG.SW</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CSCA.MI</t>
+          <t>SXR2.DE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>IQQI.DE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IBTM.MI</t>
+          <t>IBGX.AS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>VHYL.MI</t>
+          <t>VHYL.L</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LTAM.MI</t>
+          <t>LTAM.L</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EMVL.MI</t>
+          <t>EMVL.L</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EMID.MI</t>
+          <t>EMID.L</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>AIGI.MI</t>
+          <t>AIGI.L</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>COPA.MI</t>
+          <t>COPA.L</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ALUM.MI</t>
+          <t>ALUM.L</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ZINC.MI</t>
+          <t>ZINC.L</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MINE.MI</t>
+          <t>COPM.AS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>BATG.MI</t>
+          <t>BATG.L</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>IPRV.MI</t>
+          <t>IDPE.L</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>XLPE.MI</t>
+          <t>XLPE.L</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>XEON.MI</t>
+          <t>XEON.DE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>IEGE.MI</t>
+          <t>DLTM.L</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>IUSE.MI</t>
+          <t>IUSE.L</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IWDE.MI</t>
+          <t>IWDE.L</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O227"/>
+  <dimension ref="A1:O243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ECEA.DE</t>
+          <t>EUEB.DE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -14367,6 +14367,950 @@
       <c r="O227" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>0</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>0XCK.IL</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Multi Units France - Lyxor FTSE Italia Mid Cap PIR</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Azionari Italia</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>FR0011758085</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>0</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>WLDX.MI</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Amundi MSCI World Ex USA Screened UCITS ETF Acc</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Azionari Sviluppati</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>FR0013209921</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>0</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>MAA.PA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Amundi Euro Highest Rated Macro-Weighted Governmen</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Obbligazionari Governo</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Parigi</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>LU1287023342</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>0</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>LU2037748345.SG</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Smart Cities ESG Sc</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Azionari Tematici</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Singapur</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>LU2037748345</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>0</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>IE000LAP5Z18.SG</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Amundi S&amp;P 500 Equal Weight ESG</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Azionari USA</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Singapur</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>IE000LAP5Z18</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>0</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>0E2B.IL</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>LYXOR Index Fund - Lyxor Smart Overnight Return</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Liquidità</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>LU1190417599</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>0</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>XMGA.DE</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Amundi MSCI USA Ex Mega Cap UCITS ETF USD Accumula</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Azionari USA</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Francoforte</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>IE000XL4IXU1</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>0</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>PLAN.PA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Multi Units Luxembourg - Lyxor Corporate Green Bon</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Obbligazionari Corporate</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Parigi</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>LU2370241684</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>0</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>IART.L</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>iShares AI Innovation Active UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Azionari Tematici</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Londra</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>IE000G0E83X3</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>0</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>LU2240851688.SG</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Amundi DAX 50 ESG UCITS ETF - E</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Azionari Europa</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Singapur</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>LU2240851688</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>0</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>LU2109787635.SG</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Amundi Index MSCI EMU SRI PBA U</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Azionari Europa</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Singapur</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>LU2109787635</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>0</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>WATC.SW</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Water UCITS ETF Acc</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Azionari Tematici</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Svizzera</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>FR0014002CH1</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>0</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CSBGU7.SW</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>iShares VII PLC - iShares VII PLC - iShares $ Trea</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Obbligazionari Governo</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Svizzera</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>IE00B3VWN393</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>0</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>LVO.MI</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Amundi S&amp;P 500 VIX Futures Enhanced Roll UCITS ETF</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Azionari Alternativi</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>LU0832435464</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>0</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CSSPX.MI</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Azionari USA</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>IE00B5BMR087</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>0</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>WOEE.DE</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>iShares World Equity Enhanced Active UCITS ETF USD</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Azionari Sviluppati</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Francoforte</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>IE000D8XC064</t>
         </is>
       </c>
     </row>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O243"/>
+  <dimension ref="A1:O241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -14422,7 +14422,6 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
           <t>FR0011758085</t>
@@ -14481,7 +14480,6 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
           <t>FR0013209921</t>
@@ -14540,7 +14538,6 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
           <t>LU1287023342</t>
@@ -14553,27 +14550,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>LU2037748345.SG</t>
+          <t>0E2B.IL</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Amundi MSCI Smart Cities ESG Sc</t>
+          <t>LYXOR Index Fund - Lyxor Smart Overnight Return</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Azionari Tematici</t>
+          <t>Liquidità</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -14599,10 +14596,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
-          <t>LU2037748345</t>
+          <t>LU1190417599</t>
         </is>
       </c>
     </row>
@@ -14612,12 +14608,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IE000LAP5Z18.SG</t>
+          <t>XMGA.DE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Equal Weight ESG</t>
+          <t>Amundi MSCI USA Ex Mega Cap UCITS ETF USD Accumula</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14627,7 +14623,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Francoforte</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -14658,10 +14654,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>IE000LAP5Z18</t>
+          <t>IE000XL4IXU1</t>
         </is>
       </c>
     </row>
@@ -14671,22 +14666,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0E2B.IL</t>
+          <t>PLAN.PA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>LYXOR Index Fund - Lyxor Smart Overnight Return</t>
+          <t>Multi Units Luxembourg - Lyxor Corporate Green Bon</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Liquidità</t>
+          <t>Obbligazionari Corporate</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Parigi</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -14717,10 +14712,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
-          <t>LU1190417599</t>
+          <t>LU2370241684</t>
         </is>
       </c>
     </row>
@@ -14730,22 +14724,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>XMGA.DE</t>
+          <t>IART.L</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Ex Mega Cap UCITS ETF USD Accumula</t>
+          <t>iShares AI Innovation Active UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Azionari USA</t>
+          <t>Azionari Tematici</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Francoforte</t>
+          <t>Londra</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -14776,10 +14770,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr">
         <is>
-          <t>IE000XL4IXU1</t>
+          <t>IE000G0E83X3</t>
         </is>
       </c>
     </row>
@@ -14789,22 +14782,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PLAN.PA</t>
+          <t>EXS1.DE</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Multi Units Luxembourg - Lyxor Corporate Green Bon</t>
+          <t>Amundi DAX 50 ESG UCITS ETF - E</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Obbligazionari Corporate</t>
+          <t>Azionari Europa</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Parigi</t>
+          <t>Singapur</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -14835,10 +14828,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
         <is>
-          <t>LU2370241684</t>
+          <t>LU2240851688</t>
         </is>
       </c>
     </row>
@@ -14848,27 +14840,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>IART.L</t>
+          <t>MSEU.L</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>iShares AI Innovation Active UCITS ETF USD (Acc)</t>
+          <t>Amundi Index MSCI EMU SRI PBA U</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Azionari Tematici</t>
+          <t>Azionari Europa</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Londra</t>
+          <t>Singapur</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -14894,10 +14886,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
         <is>
-          <t>IE000G0E83X3</t>
+          <t>LU2109787635</t>
         </is>
       </c>
     </row>
@@ -14907,22 +14898,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>LU2240851688.SG</t>
+          <t>WATC.SW</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Amundi DAX 50 ESG UCITS ETF - E</t>
+          <t>Amundi MSCI Water UCITS ETF Acc</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Azionari Tematici</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Svizzera</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -14953,10 +14944,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr">
         <is>
-          <t>LU2240851688</t>
+          <t>FR0014002CH1</t>
         </is>
       </c>
     </row>
@@ -14966,27 +14956,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>LU2109787635.SG</t>
+          <t>CSBGU7.SW</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Amundi Index MSCI EMU SRI PBA U</t>
+          <t>iShares VII PLC - iShares VII PLC - iShares $ Trea</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Obbligazionari Governo</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Svizzera</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -15012,10 +15002,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr">
         <is>
-          <t>LU2109787635</t>
+          <t>IE00B3VWN393</t>
         </is>
       </c>
     </row>
@@ -15025,22 +15014,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>WATC.SW</t>
+          <t>LVO.MI</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Amundi MSCI Water UCITS ETF Acc</t>
+          <t>Amundi S&amp;P 500 VIX Futures Enhanced Roll UCITS ETF</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Azionari Tematici</t>
+          <t>Azionari Alternativi</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Svizzera</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -15071,10 +15060,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
         <is>
-          <t>FR0014002CH1</t>
+          <t>LU0832435464</t>
         </is>
       </c>
     </row>
@@ -15084,22 +15072,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>CSBGU7.SW</t>
+          <t>CSSPX.MI</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares VII PLC - iShares $ Trea</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Obbligazionari Governo</t>
+          <t>Azionari USA</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Svizzera</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -15130,10 +15118,9 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr">
         <is>
-          <t>IE00B3VWN393</t>
+          <t>IE00B5BMR087</t>
         </is>
       </c>
     </row>
@@ -15143,27 +15130,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>LVO.MI</t>
+          <t>WOEE.DE</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 VIX Futures Enhanced Roll UCITS ETF</t>
+          <t>iShares World Equity Enhanced Active UCITS ETF USD</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Azionari Alternativi</t>
+          <t>Azionari Sviluppati</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Francoforte</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -15189,126 +15176,7 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr">
-        <is>
-          <t>LU0832435464</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>0</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>CSSPX.MI</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Azionari USA</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G242" t="n">
-        <v>0</v>
-      </c>
-      <c r="H242" t="n">
-        <v>0</v>
-      </c>
-      <c r="I242" t="n">
-        <v>0</v>
-      </c>
-      <c r="J242" t="n">
-        <v>0</v>
-      </c>
-      <c r="K242" t="n">
-        <v>0</v>
-      </c>
-      <c r="L242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>IE00B5BMR087</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>0</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>WOEE.DE</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>iShares World Equity Enhanced Active UCITS ETF USD</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>Azionari Sviluppati</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>Francoforte</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" t="n">
-        <v>0</v>
-      </c>
-      <c r="I243" t="n">
-        <v>0</v>
-      </c>
-      <c r="J243" t="n">
-        <v>0</v>
-      </c>
-      <c r="K243" t="n">
-        <v>0</v>
-      </c>
-      <c r="L243" t="n">
-        <v>0</v>
-      </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr">
         <is>
           <t>IE000D8XC064</t>
         </is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11810,6 +11810,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>IE00BDVWFV31</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -11868,6 +11873,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>IE00B0M63284</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -11926,6 +11936,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>IE00BWXC8680</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -11984,6 +11999,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>IE00B0M63912</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -12042,6 +12062,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>IE00B0M63961</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -12100,6 +12125,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>IE00B0M63507</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -12156,6 +12186,11 @@
       <c r="N186" t="inlineStr">
         <is>
           <t>2026-06-03 20:09</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>IE00BVXVFY75</t>
         </is>
       </c>
     </row>
@@ -12216,6 +12251,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>IE00B0M63284</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -12335,6 +12375,11 @@
       <c r="N189" t="inlineStr">
         <is>
           <t>2026-06-03 20:09</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>IE00BFXR5895</t>
         </is>
       </c>
     </row>
@@ -12521,6 +12566,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>DE000A0Q4MJ7</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -12579,6 +12629,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>DE000A0QLW44</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -12700,6 +12755,11 @@
           <t>2026-06-03 20:09</t>
         </is>
       </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>IE00BMDX3P59</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
@@ -12819,6 +12879,11 @@
       <c r="N197" t="inlineStr">
         <is>
           <t>2026-06-03 20:09</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>IE00BYPMDN47</t>
         </is>
       </c>
     </row>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -3250,7 +3250,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -12322,7 +12322,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -12322,7 +12322,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -730,7 +730,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WAT.PA</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-03 20:09</t>
+          <t>2026-07-07 15:43</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>UHYC.L</t>
+          <t>USHYC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Amundi IS USD HY Corp. Bond ESG UCITS ETF Acc</t>
+          <t>AMUNDI USD HIGH YIELD CORPORATE BOND ESG</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>11.906</v>
+        <v>10.502</v>
       </c>
       <c r="H130" t="n">
         <v>12.5815</v>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-06-03 20:09</t>
+          <t>2026-07-07 15:51</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>WAT.PA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,9 +2646,6 @@
         <is>
           <t>EUR</t>
         </is>
-      </c>
-      <c r="G35" t="n">
-        <v>66.723</v>
       </c>
       <c r="H35" t="n">
         <v>67.0294</v>
@@ -2672,7 +2669,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-07 15:43</t>
+          <t>2026-07-07 15:53</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,7 +541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -13390,7 +13390,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -13390,7 +13390,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -541,7 +541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -541,7 +541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -541,7 +541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -541,7 +541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -541,7 +541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -730,7 +730,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O241"/>
+  <dimension ref="A1:O237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,19 +572,19 @@
         <v>159.94</v>
       </c>
       <c r="H2" t="n">
-        <v>162.9143</v>
+        <v>162.5284</v>
       </c>
       <c r="I2" t="n">
-        <v>179.0061</v>
+        <v>178.045</v>
       </c>
       <c r="J2" t="n">
-        <v>45.6</v>
+        <v>45.2</v>
       </c>
       <c r="K2" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4549</v>
+        <v>1.6006</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -635,19 +635,19 @@
         <v>49.275</v>
       </c>
       <c r="H3" t="n">
-        <v>48.9777</v>
+        <v>48.9867</v>
       </c>
       <c r="I3" t="n">
-        <v>49.6305</v>
+        <v>50.0463</v>
       </c>
       <c r="J3" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>13.8</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0001</v>
+        <v>0.016</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -698,19 +698,19 @@
         <v>140.54</v>
       </c>
       <c r="H4" t="n">
-        <v>133.8276</v>
+        <v>133.5105</v>
       </c>
       <c r="I4" t="n">
-        <v>134.5908</v>
+        <v>131.3212</v>
       </c>
       <c r="J4" t="n">
-        <v>64.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5657</v>
+        <v>1.4364</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -761,19 +761,19 @@
         <v>2.931</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8578</v>
+        <v>2.8624</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7601</v>
+        <v>2.7975</v>
       </c>
       <c r="J5" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="K5" t="n">
-        <v>21.7</v>
+        <v>23.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0068</v>
+        <v>0.0102</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -824,19 +824,19 @@
         <v>25.32</v>
       </c>
       <c r="H6" t="n">
-        <v>25.4514</v>
+        <v>25.4537</v>
       </c>
       <c r="I6" t="n">
-        <v>24.8008</v>
+        <v>24.9004</v>
       </c>
       <c r="J6" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="K6" t="n">
-        <v>21.4</v>
+        <v>18.1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0516</v>
+        <v>-0.0609</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -887,19 +887,19 @@
         <v>209.15</v>
       </c>
       <c r="H7" t="n">
-        <v>201.9936</v>
+        <v>201.8023</v>
       </c>
       <c r="I7" t="n">
-        <v>201.0574</v>
+        <v>198.828</v>
       </c>
       <c r="J7" t="n">
-        <v>66.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>25.2</v>
+        <v>19.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4618</v>
+        <v>1.3952</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -950,19 +950,19 @@
         <v>499.85</v>
       </c>
       <c r="H8" t="n">
-        <v>501.842</v>
+        <v>502.295</v>
       </c>
       <c r="I8" t="n">
-        <v>485.093</v>
+        <v>484.578</v>
       </c>
       <c r="J8" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="K8" t="n">
-        <v>21.7</v>
+        <v>33.8</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.8694</v>
+        <v>-2.846</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1013,19 +1013,19 @@
         <v>42.72</v>
       </c>
       <c r="H9" t="n">
-        <v>42.5963</v>
+        <v>42.5591</v>
       </c>
       <c r="I9" t="n">
-        <v>44.3056</v>
+        <v>44.4363</v>
       </c>
       <c r="J9" t="n">
         <v>48.6</v>
       </c>
       <c r="K9" t="n">
-        <v>17.2</v>
+        <v>22.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2228</v>
+        <v>0.2385</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1076,19 +1076,19 @@
         <v>106.16</v>
       </c>
       <c r="H10" t="n">
-        <v>104.9037</v>
+        <v>104.8416</v>
       </c>
       <c r="I10" t="n">
-        <v>103.1327</v>
+        <v>102.166</v>
       </c>
       <c r="J10" t="n">
-        <v>55.8</v>
+        <v>57.2</v>
       </c>
       <c r="K10" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0326</v>
+        <v>-0.0454</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1139,19 +1139,19 @@
         <v>47.385</v>
       </c>
       <c r="H11" t="n">
-        <v>45.8768</v>
+        <v>45.8944</v>
       </c>
       <c r="I11" t="n">
-        <v>44.4235</v>
+        <v>44.4644</v>
       </c>
       <c r="J11" t="n">
-        <v>69.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K11" t="n">
-        <v>28.1</v>
+        <v>29.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1677</v>
+        <v>0.1818</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1202,19 +1202,19 @@
         <v>52.51</v>
       </c>
       <c r="H12" t="n">
-        <v>52.1634</v>
+        <v>52.0314</v>
       </c>
       <c r="I12" t="n">
-        <v>53.9115</v>
+        <v>52.7566</v>
       </c>
       <c r="J12" t="n">
-        <v>50.4</v>
+        <v>52.1</v>
       </c>
       <c r="K12" t="n">
-        <v>16.6</v>
+        <v>19.7</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2538</v>
+        <v>0.189</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1265,19 +1265,19 @@
         <v>39.21</v>
       </c>
       <c r="H13" t="n">
-        <v>39.3715</v>
+        <v>39.3615</v>
       </c>
       <c r="I13" t="n">
-        <v>40.7767</v>
+        <v>41.0084</v>
       </c>
       <c r="J13" t="n">
-        <v>47.6</v>
+        <v>46.9</v>
       </c>
       <c r="K13" t="n">
-        <v>16.8</v>
+        <v>17.8</v>
       </c>
       <c r="L13" t="n">
-        <v>0.157</v>
+        <v>0.194</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1328,19 +1328,19 @@
         <v>103.78</v>
       </c>
       <c r="H14" t="n">
-        <v>104.486</v>
+        <v>104.5729</v>
       </c>
       <c r="I14" t="n">
-        <v>103.9554</v>
+        <v>104.7524</v>
       </c>
       <c r="J14" t="n">
-        <v>45.9</v>
+        <v>44.4</v>
       </c>
       <c r="K14" t="n">
-        <v>13.2</v>
+        <v>15.1</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2743</v>
+        <v>-0.2331</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1391,19 +1391,19 @@
         <v>220.64</v>
       </c>
       <c r="H15" t="n">
-        <v>215.6379</v>
+        <v>215.758</v>
       </c>
       <c r="I15" t="n">
-        <v>214.0142</v>
+        <v>215.5216</v>
       </c>
       <c r="J15" t="n">
-        <v>61.3</v>
+        <v>61.7</v>
       </c>
       <c r="K15" t="n">
-        <v>10.2</v>
+        <v>12.9</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.9101</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1454,19 +1454,19 @@
         <v>623.03</v>
       </c>
       <c r="H16" t="n">
-        <v>613.093</v>
+        <v>613.4462</v>
       </c>
       <c r="I16" t="n">
-        <v>610.8652</v>
+        <v>614.4682</v>
       </c>
       <c r="J16" t="n">
         <v>57.5</v>
       </c>
       <c r="K16" t="n">
-        <v>8.9</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9606</v>
+        <v>1.3115</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1517,19 +1517,19 @@
         <v>15.008</v>
       </c>
       <c r="H17" t="n">
-        <v>14.4361</v>
+        <v>14.4265</v>
       </c>
       <c r="I17" t="n">
-        <v>14.4872</v>
+        <v>14.3818</v>
       </c>
       <c r="J17" t="n">
-        <v>62.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>21.8</v>
+        <v>17.9</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1193</v>
+        <v>0.1145</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1580,19 +1580,19 @@
         <v>72.994</v>
       </c>
       <c r="H18" t="n">
-        <v>72.8779</v>
+        <v>72.8548</v>
       </c>
       <c r="I18" t="n">
-        <v>74.553</v>
+        <v>74.703</v>
       </c>
       <c r="J18" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="K18" t="n">
-        <v>17.2</v>
+        <v>15.1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2665</v>
+        <v>0.3068</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1643,19 +1643,19 @@
         <v>98.90000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>98.76220000000001</v>
+        <v>98.7308</v>
       </c>
       <c r="I19" t="n">
-        <v>101.0454</v>
+        <v>101.2544</v>
       </c>
       <c r="J19" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="K19" t="n">
-        <v>13.6</v>
+        <v>15</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3569</v>
+        <v>0.4118</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1706,19 +1706,19 @@
         <v>7.492</v>
       </c>
       <c r="H20" t="n">
-        <v>7.4793</v>
+        <v>7.4768</v>
       </c>
       <c r="I20" t="n">
-        <v>7.6557</v>
+        <v>7.6716</v>
       </c>
       <c r="J20" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="K20" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0284</v>
+        <v>0.0323</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1769,19 +1769,19 @@
         <v>150.13</v>
       </c>
       <c r="H21" t="n">
-        <v>146.6119</v>
+        <v>146.6907</v>
       </c>
       <c r="I21" t="n">
-        <v>145.4245</v>
+        <v>146.4499</v>
       </c>
       <c r="J21" t="n">
-        <v>61.6</v>
+        <v>62</v>
       </c>
       <c r="K21" t="n">
-        <v>10.4</v>
+        <v>13.1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5389</v>
+        <v>0.6281</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1832,19 +1832,19 @@
         <v>74.83</v>
       </c>
       <c r="H22" t="n">
-        <v>72.86020000000001</v>
+        <v>72.9843</v>
       </c>
       <c r="I22" t="n">
-        <v>69.7089</v>
+        <v>70.9622</v>
       </c>
       <c r="J22" t="n">
-        <v>64.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>21.7</v>
+        <v>26.5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1201</v>
+        <v>0.2137</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1895,19 +1895,19 @@
         <v>7.189</v>
       </c>
       <c r="H23" t="n">
-        <v>7.1905</v>
+        <v>7.1877</v>
       </c>
       <c r="I23" t="n">
-        <v>7.3746</v>
+        <v>7.3886</v>
       </c>
       <c r="J23" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="K23" t="n">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0259</v>
+        <v>0.0301</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2021,19 +2021,19 @@
         <v>359.51</v>
       </c>
       <c r="H25" t="n">
-        <v>353.9907</v>
+        <v>354.2401</v>
       </c>
       <c r="I25" t="n">
-        <v>354.2514</v>
+        <v>357.9028</v>
       </c>
       <c r="J25" t="n">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="K25" t="n">
-        <v>10.7</v>
+        <v>13.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.0989</v>
+        <v>1.4257</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2084,19 +2084,19 @@
         <v>97.68000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>97.5899</v>
+        <v>97.56180000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>99.54600000000001</v>
+        <v>99.76739999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="K26" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3075</v>
+        <v>0.3603</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2147,19 +2147,19 @@
         <v>35.32</v>
       </c>
       <c r="H27" t="n">
-        <v>34.7911</v>
+        <v>34.7432</v>
       </c>
       <c r="I27" t="n">
-        <v>34.6856</v>
+        <v>34.0601</v>
       </c>
       <c r="J27" t="n">
-        <v>56.5</v>
+        <v>58.7</v>
       </c>
       <c r="K27" t="n">
-        <v>14.6</v>
+        <v>20.7</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0118</v>
+        <v>-0.0329</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2210,19 +2210,19 @@
         <v>124.15</v>
       </c>
       <c r="H28" t="n">
-        <v>124.1713</v>
+        <v>124.0728</v>
       </c>
       <c r="I28" t="n">
-        <v>128.4485</v>
+        <v>128.2117</v>
       </c>
       <c r="J28" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="K28" t="n">
-        <v>12.6</v>
+        <v>16.9</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6438</v>
+        <v>0.6912</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2273,19 +2273,19 @@
         <v>58.07</v>
       </c>
       <c r="H29" t="n">
-        <v>56.3641</v>
+        <v>56.3533</v>
       </c>
       <c r="I29" t="n">
-        <v>55.3494</v>
+        <v>55.3324</v>
       </c>
       <c r="J29" t="n">
-        <v>70.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>18.6</v>
+        <v>24.5</v>
       </c>
       <c r="L29" t="n">
-        <v>0.22</v>
+        <v>0.2215</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2336,19 +2336,19 @@
         <v>478.3</v>
       </c>
       <c r="H30" t="n">
-        <v>471.5029</v>
+        <v>471.9337</v>
       </c>
       <c r="I30" t="n">
-        <v>458.9154</v>
+        <v>462.61</v>
       </c>
       <c r="J30" t="n">
-        <v>71.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>41.7</v>
+        <v>34.2</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1324</v>
+        <v>0.4038</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2399,19 +2399,19 @@
         <v>402.85</v>
       </c>
       <c r="H31" t="n">
-        <v>388.01</v>
+        <v>388.697</v>
       </c>
       <c r="I31" t="n">
-        <v>370.8578</v>
+        <v>378.052</v>
       </c>
       <c r="J31" t="n">
-        <v>68.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>21.5</v>
+        <v>26.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4511</v>
+        <v>1.9985</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2462,19 +2462,19 @@
         <v>25.075</v>
       </c>
       <c r="H32" t="n">
-        <v>24.4749</v>
+        <v>24.4763</v>
       </c>
       <c r="I32" t="n">
-        <v>23.7894</v>
+        <v>23.794</v>
       </c>
       <c r="J32" t="n">
-        <v>74.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>40.4</v>
+        <v>43.4</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0667</v>
+        <v>0.0702</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2525,19 +2525,19 @@
         <v>193.9</v>
       </c>
       <c r="H33" t="n">
-        <v>194.3383</v>
+        <v>194.2662</v>
       </c>
       <c r="I33" t="n">
-        <v>199.4354</v>
+        <v>199.9116</v>
       </c>
       <c r="J33" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="K33" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6676</v>
+        <v>0.7875</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2588,19 +2588,19 @@
         <v>7.419</v>
       </c>
       <c r="H34" t="n">
-        <v>7.4329</v>
+        <v>7.4296</v>
       </c>
       <c r="I34" t="n">
-        <v>7.6427</v>
+        <v>7.6523</v>
       </c>
       <c r="J34" t="n">
-        <v>48.3</v>
+        <v>47.9</v>
       </c>
       <c r="K34" t="n">
-        <v>10.6</v>
+        <v>15.1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0252</v>
+        <v>0.03</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2651,19 +2651,19 @@
         <v>72.14</v>
       </c>
       <c r="H35" t="n">
-        <v>70.9495</v>
+        <v>71.0098</v>
       </c>
       <c r="I35" t="n">
-        <v>69.6751</v>
+        <v>70.4986</v>
       </c>
       <c r="J35" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
       <c r="K35" t="n">
-        <v>22.3</v>
+        <v>15.7</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1318</v>
+        <v>0.1796</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2714,19 +2714,19 @@
         <v>158.06</v>
       </c>
       <c r="H36" t="n">
-        <v>153.8368</v>
+        <v>153.9353</v>
       </c>
       <c r="I36" t="n">
-        <v>151.3416</v>
+        <v>152.3692</v>
       </c>
       <c r="J36" t="n">
-        <v>65.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="K36" t="n">
-        <v>21</v>
+        <v>22.7</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8255</v>
+        <v>0.9071</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2777,19 +2777,19 @@
         <v>96.95</v>
       </c>
       <c r="H37" t="n">
-        <v>96.9607</v>
+        <v>97.0891</v>
       </c>
       <c r="I37" t="n">
-        <v>95.1538</v>
+        <v>96.3214</v>
       </c>
       <c r="J37" t="n">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>13</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.2137</v>
+        <v>-0.1473</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2840,19 +2840,19 @@
         <v>69.41</v>
       </c>
       <c r="H38" t="n">
-        <v>68.8563</v>
+        <v>68.86620000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>69.92740000000001</v>
+        <v>70.3866</v>
       </c>
       <c r="J38" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="K38" t="n">
-        <v>15.2</v>
+        <v>12.9</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2468</v>
+        <v>0.301</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2903,19 +2903,19 @@
         <v>69.41</v>
       </c>
       <c r="H39" t="n">
-        <v>68.9645</v>
+        <v>68.9303</v>
       </c>
       <c r="I39" t="n">
-        <v>70.4962</v>
+        <v>70.5958</v>
       </c>
       <c r="J39" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="K39" t="n">
         <v>16.1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3249</v>
+        <v>0.341</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2966,19 +2966,19 @@
         <v>345.45</v>
       </c>
       <c r="H40" t="n">
-        <v>344.945</v>
+        <v>345.2244</v>
       </c>
       <c r="I40" t="n">
-        <v>337.5376</v>
+        <v>340.259</v>
       </c>
       <c r="J40" t="n">
-        <v>53.5</v>
+        <v>52.9</v>
       </c>
       <c r="K40" t="n">
-        <v>17.7</v>
+        <v>20.2</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3639</v>
+        <v>-0.2146</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3029,19 +3029,19 @@
         <v>720.1</v>
       </c>
       <c r="H41" t="n">
-        <v>711.9391000000001</v>
+        <v>712.1966</v>
       </c>
       <c r="I41" t="n">
-        <v>704.794</v>
+        <v>705.748</v>
       </c>
       <c r="J41" t="n">
-        <v>60</v>
+        <v>61.1</v>
       </c>
       <c r="K41" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7055</v>
+        <v>0.8114</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3092,19 +3092,19 @@
         <v>448.35</v>
       </c>
       <c r="H42" t="n">
-        <v>442.6781</v>
+        <v>442.6334</v>
       </c>
       <c r="I42" t="n">
-        <v>441.3632</v>
+        <v>441.066</v>
       </c>
       <c r="J42" t="n">
-        <v>61.8</v>
+        <v>63.3</v>
       </c>
       <c r="K42" t="n">
-        <v>21.5</v>
+        <v>17.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.2187</v>
+        <v>1.2923</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3155,19 +3155,19 @@
         <v>197.44</v>
       </c>
       <c r="H43" t="n">
-        <v>193.9155</v>
+        <v>194.0736</v>
       </c>
       <c r="I43" t="n">
-        <v>188.9752</v>
+        <v>190.5228</v>
       </c>
       <c r="J43" t="n">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="K43" t="n">
-        <v>35.7</v>
+        <v>28.4</v>
       </c>
       <c r="L43" t="n">
-        <v>0.295</v>
+        <v>0.4152</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3218,19 +3218,19 @@
         <v>251.95</v>
       </c>
       <c r="H44" t="n">
-        <v>247.8356</v>
+        <v>248.0287</v>
       </c>
       <c r="I44" t="n">
-        <v>244.1108</v>
+        <v>245.822</v>
       </c>
       <c r="J44" t="n">
-        <v>67.7</v>
+        <v>68.7</v>
       </c>
       <c r="K44" t="n">
-        <v>28.2</v>
+        <v>20.2</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4094</v>
+        <v>0.5596</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3281,19 +3281,19 @@
         <v>126.68</v>
       </c>
       <c r="H45" t="n">
-        <v>124.6201</v>
+        <v>124.7188</v>
       </c>
       <c r="I45" t="n">
-        <v>122.724</v>
+        <v>123.6012</v>
       </c>
       <c r="J45" t="n">
-        <v>66.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>25.3</v>
+        <v>19.7</v>
       </c>
       <c r="L45" t="n">
-        <v>0.1941</v>
+        <v>0.2704</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3344,19 +3344,19 @@
         <v>55.07</v>
       </c>
       <c r="H46" t="n">
-        <v>53.849</v>
+        <v>53.8933</v>
       </c>
       <c r="I46" t="n">
-        <v>53.062</v>
+        <v>53.4528</v>
       </c>
       <c r="J46" t="n">
-        <v>64.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>14.6</v>
+        <v>17.7</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1589</v>
+        <v>0.2012</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3407,19 +3407,19 @@
         <v>99.65000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>98.139</v>
+        <v>98.20489999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>97.0538</v>
+        <v>97.75839999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>65.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>24.5</v>
+        <v>18.1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1807</v>
+        <v>0.2429</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3470,19 +3470,19 @@
         <v>453</v>
       </c>
       <c r="H48" t="n">
-        <v>445.6488</v>
+        <v>445.9883</v>
       </c>
       <c r="I48" t="n">
-        <v>439.061</v>
+        <v>442.12</v>
       </c>
       <c r="J48" t="n">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="K48" t="n">
-        <v>26.1</v>
+        <v>20.1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7013</v>
+        <v>0.9779</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3533,19 +3533,19 @@
         <v>391.4</v>
       </c>
       <c r="H49" t="n">
-        <v>389.4834</v>
+        <v>389.8288</v>
       </c>
       <c r="I49" t="n">
-        <v>387.7556</v>
+        <v>392.5368</v>
       </c>
       <c r="J49" t="n">
-        <v>53.5</v>
+        <v>52.3</v>
       </c>
       <c r="K49" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="L49" t="n">
-        <v>0.352</v>
+        <v>0.7624</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3596,19 +3596,19 @@
         <v>6.851</v>
       </c>
       <c r="H50" t="n">
-        <v>6.7321</v>
+        <v>6.737</v>
       </c>
       <c r="I50" t="n">
-        <v>6.6323</v>
+        <v>6.6779</v>
       </c>
       <c r="J50" t="n">
-        <v>67.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K50" t="n">
-        <v>26.9</v>
+        <v>19.5</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0121</v>
+        <v>0.0161</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3659,19 +3659,19 @@
         <v>31.265</v>
       </c>
       <c r="H51" t="n">
-        <v>30.9701</v>
+        <v>30.9954</v>
       </c>
       <c r="I51" t="n">
-        <v>30.7152</v>
+        <v>30.9611</v>
       </c>
       <c r="J51" t="n">
-        <v>60.4</v>
+        <v>59.8</v>
       </c>
       <c r="K51" t="n">
-        <v>25.3</v>
+        <v>15.3</v>
       </c>
       <c r="L51" t="n">
-        <v>0.0214</v>
+        <v>0.0447</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3722,19 +3722,19 @@
         <v>42.85</v>
       </c>
       <c r="H52" t="n">
-        <v>42.461</v>
+        <v>42.4977</v>
       </c>
       <c r="I52" t="n">
-        <v>42.1222</v>
+        <v>42.4747</v>
       </c>
       <c r="J52" t="n">
-        <v>59.3</v>
+        <v>58.7</v>
       </c>
       <c r="K52" t="n">
-        <v>16.8</v>
+        <v>13.1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.029</v>
+        <v>0.062</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3785,19 +3785,19 @@
         <v>155.4</v>
       </c>
       <c r="H53" t="n">
-        <v>154.2213</v>
+        <v>154.4778</v>
       </c>
       <c r="I53" t="n">
-        <v>152.7365</v>
+        <v>154.8696</v>
       </c>
       <c r="J53" t="n">
-        <v>53.6</v>
+        <v>52.6</v>
       </c>
       <c r="K53" t="n">
-        <v>11.4</v>
+        <v>16.7</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.2586</v>
+        <v>-0.1338</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3848,19 +3848,19 @@
         <v>132.9</v>
       </c>
       <c r="H54" t="n">
-        <v>129.9572</v>
+        <v>130.0673</v>
       </c>
       <c r="I54" t="n">
-        <v>128.8304</v>
+        <v>129.8708</v>
       </c>
       <c r="J54" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="K54" t="n">
-        <v>15.1</v>
+        <v>16.2</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4219</v>
+        <v>0.541</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3911,19 +3911,19 @@
         <v>127.42</v>
       </c>
       <c r="H55" t="n">
-        <v>125.0405</v>
+        <v>125.1567</v>
       </c>
       <c r="I55" t="n">
-        <v>123.42</v>
+        <v>124.498</v>
       </c>
       <c r="J55" t="n">
-        <v>66.2</v>
+        <v>66.5</v>
       </c>
       <c r="K55" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2573</v>
+        <v>0.3404</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -3974,19 +3974,19 @@
         <v>110.54</v>
       </c>
       <c r="H56" t="n">
-        <v>109.1627</v>
+        <v>109.1056</v>
       </c>
       <c r="I56" t="n">
-        <v>113.4792</v>
+        <v>114.1372</v>
       </c>
       <c r="J56" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="K56" t="n">
-        <v>16.6</v>
+        <v>14.4</v>
       </c>
       <c r="L56" t="n">
-        <v>0.6337</v>
+        <v>0.7703</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4037,19 +4037,19 @@
         <v>132.56</v>
       </c>
       <c r="H57" t="n">
-        <v>129.8798</v>
+        <v>129.9891</v>
       </c>
       <c r="I57" t="n">
-        <v>128.808</v>
+        <v>129.8384</v>
       </c>
       <c r="J57" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="K57" t="n">
-        <v>14</v>
+        <v>17.1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4104</v>
+        <v>0.5285</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4100,19 +4100,19 @@
         <v>74.23999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>72.4312</v>
+        <v>72.4902</v>
       </c>
       <c r="I58" t="n">
-        <v>71.2102</v>
+        <v>71.754</v>
       </c>
       <c r="J58" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="K58" t="n">
-        <v>18.6</v>
+        <v>19.2</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2435</v>
+        <v>0.2984</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4163,19 +4163,19 @@
         <v>43.79</v>
       </c>
       <c r="H59" t="n">
-        <v>42.6026</v>
+        <v>42.627</v>
       </c>
       <c r="I59" t="n">
-        <v>42.0487</v>
+        <v>42.293</v>
       </c>
       <c r="J59" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="K59" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1703</v>
+        <v>0.2014</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4226,19 +4226,19 @@
         <v>429.65</v>
       </c>
       <c r="H60" t="n">
-        <v>421.396</v>
+        <v>421.6612</v>
       </c>
       <c r="I60" t="n">
-        <v>418.579</v>
+        <v>421.192</v>
       </c>
       <c r="J60" t="n">
-        <v>64.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="L60" t="n">
-        <v>1.1789</v>
+        <v>1.5525</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4289,19 +4289,19 @@
         <v>473.85</v>
       </c>
       <c r="H61" t="n">
-        <v>467.2303</v>
+        <v>467.7272</v>
       </c>
       <c r="I61" t="n">
-        <v>460.735</v>
+        <v>465.156</v>
       </c>
       <c r="J61" t="n">
-        <v>59.1</v>
+        <v>58.4</v>
       </c>
       <c r="K61" t="n">
-        <v>24.8</v>
+        <v>19.1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.8747</v>
+        <v>1.279</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4352,19 +4352,19 @@
         <v>5.171</v>
       </c>
       <c r="H62" t="n">
-        <v>5.0991</v>
+        <v>5.1093</v>
       </c>
       <c r="I62" t="n">
-        <v>5.0287</v>
+        <v>5.0897</v>
       </c>
       <c r="J62" t="n">
-        <v>62.2</v>
+        <v>55.8</v>
       </c>
       <c r="K62" t="n">
-        <v>16.9</v>
+        <v>5.3</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0058</v>
+        <v>0.0107</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4415,19 +4415,19 @@
         <v>220.05</v>
       </c>
       <c r="H63" t="n">
-        <v>216.1843</v>
+        <v>216.32</v>
       </c>
       <c r="I63" t="n">
-        <v>215.543</v>
+        <v>216.77</v>
       </c>
       <c r="J63" t="n">
-        <v>62.2</v>
+        <v>62.7</v>
       </c>
       <c r="K63" t="n">
-        <v>19.4</v>
+        <v>16.5</v>
       </c>
       <c r="L63" t="n">
-        <v>0.6213</v>
+        <v>0.7613</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4478,19 +4478,19 @@
         <v>93.3</v>
       </c>
       <c r="H64" t="n">
-        <v>92.0971</v>
+        <v>92.158</v>
       </c>
       <c r="I64" t="n">
-        <v>91.5544</v>
+        <v>92.1114</v>
       </c>
       <c r="J64" t="n">
         <v>61</v>
       </c>
       <c r="K64" t="n">
-        <v>17.2</v>
+        <v>16.2</v>
       </c>
       <c r="L64" t="n">
-        <v>0.1797</v>
+        <v>0.2357</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4541,19 +4541,19 @@
         <v>43.235</v>
       </c>
       <c r="H65" t="n">
-        <v>43.8125</v>
+        <v>43.8489</v>
       </c>
       <c r="I65" t="n">
-        <v>43.1859</v>
+        <v>43.5144</v>
       </c>
       <c r="J65" t="n">
-        <v>41.8</v>
+        <v>39.3</v>
       </c>
       <c r="K65" t="n">
-        <v>22.1</v>
+        <v>23.6</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.2049</v>
+        <v>-0.1841</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4604,19 +4604,19 @@
         <v>173.65</v>
       </c>
       <c r="H66" t="n">
-        <v>171.546</v>
+        <v>171.5135</v>
       </c>
       <c r="I66" t="n">
-        <v>175.4274</v>
+        <v>176.8936</v>
       </c>
       <c r="J66" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="K66" t="n">
-        <v>13.4</v>
+        <v>11.1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5168</v>
+        <v>0.6687</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4730,19 +4730,19 @@
         <v>611.17</v>
       </c>
       <c r="H68" t="n">
-        <v>601.6184</v>
+        <v>601.8444</v>
       </c>
       <c r="I68" t="n">
-        <v>598.3737</v>
+        <v>600.3972</v>
       </c>
       <c r="J68" t="n">
-        <v>62.3</v>
+        <v>62.9</v>
       </c>
       <c r="K68" t="n">
-        <v>14.6</v>
+        <v>16.8</v>
       </c>
       <c r="L68" t="n">
-        <v>1.5484</v>
+        <v>1.8215</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -4856,19 +4856,19 @@
         <v>5.2056</v>
       </c>
       <c r="H70" t="n">
-        <v>5.2028</v>
+        <v>5.2034</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2088</v>
+        <v>5.2171</v>
       </c>
       <c r="J70" t="n">
-        <v>51.2</v>
+        <v>50.2</v>
       </c>
       <c r="K70" t="n">
-        <v>17.7</v>
+        <v>21.7</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0025</v>
+        <v>0.0032</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -4916,22 +4916,22 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6.254</v>
+        <v>6.272</v>
       </c>
       <c r="H71" t="n">
-        <v>6.1468</v>
+        <v>6.1587</v>
       </c>
       <c r="I71" t="n">
-        <v>6.085</v>
+        <v>6.0901</v>
       </c>
       <c r="J71" t="n">
-        <v>63.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0122</v>
+        <v>0.0141</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -4982,19 +4982,19 @@
         <v>153.43</v>
       </c>
       <c r="H72" t="n">
-        <v>153.2584</v>
+        <v>153.2602</v>
       </c>
       <c r="I72" t="n">
-        <v>153.9964</v>
+        <v>154.3848</v>
       </c>
       <c r="J72" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="K72" t="n">
-        <v>21.5</v>
+        <v>23.6</v>
       </c>
       <c r="L72" t="n">
-        <v>0.1855</v>
+        <v>0.2193</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5045,19 +5045,19 @@
         <v>512.6799999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>508.8184</v>
+        <v>509.925</v>
       </c>
       <c r="I73" t="n">
-        <v>497.5632</v>
+        <v>505.0452</v>
       </c>
       <c r="J73" t="n">
-        <v>55.3</v>
+        <v>53.7</v>
       </c>
       <c r="K73" t="n">
-        <v>14.8</v>
+        <v>18.4</v>
       </c>
       <c r="L73" t="n">
-        <v>-1.3772</v>
+        <v>-0.8294</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5108,19 +5108,19 @@
         <v>199.85</v>
       </c>
       <c r="H74" t="n">
-        <v>199.794</v>
+        <v>199.7858</v>
       </c>
       <c r="I74" t="n">
-        <v>200.8926</v>
+        <v>201.3802</v>
       </c>
       <c r="J74" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="K74" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2126</v>
+        <v>0.2566</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5171,19 +5171,19 @@
         <v>4.9561</v>
       </c>
       <c r="H75" t="n">
-        <v>4.941</v>
+        <v>4.945</v>
       </c>
       <c r="I75" t="n">
-        <v>4.9444</v>
+        <v>4.966</v>
       </c>
       <c r="J75" t="n">
-        <v>55.3</v>
+        <v>51.5</v>
       </c>
       <c r="K75" t="n">
-        <v>19.7</v>
+        <v>5.6</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0019</v>
+        <v>0.0034</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5234,19 +5234,19 @@
         <v>128.32</v>
       </c>
       <c r="H76" t="n">
-        <v>126.049</v>
+        <v>126.1132</v>
       </c>
       <c r="I76" t="n">
-        <v>124.8384</v>
+        <v>125.3218</v>
       </c>
       <c r="J76" t="n">
-        <v>64.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="K76" t="n">
-        <v>16.5</v>
+        <v>18.1</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3066</v>
+        <v>0.3641</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5297,19 +5297,19 @@
         <v>229.34</v>
       </c>
       <c r="H77" t="n">
-        <v>228.35</v>
+        <v>228.3666</v>
       </c>
       <c r="I77" t="n">
-        <v>228.5411</v>
+        <v>228.8394</v>
       </c>
       <c r="J77" t="n">
-        <v>61.5</v>
+        <v>62</v>
       </c>
       <c r="K77" t="n">
-        <v>19.6</v>
+        <v>23.3</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2025</v>
+        <v>0.2324</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5360,19 +5360,19 @@
         <v>14.208</v>
       </c>
       <c r="H78" t="n">
-        <v>13.8195</v>
+        <v>13.858</v>
       </c>
       <c r="I78" t="n">
-        <v>13.6519</v>
+        <v>13.6846</v>
       </c>
       <c r="J78" t="n">
-        <v>70</v>
+        <v>71.7</v>
       </c>
       <c r="K78" t="n">
-        <v>62</v>
+        <v>19.4</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0527</v>
+        <v>0.0567</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5423,19 +5423,19 @@
         <v>269.1</v>
       </c>
       <c r="H79" t="n">
-        <v>263.8421</v>
+        <v>263.9074</v>
       </c>
       <c r="I79" t="n">
-        <v>261.711</v>
+        <v>261.873</v>
       </c>
       <c r="J79" t="n">
-        <v>65.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>17.7</v>
+        <v>19.9</v>
       </c>
       <c r="L79" t="n">
-        <v>0.8949</v>
+        <v>0.9585</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -5486,19 +5486,19 @@
         <v>54.33</v>
       </c>
       <c r="H80" t="n">
-        <v>54.2899</v>
+        <v>54.2933</v>
       </c>
       <c r="I80" t="n">
-        <v>54.3613</v>
+        <v>54.4308</v>
       </c>
       <c r="J80" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="K80" t="n">
-        <v>21</v>
+        <v>18.1</v>
       </c>
       <c r="L80" t="n">
-        <v>0.0293</v>
+        <v>0.0363</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -5549,19 +5549,19 @@
         <v>280.45</v>
       </c>
       <c r="H81" t="n">
-        <v>276.5246</v>
+        <v>276.1585</v>
       </c>
       <c r="I81" t="n">
-        <v>281.351</v>
+        <v>279.312</v>
       </c>
       <c r="J81" t="n">
-        <v>54.8</v>
+        <v>56.8</v>
       </c>
       <c r="K81" t="n">
-        <v>12.4</v>
+        <v>15.3</v>
       </c>
       <c r="L81" t="n">
-        <v>1.5934</v>
+        <v>1.424</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -5612,19 +5612,19 @@
         <v>152.825</v>
       </c>
       <c r="H82" t="n">
-        <v>152.8179</v>
+        <v>152.8169</v>
       </c>
       <c r="I82" t="n">
-        <v>153.4153</v>
+        <v>153.7145</v>
       </c>
       <c r="J82" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="K82" t="n">
-        <v>24.5</v>
+        <v>21.9</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1275</v>
+        <v>0.1544</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5675,19 +5675,19 @@
         <v>232.56</v>
       </c>
       <c r="H83" t="n">
-        <v>232.4752</v>
+        <v>232.4774</v>
       </c>
       <c r="I83" t="n">
-        <v>233.2107</v>
+        <v>233.6296</v>
       </c>
       <c r="J83" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
       <c r="K83" t="n">
-        <v>16.5</v>
+        <v>22.6</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1896</v>
+        <v>0.2272</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5801,19 +5801,19 @@
         <v>45.695</v>
       </c>
       <c r="H85" t="n">
-        <v>45.6059</v>
+        <v>45.6066</v>
       </c>
       <c r="I85" t="n">
-        <v>45.715</v>
+        <v>45.7866</v>
       </c>
       <c r="J85" t="n">
         <v>53.9</v>
       </c>
       <c r="K85" t="n">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="L85" t="n">
-        <v>0.037</v>
+        <v>0.0435</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -5864,19 +5864,19 @@
         <v>235.04</v>
       </c>
       <c r="H86" t="n">
-        <v>234.9006</v>
+        <v>234.9043</v>
       </c>
       <c r="I86" t="n">
-        <v>235.5554</v>
+        <v>235.9214</v>
       </c>
       <c r="J86" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="K86" t="n">
-        <v>25.8</v>
+        <v>22.2</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1709</v>
+        <v>0.2032</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -5927,19 +5927,19 @@
         <v>698.0700000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>685.8943</v>
+        <v>686.24</v>
       </c>
       <c r="I87" t="n">
-        <v>679.5151</v>
+        <v>682.0948</v>
       </c>
       <c r="J87" t="n">
-        <v>64.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="K87" t="n">
-        <v>16.1</v>
+        <v>18.2</v>
       </c>
       <c r="L87" t="n">
-        <v>1.6565</v>
+        <v>1.9668</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -5990,19 +5990,19 @@
         <v>432.36</v>
       </c>
       <c r="H88" t="n">
-        <v>424.6863</v>
+        <v>424.904</v>
       </c>
       <c r="I88" t="n">
-        <v>420.6308</v>
+        <v>422.2584</v>
       </c>
       <c r="J88" t="n">
-        <v>64.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="L88" t="n">
-        <v>1.0416</v>
+        <v>1.2362</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6053,19 +6053,19 @@
         <v>268.41</v>
       </c>
       <c r="H89" t="n">
-        <v>267.4035</v>
+        <v>267.4507</v>
       </c>
       <c r="I89" t="n">
-        <v>267.3749</v>
+        <v>267.7801</v>
       </c>
       <c r="J89" t="n">
-        <v>59.6</v>
+        <v>59.2</v>
       </c>
       <c r="K89" t="n">
-        <v>18</v>
+        <v>16.1</v>
       </c>
       <c r="L89" t="n">
-        <v>0.1491</v>
+        <v>0.1884</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6116,19 +6116,19 @@
         <v>41.625</v>
       </c>
       <c r="H90" t="n">
-        <v>41.6109</v>
+        <v>41.6103</v>
       </c>
       <c r="I90" t="n">
-        <v>41.7473</v>
+        <v>41.8143</v>
       </c>
       <c r="J90" t="n">
-        <v>49.7</v>
+        <v>49.3</v>
       </c>
       <c r="K90" t="n">
-        <v>21.8</v>
+        <v>22.3</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0313</v>
+        <v>0.0373</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6179,19 +6179,19 @@
         <v>7.3818</v>
       </c>
       <c r="H91" t="n">
-        <v>7.3852</v>
+        <v>7.3846</v>
       </c>
       <c r="I91" t="n">
-        <v>7.4284</v>
+        <v>7.4432</v>
       </c>
       <c r="J91" t="n">
-        <v>48</v>
+        <v>47.6</v>
       </c>
       <c r="K91" t="n">
-        <v>25.7</v>
+        <v>22.7</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0073</v>
+        <v>0.0086</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6242,19 +6242,19 @@
         <v>19.144</v>
       </c>
       <c r="H92" t="n">
-        <v>18.8062</v>
+        <v>18.8159</v>
       </c>
       <c r="I92" t="n">
-        <v>18.6288</v>
+        <v>18.7004</v>
       </c>
       <c r="J92" t="n">
-        <v>65</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K92" t="n">
-        <v>18.2</v>
+        <v>18.6</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0458</v>
+        <v>0.0544</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6305,19 +6305,19 @@
         <v>220.29</v>
       </c>
       <c r="H93" t="n">
-        <v>220.3482</v>
+        <v>220.3443</v>
       </c>
       <c r="I93" t="n">
-        <v>221.0366</v>
+        <v>221.3882</v>
       </c>
       <c r="J93" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="K93" t="n">
-        <v>17.5</v>
+        <v>20.8</v>
       </c>
       <c r="L93" t="n">
-        <v>0.1472</v>
+        <v>0.1784</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -6368,19 +6368,19 @@
         <v>48.98</v>
       </c>
       <c r="H94" t="n">
-        <v>49.0437</v>
+        <v>49.0454</v>
       </c>
       <c r="I94" t="n">
-        <v>49.1991</v>
+        <v>49.2951</v>
       </c>
       <c r="J94" t="n">
-        <v>45.9</v>
+        <v>44.7</v>
       </c>
       <c r="K94" t="n">
-        <v>18.3</v>
+        <v>20.4</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0184</v>
+        <v>0.0266</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -6431,19 +6431,19 @@
         <v>55.28</v>
       </c>
       <c r="H95" t="n">
-        <v>55.2306</v>
+        <v>55.2355</v>
       </c>
       <c r="I95" t="n">
-        <v>55.241</v>
+        <v>55.2952</v>
       </c>
       <c r="J95" t="n">
-        <v>53.9</v>
+        <v>53.2</v>
       </c>
       <c r="K95" t="n">
-        <v>10</v>
+        <v>18.3</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0216</v>
+        <v>0.0265</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6494,19 +6494,19 @@
         <v>137.24</v>
       </c>
       <c r="H96" t="n">
-        <v>137.195</v>
+        <v>137.2038</v>
       </c>
       <c r="I96" t="n">
-        <v>137.4872</v>
+        <v>137.6715</v>
       </c>
       <c r="J96" t="n">
-        <v>50.1</v>
+        <v>49.3</v>
       </c>
       <c r="K96" t="n">
-        <v>14.1</v>
+        <v>21</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0764</v>
+        <v>0.0945</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -6620,19 +6620,19 @@
         <v>24.255</v>
       </c>
       <c r="H98" t="n">
-        <v>24.0509</v>
+        <v>24.0329</v>
       </c>
       <c r="I98" t="n">
-        <v>25.0499</v>
+        <v>25.0126</v>
       </c>
       <c r="J98" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="K98" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="L98" t="n">
-        <v>0.1606</v>
+        <v>0.1695</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -6683,19 +6683,19 @@
         <v>197.92</v>
       </c>
       <c r="H99" t="n">
-        <v>193.2831</v>
+        <v>193.351</v>
       </c>
       <c r="I99" t="n">
-        <v>191.6099</v>
+        <v>192.4156</v>
       </c>
       <c r="J99" t="n">
-        <v>65.3</v>
+        <v>65.8</v>
       </c>
       <c r="K99" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="L99" t="n">
-        <v>0.8174</v>
+        <v>0.9171</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -6746,19 +6746,19 @@
         <v>49.42</v>
       </c>
       <c r="H100" t="n">
-        <v>49.4208</v>
+        <v>49.4202</v>
       </c>
       <c r="I100" t="n">
-        <v>49.5848</v>
+        <v>49.6681</v>
       </c>
       <c r="J100" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="K100" t="n">
-        <v>22</v>
+        <v>21.2</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0348</v>
+        <v>0.0422</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6809,19 +6809,19 @@
         <v>131.295</v>
       </c>
       <c r="H101" t="n">
-        <v>131.1915</v>
+        <v>131.196</v>
       </c>
       <c r="I101" t="n">
-        <v>131.3812</v>
+        <v>131.5264</v>
       </c>
       <c r="J101" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="K101" t="n">
-        <v>24.3</v>
+        <v>21.5</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0677</v>
+        <v>0.0806</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -6872,19 +6872,19 @@
         <v>7.252</v>
       </c>
       <c r="H102" t="n">
-        <v>7.1077</v>
+        <v>7.109</v>
       </c>
       <c r="I102" t="n">
-        <v>7.05</v>
+        <v>7.0507</v>
       </c>
       <c r="J102" t="n">
-        <v>65.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K102" t="n">
-        <v>13.9</v>
+        <v>19.2</v>
       </c>
       <c r="L102" t="n">
-        <v>0.0251</v>
+        <v>0.0267</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -6935,19 +6935,19 @@
         <v>141.695</v>
       </c>
       <c r="H103" t="n">
-        <v>141.8808</v>
+        <v>141.8501</v>
       </c>
       <c r="I103" t="n">
-        <v>143.1854</v>
+        <v>143.551</v>
       </c>
       <c r="J103" t="n">
-        <v>47.4</v>
+        <v>47</v>
       </c>
       <c r="K103" t="n">
-        <v>24.9</v>
+        <v>21.6</v>
       </c>
       <c r="L103" t="n">
-        <v>0.19</v>
+        <v>0.2241</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -6998,19 +6998,19 @@
         <v>104.83</v>
       </c>
       <c r="H104" t="n">
-        <v>104.7224</v>
+        <v>104.7286</v>
       </c>
       <c r="I104" t="n">
-        <v>104.7088</v>
+        <v>104.7918</v>
       </c>
       <c r="J104" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
       <c r="K104" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="L104" t="n">
-        <v>0.0294</v>
+        <v>0.0364</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7061,19 +7061,19 @@
         <v>107.42</v>
       </c>
       <c r="H105" t="n">
-        <v>107.431</v>
+        <v>107.4395</v>
       </c>
       <c r="I105" t="n">
-        <v>107.5793</v>
+        <v>107.71</v>
       </c>
       <c r="J105" t="n">
         <v>43.6</v>
       </c>
       <c r="K105" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="L105" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0194</v>
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7124,19 +7124,19 @@
         <v>202.96</v>
       </c>
       <c r="H106" t="n">
-        <v>203.0952</v>
+        <v>203.0905</v>
       </c>
       <c r="I106" t="n">
-        <v>203.8346</v>
+        <v>204.1197</v>
       </c>
       <c r="J106" t="n">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
       <c r="K106" t="n">
-        <v>19.1</v>
+        <v>25.8</v>
       </c>
       <c r="L106" t="n">
-        <v>0.1393</v>
+        <v>0.1669</v>
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7187,19 +7187,19 @@
         <v>112.88</v>
       </c>
       <c r="H107" t="n">
-        <v>112.7736</v>
+        <v>112.7807</v>
       </c>
       <c r="I107" t="n">
-        <v>112.5927</v>
+        <v>112.6397</v>
       </c>
       <c r="J107" t="n">
-        <v>62.9</v>
+        <v>62.2</v>
       </c>
       <c r="K107" t="n">
-        <v>70.3</v>
+        <v>29</v>
       </c>
       <c r="L107" t="n">
-        <v>-0.0025</v>
+        <v>0.0027</v>
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7250,19 +7250,19 @@
         <v>5.0634</v>
       </c>
       <c r="H108" t="n">
-        <v>5.0549</v>
+        <v>5.0551</v>
       </c>
       <c r="I108" t="n">
-        <v>5.0472</v>
+        <v>5.0493</v>
       </c>
       <c r="J108" t="n">
-        <v>72.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K108" t="n">
-        <v>15.9</v>
+        <v>27.8</v>
       </c>
       <c r="L108" t="n">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7313,19 +7313,19 @@
         <v>75.282</v>
       </c>
       <c r="H109" t="n">
-        <v>74.92659999999999</v>
+        <v>74.9361</v>
       </c>
       <c r="I109" t="n">
-        <v>74.9088</v>
+        <v>74.99169999999999</v>
       </c>
       <c r="J109" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
       <c r="K109" t="n">
-        <v>17.3</v>
+        <v>19.2</v>
       </c>
       <c r="L109" t="n">
-        <v>0.0634</v>
+        <v>0.0709</v>
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -7376,19 +7376,19 @@
         <v>119.22</v>
       </c>
       <c r="H110" t="n">
-        <v>119.0879</v>
+        <v>119.0953</v>
       </c>
       <c r="I110" t="n">
-        <v>119.0882</v>
+        <v>119.1766</v>
       </c>
       <c r="J110" t="n">
-        <v>57</v>
+        <v>56.6</v>
       </c>
       <c r="K110" t="n">
-        <v>19.3</v>
+        <v>25.7</v>
       </c>
       <c r="L110" t="n">
-        <v>0.035</v>
+        <v>0.0431</v>
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -7439,19 +7439,19 @@
         <v>108.28</v>
       </c>
       <c r="H111" t="n">
-        <v>105.9942</v>
+        <v>106.0282</v>
       </c>
       <c r="I111" t="n">
-        <v>105.0873</v>
+        <v>104.9556</v>
       </c>
       <c r="J111" t="n">
-        <v>62.9</v>
+        <v>63.9</v>
       </c>
       <c r="K111" t="n">
-        <v>15.7</v>
+        <v>18.9</v>
       </c>
       <c r="L111" t="n">
-        <v>0.4008</v>
+        <v>0.4125</v>
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -7502,19 +7502,19 @@
         <v>128.1</v>
       </c>
       <c r="H112" t="n">
-        <v>127.9667</v>
+        <v>127.9739</v>
       </c>
       <c r="I112" t="n">
-        <v>127.9234</v>
+        <v>128.0284</v>
       </c>
       <c r="J112" t="n">
-        <v>56.9</v>
+        <v>56.6</v>
       </c>
       <c r="K112" t="n">
-        <v>16.3</v>
+        <v>20.4</v>
       </c>
       <c r="L112" t="n">
-        <v>0.0379</v>
+        <v>0.0462</v>
       </c>
       <c r="M112" s="6" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7565,19 +7565,19 @@
         <v>101.64</v>
       </c>
       <c r="H113" t="n">
-        <v>101.5546</v>
+        <v>101.5613</v>
       </c>
       <c r="I113" t="n">
-        <v>101.5596</v>
+        <v>101.6326</v>
       </c>
       <c r="J113" t="n">
-        <v>67.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="K113" t="n">
-        <v>22.6</v>
+        <v>28.5</v>
       </c>
       <c r="L113" t="n">
-        <v>0.0044</v>
+        <v>0.0109</v>
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -7691,19 +7691,19 @@
         <v>54.496</v>
       </c>
       <c r="H115" t="n">
-        <v>54.4211</v>
+        <v>54.4251</v>
       </c>
       <c r="I115" t="n">
-        <v>54.3824</v>
+        <v>54.4202</v>
       </c>
       <c r="J115" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
       <c r="K115" t="n">
-        <v>16.4</v>
+        <v>17.9</v>
       </c>
       <c r="L115" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0133</v>
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -7817,19 +7817,19 @@
         <v>413.11</v>
       </c>
       <c r="H117" t="n">
-        <v>407.4671</v>
+        <v>408.1097</v>
       </c>
       <c r="I117" t="n">
-        <v>393.2655</v>
+        <v>398.6704</v>
       </c>
       <c r="J117" t="n">
-        <v>65.2</v>
+        <v>64.3</v>
       </c>
       <c r="K117" t="n">
-        <v>42.7</v>
+        <v>36.2</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.4808</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -7880,19 +7880,19 @@
         <v>44.2</v>
       </c>
       <c r="H118" t="n">
-        <v>43.1208</v>
+        <v>43.1379</v>
       </c>
       <c r="I118" t="n">
-        <v>42.4842</v>
+        <v>42.674</v>
       </c>
       <c r="J118" t="n">
-        <v>69.8</v>
+        <v>71.5</v>
       </c>
       <c r="K118" t="n">
-        <v>23.1</v>
+        <v>20.8</v>
       </c>
       <c r="L118" t="n">
-        <v>0.1579</v>
+        <v>0.1796</v>
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -7943,19 +7943,19 @@
         <v>636.2</v>
       </c>
       <c r="H119" t="n">
-        <v>624.4930000000001</v>
+        <v>624.8237</v>
       </c>
       <c r="I119" t="n">
-        <v>618.324</v>
+        <v>620.776</v>
       </c>
       <c r="J119" t="n">
-        <v>65</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K119" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="L119" t="n">
-        <v>1.5326</v>
+        <v>1.8356</v>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8006,19 +8006,19 @@
         <v>138.56</v>
       </c>
       <c r="H120" t="n">
-        <v>138.2244</v>
+        <v>138.2393</v>
       </c>
       <c r="I120" t="n">
-        <v>137.8586</v>
+        <v>137.9578</v>
       </c>
       <c r="J120" t="n">
-        <v>66.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K120" t="n">
-        <v>25.9</v>
+        <v>23.2</v>
       </c>
       <c r="L120" t="n">
-        <v>0.0133</v>
+        <v>0.0236</v>
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>15.5733003616333</v>
+        <v>15.5733</v>
       </c>
       <c r="H121" t="n">
         <v>15.4142</v>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>126.9199981689453</v>
+        <v>126.92</v>
       </c>
       <c r="H122" t="n">
         <v>126.4026</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>114.1999969482422</v>
+        <v>114.2</v>
       </c>
       <c r="H123" t="n">
         <v>113.6715</v>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -8258,19 +8258,19 @@
         <v>21.265</v>
       </c>
       <c r="H124" t="n">
-        <v>20.77</v>
+        <v>20.7721</v>
       </c>
       <c r="I124" t="n">
-        <v>20.0843</v>
+        <v>20.1432</v>
       </c>
       <c r="J124" t="n">
-        <v>64.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="K124" t="n">
-        <v>38.2</v>
+        <v>26.6</v>
       </c>
       <c r="L124" t="n">
-        <v>0.0462</v>
+        <v>0.0501</v>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -8321,19 +8321,19 @@
         <v>48.985</v>
       </c>
       <c r="H125" t="n">
-        <v>49.0643</v>
+        <v>49.073</v>
       </c>
       <c r="I125" t="n">
-        <v>49.1271</v>
+        <v>49.2792</v>
       </c>
       <c r="J125" t="n">
-        <v>45.2</v>
+        <v>42.9</v>
       </c>
       <c r="K125" t="n">
-        <v>16.2</v>
+        <v>20.5</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.0146</v>
+        <v>-0.0026</v>
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -8384,19 +8384,19 @@
         <v>63.33</v>
       </c>
       <c r="H126" t="n">
-        <v>63.1192</v>
+        <v>63.1156</v>
       </c>
       <c r="I126" t="n">
-        <v>63.0855</v>
+        <v>63.0211</v>
       </c>
       <c r="J126" t="n">
-        <v>58.5</v>
+        <v>59.9</v>
       </c>
       <c r="K126" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="L126" t="n">
-        <v>0.0599</v>
+        <v>0.0567</v>
       </c>
       <c r="M126" s="6" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -8447,19 +8447,19 @@
         <v>238.95</v>
       </c>
       <c r="H127" t="n">
-        <v>232.8015</v>
+        <v>232.9507</v>
       </c>
       <c r="I127" t="n">
-        <v>228.655</v>
+        <v>229.596</v>
       </c>
       <c r="J127" t="n">
-        <v>69.3</v>
+        <v>71.2</v>
       </c>
       <c r="K127" t="n">
-        <v>20.5</v>
+        <v>24.2</v>
       </c>
       <c r="L127" t="n">
-        <v>0.9142</v>
+        <v>0.9938</v>
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8542,7 +8542,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -8570,31 +8570,31 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>39.95</v>
+        <v>40.46</v>
       </c>
       <c r="H129" t="n">
-        <v>39.6305</v>
+        <v>39.6386</v>
       </c>
       <c r="I129" t="n">
-        <v>39.7218</v>
+        <v>38.7669</v>
       </c>
       <c r="J129" t="n">
-        <v>53.4</v>
+        <v>60.8</v>
       </c>
       <c r="K129" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="L129" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="M129" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0118</v>
+      </c>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
+          <t>L0 RECOVERY</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>USHYC</t>
+          <t>USHYC.MI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -8696,22 +8696,22 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>65.63</v>
+        <v>65.56</v>
       </c>
       <c r="H131" t="n">
-        <v>65.4991</v>
+        <v>65.50700000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>65.8</v>
+        <v>65.84180000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>52</v>
+        <v>49.8</v>
       </c>
       <c r="K131" t="n">
-        <v>14.2</v>
+        <v>18</v>
       </c>
       <c r="L131" t="n">
-        <v>0.0476</v>
+        <v>0.0608</v>
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -8762,19 +8762,19 @@
         <v>155.36</v>
       </c>
       <c r="H132" t="n">
-        <v>155.2061</v>
+        <v>155.216</v>
       </c>
       <c r="I132" t="n">
-        <v>155.782</v>
+        <v>155.9432</v>
       </c>
       <c r="J132" t="n">
-        <v>50.7</v>
+        <v>50.2</v>
       </c>
       <c r="K132" t="n">
-        <v>13.9</v>
+        <v>18.2</v>
       </c>
       <c r="L132" t="n">
-        <v>0.1189</v>
+        <v>0.1442</v>
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -8822,22 +8822,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>7.277</v>
+        <v>7.286</v>
       </c>
       <c r="H133" t="n">
-        <v>7.0869</v>
+        <v>7.1072</v>
       </c>
       <c r="I133" t="n">
-        <v>7.051</v>
+        <v>7.0515</v>
       </c>
       <c r="J133" t="n">
-        <v>67.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K133" t="n">
-        <v>17.6</v>
+        <v>22.4</v>
       </c>
       <c r="L133" t="n">
-        <v>0.0308</v>
+        <v>0.034</v>
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -8888,19 +8888,19 @@
         <v>147.14</v>
       </c>
       <c r="H134" t="n">
-        <v>147.9538</v>
+        <v>147.9998</v>
       </c>
       <c r="I134" t="n">
-        <v>148.3365</v>
+        <v>149.1018</v>
       </c>
       <c r="J134" t="n">
-        <v>39.5</v>
+        <v>36.7</v>
       </c>
       <c r="K134" t="n">
-        <v>20.8</v>
+        <v>23.7</v>
       </c>
       <c r="L134" t="n">
-        <v>-0.17</v>
+        <v>-0.1171</v>
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -8951,19 +8951,19 @@
         <v>181.95</v>
       </c>
       <c r="H135" t="n">
-        <v>178.1102</v>
+        <v>178.1293</v>
       </c>
       <c r="I135" t="n">
-        <v>176.9466</v>
+        <v>176.7318</v>
       </c>
       <c r="J135" t="n">
-        <v>64</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K135" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="L135" t="n">
-        <v>0.7348</v>
+        <v>0.7581</v>
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -9077,19 +9077,19 @@
         <v>133.79</v>
       </c>
       <c r="H137" t="n">
-        <v>131.4565</v>
+        <v>131.5169</v>
       </c>
       <c r="I137" t="n">
-        <v>130.3913</v>
+        <v>130.7818</v>
       </c>
       <c r="J137" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="K137" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="L137" t="n">
-        <v>0.3488</v>
+        <v>0.4042</v>
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -9140,19 +9140,19 @@
         <v>72.98999999999999</v>
       </c>
       <c r="H138" t="n">
-        <v>73.0916</v>
+        <v>73.0887</v>
       </c>
       <c r="I138" t="n">
-        <v>73.5702</v>
+        <v>73.63</v>
       </c>
       <c r="J138" t="n">
-        <v>44.3</v>
+        <v>43.7</v>
       </c>
       <c r="K138" t="n">
-        <v>37.4</v>
+        <v>30.5</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0432</v>
+        <v>0.0499</v>
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -9203,19 +9203,19 @@
         <v>18.663</v>
       </c>
       <c r="H139" t="n">
-        <v>18.7248</v>
+        <v>18.7296</v>
       </c>
       <c r="I139" t="n">
-        <v>18.8459</v>
+        <v>18.9358</v>
       </c>
       <c r="J139" t="n">
-        <v>43.2</v>
+        <v>41.1</v>
       </c>
       <c r="K139" t="n">
-        <v>24.5</v>
+        <v>32.5</v>
       </c>
       <c r="L139" t="n">
-        <v>-0.0107</v>
+        <v>-0.0036</v>
       </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -9266,19 +9266,19 @@
         <v>46.275</v>
       </c>
       <c r="H140" t="n">
-        <v>46.3304</v>
+        <v>46.3276</v>
       </c>
       <c r="I140" t="n">
-        <v>46.4763</v>
+        <v>46.5205</v>
       </c>
       <c r="J140" t="n">
-        <v>46.2</v>
+        <v>45.6</v>
       </c>
       <c r="K140" t="n">
-        <v>14.2</v>
+        <v>16.7</v>
       </c>
       <c r="L140" t="n">
-        <v>0.0153</v>
+        <v>0.0192</v>
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -9392,19 +9392,19 @@
         <v>45.03</v>
       </c>
       <c r="H142" t="n">
-        <v>45.1252</v>
+        <v>45.1313</v>
       </c>
       <c r="I142" t="n">
-        <v>45.1989</v>
+        <v>45.3419</v>
       </c>
       <c r="J142" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K142" t="n">
-        <v>9.9</v>
+        <v>20.6</v>
       </c>
       <c r="L142" t="n">
-        <v>-0.0105</v>
+        <v>0</v>
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -9581,19 +9581,19 @@
         <v>122.36</v>
       </c>
       <c r="H145" t="n">
-        <v>119.8286</v>
+        <v>120.1326</v>
       </c>
       <c r="I145" t="n">
-        <v>119.3579</v>
+        <v>120.0491</v>
       </c>
       <c r="J145" t="n">
-        <v>63.9</v>
+        <v>63.8</v>
       </c>
       <c r="K145" t="n">
-        <v>67.09999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="L145" t="n">
-        <v>0.3972</v>
+        <v>0.5071</v>
       </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -9641,22 +9641,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>117.64</v>
+        <v>119.46</v>
       </c>
       <c r="H146" t="n">
-        <v>114.9473</v>
+        <v>115.3394</v>
       </c>
       <c r="I146" t="n">
-        <v>117.3468</v>
+        <v>116.96</v>
       </c>
       <c r="J146" t="n">
-        <v>57.1</v>
+        <v>62.3</v>
       </c>
       <c r="K146" t="n">
-        <v>14.7</v>
+        <v>18.2</v>
       </c>
       <c r="L146" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.9096</v>
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -9707,19 +9707,19 @@
         <v>24.345</v>
       </c>
       <c r="H147" t="n">
-        <v>23.8865</v>
+        <v>23.8713</v>
       </c>
       <c r="I147" t="n">
-        <v>23.193</v>
+        <v>22.8941</v>
       </c>
       <c r="J147" t="n">
-        <v>61.2</v>
+        <v>63.8</v>
       </c>
       <c r="K147" t="n">
-        <v>24.7</v>
+        <v>30.7</v>
       </c>
       <c r="L147" t="n">
-        <v>0.0347</v>
+        <v>0.0123</v>
       </c>
       <c r="M147" s="5" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -9770,19 +9770,19 @@
         <v>105.9</v>
       </c>
       <c r="H148" t="n">
-        <v>103.7203</v>
+        <v>103.6547</v>
       </c>
       <c r="I148" t="n">
-        <v>100.7332</v>
+        <v>99.43559999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>61.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K148" t="n">
-        <v>26.4</v>
+        <v>30.3</v>
       </c>
       <c r="L148" t="n">
-        <v>0.1818</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -9833,19 +9833,19 @@
         <v>62.12</v>
       </c>
       <c r="H149" t="n">
-        <v>60.0774</v>
+        <v>60.2946</v>
       </c>
       <c r="I149" t="n">
-        <v>59.5169</v>
+        <v>59.5302</v>
       </c>
       <c r="J149" t="n">
-        <v>67.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K149" t="n">
-        <v>62.9</v>
+        <v>22.6</v>
       </c>
       <c r="L149" t="n">
-        <v>0.3901</v>
+        <v>0.3952</v>
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9896,19 +9896,19 @@
         <v>6.437</v>
       </c>
       <c r="H150" t="n">
-        <v>6.3121</v>
+        <v>6.3154</v>
       </c>
       <c r="I150" t="n">
-        <v>6.2549</v>
+        <v>6.2791</v>
       </c>
       <c r="J150" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="K150" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="L150" t="n">
-        <v>0.0181</v>
+        <v>0.0212</v>
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -9959,19 +9959,19 @@
         <v>138.92</v>
       </c>
       <c r="H151" t="n">
-        <v>135.7904</v>
+        <v>135.8221</v>
       </c>
       <c r="I151" t="n">
-        <v>135.467</v>
+        <v>135.615</v>
       </c>
       <c r="J151" t="n">
-        <v>63.8</v>
+        <v>64.8</v>
       </c>
       <c r="K151" t="n">
-        <v>17.9</v>
+        <v>19.6</v>
       </c>
       <c r="L151" t="n">
-        <v>0.6655</v>
+        <v>0.7306</v>
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10022,19 +10022,19 @@
         <v>5.073</v>
       </c>
       <c r="H152" t="n">
-        <v>4.9722</v>
+        <v>4.9746</v>
       </c>
       <c r="I152" t="n">
-        <v>4.9275</v>
+        <v>4.9471</v>
       </c>
       <c r="J152" t="n">
-        <v>65.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K152" t="n">
-        <v>17.5</v>
+        <v>19.8</v>
       </c>
       <c r="L152" t="n">
-        <v>0.0147</v>
+        <v>0.0171</v>
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -10085,19 +10085,19 @@
         <v>25.975</v>
       </c>
       <c r="H153" t="n">
-        <v>25.6695</v>
+        <v>25.6858</v>
       </c>
       <c r="I153" t="n">
-        <v>25.371</v>
+        <v>25.6728</v>
       </c>
       <c r="J153" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
       <c r="K153" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="L153" t="n">
-        <v>0.0474</v>
+        <v>0.0641</v>
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -10148,19 +10148,19 @@
         <v>97.08</v>
       </c>
       <c r="H154" t="n">
-        <v>96.6611</v>
+        <v>96.8188</v>
       </c>
       <c r="I154" t="n">
-        <v>93.2902</v>
+        <v>94.779</v>
       </c>
       <c r="J154" t="n">
-        <v>59.6</v>
+        <v>57.8</v>
       </c>
       <c r="K154" t="n">
-        <v>38.9</v>
+        <v>44.7</v>
       </c>
       <c r="L154" t="n">
-        <v>-0.2152</v>
+        <v>-0.1338</v>
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -10180,7 +10180,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10211,28 +10211,28 @@
         <v>819.83</v>
       </c>
       <c r="H155" t="n">
-        <v>811.5088</v>
+        <v>812.0227</v>
       </c>
       <c r="I155" t="n">
-        <v>800.9849</v>
+        <v>810.265</v>
       </c>
       <c r="J155" t="n">
-        <v>58.1</v>
+        <v>58.2</v>
       </c>
       <c r="K155" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="L155" t="n">
-        <v>1.3948</v>
-      </c>
-      <c r="M155" s="5" t="inlineStr">
-        <is>
-          <t>L0 RECOVERY</t>
+        <v>1.8963</v>
+      </c>
+      <c r="M155" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -10274,19 +10274,19 @@
         <v>211.22</v>
       </c>
       <c r="H156" t="n">
-        <v>208.4305</v>
+        <v>208.466</v>
       </c>
       <c r="I156" t="n">
-        <v>207.772</v>
+        <v>208.5286</v>
       </c>
       <c r="J156" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
       <c r="K156" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="L156" t="n">
-        <v>0.5466</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -10337,19 +10337,19 @@
         <v>664</v>
       </c>
       <c r="H157" t="n">
-        <v>653.3344</v>
+        <v>653.086</v>
       </c>
       <c r="I157" t="n">
-        <v>663.934</v>
+        <v>662.1900000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>55</v>
+        <v>55.5</v>
       </c>
       <c r="K157" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="L157" t="n">
-        <v>3.7879</v>
+        <v>3.9674</v>
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -10400,7 +10400,7 @@
         <v>104.1</v>
       </c>
       <c r="H158" t="n">
-        <v>102.6756</v>
+        <v>102.6688</v>
       </c>
       <c r="I158" t="n">
         <v>104.1894</v>
@@ -10409,10 +10409,10 @@
         <v>54.6</v>
       </c>
       <c r="K158" t="n">
-        <v>16.2</v>
+        <v>13.5</v>
       </c>
       <c r="L158" t="n">
-        <v>0.4563</v>
+        <v>0.435</v>
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -10463,19 +10463,19 @@
         <v>18.452</v>
       </c>
       <c r="H159" t="n">
-        <v>18.8474</v>
+        <v>18.8559</v>
       </c>
       <c r="I159" t="n">
-        <v>19.1468</v>
+        <v>19.1639</v>
       </c>
       <c r="J159" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="K159" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="L159" t="n">
-        <v>0.0208</v>
+        <v>0.0352</v>
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -10526,19 +10526,19 @@
         <v>104.1</v>
       </c>
       <c r="H160" t="n">
-        <v>102.6756</v>
+        <v>102.6725</v>
       </c>
       <c r="I160" t="n">
-        <v>104.1894</v>
+        <v>104.364</v>
       </c>
       <c r="J160" t="n">
-        <v>54.6</v>
+        <v>54.8</v>
       </c>
       <c r="K160" t="n">
-        <v>16.2</v>
+        <v>18.9</v>
       </c>
       <c r="L160" t="n">
-        <v>0.4563</v>
+        <v>0.5151</v>
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -10589,19 +10589,19 @@
         <v>293.15</v>
       </c>
       <c r="H161" t="n">
-        <v>289.1221</v>
+        <v>289.1083</v>
       </c>
       <c r="I161" t="n">
-        <v>293.333</v>
+        <v>293.7791</v>
       </c>
       <c r="J161" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="K161" t="n">
-        <v>16.2</v>
+        <v>18.7</v>
       </c>
       <c r="L161" t="n">
-        <v>1.2848</v>
+        <v>1.4486</v>
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -10652,19 +10652,19 @@
         <v>27.41</v>
       </c>
       <c r="H162" t="n">
-        <v>27.1446</v>
+        <v>27.1565</v>
       </c>
       <c r="I162" t="n">
-        <v>26.9425</v>
+        <v>27.0279</v>
       </c>
       <c r="J162" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="K162" t="n">
-        <v>9</v>
+        <v>11.9</v>
       </c>
       <c r="L162" t="n">
-        <v>0.036</v>
+        <v>0.0522</v>
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -10715,19 +10715,19 @@
         <v>16.406</v>
       </c>
       <c r="H163" t="n">
-        <v>16.1022</v>
+        <v>16.1132</v>
       </c>
       <c r="I163" t="n">
-        <v>15.8933</v>
+        <v>15.9456</v>
       </c>
       <c r="J163" t="n">
         <v>61.2</v>
       </c>
       <c r="K163" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="L163" t="n">
-        <v>0.0371</v>
+        <v>0.044</v>
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -10778,19 +10778,19 @@
         <v>144.28</v>
       </c>
       <c r="H164" t="n">
-        <v>139.2899</v>
+        <v>139.3194</v>
       </c>
       <c r="I164" t="n">
-        <v>139.6038</v>
+        <v>139.3794</v>
       </c>
       <c r="J164" t="n">
-        <v>61.3</v>
+        <v>62.1</v>
       </c>
       <c r="K164" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L164" t="n">
-        <v>1.0921</v>
+        <v>1.184</v>
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -10841,19 +10841,19 @@
         <v>73.94</v>
       </c>
       <c r="H165" t="n">
-        <v>72.1968</v>
+        <v>72.12869999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>70.5412</v>
+        <v>70.482</v>
       </c>
       <c r="J165" t="n">
-        <v>58.3</v>
+        <v>61.1</v>
       </c>
       <c r="K165" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L165" t="n">
-        <v>0.1582</v>
+        <v>0.0692</v>
       </c>
       <c r="M165" s="5" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10904,19 +10904,19 @@
         <v>1199.8199</v>
       </c>
       <c r="H166" t="n">
-        <v>1161.6788</v>
+        <v>1161.4551</v>
       </c>
       <c r="I166" t="n">
-        <v>1166.6264</v>
+        <v>1163.7156</v>
       </c>
       <c r="J166" t="n">
-        <v>60.7</v>
+        <v>61.8</v>
       </c>
       <c r="K166" t="n">
-        <v>14.4</v>
+        <v>16.4</v>
       </c>
       <c r="L166" t="n">
-        <v>7.4773</v>
+        <v>8.0503</v>
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -11030,19 +11030,19 @@
         <v>6.56</v>
       </c>
       <c r="H168" t="n">
-        <v>6.1002</v>
+        <v>6.1102</v>
       </c>
       <c r="I168" t="n">
-        <v>5.8153</v>
+        <v>5.8599</v>
       </c>
       <c r="J168" t="n">
-        <v>79</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K168" t="n">
-        <v>33</v>
+        <v>35.2</v>
       </c>
       <c r="L168" t="n">
-        <v>0.0618</v>
+        <v>0.0644</v>
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PHAU.MI</t>
+          <t>PHAU.L</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Londra (LSE)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -11156,19 +11156,19 @@
         <v>50.29</v>
       </c>
       <c r="H170" t="n">
-        <v>47.418</v>
+        <v>47.236</v>
       </c>
       <c r="I170" t="n">
-        <v>49.4454</v>
+        <v>47.674</v>
       </c>
       <c r="J170" t="n">
-        <v>58.6</v>
+        <v>61.5</v>
       </c>
       <c r="K170" t="n">
-        <v>23.1</v>
+        <v>16.2</v>
       </c>
       <c r="L170" t="n">
-        <v>0.6777</v>
+        <v>0.5384</v>
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -11219,19 +11219,19 @@
         <v>168.04</v>
       </c>
       <c r="H171" t="n">
-        <v>165.3153</v>
+        <v>165.3813</v>
       </c>
       <c r="I171" t="n">
-        <v>164.4076</v>
+        <v>164.9772</v>
       </c>
       <c r="J171" t="n">
-        <v>62.7</v>
+        <v>63.2</v>
       </c>
       <c r="K171" t="n">
-        <v>15</v>
+        <v>16.8</v>
       </c>
       <c r="L171" t="n">
-        <v>0.4352</v>
+        <v>0.5111</v>
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -11345,19 +11345,19 @@
         <v>30.35</v>
       </c>
       <c r="H173" t="n">
-        <v>30.5744</v>
+        <v>30.5854</v>
       </c>
       <c r="I173" t="n">
-        <v>30.3083</v>
+        <v>30.4517</v>
       </c>
       <c r="J173" t="n">
-        <v>45.9</v>
+        <v>44.8</v>
       </c>
       <c r="K173" t="n">
-        <v>10.4</v>
+        <v>12.2</v>
       </c>
       <c r="L173" t="n">
-        <v>-0.0302</v>
+        <v>-0.0253</v>
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -11408,19 +11408,19 @@
         <v>10.54</v>
       </c>
       <c r="H174" t="n">
-        <v>10.5665</v>
+        <v>10.5382</v>
       </c>
       <c r="I174" t="n">
-        <v>11.3587</v>
+        <v>11.1593</v>
       </c>
       <c r="J174" t="n">
-        <v>46.2</v>
+        <v>46.9</v>
       </c>
       <c r="K174" t="n">
-        <v>23.2</v>
+        <v>24.8</v>
       </c>
       <c r="L174" t="n">
-        <v>0.0848</v>
+        <v>0.0751</v>
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -11471,19 +11471,19 @@
         <v>204.2</v>
       </c>
       <c r="H175" t="n">
-        <v>199.461</v>
+        <v>199.3807</v>
       </c>
       <c r="I175" t="n">
-        <v>204.1078</v>
+        <v>203.8334</v>
       </c>
       <c r="J175" t="n">
-        <v>56.6</v>
+        <v>57.2</v>
       </c>
       <c r="K175" t="n">
-        <v>15.5</v>
+        <v>18.9</v>
       </c>
       <c r="L175" t="n">
-        <v>1.5573</v>
+        <v>1.7258</v>
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -11534,19 +11534,19 @@
         <v>273.75</v>
       </c>
       <c r="H176" t="n">
-        <v>269.3352</v>
+        <v>269.3831</v>
       </c>
       <c r="I176" t="n">
-        <v>265.358</v>
+        <v>265.53</v>
       </c>
       <c r="J176" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K176" t="n">
-        <v>30.2</v>
+        <v>21.3</v>
       </c>
       <c r="L176" t="n">
-        <v>0.1792</v>
+        <v>0.239</v>
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -11597,19 +11597,19 @@
         <v>33.72</v>
       </c>
       <c r="H177" t="n">
-        <v>34.393</v>
+        <v>34.4181</v>
       </c>
       <c r="I177" t="n">
-        <v>34.2962</v>
+        <v>34.5217</v>
       </c>
       <c r="J177" t="n">
-        <v>39.1</v>
+        <v>37.2</v>
       </c>
       <c r="K177" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="L177" t="n">
-        <v>-0.1857</v>
+        <v>-0.1734</v>
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -11660,19 +11660,19 @@
         <v>159.24</v>
       </c>
       <c r="H178" t="n">
-        <v>159.0779</v>
+        <v>159.0841</v>
       </c>
       <c r="I178" t="n">
-        <v>159.2944</v>
+        <v>159.4854</v>
       </c>
       <c r="J178" t="n">
-        <v>52.7</v>
+        <v>52.3</v>
       </c>
       <c r="K178" t="n">
-        <v>17.1</v>
+        <v>21.7</v>
       </c>
       <c r="L178" t="n">
-        <v>0.0853</v>
+        <v>0.1017</v>
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -11723,19 +11723,19 @@
         <v>69.55</v>
       </c>
       <c r="H179" t="n">
-        <v>68.73439999999999</v>
+        <v>68.72799999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>68.8948</v>
+        <v>68.9858</v>
       </c>
       <c r="J179" t="n">
-        <v>58.1</v>
+        <v>58.8</v>
       </c>
       <c r="K179" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="L179" t="n">
-        <v>0.1429</v>
+        <v>0.1944</v>
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -11755,7 +11755,7 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -11783,31 +11783,31 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>77.95999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="H180" t="n">
-        <v>76.607</v>
+        <v>10.414</v>
       </c>
       <c r="I180" t="n">
-        <v>77.251</v>
+        <v>10.3846</v>
       </c>
       <c r="J180" t="n">
-        <v>52</v>
+        <v>60.1</v>
       </c>
       <c r="K180" t="n">
-        <v>3.7</v>
+        <v>15.1</v>
       </c>
       <c r="L180" t="n">
-        <v>0.1682</v>
-      </c>
-      <c r="M180" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.0361</v>
+      </c>
+      <c r="M180" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -11849,19 +11849,19 @@
         <v>81.38</v>
       </c>
       <c r="H181" t="n">
-        <v>80.6019</v>
+        <v>80.6592</v>
       </c>
       <c r="I181" t="n">
-        <v>79.29300000000001</v>
+        <v>79.7216</v>
       </c>
       <c r="J181" t="n">
-        <v>65</v>
+        <v>64.8</v>
       </c>
       <c r="K181" t="n">
-        <v>34.2</v>
+        <v>28.8</v>
       </c>
       <c r="L181" t="n">
-        <v>-0.0213</v>
+        <v>0.0194</v>
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -11944,7 +11944,7 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -11972,31 +11972,31 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>77.95999999999999</v>
+        <v>116.02</v>
       </c>
       <c r="H183" t="n">
-        <v>76.607</v>
+        <v>114.8519</v>
       </c>
       <c r="I183" t="n">
-        <v>77.251</v>
+        <v>117.2556</v>
       </c>
       <c r="J183" t="n">
         <v>52</v>
       </c>
       <c r="K183" t="n">
-        <v>3.7</v>
+        <v>11.9</v>
       </c>
       <c r="L183" t="n">
-        <v>0.1682</v>
-      </c>
-      <c r="M183" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.4992</v>
+      </c>
+      <c r="M183" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -12007,7 +12007,7 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -12035,31 +12035,31 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>77.95999999999999</v>
+        <v>90.52</v>
       </c>
       <c r="H184" t="n">
-        <v>76.607</v>
+        <v>88.6602</v>
       </c>
       <c r="I184" t="n">
-        <v>77.251</v>
+        <v>87.55459999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K184" t="n">
-        <v>3.7</v>
+        <v>20.1</v>
       </c>
       <c r="L184" t="n">
-        <v>0.1682</v>
-      </c>
-      <c r="M184" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.2584</v>
+      </c>
+      <c r="M184" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -12070,7 +12070,7 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -12098,31 +12098,31 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>77.95999999999999</v>
+        <v>77.84</v>
       </c>
       <c r="H185" t="n">
-        <v>76.607</v>
+        <v>76.14019999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>77.251</v>
+        <v>74.8326</v>
       </c>
       <c r="J185" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="K185" t="n">
-        <v>3.7</v>
+        <v>20.9</v>
       </c>
       <c r="L185" t="n">
-        <v>0.1682</v>
-      </c>
-      <c r="M185" s="4" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.152</v>
+      </c>
+      <c r="M185" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -12164,19 +12164,19 @@
         <v>18.356</v>
       </c>
       <c r="H186" t="n">
-        <v>18.3221</v>
+        <v>18.3222</v>
       </c>
       <c r="I186" t="n">
-        <v>17.948</v>
+        <v>18.0126</v>
       </c>
       <c r="J186" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="K186" t="n">
-        <v>16.4</v>
+        <v>20.3</v>
       </c>
       <c r="L186" t="n">
-        <v>-0.0146</v>
+        <v>-0.0166</v>
       </c>
       <c r="M186" s="6" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -12290,19 +12290,19 @@
         <v>53.26</v>
       </c>
       <c r="H188" t="n">
-        <v>52.356</v>
+        <v>52.391</v>
       </c>
       <c r="I188" t="n">
-        <v>51.5235</v>
+        <v>51.7964</v>
       </c>
       <c r="J188" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="K188" t="n">
-        <v>18.4</v>
+        <v>22.5</v>
       </c>
       <c r="L188" t="n">
-        <v>0.0791</v>
+        <v>0.103</v>
       </c>
       <c r="M188" s="6" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -12350,22 +12350,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>8.487</v>
+        <v>8.539</v>
       </c>
       <c r="H189" t="n">
-        <v>8.321300000000001</v>
+        <v>8.3421</v>
       </c>
       <c r="I189" t="n">
-        <v>8.188499999999999</v>
+        <v>8.197900000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>70.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K189" t="n">
-        <v>22.4</v>
+        <v>23.7</v>
       </c>
       <c r="L189" t="n">
-        <v>0.0151</v>
+        <v>0.0191</v>
       </c>
       <c r="M189" s="6" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -12416,19 +12416,19 @@
         <v>17.38</v>
       </c>
       <c r="H190" t="n">
-        <v>17.0061</v>
+        <v>16.9851</v>
       </c>
       <c r="I190" t="n">
-        <v>16.9709</v>
+        <v>16.7324</v>
       </c>
       <c r="J190" t="n">
-        <v>65.2</v>
+        <v>69.8</v>
       </c>
       <c r="K190" t="n">
-        <v>12.3</v>
+        <v>21.3</v>
       </c>
       <c r="L190" t="n">
-        <v>0.0587</v>
+        <v>0.0474</v>
       </c>
       <c r="M190" s="6" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -12479,19 +12479,19 @@
         <v>50.34</v>
       </c>
       <c r="H191" t="n">
-        <v>48.648</v>
+        <v>48.6169</v>
       </c>
       <c r="I191" t="n">
-        <v>47.8578</v>
+        <v>47.4472</v>
       </c>
       <c r="J191" t="n">
-        <v>66.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K191" t="n">
-        <v>15.7</v>
+        <v>19.9</v>
       </c>
       <c r="L191" t="n">
-        <v>0.2232</v>
+        <v>0.2174</v>
       </c>
       <c r="M191" s="6" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -12542,19 +12542,19 @@
         <v>3.83</v>
       </c>
       <c r="H192" t="n">
-        <v>3.7548</v>
+        <v>3.7451</v>
       </c>
       <c r="I192" t="n">
-        <v>3.8289</v>
+        <v>3.7215</v>
       </c>
       <c r="J192" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K192" t="n">
-        <v>19.1</v>
+        <v>16.4</v>
       </c>
       <c r="L192" t="n">
-        <v>0.0188</v>
+        <v>0.0124</v>
       </c>
       <c r="M192" s="6" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -12605,19 +12605,19 @@
         <v>11.256</v>
       </c>
       <c r="H193" t="n">
-        <v>10.8897</v>
+        <v>10.8956</v>
       </c>
       <c r="I193" t="n">
-        <v>10.6656</v>
+        <v>10.6814</v>
       </c>
       <c r="J193" t="n">
-        <v>69.3</v>
+        <v>71.8</v>
       </c>
       <c r="K193" t="n">
-        <v>18.2</v>
+        <v>19.7</v>
       </c>
       <c r="L193" t="n">
-        <v>0.039</v>
+        <v>0.0427</v>
       </c>
       <c r="M193" s="6" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -12668,19 +12668,19 @@
         <v>9.83</v>
       </c>
       <c r="H194" t="n">
-        <v>9.238099999999999</v>
+        <v>9.216100000000001</v>
       </c>
       <c r="I194" t="n">
-        <v>9.2385</v>
+        <v>9.039400000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>64.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K194" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="L194" t="n">
-        <v>0.1229</v>
+        <v>0.1162</v>
       </c>
       <c r="M194" s="6" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -12731,19 +12731,19 @@
         <v>27.435</v>
       </c>
       <c r="H195" t="n">
-        <v>27.4411</v>
+        <v>27.348</v>
       </c>
       <c r="I195" t="n">
-        <v>29.7554</v>
+        <v>29.1584</v>
       </c>
       <c r="J195" t="n">
-        <v>46.4</v>
+        <v>47.5</v>
       </c>
       <c r="K195" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L195" t="n">
-        <v>0.2974</v>
+        <v>0.2626</v>
       </c>
       <c r="M195" s="6" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -12794,19 +12794,19 @@
         <v>4.874</v>
       </c>
       <c r="H196" t="n">
-        <v>4.9079</v>
+        <v>4.9097</v>
       </c>
       <c r="I196" t="n">
-        <v>4.8643</v>
+        <v>4.8874</v>
       </c>
       <c r="J196" t="n">
-        <v>46.1</v>
+        <v>45.1</v>
       </c>
       <c r="K196" t="n">
-        <v>9.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="L196" t="n">
-        <v>-0.0047</v>
+        <v>-0.0038</v>
       </c>
       <c r="M196" s="6" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -12857,19 +12857,19 @@
         <v>90.58</v>
       </c>
       <c r="H197" t="n">
-        <v>88.4293</v>
+        <v>88.4653</v>
       </c>
       <c r="I197" t="n">
-        <v>87.1478</v>
+        <v>87.55119999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>68.5</v>
+        <v>70</v>
       </c>
       <c r="K197" t="n">
-        <v>18.7</v>
+        <v>19.5</v>
       </c>
       <c r="L197" t="n">
-        <v>0.3195</v>
+        <v>0.3652</v>
       </c>
       <c r="M197" s="6" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>149.8430023193359</v>
+        <v>149.843</v>
       </c>
       <c r="H198" t="n">
         <v>149.1741</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -12983,19 +12983,19 @@
         <v>141.25</v>
       </c>
       <c r="H199" t="n">
-        <v>141.0985</v>
+        <v>141.1067</v>
       </c>
       <c r="I199" t="n">
-        <v>141.0346</v>
+        <v>141.1452</v>
       </c>
       <c r="J199" t="n">
-        <v>58.5</v>
+        <v>58</v>
       </c>
       <c r="K199" t="n">
-        <v>14.3</v>
+        <v>15.6</v>
       </c>
       <c r="L199" t="n">
-        <v>0.0345</v>
+        <v>0.0429</v>
       </c>
       <c r="M199" s="6" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -13046,19 +13046,19 @@
         <v>158.41</v>
       </c>
       <c r="H200" t="n">
-        <v>155.0825</v>
+        <v>155.1038</v>
       </c>
       <c r="I200" t="n">
-        <v>154.0477</v>
+        <v>153.8703</v>
       </c>
       <c r="J200" t="n">
-        <v>63.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K200" t="n">
-        <v>32.6</v>
+        <v>19.5</v>
       </c>
       <c r="L200" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="M200" s="6" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -13109,19 +13109,19 @@
         <v>120.58</v>
       </c>
       <c r="H201" t="n">
-        <v>118.0801</v>
+        <v>118.1109</v>
       </c>
       <c r="I201" t="n">
-        <v>117.1324</v>
+        <v>117.2044</v>
       </c>
       <c r="J201" t="n">
-        <v>65.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K201" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="L201" t="n">
-        <v>0.4103</v>
+        <v>0.4406</v>
       </c>
       <c r="M201" s="6" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -13172,19 +13172,19 @@
         <v>358.1</v>
       </c>
       <c r="H202" t="n">
-        <v>345.8719</v>
+        <v>345.4927</v>
       </c>
       <c r="I202" t="n">
-        <v>348.4666</v>
+        <v>344.482</v>
       </c>
       <c r="J202" t="n">
-        <v>61.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K202" t="n">
-        <v>22</v>
+        <v>14.1</v>
       </c>
       <c r="L202" t="n">
-        <v>2.3487</v>
+        <v>1.9731</v>
       </c>
       <c r="M202" s="6" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -13235,19 +13235,19 @@
         <v>6.425</v>
       </c>
       <c r="H203" t="n">
-        <v>6.4003</v>
+        <v>6.3883</v>
       </c>
       <c r="I203" t="n">
-        <v>6.3464</v>
+        <v>6.2553</v>
       </c>
       <c r="J203" t="n">
-        <v>50.6</v>
+        <v>52.5</v>
       </c>
       <c r="K203" t="n">
-        <v>12.2</v>
+        <v>10.4</v>
       </c>
       <c r="L203" t="n">
-        <v>0.0089</v>
+        <v>-0.0065</v>
       </c>
       <c r="M203" s="6" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -13298,19 +13298,19 @@
         <v>28.175</v>
       </c>
       <c r="H204" t="n">
-        <v>28.1659</v>
+        <v>28.1481</v>
       </c>
       <c r="I204" t="n">
-        <v>27.8315</v>
+        <v>27.5093</v>
       </c>
       <c r="J204" t="n">
-        <v>50.7</v>
+        <v>51.7</v>
       </c>
       <c r="K204" t="n">
-        <v>20</v>
+        <v>24.3</v>
       </c>
       <c r="L204" t="n">
-        <v>-0.1052</v>
+        <v>-0.1334</v>
       </c>
       <c r="M204" s="6" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -13361,19 +13361,19 @@
         <v>125.84</v>
       </c>
       <c r="H205" t="n">
-        <v>121.709</v>
+        <v>121.6823</v>
       </c>
       <c r="I205" t="n">
-        <v>122.2024</v>
+        <v>121.8712</v>
       </c>
       <c r="J205" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="K205" t="n">
-        <v>13.2</v>
+        <v>16.6</v>
       </c>
       <c r="L205" t="n">
-        <v>0.7947</v>
+        <v>0.8528</v>
       </c>
       <c r="M205" s="6" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -13424,19 +13424,19 @@
         <v>41.065</v>
       </c>
       <c r="H206" t="n">
-        <v>38.7031</v>
+        <v>38.8336</v>
       </c>
       <c r="I206" t="n">
-        <v>37.5063</v>
+        <v>38.0084</v>
       </c>
       <c r="J206" t="n">
-        <v>64.2</v>
+        <v>63.9</v>
       </c>
       <c r="K206" t="n">
-        <v>22.5</v>
+        <v>21.3</v>
       </c>
       <c r="L206" t="n">
-        <v>0.2216</v>
+        <v>0.2969</v>
       </c>
       <c r="M206" s="6" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -13487,19 +13487,19 @@
         <v>9.574999999999999</v>
       </c>
       <c r="H207" t="n">
-        <v>9.334899999999999</v>
+        <v>9.336600000000001</v>
       </c>
       <c r="I207" t="n">
-        <v>9.5921</v>
+        <v>9.623900000000001</v>
       </c>
       <c r="J207" t="n">
         <v>55.3</v>
       </c>
       <c r="K207" t="n">
-        <v>16</v>
+        <v>19.2</v>
       </c>
       <c r="L207" t="n">
-        <v>0.0764</v>
+        <v>0.0893</v>
       </c>
       <c r="M207" s="6" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -13550,19 +13550,19 @@
         <v>9.153</v>
       </c>
       <c r="H208" t="n">
-        <v>9.2202</v>
+        <v>9.198399999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>9.8942</v>
+        <v>9.7631</v>
       </c>
       <c r="J208" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="K208" t="n">
-        <v>22.6</v>
+        <v>25.2</v>
       </c>
       <c r="L208" t="n">
-        <v>0.0599</v>
+        <v>0.0536</v>
       </c>
       <c r="M208" s="6" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -13586,46 +13586,46 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>NDXH2.PA</t>
+          <t>IGLN.L</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Amundi Core Nasdaq-100 Swap UCITS ETF EUR Hdg Acc</t>
+          <t>iShares Physical Gold ETC</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Stati Uniti</t>
+          <t>Oro / Metalli Preziosi</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Londra (LSE)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>104.1</v>
+        <v>83.52</v>
       </c>
       <c r="H209" t="n">
-        <v>102.6688</v>
+        <v>80.02330000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>104.1894</v>
+        <v>80.63679999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>54.6</v>
+        <v>62.6</v>
       </c>
       <c r="K209" t="n">
-        <v>13.5</v>
+        <v>20.7</v>
       </c>
       <c r="L209" t="n">
-        <v>0.435</v>
+        <v>0.6874</v>
       </c>
       <c r="M209" s="6" t="inlineStr">
         <is>
@@ -13634,43 +13634,61 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>LU1954152853</t>
+          <t>DE000A1RX996</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
+      <c r="A210" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>IGLN.L</t>
+          <t>PHPT.MI</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>iShares Physical Gold ETC</t>
+          <t>WisdomTree Physical Platinum ETC</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Oro / Metalli Preziosi</t>
+          <t>Metalli Preziosi</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Londra (LSE)</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>138.87</v>
+      </c>
+      <c r="H210" t="n">
+        <v>131.9958</v>
+      </c>
+      <c r="I210" t="n">
+        <v>129.972</v>
+      </c>
+      <c r="J210" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="K210" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L210" t="n">
+        <v>1.202</v>
       </c>
       <c r="M210" s="6" t="inlineStr">
         <is>
@@ -13679,12 +13697,12 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>DE000A1RX996</t>
+          <t>DE000A0N62E5</t>
         </is>
       </c>
     </row>
@@ -13694,46 +13712,46 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PHPT.MI</t>
+          <t>BITC.SW</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>WisdomTree Physical Platinum ETC</t>
+          <t>CoinShares Physical Bitcoin ETP</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Metalli Preziosi</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Swiss (SIX)</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>138.87</v>
+        <v>50.23</v>
       </c>
       <c r="H211" t="n">
-        <v>132.3354</v>
+        <v>46.459</v>
       </c>
       <c r="I211" t="n">
-        <v>133.3248</v>
+        <v>45.9164</v>
       </c>
       <c r="J211" t="n">
-        <v>61.7</v>
+        <v>67</v>
       </c>
       <c r="K211" t="n">
-        <v>22.3</v>
+        <v>11.4</v>
       </c>
       <c r="L211" t="n">
-        <v>1.5007</v>
+        <v>0.2876</v>
       </c>
       <c r="M211" s="6" t="inlineStr">
         <is>
@@ -13742,27 +13760,27 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>DE000A0N62E5</t>
+          <t>GB00BLD4ZL17</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
+      <c r="A212" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>BITC.SW</t>
+          <t>ETHE.SW</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CoinShares Physical Bitcoin ETP</t>
+          <t>CoinShares Ethereum Staking ETP</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -13780,6 +13798,24 @@
           <t>CHF</t>
         </is>
       </c>
+      <c r="G212" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="H212" t="n">
+        <v>45.899</v>
+      </c>
+      <c r="I212" t="n">
+        <v>43.5412</v>
+      </c>
+      <c r="J212" t="n">
+        <v>57</v>
+      </c>
+      <c r="K212" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L212" t="n">
+        <v>-0.1238</v>
+      </c>
       <c r="M212" s="6" t="inlineStr">
         <is>
           <t>L3</t>
@@ -13787,12 +13823,12 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>GB00BLD4ZL17</t>
+          <t>GB00BLD4ZM24</t>
         </is>
       </c>
     </row>
@@ -13802,12 +13838,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ETHE.SW</t>
+          <t>SLNC.SW</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CoinShares Ethereum Staking ETP</t>
+          <t>CoinShares Solana Staking ETP</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13825,6 +13861,21 @@
           <t>CHF</t>
         </is>
       </c>
+      <c r="G213" t="n">
+        <v>6.795</v>
+      </c>
+      <c r="H213" t="n">
+        <v>7.0117</v>
+      </c>
+      <c r="J213" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K213" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.0194</v>
+      </c>
       <c r="M213" s="6" t="inlineStr">
         <is>
           <t>L3</t>
@@ -13832,12 +13883,12 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>GB00BLD4ZM24</t>
+          <t>GB00BKJG2L22</t>
         </is>
       </c>
     </row>
@@ -13847,12 +13898,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SLNC.SW</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CoinShares Solana Staking ETP</t>
+          <t>Bitwise Physical Bitcoin ETP</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13862,13 +13913,31 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Swiss (SIX)</t>
+          <t>Xetra</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CHF</t>
-        </is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>49.326</v>
+      </c>
+      <c r="H214" t="n">
+        <v>49.3863</v>
+      </c>
+      <c r="I214" t="n">
+        <v>49.0059</v>
+      </c>
+      <c r="J214" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="K214" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L214" t="n">
+        <v>-0.0113</v>
       </c>
       <c r="M214" s="6" t="inlineStr">
         <is>
@@ -13877,12 +13946,12 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>GB00BKJG2L22</t>
+          <t>DE000A27Z304</t>
         </is>
       </c>
     </row>
@@ -13892,12 +13961,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>DA21.DE</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bitwise Physical Bitcoin ETP</t>
+          <t>Bitwise MSCI Digital Assets Select 20 ETP</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13912,8 +13981,26 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>75.05500000000001</v>
+      </c>
+      <c r="H215" t="n">
+        <v>75.3154</v>
+      </c>
+      <c r="I215" t="n">
+        <v>74.4832</v>
+      </c>
+      <c r="J215" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="K215" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="L215" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="M215" s="6" t="inlineStr">
         <is>
@@ -13922,12 +14009,12 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>DE000A27Z304</t>
+          <t>DE000A3G3ZL3</t>
         </is>
       </c>
     </row>
@@ -13937,28 +14024,46 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DA21.DE</t>
+          <t>3LNV.MI</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bitwise MSCI Digital Assets Select 20 ETP</t>
+          <t>GraniteShares 3x Long NVIDIA Daily ETP</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Leva Singolo Titolo</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Xetra</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1.7726</v>
+      </c>
+      <c r="I216" t="n">
+        <v>7.9328</v>
+      </c>
+      <c r="J216" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="K216" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.4943</v>
       </c>
       <c r="M216" s="6" t="inlineStr">
         <is>
@@ -13967,12 +14072,12 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>DE000A3G3ZL3</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13982,12 +14087,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>3LNV.MI</t>
+          <t>3SNV.MI</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long NVIDIA Daily ETP</t>
+          <t>GraniteShares -3x Short NVIDIA Daily ETP</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -14006,22 +14111,22 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>33.47</v>
+        <v>0.2459</v>
       </c>
       <c r="H217" t="n">
-        <v>29.0208</v>
+        <v>1.7726</v>
       </c>
       <c r="I217" t="n">
-        <v>30.0151</v>
+        <v>7.9328</v>
       </c>
       <c r="J217" t="n">
-        <v>60.5</v>
+        <v>47.6</v>
       </c>
       <c r="K217" t="n">
-        <v>15.6</v>
+        <v>4.6</v>
       </c>
       <c r="L217" t="n">
-        <v>0.7405</v>
+        <v>0.4943</v>
       </c>
       <c r="M217" s="6" t="inlineStr">
         <is>
@@ -14030,7 +14135,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -14045,12 +14150,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>3SNV.MI</t>
+          <t>3LTS.MI</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>GraniteShares -3x Short NVIDIA Daily ETP</t>
+          <t>GraniteShares 3x Long Tesla Daily ETP</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -14072,19 +14177,19 @@
         <v>0.2459</v>
       </c>
       <c r="H218" t="n">
-        <v>0.3129</v>
+        <v>1.7726</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3355</v>
+        <v>7.9328</v>
       </c>
       <c r="J218" t="n">
-        <v>34.3</v>
+        <v>47.6</v>
       </c>
       <c r="K218" t="n">
-        <v>17.5</v>
+        <v>4.6</v>
       </c>
       <c r="L218" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.4943</v>
       </c>
       <c r="M218" s="6" t="inlineStr">
         <is>
@@ -14093,7 +14198,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -14108,12 +14213,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>3LTS.MI</t>
+          <t>3LMS.L</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long Tesla Daily ETP</t>
+          <t>GraniteShares 3x Long Microsoft Daily ETP</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -14123,12 +14228,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Londra (LSE)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -14156,7 +14261,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -14171,12 +14276,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>3LMS.MI</t>
+          <t>3LAP.MI</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long Microsoft Daily ETP</t>
+          <t>GraniteShares 3x Long Apple Daily ETP</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -14219,7 +14324,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -14234,12 +14339,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>3LAP.MI</t>
+          <t>3LAM.MI</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long Apple Daily ETP</t>
+          <t>GraniteShares 3x Long Amazon Daily ETP</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -14282,7 +14387,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -14297,12 +14402,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>3LAM.MI</t>
+          <t>3LFB.MI</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long Amazon Daily ETP</t>
+          <t>GraniteShares 3x Long Meta Daily ETP</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -14345,7 +14450,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -14360,12 +14465,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>3LFB.MI</t>
+          <t>3MIB.MI</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long Meta Daily ETP</t>
+          <t>GraniteShares 3x Long FTSE MIB Daily ETP</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -14408,7 +14513,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -14423,22 +14528,22 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>3LIS.MI</t>
+          <t>0XCK.IL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long Intesa Sanpaolo Daily ETP</t>
+          <t>Multi Units France - Lyxor FTSE Italia Mid Cap PIR</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Leva Singolo Titolo</t>
+          <t>Azionari Italia</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -14447,22 +14552,22 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.2459</v>
+        <v>256.7</v>
       </c>
       <c r="H224" t="n">
-        <v>1.7726</v>
+        <v>251.5563</v>
       </c>
       <c r="I224" t="n">
-        <v>7.9328</v>
+        <v>251.891</v>
       </c>
       <c r="J224" t="n">
-        <v>47.6</v>
+        <v>61</v>
       </c>
       <c r="K224" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="L224" t="n">
-        <v>0.4943</v>
+        <v>0.6822</v>
       </c>
       <c r="M224" s="6" t="inlineStr">
         <is>
@@ -14471,12 +14576,12 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FR0011758085</t>
         </is>
       </c>
     </row>
@@ -14486,17 +14591,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3LUC.MI</t>
+          <t>WLDX.MI</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long UniCredit Daily ETP</t>
+          <t>Amundi MSCI World Ex USA Screened UCITS ETF Acc</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Leva Singolo Titolo</t>
+          <t>Azionari Sviluppati</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14510,22 +14615,22 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.2459</v>
+        <v>254.69</v>
       </c>
       <c r="H225" t="n">
-        <v>1.7726</v>
+        <v>249.4001</v>
       </c>
       <c r="I225" t="n">
-        <v>7.9328</v>
+        <v>247.8684</v>
       </c>
       <c r="J225" t="n">
-        <v>47.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K225" t="n">
-        <v>4.6</v>
+        <v>29.6</v>
       </c>
       <c r="L225" t="n">
-        <v>0.4943</v>
+        <v>0.5782</v>
       </c>
       <c r="M225" s="6" t="inlineStr">
         <is>
@@ -14534,12 +14639,12 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FR0013209921</t>
         </is>
       </c>
     </row>
@@ -14549,22 +14654,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>3MIB.MI</t>
+          <t>MAA.PA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long FTSE MIB Daily ETP</t>
+          <t>Amundi Euro Highest Rated Macro-Weighted Governmen</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Leva Singolo Titolo</t>
+          <t>Obbligazionari Governo</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Parigi</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -14573,22 +14678,22 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.2459</v>
+        <v>125.7</v>
       </c>
       <c r="H226" t="n">
-        <v>1.7726</v>
+        <v>125.6905</v>
       </c>
       <c r="I226" t="n">
-        <v>7.9328</v>
+        <v>126.3994</v>
       </c>
       <c r="J226" t="n">
         <v>47.6</v>
       </c>
       <c r="K226" t="n">
-        <v>4.6</v>
+        <v>28.6</v>
       </c>
       <c r="L226" t="n">
-        <v>0.4943</v>
+        <v>0.12</v>
       </c>
       <c r="M226" s="6" t="inlineStr">
         <is>
@@ -14597,12 +14702,12 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LU1287023342</t>
         </is>
       </c>
     </row>
@@ -14612,22 +14717,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>3MBS.MI</t>
+          <t>0E2B.IL</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>GraniteShares -3x Short FTSE MIB Daily ETP</t>
+          <t>LYXOR Index Fund - Lyxor Smart Overnight Return</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Leva Singolo Titolo</t>
+          <t>Liquidità</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14636,22 +14741,22 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.2459</v>
+        <v>109.7</v>
       </c>
       <c r="H227" t="n">
-        <v>1.7726</v>
+        <v>117.9077</v>
       </c>
       <c r="I227" t="n">
-        <v>7.9328</v>
+        <v>126.9181</v>
       </c>
       <c r="J227" t="n">
-        <v>47.6</v>
+        <v>48.2</v>
       </c>
       <c r="K227" t="n">
-        <v>4.6</v>
+        <v>18.6</v>
       </c>
       <c r="L227" t="n">
-        <v>0.4943</v>
+        <v>-0.2293</v>
       </c>
       <c r="M227" s="6" t="inlineStr">
         <is>
@@ -14660,12 +14765,12 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LU1190417599</t>
         </is>
       </c>
     </row>
@@ -14675,46 +14780,46 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0XCK.IL</t>
+          <t>XMGA.DE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Multi Units France - Lyxor FTSE Italia Mid Cap PIR</t>
+          <t>Amundi MSCI USA Ex Mega Cap UCITS ETF USD Accumula</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Azionari Italia</t>
+          <t>Azionari USA</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Francoforte</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>256.7</v>
+        <v>10.532</v>
       </c>
       <c r="H228" t="n">
-        <v>251.5563</v>
+        <v>10.4031</v>
       </c>
       <c r="I228" t="n">
-        <v>251.891</v>
+        <v>10.3464</v>
       </c>
       <c r="J228" t="n">
-        <v>61</v>
+        <v>60.8</v>
       </c>
       <c r="K228" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="L228" t="n">
-        <v>0.6822</v>
+        <v>0.0167</v>
       </c>
       <c r="M228" s="6" t="inlineStr">
         <is>
@@ -14723,12 +14828,12 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>FR0011758085</t>
+          <t>IE000XL4IXU1</t>
         </is>
       </c>
     </row>
@@ -14738,22 +14843,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>WLDX.MI</t>
+          <t>PLAN.PA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Ex USA Screened UCITS ETF Acc</t>
+          <t>Multi Units Luxembourg - Lyxor Corporate Green Bon</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Azionari Sviluppati</t>
+          <t>Obbligazionari Corporate</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Parigi</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -14762,22 +14867,22 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>251.53</v>
+        <v>9.913</v>
       </c>
       <c r="H229" t="n">
-        <v>248.6432</v>
+        <v>9.930400000000001</v>
       </c>
       <c r="I229" t="n">
-        <v>245.9456</v>
+        <v>9.963200000000001</v>
       </c>
       <c r="J229" t="n">
-        <v>73.09999999999999</v>
+        <v>45.2</v>
       </c>
       <c r="K229" t="n">
-        <v>24.7</v>
+        <v>14.5</v>
       </c>
       <c r="L229" t="n">
-        <v>0.2317</v>
+        <v>0.001</v>
       </c>
       <c r="M229" s="6" t="inlineStr">
         <is>
@@ -14786,12 +14891,12 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>FR0013209921</t>
+          <t>LU2370241684</t>
         </is>
       </c>
     </row>
@@ -14801,46 +14906,46 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MAA.PA</t>
+          <t>IART.L</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Amundi Euro Highest Rated Macro-Weighted Governmen</t>
+          <t>iShares AI Innovation Active UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Obbligazionari Governo</t>
+          <t>Azionari Tematici</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Parigi</t>
+          <t>Londra</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>125.7</v>
+        <v>5.948</v>
       </c>
       <c r="H230" t="n">
-        <v>125.693</v>
+        <v>5.9315</v>
       </c>
       <c r="I230" t="n">
-        <v>126.1952</v>
+        <v>6.3945</v>
       </c>
       <c r="J230" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
       <c r="K230" t="n">
-        <v>20.9</v>
+        <v>17.8</v>
       </c>
       <c r="L230" t="n">
-        <v>0.1026</v>
+        <v>0.0645</v>
       </c>
       <c r="M230" s="6" t="inlineStr">
         <is>
@@ -14849,12 +14954,12 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>LU1287023342</t>
+          <t>IE000G0E83X3</t>
         </is>
       </c>
     </row>
@@ -14864,22 +14969,22 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0E2B.IL</t>
+          <t>EXS1.DE</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>LYXOR Index Fund - Lyxor Smart Overnight Return</t>
+          <t>Amundi DAX 50 ESG UCITS ETF - E</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Liquidità</t>
+          <t>Azionari Europa</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Singapur</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -14888,22 +14993,22 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>109.7</v>
+        <v>216.7</v>
       </c>
       <c r="H231" t="n">
-        <v>109.5848</v>
+        <v>211.1017</v>
       </c>
       <c r="I231" t="n">
-        <v>109.4233</v>
+        <v>208.044</v>
       </c>
       <c r="J231" t="n">
-        <v>84.2</v>
+        <v>71.3</v>
       </c>
       <c r="K231" t="n">
-        <v>65.40000000000001</v>
+        <v>24.1</v>
       </c>
       <c r="L231" t="n">
-        <v>0.0009</v>
+        <v>0.9228</v>
       </c>
       <c r="M231" s="6" t="inlineStr">
         <is>
@@ -14912,12 +15017,12 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>LU1190417599</t>
+          <t>LU2240851688</t>
         </is>
       </c>
     </row>
@@ -14927,46 +15032,46 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>XMGA.DE</t>
+          <t>MSEU.L</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Ex Mega Cap UCITS ETF USD Accumula</t>
+          <t>Amundi Index MSCI EMU SRI PBA U</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Azionari USA</t>
+          <t>Azionari Europa</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Francoforte</t>
+          <t>Singapur</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>10.532</v>
+        <v>367.9</v>
       </c>
       <c r="H232" t="n">
-        <v>10.3958</v>
+        <v>358.8273</v>
       </c>
       <c r="I232" t="n">
-        <v>10.283</v>
+        <v>354.94</v>
       </c>
       <c r="J232" t="n">
-        <v>61.1</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K232" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="L232" t="n">
-        <v>0.0103</v>
+        <v>1.5303</v>
       </c>
       <c r="M232" s="6" t="inlineStr">
         <is>
@@ -14975,12 +15080,12 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>IE000XL4IXU1</t>
+          <t>LU2109787635</t>
         </is>
       </c>
     </row>
@@ -14990,22 +15095,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PLAN.PA</t>
+          <t>WATC.SW</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Multi Units Luxembourg - Lyxor Corporate Green Bon</t>
+          <t>Amundi MSCI Water UCITS ETF Acc</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Obbligazionari Corporate</t>
+          <t>Azionari Tematici</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Parigi</t>
+          <t>Svizzera</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -15014,22 +15119,22 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>9.913</v>
+        <v>6.746</v>
       </c>
       <c r="H233" t="n">
-        <v>9.9292</v>
+        <v>6.546</v>
       </c>
       <c r="I233" t="n">
-        <v>9.9411</v>
+        <v>6.3875</v>
       </c>
       <c r="J233" t="n">
-        <v>46.4</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K233" t="n">
-        <v>17.4</v>
+        <v>23.6</v>
       </c>
       <c r="L233" t="n">
-        <v>-0.0007</v>
+        <v>0.0146</v>
       </c>
       <c r="M233" s="6" t="inlineStr">
         <is>
@@ -15038,12 +15143,12 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>LU2370241684</t>
+          <t>FR0014002CH1</t>
         </is>
       </c>
     </row>
@@ -15053,22 +15158,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>IART.L</t>
+          <t>CSBGU7.SW</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>iShares AI Innovation Active UCITS ETF USD (Acc)</t>
+          <t>iShares VII PLC - iShares VII PLC - iShares $ Trea</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Azionari Tematici</t>
+          <t>Obbligazionari Governo</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Londra</t>
+          <t>Svizzera</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -15077,22 +15182,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>5.948</v>
+        <v>142.75</v>
       </c>
       <c r="H234" t="n">
-        <v>5.9419</v>
+        <v>142.7</v>
       </c>
       <c r="I234" t="n">
-        <v>6.379</v>
+        <v>142.9022</v>
       </c>
       <c r="J234" t="n">
-        <v>48.6</v>
+        <v>50.6</v>
       </c>
       <c r="K234" t="n">
-        <v>18.5</v>
+        <v>7.7</v>
       </c>
       <c r="L234" t="n">
-        <v>0.0584</v>
+        <v>0.0489</v>
       </c>
       <c r="M234" s="6" t="inlineStr">
         <is>
@@ -15101,12 +15206,12 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>IE000G0E83X3</t>
+          <t>IE00B3VWN393</t>
         </is>
       </c>
     </row>
@@ -15116,22 +15221,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EXS1.DE</t>
+          <t>LVO.MI</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Amundi DAX 50 ESG UCITS ETF - E</t>
+          <t>Amundi S&amp;P 500 VIX Futures Enhanced Roll UCITS ETF</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Azionari Alternativi</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -15140,22 +15245,22 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>216.7</v>
+        <v>0.6694</v>
       </c>
       <c r="H235" t="n">
-        <v>210.9688</v>
+        <v>0.6839</v>
       </c>
       <c r="I235" t="n">
-        <v>207.2072</v>
+        <v>0.6936</v>
       </c>
       <c r="J235" t="n">
-        <v>69.40000000000001</v>
+        <v>39.5</v>
       </c>
       <c r="K235" t="n">
-        <v>19.8</v>
+        <v>19.1</v>
       </c>
       <c r="L235" t="n">
-        <v>0.8514</v>
+        <v>-0.0022</v>
       </c>
       <c r="M235" s="6" t="inlineStr">
         <is>
@@ -15164,12 +15269,12 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>LU2240851688</t>
+          <t>LU0832435464</t>
         </is>
       </c>
     </row>
@@ -15179,46 +15284,46 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MSEU.L</t>
+          <t>CSSPX.MI</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Amundi Index MSCI EMU SRI PBA U</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Azionari USA</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>367.9</v>
+        <v>721.65</v>
       </c>
       <c r="H236" t="n">
-        <v>358.5209</v>
+        <v>709.2702</v>
       </c>
       <c r="I236" t="n">
-        <v>352.193</v>
+        <v>705.3844</v>
       </c>
       <c r="J236" t="n">
-        <v>68.3</v>
+        <v>62.5</v>
       </c>
       <c r="K236" t="n">
-        <v>12.3</v>
+        <v>17.2</v>
       </c>
       <c r="L236" t="n">
-        <v>1.249</v>
+        <v>2.1995</v>
       </c>
       <c r="M236" s="6" t="inlineStr">
         <is>
@@ -15227,12 +15332,12 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>LU2109787635</t>
+          <t>IE00B5BMR087</t>
         </is>
       </c>
     </row>
@@ -15242,46 +15347,46 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>WATC.SW</t>
+          <t>WOEE.DE</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Amundi MSCI Water UCITS ETF Acc</t>
+          <t>iShares World Equity Enhanced Active UCITS ETF USD</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Azionari Tematici</t>
+          <t>Azionari Sviluppati</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Svizzera</t>
+          <t>Francoforte</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>6.746</v>
+        <v>6.398</v>
       </c>
       <c r="H237" t="n">
-        <v>6.546</v>
+        <v>6.2833</v>
       </c>
       <c r="I237" t="n">
-        <v>6.3875</v>
+        <v>6.2401</v>
       </c>
       <c r="J237" t="n">
-        <v>68.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K237" t="n">
-        <v>23.6</v>
+        <v>18.3</v>
       </c>
       <c r="L237" t="n">
-        <v>0.0146</v>
+        <v>0.0187</v>
       </c>
       <c r="M237" s="6" t="inlineStr">
         <is>
@@ -15290,262 +15395,10 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>2026-08-07 07:59</t>
+          <t>2026-08-07 10:34</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
-        <is>
-          <t>FR0014002CH1</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>3</v>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>CSBGU7.SW</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>iShares VII PLC - iShares VII PLC - iShares $ Trea</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>Obbligazionari Governo</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>Svizzera</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G238" t="n">
-        <v>142.75</v>
-      </c>
-      <c r="H238" t="n">
-        <v>142.6971</v>
-      </c>
-      <c r="I238" t="n">
-        <v>142.7938</v>
-      </c>
-      <c r="J238" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="K238" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L238" t="n">
-        <v>0.0455</v>
-      </c>
-      <c r="M238" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="N238" t="inlineStr">
-        <is>
-          <t>2026-08-07 07:59</t>
-        </is>
-      </c>
-      <c r="O238" t="inlineStr">
-        <is>
-          <t>IE00B3VWN393</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>3</v>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>LVO.MI</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Amundi S&amp;P 500 VIX Futures Enhanced Roll UCITS ETF</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>Azionari Alternativi</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G239" t="n">
-        <v>0.6694</v>
-      </c>
-      <c r="H239" t="n">
-        <v>0.6852</v>
-      </c>
-      <c r="I239" t="n">
-        <v>0.7030999999999999</v>
-      </c>
-      <c r="J239" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="K239" t="n">
-        <v>12</v>
-      </c>
-      <c r="L239" t="n">
-        <v>-0.0014</v>
-      </c>
-      <c r="M239" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>2026-08-07 07:59</t>
-        </is>
-      </c>
-      <c r="O239" t="inlineStr">
-        <is>
-          <t>LU0832435464</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>3</v>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>CSSPX.MI</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>Azionari USA</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G240" t="n">
-        <v>721.65</v>
-      </c>
-      <c r="H240" t="n">
-        <v>708.9444</v>
-      </c>
-      <c r="I240" t="n">
-        <v>703.2442</v>
-      </c>
-      <c r="J240" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="K240" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="L240" t="n">
-        <v>1.8993</v>
-      </c>
-      <c r="M240" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr">
-        <is>
-          <t>2026-08-07 07:59</t>
-        </is>
-      </c>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>IE00B5BMR087</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>3</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>WOEE.DE</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>iShares World Equity Enhanced Active UCITS ETF USD</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Azionari Sviluppati</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>Francoforte</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G241" t="n">
-        <v>6.398</v>
-      </c>
-      <c r="H241" t="n">
-        <v>6.2805</v>
-      </c>
-      <c r="I241" t="n">
-        <v>6.2199</v>
-      </c>
-      <c r="J241" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="K241" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="M241" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr">
-        <is>
-          <t>2026-08-07 07:59</t>
-        </is>
-      </c>
-      <c r="O241" t="inlineStr">
         <is>
           <t>IE000D8XC064</t>
         </is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>159.94</v>
+        <v>160.26</v>
       </c>
       <c r="H2" t="n">
-        <v>162.5284</v>
+        <v>162.9448</v>
       </c>
       <c r="I2" t="n">
-        <v>178.045</v>
+        <v>179.0125</v>
       </c>
       <c r="J2" t="n">
-        <v>45.2</v>
+        <v>45.9</v>
       </c>
       <c r="K2" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6006</v>
+        <v>1.4753</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>49.275</v>
+        <v>48.395</v>
       </c>
       <c r="H3" t="n">
-        <v>48.9867</v>
+        <v>48.8939</v>
       </c>
       <c r="I3" t="n">
-        <v>50.0463</v>
+        <v>49.6129</v>
       </c>
       <c r="J3" t="n">
-        <v>50.6</v>
+        <v>45.4</v>
       </c>
       <c r="K3" t="n">
-        <v>13.8</v>
+        <v>17.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.016</v>
+        <v>-0.0562</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>140.54</v>
+        <v>140.32</v>
       </c>
       <c r="H4" t="n">
-        <v>133.5105</v>
+        <v>133.8067</v>
       </c>
       <c r="I4" t="n">
-        <v>131.3212</v>
+        <v>134.5864</v>
       </c>
       <c r="J4" t="n">
-        <v>68.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="K4" t="n">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4364</v>
+        <v>1.5516</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -758,22 +758,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.931</v>
+        <v>2.938</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8624</v>
+        <v>2.8584</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7975</v>
+        <v>2.7603</v>
       </c>
       <c r="J5" t="n">
-        <v>62.2</v>
+        <v>63.1</v>
       </c>
       <c r="K5" t="n">
-        <v>23.4</v>
+        <v>21.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0102</v>
+        <v>0.0073</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -821,22 +821,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>25.32</v>
+        <v>24.935</v>
       </c>
       <c r="H6" t="n">
-        <v>25.4537</v>
+        <v>25.4148</v>
       </c>
       <c r="I6" t="n">
-        <v>24.9004</v>
+        <v>24.7931</v>
       </c>
       <c r="J6" t="n">
-        <v>49.5</v>
+        <v>44</v>
       </c>
       <c r="K6" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0609</v>
+        <v>-0.0762</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>209.15</v>
+        <v>209.1</v>
       </c>
       <c r="H7" t="n">
-        <v>201.8023</v>
+        <v>201.9889</v>
       </c>
       <c r="I7" t="n">
-        <v>198.828</v>
+        <v>201.0564</v>
       </c>
       <c r="J7" t="n">
-        <v>69.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="K7" t="n">
-        <v>19.2</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3952</v>
+        <v>1.4586</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>499.85</v>
+        <v>498.8</v>
       </c>
       <c r="H8" t="n">
-        <v>502.295</v>
+        <v>501.742</v>
       </c>
       <c r="I8" t="n">
-        <v>484.578</v>
+        <v>485.072</v>
       </c>
       <c r="J8" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="K8" t="n">
-        <v>33.8</v>
+        <v>22.2</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.846</v>
+        <v>-2.9364</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1013,19 +1013,19 @@
         <v>42.72</v>
       </c>
       <c r="H9" t="n">
-        <v>42.5591</v>
+        <v>42.5963</v>
       </c>
       <c r="I9" t="n">
-        <v>44.4363</v>
+        <v>44.3056</v>
       </c>
       <c r="J9" t="n">
         <v>48.6</v>
       </c>
       <c r="K9" t="n">
-        <v>22.4</v>
+        <v>17.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2385</v>
+        <v>0.2228</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>106.16</v>
+        <v>105.5</v>
       </c>
       <c r="H10" t="n">
-        <v>104.8416</v>
+        <v>104.8408</v>
       </c>
       <c r="I10" t="n">
-        <v>102.166</v>
+        <v>103.1195</v>
       </c>
       <c r="J10" t="n">
-        <v>57.2</v>
+        <v>53.5</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0454</v>
+        <v>-0.0095</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1136,22 +1136,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>47.385</v>
+        <v>47.49</v>
       </c>
       <c r="H11" t="n">
-        <v>45.8944</v>
+        <v>45.8868</v>
       </c>
       <c r="I11" t="n">
-        <v>44.4644</v>
+        <v>44.4256</v>
       </c>
       <c r="J11" t="n">
-        <v>71.3</v>
+        <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>29.1</v>
+        <v>27.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1818</v>
+        <v>0.1744</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1199,22 +1199,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>52.51</v>
+        <v>52.63</v>
       </c>
       <c r="H12" t="n">
-        <v>52.0314</v>
+        <v>52.1748</v>
       </c>
       <c r="I12" t="n">
-        <v>52.7566</v>
+        <v>53.9139</v>
       </c>
       <c r="J12" t="n">
-        <v>52.1</v>
+        <v>51.1</v>
       </c>
       <c r="K12" t="n">
-        <v>19.7</v>
+        <v>16.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.189</v>
+        <v>0.2615</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>39.21</v>
+        <v>39.345</v>
       </c>
       <c r="H13" t="n">
-        <v>39.3615</v>
+        <v>39.3844</v>
       </c>
       <c r="I13" t="n">
-        <v>41.0084</v>
+        <v>40.7794</v>
       </c>
       <c r="J13" t="n">
-        <v>46.9</v>
+        <v>48.3</v>
       </c>
       <c r="K13" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="L13" t="n">
-        <v>0.194</v>
+        <v>0.1656</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1325,22 +1325,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>103.78</v>
+        <v>104.32</v>
       </c>
       <c r="H14" t="n">
-        <v>104.5729</v>
+        <v>104.5374</v>
       </c>
       <c r="I14" t="n">
-        <v>104.7524</v>
+        <v>103.9662</v>
       </c>
       <c r="J14" t="n">
-        <v>44.4</v>
+        <v>48.8</v>
       </c>
       <c r="K14" t="n">
-        <v>15.1</v>
+        <v>13.5</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2331</v>
+        <v>-0.2398</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1388,22 +1388,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>220.64</v>
+        <v>222.34</v>
       </c>
       <c r="H15" t="n">
-        <v>215.758</v>
+        <v>215.7998</v>
       </c>
       <c r="I15" t="n">
-        <v>215.5216</v>
+        <v>214.0482</v>
       </c>
       <c r="J15" t="n">
-        <v>61.7</v>
+        <v>63.6</v>
       </c>
       <c r="K15" t="n">
-        <v>12.9</v>
+        <v>10.6</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9101</v>
+        <v>0.8882</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1451,22 +1451,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>623.03</v>
+        <v>625.66</v>
       </c>
       <c r="H16" t="n">
-        <v>613.4462</v>
+        <v>613.3434</v>
       </c>
       <c r="I16" t="n">
-        <v>614.4682</v>
+        <v>610.9178000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>57.5</v>
+        <v>58.9</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3115</v>
+        <v>1.1285</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1514,22 +1514,22 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>15.008</v>
+        <v>15.504</v>
       </c>
       <c r="H17" t="n">
-        <v>14.4265</v>
+        <v>14.4834</v>
       </c>
       <c r="I17" t="n">
-        <v>14.3818</v>
+        <v>14.4972</v>
       </c>
       <c r="J17" t="n">
-        <v>65.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="K17" t="n">
-        <v>17.9</v>
+        <v>23.1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1145</v>
+        <v>0.151</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1577,22 +1577,22 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>72.994</v>
+        <v>73.304</v>
       </c>
       <c r="H18" t="n">
-        <v>72.8548</v>
+        <v>72.9074</v>
       </c>
       <c r="I18" t="n">
-        <v>74.703</v>
+        <v>74.5592</v>
       </c>
       <c r="J18" t="n">
-        <v>49.2</v>
+        <v>50.8</v>
       </c>
       <c r="K18" t="n">
-        <v>15.1</v>
+        <v>17.1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3068</v>
+        <v>0.2863</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1640,22 +1640,22 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>98.90000000000001</v>
+        <v>99.38</v>
       </c>
       <c r="H19" t="n">
-        <v>98.7308</v>
+        <v>98.8079</v>
       </c>
       <c r="I19" t="n">
-        <v>101.2544</v>
+        <v>101.055</v>
       </c>
       <c r="J19" t="n">
-        <v>49.1</v>
+        <v>50.9</v>
       </c>
       <c r="K19" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4118</v>
+        <v>0.3875</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7.492</v>
+        <v>7.5248</v>
       </c>
       <c r="H20" t="n">
-        <v>7.4768</v>
+        <v>7.4824</v>
       </c>
       <c r="I20" t="n">
-        <v>7.6716</v>
+        <v>7.6564</v>
       </c>
       <c r="J20" t="n">
-        <v>49.2</v>
+        <v>50.8</v>
       </c>
       <c r="K20" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0323</v>
+        <v>0.0305</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1766,22 +1766,22 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>150.13</v>
+        <v>151.09</v>
       </c>
       <c r="H21" t="n">
-        <v>146.6907</v>
+        <v>146.7033</v>
       </c>
       <c r="I21" t="n">
-        <v>146.4499</v>
+        <v>145.4437</v>
       </c>
       <c r="J21" t="n">
-        <v>62</v>
+        <v>63.5</v>
       </c>
       <c r="K21" t="n">
-        <v>13.1</v>
+        <v>10.8</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6281</v>
+        <v>0.6001</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1829,22 +1829,22 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>74.83</v>
+        <v>75.06</v>
       </c>
       <c r="H22" t="n">
-        <v>72.9843</v>
+        <v>72.88209999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>70.9622</v>
+        <v>69.7135</v>
       </c>
       <c r="J22" t="n">
-        <v>64.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="K22" t="n">
-        <v>26.5</v>
+        <v>21.5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2137</v>
+        <v>0.1348</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1892,22 +1892,22 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7.189</v>
+        <v>7.222</v>
       </c>
       <c r="H23" t="n">
-        <v>7.1877</v>
+        <v>7.1937</v>
       </c>
       <c r="I23" t="n">
-        <v>7.3886</v>
+        <v>7.3753</v>
       </c>
       <c r="J23" t="n">
-        <v>48.4</v>
+        <v>50.1</v>
       </c>
       <c r="K23" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0301</v>
+        <v>0.028</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1955,22 +1955,22 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>258.75</v>
+        <v>259.05</v>
       </c>
       <c r="H24" t="n">
-        <v>253.2644</v>
+        <v>253.8154</v>
       </c>
       <c r="I24" t="n">
-        <v>251.242</v>
+        <v>251.51</v>
       </c>
       <c r="J24" t="n">
-        <v>66.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7179</v>
+        <v>0.7809</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2018,22 +2018,22 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>359.51</v>
+        <v>362.39</v>
       </c>
       <c r="H25" t="n">
-        <v>354.2401</v>
+        <v>354.265</v>
       </c>
       <c r="I25" t="n">
-        <v>357.9028</v>
+        <v>354.309</v>
       </c>
       <c r="J25" t="n">
-        <v>55.6</v>
+        <v>58.4</v>
       </c>
       <c r="K25" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4257</v>
+        <v>1.2827</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2081,22 +2081,22 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>97.68000000000001</v>
+        <v>98.14</v>
       </c>
       <c r="H26" t="n">
-        <v>97.56180000000001</v>
+        <v>97.6337</v>
       </c>
       <c r="I26" t="n">
-        <v>99.76739999999999</v>
+        <v>99.5552</v>
       </c>
       <c r="J26" t="n">
-        <v>49.1</v>
+        <v>50.9</v>
       </c>
       <c r="K26" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3603</v>
+        <v>0.3368</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2144,22 +2144,22 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>35.32</v>
+        <v>35.185</v>
       </c>
       <c r="H27" t="n">
-        <v>34.7432</v>
+        <v>34.7782</v>
       </c>
       <c r="I27" t="n">
-        <v>34.0601</v>
+        <v>34.6829</v>
       </c>
       <c r="J27" t="n">
-        <v>58.7</v>
+        <v>55.2</v>
       </c>
       <c r="K27" t="n">
-        <v>20.7</v>
+        <v>14.6</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.0329</v>
+        <v>0.0032</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2207,22 +2207,22 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>124.15</v>
+        <v>125.28</v>
       </c>
       <c r="H28" t="n">
-        <v>124.0728</v>
+        <v>124.2789</v>
       </c>
       <c r="I28" t="n">
-        <v>128.2117</v>
+        <v>128.4711</v>
       </c>
       <c r="J28" t="n">
-        <v>48.5</v>
+        <v>50.8</v>
       </c>
       <c r="K28" t="n">
-        <v>16.9</v>
+        <v>12.3</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6912</v>
+        <v>0.716</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2270,22 +2270,22 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>58.07</v>
+        <v>58.29</v>
       </c>
       <c r="H29" t="n">
-        <v>56.3533</v>
+        <v>56.385</v>
       </c>
       <c r="I29" t="n">
-        <v>55.3324</v>
+        <v>55.3538</v>
       </c>
       <c r="J29" t="n">
-        <v>72.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K29" t="n">
-        <v>24.5</v>
+        <v>18.8</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2215</v>
+        <v>0.2341</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2333,22 +2333,22 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>478.3</v>
+        <v>479</v>
       </c>
       <c r="H30" t="n">
-        <v>471.9337</v>
+        <v>471.5696</v>
       </c>
       <c r="I30" t="n">
-        <v>462.61</v>
+        <v>458.9294</v>
       </c>
       <c r="J30" t="n">
-        <v>71.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K30" t="n">
-        <v>34.2</v>
+        <v>41.2</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4038</v>
+        <v>0.1771</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2396,22 +2396,22 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>402.85</v>
+        <v>402.9</v>
       </c>
       <c r="H31" t="n">
-        <v>388.697</v>
+        <v>388.0148</v>
       </c>
       <c r="I31" t="n">
-        <v>378.052</v>
+        <v>370.8588</v>
       </c>
       <c r="J31" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="K31" t="n">
-        <v>26.2</v>
+        <v>21.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.9985</v>
+        <v>1.4543</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2459,22 +2459,22 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>25.075</v>
+        <v>25.23</v>
       </c>
       <c r="H32" t="n">
-        <v>24.4763</v>
+        <v>24.4896</v>
       </c>
       <c r="I32" t="n">
-        <v>23.794</v>
+        <v>23.7925</v>
       </c>
       <c r="J32" t="n">
-        <v>77.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>43.4</v>
+        <v>39.9</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0702</v>
+        <v>0.0766</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2522,22 +2522,22 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>193.9</v>
+        <v>195.11</v>
       </c>
       <c r="H33" t="n">
-        <v>194.2662</v>
+        <v>194.4535</v>
       </c>
       <c r="I33" t="n">
-        <v>199.9116</v>
+        <v>199.4596</v>
       </c>
       <c r="J33" t="n">
-        <v>47.8</v>
+        <v>49.9</v>
       </c>
       <c r="K33" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="L33" t="n">
-        <v>0.7875</v>
+        <v>0.7448</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2585,22 +2585,22 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>7.419</v>
+        <v>7.431</v>
       </c>
       <c r="H34" t="n">
-        <v>7.4296</v>
+        <v>7.434</v>
       </c>
       <c r="I34" t="n">
-        <v>7.6523</v>
+        <v>7.6429</v>
       </c>
       <c r="J34" t="n">
-        <v>47.9</v>
+        <v>48.8</v>
       </c>
       <c r="K34" t="n">
-        <v>15.1</v>
+        <v>10.5</v>
       </c>
       <c r="L34" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2648,22 +2648,22 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>72.14</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>71.0098</v>
+        <v>70.9828</v>
       </c>
       <c r="I35" t="n">
-        <v>70.4986</v>
+        <v>69.68210000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>59.7</v>
+        <v>62.4</v>
       </c>
       <c r="K35" t="n">
-        <v>15.7</v>
+        <v>22</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1796</v>
+        <v>0.1541</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2711,22 +2711,22 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>158.06</v>
+        <v>158.34</v>
       </c>
       <c r="H36" t="n">
-        <v>153.9353</v>
+        <v>153.8635</v>
       </c>
       <c r="I36" t="n">
-        <v>152.3692</v>
+        <v>151.3472</v>
       </c>
       <c r="J36" t="n">
-        <v>66.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="L36" t="n">
-        <v>0.9071</v>
+        <v>0.8433</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2774,22 +2774,22 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>96.95</v>
+        <v>97.34</v>
       </c>
       <c r="H37" t="n">
-        <v>97.0891</v>
+        <v>96.9978</v>
       </c>
       <c r="I37" t="n">
-        <v>96.3214</v>
+        <v>95.16160000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>50.1</v>
+        <v>52.8</v>
       </c>
       <c r="K37" t="n">
-        <v>13</v>
+        <v>17.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.1473</v>
+        <v>-0.1888</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2837,22 +2837,22 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>69.41</v>
+        <v>69.91</v>
       </c>
       <c r="H38" t="n">
-        <v>68.86620000000001</v>
+        <v>68.90389999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>70.3866</v>
+        <v>69.9374</v>
       </c>
       <c r="J38" t="n">
-        <v>51.7</v>
+        <v>54.5</v>
       </c>
       <c r="K38" t="n">
-        <v>12.9</v>
+        <v>14.9</v>
       </c>
       <c r="L38" t="n">
-        <v>0.301</v>
+        <v>0.2787</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>69.41</v>
+        <v>69.86</v>
       </c>
       <c r="H39" t="n">
-        <v>68.9303</v>
+        <v>69.0073</v>
       </c>
       <c r="I39" t="n">
-        <v>70.5958</v>
+        <v>70.5052</v>
       </c>
       <c r="J39" t="n">
-        <v>51.2</v>
+        <v>53.1</v>
       </c>
       <c r="K39" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="L39" t="n">
-        <v>0.341</v>
+        <v>0.3536</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2963,22 +2963,22 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>345.45</v>
+        <v>346.9</v>
       </c>
       <c r="H40" t="n">
-        <v>345.2244</v>
+        <v>345.0831</v>
       </c>
       <c r="I40" t="n">
-        <v>340.259</v>
+        <v>337.5666</v>
       </c>
       <c r="J40" t="n">
-        <v>52.9</v>
+        <v>56</v>
       </c>
       <c r="K40" t="n">
-        <v>20.2</v>
+        <v>17.4</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.2146</v>
+        <v>-0.2714</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3026,22 +3026,22 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>720.1</v>
+        <v>720</v>
       </c>
       <c r="H41" t="n">
-        <v>712.1966</v>
+        <v>711.9295</v>
       </c>
       <c r="I41" t="n">
-        <v>705.748</v>
+        <v>704.792</v>
       </c>
       <c r="J41" t="n">
-        <v>61.1</v>
+        <v>60</v>
       </c>
       <c r="K41" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="L41" t="n">
-        <v>0.8114</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3089,22 +3089,22 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>448.35</v>
+        <v>448.25</v>
       </c>
       <c r="H42" t="n">
-        <v>442.6334</v>
+        <v>442.6686</v>
       </c>
       <c r="I42" t="n">
-        <v>441.066</v>
+        <v>441.3612</v>
       </c>
       <c r="J42" t="n">
-        <v>63.3</v>
+        <v>61.5</v>
       </c>
       <c r="K42" t="n">
-        <v>17.2</v>
+        <v>21.1</v>
       </c>
       <c r="L42" t="n">
-        <v>1.2923</v>
+        <v>1.2123</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3152,22 +3152,22 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>197.44</v>
+        <v>197.7</v>
       </c>
       <c r="H43" t="n">
-        <v>194.0736</v>
+        <v>193.9403</v>
       </c>
       <c r="I43" t="n">
-        <v>190.5228</v>
+        <v>188.9804</v>
       </c>
       <c r="J43" t="n">
-        <v>68.3</v>
+        <v>69</v>
       </c>
       <c r="K43" t="n">
-        <v>28.4</v>
+        <v>35.4</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4152</v>
+        <v>0.3116</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Parigi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3215,22 +3215,22 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>251.95</v>
+        <v>252.05</v>
       </c>
       <c r="H44" t="n">
-        <v>248.0287</v>
+        <v>247.8451</v>
       </c>
       <c r="I44" t="n">
-        <v>245.822</v>
+        <v>244.1128</v>
       </c>
       <c r="J44" t="n">
-        <v>68.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>20.2</v>
+        <v>28.5</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5596</v>
+        <v>0.4157</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3278,22 +3278,22 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>126.68</v>
+        <v>126.78</v>
       </c>
       <c r="H45" t="n">
-        <v>124.7188</v>
+        <v>124.6297</v>
       </c>
       <c r="I45" t="n">
-        <v>123.6012</v>
+        <v>122.726</v>
       </c>
       <c r="J45" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>19.7</v>
+        <v>25.6</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2704</v>
+        <v>0.2005</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3344,19 +3344,19 @@
         <v>55.07</v>
       </c>
       <c r="H46" t="n">
-        <v>53.8933</v>
+        <v>53.849</v>
       </c>
       <c r="I46" t="n">
-        <v>53.4528</v>
+        <v>53.062</v>
       </c>
       <c r="J46" t="n">
-        <v>64.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>17.7</v>
+        <v>14.3</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2012</v>
+        <v>0.1589</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3404,22 +3404,22 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>99.65000000000001</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>98.20489999999999</v>
+        <v>98.1523</v>
       </c>
       <c r="I47" t="n">
-        <v>97.75839999999999</v>
+        <v>97.0566</v>
       </c>
       <c r="J47" t="n">
-        <v>65.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="K47" t="n">
-        <v>18.1</v>
+        <v>24.8</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2429</v>
+        <v>0.1897</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3467,22 +3467,22 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>453</v>
+        <v>453.85</v>
       </c>
       <c r="H48" t="n">
-        <v>445.9883</v>
+        <v>445.7298</v>
       </c>
       <c r="I48" t="n">
-        <v>442.12</v>
+        <v>439.078</v>
       </c>
       <c r="J48" t="n">
         <v>68.5</v>
       </c>
       <c r="K48" t="n">
-        <v>20.1</v>
+        <v>26.4</v>
       </c>
       <c r="L48" t="n">
-        <v>0.9779</v>
+        <v>0.7556</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3530,22 +3530,22 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>391.4</v>
+        <v>393.97</v>
       </c>
       <c r="H49" t="n">
-        <v>389.8288</v>
+        <v>389.7282</v>
       </c>
       <c r="I49" t="n">
-        <v>392.5368</v>
+        <v>387.807</v>
       </c>
       <c r="J49" t="n">
-        <v>52.3</v>
+        <v>57.2</v>
       </c>
       <c r="K49" t="n">
-        <v>14.2</v>
+        <v>13</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7624</v>
+        <v>0.516</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3593,22 +3593,22 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6.851</v>
+        <v>6.857</v>
       </c>
       <c r="H50" t="n">
-        <v>6.737</v>
+        <v>6.7327</v>
       </c>
       <c r="I50" t="n">
-        <v>6.6779</v>
+        <v>6.6324</v>
       </c>
       <c r="J50" t="n">
-        <v>68.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0161</v>
+        <v>0.0125</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3656,22 +3656,22 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>31.265</v>
+        <v>31.33</v>
       </c>
       <c r="H51" t="n">
-        <v>30.9954</v>
+        <v>30.9763</v>
       </c>
       <c r="I51" t="n">
-        <v>30.9611</v>
+        <v>30.7165</v>
       </c>
       <c r="J51" t="n">
-        <v>59.8</v>
+        <v>61.8</v>
       </c>
       <c r="K51" t="n">
-        <v>15.3</v>
+        <v>25.5</v>
       </c>
       <c r="L51" t="n">
-        <v>0.0447</v>
+        <v>0.0256</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3719,22 +3719,22 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>42.85</v>
+        <v>42.885</v>
       </c>
       <c r="H52" t="n">
-        <v>42.4977</v>
+        <v>42.4643</v>
       </c>
       <c r="I52" t="n">
-        <v>42.4747</v>
+        <v>42.1229</v>
       </c>
       <c r="J52" t="n">
-        <v>58.7</v>
+        <v>59.8</v>
       </c>
       <c r="K52" t="n">
-        <v>13.1</v>
+        <v>17.1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.062</v>
+        <v>0.0312</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3782,22 +3782,22 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>155.4</v>
+        <v>155.06</v>
       </c>
       <c r="H53" t="n">
-        <v>154.4778</v>
+        <v>154.1889</v>
       </c>
       <c r="I53" t="n">
-        <v>154.8696</v>
+        <v>152.7297</v>
       </c>
       <c r="J53" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="K53" t="n">
-        <v>16.7</v>
+        <v>11.3</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.1338</v>
+        <v>-0.2802</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3845,22 +3845,22 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>132.9</v>
+        <v>132.78</v>
       </c>
       <c r="H54" t="n">
-        <v>130.0673</v>
+        <v>129.9458</v>
       </c>
       <c r="I54" t="n">
-        <v>129.8708</v>
+        <v>128.828</v>
       </c>
       <c r="J54" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="K54" t="n">
-        <v>16.2</v>
+        <v>15.1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.541</v>
+        <v>0.4142</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3908,22 +3908,22 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>127.42</v>
+        <v>127.68</v>
       </c>
       <c r="H55" t="n">
-        <v>125.1567</v>
+        <v>125.0653</v>
       </c>
       <c r="I55" t="n">
-        <v>124.498</v>
+        <v>123.4252</v>
       </c>
       <c r="J55" t="n">
-        <v>66.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>22</v>
+        <v>19.7</v>
       </c>
       <c r="L55" t="n">
-        <v>0.3404</v>
+        <v>0.2739</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -3971,22 +3971,22 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>110.54</v>
+        <v>111.11</v>
       </c>
       <c r="H56" t="n">
-        <v>109.1056</v>
+        <v>109.217</v>
       </c>
       <c r="I56" t="n">
-        <v>114.1372</v>
+        <v>113.4906</v>
       </c>
       <c r="J56" t="n">
-        <v>51.1</v>
+        <v>52.1</v>
       </c>
       <c r="K56" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="L56" t="n">
-        <v>0.7703</v>
+        <v>0.6701</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4034,22 +4034,22 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>132.56</v>
+        <v>132.8</v>
       </c>
       <c r="H57" t="n">
-        <v>129.9891</v>
+        <v>129.9027</v>
       </c>
       <c r="I57" t="n">
-        <v>129.8384</v>
+        <v>128.8128</v>
       </c>
       <c r="J57" t="n">
-        <v>61.4</v>
+        <v>62.3</v>
       </c>
       <c r="K57" t="n">
-        <v>17.1</v>
+        <v>13.9</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5285</v>
+        <v>0.4257</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4097,22 +4097,22 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>74.23999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>72.4902</v>
+        <v>72.4389</v>
       </c>
       <c r="I58" t="n">
-        <v>71.754</v>
+        <v>71.2118</v>
       </c>
       <c r="J58" t="n">
-        <v>68.8</v>
+        <v>68.2</v>
       </c>
       <c r="K58" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2984</v>
+        <v>0.2486</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4160,22 +4160,22 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>43.79</v>
+        <v>43.805</v>
       </c>
       <c r="H59" t="n">
-        <v>42.627</v>
+        <v>42.604</v>
       </c>
       <c r="I59" t="n">
-        <v>42.293</v>
+        <v>42.049</v>
       </c>
       <c r="J59" t="n">
-        <v>68.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2014</v>
+        <v>0.1713</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4223,22 +4223,22 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>429.65</v>
+        <v>429.7</v>
       </c>
       <c r="H60" t="n">
-        <v>421.6612</v>
+        <v>421.4007</v>
       </c>
       <c r="I60" t="n">
-        <v>421.192</v>
+        <v>418.58</v>
       </c>
       <c r="J60" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="K60" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="L60" t="n">
-        <v>1.5525</v>
+        <v>1.1821</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4286,22 +4286,22 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>473.85</v>
+        <v>473.3</v>
       </c>
       <c r="H61" t="n">
-        <v>467.7272</v>
+        <v>467.1779</v>
       </c>
       <c r="I61" t="n">
-        <v>465.156</v>
+        <v>460.724</v>
       </c>
       <c r="J61" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="K61" t="n">
-        <v>19.1</v>
+        <v>24.6</v>
       </c>
       <c r="L61" t="n">
-        <v>1.279</v>
+        <v>0.8396</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4349,22 +4349,22 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.171</v>
+        <v>5.184</v>
       </c>
       <c r="H62" t="n">
-        <v>5.1093</v>
+        <v>5.1004</v>
       </c>
       <c r="I62" t="n">
-        <v>5.0897</v>
+        <v>5.029</v>
       </c>
       <c r="J62" t="n">
-        <v>55.8</v>
+        <v>63.4</v>
       </c>
       <c r="K62" t="n">
-        <v>5.3</v>
+        <v>16.9</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0107</v>
+        <v>0.0067</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4412,22 +4412,22 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>220.05</v>
+        <v>220.55</v>
       </c>
       <c r="H63" t="n">
-        <v>216.32</v>
+        <v>216.2319</v>
       </c>
       <c r="I63" t="n">
-        <v>216.77</v>
+        <v>215.553</v>
       </c>
       <c r="J63" t="n">
-        <v>62.7</v>
+        <v>63.2</v>
       </c>
       <c r="K63" t="n">
-        <v>16.5</v>
+        <v>19.7</v>
       </c>
       <c r="L63" t="n">
-        <v>0.7613</v>
+        <v>0.6532</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4475,22 +4475,22 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>93.3</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>92.158</v>
+        <v>92.1229</v>
       </c>
       <c r="I64" t="n">
-        <v>92.1114</v>
+        <v>91.5598</v>
       </c>
       <c r="J64" t="n">
-        <v>61</v>
+        <v>62.5</v>
       </c>
       <c r="K64" t="n">
-        <v>16.2</v>
+        <v>17.5</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2357</v>
+        <v>0.197</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4538,22 +4538,22 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>43.235</v>
+        <v>43.325</v>
       </c>
       <c r="H65" t="n">
-        <v>43.8489</v>
+        <v>43.8211</v>
       </c>
       <c r="I65" t="n">
-        <v>43.5144</v>
+        <v>43.1877</v>
       </c>
       <c r="J65" t="n">
-        <v>39.3</v>
+        <v>43</v>
       </c>
       <c r="K65" t="n">
-        <v>23.6</v>
+        <v>22</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.1841</v>
+        <v>-0.1992</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4601,22 +4601,22 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>173.65</v>
+        <v>174.52</v>
       </c>
       <c r="H66" t="n">
-        <v>171.5135</v>
+        <v>171.6288</v>
       </c>
       <c r="I66" t="n">
-        <v>176.8936</v>
+        <v>175.4448</v>
       </c>
       <c r="J66" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K66" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="L66" t="n">
-        <v>0.6687</v>
+        <v>0.5723</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4667,19 +4667,19 @@
         <v>72.56</v>
       </c>
       <c r="H67" t="n">
-        <v>71.4521</v>
+        <v>71.55759999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>71.093</v>
+        <v>71.1482</v>
       </c>
       <c r="J67" t="n">
         <v>66</v>
       </c>
       <c r="K67" t="n">
-        <v>11.1</v>
+        <v>12</v>
       </c>
       <c r="L67" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1065</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>611.17</v>
+        <v>613.1799999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>601.8444</v>
+        <v>601.8099</v>
       </c>
       <c r="I68" t="n">
-        <v>600.3972</v>
+        <v>598.4139</v>
       </c>
       <c r="J68" t="n">
-        <v>62.9</v>
+        <v>63.9</v>
       </c>
       <c r="K68" t="n">
-        <v>16.8</v>
+        <v>14.7</v>
       </c>
       <c r="L68" t="n">
-        <v>1.8215</v>
+        <v>1.6766</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4790,22 +4790,22 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>170.785</v>
+        <v>171.17</v>
       </c>
       <c r="H69" t="n">
-        <v>170.9144</v>
+        <v>170.9388</v>
       </c>
       <c r="I69" t="n">
-        <v>171.3486</v>
+        <v>171.3316</v>
       </c>
       <c r="J69" t="n">
-        <v>46.1</v>
+        <v>53</v>
       </c>
       <c r="K69" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="L69" t="n">
-        <v>0.016</v>
+        <v>0.0457</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -4853,22 +4853,22 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5.2056</v>
+        <v>5.2116</v>
       </c>
       <c r="H70" t="n">
-        <v>5.2034</v>
+        <v>5.2033</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2171</v>
+        <v>5.2089</v>
       </c>
       <c r="J70" t="n">
-        <v>50.2</v>
+        <v>54.8</v>
       </c>
       <c r="K70" t="n">
-        <v>21.7</v>
+        <v>18.7</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0032</v>
+        <v>0.0029</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -4916,22 +4916,22 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6.272</v>
+        <v>6.271</v>
       </c>
       <c r="H71" t="n">
-        <v>6.1587</v>
+        <v>6.1586</v>
       </c>
       <c r="I71" t="n">
         <v>6.0901</v>
       </c>
       <c r="J71" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="K71" t="n">
         <v>14.9</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0141</v>
+        <v>0.014</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -4979,22 +4979,22 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>153.43</v>
+        <v>153.61</v>
       </c>
       <c r="H72" t="n">
-        <v>153.2602</v>
+        <v>153.2756</v>
       </c>
       <c r="I72" t="n">
-        <v>154.3848</v>
+        <v>154</v>
       </c>
       <c r="J72" t="n">
-        <v>50.1</v>
+        <v>52</v>
       </c>
       <c r="K72" t="n">
-        <v>23.6</v>
+        <v>21.7</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2193</v>
+        <v>0.197</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5042,22 +5042,22 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>512.6799999999999</v>
+        <v>513.3200000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>509.925</v>
+        <v>508.8793</v>
       </c>
       <c r="I73" t="n">
-        <v>505.0452</v>
+        <v>497.576</v>
       </c>
       <c r="J73" t="n">
-        <v>53.7</v>
+        <v>55.8</v>
       </c>
       <c r="K73" t="n">
-        <v>18.4</v>
+        <v>14.8</v>
       </c>
       <c r="L73" t="n">
-        <v>-0.8294</v>
+        <v>-1.3364</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5105,22 +5105,22 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>199.85</v>
+        <v>200.16</v>
       </c>
       <c r="H74" t="n">
-        <v>199.7858</v>
+        <v>199.8235</v>
       </c>
       <c r="I74" t="n">
-        <v>201.3802</v>
+        <v>200.8988</v>
       </c>
       <c r="J74" t="n">
-        <v>48.7</v>
+        <v>51.1</v>
       </c>
       <c r="K74" t="n">
-        <v>22.5</v>
+        <v>21.3</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2566</v>
+        <v>0.2323</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5168,22 +5168,22 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>4.9561</v>
+        <v>4.948</v>
       </c>
       <c r="H75" t="n">
-        <v>4.945</v>
+        <v>4.9403</v>
       </c>
       <c r="I75" t="n">
-        <v>4.966</v>
+        <v>4.9442</v>
       </c>
       <c r="J75" t="n">
-        <v>51.5</v>
+        <v>52.8</v>
       </c>
       <c r="K75" t="n">
-        <v>5.6</v>
+        <v>19.7</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0034</v>
+        <v>0.0014</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5231,22 +5231,22 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>128.32</v>
+        <v>128.65</v>
       </c>
       <c r="H76" t="n">
-        <v>126.1132</v>
+        <v>126.0804</v>
       </c>
       <c r="I76" t="n">
-        <v>125.3218</v>
+        <v>124.845</v>
       </c>
       <c r="J76" t="n">
-        <v>65</v>
+        <v>65.8</v>
       </c>
       <c r="K76" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3641</v>
+        <v>0.3277</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5294,22 +5294,22 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>229.34</v>
+        <v>228.72</v>
       </c>
       <c r="H77" t="n">
-        <v>228.3666</v>
+        <v>228.291</v>
       </c>
       <c r="I77" t="n">
-        <v>228.8394</v>
+        <v>228.5287</v>
       </c>
       <c r="J77" t="n">
-        <v>62</v>
+        <v>54.7</v>
       </c>
       <c r="K77" t="n">
-        <v>23.3</v>
+        <v>18.5</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2324</v>
+        <v>0.1629</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5357,22 +5357,22 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>14.208</v>
+        <v>14.1346</v>
       </c>
       <c r="H78" t="n">
-        <v>13.858</v>
+        <v>13.8125</v>
       </c>
       <c r="I78" t="n">
-        <v>13.6846</v>
+        <v>13.6505</v>
       </c>
       <c r="J78" t="n">
-        <v>71.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>19.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0567</v>
+        <v>0.0481</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5420,22 +5420,22 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>269.1</v>
+        <v>270.6</v>
       </c>
       <c r="H79" t="n">
-        <v>263.9074</v>
+        <v>263.985</v>
       </c>
       <c r="I79" t="n">
-        <v>261.873</v>
+        <v>261.741</v>
       </c>
       <c r="J79" t="n">
-        <v>66.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K79" t="n">
-        <v>19.9</v>
+        <v>17.9</v>
       </c>
       <c r="L79" t="n">
-        <v>0.9585</v>
+        <v>0.9906</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -5483,22 +5483,22 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>54.33</v>
+        <v>54.42</v>
       </c>
       <c r="H80" t="n">
-        <v>54.2933</v>
+        <v>54.2984</v>
       </c>
       <c r="I80" t="n">
-        <v>54.4308</v>
+        <v>54.3631</v>
       </c>
       <c r="J80" t="n">
-        <v>51</v>
+        <v>55.4</v>
       </c>
       <c r="K80" t="n">
-        <v>18.1</v>
+        <v>21</v>
       </c>
       <c r="L80" t="n">
-        <v>0.0363</v>
+        <v>0.035</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -5546,22 +5546,22 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>280.45</v>
+        <v>282.65</v>
       </c>
       <c r="H81" t="n">
-        <v>276.1585</v>
+        <v>276.7342</v>
       </c>
       <c r="I81" t="n">
-        <v>279.312</v>
+        <v>281.395</v>
       </c>
       <c r="J81" t="n">
-        <v>56.8</v>
+        <v>57.5</v>
       </c>
       <c r="K81" t="n">
-        <v>15.3</v>
+        <v>12.7</v>
       </c>
       <c r="L81" t="n">
-        <v>1.424</v>
+        <v>1.7338</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -5609,22 +5609,22 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>152.825</v>
+        <v>153.045</v>
       </c>
       <c r="H82" t="n">
-        <v>152.8169</v>
+        <v>152.8389</v>
       </c>
       <c r="I82" t="n">
-        <v>153.7145</v>
+        <v>153.4197</v>
       </c>
       <c r="J82" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="K82" t="n">
-        <v>21.9</v>
+        <v>24.5</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1544</v>
+        <v>0.1416</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5672,22 +5672,22 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>232.56</v>
+        <v>232.91</v>
       </c>
       <c r="H83" t="n">
-        <v>232.4774</v>
+        <v>232.5086</v>
       </c>
       <c r="I83" t="n">
-        <v>233.6296</v>
+        <v>233.2177</v>
       </c>
       <c r="J83" t="n">
-        <v>49.3</v>
+        <v>52.8</v>
       </c>
       <c r="K83" t="n">
-        <v>22.6</v>
+        <v>16.6</v>
       </c>
       <c r="L83" t="n">
-        <v>0.2272</v>
+        <v>0.2119</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -5735,22 +5735,22 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>137.34</v>
+        <v>137.24</v>
       </c>
       <c r="H84" t="n">
-        <v>137.0697</v>
+        <v>137.0859</v>
       </c>
       <c r="I84" t="n">
-        <v>137.3682</v>
+        <v>137.358</v>
       </c>
       <c r="J84" t="n">
-        <v>54.8</v>
+        <v>52.6</v>
       </c>
       <c r="K84" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0881</v>
+        <v>0.0876</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>45.695</v>
+        <v>45.685</v>
       </c>
       <c r="H85" t="n">
-        <v>45.6066</v>
+        <v>45.6049</v>
       </c>
       <c r="I85" t="n">
-        <v>45.7866</v>
+        <v>45.7148</v>
       </c>
       <c r="J85" t="n">
-        <v>53.9</v>
+        <v>53.4</v>
       </c>
       <c r="K85" t="n">
-        <v>23.4</v>
+        <v>22.4</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0435</v>
+        <v>0.0364</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -5861,22 +5861,22 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>235.04</v>
+        <v>235.33</v>
       </c>
       <c r="H86" t="n">
-        <v>234.9043</v>
+        <v>234.9282</v>
       </c>
       <c r="I86" t="n">
-        <v>235.9214</v>
+        <v>235.5612</v>
       </c>
       <c r="J86" t="n">
-        <v>49.9</v>
+        <v>52.7</v>
       </c>
       <c r="K86" t="n">
-        <v>22.2</v>
+        <v>25.7</v>
       </c>
       <c r="L86" t="n">
-        <v>0.2032</v>
+        <v>0.1894</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -5924,22 +5924,22 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>698.0700000000001</v>
+        <v>699.77</v>
       </c>
       <c r="H87" t="n">
-        <v>686.24</v>
+        <v>686.0562</v>
       </c>
       <c r="I87" t="n">
-        <v>682.0948</v>
+        <v>679.5491</v>
       </c>
       <c r="J87" t="n">
-        <v>64.8</v>
+        <v>65.5</v>
       </c>
       <c r="K87" t="n">
-        <v>18.2</v>
+        <v>16.2</v>
       </c>
       <c r="L87" t="n">
-        <v>1.9668</v>
+        <v>1.765</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -5987,22 +5987,22 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>432.36</v>
+        <v>433.37</v>
       </c>
       <c r="H88" t="n">
-        <v>424.904</v>
+        <v>424.7825</v>
       </c>
       <c r="I88" t="n">
-        <v>422.2584</v>
+        <v>420.651</v>
       </c>
       <c r="J88" t="n">
-        <v>65.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="K88" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="L88" t="n">
-        <v>1.2362</v>
+        <v>1.1061</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6050,22 +6050,22 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>268.41</v>
+        <v>267.94</v>
       </c>
       <c r="H89" t="n">
-        <v>267.4507</v>
+        <v>267.3588</v>
       </c>
       <c r="I89" t="n">
-        <v>267.7801</v>
+        <v>267.3655</v>
       </c>
       <c r="J89" t="n">
-        <v>59.2</v>
+        <v>55.8</v>
       </c>
       <c r="K89" t="n">
-        <v>16.1</v>
+        <v>18</v>
       </c>
       <c r="L89" t="n">
-        <v>0.1884</v>
+        <v>0.1191</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6113,22 +6113,22 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>41.625</v>
+        <v>41.673</v>
       </c>
       <c r="H90" t="n">
-        <v>41.6103</v>
+        <v>41.6154</v>
       </c>
       <c r="I90" t="n">
-        <v>41.8143</v>
+        <v>41.7482</v>
       </c>
       <c r="J90" t="n">
-        <v>49.3</v>
+        <v>51.9</v>
       </c>
       <c r="K90" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0373</v>
+        <v>0.0343</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6176,22 +6176,22 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>7.3818</v>
+        <v>7.391</v>
       </c>
       <c r="H91" t="n">
-        <v>7.3846</v>
+        <v>7.3861</v>
       </c>
       <c r="I91" t="n">
-        <v>7.4432</v>
+        <v>7.4286</v>
       </c>
       <c r="J91" t="n">
-        <v>47.6</v>
+        <v>49.6</v>
       </c>
       <c r="K91" t="n">
-        <v>22.7</v>
+        <v>25.7</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0086</v>
+        <v>0.0078</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6239,22 +6239,22 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>19.144</v>
+        <v>19.192</v>
       </c>
       <c r="H92" t="n">
-        <v>18.8159</v>
+        <v>18.8108</v>
       </c>
       <c r="I92" t="n">
-        <v>18.7004</v>
+        <v>18.6298</v>
       </c>
       <c r="J92" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="K92" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0544</v>
+        <v>0.0489</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6302,22 +6302,22 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>220.29</v>
+        <v>220.48</v>
       </c>
       <c r="H93" t="n">
-        <v>220.3443</v>
+        <v>220.3663</v>
       </c>
       <c r="I93" t="n">
-        <v>221.3882</v>
+        <v>221.0404</v>
       </c>
       <c r="J93" t="n">
-        <v>48.7</v>
+        <v>50.1</v>
       </c>
       <c r="K93" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="L93" t="n">
-        <v>0.1784</v>
+        <v>0.1593</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -6365,22 +6365,22 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>48.98</v>
+        <v>48.975</v>
       </c>
       <c r="H94" t="n">
-        <v>49.0454</v>
+        <v>49.0432</v>
       </c>
       <c r="I94" t="n">
-        <v>49.2951</v>
+        <v>49.199</v>
       </c>
       <c r="J94" t="n">
-        <v>44.7</v>
+        <v>45.7</v>
       </c>
       <c r="K94" t="n">
-        <v>20.4</v>
+        <v>18.3</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0266</v>
+        <v>0.0181</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -6428,22 +6428,22 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>55.28</v>
+        <v>55.34</v>
       </c>
       <c r="H95" t="n">
-        <v>55.2355</v>
+        <v>55.2363</v>
       </c>
       <c r="I95" t="n">
-        <v>55.2952</v>
+        <v>55.2422</v>
       </c>
       <c r="J95" t="n">
-        <v>53.2</v>
+        <v>58.3</v>
       </c>
       <c r="K95" t="n">
-        <v>18.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0265</v>
+        <v>0.0254</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6491,22 +6491,22 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>137.24</v>
+        <v>137.45</v>
       </c>
       <c r="H96" t="n">
-        <v>137.2038</v>
+        <v>137.215</v>
       </c>
       <c r="I96" t="n">
-        <v>137.6715</v>
+        <v>137.4914</v>
       </c>
       <c r="J96" t="n">
-        <v>49.3</v>
+        <v>54</v>
       </c>
       <c r="K96" t="n">
-        <v>21</v>
+        <v>13.8</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0945</v>
+        <v>0.0898</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6554,22 +6554,22 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>22.705</v>
+        <v>22.745</v>
       </c>
       <c r="H97" t="n">
-        <v>22.6254</v>
+        <v>22.6368</v>
       </c>
       <c r="I97" t="n">
-        <v>22.6441</v>
+        <v>22.646</v>
       </c>
       <c r="J97" t="n">
-        <v>55.5</v>
+        <v>58</v>
       </c>
       <c r="K97" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="L97" t="n">
-        <v>0.0122</v>
+        <v>0.0177</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -6617,22 +6617,22 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>24.255</v>
+        <v>24.735</v>
       </c>
       <c r="H98" t="n">
-        <v>24.0329</v>
+        <v>24.0966</v>
       </c>
       <c r="I98" t="n">
-        <v>25.0126</v>
+        <v>25.0595</v>
       </c>
       <c r="J98" t="n">
-        <v>50.6</v>
+        <v>55.3</v>
       </c>
       <c r="K98" t="n">
-        <v>21</v>
+        <v>21.9</v>
       </c>
       <c r="L98" t="n">
-        <v>0.1695</v>
+        <v>0.1912</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -6680,22 +6680,22 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>197.92</v>
+        <v>198.2</v>
       </c>
       <c r="H99" t="n">
-        <v>193.351</v>
+        <v>193.3098</v>
       </c>
       <c r="I99" t="n">
-        <v>192.4156</v>
+        <v>191.6155</v>
       </c>
       <c r="J99" t="n">
         <v>65.8</v>
       </c>
       <c r="K99" t="n">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="L99" t="n">
-        <v>0.9171</v>
+        <v>0.8353</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -6743,22 +6743,22 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>49.42</v>
+        <v>49.48</v>
       </c>
       <c r="H100" t="n">
-        <v>49.4202</v>
+        <v>49.4265</v>
       </c>
       <c r="I100" t="n">
-        <v>49.6681</v>
+        <v>49.586</v>
       </c>
       <c r="J100" t="n">
-        <v>48.4</v>
+        <v>51.2</v>
       </c>
       <c r="K100" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0422</v>
+        <v>0.0386</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6806,22 +6806,22 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>131.295</v>
+        <v>131.375</v>
       </c>
       <c r="H101" t="n">
-        <v>131.196</v>
+        <v>131.1992</v>
       </c>
       <c r="I101" t="n">
-        <v>131.5264</v>
+        <v>131.3828</v>
       </c>
       <c r="J101" t="n">
-        <v>51.5</v>
+        <v>53.5</v>
       </c>
       <c r="K101" t="n">
-        <v>21.5</v>
+        <v>24.4</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0806</v>
+        <v>0.0728</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -6869,22 +6869,22 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>7.252</v>
+        <v>7.298</v>
       </c>
       <c r="H102" t="n">
-        <v>7.109</v>
+        <v>7.1121</v>
       </c>
       <c r="I102" t="n">
-        <v>7.0507</v>
+        <v>7.0509</v>
       </c>
       <c r="J102" t="n">
-        <v>66.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="K102" t="n">
-        <v>19.2</v>
+        <v>14.3</v>
       </c>
       <c r="L102" t="n">
-        <v>0.0267</v>
+        <v>0.028</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -6932,22 +6932,22 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>141.695</v>
+        <v>141.915</v>
       </c>
       <c r="H103" t="n">
-        <v>141.8501</v>
+        <v>141.9017</v>
       </c>
       <c r="I103" t="n">
-        <v>143.551</v>
+        <v>143.1898</v>
       </c>
       <c r="J103" t="n">
-        <v>47</v>
+        <v>48.7</v>
       </c>
       <c r="K103" t="n">
-        <v>21.6</v>
+        <v>25</v>
       </c>
       <c r="L103" t="n">
-        <v>0.2241</v>
+        <v>0.204</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -6995,22 +6995,22 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>104.83</v>
+        <v>104.84</v>
       </c>
       <c r="H104" t="n">
-        <v>104.7286</v>
+        <v>104.7234</v>
       </c>
       <c r="I104" t="n">
-        <v>104.7918</v>
+        <v>104.709</v>
       </c>
       <c r="J104" t="n">
-        <v>56.5</v>
+        <v>57.2</v>
       </c>
       <c r="K104" t="n">
-        <v>17</v>
+        <v>15.3</v>
       </c>
       <c r="L104" t="n">
-        <v>0.0364</v>
+        <v>0.03</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7058,22 +7058,22 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>107.42</v>
+        <v>107.35</v>
       </c>
       <c r="H105" t="n">
-        <v>107.4395</v>
+        <v>107.4243</v>
       </c>
       <c r="I105" t="n">
-        <v>107.71</v>
+        <v>107.5779</v>
       </c>
       <c r="J105" t="n">
-        <v>43.6</v>
+        <v>29.4</v>
       </c>
       <c r="K105" t="n">
-        <v>34.2</v>
+        <v>36</v>
       </c>
       <c r="L105" t="n">
-        <v>0.0194</v>
+        <v>0.004</v>
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7121,22 +7121,22 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>202.96</v>
+        <v>203.16</v>
       </c>
       <c r="H106" t="n">
-        <v>203.0905</v>
+        <v>203.1143</v>
       </c>
       <c r="I106" t="n">
-        <v>204.1197</v>
+        <v>203.8386</v>
       </c>
       <c r="J106" t="n">
-        <v>46.7</v>
+        <v>49.3</v>
       </c>
       <c r="K106" t="n">
-        <v>25.8</v>
+        <v>19</v>
       </c>
       <c r="L106" t="n">
-        <v>0.1669</v>
+        <v>0.1521</v>
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7187,19 +7187,19 @@
         <v>112.88</v>
       </c>
       <c r="H107" t="n">
-        <v>112.7807</v>
+        <v>112.7736</v>
       </c>
       <c r="I107" t="n">
-        <v>112.6397</v>
+        <v>112.5927</v>
       </c>
       <c r="J107" t="n">
-        <v>62.2</v>
+        <v>62.9</v>
       </c>
       <c r="K107" t="n">
-        <v>29</v>
+        <v>70.3</v>
       </c>
       <c r="L107" t="n">
-        <v>0.0027</v>
+        <v>-0.0025</v>
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7247,22 +7247,22 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>5.0634</v>
+        <v>5.0638</v>
       </c>
       <c r="H108" t="n">
-        <v>5.0551</v>
+        <v>5.0549</v>
       </c>
       <c r="I108" t="n">
-        <v>5.0493</v>
+        <v>5.0472</v>
       </c>
       <c r="J108" t="n">
-        <v>73.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K108" t="n">
-        <v>27.8</v>
+        <v>15.9</v>
       </c>
       <c r="L108" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7310,22 +7310,22 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>75.282</v>
+        <v>75.298</v>
       </c>
       <c r="H109" t="n">
-        <v>74.9361</v>
+        <v>74.9281</v>
       </c>
       <c r="I109" t="n">
-        <v>74.99169999999999</v>
+        <v>74.9092</v>
       </c>
       <c r="J109" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="K109" t="n">
-        <v>19.2</v>
+        <v>17.5</v>
       </c>
       <c r="L109" t="n">
-        <v>0.0709</v>
+        <v>0.0645</v>
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -7373,22 +7373,22 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>119.22</v>
+        <v>119.24</v>
       </c>
       <c r="H110" t="n">
-        <v>119.0953</v>
+        <v>119.0898</v>
       </c>
       <c r="I110" t="n">
-        <v>119.1766</v>
+        <v>119.0886</v>
       </c>
       <c r="J110" t="n">
-        <v>56.6</v>
+        <v>57.8</v>
       </c>
       <c r="K110" t="n">
-        <v>25.7</v>
+        <v>19.2</v>
       </c>
       <c r="L110" t="n">
-        <v>0.0431</v>
+        <v>0.0362</v>
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -7436,22 +7436,22 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>108.28</v>
+        <v>108.64</v>
       </c>
       <c r="H111" t="n">
-        <v>106.0282</v>
+        <v>106.0285</v>
       </c>
       <c r="I111" t="n">
-        <v>104.9556</v>
+        <v>105.0945</v>
       </c>
       <c r="J111" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K111" t="n">
-        <v>18.9</v>
+        <v>15.9</v>
       </c>
       <c r="L111" t="n">
-        <v>0.4125</v>
+        <v>0.4238</v>
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -7499,22 +7499,22 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>128.1</v>
+        <v>128.13</v>
       </c>
       <c r="H112" t="n">
-        <v>127.9739</v>
+        <v>127.9695</v>
       </c>
       <c r="I112" t="n">
-        <v>128.0284</v>
+        <v>127.924</v>
       </c>
       <c r="J112" t="n">
-        <v>56.6</v>
+        <v>58.4</v>
       </c>
       <c r="K112" t="n">
-        <v>20.4</v>
+        <v>16.2</v>
       </c>
       <c r="L112" t="n">
-        <v>0.0462</v>
+        <v>0.0398</v>
       </c>
       <c r="M112" s="6" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7562,22 +7562,22 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>101.64</v>
+        <v>101.52</v>
       </c>
       <c r="H113" t="n">
-        <v>101.5613</v>
+        <v>101.5432</v>
       </c>
       <c r="I113" t="n">
-        <v>101.6326</v>
+        <v>101.5572</v>
       </c>
       <c r="J113" t="n">
-        <v>60</v>
+        <v>40.1</v>
       </c>
       <c r="K113" t="n">
-        <v>28.5</v>
+        <v>21.7</v>
       </c>
       <c r="L113" t="n">
-        <v>0.0109</v>
+        <v>-0.0033</v>
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7625,22 +7625,22 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>108.01</v>
+        <v>108.08</v>
       </c>
       <c r="H114" t="n">
-        <v>107.7556</v>
+        <v>107.7865</v>
       </c>
       <c r="I114" t="n">
-        <v>107.7946</v>
+        <v>107.8022</v>
       </c>
       <c r="J114" t="n">
-        <v>56.1</v>
+        <v>57.6</v>
       </c>
       <c r="K114" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="L114" t="n">
-        <v>0.0416</v>
+        <v>0.054</v>
       </c>
       <c r="M114" s="6" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -7688,22 +7688,22 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>54.496</v>
+        <v>54.49</v>
       </c>
       <c r="H115" t="n">
-        <v>54.4251</v>
+        <v>54.4205</v>
       </c>
       <c r="I115" t="n">
-        <v>54.4202</v>
+        <v>54.3823</v>
       </c>
       <c r="J115" t="n">
-        <v>60.7</v>
+        <v>60.3</v>
       </c>
       <c r="K115" t="n">
-        <v>17.9</v>
+        <v>16.4</v>
       </c>
       <c r="L115" t="n">
-        <v>0.0133</v>
+        <v>0.0092</v>
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -7751,22 +7751,22 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>85.22</v>
+        <v>85.12</v>
       </c>
       <c r="H116" t="n">
-        <v>85.3655</v>
+        <v>85.34220000000001</v>
       </c>
       <c r="I116" t="n">
-        <v>85.19280000000001</v>
+        <v>85.22320000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>46.8</v>
+        <v>44.5</v>
       </c>
       <c r="K116" t="n">
-        <v>24.5</v>
+        <v>26.6</v>
       </c>
       <c r="L116" t="n">
-        <v>-0.0688</v>
+        <v>-0.0648</v>
       </c>
       <c r="M116" s="6" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -7814,22 +7814,22 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>413.11</v>
+        <v>412.31</v>
       </c>
       <c r="H117" t="n">
-        <v>408.1097</v>
+        <v>407.3909</v>
       </c>
       <c r="I117" t="n">
-        <v>398.6704</v>
+        <v>393.2495</v>
       </c>
       <c r="J117" t="n">
-        <v>64.3</v>
+        <v>63.5</v>
       </c>
       <c r="K117" t="n">
-        <v>36.2</v>
+        <v>42.5</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -7877,22 +7877,22 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>44.2</v>
+        <v>44.18</v>
       </c>
       <c r="H118" t="n">
-        <v>43.1379</v>
+        <v>43.1189</v>
       </c>
       <c r="I118" t="n">
-        <v>42.674</v>
+        <v>42.4838</v>
       </c>
       <c r="J118" t="n">
-        <v>71.5</v>
+        <v>69.7</v>
       </c>
       <c r="K118" t="n">
-        <v>20.8</v>
+        <v>23.1</v>
       </c>
       <c r="L118" t="n">
-        <v>0.1796</v>
+        <v>0.1567</v>
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -7940,22 +7940,22 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>636.2</v>
+        <v>637.9</v>
       </c>
       <c r="H119" t="n">
-        <v>624.8237</v>
+        <v>624.6549</v>
       </c>
       <c r="I119" t="n">
-        <v>620.776</v>
+        <v>618.3579999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="K119" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="L119" t="n">
-        <v>1.8356</v>
+        <v>1.6411</v>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8003,22 +8003,22 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>138.56</v>
+        <v>138.43</v>
       </c>
       <c r="H120" t="n">
-        <v>138.2393</v>
+        <v>138.212</v>
       </c>
       <c r="I120" t="n">
-        <v>137.9578</v>
+        <v>137.856</v>
       </c>
       <c r="J120" t="n">
-        <v>66.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="K120" t="n">
-        <v>23.2</v>
+        <v>25.9</v>
       </c>
       <c r="L120" t="n">
-        <v>0.0236</v>
+        <v>0.005</v>
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>15.5733</v>
+        <v>15.57359981536865</v>
       </c>
       <c r="H121" t="n">
         <v>15.4142</v>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>126.92</v>
+        <v>126.9400024414062</v>
       </c>
       <c r="H122" t="n">
         <v>126.4026</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>114.2</v>
+        <v>114.1900024414062</v>
       </c>
       <c r="H123" t="n">
         <v>113.6715</v>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -8255,31 +8255,31 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>21.265</v>
+        <v>21.395</v>
       </c>
       <c r="H124" t="n">
-        <v>20.7721</v>
+        <v>20.7823</v>
       </c>
       <c r="I124" t="n">
-        <v>20.1432</v>
+        <v>20.0869</v>
       </c>
       <c r="J124" t="n">
-        <v>66.2</v>
+        <v>66.8</v>
       </c>
       <c r="K124" t="n">
-        <v>26.6</v>
+        <v>37.7</v>
       </c>
       <c r="L124" t="n">
-        <v>0.0501</v>
-      </c>
-      <c r="M124" s="5" t="inlineStr">
-        <is>
-          <t>L0 RECOVERY</t>
+        <v>0.0545</v>
+      </c>
+      <c r="M124" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -8318,22 +8318,22 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>48.985</v>
+        <v>48.945</v>
       </c>
       <c r="H125" t="n">
-        <v>49.073</v>
+        <v>49.0605</v>
       </c>
       <c r="I125" t="n">
-        <v>49.2792</v>
+        <v>49.1263</v>
       </c>
       <c r="J125" t="n">
-        <v>42.9</v>
+        <v>43.5</v>
       </c>
       <c r="K125" t="n">
-        <v>20.5</v>
+        <v>16</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.0026</v>
+        <v>-0.0171</v>
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -8381,22 +8381,22 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>63.33</v>
+        <v>63.51</v>
       </c>
       <c r="H126" t="n">
-        <v>63.1156</v>
+        <v>63.1363</v>
       </c>
       <c r="I126" t="n">
-        <v>63.0211</v>
+        <v>63.0891</v>
       </c>
       <c r="J126" t="n">
-        <v>59.9</v>
+        <v>63.2</v>
       </c>
       <c r="K126" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="L126" t="n">
-        <v>0.0567</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M126" s="6" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -8444,22 +8444,22 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>238.95</v>
+        <v>239.55</v>
       </c>
       <c r="H127" t="n">
-        <v>232.9507</v>
+        <v>232.8586</v>
       </c>
       <c r="I127" t="n">
-        <v>229.596</v>
+        <v>228.667</v>
       </c>
       <c r="J127" t="n">
-        <v>71.2</v>
+        <v>70.2</v>
       </c>
       <c r="K127" t="n">
-        <v>24.2</v>
+        <v>20.8</v>
       </c>
       <c r="L127" t="n">
-        <v>0.9938</v>
+        <v>0.9525</v>
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -8507,22 +8507,22 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>345.95</v>
+        <v>346.55</v>
       </c>
       <c r="H128" t="n">
-        <v>344.8826</v>
+        <v>345.0414</v>
       </c>
       <c r="I128" t="n">
-        <v>337.021</v>
+        <v>337.229</v>
       </c>
       <c r="J128" t="n">
-        <v>54.8</v>
+        <v>55.8</v>
       </c>
       <c r="K128" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="L128" t="n">
-        <v>-0.1617</v>
+        <v>-0.3235</v>
       </c>
       <c r="M128" s="6" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8570,31 +8570,31 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>40.46</v>
+        <v>40.375</v>
       </c>
       <c r="H129" t="n">
-        <v>39.6386</v>
+        <v>39.7014</v>
       </c>
       <c r="I129" t="n">
-        <v>38.7669</v>
+        <v>39.678</v>
       </c>
       <c r="J129" t="n">
-        <v>60.8</v>
+        <v>57.3</v>
       </c>
       <c r="K129" t="n">
-        <v>22.1</v>
+        <v>17</v>
       </c>
       <c r="L129" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="M129" s="5" t="inlineStr">
-        <is>
-          <t>L0 RECOVERY</t>
+        <v>0.0711</v>
+      </c>
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8633,22 +8633,22 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>10.474</v>
+        <v>10.398</v>
       </c>
       <c r="H130" t="n">
-        <v>10.4681</v>
+        <v>10.4181</v>
       </c>
       <c r="I130" t="n">
-        <v>10.3903</v>
+        <v>10.4064</v>
       </c>
       <c r="J130" t="n">
-        <v>56.8</v>
+        <v>47.1</v>
       </c>
       <c r="K130" t="n">
-        <v>26.7</v>
+        <v>11.9</v>
       </c>
       <c r="L130" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -8696,22 +8696,22 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>65.56</v>
+        <v>65.62</v>
       </c>
       <c r="H131" t="n">
-        <v>65.50700000000001</v>
+        <v>65.5107</v>
       </c>
       <c r="I131" t="n">
-        <v>65.84180000000001</v>
+        <v>65.7932</v>
       </c>
       <c r="J131" t="n">
-        <v>49.8</v>
+        <v>51.7</v>
       </c>
       <c r="K131" t="n">
-        <v>18</v>
+        <v>13.2</v>
       </c>
       <c r="L131" t="n">
-        <v>0.0608</v>
+        <v>0.0558</v>
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -8759,22 +8759,22 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>155.36</v>
+        <v>155.59</v>
       </c>
       <c r="H132" t="n">
-        <v>155.216</v>
+        <v>155.228</v>
       </c>
       <c r="I132" t="n">
-        <v>155.9432</v>
+        <v>155.7866</v>
       </c>
       <c r="J132" t="n">
-        <v>50.2</v>
+        <v>52.6</v>
       </c>
       <c r="K132" t="n">
-        <v>18.2</v>
+        <v>13.6</v>
       </c>
       <c r="L132" t="n">
-        <v>0.1442</v>
+        <v>0.1336</v>
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -8822,22 +8822,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>7.286</v>
+        <v>7.307</v>
       </c>
       <c r="H133" t="n">
-        <v>7.1072</v>
+        <v>7.1079</v>
       </c>
       <c r="I133" t="n">
-        <v>7.0515</v>
+        <v>7.0547</v>
       </c>
       <c r="J133" t="n">
         <v>68.7</v>
       </c>
       <c r="K133" t="n">
-        <v>22.4</v>
+        <v>18.7</v>
       </c>
       <c r="L133" t="n">
-        <v>0.034</v>
+        <v>0.0341</v>
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -8885,22 +8885,22 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>147.14</v>
+        <v>146.825</v>
       </c>
       <c r="H134" t="n">
-        <v>147.9998</v>
+        <v>147.9238</v>
       </c>
       <c r="I134" t="n">
-        <v>149.1018</v>
+        <v>148.3302</v>
       </c>
       <c r="J134" t="n">
-        <v>36.7</v>
+        <v>37.1</v>
       </c>
       <c r="K134" t="n">
-        <v>23.7</v>
+        <v>21.2</v>
       </c>
       <c r="L134" t="n">
-        <v>-0.1171</v>
+        <v>-0.1901</v>
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -8948,22 +8948,22 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>181.95</v>
+        <v>182.93</v>
       </c>
       <c r="H135" t="n">
-        <v>178.1293</v>
+        <v>178.2035</v>
       </c>
       <c r="I135" t="n">
-        <v>176.7318</v>
+        <v>176.9662</v>
       </c>
       <c r="J135" t="n">
-        <v>65.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="K135" t="n">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="L135" t="n">
-        <v>0.7581</v>
+        <v>0.7974</v>
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -9014,19 +9014,19 @@
         <v>70.23</v>
       </c>
       <c r="H136" t="n">
-        <v>70.4586</v>
+        <v>70.43689999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>70.634</v>
+        <v>70.64879999999999</v>
       </c>
       <c r="J136" t="n">
         <v>44.6</v>
       </c>
       <c r="K136" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="L136" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0524</v>
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -9074,22 +9074,22 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>133.79</v>
+        <v>134.09</v>
       </c>
       <c r="H137" t="n">
-        <v>131.5169</v>
+        <v>131.4851</v>
       </c>
       <c r="I137" t="n">
-        <v>130.7818</v>
+        <v>130.3973</v>
       </c>
       <c r="J137" t="n">
-        <v>62.5</v>
+        <v>63.1</v>
       </c>
       <c r="K137" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="L137" t="n">
-        <v>0.4042</v>
+        <v>0.368</v>
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -9137,22 +9137,22 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>72.98999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H138" t="n">
-        <v>73.0887</v>
+        <v>73.10209999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>73.63</v>
+        <v>73.5724</v>
       </c>
       <c r="J138" t="n">
-        <v>43.7</v>
+        <v>47.1</v>
       </c>
       <c r="K138" t="n">
-        <v>30.5</v>
+        <v>37</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0499</v>
+        <v>0.0502</v>
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -9200,22 +9200,22 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18.663</v>
+        <v>18.5705</v>
       </c>
       <c r="H139" t="n">
-        <v>18.7296</v>
+        <v>18.716</v>
       </c>
       <c r="I139" t="n">
-        <v>18.9358</v>
+        <v>18.844</v>
       </c>
       <c r="J139" t="n">
-        <v>41.1</v>
+        <v>36.2</v>
       </c>
       <c r="K139" t="n">
-        <v>32.5</v>
+        <v>24.5</v>
       </c>
       <c r="L139" t="n">
-        <v>-0.0036</v>
+        <v>-0.0166</v>
       </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -9263,22 +9263,22 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>46.275</v>
+        <v>46.355</v>
       </c>
       <c r="H140" t="n">
-        <v>46.3276</v>
+        <v>46.338</v>
       </c>
       <c r="I140" t="n">
-        <v>46.5205</v>
+        <v>46.4779</v>
       </c>
       <c r="J140" t="n">
-        <v>45.6</v>
+        <v>49.6</v>
       </c>
       <c r="K140" t="n">
-        <v>16.7</v>
+        <v>14.2</v>
       </c>
       <c r="L140" t="n">
-        <v>0.0192</v>
+        <v>0.0204</v>
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9326,22 +9326,22 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>81.58</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="H141" t="n">
-        <v>81.9282</v>
+        <v>81.85980000000001</v>
       </c>
       <c r="I141" t="n">
         <v>82.1906</v>
       </c>
       <c r="J141" t="n">
-        <v>43.2</v>
+        <v>38.5</v>
       </c>
       <c r="K141" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="L141" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0849</v>
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -9389,22 +9389,22 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>45.03</v>
+        <v>45.075</v>
       </c>
       <c r="H142" t="n">
-        <v>45.1313</v>
+        <v>45.1295</v>
       </c>
       <c r="I142" t="n">
-        <v>45.3419</v>
+        <v>45.1998</v>
       </c>
       <c r="J142" t="n">
-        <v>42</v>
+        <v>46.1</v>
       </c>
       <c r="K142" t="n">
-        <v>20.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>-0.0076</v>
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -9455,19 +9455,19 @@
         <v>8.752000000000001</v>
       </c>
       <c r="H143" t="n">
-        <v>8.8073</v>
+        <v>8.802099999999999</v>
       </c>
       <c r="I143" t="n">
-        <v>8.8371</v>
+        <v>8.8375</v>
       </c>
       <c r="J143" t="n">
         <v>37.6</v>
       </c>
       <c r="K143" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="L143" t="n">
-        <v>-0.0109</v>
+        <v>-0.0094</v>
       </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -9515,22 +9515,22 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>89.72</v>
+        <v>90.92</v>
       </c>
       <c r="H144" t="n">
-        <v>87.6067</v>
+        <v>87.92230000000001</v>
       </c>
       <c r="I144" t="n">
-        <v>87.5296</v>
+        <v>87.6178</v>
       </c>
       <c r="J144" t="n">
-        <v>63.3</v>
+        <v>67.8</v>
       </c>
       <c r="K144" t="n">
-        <v>16.6</v>
+        <v>18.5</v>
       </c>
       <c r="L144" t="n">
-        <v>0.3837</v>
+        <v>0.4746</v>
       </c>
       <c r="M144" s="6" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -9578,22 +9578,22 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>122.36</v>
+        <v>121.8447</v>
       </c>
       <c r="H145" t="n">
-        <v>120.1326</v>
+        <v>119.7795</v>
       </c>
       <c r="I145" t="n">
-        <v>120.0491</v>
+        <v>119.3476</v>
       </c>
       <c r="J145" t="n">
-        <v>63.8</v>
+        <v>61.1</v>
       </c>
       <c r="K145" t="n">
-        <v>19.7</v>
+        <v>70.3</v>
       </c>
       <c r="L145" t="n">
-        <v>0.5071</v>
+        <v>0.3643</v>
       </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -9641,22 +9641,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>119.46</v>
+        <v>119.96</v>
       </c>
       <c r="H146" t="n">
-        <v>115.3394</v>
+        <v>115.4247</v>
       </c>
       <c r="I146" t="n">
-        <v>116.96</v>
+        <v>117.4304</v>
       </c>
       <c r="J146" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="K146" t="n">
-        <v>18.2</v>
+        <v>15.8</v>
       </c>
       <c r="L146" t="n">
-        <v>0.9096</v>
+        <v>0.8577</v>
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -9704,31 +9704,31 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>24.345</v>
+        <v>24.515</v>
       </c>
       <c r="H147" t="n">
-        <v>23.8713</v>
+        <v>23.9027</v>
       </c>
       <c r="I147" t="n">
-        <v>22.8941</v>
+        <v>23.1964</v>
       </c>
       <c r="J147" t="n">
-        <v>63.8</v>
+        <v>63.3</v>
       </c>
       <c r="K147" t="n">
-        <v>30.7</v>
+        <v>24.9</v>
       </c>
       <c r="L147" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="M147" s="5" t="inlineStr">
-        <is>
-          <t>L0 RECOVERY</t>
+        <v>0.0455</v>
+      </c>
+      <c r="M147" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -9767,31 +9767,31 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>105.9</v>
+        <v>106.65</v>
       </c>
       <c r="H148" t="n">
-        <v>103.6547</v>
+        <v>103.7917</v>
       </c>
       <c r="I148" t="n">
-        <v>99.43559999999999</v>
+        <v>100.7482</v>
       </c>
       <c r="J148" t="n">
-        <v>64.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="K148" t="n">
-        <v>30.3</v>
+        <v>26.6</v>
       </c>
       <c r="L148" t="n">
-        <v>0.08550000000000001</v>
-      </c>
-      <c r="M148" s="5" t="inlineStr">
-        <is>
-          <t>L0 RECOVERY</t>
+        <v>0.2297</v>
+      </c>
+      <c r="M148" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -9830,22 +9830,22 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>62.12</v>
+        <v>62.0927</v>
       </c>
       <c r="H149" t="n">
-        <v>60.2946</v>
+        <v>60.0748</v>
       </c>
       <c r="I149" t="n">
-        <v>59.5302</v>
+        <v>59.5163</v>
       </c>
       <c r="J149" t="n">
-        <v>67.5</v>
+        <v>66.8</v>
       </c>
       <c r="K149" t="n">
-        <v>22.6</v>
+        <v>66</v>
       </c>
       <c r="L149" t="n">
-        <v>0.3952</v>
+        <v>0.3884</v>
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9893,22 +9893,22 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>6.437</v>
+        <v>6.46</v>
       </c>
       <c r="H150" t="n">
-        <v>6.3154</v>
+        <v>6.3142</v>
       </c>
       <c r="I150" t="n">
-        <v>6.2791</v>
+        <v>6.2553</v>
       </c>
       <c r="J150" t="n">
-        <v>63.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K150" t="n">
-        <v>18.3</v>
+        <v>19.3</v>
       </c>
       <c r="L150" t="n">
-        <v>0.0212</v>
+        <v>0.0195</v>
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -9956,22 +9956,22 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>138.92</v>
+        <v>139.6</v>
       </c>
       <c r="H151" t="n">
-        <v>135.8221</v>
+        <v>135.8552</v>
       </c>
       <c r="I151" t="n">
-        <v>135.615</v>
+        <v>135.4806</v>
       </c>
       <c r="J151" t="n">
-        <v>64.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K151" t="n">
-        <v>19.6</v>
+        <v>18.2</v>
       </c>
       <c r="L151" t="n">
-        <v>0.7306</v>
+        <v>0.7088</v>
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10019,22 +10019,22 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>5.073</v>
+        <v>5.087</v>
       </c>
       <c r="H152" t="n">
-        <v>4.9746</v>
+        <v>4.9736</v>
       </c>
       <c r="I152" t="n">
-        <v>4.9471</v>
+        <v>4.9278</v>
       </c>
       <c r="J152" t="n">
-        <v>66.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="K152" t="n">
-        <v>19.8</v>
+        <v>17.6</v>
       </c>
       <c r="L152" t="n">
-        <v>0.0171</v>
+        <v>0.0156</v>
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -10082,22 +10082,22 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>25.975</v>
+        <v>25.925</v>
       </c>
       <c r="H153" t="n">
-        <v>25.6858</v>
+        <v>25.6647</v>
       </c>
       <c r="I153" t="n">
-        <v>25.6728</v>
+        <v>25.37</v>
       </c>
       <c r="J153" t="n">
-        <v>58.9</v>
+        <v>57.8</v>
       </c>
       <c r="K153" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="L153" t="n">
-        <v>0.0641</v>
+        <v>0.0442</v>
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -10145,22 +10145,22 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>97.08</v>
+        <v>97.66</v>
       </c>
       <c r="H154" t="n">
-        <v>96.8188</v>
+        <v>96.71639999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>94.779</v>
+        <v>93.3018</v>
       </c>
       <c r="J154" t="n">
-        <v>57.8</v>
+        <v>66.3</v>
       </c>
       <c r="K154" t="n">
-        <v>44.7</v>
+        <v>39.7</v>
       </c>
       <c r="L154" t="n">
-        <v>-0.1338</v>
+        <v>-0.1782</v>
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -10208,22 +10208,22 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>819.83</v>
+        <v>821.05</v>
       </c>
       <c r="H155" t="n">
-        <v>812.0227</v>
+        <v>811.6249</v>
       </c>
       <c r="I155" t="n">
-        <v>810.265</v>
+        <v>801.0093000000001</v>
       </c>
       <c r="J155" t="n">
-        <v>58.2</v>
+        <v>59.1</v>
       </c>
       <c r="K155" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="L155" t="n">
-        <v>1.8963</v>
+        <v>1.4727</v>
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -10271,22 +10271,22 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>211.22</v>
+        <v>211.4</v>
       </c>
       <c r="H156" t="n">
-        <v>208.466</v>
+        <v>208.4477</v>
       </c>
       <c r="I156" t="n">
-        <v>208.5286</v>
+        <v>207.7756</v>
       </c>
       <c r="J156" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="K156" t="n">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
       <c r="L156" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.5581</v>
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -10334,22 +10334,22 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>664</v>
+        <v>670.4</v>
       </c>
       <c r="H157" t="n">
-        <v>653.086</v>
+        <v>653.944</v>
       </c>
       <c r="I157" t="n">
-        <v>662.1900000000001</v>
+        <v>664.062</v>
       </c>
       <c r="J157" t="n">
-        <v>55.5</v>
+        <v>57.8</v>
       </c>
       <c r="K157" t="n">
-        <v>19.5</v>
+        <v>16.8</v>
       </c>
       <c r="L157" t="n">
-        <v>3.9674</v>
+        <v>4.1964</v>
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -10397,22 +10397,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>104.1</v>
+        <v>104.65</v>
       </c>
       <c r="H158" t="n">
-        <v>102.6688</v>
+        <v>102.728</v>
       </c>
       <c r="I158" t="n">
-        <v>104.1894</v>
+        <v>104.2004</v>
       </c>
       <c r="J158" t="n">
-        <v>54.6</v>
+        <v>56.3</v>
       </c>
       <c r="K158" t="n">
-        <v>13.5</v>
+        <v>16.1</v>
       </c>
       <c r="L158" t="n">
-        <v>0.435</v>
+        <v>0.4914</v>
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -10460,22 +10460,22 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>18.452</v>
+        <v>18.232</v>
       </c>
       <c r="H159" t="n">
-        <v>18.8559</v>
+        <v>18.8264</v>
       </c>
       <c r="I159" t="n">
-        <v>19.1639</v>
+        <v>19.1424</v>
       </c>
       <c r="J159" t="n">
-        <v>46.9</v>
+        <v>46.1</v>
       </c>
       <c r="K159" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="L159" t="n">
-        <v>0.0352</v>
+        <v>0.0068</v>
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -10523,22 +10523,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>104.1</v>
+        <v>104.65</v>
       </c>
       <c r="H160" t="n">
-        <v>102.6725</v>
+        <v>102.728</v>
       </c>
       <c r="I160" t="n">
-        <v>104.364</v>
+        <v>104.2004</v>
       </c>
       <c r="J160" t="n">
-        <v>54.8</v>
+        <v>56.3</v>
       </c>
       <c r="K160" t="n">
-        <v>18.9</v>
+        <v>16.1</v>
       </c>
       <c r="L160" t="n">
-        <v>0.5151</v>
+        <v>0.4914</v>
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -10586,22 +10586,22 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>293.15</v>
+        <v>294.75</v>
       </c>
       <c r="H161" t="n">
-        <v>289.1083</v>
+        <v>289.2745</v>
       </c>
       <c r="I161" t="n">
-        <v>293.7791</v>
+        <v>293.365</v>
       </c>
       <c r="J161" t="n">
-        <v>54.8</v>
+        <v>56.4</v>
       </c>
       <c r="K161" t="n">
-        <v>18.7</v>
+        <v>16</v>
       </c>
       <c r="L161" t="n">
-        <v>1.4486</v>
+        <v>1.3869</v>
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -10649,22 +10649,22 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>27.41</v>
+        <v>27.48</v>
       </c>
       <c r="H162" t="n">
-        <v>27.1565</v>
+        <v>27.1513</v>
       </c>
       <c r="I162" t="n">
-        <v>27.0279</v>
+        <v>26.9439</v>
       </c>
       <c r="J162" t="n">
-        <v>55.3</v>
+        <v>56.6</v>
       </c>
       <c r="K162" t="n">
-        <v>11.9</v>
+        <v>9</v>
       </c>
       <c r="L162" t="n">
-        <v>0.0522</v>
+        <v>0.0404</v>
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -10712,22 +10712,22 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>16.406</v>
+        <v>16.492</v>
       </c>
       <c r="H163" t="n">
-        <v>16.1132</v>
+        <v>16.1104</v>
       </c>
       <c r="I163" t="n">
-        <v>15.9456</v>
+        <v>15.895</v>
       </c>
       <c r="J163" t="n">
-        <v>61.2</v>
+        <v>63</v>
       </c>
       <c r="K163" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="L163" t="n">
-        <v>0.044</v>
+        <v>0.0426</v>
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -10775,22 +10775,22 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>144.28</v>
+        <v>144.13</v>
       </c>
       <c r="H164" t="n">
-        <v>139.3194</v>
+        <v>139.2756</v>
       </c>
       <c r="I164" t="n">
-        <v>139.3794</v>
+        <v>139.6008</v>
       </c>
       <c r="J164" t="n">
-        <v>62.1</v>
+        <v>61.1</v>
       </c>
       <c r="K164" t="n">
-        <v>19</v>
+        <v>16.2</v>
       </c>
       <c r="L164" t="n">
-        <v>1.184</v>
+        <v>1.0825</v>
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -10838,31 +10838,31 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>73.94</v>
+        <v>74.17</v>
       </c>
       <c r="H165" t="n">
-        <v>72.12869999999999</v>
+        <v>72.2187</v>
       </c>
       <c r="I165" t="n">
-        <v>70.482</v>
+        <v>70.5458</v>
       </c>
       <c r="J165" t="n">
-        <v>61.1</v>
+        <v>59.1</v>
       </c>
       <c r="K165" t="n">
-        <v>16</v>
+        <v>15.1</v>
       </c>
       <c r="L165" t="n">
-        <v>0.0692</v>
-      </c>
-      <c r="M165" s="5" t="inlineStr">
-        <is>
-          <t>L0 RECOVERY</t>
+        <v>0.1728</v>
+      </c>
+      <c r="M165" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10901,22 +10901,22 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1199.8199</v>
+        <v>1207.88</v>
       </c>
       <c r="H166" t="n">
-        <v>1161.4551</v>
+        <v>1162.4464</v>
       </c>
       <c r="I166" t="n">
-        <v>1163.7156</v>
+        <v>1166.7876</v>
       </c>
       <c r="J166" t="n">
-        <v>61.8</v>
+        <v>62.2</v>
       </c>
       <c r="K166" t="n">
-        <v>16.4</v>
+        <v>14.7</v>
       </c>
       <c r="L166" t="n">
-        <v>8.0503</v>
+        <v>7.9916</v>
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10964,22 +10964,22 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>21</v>
+        <v>21.15</v>
       </c>
       <c r="H167" t="n">
-        <v>20.2985</v>
+        <v>20.3796</v>
       </c>
       <c r="I167" t="n">
-        <v>20.1272</v>
+        <v>20.1461</v>
       </c>
       <c r="J167" t="n">
-        <v>63.2</v>
+        <v>65</v>
       </c>
       <c r="K167" t="n">
-        <v>15.9</v>
+        <v>16.4</v>
       </c>
       <c r="L167" t="n">
-        <v>0.1376</v>
+        <v>0.1401</v>
       </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -11027,22 +11027,22 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>6.56</v>
+        <v>6.432</v>
       </c>
       <c r="H168" t="n">
-        <v>6.1102</v>
+        <v>6.088</v>
       </c>
       <c r="I168" t="n">
-        <v>5.8599</v>
+        <v>5.8128</v>
       </c>
       <c r="J168" t="n">
-        <v>81.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K168" t="n">
-        <v>35.2</v>
+        <v>33</v>
       </c>
       <c r="L168" t="n">
-        <v>0.0644</v>
+        <v>0.0537</v>
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11090,22 +11090,22 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>334.96</v>
+        <v>403.35</v>
       </c>
       <c r="H169" t="n">
-        <v>334.1388</v>
+        <v>383.0426</v>
       </c>
       <c r="I169" t="n">
-        <v>338.5524</v>
+        <v>385.7359</v>
       </c>
       <c r="J169" t="n">
-        <v>49.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K169" t="n">
-        <v>16.8</v>
+        <v>21.1</v>
       </c>
       <c r="L169" t="n">
-        <v>0.8454</v>
+        <v>3.5414</v>
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -11153,22 +11153,22 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>50.29</v>
+        <v>50.03</v>
       </c>
       <c r="H170" t="n">
-        <v>47.236</v>
+        <v>47.3933</v>
       </c>
       <c r="I170" t="n">
-        <v>47.674</v>
+        <v>49.4402</v>
       </c>
       <c r="J170" t="n">
-        <v>61.5</v>
+        <v>57.9</v>
       </c>
       <c r="K170" t="n">
-        <v>16.2</v>
+        <v>23.5</v>
       </c>
       <c r="L170" t="n">
-        <v>0.5384</v>
+        <v>0.6611</v>
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -11216,22 +11216,22 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>168.04</v>
+        <v>168.38</v>
       </c>
       <c r="H171" t="n">
-        <v>165.3813</v>
+        <v>165.3476</v>
       </c>
       <c r="I171" t="n">
-        <v>164.9772</v>
+        <v>164.4144</v>
       </c>
       <c r="J171" t="n">
-        <v>63.2</v>
+        <v>63.7</v>
       </c>
       <c r="K171" t="n">
-        <v>16.8</v>
+        <v>15.2</v>
       </c>
       <c r="L171" t="n">
-        <v>0.5111</v>
+        <v>0.4569</v>
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -11291,10 +11291,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="K172" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L172" t="n">
-        <v>-0.0012</v>
+        <v>-0.0011</v>
       </c>
       <c r="M172" s="6" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -11342,22 +11342,22 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>30.35</v>
+        <v>30.63</v>
       </c>
       <c r="H173" t="n">
-        <v>30.5854</v>
+        <v>30.6011</v>
       </c>
       <c r="I173" t="n">
-        <v>30.4517</v>
+        <v>30.3139</v>
       </c>
       <c r="J173" t="n">
-        <v>44.8</v>
+        <v>51.6</v>
       </c>
       <c r="K173" t="n">
-        <v>12.2</v>
+        <v>10.5</v>
       </c>
       <c r="L173" t="n">
-        <v>-0.0253</v>
+        <v>-0.0123</v>
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -11405,22 +11405,22 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>10.54</v>
+        <v>10.508</v>
       </c>
       <c r="H174" t="n">
-        <v>10.5382</v>
+        <v>10.5635</v>
       </c>
       <c r="I174" t="n">
-        <v>11.1593</v>
+        <v>11.3581</v>
       </c>
       <c r="J174" t="n">
-        <v>46.9</v>
+        <v>45.6</v>
       </c>
       <c r="K174" t="n">
-        <v>24.8</v>
+        <v>22.8</v>
       </c>
       <c r="L174" t="n">
-        <v>0.0751</v>
+        <v>0.0828</v>
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -11468,22 +11468,22 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>204.2</v>
+        <v>204.65</v>
       </c>
       <c r="H175" t="n">
-        <v>199.3807</v>
+        <v>199.5038</v>
       </c>
       <c r="I175" t="n">
-        <v>203.8334</v>
+        <v>204.1168</v>
       </c>
       <c r="J175" t="n">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
       <c r="K175" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="L175" t="n">
-        <v>1.7258</v>
+        <v>1.5861</v>
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -11531,22 +11531,22 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>273.75</v>
+        <v>274.4</v>
       </c>
       <c r="H176" t="n">
-        <v>269.3831</v>
+        <v>269.3971</v>
       </c>
       <c r="I176" t="n">
-        <v>265.53</v>
+        <v>265.371</v>
       </c>
       <c r="J176" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K176" t="n">
-        <v>21.3</v>
+        <v>30.4</v>
       </c>
       <c r="L176" t="n">
-        <v>0.239</v>
+        <v>0.2207</v>
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -11594,22 +11594,22 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>33.72</v>
+        <v>33.745</v>
       </c>
       <c r="H177" t="n">
-        <v>34.4181</v>
+        <v>34.3954</v>
       </c>
       <c r="I177" t="n">
-        <v>34.5217</v>
+        <v>34.2967</v>
       </c>
       <c r="J177" t="n">
-        <v>37.2</v>
+        <v>39.4</v>
       </c>
       <c r="K177" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="L177" t="n">
-        <v>-0.1734</v>
+        <v>-0.1842</v>
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -11657,22 +11657,22 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>159.24</v>
+        <v>159.28</v>
       </c>
       <c r="H178" t="n">
-        <v>159.0841</v>
+        <v>159.0817</v>
       </c>
       <c r="I178" t="n">
-        <v>159.4854</v>
+        <v>159.2952</v>
       </c>
       <c r="J178" t="n">
-        <v>52.3</v>
+        <v>53.4</v>
       </c>
       <c r="K178" t="n">
-        <v>21.7</v>
+        <v>17</v>
       </c>
       <c r="L178" t="n">
-        <v>0.1017</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -11720,22 +11720,22 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>69.55</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H179" t="n">
-        <v>68.72799999999999</v>
+        <v>68.73909999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>68.9858</v>
+        <v>68.89579999999999</v>
       </c>
       <c r="J179" t="n">
-        <v>58.8</v>
+        <v>58.6</v>
       </c>
       <c r="K179" t="n">
         <v>12.5</v>
       </c>
       <c r="L179" t="n">
-        <v>0.1944</v>
+        <v>0.1461</v>
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -11783,22 +11783,22 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>10.58</v>
+        <v>10.662</v>
       </c>
       <c r="H180" t="n">
-        <v>10.414</v>
+        <v>10.4218</v>
       </c>
       <c r="I180" t="n">
-        <v>10.3846</v>
+        <v>10.3862</v>
       </c>
       <c r="J180" t="n">
-        <v>60.1</v>
+        <v>63.6</v>
       </c>
       <c r="K180" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="L180" t="n">
-        <v>0.0361</v>
+        <v>0.0413</v>
       </c>
       <c r="M180" s="6" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -11846,22 +11846,22 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>81.38</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="H181" t="n">
-        <v>80.6592</v>
+        <v>80.6095</v>
       </c>
       <c r="I181" t="n">
-        <v>79.7216</v>
+        <v>79.2946</v>
       </c>
       <c r="J181" t="n">
-        <v>64.8</v>
+        <v>65.7</v>
       </c>
       <c r="K181" t="n">
-        <v>28.8</v>
+        <v>34.2</v>
       </c>
       <c r="L181" t="n">
-        <v>0.0194</v>
+        <v>-0.0161</v>
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -11909,22 +11909,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>229.2</v>
+        <v>232.2</v>
       </c>
       <c r="H182" t="n">
-        <v>230.5386</v>
+        <v>230.6968</v>
       </c>
       <c r="I182" t="n">
-        <v>228.078</v>
+        <v>228.225</v>
       </c>
       <c r="J182" t="n">
-        <v>48.1</v>
+        <v>53.2</v>
       </c>
       <c r="K182" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="L182" t="n">
-        <v>-0.7115</v>
+        <v>-0.4565</v>
       </c>
       <c r="M182" s="6" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -11972,22 +11972,22 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>116.02</v>
+        <v>115.72</v>
       </c>
       <c r="H183" t="n">
-        <v>114.8519</v>
+        <v>114.8233</v>
       </c>
       <c r="I183" t="n">
-        <v>117.2556</v>
+        <v>117.2496</v>
       </c>
       <c r="J183" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="K183" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="L183" t="n">
-        <v>0.4992</v>
+        <v>0.4801</v>
       </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -12035,22 +12035,22 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>90.52</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="H184" t="n">
-        <v>88.6602</v>
+        <v>88.6782</v>
       </c>
       <c r="I184" t="n">
-        <v>87.55459999999999</v>
+        <v>87.55840000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>66</v>
+        <v>66.8</v>
       </c>
       <c r="K184" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="L184" t="n">
-        <v>0.2584</v>
+        <v>0.2705</v>
       </c>
       <c r="M184" s="6" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -12098,22 +12098,22 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>77.84</v>
+        <v>78</v>
       </c>
       <c r="H185" t="n">
-        <v>76.14019999999999</v>
+        <v>76.1555</v>
       </c>
       <c r="I185" t="n">
-        <v>74.8326</v>
+        <v>74.83580000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="K185" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="L185" t="n">
-        <v>0.152</v>
+        <v>0.1622</v>
       </c>
       <c r="M185" s="6" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -12161,22 +12161,22 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>18.356</v>
+        <v>18.214</v>
       </c>
       <c r="H186" t="n">
-        <v>18.3222</v>
+        <v>18.3086</v>
       </c>
       <c r="I186" t="n">
-        <v>18.0126</v>
+        <v>17.9452</v>
       </c>
       <c r="J186" t="n">
-        <v>54.1</v>
+        <v>48.8</v>
       </c>
       <c r="K186" t="n">
-        <v>20.3</v>
+        <v>15.9</v>
       </c>
       <c r="L186" t="n">
-        <v>-0.0166</v>
+        <v>-0.0236</v>
       </c>
       <c r="M186" s="6" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -12224,22 +12224,22 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>81.38</v>
+        <v>39.185</v>
       </c>
       <c r="H187" t="n">
-        <v>80.6592</v>
+        <v>38.6718</v>
       </c>
       <c r="I187" t="n">
-        <v>79.7216</v>
+        <v>39.1903</v>
       </c>
       <c r="J187" t="n">
-        <v>64.8</v>
+        <v>55.8</v>
       </c>
       <c r="K187" t="n">
-        <v>28.8</v>
+        <v>14.5</v>
       </c>
       <c r="L187" t="n">
-        <v>0.0194</v>
+        <v>0.1303</v>
       </c>
       <c r="M187" s="6" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -12287,22 +12287,22 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>53.26</v>
+        <v>53.5</v>
       </c>
       <c r="H188" t="n">
-        <v>52.391</v>
+        <v>52.3789</v>
       </c>
       <c r="I188" t="n">
-        <v>51.7964</v>
+        <v>51.5283</v>
       </c>
       <c r="J188" t="n">
-        <v>67.3</v>
+        <v>69</v>
       </c>
       <c r="K188" t="n">
-        <v>22.5</v>
+        <v>18.7</v>
       </c>
       <c r="L188" t="n">
-        <v>0.103</v>
+        <v>0.0944</v>
       </c>
       <c r="M188" s="6" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -12350,22 +12350,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>8.539</v>
+        <v>8.523</v>
       </c>
       <c r="H189" t="n">
-        <v>8.3421</v>
+        <v>8.3405</v>
       </c>
       <c r="I189" t="n">
-        <v>8.197900000000001</v>
+        <v>8.1976</v>
       </c>
       <c r="J189" t="n">
-        <v>73.5</v>
+        <v>72.7</v>
       </c>
       <c r="K189" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="L189" t="n">
-        <v>0.0191</v>
+        <v>0.0181</v>
       </c>
       <c r="M189" s="6" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -12413,22 +12413,22 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>17.38</v>
+        <v>17.144</v>
       </c>
       <c r="H190" t="n">
-        <v>16.9851</v>
+        <v>16.9837</v>
       </c>
       <c r="I190" t="n">
-        <v>16.7324</v>
+        <v>16.9662</v>
       </c>
       <c r="J190" t="n">
-        <v>69.8</v>
+        <v>56.6</v>
       </c>
       <c r="K190" t="n">
-        <v>21.3</v>
+        <v>12.2</v>
       </c>
       <c r="L190" t="n">
-        <v>0.0474</v>
+        <v>0.0436</v>
       </c>
       <c r="M190" s="6" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -12476,22 +12476,22 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>50.34</v>
+        <v>49.215</v>
       </c>
       <c r="H191" t="n">
-        <v>48.6169</v>
+        <v>48.5409</v>
       </c>
       <c r="I191" t="n">
-        <v>47.4472</v>
+        <v>47.8353</v>
       </c>
       <c r="J191" t="n">
-        <v>69.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="K191" t="n">
-        <v>19.9</v>
+        <v>14.6</v>
       </c>
       <c r="L191" t="n">
-        <v>0.2174</v>
+        <v>0.1514</v>
       </c>
       <c r="M191" s="6" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -12539,22 +12539,22 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>3.83</v>
+        <v>3.8075</v>
       </c>
       <c r="H192" t="n">
-        <v>3.7451</v>
+        <v>3.7527</v>
       </c>
       <c r="I192" t="n">
-        <v>3.7215</v>
+        <v>3.8284</v>
       </c>
       <c r="J192" t="n">
-        <v>64</v>
+        <v>56.6</v>
       </c>
       <c r="K192" t="n">
-        <v>16.4</v>
+        <v>19.1</v>
       </c>
       <c r="L192" t="n">
-        <v>0.0124</v>
+        <v>0.0173</v>
       </c>
       <c r="M192" s="6" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -12602,22 +12602,22 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>11.256</v>
+        <v>11.006</v>
       </c>
       <c r="H193" t="n">
-        <v>10.8956</v>
+        <v>10.8659</v>
       </c>
       <c r="I193" t="n">
-        <v>10.6814</v>
+        <v>10.6606</v>
       </c>
       <c r="J193" t="n">
-        <v>71.8</v>
+        <v>57.4</v>
       </c>
       <c r="K193" t="n">
-        <v>19.7</v>
+        <v>18.1</v>
       </c>
       <c r="L193" t="n">
-        <v>0.0427</v>
+        <v>0.0231</v>
       </c>
       <c r="M193" s="6" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -12665,22 +12665,22 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>9.83</v>
+        <v>9.978999999999999</v>
       </c>
       <c r="H194" t="n">
-        <v>9.216100000000001</v>
+        <v>9.2523</v>
       </c>
       <c r="I194" t="n">
-        <v>9.039400000000001</v>
+        <v>9.2415</v>
       </c>
       <c r="J194" t="n">
-        <v>67.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="K194" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="L194" t="n">
-        <v>0.1162</v>
+        <v>0.1325</v>
       </c>
       <c r="M194" s="6" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -12728,22 +12728,22 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>27.435</v>
+        <v>27.675</v>
       </c>
       <c r="H195" t="n">
-        <v>27.348</v>
+        <v>27.464</v>
       </c>
       <c r="I195" t="n">
-        <v>29.1584</v>
+        <v>29.7602</v>
       </c>
       <c r="J195" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="K195" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
       <c r="L195" t="n">
-        <v>0.2626</v>
+        <v>0.3127</v>
       </c>
       <c r="M195" s="6" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -12791,22 +12791,22 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>4.874</v>
+        <v>4.9125</v>
       </c>
       <c r="H196" t="n">
-        <v>4.9097</v>
+        <v>4.9115</v>
       </c>
       <c r="I196" t="n">
-        <v>4.8874</v>
+        <v>4.8651</v>
       </c>
       <c r="J196" t="n">
-        <v>45.1</v>
+        <v>51.1</v>
       </c>
       <c r="K196" t="n">
-        <v>10.6</v>
+        <v>9.9</v>
       </c>
       <c r="L196" t="n">
-        <v>-0.0038</v>
+        <v>-0.0022</v>
       </c>
       <c r="M196" s="6" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -12854,22 +12854,22 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>90.58</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="H197" t="n">
-        <v>88.4653</v>
+        <v>88.44159999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>87.55119999999999</v>
+        <v>87.1504</v>
       </c>
       <c r="J197" t="n">
-        <v>70</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K197" t="n">
-        <v>19.5</v>
+        <v>18.7</v>
       </c>
       <c r="L197" t="n">
-        <v>0.3652</v>
+        <v>0.3278</v>
       </c>
       <c r="M197" s="6" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>149.843</v>
+        <v>149.8600006103516</v>
       </c>
       <c r="H198" t="n">
         <v>149.1741</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -12980,22 +12980,22 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>141.25</v>
+        <v>141.26</v>
       </c>
       <c r="H199" t="n">
-        <v>141.1067</v>
+        <v>141.0994</v>
       </c>
       <c r="I199" t="n">
-        <v>141.1452</v>
+        <v>141.0348</v>
       </c>
       <c r="J199" t="n">
-        <v>58</v>
+        <v>58.9</v>
       </c>
       <c r="K199" t="n">
-        <v>15.6</v>
+        <v>14</v>
       </c>
       <c r="L199" t="n">
-        <v>0.0429</v>
+        <v>0.0352</v>
       </c>
       <c r="M199" s="6" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -13043,22 +13043,22 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>158.41</v>
+        <v>159.38</v>
       </c>
       <c r="H200" t="n">
-        <v>155.1038</v>
+        <v>155.1749</v>
       </c>
       <c r="I200" t="n">
-        <v>153.8703</v>
+        <v>154.0671</v>
       </c>
       <c r="J200" t="n">
-        <v>64.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K200" t="n">
-        <v>19.5</v>
+        <v>32.7</v>
       </c>
       <c r="L200" t="n">
-        <v>0.657</v>
+        <v>0.6955</v>
       </c>
       <c r="M200" s="6" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -13106,22 +13106,22 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>120.58</v>
+        <v>121.115</v>
       </c>
       <c r="H201" t="n">
-        <v>118.1109</v>
+        <v>118.1311</v>
       </c>
       <c r="I201" t="n">
-        <v>117.2044</v>
+        <v>117.1431</v>
       </c>
       <c r="J201" t="n">
-        <v>66.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K201" t="n">
-        <v>19.5</v>
+        <v>18.2</v>
       </c>
       <c r="L201" t="n">
-        <v>0.4406</v>
+        <v>0.4444</v>
       </c>
       <c r="M201" s="6" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -13169,22 +13169,22 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>358.1</v>
+        <v>362.17</v>
       </c>
       <c r="H202" t="n">
-        <v>345.4927</v>
+        <v>346.2595</v>
       </c>
       <c r="I202" t="n">
-        <v>344.482</v>
+        <v>348.548</v>
       </c>
       <c r="J202" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="K202" t="n">
-        <v>14.1</v>
+        <v>22.5</v>
       </c>
       <c r="L202" t="n">
-        <v>1.9731</v>
+        <v>2.6085</v>
       </c>
       <c r="M202" s="6" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -13232,22 +13232,22 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>6.425</v>
+        <v>6.489</v>
       </c>
       <c r="H203" t="n">
-        <v>6.3883</v>
+        <v>6.4064</v>
       </c>
       <c r="I203" t="n">
-        <v>6.2553</v>
+        <v>6.3477</v>
       </c>
       <c r="J203" t="n">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="K203" t="n">
-        <v>10.4</v>
+        <v>11.9</v>
       </c>
       <c r="L203" t="n">
-        <v>-0.0065</v>
+        <v>0.013</v>
       </c>
       <c r="M203" s="6" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -13295,22 +13295,22 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>28.175</v>
+        <v>28.265</v>
       </c>
       <c r="H204" t="n">
-        <v>28.1481</v>
+        <v>28.1744</v>
       </c>
       <c r="I204" t="n">
-        <v>27.5093</v>
+        <v>27.8333</v>
       </c>
       <c r="J204" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="K204" t="n">
-        <v>24.3</v>
+        <v>20</v>
       </c>
       <c r="L204" t="n">
-        <v>-0.1334</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="M204" s="6" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -13358,22 +13358,22 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>125.84</v>
+        <v>126.48</v>
       </c>
       <c r="H205" t="n">
-        <v>121.6823</v>
+        <v>121.7699</v>
       </c>
       <c r="I205" t="n">
-        <v>121.8712</v>
+        <v>122.2152</v>
       </c>
       <c r="J205" t="n">
         <v>62.4</v>
       </c>
       <c r="K205" t="n">
-        <v>16.6</v>
+        <v>13.4</v>
       </c>
       <c r="L205" t="n">
-        <v>0.8528</v>
+        <v>0.8355</v>
       </c>
       <c r="M205" s="6" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -13421,22 +13421,22 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>41.065</v>
+        <v>40.37</v>
       </c>
       <c r="H206" t="n">
-        <v>38.8336</v>
+        <v>38.6369</v>
       </c>
       <c r="I206" t="n">
-        <v>38.0084</v>
+        <v>37.4924</v>
       </c>
       <c r="J206" t="n">
-        <v>63.9</v>
+        <v>61.6</v>
       </c>
       <c r="K206" t="n">
-        <v>21.3</v>
+        <v>22.6</v>
       </c>
       <c r="L206" t="n">
-        <v>0.2969</v>
+        <v>0.1772</v>
       </c>
       <c r="M206" s="6" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -13484,22 +13484,22 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>9.574999999999999</v>
+        <v>9.631</v>
       </c>
       <c r="H207" t="n">
-        <v>9.336600000000001</v>
+        <v>9.340299999999999</v>
       </c>
       <c r="I207" t="n">
-        <v>9.623900000000001</v>
+        <v>9.5932</v>
       </c>
       <c r="J207" t="n">
-        <v>55.3</v>
+        <v>56.4</v>
       </c>
       <c r="K207" t="n">
-        <v>19.2</v>
+        <v>16.2</v>
       </c>
       <c r="L207" t="n">
-        <v>0.0893</v>
+        <v>0.08</v>
       </c>
       <c r="M207" s="6" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -13547,22 +13547,22 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>9.153</v>
+        <v>9.093999999999999</v>
       </c>
       <c r="H208" t="n">
-        <v>9.198399999999999</v>
+        <v>9.214600000000001</v>
       </c>
       <c r="I208" t="n">
-        <v>9.7631</v>
+        <v>9.893000000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>45.2</v>
+        <v>43.6</v>
       </c>
       <c r="K208" t="n">
-        <v>25.2</v>
+        <v>22.2</v>
       </c>
       <c r="L208" t="n">
-        <v>0.0536</v>
+        <v>0.0561</v>
       </c>
       <c r="M208" s="6" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -13610,22 +13610,22 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>83.52</v>
+        <v>84.39</v>
       </c>
       <c r="H209" t="n">
-        <v>80.02330000000001</v>
+        <v>80.1062</v>
       </c>
       <c r="I209" t="n">
-        <v>80.63679999999999</v>
+        <v>80.6541</v>
       </c>
       <c r="J209" t="n">
-        <v>62.6</v>
+        <v>64.7</v>
       </c>
       <c r="K209" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="L209" t="n">
-        <v>0.6874</v>
+        <v>0.743</v>
       </c>
       <c r="M209" s="6" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -13673,22 +13673,22 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>138.87</v>
+        <v>137.68</v>
       </c>
       <c r="H210" t="n">
-        <v>131.9958</v>
+        <v>132.2221</v>
       </c>
       <c r="I210" t="n">
-        <v>129.972</v>
+        <v>133.301</v>
       </c>
       <c r="J210" t="n">
-        <v>65.2</v>
+        <v>60.1</v>
       </c>
       <c r="K210" t="n">
-        <v>14.8</v>
+        <v>22.6</v>
       </c>
       <c r="L210" t="n">
-        <v>1.202</v>
+        <v>1.4248</v>
       </c>
       <c r="M210" s="6" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -13736,22 +13736,22 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>50.23</v>
+        <v>46.345</v>
       </c>
       <c r="H211" t="n">
-        <v>46.459</v>
+        <v>46.089</v>
       </c>
       <c r="I211" t="n">
-        <v>45.9164</v>
+        <v>45.8387</v>
       </c>
       <c r="J211" t="n">
-        <v>67</v>
+        <v>51.1</v>
       </c>
       <c r="K211" t="n">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
       <c r="L211" t="n">
-        <v>0.2876</v>
+        <v>0.0397</v>
       </c>
       <c r="M211" s="6" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -13799,22 +13799,22 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>47.15</v>
+        <v>47.03</v>
       </c>
       <c r="H212" t="n">
-        <v>45.899</v>
+        <v>46.0067</v>
       </c>
       <c r="I212" t="n">
-        <v>43.5412</v>
+        <v>43.5215</v>
       </c>
       <c r="J212" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="K212" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="L212" t="n">
-        <v>-0.1238</v>
+        <v>-0.0987</v>
       </c>
       <c r="M212" s="6" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -13865,16 +13865,16 @@
         <v>6.795</v>
       </c>
       <c r="H213" t="n">
-        <v>7.0117</v>
+        <v>6.9911</v>
       </c>
       <c r="J213" t="n">
         <v>35.9</v>
       </c>
       <c r="K213" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="L213" t="n">
-        <v>0.0194</v>
+        <v>0.0237</v>
       </c>
       <c r="M213" s="6" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -13922,22 +13922,22 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>49.326</v>
+        <v>49.704</v>
       </c>
       <c r="H214" t="n">
-        <v>49.3863</v>
+        <v>49.4223</v>
       </c>
       <c r="I214" t="n">
-        <v>49.0059</v>
+        <v>49.0134</v>
       </c>
       <c r="J214" t="n">
-        <v>49.1</v>
+        <v>51.1</v>
       </c>
       <c r="K214" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="L214" t="n">
-        <v>-0.0113</v>
+        <v>0.0128</v>
       </c>
       <c r="M214" s="6" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -13985,22 +13985,22 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>75.05500000000001</v>
+        <v>75.4952</v>
       </c>
       <c r="H215" t="n">
-        <v>75.3154</v>
+        <v>75.3428</v>
       </c>
       <c r="I215" t="n">
-        <v>74.4832</v>
+        <v>74.6849</v>
       </c>
       <c r="J215" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
       <c r="K215" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="L215" t="n">
-        <v>-0.0225</v>
+        <v>-0.0064</v>
       </c>
       <c r="M215" s="6" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -14048,22 +14048,22 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.2459</v>
+        <v>36.08</v>
       </c>
       <c r="H216" t="n">
-        <v>1.7726</v>
+        <v>29.6931</v>
       </c>
       <c r="I216" t="n">
-        <v>7.9328</v>
+        <v>30.0027</v>
       </c>
       <c r="J216" t="n">
-        <v>47.6</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K216" t="n">
-        <v>4.6</v>
+        <v>16.5</v>
       </c>
       <c r="L216" t="n">
-        <v>0.4943</v>
+        <v>1.0168</v>
       </c>
       <c r="M216" s="6" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -14111,22 +14111,22 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.2459</v>
+        <v>0.2334</v>
       </c>
       <c r="H217" t="n">
-        <v>1.7726</v>
+        <v>0.3117</v>
       </c>
       <c r="I217" t="n">
-        <v>7.9328</v>
+        <v>0.3352</v>
       </c>
       <c r="J217" t="n">
-        <v>47.6</v>
+        <v>32.7</v>
       </c>
       <c r="K217" t="n">
-        <v>4.6</v>
+        <v>17.6</v>
       </c>
       <c r="L217" t="n">
-        <v>0.4943</v>
+        <v>-0.0107</v>
       </c>
       <c r="M217" s="6" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -14174,22 +14174,22 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.2459</v>
+        <v>0.9905</v>
       </c>
       <c r="H218" t="n">
-        <v>1.7726</v>
+        <v>1.1993</v>
       </c>
       <c r="I218" t="n">
-        <v>7.9328</v>
+        <v>1.8097</v>
       </c>
       <c r="J218" t="n">
-        <v>47.6</v>
+        <v>36.9</v>
       </c>
       <c r="K218" t="n">
-        <v>4.6</v>
+        <v>27.8</v>
       </c>
       <c r="L218" t="n">
-        <v>0.4943</v>
+        <v>0.0122</v>
       </c>
       <c r="M218" s="6" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -14237,22 +14237,22 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.2459</v>
+        <v>24.5525</v>
       </c>
       <c r="H219" t="n">
-        <v>1.7726</v>
+        <v>17.5473</v>
       </c>
       <c r="I219" t="n">
-        <v>7.9328</v>
+        <v>14.3816</v>
       </c>
       <c r="J219" t="n">
-        <v>47.6</v>
+        <v>77.8</v>
       </c>
       <c r="K219" t="n">
-        <v>4.6</v>
+        <v>30.8</v>
       </c>
       <c r="L219" t="n">
-        <v>0.4943</v>
+        <v>1.2888</v>
       </c>
       <c r="M219" s="6" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -14300,22 +14300,22 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.2459</v>
+        <v>45.155</v>
       </c>
       <c r="H220" t="n">
-        <v>1.7726</v>
+        <v>47.9756</v>
       </c>
       <c r="I220" t="n">
-        <v>7.9328</v>
+        <v>46.0371</v>
       </c>
       <c r="J220" t="n">
-        <v>47.6</v>
+        <v>46</v>
       </c>
       <c r="K220" t="n">
-        <v>4.6</v>
+        <v>25.6</v>
       </c>
       <c r="L220" t="n">
-        <v>0.4943</v>
+        <v>-1.6245</v>
       </c>
       <c r="M220" s="6" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -14363,22 +14363,22 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.2459</v>
+        <v>362.53</v>
       </c>
       <c r="H221" t="n">
-        <v>1.7726</v>
+        <v>450.6588</v>
       </c>
       <c r="I221" t="n">
-        <v>7.9328</v>
+        <v>552.1660000000001</v>
       </c>
       <c r="J221" t="n">
-        <v>47.6</v>
+        <v>43.1</v>
       </c>
       <c r="K221" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="L221" t="n">
-        <v>0.4943</v>
+        <v>-7.9562</v>
       </c>
       <c r="M221" s="6" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -14426,22 +14426,22 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.2459</v>
+        <v>24.92</v>
       </c>
       <c r="H222" t="n">
-        <v>1.7726</v>
+        <v>26.3708</v>
       </c>
       <c r="I222" t="n">
-        <v>7.9328</v>
+        <v>28.0544</v>
       </c>
       <c r="J222" t="n">
-        <v>47.6</v>
+        <v>46.2</v>
       </c>
       <c r="K222" t="n">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="L222" t="n">
-        <v>0.4943</v>
+        <v>-0.4212</v>
       </c>
       <c r="M222" s="6" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -14489,22 +14489,22 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.2459</v>
+        <v>24.92</v>
       </c>
       <c r="H223" t="n">
-        <v>1.7726</v>
+        <v>26.3687</v>
       </c>
       <c r="I223" t="n">
-        <v>7.9328</v>
+        <v>28.0544</v>
       </c>
       <c r="J223" t="n">
-        <v>47.6</v>
+        <v>46.2</v>
       </c>
       <c r="K223" t="n">
-        <v>4.6</v>
+        <v>18.6</v>
       </c>
       <c r="L223" t="n">
-        <v>0.4943</v>
+        <v>-0.4252</v>
       </c>
       <c r="M223" s="6" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -14552,22 +14552,22 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>256.7</v>
+        <v>255.8</v>
       </c>
       <c r="H224" t="n">
-        <v>251.5563</v>
+        <v>251.9604</v>
       </c>
       <c r="I224" t="n">
-        <v>251.891</v>
+        <v>252.01</v>
       </c>
       <c r="J224" t="n">
-        <v>61</v>
+        <v>58.9</v>
       </c>
       <c r="K224" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="L224" t="n">
-        <v>0.6822</v>
+        <v>0.7578</v>
       </c>
       <c r="M224" s="6" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -14615,22 +14615,22 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>254.69</v>
+        <v>254.37</v>
       </c>
       <c r="H225" t="n">
-        <v>249.4001</v>
+        <v>249.1886</v>
       </c>
       <c r="I225" t="n">
-        <v>247.8684</v>
+        <v>246.2408</v>
       </c>
       <c r="J225" t="n">
-        <v>83.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K225" t="n">
-        <v>29.6</v>
+        <v>26.7</v>
       </c>
       <c r="L225" t="n">
-        <v>0.5782</v>
+        <v>0.4209</v>
       </c>
       <c r="M225" s="6" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -14678,22 +14678,22 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>125.7</v>
+        <v>125.9</v>
       </c>
       <c r="H226" t="n">
-        <v>125.6905</v>
+        <v>125.712</v>
       </c>
       <c r="I226" t="n">
-        <v>126.3994</v>
+        <v>126.1992</v>
       </c>
       <c r="J226" t="n">
-        <v>47.6</v>
+        <v>52.6</v>
       </c>
       <c r="K226" t="n">
-        <v>28.6</v>
+        <v>20.9</v>
       </c>
       <c r="L226" t="n">
-        <v>0.12</v>
+        <v>0.1154</v>
       </c>
       <c r="M226" s="6" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -14744,19 +14744,19 @@
         <v>109.7</v>
       </c>
       <c r="H227" t="n">
-        <v>117.9077</v>
+        <v>109.5848</v>
       </c>
       <c r="I227" t="n">
-        <v>126.9181</v>
+        <v>109.4233</v>
       </c>
       <c r="J227" t="n">
-        <v>48.2</v>
+        <v>84.2</v>
       </c>
       <c r="K227" t="n">
-        <v>18.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L227" t="n">
-        <v>-0.2293</v>
+        <v>0.0009</v>
       </c>
       <c r="M227" s="6" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -14804,22 +14804,22 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>10.532</v>
+        <v>10.574</v>
       </c>
       <c r="H228" t="n">
-        <v>10.4031</v>
+        <v>10.3998</v>
       </c>
       <c r="I228" t="n">
-        <v>10.3464</v>
+        <v>10.2839</v>
       </c>
       <c r="J228" t="n">
-        <v>60.8</v>
+        <v>63.1</v>
       </c>
       <c r="K228" t="n">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
       <c r="L228" t="n">
-        <v>0.0167</v>
+        <v>0.0129</v>
       </c>
       <c r="M228" s="6" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -14867,22 +14867,22 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>9.913</v>
+        <v>9.922000000000001</v>
       </c>
       <c r="H229" t="n">
-        <v>9.930400000000001</v>
+        <v>9.93</v>
       </c>
       <c r="I229" t="n">
-        <v>9.963200000000001</v>
+        <v>9.9413</v>
       </c>
       <c r="J229" t="n">
-        <v>45.2</v>
+        <v>48</v>
       </c>
       <c r="K229" t="n">
-        <v>14.5</v>
+        <v>17.4</v>
       </c>
       <c r="L229" t="n">
-        <v>0.001</v>
+        <v>-0.0002</v>
       </c>
       <c r="M229" s="6" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -14930,22 +14930,22 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>5.948</v>
+        <v>5.985</v>
       </c>
       <c r="H230" t="n">
-        <v>5.9315</v>
+        <v>5.9454</v>
       </c>
       <c r="I230" t="n">
-        <v>6.3945</v>
+        <v>6.3798</v>
       </c>
       <c r="J230" t="n">
-        <v>48.5</v>
+        <v>49.3</v>
       </c>
       <c r="K230" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="L230" t="n">
-        <v>0.0645</v>
+        <v>0.0608</v>
       </c>
       <c r="M230" s="6" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -14993,22 +14993,22 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>216.7</v>
+        <v>217.1</v>
       </c>
       <c r="H231" t="n">
-        <v>211.1017</v>
+        <v>211.0069</v>
       </c>
       <c r="I231" t="n">
-        <v>208.044</v>
+        <v>207.2152</v>
       </c>
       <c r="J231" t="n">
-        <v>71.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K231" t="n">
-        <v>24.1</v>
+        <v>20.1</v>
       </c>
       <c r="L231" t="n">
-        <v>0.9228</v>
+        <v>0.877</v>
       </c>
       <c r="M231" s="6" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -15056,22 +15056,22 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>367.9</v>
+        <v>368.375</v>
       </c>
       <c r="H232" t="n">
-        <v>358.8273</v>
+        <v>358.5662</v>
       </c>
       <c r="I232" t="n">
-        <v>354.94</v>
+        <v>352.2025</v>
       </c>
       <c r="J232" t="n">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="K232" t="n">
-        <v>20.1</v>
+        <v>12.6</v>
       </c>
       <c r="L232" t="n">
-        <v>1.5303</v>
+        <v>1.2794</v>
       </c>
       <c r="M232" s="6" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -15122,19 +15122,19 @@
         <v>6.746</v>
       </c>
       <c r="H233" t="n">
-        <v>6.546</v>
+        <v>6.565</v>
       </c>
       <c r="I233" t="n">
-        <v>6.3875</v>
+        <v>6.4008</v>
       </c>
       <c r="J233" t="n">
         <v>68.59999999999999</v>
       </c>
       <c r="K233" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="L233" t="n">
-        <v>0.0146</v>
+        <v>0.0175</v>
       </c>
       <c r="M233" s="6" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -15182,22 +15182,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>142.75</v>
+        <v>143.2</v>
       </c>
       <c r="H234" t="n">
-        <v>142.7</v>
+        <v>142.74</v>
       </c>
       <c r="I234" t="n">
-        <v>142.9022</v>
+        <v>142.8028</v>
       </c>
       <c r="J234" t="n">
-        <v>50.6</v>
+        <v>57.7</v>
       </c>
       <c r="K234" t="n">
-        <v>7.7</v>
+        <v>12.1</v>
       </c>
       <c r="L234" t="n">
-        <v>0.0489</v>
+        <v>0.0742</v>
       </c>
       <c r="M234" s="6" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -15248,19 +15248,19 @@
         <v>0.6694</v>
       </c>
       <c r="H235" t="n">
-        <v>0.6839</v>
+        <v>0.6852</v>
       </c>
       <c r="I235" t="n">
-        <v>0.6936</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="J235" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="K235" t="n">
-        <v>19.1</v>
+        <v>12</v>
       </c>
       <c r="L235" t="n">
-        <v>-0.0022</v>
+        <v>-0.0014</v>
       </c>
       <c r="M235" s="6" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -15308,22 +15308,22 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>721.65</v>
+        <v>723.21</v>
       </c>
       <c r="H236" t="n">
-        <v>709.2702</v>
+        <v>709.0929</v>
       </c>
       <c r="I236" t="n">
-        <v>705.3844</v>
+        <v>703.2754</v>
       </c>
       <c r="J236" t="n">
-        <v>62.5</v>
+        <v>63.1</v>
       </c>
       <c r="K236" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="L236" t="n">
-        <v>2.1995</v>
+        <v>1.9988</v>
       </c>
       <c r="M236" s="6" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -15371,22 +15371,22 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>6.398</v>
+        <v>6.416</v>
       </c>
       <c r="H237" t="n">
-        <v>6.2833</v>
+        <v>6.2822</v>
       </c>
       <c r="I237" t="n">
-        <v>6.2401</v>
+        <v>6.2203</v>
       </c>
       <c r="J237" t="n">
-        <v>65.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="K237" t="n">
-        <v>18.3</v>
+        <v>16.4</v>
       </c>
       <c r="L237" t="n">
-        <v>0.0187</v>
+        <v>0.0171</v>
       </c>
       <c r="M237" s="6" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>2026-08-07 10:34</t>
+          <t>2026-08-09 21:35</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -6526,7 +6526,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -667,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -2179,7 +2179,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -604,7 +604,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>160.26</v>
+        <v>173.24</v>
       </c>
       <c r="H2" t="n">
-        <v>162.9448</v>
+        <v>168.8416</v>
       </c>
       <c r="I2" t="n">
-        <v>179.0125</v>
+        <v>174.051</v>
       </c>
       <c r="J2" t="n">
-        <v>45.9</v>
+        <v>53.7</v>
       </c>
       <c r="K2" t="n">
-        <v>19.7</v>
+        <v>11.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4753</v>
+        <v>1.2536</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>48.395</v>
+        <v>51.46</v>
       </c>
       <c r="H3" t="n">
-        <v>48.8939</v>
+        <v>50.1554</v>
       </c>
       <c r="I3" t="n">
-        <v>49.6129</v>
+        <v>49.9738</v>
       </c>
       <c r="J3" t="n">
-        <v>45.4</v>
+        <v>60</v>
       </c>
       <c r="K3" t="n">
-        <v>17.7</v>
+        <v>14.8</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0562</v>
+        <v>0.3312</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>140.32</v>
+        <v>145.66</v>
       </c>
       <c r="H4" t="n">
-        <v>133.8067</v>
+        <v>139.1903</v>
       </c>
       <c r="I4" t="n">
-        <v>134.5864</v>
+        <v>134.1088</v>
       </c>
       <c r="J4" t="n">
-        <v>64.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>21.7</v>
+        <v>20.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5516</v>
+        <v>0.6105</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -758,22 +758,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.938</v>
+        <v>2.976</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8584</v>
+        <v>2.9067</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7603</v>
+        <v>2.8342</v>
       </c>
       <c r="J5" t="n">
-        <v>63.1</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>21.7</v>
+        <v>20.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0073</v>
+        <v>-0.0021</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>24.935</v>
+        <v>24.63</v>
       </c>
       <c r="H6" t="n">
-        <v>25.4148</v>
+        <v>24.5263</v>
       </c>
       <c r="I6" t="n">
-        <v>24.7931</v>
+        <v>24.8082</v>
       </c>
       <c r="J6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K6" t="n">
-        <v>21.1</v>
+        <v>18.3</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0762</v>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.002</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>209.1</v>
+        <v>212.3</v>
       </c>
       <c r="H7" t="n">
-        <v>201.9889</v>
+        <v>206.4392</v>
       </c>
       <c r="I7" t="n">
-        <v>201.0564</v>
+        <v>201.5365</v>
       </c>
       <c r="J7" t="n">
-        <v>66.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4586</v>
+        <v>0.4389</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>498.8</v>
+        <v>523.1</v>
       </c>
       <c r="H8" t="n">
-        <v>501.742</v>
+        <v>517.058</v>
       </c>
       <c r="I8" t="n">
-        <v>485.072</v>
+        <v>496.812</v>
       </c>
       <c r="J8" t="n">
-        <v>50.1</v>
+        <v>59.6</v>
       </c>
       <c r="K8" t="n">
-        <v>22.2</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.9364</v>
+        <v>0.6837</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>42.72</v>
+        <v>42.025</v>
       </c>
       <c r="H9" t="n">
-        <v>42.5963</v>
+        <v>42.5941</v>
       </c>
       <c r="I9" t="n">
-        <v>44.3056</v>
+        <v>43.7204</v>
       </c>
       <c r="J9" t="n">
-        <v>48.6</v>
+        <v>43.1</v>
       </c>
       <c r="K9" t="n">
-        <v>17.2</v>
+        <v>14.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2228</v>
+        <v>-0.045</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>105.5</v>
+        <v>109.92</v>
       </c>
       <c r="H10" t="n">
-        <v>104.8408</v>
+        <v>108.7322</v>
       </c>
       <c r="I10" t="n">
-        <v>103.1195</v>
+        <v>104.5834</v>
       </c>
       <c r="J10" t="n">
-        <v>53.5</v>
+        <v>58.4</v>
       </c>
       <c r="K10" t="n">
-        <v>13.5</v>
+        <v>22.2</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0095</v>
+        <v>0.0828</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1136,22 +1136,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>47.49</v>
+        <v>48.09</v>
       </c>
       <c r="H11" t="n">
-        <v>45.8868</v>
+        <v>47.0747</v>
       </c>
       <c r="I11" t="n">
-        <v>44.4256</v>
+        <v>45.4573</v>
       </c>
       <c r="J11" t="n">
-        <v>70</v>
+        <v>63.8</v>
       </c>
       <c r="K11" t="n">
-        <v>27.9</v>
+        <v>25.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1744</v>
+        <v>-0.0761</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1199,22 +1199,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>52.63</v>
+        <v>52.97</v>
       </c>
       <c r="H12" t="n">
-        <v>52.1748</v>
+        <v>52.6244</v>
       </c>
       <c r="I12" t="n">
-        <v>53.9139</v>
+        <v>52.7161</v>
       </c>
       <c r="J12" t="n">
-        <v>51.1</v>
+        <v>52.6</v>
       </c>
       <c r="K12" t="n">
-        <v>16.6</v>
+        <v>10.1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2615</v>
+        <v>0.1111</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1262,31 +1262,31 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>39.345</v>
+        <v>40.415</v>
       </c>
       <c r="H13" t="n">
-        <v>39.3844</v>
+        <v>39.8886</v>
       </c>
       <c r="I13" t="n">
-        <v>40.7794</v>
+        <v>40.5244</v>
       </c>
       <c r="J13" t="n">
-        <v>48.3</v>
+        <v>53.5</v>
       </c>
       <c r="K13" t="n">
-        <v>16.7</v>
+        <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1656</v>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.1177</v>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1325,22 +1325,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>104.32</v>
+        <v>101.7</v>
       </c>
       <c r="H14" t="n">
-        <v>104.5374</v>
+        <v>102.7373</v>
       </c>
       <c r="I14" t="n">
-        <v>103.9662</v>
+        <v>104.1232</v>
       </c>
       <c r="J14" t="n">
-        <v>48.8</v>
+        <v>41.7</v>
       </c>
       <c r="K14" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2398</v>
+        <v>-0.1566</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1388,22 +1388,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>222.34</v>
+        <v>218.56</v>
       </c>
       <c r="H15" t="n">
-        <v>215.7998</v>
+        <v>218.6194</v>
       </c>
       <c r="I15" t="n">
-        <v>214.0482</v>
+        <v>216.7726</v>
       </c>
       <c r="J15" t="n">
-        <v>63.6</v>
+        <v>51.1</v>
       </c>
       <c r="K15" t="n">
-        <v>10.6</v>
+        <v>13.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8882</v>
+        <v>-0.6944</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1451,22 +1451,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>625.66</v>
+        <v>628.22</v>
       </c>
       <c r="H16" t="n">
-        <v>613.3434</v>
+        <v>624.0568</v>
       </c>
       <c r="I16" t="n">
-        <v>610.9178000000001</v>
+        <v>618.4206</v>
       </c>
       <c r="J16" t="n">
-        <v>58.9</v>
+        <v>54.8</v>
       </c>
       <c r="K16" t="n">
-        <v>9.1</v>
+        <v>13.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1285</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1514,22 +1514,22 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>15.504</v>
+        <v>16.104</v>
       </c>
       <c r="H17" t="n">
-        <v>14.4834</v>
+        <v>15.3135</v>
       </c>
       <c r="I17" t="n">
-        <v>14.4972</v>
+        <v>14.7056</v>
       </c>
       <c r="J17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K17" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0.151</v>
+        <v>0.0755</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1577,22 +1577,22 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>73.304</v>
+        <v>74.264</v>
       </c>
       <c r="H18" t="n">
-        <v>72.9074</v>
+        <v>73.6448</v>
       </c>
       <c r="I18" t="n">
-        <v>74.5592</v>
+        <v>74.2517</v>
       </c>
       <c r="J18" t="n">
-        <v>50.8</v>
+        <v>53</v>
       </c>
       <c r="K18" t="n">
-        <v>17.1</v>
+        <v>8.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2863</v>
+        <v>0.1024</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1640,22 +1640,22 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>99.38</v>
+        <v>100.63</v>
       </c>
       <c r="H19" t="n">
-        <v>98.8079</v>
+        <v>99.8035</v>
       </c>
       <c r="I19" t="n">
-        <v>101.055</v>
+        <v>100.6356</v>
       </c>
       <c r="J19" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="K19" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3875</v>
+        <v>0.1434</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1703,31 +1703,31 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7.5248</v>
+        <v>7.6176</v>
       </c>
       <c r="H20" t="n">
-        <v>7.4824</v>
+        <v>7.5568</v>
       </c>
       <c r="I20" t="n">
-        <v>7.6564</v>
+        <v>7.6219</v>
       </c>
       <c r="J20" t="n">
-        <v>50.8</v>
+        <v>52.9</v>
       </c>
       <c r="K20" t="n">
-        <v>15.3</v>
+        <v>8.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0118</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1766,22 +1766,22 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>151.09</v>
+        <v>148.53</v>
       </c>
       <c r="H21" t="n">
-        <v>146.7033</v>
+        <v>148.5767</v>
       </c>
       <c r="I21" t="n">
-        <v>145.4437</v>
+        <v>147.3127</v>
       </c>
       <c r="J21" t="n">
-        <v>63.5</v>
+        <v>51</v>
       </c>
       <c r="K21" t="n">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6001</v>
+        <v>-0.4769</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1829,22 +1829,22 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>75.06</v>
+        <v>74.7</v>
       </c>
       <c r="H22" t="n">
-        <v>72.88209999999999</v>
+        <v>73.9417</v>
       </c>
       <c r="I22" t="n">
-        <v>69.7135</v>
+        <v>72.0916</v>
       </c>
       <c r="J22" t="n">
-        <v>66</v>
+        <v>58.2</v>
       </c>
       <c r="K22" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1348</v>
+        <v>-0.299</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1892,22 +1892,22 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7.222</v>
+        <v>7.301</v>
       </c>
       <c r="H23" t="n">
-        <v>7.1937</v>
+        <v>7.2558</v>
       </c>
       <c r="I23" t="n">
-        <v>7.3753</v>
+        <v>7.3339</v>
       </c>
       <c r="J23" t="n">
-        <v>50.1</v>
+        <v>52.1</v>
       </c>
       <c r="K23" t="n">
-        <v>15.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.028</v>
+        <v>0.0101</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1955,22 +1955,22 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>259.05</v>
+        <v>257.45</v>
       </c>
       <c r="H24" t="n">
-        <v>253.8154</v>
+        <v>256.3548</v>
       </c>
       <c r="I24" t="n">
-        <v>251.51</v>
+        <v>254.068</v>
       </c>
       <c r="J24" t="n">
-        <v>67.09999999999999</v>
+        <v>56</v>
       </c>
       <c r="K24" t="n">
-        <v>15.8</v>
+        <v>17.1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7809</v>
+        <v>-0.4824</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2018,22 +2018,22 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>362.39</v>
+        <v>353</v>
       </c>
       <c r="H25" t="n">
-        <v>354.265</v>
+        <v>356.22</v>
       </c>
       <c r="I25" t="n">
-        <v>354.309</v>
+        <v>357.5541</v>
       </c>
       <c r="J25" t="n">
-        <v>58.4</v>
+        <v>46.4</v>
       </c>
       <c r="K25" t="n">
-        <v>10.9</v>
+        <v>13.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2827</v>
+        <v>-1.2891</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2081,22 +2081,22 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>98.14</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>97.6337</v>
+        <v>98.5659</v>
       </c>
       <c r="I26" t="n">
-        <v>99.5552</v>
+        <v>99.252</v>
       </c>
       <c r="J26" t="n">
-        <v>50.9</v>
+        <v>51.9</v>
       </c>
       <c r="K26" t="n">
-        <v>13.4</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3368</v>
+        <v>0.0987</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2144,22 +2144,22 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>35.185</v>
+        <v>36.33</v>
       </c>
       <c r="H27" t="n">
-        <v>34.7782</v>
+        <v>35.8955</v>
       </c>
       <c r="I27" t="n">
-        <v>34.6829</v>
+        <v>34.7695</v>
       </c>
       <c r="J27" t="n">
-        <v>55.2</v>
+        <v>57.8</v>
       </c>
       <c r="K27" t="n">
-        <v>14.6</v>
+        <v>20.7</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0032</v>
+        <v>0.074</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2207,22 +2207,22 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>125.28</v>
+        <v>128.39</v>
       </c>
       <c r="H28" t="n">
-        <v>124.2789</v>
+        <v>126.6266</v>
       </c>
       <c r="I28" t="n">
-        <v>128.4711</v>
+        <v>127.4388</v>
       </c>
       <c r="J28" t="n">
-        <v>50.8</v>
+        <v>54.2</v>
       </c>
       <c r="K28" t="n">
-        <v>12.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>0.716</v>
+        <v>0.3672</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2270,22 +2270,22 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>58.29</v>
+        <v>57.85</v>
       </c>
       <c r="H29" t="n">
-        <v>56.385</v>
+        <v>57.0607</v>
       </c>
       <c r="I29" t="n">
-        <v>55.3538</v>
+        <v>56.005</v>
       </c>
       <c r="J29" t="n">
-        <v>71.3</v>
+        <v>62.2</v>
       </c>
       <c r="K29" t="n">
-        <v>18.8</v>
+        <v>17.6</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2341</v>
+        <v>-0.0485</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2333,22 +2333,22 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>479</v>
+        <v>477.8</v>
       </c>
       <c r="H30" t="n">
-        <v>471.5696</v>
+        <v>474.4539</v>
       </c>
       <c r="I30" t="n">
-        <v>458.9294</v>
+        <v>466.9999</v>
       </c>
       <c r="J30" t="n">
-        <v>72.2</v>
+        <v>62.9</v>
       </c>
       <c r="K30" t="n">
-        <v>41.2</v>
+        <v>26.9</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1771</v>
+        <v>-0.8336</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2396,22 +2396,22 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>402.9</v>
+        <v>401.55</v>
       </c>
       <c r="H31" t="n">
-        <v>388.0148</v>
+        <v>396.4022</v>
       </c>
       <c r="I31" t="n">
-        <v>370.8588</v>
+        <v>384.801</v>
       </c>
       <c r="J31" t="n">
-        <v>68.3</v>
+        <v>60</v>
       </c>
       <c r="K31" t="n">
-        <v>21.3</v>
+        <v>24</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4543</v>
+        <v>-1.6301</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2459,22 +2459,22 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>25.23</v>
+        <v>25.125</v>
       </c>
       <c r="H32" t="n">
-        <v>24.4896</v>
+        <v>24.8806</v>
       </c>
       <c r="I32" t="n">
-        <v>23.7925</v>
+        <v>24.2116</v>
       </c>
       <c r="J32" t="n">
-        <v>80.59999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="K32" t="n">
-        <v>39.9</v>
+        <v>32.4</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0766</v>
+        <v>-0.0703</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2522,22 +2522,22 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>195.11</v>
+        <v>196.92</v>
       </c>
       <c r="H33" t="n">
-        <v>194.4535</v>
+        <v>196.6963</v>
       </c>
       <c r="I33" t="n">
-        <v>199.4596</v>
+        <v>198.5554</v>
       </c>
       <c r="J33" t="n">
-        <v>49.9</v>
+        <v>50.4</v>
       </c>
       <c r="K33" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>0.7448</v>
+        <v>0.1824</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2585,22 +2585,22 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>7.431</v>
+        <v>7.522</v>
       </c>
       <c r="H34" t="n">
-        <v>7.434</v>
+        <v>7.5003</v>
       </c>
       <c r="I34" t="n">
-        <v>7.6429</v>
+        <v>7.5893</v>
       </c>
       <c r="J34" t="n">
-        <v>48.8</v>
+        <v>50.8</v>
       </c>
       <c r="K34" t="n">
-        <v>10.5</v>
+        <v>8.1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2648,22 +2648,22 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>72.48999999999999</v>
+        <v>70.98</v>
       </c>
       <c r="H35" t="n">
-        <v>70.9828</v>
+        <v>70.9635</v>
       </c>
       <c r="I35" t="n">
-        <v>69.68210000000001</v>
+        <v>70.65519999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>62.4</v>
+        <v>51.1</v>
       </c>
       <c r="K35" t="n">
-        <v>22</v>
+        <v>10.8</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1541</v>
+        <v>-0.1621</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2711,22 +2711,22 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>158.34</v>
+        <v>156.4</v>
       </c>
       <c r="H36" t="n">
-        <v>153.8635</v>
+        <v>155.7946</v>
       </c>
       <c r="I36" t="n">
-        <v>151.3472</v>
+        <v>153.464</v>
       </c>
       <c r="J36" t="n">
-        <v>66.09999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="K36" t="n">
-        <v>21</v>
+        <v>16.1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8433</v>
+        <v>-0.4293</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2774,22 +2774,22 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>97.34</v>
+        <v>94.67</v>
       </c>
       <c r="H37" t="n">
-        <v>96.9978</v>
+        <v>94.9897</v>
       </c>
       <c r="I37" t="n">
-        <v>95.16160000000001</v>
+        <v>95.834</v>
       </c>
       <c r="J37" t="n">
-        <v>52.8</v>
+        <v>47.3</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>13.1</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.1888</v>
+        <v>-0.1558</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2837,22 +2837,22 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>69.91</v>
+        <v>69.56</v>
       </c>
       <c r="H38" t="n">
-        <v>68.90389999999999</v>
+        <v>69.3737</v>
       </c>
       <c r="I38" t="n">
-        <v>69.9374</v>
+        <v>69.95659999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>54.5</v>
+        <v>51</v>
       </c>
       <c r="K38" t="n">
-        <v>14.9</v>
+        <v>10.1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2787</v>
+        <v>-0.0307</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>69.86</v>
+        <v>70.19</v>
       </c>
       <c r="H39" t="n">
-        <v>69.0073</v>
+        <v>69.7034</v>
       </c>
       <c r="I39" t="n">
-        <v>70.5052</v>
+        <v>70.2092</v>
       </c>
       <c r="J39" t="n">
-        <v>53.1</v>
+        <v>52.5</v>
       </c>
       <c r="K39" t="n">
-        <v>15.8</v>
+        <v>9.6</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3536</v>
+        <v>0.0505</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2963,22 +2963,22 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>346.9</v>
+        <v>339.8</v>
       </c>
       <c r="H40" t="n">
-        <v>345.0831</v>
+        <v>341.7948</v>
       </c>
       <c r="I40" t="n">
-        <v>337.5666</v>
+        <v>340.909</v>
       </c>
       <c r="J40" t="n">
-        <v>56</v>
+        <v>45.5</v>
       </c>
       <c r="K40" t="n">
-        <v>17.4</v>
+        <v>13.5</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.2714</v>
+        <v>-0.8522</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3026,22 +3026,22 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>720</v>
+        <v>730.4</v>
       </c>
       <c r="H41" t="n">
-        <v>711.9295</v>
+        <v>719.1455999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>704.792</v>
+        <v>710.15</v>
       </c>
       <c r="J41" t="n">
-        <v>60</v>
+        <v>65.7</v>
       </c>
       <c r="K41" t="n">
-        <v>19.5</v>
+        <v>16.3</v>
       </c>
       <c r="L41" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.5833</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3089,22 +3089,22 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>448.25</v>
+        <v>446.5</v>
       </c>
       <c r="H42" t="n">
-        <v>442.6686</v>
+        <v>444.5779</v>
       </c>
       <c r="I42" t="n">
-        <v>441.3612</v>
+        <v>442.49</v>
       </c>
       <c r="J42" t="n">
-        <v>61.5</v>
+        <v>53.9</v>
       </c>
       <c r="K42" t="n">
-        <v>21.1</v>
+        <v>12.9</v>
       </c>
       <c r="L42" t="n">
-        <v>1.2123</v>
+        <v>-0.6502</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3152,22 +3152,22 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>197.7</v>
+        <v>196.6</v>
       </c>
       <c r="H43" t="n">
-        <v>193.9403</v>
+        <v>195.3595</v>
       </c>
       <c r="I43" t="n">
-        <v>188.9804</v>
+        <v>192.4008</v>
       </c>
       <c r="J43" t="n">
-        <v>69</v>
+        <v>59.5</v>
       </c>
       <c r="K43" t="n">
-        <v>35.4</v>
+        <v>21.5</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3116</v>
+        <v>-0.4651</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3215,22 +3215,22 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>252.05</v>
+        <v>251.4</v>
       </c>
       <c r="H44" t="n">
-        <v>247.8451</v>
+        <v>249.8229</v>
       </c>
       <c r="I44" t="n">
-        <v>244.1128</v>
+        <v>247.2018</v>
       </c>
       <c r="J44" t="n">
-        <v>67.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="K44" t="n">
-        <v>28.5</v>
+        <v>18.8</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4157</v>
+        <v>-0.3316</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3278,22 +3278,22 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>126.78</v>
+        <v>126.44</v>
       </c>
       <c r="H45" t="n">
-        <v>124.6297</v>
+        <v>125.5781</v>
       </c>
       <c r="I45" t="n">
-        <v>122.726</v>
+        <v>124.2888</v>
       </c>
       <c r="J45" t="n">
-        <v>67.09999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="K45" t="n">
-        <v>25.6</v>
+        <v>18.1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2005</v>
+        <v>-0.1625</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3341,22 +3341,22 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>55.07</v>
+        <v>54.11</v>
       </c>
       <c r="H46" t="n">
-        <v>53.849</v>
+        <v>54.2172</v>
       </c>
       <c r="I46" t="n">
-        <v>53.062</v>
+        <v>53.7732</v>
       </c>
       <c r="J46" t="n">
-        <v>64.40000000000001</v>
+        <v>50.4</v>
       </c>
       <c r="K46" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1589</v>
+        <v>-0.1528</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3404,22 +3404,22 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>99.79000000000001</v>
+        <v>99.67</v>
       </c>
       <c r="H47" t="n">
-        <v>98.1523</v>
+        <v>98.91719999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>97.0566</v>
+        <v>98.13200000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>66.2</v>
+        <v>60.8</v>
       </c>
       <c r="K47" t="n">
-        <v>24.8</v>
+        <v>17.8</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1897</v>
+        <v>-0.1105</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3467,22 +3467,22 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>453.85</v>
+        <v>451.8</v>
       </c>
       <c r="H48" t="n">
-        <v>445.7298</v>
+        <v>448.7906</v>
       </c>
       <c r="I48" t="n">
-        <v>439.078</v>
+        <v>444.458</v>
       </c>
       <c r="J48" t="n">
-        <v>68.5</v>
+        <v>59.7</v>
       </c>
       <c r="K48" t="n">
-        <v>26.4</v>
+        <v>18.4</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7556</v>
+        <v>-0.6099</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3530,22 +3530,22 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>393.97</v>
+        <v>388.43</v>
       </c>
       <c r="H49" t="n">
-        <v>389.7282</v>
+        <v>391.0028</v>
       </c>
       <c r="I49" t="n">
-        <v>387.807</v>
+        <v>391.6199</v>
       </c>
       <c r="J49" t="n">
-        <v>57.2</v>
+        <v>45.4</v>
       </c>
       <c r="K49" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="L49" t="n">
-        <v>0.516</v>
+        <v>-0.8675</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3593,22 +3593,22 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6.857</v>
+        <v>6.837</v>
       </c>
       <c r="H50" t="n">
-        <v>6.7327</v>
+        <v>6.7963</v>
       </c>
       <c r="I50" t="n">
-        <v>6.6324</v>
+        <v>6.7189</v>
       </c>
       <c r="J50" t="n">
-        <v>68.09999999999999</v>
+        <v>59.1</v>
       </c>
       <c r="K50" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0125</v>
+        <v>-0.0091</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3656,22 +3656,22 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>31.33</v>
+        <v>31.245</v>
       </c>
       <c r="H51" t="n">
-        <v>30.9763</v>
+        <v>31.0679</v>
       </c>
       <c r="I51" t="n">
-        <v>30.7165</v>
+        <v>30.9876</v>
       </c>
       <c r="J51" t="n">
-        <v>61.8</v>
+        <v>57.4</v>
       </c>
       <c r="K51" t="n">
-        <v>25.5</v>
+        <v>12.4</v>
       </c>
       <c r="L51" t="n">
-        <v>0.0256</v>
+        <v>-0.0242</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3719,22 +3719,22 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>42.885</v>
+        <v>42.83</v>
       </c>
       <c r="H52" t="n">
-        <v>42.4643</v>
+        <v>42.5535</v>
       </c>
       <c r="I52" t="n">
-        <v>42.1229</v>
+        <v>42.4851</v>
       </c>
       <c r="J52" t="n">
-        <v>59.8</v>
+        <v>57.4</v>
       </c>
       <c r="K52" t="n">
-        <v>17.1</v>
+        <v>11.7</v>
       </c>
       <c r="L52" t="n">
-        <v>0.0312</v>
+        <v>-0.0299</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3782,31 +3782,31 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>155.06</v>
+        <v>156.2</v>
       </c>
       <c r="H53" t="n">
-        <v>154.1889</v>
+        <v>154.5751</v>
       </c>
       <c r="I53" t="n">
-        <v>152.7297</v>
+        <v>154.3367</v>
       </c>
       <c r="J53" t="n">
-        <v>52.8</v>
+        <v>55.8</v>
       </c>
       <c r="K53" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.2802</v>
-      </c>
-      <c r="M53" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.335</v>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3845,22 +3845,22 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>132.78</v>
+        <v>129.82</v>
       </c>
       <c r="H54" t="n">
-        <v>129.9458</v>
+        <v>130.3766</v>
       </c>
       <c r="I54" t="n">
-        <v>128.828</v>
+        <v>130.1476</v>
       </c>
       <c r="J54" t="n">
-        <v>62.6</v>
+        <v>47.9</v>
       </c>
       <c r="K54" t="n">
-        <v>15.1</v>
+        <v>10.5</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4142</v>
+        <v>-0.3481</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3908,22 +3908,22 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>127.68</v>
+        <v>127.44</v>
       </c>
       <c r="H55" t="n">
-        <v>125.0653</v>
+        <v>126.1435</v>
       </c>
       <c r="I55" t="n">
-        <v>123.4252</v>
+        <v>124.9616</v>
       </c>
       <c r="J55" t="n">
-        <v>67.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="K55" t="n">
-        <v>19.7</v>
+        <v>16.2</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2739</v>
+        <v>-0.057</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -3971,22 +3971,22 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>111.11</v>
+        <v>106.66</v>
       </c>
       <c r="H56" t="n">
-        <v>109.217</v>
+        <v>109.2443</v>
       </c>
       <c r="I56" t="n">
-        <v>113.4906</v>
+        <v>112.407</v>
       </c>
       <c r="J56" t="n">
-        <v>52.1</v>
+        <v>44.4</v>
       </c>
       <c r="K56" t="n">
-        <v>16.5</v>
+        <v>10.6</v>
       </c>
       <c r="L56" t="n">
-        <v>0.6701</v>
+        <v>-0.3334</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4034,22 +4034,22 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>132.8</v>
+        <v>129.62</v>
       </c>
       <c r="H57" t="n">
-        <v>129.9027</v>
+        <v>130.3574</v>
       </c>
       <c r="I57" t="n">
-        <v>128.8128</v>
+        <v>130.1368</v>
       </c>
       <c r="J57" t="n">
-        <v>62.3</v>
+        <v>46.7</v>
       </c>
       <c r="K57" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4257</v>
+        <v>-0.3942</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4097,22 +4097,22 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>74.31999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="H58" t="n">
-        <v>72.4389</v>
+        <v>73.41249999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>71.2118</v>
+        <v>72.3462</v>
       </c>
       <c r="J58" t="n">
-        <v>68.2</v>
+        <v>57</v>
       </c>
       <c r="K58" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2486</v>
+        <v>-0.1666</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4160,22 +4160,22 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>43.805</v>
+        <v>43.675</v>
       </c>
       <c r="H59" t="n">
-        <v>42.604</v>
+        <v>43.3065</v>
       </c>
       <c r="I59" t="n">
-        <v>42.049</v>
+        <v>42.6545</v>
       </c>
       <c r="J59" t="n">
-        <v>67.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="K59" t="n">
-        <v>17.7</v>
+        <v>19.8</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1713</v>
+        <v>-0.0699</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4223,22 +4223,22 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>429.7</v>
+        <v>426.1</v>
       </c>
       <c r="H60" t="n">
-        <v>421.4007</v>
+        <v>423.9702</v>
       </c>
       <c r="I60" t="n">
-        <v>418.58</v>
+        <v>422.143</v>
       </c>
       <c r="J60" t="n">
-        <v>64.7</v>
+        <v>55.6</v>
       </c>
       <c r="K60" t="n">
-        <v>17.1</v>
+        <v>14.5</v>
       </c>
       <c r="L60" t="n">
-        <v>1.1821</v>
+        <v>-0.7015</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4286,22 +4286,22 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>473.3</v>
+        <v>466.95</v>
       </c>
       <c r="H61" t="n">
-        <v>467.1779</v>
+        <v>466.7478</v>
       </c>
       <c r="I61" t="n">
-        <v>460.724</v>
+        <v>465.722</v>
       </c>
       <c r="J61" t="n">
-        <v>58.5</v>
+        <v>51</v>
       </c>
       <c r="K61" t="n">
-        <v>24.6</v>
+        <v>14.2</v>
       </c>
       <c r="L61" t="n">
-        <v>0.8396</v>
+        <v>-1.2102</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4349,22 +4349,22 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.184</v>
+        <v>5.119</v>
       </c>
       <c r="H62" t="n">
-        <v>5.1004</v>
+        <v>5.1303</v>
       </c>
       <c r="I62" t="n">
-        <v>5.029</v>
+        <v>5.0825</v>
       </c>
       <c r="J62" t="n">
-        <v>63.4</v>
+        <v>49.8</v>
       </c>
       <c r="K62" t="n">
-        <v>16.9</v>
+        <v>16</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0067</v>
+        <v>-0.0143</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4412,22 +4412,22 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>220.55</v>
+        <v>219.45</v>
       </c>
       <c r="H63" t="n">
-        <v>216.2319</v>
+        <v>218.3492</v>
       </c>
       <c r="I63" t="n">
-        <v>215.553</v>
+        <v>217.184</v>
       </c>
       <c r="J63" t="n">
-        <v>63.2</v>
+        <v>55.5</v>
       </c>
       <c r="K63" t="n">
-        <v>19.7</v>
+        <v>12.6</v>
       </c>
       <c r="L63" t="n">
-        <v>0.6532</v>
+        <v>-0.2034</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4475,22 +4475,22 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>93.56999999999999</v>
+        <v>93</v>
       </c>
       <c r="H64" t="n">
-        <v>92.1229</v>
+        <v>92.58929999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>91.5598</v>
+        <v>92.259</v>
       </c>
       <c r="J64" t="n">
-        <v>62.5</v>
+        <v>56</v>
       </c>
       <c r="K64" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="L64" t="n">
-        <v>0.197</v>
+        <v>-0.073</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4538,22 +4538,22 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>43.325</v>
+        <v>42.875</v>
       </c>
       <c r="H65" t="n">
-        <v>43.8211</v>
+        <v>43.1391</v>
       </c>
       <c r="I65" t="n">
-        <v>43.1877</v>
+        <v>43.4127</v>
       </c>
       <c r="J65" t="n">
-        <v>43</v>
+        <v>44.1</v>
       </c>
       <c r="K65" t="n">
-        <v>22</v>
+        <v>18.9</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.1992</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4601,22 +4601,22 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>174.52</v>
+        <v>166.32</v>
       </c>
       <c r="H66" t="n">
-        <v>171.6288</v>
+        <v>170.5487</v>
       </c>
       <c r="I66" t="n">
-        <v>175.4448</v>
+        <v>174.4792</v>
       </c>
       <c r="J66" t="n">
-        <v>54</v>
+        <v>39.6</v>
       </c>
       <c r="K66" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5723</v>
+        <v>-0.4108</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4664,22 +4664,22 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>72.56</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>71.55759999999999</v>
+        <v>72.04519999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>71.1482</v>
+        <v>71.69799999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>66</v>
+        <v>52.1</v>
       </c>
       <c r="K67" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="L67" t="n">
-        <v>0.1065</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>613.1799999999999</v>
+        <v>606.8</v>
       </c>
       <c r="H68" t="n">
-        <v>601.8099</v>
+        <v>606.7602000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>598.4139</v>
+        <v>602.9212</v>
       </c>
       <c r="J68" t="n">
-        <v>63.9</v>
+        <v>51.5</v>
       </c>
       <c r="K68" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="L68" t="n">
-        <v>1.6766</v>
+        <v>-1.1848</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4790,22 +4790,22 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>171.17</v>
+        <v>170.54</v>
       </c>
       <c r="H69" t="n">
-        <v>170.9388</v>
+        <v>170.833</v>
       </c>
       <c r="I69" t="n">
-        <v>171.3316</v>
+        <v>171.1758</v>
       </c>
       <c r="J69" t="n">
-        <v>53</v>
+        <v>43.4</v>
       </c>
       <c r="K69" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="L69" t="n">
-        <v>0.0457</v>
+        <v>-0.0366</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -4853,22 +4853,22 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5.2116</v>
+        <v>5.197</v>
       </c>
       <c r="H70" t="n">
-        <v>5.2033</v>
+        <v>5.1989</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2089</v>
+        <v>5.2092</v>
       </c>
       <c r="J70" t="n">
-        <v>54.8</v>
+        <v>48</v>
       </c>
       <c r="K70" t="n">
-        <v>18.7</v>
+        <v>11.2</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -4916,22 +4916,22 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6.271</v>
+        <v>6.168</v>
       </c>
       <c r="H71" t="n">
-        <v>6.1586</v>
+        <v>6.2106</v>
       </c>
       <c r="I71" t="n">
-        <v>6.0901</v>
+        <v>6.1419</v>
       </c>
       <c r="J71" t="n">
-        <v>64.5</v>
+        <v>46.2</v>
       </c>
       <c r="K71" t="n">
-        <v>14.9</v>
+        <v>16.1</v>
       </c>
       <c r="L71" t="n">
-        <v>0.014</v>
+        <v>-0.0139</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -4979,22 +4979,22 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>153.61</v>
+        <v>152.21</v>
       </c>
       <c r="H72" t="n">
-        <v>153.2756</v>
+        <v>152.5357</v>
       </c>
       <c r="I72" t="n">
-        <v>154</v>
+        <v>153.649</v>
       </c>
       <c r="J72" t="n">
-        <v>52</v>
+        <v>45.2</v>
       </c>
       <c r="K72" t="n">
-        <v>21.7</v>
+        <v>14.7</v>
       </c>
       <c r="L72" t="n">
-        <v>0.197</v>
+        <v>-0.0604</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5042,22 +5042,22 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>513.3200000000001</v>
+        <v>531.8099999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>508.8793</v>
+        <v>521.4675</v>
       </c>
       <c r="I73" t="n">
-        <v>497.576</v>
+        <v>509.6248</v>
       </c>
       <c r="J73" t="n">
-        <v>55.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>14.8</v>
+        <v>22.1</v>
       </c>
       <c r="L73" t="n">
-        <v>-1.3364</v>
+        <v>1.1253</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5105,22 +5105,22 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>200.16</v>
+        <v>197.94</v>
       </c>
       <c r="H74" t="n">
-        <v>199.8235</v>
+        <v>198.4928</v>
       </c>
       <c r="I74" t="n">
-        <v>200.8988</v>
+        <v>200.2558</v>
       </c>
       <c r="J74" t="n">
-        <v>51.1</v>
+        <v>43.6</v>
       </c>
       <c r="K74" t="n">
-        <v>21.3</v>
+        <v>16.6</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2323</v>
+        <v>-0.0864</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5168,22 +5168,22 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>4.948</v>
+        <v>4.9385</v>
       </c>
       <c r="H75" t="n">
-        <v>4.9403</v>
+        <v>4.9436</v>
       </c>
       <c r="I75" t="n">
-        <v>4.9442</v>
+        <v>4.9472</v>
       </c>
       <c r="J75" t="n">
-        <v>52.8</v>
+        <v>47.9</v>
       </c>
       <c r="K75" t="n">
-        <v>19.7</v>
+        <v>8.6</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0014</v>
+        <v>-0.0004</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5231,22 +5231,22 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>128.65</v>
+        <v>126.87</v>
       </c>
       <c r="H76" t="n">
-        <v>126.0804</v>
+        <v>127.0381</v>
       </c>
       <c r="I76" t="n">
-        <v>124.845</v>
+        <v>126.0044</v>
       </c>
       <c r="J76" t="n">
-        <v>65.8</v>
+        <v>50.5</v>
       </c>
       <c r="K76" t="n">
-        <v>16.7</v>
+        <v>15.1</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3277</v>
+        <v>-0.3053</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5294,22 +5294,22 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>228.72</v>
+        <v>227.83</v>
       </c>
       <c r="H77" t="n">
-        <v>228.291</v>
+        <v>228.044</v>
       </c>
       <c r="I77" t="n">
-        <v>228.5287</v>
+        <v>228.4766</v>
       </c>
       <c r="J77" t="n">
-        <v>54.7</v>
+        <v>46.2</v>
       </c>
       <c r="K77" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="L77" t="n">
-        <v>0.1629</v>
+        <v>-0.0456</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5357,22 +5357,22 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>14.1346</v>
+        <v>14.304</v>
       </c>
       <c r="H78" t="n">
-        <v>13.8125</v>
+        <v>14.1309</v>
       </c>
       <c r="I78" t="n">
-        <v>13.6505</v>
+        <v>13.8427</v>
       </c>
       <c r="J78" t="n">
-        <v>67.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>65.09999999999999</v>
+        <v>25.9</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0481</v>
+        <v>-0.0068</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5420,22 +5420,22 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>270.6</v>
+        <v>268.85</v>
       </c>
       <c r="H79" t="n">
-        <v>263.985</v>
+        <v>267.5988</v>
       </c>
       <c r="I79" t="n">
-        <v>261.741</v>
+        <v>264.036</v>
       </c>
       <c r="J79" t="n">
-        <v>67.7</v>
+        <v>56.8</v>
       </c>
       <c r="K79" t="n">
-        <v>17.9</v>
+        <v>18.9</v>
       </c>
       <c r="L79" t="n">
-        <v>0.9906</v>
+        <v>-0.3957</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -5483,22 +5483,22 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>54.42</v>
+        <v>54.25</v>
       </c>
       <c r="H80" t="n">
-        <v>54.2984</v>
+        <v>54.2402</v>
       </c>
       <c r="I80" t="n">
-        <v>54.3631</v>
+        <v>54.3488</v>
       </c>
       <c r="J80" t="n">
-        <v>55.4</v>
+        <v>49.8</v>
       </c>
       <c r="K80" t="n">
-        <v>21</v>
+        <v>10.4</v>
       </c>
       <c r="L80" t="n">
-        <v>0.035</v>
+        <v>-0.0067</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -5546,22 +5546,22 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>282.65</v>
+        <v>269.95</v>
       </c>
       <c r="H81" t="n">
-        <v>276.7342</v>
+        <v>275.0829</v>
       </c>
       <c r="I81" t="n">
-        <v>281.395</v>
+        <v>277.912</v>
       </c>
       <c r="J81" t="n">
-        <v>57.5</v>
+        <v>39.3</v>
       </c>
       <c r="K81" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="L81" t="n">
-        <v>1.7338</v>
+        <v>-0.9843</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -5609,22 +5609,22 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>153.045</v>
+        <v>151.745</v>
       </c>
       <c r="H82" t="n">
-        <v>152.8389</v>
+        <v>152.1472</v>
       </c>
       <c r="I82" t="n">
-        <v>153.4197</v>
+        <v>153.0919</v>
       </c>
       <c r="J82" t="n">
-        <v>51.2</v>
+        <v>42.9</v>
       </c>
       <c r="K82" t="n">
-        <v>24.5</v>
+        <v>13.1</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1416</v>
+        <v>-0.0397</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5672,22 +5672,22 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>232.91</v>
+        <v>230.8</v>
       </c>
       <c r="H83" t="n">
-        <v>232.5086</v>
+        <v>231.6066</v>
       </c>
       <c r="I83" t="n">
-        <v>233.2177</v>
+        <v>232.8236</v>
       </c>
       <c r="J83" t="n">
-        <v>52.8</v>
+        <v>38.8</v>
       </c>
       <c r="K83" t="n">
-        <v>16.6</v>
+        <v>17.4</v>
       </c>
       <c r="L83" t="n">
-        <v>0.2119</v>
+        <v>-0.093</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -5735,22 +5735,22 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>137.24</v>
+        <v>136.85</v>
       </c>
       <c r="H84" t="n">
-        <v>137.0859</v>
+        <v>136.9204</v>
       </c>
       <c r="I84" t="n">
-        <v>137.358</v>
+        <v>137.2784</v>
       </c>
       <c r="J84" t="n">
-        <v>52.6</v>
+        <v>46.9</v>
       </c>
       <c r="K84" t="n">
-        <v>16.9</v>
+        <v>12.1</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0876</v>
+        <v>-0.019</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>45.685</v>
+        <v>45.375</v>
       </c>
       <c r="H85" t="n">
-        <v>45.6049</v>
+        <v>45.464</v>
       </c>
       <c r="I85" t="n">
-        <v>45.7148</v>
+        <v>45.6562</v>
       </c>
       <c r="J85" t="n">
-        <v>53.4</v>
+        <v>42.5</v>
       </c>
       <c r="K85" t="n">
-        <v>22.4</v>
+        <v>15.8</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0364</v>
+        <v>-0.0155</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -5861,22 +5861,22 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>235.33</v>
+        <v>234.07</v>
       </c>
       <c r="H86" t="n">
-        <v>234.9282</v>
+        <v>234.2917</v>
       </c>
       <c r="I86" t="n">
-        <v>235.5612</v>
+        <v>235.251</v>
       </c>
       <c r="J86" t="n">
-        <v>52.7</v>
+        <v>46</v>
       </c>
       <c r="K86" t="n">
-        <v>25.7</v>
+        <v>13.8</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1894</v>
+        <v>-0.0428</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -5924,22 +5924,22 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>699.77</v>
+        <v>689.87</v>
       </c>
       <c r="H87" t="n">
-        <v>686.0562</v>
+        <v>691.0962</v>
       </c>
       <c r="I87" t="n">
-        <v>679.5491</v>
+        <v>685.7015</v>
       </c>
       <c r="J87" t="n">
-        <v>65.5</v>
+        <v>50.1</v>
       </c>
       <c r="K87" t="n">
         <v>16.2</v>
       </c>
       <c r="L87" t="n">
-        <v>1.765</v>
+        <v>-1.6878</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -5987,22 +5987,22 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>433.37</v>
+        <v>427.25</v>
       </c>
       <c r="H88" t="n">
-        <v>424.7825</v>
+        <v>427.9214</v>
       </c>
       <c r="I88" t="n">
-        <v>420.651</v>
+        <v>424.512</v>
       </c>
       <c r="J88" t="n">
-        <v>66</v>
+        <v>50.3</v>
       </c>
       <c r="K88" t="n">
-        <v>18.1</v>
+        <v>16.5</v>
       </c>
       <c r="L88" t="n">
-        <v>1.1061</v>
+        <v>-1.0493</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6050,22 +6050,22 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>267.94</v>
+        <v>267.83</v>
       </c>
       <c r="H89" t="n">
-        <v>267.3588</v>
+        <v>267.8385</v>
       </c>
       <c r="I89" t="n">
-        <v>267.3655</v>
+        <v>267.7348</v>
       </c>
       <c r="J89" t="n">
-        <v>55.8</v>
+        <v>51.1</v>
       </c>
       <c r="K89" t="n">
-        <v>18</v>
+        <v>10.6</v>
       </c>
       <c r="L89" t="n">
-        <v>0.1191</v>
+        <v>-0.028</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6113,22 +6113,22 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>41.673</v>
+        <v>41.338</v>
       </c>
       <c r="H90" t="n">
-        <v>41.6154</v>
+        <v>41.4477</v>
       </c>
       <c r="I90" t="n">
-        <v>41.7482</v>
+        <v>41.669</v>
       </c>
       <c r="J90" t="n">
-        <v>51.9</v>
+        <v>41.8</v>
       </c>
       <c r="K90" t="n">
-        <v>21.8</v>
+        <v>16.1</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0343</v>
+        <v>-0.0133</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6176,22 +6176,22 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>7.391</v>
+        <v>7.2924</v>
       </c>
       <c r="H91" t="n">
-        <v>7.3861</v>
+        <v>7.3315</v>
       </c>
       <c r="I91" t="n">
-        <v>7.4286</v>
+        <v>7.4003</v>
       </c>
       <c r="J91" t="n">
-        <v>49.6</v>
+        <v>39.5</v>
       </c>
       <c r="K91" t="n">
-        <v>25.7</v>
+        <v>18.3</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0078</v>
+        <v>-0.0043</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6239,22 +6239,22 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>19.192</v>
+        <v>18.914</v>
       </c>
       <c r="H92" t="n">
-        <v>18.8108</v>
+        <v>18.952</v>
       </c>
       <c r="I92" t="n">
-        <v>18.6298</v>
+        <v>18.8005</v>
       </c>
       <c r="J92" t="n">
-        <v>66.2</v>
+        <v>49.9</v>
       </c>
       <c r="K92" t="n">
-        <v>18.3</v>
+        <v>16.6</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0489</v>
+        <v>-0.0466</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6302,22 +6302,22 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>220.48</v>
+        <v>218.54</v>
       </c>
       <c r="H93" t="n">
-        <v>220.3663</v>
+        <v>219.3647</v>
       </c>
       <c r="I93" t="n">
-        <v>221.0404</v>
+        <v>220.6</v>
       </c>
       <c r="J93" t="n">
-        <v>50.1</v>
+        <v>40.6</v>
       </c>
       <c r="K93" t="n">
-        <v>17.4</v>
+        <v>14.7</v>
       </c>
       <c r="L93" t="n">
-        <v>0.1593</v>
+        <v>-0.0989</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -6365,22 +6365,22 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>48.975</v>
+        <v>48.79</v>
       </c>
       <c r="H94" t="n">
-        <v>49.0432</v>
+        <v>48.8686</v>
       </c>
       <c r="I94" t="n">
-        <v>49.199</v>
+        <v>49.1251</v>
       </c>
       <c r="J94" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="K94" t="n">
-        <v>18.3</v>
+        <v>14.1</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0181</v>
+        <v>-0.0107</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -6428,22 +6428,22 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>55.34</v>
+        <v>55.21</v>
       </c>
       <c r="H95" t="n">
-        <v>55.2363</v>
+        <v>55.2414</v>
       </c>
       <c r="I95" t="n">
-        <v>55.2422</v>
+        <v>55.2654</v>
       </c>
       <c r="J95" t="n">
-        <v>58.3</v>
+        <v>46.9</v>
       </c>
       <c r="K95" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0254</v>
+        <v>-0.0076</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6491,22 +6491,22 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>137.45</v>
+        <v>136.77</v>
       </c>
       <c r="H96" t="n">
-        <v>137.215</v>
+        <v>137.0477</v>
       </c>
       <c r="I96" t="n">
-        <v>137.4914</v>
+        <v>137.4054</v>
       </c>
       <c r="J96" t="n">
-        <v>54</v>
+        <v>42.7</v>
       </c>
       <c r="K96" t="n">
-        <v>13.8</v>
+        <v>12.1</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0898</v>
+        <v>-0.0267</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6554,22 +6554,22 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>22.745</v>
+        <v>22.705</v>
       </c>
       <c r="H97" t="n">
-        <v>22.6368</v>
+        <v>22.6846</v>
       </c>
       <c r="I97" t="n">
-        <v>22.646</v>
+        <v>22.6698</v>
       </c>
       <c r="J97" t="n">
-        <v>58</v>
+        <v>52.2</v>
       </c>
       <c r="K97" t="n">
-        <v>12.9</v>
+        <v>7.3</v>
       </c>
       <c r="L97" t="n">
-        <v>0.0177</v>
+        <v>0.0024</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -6617,22 +6617,22 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>24.735</v>
+        <v>24.345</v>
       </c>
       <c r="H98" t="n">
-        <v>24.0966</v>
+        <v>24.5034</v>
       </c>
       <c r="I98" t="n">
-        <v>25.0595</v>
+        <v>24.8054</v>
       </c>
       <c r="J98" t="n">
-        <v>55.3</v>
+        <v>47.5</v>
       </c>
       <c r="K98" t="n">
-        <v>21.9</v>
+        <v>12.5</v>
       </c>
       <c r="L98" t="n">
-        <v>0.1912</v>
+        <v>0.0004</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -6680,22 +6680,22 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>198.2</v>
+        <v>195.51</v>
       </c>
       <c r="H99" t="n">
-        <v>193.3098</v>
+        <v>195.6562</v>
       </c>
       <c r="I99" t="n">
-        <v>191.6155</v>
+        <v>193.5649</v>
       </c>
       <c r="J99" t="n">
-        <v>65.8</v>
+        <v>51.5</v>
       </c>
       <c r="K99" t="n">
-        <v>19.6</v>
+        <v>17</v>
       </c>
       <c r="L99" t="n">
-        <v>0.8353</v>
+        <v>-0.4947</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -6743,22 +6743,22 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>49.48</v>
+        <v>49.16</v>
       </c>
       <c r="H100" t="n">
-        <v>49.4265</v>
+        <v>49.2327</v>
       </c>
       <c r="I100" t="n">
-        <v>49.586</v>
+        <v>49.4954</v>
       </c>
       <c r="J100" t="n">
-        <v>51.2</v>
+        <v>44.1</v>
       </c>
       <c r="K100" t="n">
-        <v>22</v>
+        <v>15.9</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0386</v>
+        <v>-0.0123</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6806,22 +6806,22 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>131.375</v>
+        <v>131.01</v>
       </c>
       <c r="H101" t="n">
-        <v>131.1992</v>
+        <v>131.0514</v>
       </c>
       <c r="I101" t="n">
-        <v>131.3828</v>
+        <v>131.3172</v>
       </c>
       <c r="J101" t="n">
-        <v>53.5</v>
+        <v>47.6</v>
       </c>
       <c r="K101" t="n">
-        <v>24.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0728</v>
+        <v>-0.0072</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -6869,22 +6869,22 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>7.298</v>
+        <v>7.262</v>
       </c>
       <c r="H102" t="n">
-        <v>7.1121</v>
+        <v>7.2248</v>
       </c>
       <c r="I102" t="n">
-        <v>7.0509</v>
+        <v>7.1167</v>
       </c>
       <c r="J102" t="n">
-        <v>68.2</v>
+        <v>58.3</v>
       </c>
       <c r="K102" t="n">
-        <v>14.3</v>
+        <v>20.6</v>
       </c>
       <c r="L102" t="n">
-        <v>0.028</v>
+        <v>-0.0105</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -6932,22 +6932,22 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>141.915</v>
+        <v>138.95</v>
       </c>
       <c r="H103" t="n">
-        <v>141.9017</v>
+        <v>140.1045</v>
       </c>
       <c r="I103" t="n">
-        <v>143.1898</v>
+        <v>142.2602</v>
       </c>
       <c r="J103" t="n">
-        <v>48.7</v>
+        <v>39.6</v>
       </c>
       <c r="K103" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="L103" t="n">
-        <v>0.204</v>
+        <v>-0.1389</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -6995,22 +6995,22 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>104.84</v>
+        <v>104.78</v>
       </c>
       <c r="H104" t="n">
-        <v>104.7234</v>
+        <v>104.7498</v>
       </c>
       <c r="I104" t="n">
-        <v>104.709</v>
+        <v>104.7592</v>
       </c>
       <c r="J104" t="n">
-        <v>57.2</v>
+        <v>52.5</v>
       </c>
       <c r="K104" t="n">
-        <v>15.3</v>
+        <v>9.1</v>
       </c>
       <c r="L104" t="n">
-        <v>0.03</v>
+        <v>-0.0005</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7058,22 +7058,22 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>107.35</v>
+        <v>107.11</v>
       </c>
       <c r="H105" t="n">
-        <v>107.4243</v>
+        <v>107.3331</v>
       </c>
       <c r="I105" t="n">
-        <v>107.5779</v>
+        <v>107.5512</v>
       </c>
       <c r="J105" t="n">
-        <v>29.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K105" t="n">
-        <v>36</v>
+        <v>46.8</v>
       </c>
       <c r="L105" t="n">
-        <v>0.004</v>
+        <v>-0.0102</v>
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7121,22 +7121,22 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>203.16</v>
+        <v>201.49</v>
       </c>
       <c r="H106" t="n">
-        <v>203.1143</v>
+        <v>202.1836</v>
       </c>
       <c r="I106" t="n">
-        <v>203.8386</v>
+        <v>203.3558</v>
       </c>
       <c r="J106" t="n">
-        <v>49.3</v>
+        <v>38</v>
       </c>
       <c r="K106" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="L106" t="n">
-        <v>0.1521</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7184,22 +7184,22 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>112.88</v>
+        <v>113.02</v>
       </c>
       <c r="H107" t="n">
-        <v>112.7736</v>
+        <v>112.923</v>
       </c>
       <c r="I107" t="n">
-        <v>112.5927</v>
+        <v>112.741</v>
       </c>
       <c r="J107" t="n">
-        <v>62.9</v>
+        <v>59.6</v>
       </c>
       <c r="K107" t="n">
-        <v>70.3</v>
+        <v>26.2</v>
       </c>
       <c r="L107" t="n">
-        <v>-0.0025</v>
+        <v>-0.001</v>
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7247,22 +7247,22 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>5.0638</v>
+        <v>5.0642</v>
       </c>
       <c r="H108" t="n">
-        <v>5.0549</v>
+        <v>5.0622</v>
       </c>
       <c r="I108" t="n">
-        <v>5.0472</v>
+        <v>5.0538</v>
       </c>
       <c r="J108" t="n">
-        <v>72.7</v>
+        <v>58.3</v>
       </c>
       <c r="K108" t="n">
-        <v>15.9</v>
+        <v>29.9</v>
       </c>
       <c r="L108" t="n">
-        <v>0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7310,22 +7310,22 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>75.298</v>
+        <v>75.416</v>
       </c>
       <c r="H109" t="n">
-        <v>74.9281</v>
+        <v>75.1326</v>
       </c>
       <c r="I109" t="n">
-        <v>74.9092</v>
+        <v>75.0243</v>
       </c>
       <c r="J109" t="n">
-        <v>61</v>
+        <v>58.7</v>
       </c>
       <c r="K109" t="n">
-        <v>17.5</v>
+        <v>13.1</v>
       </c>
       <c r="L109" t="n">
-        <v>0.0645</v>
+        <v>0.0131</v>
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -7373,22 +7373,22 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>119.24</v>
+        <v>119.15</v>
       </c>
       <c r="H110" t="n">
-        <v>119.0898</v>
+        <v>119.1114</v>
       </c>
       <c r="I110" t="n">
-        <v>119.0886</v>
+        <v>119.1323</v>
       </c>
       <c r="J110" t="n">
-        <v>57.8</v>
+        <v>53.6</v>
       </c>
       <c r="K110" t="n">
-        <v>19.2</v>
+        <v>10.4</v>
       </c>
       <c r="L110" t="n">
-        <v>0.0362</v>
+        <v>0.0005</v>
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -7436,22 +7436,22 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>108.64</v>
+        <v>106.64</v>
       </c>
       <c r="H111" t="n">
-        <v>106.0285</v>
+        <v>106.8234</v>
       </c>
       <c r="I111" t="n">
-        <v>105.0945</v>
+        <v>105.7246</v>
       </c>
       <c r="J111" t="n">
-        <v>64.09999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="K111" t="n">
-        <v>15.9</v>
+        <v>12.3</v>
       </c>
       <c r="L111" t="n">
-        <v>0.4238</v>
+        <v>-0.2589</v>
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -7499,22 +7499,22 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>128.13</v>
+        <v>127.94</v>
       </c>
       <c r="H112" t="n">
-        <v>127.9695</v>
+        <v>127.9686</v>
       </c>
       <c r="I112" t="n">
-        <v>127.924</v>
+        <v>127.9876</v>
       </c>
       <c r="J112" t="n">
-        <v>58.4</v>
+        <v>48.7</v>
       </c>
       <c r="K112" t="n">
-        <v>16.2</v>
+        <v>8.5</v>
       </c>
       <c r="L112" t="n">
-        <v>0.0398</v>
+        <v>-0.0107</v>
       </c>
       <c r="M112" s="6" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7562,22 +7562,22 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>101.52</v>
+        <v>101.56</v>
       </c>
       <c r="H113" t="n">
-        <v>101.5432</v>
+        <v>101.5368</v>
       </c>
       <c r="I113" t="n">
-        <v>101.5572</v>
+        <v>101.5892</v>
       </c>
       <c r="J113" t="n">
-        <v>40.1</v>
+        <v>57.5</v>
       </c>
       <c r="K113" t="n">
-        <v>21.7</v>
+        <v>23.2</v>
       </c>
       <c r="L113" t="n">
-        <v>-0.0033</v>
+        <v>0.0075</v>
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7625,22 +7625,22 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>108.08</v>
+        <v>108.12</v>
       </c>
       <c r="H114" t="n">
-        <v>107.7865</v>
+        <v>107.9422</v>
       </c>
       <c r="I114" t="n">
-        <v>107.8022</v>
+        <v>107.9238</v>
       </c>
       <c r="J114" t="n">
-        <v>57.6</v>
+        <v>56.5</v>
       </c>
       <c r="K114" t="n">
-        <v>19.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L114" t="n">
-        <v>0.054</v>
+        <v>-0.0041</v>
       </c>
       <c r="M114" s="6" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -7688,22 +7688,22 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>54.49</v>
+        <v>54.518</v>
       </c>
       <c r="H115" t="n">
-        <v>54.4205</v>
+        <v>54.4651</v>
       </c>
       <c r="I115" t="n">
-        <v>54.3823</v>
+        <v>54.4288</v>
       </c>
       <c r="J115" t="n">
-        <v>60.3</v>
+        <v>60.8</v>
       </c>
       <c r="K115" t="n">
-        <v>16.4</v>
+        <v>14.1</v>
       </c>
       <c r="L115" t="n">
-        <v>0.0092</v>
+        <v>0.0021</v>
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -7751,22 +7751,22 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>85.12</v>
+        <v>84.11</v>
       </c>
       <c r="H116" t="n">
-        <v>85.34220000000001</v>
+        <v>84.95480000000001</v>
       </c>
       <c r="I116" t="n">
-        <v>85.22320000000001</v>
+        <v>85.37860000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>44.5</v>
+        <v>25.3</v>
       </c>
       <c r="K116" t="n">
-        <v>26.6</v>
+        <v>39.7</v>
       </c>
       <c r="L116" t="n">
-        <v>-0.0648</v>
+        <v>-0.1149</v>
       </c>
       <c r="M116" s="6" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -7814,22 +7814,22 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>412.31</v>
+        <v>409.51</v>
       </c>
       <c r="H117" t="n">
-        <v>407.3909</v>
+        <v>408.4608</v>
       </c>
       <c r="I117" t="n">
-        <v>393.2495</v>
+        <v>402.824</v>
       </c>
       <c r="J117" t="n">
-        <v>63.5</v>
+        <v>54.3</v>
       </c>
       <c r="K117" t="n">
-        <v>42.5</v>
+        <v>24.7</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-1.4668</v>
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -7877,22 +7877,22 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>44.18</v>
+        <v>43.04</v>
       </c>
       <c r="H118" t="n">
-        <v>43.1189</v>
+        <v>43.2507</v>
       </c>
       <c r="I118" t="n">
-        <v>42.4838</v>
+        <v>42.9006</v>
       </c>
       <c r="J118" t="n">
-        <v>69.7</v>
+        <v>47.1</v>
       </c>
       <c r="K118" t="n">
-        <v>23.1</v>
+        <v>16.4</v>
       </c>
       <c r="L118" t="n">
-        <v>0.1567</v>
+        <v>-0.1474</v>
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -7940,22 +7940,22 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>637.9</v>
+        <v>627.7</v>
       </c>
       <c r="H119" t="n">
-        <v>624.6549</v>
+        <v>629.0346</v>
       </c>
       <c r="I119" t="n">
-        <v>618.3579999999999</v>
+        <v>624.098</v>
       </c>
       <c r="J119" t="n">
-        <v>66.2</v>
+        <v>49.8</v>
       </c>
       <c r="K119" t="n">
-        <v>18.9</v>
+        <v>16.3</v>
       </c>
       <c r="L119" t="n">
-        <v>1.6411</v>
+        <v>-1.5878</v>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8003,22 +8003,22 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>138.43</v>
+        <v>138.59</v>
       </c>
       <c r="H120" t="n">
-        <v>138.212</v>
+        <v>138.4553</v>
       </c>
       <c r="I120" t="n">
-        <v>137.856</v>
+        <v>138.1288</v>
       </c>
       <c r="J120" t="n">
-        <v>62.2</v>
+        <v>57.4</v>
       </c>
       <c r="K120" t="n">
-        <v>25.9</v>
+        <v>20.4</v>
       </c>
       <c r="L120" t="n">
-        <v>0.005</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>15.57359981536865</v>
+        <v>15.5887</v>
       </c>
       <c r="H121" t="n">
         <v>15.4142</v>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>126.9400024414062</v>
+        <v>127.06</v>
       </c>
       <c r="H122" t="n">
         <v>126.4026</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>114.1900024414062</v>
+        <v>114.31</v>
       </c>
       <c r="H123" t="n">
         <v>113.6715</v>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -8255,22 +8255,22 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>21.395</v>
+        <v>21.055</v>
       </c>
       <c r="H124" t="n">
-        <v>20.7823</v>
+        <v>20.867</v>
       </c>
       <c r="I124" t="n">
-        <v>20.0869</v>
+        <v>20.4311</v>
       </c>
       <c r="J124" t="n">
-        <v>66.8</v>
+        <v>57.2</v>
       </c>
       <c r="K124" t="n">
-        <v>37.7</v>
+        <v>15.5</v>
       </c>
       <c r="L124" t="n">
-        <v>0.0545</v>
+        <v>-0.0582</v>
       </c>
       <c r="M124" s="6" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -8318,22 +8318,22 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>48.945</v>
+        <v>48.57</v>
       </c>
       <c r="H125" t="n">
-        <v>49.0605</v>
+        <v>48.7716</v>
       </c>
       <c r="I125" t="n">
-        <v>49.1263</v>
+        <v>49.0925</v>
       </c>
       <c r="J125" t="n">
-        <v>43.5</v>
+        <v>36.5</v>
       </c>
       <c r="K125" t="n">
-        <v>16</v>
+        <v>21.9</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.0171</v>
+        <v>-0.03</v>
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -8381,22 +8381,22 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>63.51</v>
+        <v>63.72</v>
       </c>
       <c r="H126" t="n">
-        <v>63.1363</v>
+        <v>63.4465</v>
       </c>
       <c r="I126" t="n">
-        <v>63.0891</v>
+        <v>63.1626</v>
       </c>
       <c r="J126" t="n">
-        <v>63.2</v>
+        <v>65.2</v>
       </c>
       <c r="K126" t="n">
-        <v>16.3</v>
+        <v>19.6</v>
       </c>
       <c r="L126" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0245</v>
       </c>
       <c r="M126" s="6" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -8444,22 +8444,22 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>239.55</v>
+        <v>239.1</v>
       </c>
       <c r="H127" t="n">
-        <v>232.8586</v>
+        <v>236.7473</v>
       </c>
       <c r="I127" t="n">
-        <v>228.667</v>
+        <v>231.978</v>
       </c>
       <c r="J127" t="n">
-        <v>70.2</v>
+        <v>61.3</v>
       </c>
       <c r="K127" t="n">
-        <v>20.8</v>
+        <v>22.3</v>
       </c>
       <c r="L127" t="n">
-        <v>0.9525</v>
+        <v>-0.3987</v>
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -8507,22 +8507,22 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>346.55</v>
+        <v>339.75</v>
       </c>
       <c r="H128" t="n">
-        <v>345.0414</v>
+        <v>342.2054</v>
       </c>
       <c r="I128" t="n">
-        <v>337.229</v>
+        <v>340.398</v>
       </c>
       <c r="J128" t="n">
-        <v>55.8</v>
+        <v>44.5</v>
       </c>
       <c r="K128" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="L128" t="n">
-        <v>-0.3235</v>
+        <v>-1.2755</v>
       </c>
       <c r="M128" s="6" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8570,22 +8570,22 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>40.375</v>
+        <v>42.64</v>
       </c>
       <c r="H129" t="n">
-        <v>39.7014</v>
+        <v>41.1921</v>
       </c>
       <c r="I129" t="n">
-        <v>39.678</v>
+        <v>39.6822</v>
       </c>
       <c r="J129" t="n">
-        <v>57.3</v>
+        <v>68.2</v>
       </c>
       <c r="K129" t="n">
-        <v>17</v>
+        <v>23.5</v>
       </c>
       <c r="L129" t="n">
-        <v>0.0711</v>
+        <v>0.1846</v>
       </c>
       <c r="M129" s="6" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8633,22 +8633,22 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>10.398</v>
+        <v>10.328</v>
       </c>
       <c r="H130" t="n">
-        <v>10.4181</v>
+        <v>10.3664</v>
       </c>
       <c r="I130" t="n">
-        <v>10.4064</v>
+        <v>10.4256</v>
       </c>
       <c r="J130" t="n">
-        <v>47.1</v>
+        <v>43.4</v>
       </c>
       <c r="K130" t="n">
-        <v>11.9</v>
+        <v>13.9</v>
       </c>
       <c r="L130" t="n">
-        <v>-0.0091</v>
+        <v>-0.0097</v>
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -8696,22 +8696,22 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>65.62</v>
+        <v>65.56</v>
       </c>
       <c r="H131" t="n">
-        <v>65.5107</v>
+        <v>65.49760000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>65.7932</v>
+        <v>65.7046</v>
       </c>
       <c r="J131" t="n">
-        <v>51.7</v>
+        <v>51.1</v>
       </c>
       <c r="K131" t="n">
-        <v>13.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L131" t="n">
-        <v>0.0558</v>
+        <v>0.0121</v>
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -8759,22 +8759,22 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>155.59</v>
+        <v>155.29</v>
       </c>
       <c r="H132" t="n">
-        <v>155.228</v>
+        <v>155.2878</v>
       </c>
       <c r="I132" t="n">
-        <v>155.7866</v>
+        <v>155.6728</v>
       </c>
       <c r="J132" t="n">
-        <v>52.6</v>
+        <v>49.8</v>
       </c>
       <c r="K132" t="n">
-        <v>13.6</v>
+        <v>7.5</v>
       </c>
       <c r="L132" t="n">
-        <v>0.1336</v>
+        <v>0.0143</v>
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -8822,22 +8822,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>7.307</v>
+        <v>7.256</v>
       </c>
       <c r="H133" t="n">
-        <v>7.1079</v>
+        <v>7.2307</v>
       </c>
       <c r="I133" t="n">
-        <v>7.0547</v>
+        <v>7.1128</v>
       </c>
       <c r="J133" t="n">
-        <v>68.7</v>
+        <v>56</v>
       </c>
       <c r="K133" t="n">
-        <v>18.7</v>
+        <v>22.6</v>
       </c>
       <c r="L133" t="n">
-        <v>0.0341</v>
+        <v>-0.0046</v>
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -8885,22 +8885,22 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>146.825</v>
+        <v>145.52</v>
       </c>
       <c r="H134" t="n">
-        <v>147.9238</v>
+        <v>146.4767</v>
       </c>
       <c r="I134" t="n">
-        <v>148.3302</v>
+        <v>148.1424</v>
       </c>
       <c r="J134" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="K134" t="n">
-        <v>21.2</v>
+        <v>24.8</v>
       </c>
       <c r="L134" t="n">
-        <v>-0.1901</v>
+        <v>-0.1306</v>
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -8948,22 +8948,22 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>182.93</v>
+        <v>180.99</v>
       </c>
       <c r="H135" t="n">
-        <v>178.2035</v>
+        <v>180.7586</v>
       </c>
       <c r="I135" t="n">
-        <v>176.9662</v>
+        <v>178.2616</v>
       </c>
       <c r="J135" t="n">
-        <v>66</v>
+        <v>53.5</v>
       </c>
       <c r="K135" t="n">
-        <v>18.7</v>
+        <v>17.5</v>
       </c>
       <c r="L135" t="n">
-        <v>0.7974</v>
+        <v>-0.305</v>
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -9011,22 +9011,22 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>70.23</v>
+        <v>69.28</v>
       </c>
       <c r="H136" t="n">
-        <v>70.43689999999999</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>70.64879999999999</v>
+        <v>70.5784</v>
       </c>
       <c r="J136" t="n">
-        <v>44.6</v>
+        <v>34.8</v>
       </c>
       <c r="K136" t="n">
-        <v>19</v>
+        <v>21.1</v>
       </c>
       <c r="L136" t="n">
-        <v>-0.0524</v>
+        <v>-0.0701</v>
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -9074,22 +9074,22 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>134.09</v>
+        <v>131.77</v>
       </c>
       <c r="H137" t="n">
-        <v>131.4851</v>
+        <v>132.2912</v>
       </c>
       <c r="I137" t="n">
-        <v>130.3973</v>
+        <v>131.4068</v>
       </c>
       <c r="J137" t="n">
-        <v>63.1</v>
+        <v>48.1</v>
       </c>
       <c r="K137" t="n">
-        <v>17.7</v>
+        <v>15.4</v>
       </c>
       <c r="L137" t="n">
-        <v>0.368</v>
+        <v>-0.3579</v>
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -9137,22 +9137,22 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>73.09999999999999</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>73.10209999999999</v>
+        <v>72.9405</v>
       </c>
       <c r="I138" t="n">
-        <v>73.5724</v>
+        <v>73.3556</v>
       </c>
       <c r="J138" t="n">
-        <v>47.1</v>
+        <v>50.2</v>
       </c>
       <c r="K138" t="n">
-        <v>37</v>
+        <v>17.6</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0502</v>
+        <v>0.0319</v>
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -9200,22 +9200,22 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18.5705</v>
+        <v>18.3495</v>
       </c>
       <c r="H139" t="n">
-        <v>18.716</v>
+        <v>18.4931</v>
       </c>
       <c r="I139" t="n">
-        <v>18.844</v>
+        <v>18.7702</v>
       </c>
       <c r="J139" t="n">
-        <v>36.2</v>
+        <v>33.9</v>
       </c>
       <c r="K139" t="n">
-        <v>24.5</v>
+        <v>30.1</v>
       </c>
       <c r="L139" t="n">
-        <v>-0.0166</v>
+        <v>-0.0136</v>
       </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -9263,22 +9263,22 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>46.355</v>
+        <v>46.24</v>
       </c>
       <c r="H140" t="n">
-        <v>46.338</v>
+        <v>46.2369</v>
       </c>
       <c r="I140" t="n">
-        <v>46.4779</v>
+        <v>46.4091</v>
       </c>
       <c r="J140" t="n">
-        <v>49.6</v>
+        <v>48.7</v>
       </c>
       <c r="K140" t="n">
-        <v>14.2</v>
+        <v>10.6</v>
       </c>
       <c r="L140" t="n">
-        <v>0.0204</v>
+        <v>0.0058</v>
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9326,22 +9326,22 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>81.20999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="H141" t="n">
-        <v>81.85980000000001</v>
+        <v>81.1093</v>
       </c>
       <c r="I141" t="n">
-        <v>82.1906</v>
+        <v>82.045</v>
       </c>
       <c r="J141" t="n">
-        <v>38.5</v>
+        <v>28.4</v>
       </c>
       <c r="K141" t="n">
-        <v>15.1</v>
+        <v>23.2</v>
       </c>
       <c r="L141" t="n">
-        <v>-0.0849</v>
+        <v>-0.1103</v>
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -9389,22 +9389,22 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>45.075</v>
+        <v>44.61</v>
       </c>
       <c r="H142" t="n">
-        <v>45.1295</v>
+        <v>44.8314</v>
       </c>
       <c r="I142" t="n">
-        <v>45.1998</v>
+        <v>45.1559</v>
       </c>
       <c r="J142" t="n">
-        <v>46.1</v>
+        <v>35.3</v>
       </c>
       <c r="K142" t="n">
-        <v>9.699999999999999</v>
+        <v>23.3</v>
       </c>
       <c r="L142" t="n">
-        <v>-0.0076</v>
+        <v>-0.0369</v>
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -9452,22 +9452,22 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>8.752000000000001</v>
+        <v>8.637</v>
       </c>
       <c r="H143" t="n">
-        <v>8.802099999999999</v>
+        <v>8.702999999999999</v>
       </c>
       <c r="I143" t="n">
-        <v>8.8375</v>
+        <v>8.815200000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>37.6</v>
+        <v>29.1</v>
       </c>
       <c r="K143" t="n">
-        <v>21.2</v>
+        <v>31.6</v>
       </c>
       <c r="L143" t="n">
-        <v>-0.0094</v>
+        <v>-0.0069</v>
       </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -9515,22 +9515,22 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>90.92</v>
+        <v>92.14</v>
       </c>
       <c r="H144" t="n">
-        <v>87.92230000000001</v>
+        <v>90.7465</v>
       </c>
       <c r="I144" t="n">
-        <v>87.6178</v>
+        <v>88.6584</v>
       </c>
       <c r="J144" t="n">
-        <v>67.8</v>
+        <v>64.3</v>
       </c>
       <c r="K144" t="n">
-        <v>18.5</v>
+        <v>27.2</v>
       </c>
       <c r="L144" t="n">
-        <v>0.4746</v>
+        <v>0.0523</v>
       </c>
       <c r="M144" s="6" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -9578,22 +9578,22 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>121.8447</v>
+        <v>123.84</v>
       </c>
       <c r="H145" t="n">
-        <v>119.7795</v>
+        <v>122.8038</v>
       </c>
       <c r="I145" t="n">
-        <v>119.3476</v>
+        <v>120.9202</v>
       </c>
       <c r="J145" t="n">
-        <v>61.1</v>
+        <v>58.4</v>
       </c>
       <c r="K145" t="n">
-        <v>70.3</v>
+        <v>21.2</v>
       </c>
       <c r="L145" t="n">
-        <v>0.3643</v>
+        <v>-0.0885</v>
       </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -9641,22 +9641,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>119.96</v>
+        <v>118.54</v>
       </c>
       <c r="H146" t="n">
-        <v>115.4247</v>
+        <v>118.15</v>
       </c>
       <c r="I146" t="n">
-        <v>117.4304</v>
+        <v>117.4704</v>
       </c>
       <c r="J146" t="n">
-        <v>62</v>
+        <v>52.7</v>
       </c>
       <c r="K146" t="n">
-        <v>15.8</v>
+        <v>23.4</v>
       </c>
       <c r="L146" t="n">
-        <v>0.8577</v>
+        <v>-0.0343</v>
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -9704,22 +9704,22 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>24.515</v>
+        <v>23.37</v>
       </c>
       <c r="H147" t="n">
-        <v>23.9027</v>
+        <v>23.7845</v>
       </c>
       <c r="I147" t="n">
-        <v>23.1964</v>
+        <v>23.3131</v>
       </c>
       <c r="J147" t="n">
-        <v>63.3</v>
+        <v>43.1</v>
       </c>
       <c r="K147" t="n">
-        <v>24.9</v>
+        <v>13.6</v>
       </c>
       <c r="L147" t="n">
-        <v>0.0455</v>
+        <v>-0.1252</v>
       </c>
       <c r="M147" s="6" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -9767,22 +9767,22 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>106.65</v>
+        <v>101.39</v>
       </c>
       <c r="H148" t="n">
-        <v>103.7917</v>
+        <v>103.2691</v>
       </c>
       <c r="I148" t="n">
-        <v>100.7482</v>
+        <v>101.2376</v>
       </c>
       <c r="J148" t="n">
-        <v>64</v>
+        <v>42.7</v>
       </c>
       <c r="K148" t="n">
-        <v>26.6</v>
+        <v>13.7</v>
       </c>
       <c r="L148" t="n">
-        <v>0.2297</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -9830,31 +9830,31 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>62.0927</v>
+        <v>62.01</v>
       </c>
       <c r="H149" t="n">
-        <v>60.0748</v>
+        <v>61.6128</v>
       </c>
       <c r="I149" t="n">
-        <v>59.5163</v>
+        <v>60.2569</v>
       </c>
       <c r="J149" t="n">
-        <v>66.8</v>
+        <v>57.9</v>
       </c>
       <c r="K149" t="n">
-        <v>66</v>
+        <v>21.8</v>
       </c>
       <c r="L149" t="n">
-        <v>0.3884</v>
-      </c>
-      <c r="M149" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>-0.1012</v>
+      </c>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9893,22 +9893,22 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>6.46</v>
+        <v>6.35</v>
       </c>
       <c r="H150" t="n">
-        <v>6.3142</v>
+        <v>6.3693</v>
       </c>
       <c r="I150" t="n">
-        <v>6.2553</v>
+        <v>6.3153</v>
       </c>
       <c r="J150" t="n">
-        <v>64.40000000000001</v>
+        <v>49.3</v>
       </c>
       <c r="K150" t="n">
-        <v>19.3</v>
+        <v>16.2</v>
       </c>
       <c r="L150" t="n">
-        <v>0.0195</v>
+        <v>-0.0175</v>
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -9956,22 +9956,22 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>139.6</v>
+        <v>139.95</v>
       </c>
       <c r="H151" t="n">
-        <v>135.8552</v>
+        <v>138.7875</v>
       </c>
       <c r="I151" t="n">
-        <v>135.4806</v>
+        <v>136.6764</v>
       </c>
       <c r="J151" t="n">
-        <v>65.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="K151" t="n">
-        <v>18.2</v>
+        <v>21.9</v>
       </c>
       <c r="L151" t="n">
-        <v>0.7088</v>
+        <v>-0.073</v>
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10019,22 +10019,22 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>5.087</v>
+        <v>5.003</v>
       </c>
       <c r="H152" t="n">
-        <v>4.9736</v>
+        <v>5.0109</v>
       </c>
       <c r="I152" t="n">
-        <v>4.9278</v>
+        <v>4.9724</v>
       </c>
       <c r="J152" t="n">
-        <v>66.8</v>
+        <v>50.3</v>
       </c>
       <c r="K152" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="L152" t="n">
-        <v>0.0156</v>
+        <v>-0.0128</v>
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -10082,22 +10082,22 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>25.925</v>
+        <v>25.44</v>
       </c>
       <c r="H153" t="n">
-        <v>25.6647</v>
+        <v>25.4959</v>
       </c>
       <c r="I153" t="n">
-        <v>25.37</v>
+        <v>25.6037</v>
       </c>
       <c r="J153" t="n">
-        <v>57.8</v>
+        <v>47.9</v>
       </c>
       <c r="K153" t="n">
-        <v>15</v>
+        <v>12.2</v>
       </c>
       <c r="L153" t="n">
-        <v>0.0442</v>
+        <v>-0.056</v>
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -10145,22 +10145,22 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>97.66</v>
+        <v>97.89</v>
       </c>
       <c r="H154" t="n">
-        <v>96.71639999999999</v>
+        <v>96.9426</v>
       </c>
       <c r="I154" t="n">
-        <v>93.3018</v>
+        <v>95.6142</v>
       </c>
       <c r="J154" t="n">
-        <v>66.3</v>
+        <v>60.2</v>
       </c>
       <c r="K154" t="n">
-        <v>39.7</v>
+        <v>23.6</v>
       </c>
       <c r="L154" t="n">
-        <v>-0.1782</v>
+        <v>-0.1823</v>
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -10208,22 +10208,22 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>821.05</v>
+        <v>797.52</v>
       </c>
       <c r="H155" t="n">
-        <v>811.6249</v>
+        <v>806.1774</v>
       </c>
       <c r="I155" t="n">
-        <v>801.0093000000001</v>
+        <v>808.871</v>
       </c>
       <c r="J155" t="n">
-        <v>59.1</v>
+        <v>39.9</v>
       </c>
       <c r="K155" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="L155" t="n">
-        <v>1.4727</v>
+        <v>-2.4818</v>
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -10271,22 +10271,22 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>211.4</v>
+        <v>204.14</v>
       </c>
       <c r="H156" t="n">
-        <v>208.4477</v>
+        <v>205.919</v>
       </c>
       <c r="I156" t="n">
-        <v>207.7756</v>
+        <v>207.7344</v>
       </c>
       <c r="J156" t="n">
-        <v>57.8</v>
+        <v>44.5</v>
       </c>
       <c r="K156" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="L156" t="n">
-        <v>0.5581</v>
+        <v>-0.5198</v>
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -10334,22 +10334,22 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>670.4</v>
+        <v>661.5</v>
       </c>
       <c r="H157" t="n">
-        <v>653.944</v>
+        <v>662.1251999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>664.062</v>
+        <v>662.2380000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>57.8</v>
+        <v>50</v>
       </c>
       <c r="K157" t="n">
-        <v>16.8</v>
+        <v>11.9</v>
       </c>
       <c r="L157" t="n">
-        <v>4.1964</v>
+        <v>-0.7567</v>
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>UST.PA</t>
+          <t>LU1954152853.SG</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Stoccarda</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10397,22 +10397,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>104.65</v>
+        <v>102.32</v>
       </c>
       <c r="H158" t="n">
-        <v>102.728</v>
+        <v>103.1764</v>
       </c>
       <c r="I158" t="n">
-        <v>104.2004</v>
+        <v>103.9582</v>
       </c>
       <c r="J158" t="n">
-        <v>56.3</v>
+        <v>46.2</v>
       </c>
       <c r="K158" t="n">
-        <v>16.1</v>
+        <v>14.2</v>
       </c>
       <c r="L158" t="n">
-        <v>0.4914</v>
+        <v>-0.2296</v>
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -10460,22 +10460,22 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>18.232</v>
+        <v>19.59</v>
       </c>
       <c r="H159" t="n">
-        <v>18.8264</v>
+        <v>19.5653</v>
       </c>
       <c r="I159" t="n">
-        <v>19.1424</v>
+        <v>19.2808</v>
       </c>
       <c r="J159" t="n">
-        <v>46.1</v>
+        <v>50.7</v>
       </c>
       <c r="K159" t="n">
-        <v>17.9</v>
+        <v>10.9</v>
       </c>
       <c r="L159" t="n">
-        <v>0.0068</v>
+        <v>0.017</v>
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -10523,22 +10523,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>104.65</v>
+        <v>102.32</v>
       </c>
       <c r="H160" t="n">
-        <v>102.728</v>
+        <v>103.1764</v>
       </c>
       <c r="I160" t="n">
-        <v>104.2004</v>
+        <v>103.9582</v>
       </c>
       <c r="J160" t="n">
-        <v>56.3</v>
+        <v>46.2</v>
       </c>
       <c r="K160" t="n">
-        <v>16.1</v>
+        <v>13.3</v>
       </c>
       <c r="L160" t="n">
-        <v>0.4914</v>
+        <v>-0.2297</v>
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -10586,22 +10586,22 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>294.75</v>
+        <v>288.05</v>
       </c>
       <c r="H161" t="n">
-        <v>289.2745</v>
+        <v>290.5233</v>
       </c>
       <c r="I161" t="n">
-        <v>293.365</v>
+        <v>292.681</v>
       </c>
       <c r="J161" t="n">
-        <v>56.4</v>
+        <v>46.1</v>
       </c>
       <c r="K161" t="n">
-        <v>16</v>
+        <v>13.3</v>
       </c>
       <c r="L161" t="n">
-        <v>1.3869</v>
+        <v>-0.6541</v>
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -10649,22 +10649,22 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>27.48</v>
+        <v>26.78</v>
       </c>
       <c r="H162" t="n">
-        <v>27.1513</v>
+        <v>26.8695</v>
       </c>
       <c r="I162" t="n">
-        <v>26.9439</v>
+        <v>27.0025</v>
       </c>
       <c r="J162" t="n">
-        <v>56.6</v>
+        <v>47.8</v>
       </c>
       <c r="K162" t="n">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="L162" t="n">
-        <v>0.0404</v>
+        <v>-0.0608</v>
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -10712,22 +10712,22 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>16.492</v>
+        <v>16.258</v>
       </c>
       <c r="H163" t="n">
-        <v>16.1104</v>
+        <v>16.17</v>
       </c>
       <c r="I163" t="n">
-        <v>15.895</v>
+        <v>16.0311</v>
       </c>
       <c r="J163" t="n">
-        <v>63</v>
+        <v>53.6</v>
       </c>
       <c r="K163" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="L163" t="n">
-        <v>0.0426</v>
+        <v>-0.026</v>
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -10775,22 +10775,22 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>144.13</v>
+        <v>138.59</v>
       </c>
       <c r="H164" t="n">
-        <v>139.2756</v>
+        <v>141.082</v>
       </c>
       <c r="I164" t="n">
-        <v>139.6008</v>
+        <v>140.0755</v>
       </c>
       <c r="J164" t="n">
-        <v>61.1</v>
+        <v>44.1</v>
       </c>
       <c r="K164" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="L164" t="n">
-        <v>1.0825</v>
+        <v>-0.8464</v>
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -10838,31 +10838,31 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>74.17</v>
+        <v>74.22</v>
       </c>
       <c r="H165" t="n">
-        <v>72.2187</v>
+        <v>72.78879999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>70.5458</v>
+        <v>71.5626</v>
       </c>
       <c r="J165" t="n">
-        <v>59.1</v>
+        <v>57.3</v>
       </c>
       <c r="K165" t="n">
-        <v>15.1</v>
+        <v>9.1</v>
       </c>
       <c r="L165" t="n">
-        <v>0.1728</v>
-      </c>
-      <c r="M165" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="M165" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10901,22 +10901,22 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1207.88</v>
+        <v>1159.79</v>
       </c>
       <c r="H166" t="n">
-        <v>1162.4464</v>
+        <v>1176.6192</v>
       </c>
       <c r="I166" t="n">
-        <v>1166.7876</v>
+        <v>1169.7488</v>
       </c>
       <c r="J166" t="n">
-        <v>62.2</v>
+        <v>45.2</v>
       </c>
       <c r="K166" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
       <c r="L166" t="n">
-        <v>7.9916</v>
+        <v>-5.5112</v>
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10964,22 +10964,22 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>21.15</v>
+        <v>20.765</v>
       </c>
       <c r="H167" t="n">
-        <v>20.3796</v>
+        <v>20.8054</v>
       </c>
       <c r="I167" t="n">
-        <v>20.1461</v>
+        <v>20.359</v>
       </c>
       <c r="J167" t="n">
-        <v>65</v>
+        <v>51.2</v>
       </c>
       <c r="K167" t="n">
-        <v>16.4</v>
+        <v>14.9</v>
       </c>
       <c r="L167" t="n">
-        <v>0.1401</v>
+        <v>-0.0813</v>
       </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -11027,22 +11027,22 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>6.432</v>
+        <v>6.235</v>
       </c>
       <c r="H168" t="n">
-        <v>6.088</v>
+        <v>6.3032</v>
       </c>
       <c r="I168" t="n">
-        <v>5.8128</v>
+        <v>6.014</v>
       </c>
       <c r="J168" t="n">
-        <v>75.59999999999999</v>
+        <v>49.1</v>
       </c>
       <c r="K168" t="n">
-        <v>33</v>
+        <v>27.3</v>
       </c>
       <c r="L168" t="n">
-        <v>0.0537</v>
+        <v>-0.0535</v>
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11090,22 +11090,22 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>403.35</v>
+        <v>429.87</v>
       </c>
       <c r="H169" t="n">
-        <v>383.0426</v>
+        <v>406.8066</v>
       </c>
       <c r="I169" t="n">
-        <v>385.7359</v>
+        <v>388.6464</v>
       </c>
       <c r="J169" t="n">
-        <v>64.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K169" t="n">
-        <v>21.1</v>
+        <v>24.9</v>
       </c>
       <c r="L169" t="n">
-        <v>3.5414</v>
+        <v>3.1507</v>
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -11153,22 +11153,22 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>50.03</v>
+        <v>53.08</v>
       </c>
       <c r="H170" t="n">
-        <v>47.3933</v>
+        <v>50.8147</v>
       </c>
       <c r="I170" t="n">
-        <v>49.4402</v>
+        <v>48.738</v>
       </c>
       <c r="J170" t="n">
-        <v>57.9</v>
+        <v>60.3</v>
       </c>
       <c r="K170" t="n">
-        <v>23.5</v>
+        <v>19</v>
       </c>
       <c r="L170" t="n">
-        <v>0.6611</v>
+        <v>0.447</v>
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -11216,22 +11216,22 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>168.38</v>
+        <v>166.62</v>
       </c>
       <c r="H171" t="n">
-        <v>165.3476</v>
+        <v>166.649</v>
       </c>
       <c r="I171" t="n">
-        <v>164.4144</v>
+        <v>165.6316</v>
       </c>
       <c r="J171" t="n">
-        <v>63.7</v>
+        <v>51.2</v>
       </c>
       <c r="K171" t="n">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="L171" t="n">
-        <v>0.4569</v>
+        <v>-0.3157</v>
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -11282,19 +11282,19 @@
         <v>20.035</v>
       </c>
       <c r="H172" t="n">
-        <v>20.0343</v>
+        <v>19.9075</v>
       </c>
       <c r="I172" t="n">
-        <v>20.035</v>
+        <v>19.8858</v>
       </c>
       <c r="J172" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K172" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="L172" t="n">
-        <v>-0.0011</v>
+        <v>0.0151</v>
       </c>
       <c r="M172" s="6" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -11342,22 +11342,22 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>30.63</v>
+        <v>29.87</v>
       </c>
       <c r="H173" t="n">
-        <v>30.6011</v>
+        <v>30.1297</v>
       </c>
       <c r="I173" t="n">
-        <v>30.3139</v>
+        <v>30.3453</v>
       </c>
       <c r="J173" t="n">
-        <v>51.6</v>
+        <v>40.9</v>
       </c>
       <c r="K173" t="n">
-        <v>10.5</v>
+        <v>14.9</v>
       </c>
       <c r="L173" t="n">
-        <v>-0.0123</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -11405,22 +11405,22 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>10.508</v>
+        <v>10.174</v>
       </c>
       <c r="H174" t="n">
-        <v>10.5635</v>
+        <v>10.3672</v>
       </c>
       <c r="I174" t="n">
-        <v>11.3581</v>
+        <v>10.8574</v>
       </c>
       <c r="J174" t="n">
-        <v>45.6</v>
+        <v>41.2</v>
       </c>
       <c r="K174" t="n">
-        <v>22.8</v>
+        <v>17.3</v>
       </c>
       <c r="L174" t="n">
-        <v>0.0828</v>
+        <v>0.0052</v>
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -11468,22 +11468,22 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>204.65</v>
+        <v>201.5</v>
       </c>
       <c r="H175" t="n">
-        <v>199.5038</v>
+        <v>202.6386</v>
       </c>
       <c r="I175" t="n">
-        <v>204.1168</v>
+        <v>203.2194</v>
       </c>
       <c r="J175" t="n">
-        <v>57.1</v>
+        <v>48.4</v>
       </c>
       <c r="K175" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="L175" t="n">
-        <v>1.5861</v>
+        <v>-0.4961</v>
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -11531,22 +11531,22 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>274.4</v>
+        <v>276.55</v>
       </c>
       <c r="H176" t="n">
-        <v>269.3971</v>
+        <v>274.4375</v>
       </c>
       <c r="I176" t="n">
-        <v>265.371</v>
+        <v>268.991</v>
       </c>
       <c r="J176" t="n">
-        <v>65.09999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="K176" t="n">
-        <v>30.4</v>
+        <v>24.1</v>
       </c>
       <c r="L176" t="n">
-        <v>0.2207</v>
+        <v>-0.2931</v>
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -11594,22 +11594,22 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>33.745</v>
+        <v>33.365</v>
       </c>
       <c r="H177" t="n">
-        <v>34.3954</v>
+        <v>33.6944</v>
       </c>
       <c r="I177" t="n">
-        <v>34.2967</v>
+        <v>34.1113</v>
       </c>
       <c r="J177" t="n">
-        <v>39.4</v>
+        <v>42.6</v>
       </c>
       <c r="K177" t="n">
-        <v>24.4</v>
+        <v>21.6</v>
       </c>
       <c r="L177" t="n">
-        <v>-0.1842</v>
+        <v>-0.0254</v>
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -11657,22 +11657,22 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>159.28</v>
+        <v>158.57</v>
       </c>
       <c r="H178" t="n">
-        <v>159.0817</v>
+        <v>158.8516</v>
       </c>
       <c r="I178" t="n">
-        <v>159.2952</v>
+        <v>159.2154</v>
       </c>
       <c r="J178" t="n">
-        <v>53.4</v>
+        <v>42</v>
       </c>
       <c r="K178" t="n">
-        <v>17</v>
+        <v>12.3</v>
       </c>
       <c r="L178" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.0314</v>
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -11720,22 +11720,22 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>69.59999999999999</v>
+        <v>69.98</v>
       </c>
       <c r="H179" t="n">
-        <v>68.73909999999999</v>
+        <v>69.6974</v>
       </c>
       <c r="I179" t="n">
-        <v>68.89579999999999</v>
+        <v>69.1978</v>
       </c>
       <c r="J179" t="n">
-        <v>58.6</v>
+        <v>54.2</v>
       </c>
       <c r="K179" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="L179" t="n">
-        <v>0.1461</v>
+        <v>-0.0433</v>
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -11783,22 +11783,22 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>10.662</v>
+        <v>10.738</v>
       </c>
       <c r="H180" t="n">
-        <v>10.4218</v>
+        <v>10.6282</v>
       </c>
       <c r="I180" t="n">
-        <v>10.3862</v>
+        <v>10.4842</v>
       </c>
       <c r="J180" t="n">
-        <v>63.6</v>
+        <v>60</v>
       </c>
       <c r="K180" t="n">
-        <v>15.4</v>
+        <v>20.1</v>
       </c>
       <c r="L180" t="n">
-        <v>0.0413</v>
+        <v>0.0002</v>
       </c>
       <c r="M180" s="6" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -11846,22 +11846,22 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>81.45999999999999</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="H181" t="n">
-        <v>80.6095</v>
+        <v>81.166</v>
       </c>
       <c r="I181" t="n">
-        <v>79.2946</v>
+        <v>80.2811</v>
       </c>
       <c r="J181" t="n">
-        <v>65.7</v>
+        <v>59.2</v>
       </c>
       <c r="K181" t="n">
-        <v>34.2</v>
+        <v>28.4</v>
       </c>
       <c r="L181" t="n">
-        <v>-0.0161</v>
+        <v>-0.116</v>
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -11909,22 +11909,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>232.2</v>
+        <v>235.1</v>
       </c>
       <c r="H182" t="n">
-        <v>230.6968</v>
+        <v>230.8368</v>
       </c>
       <c r="I182" t="n">
-        <v>228.225</v>
+        <v>230.291</v>
       </c>
       <c r="J182" t="n">
-        <v>53.2</v>
+        <v>58.6</v>
       </c>
       <c r="K182" t="n">
-        <v>12.8</v>
+        <v>11</v>
       </c>
       <c r="L182" t="n">
-        <v>-0.4565</v>
+        <v>0.4221</v>
       </c>
       <c r="M182" s="6" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -11972,22 +11972,22 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>115.72</v>
+        <v>116.29</v>
       </c>
       <c r="H183" t="n">
-        <v>114.8233</v>
+        <v>116.2881</v>
       </c>
       <c r="I183" t="n">
-        <v>117.2496</v>
+        <v>117.1444</v>
       </c>
       <c r="J183" t="n">
-        <v>51.4</v>
+        <v>50.2</v>
       </c>
       <c r="K183" t="n">
-        <v>11.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L183" t="n">
-        <v>0.4801</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -12035,22 +12035,22 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>90.70999999999999</v>
+        <v>90.86</v>
       </c>
       <c r="H184" t="n">
-        <v>88.6782</v>
+        <v>90.018</v>
       </c>
       <c r="I184" t="n">
-        <v>87.55840000000001</v>
+        <v>88.56059999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>66.8</v>
+        <v>61.4</v>
       </c>
       <c r="K184" t="n">
-        <v>20.2</v>
+        <v>29.9</v>
       </c>
       <c r="L184" t="n">
-        <v>0.2705</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="M184" s="6" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -12098,31 +12098,31 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>78</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H185" t="n">
-        <v>76.1555</v>
+        <v>77.6563</v>
       </c>
       <c r="I185" t="n">
-        <v>74.83580000000001</v>
+        <v>75.8283</v>
       </c>
       <c r="J185" t="n">
-        <v>70.8</v>
+        <v>71.7</v>
       </c>
       <c r="K185" t="n">
-        <v>21.2</v>
+        <v>25.7</v>
       </c>
       <c r="L185" t="n">
-        <v>0.1622</v>
-      </c>
-      <c r="M185" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0007</v>
+      </c>
+      <c r="M185" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -12161,31 +12161,31 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>18.214</v>
+        <v>18.112</v>
       </c>
       <c r="H186" t="n">
-        <v>18.3086</v>
+        <v>17.914</v>
       </c>
       <c r="I186" t="n">
-        <v>17.9452</v>
+        <v>18.0046</v>
       </c>
       <c r="J186" t="n">
-        <v>48.8</v>
+        <v>54.7</v>
       </c>
       <c r="K186" t="n">
-        <v>15.9</v>
+        <v>18.8</v>
       </c>
       <c r="L186" t="n">
-        <v>-0.0236</v>
-      </c>
-      <c r="M186" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0105</v>
+      </c>
+      <c r="M186" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -12224,22 +12224,22 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>39.185</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="H187" t="n">
-        <v>38.6718</v>
+        <v>81.166</v>
       </c>
       <c r="I187" t="n">
-        <v>39.1903</v>
+        <v>80.2811</v>
       </c>
       <c r="J187" t="n">
-        <v>55.8</v>
+        <v>59.2</v>
       </c>
       <c r="K187" t="n">
-        <v>14.5</v>
+        <v>28.4</v>
       </c>
       <c r="L187" t="n">
-        <v>0.1303</v>
+        <v>-0.116</v>
       </c>
       <c r="M187" s="6" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -12287,22 +12287,22 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>53.5</v>
+        <v>53.33</v>
       </c>
       <c r="H188" t="n">
-        <v>52.3789</v>
+        <v>52.9963</v>
       </c>
       <c r="I188" t="n">
-        <v>51.5283</v>
+        <v>52.2306</v>
       </c>
       <c r="J188" t="n">
-        <v>69</v>
+        <v>59.6</v>
       </c>
       <c r="K188" t="n">
-        <v>18.7</v>
+        <v>20.4</v>
       </c>
       <c r="L188" t="n">
-        <v>0.0944</v>
+        <v>-0.0795</v>
       </c>
       <c r="M188" s="6" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -12350,22 +12350,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>8.523</v>
+        <v>8.536</v>
       </c>
       <c r="H189" t="n">
-        <v>8.3405</v>
+        <v>8.434900000000001</v>
       </c>
       <c r="I189" t="n">
-        <v>8.1976</v>
+        <v>8.310600000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>72.7</v>
+        <v>66</v>
       </c>
       <c r="K189" t="n">
-        <v>23.8</v>
+        <v>19.3</v>
       </c>
       <c r="L189" t="n">
-        <v>0.0181</v>
+        <v>-0.0073</v>
       </c>
       <c r="M189" s="6" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -12413,22 +12413,22 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>17.144</v>
+        <v>17.046</v>
       </c>
       <c r="H190" t="n">
-        <v>16.9837</v>
+        <v>17.0183</v>
       </c>
       <c r="I190" t="n">
-        <v>16.9662</v>
+        <v>16.8752</v>
       </c>
       <c r="J190" t="n">
-        <v>56.6</v>
+        <v>51.5</v>
       </c>
       <c r="K190" t="n">
-        <v>12.2</v>
+        <v>10.1</v>
       </c>
       <c r="L190" t="n">
-        <v>0.0436</v>
+        <v>-0.0242</v>
       </c>
       <c r="M190" s="6" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -12476,22 +12476,22 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>49.215</v>
+        <v>49.09</v>
       </c>
       <c r="H191" t="n">
-        <v>48.5409</v>
+        <v>48.7019</v>
       </c>
       <c r="I191" t="n">
-        <v>47.8353</v>
+        <v>48.0109</v>
       </c>
       <c r="J191" t="n">
-        <v>56.8</v>
+        <v>54.8</v>
       </c>
       <c r="K191" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="L191" t="n">
-        <v>0.1514</v>
+        <v>-0.1083</v>
       </c>
       <c r="M191" s="6" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -12539,22 +12539,22 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>3.8075</v>
+        <v>3.706</v>
       </c>
       <c r="H192" t="n">
-        <v>3.7527</v>
+        <v>3.7548</v>
       </c>
       <c r="I192" t="n">
-        <v>3.8284</v>
+        <v>3.7456</v>
       </c>
       <c r="J192" t="n">
-        <v>56.6</v>
+        <v>43.6</v>
       </c>
       <c r="K192" t="n">
-        <v>19.1</v>
+        <v>13.9</v>
       </c>
       <c r="L192" t="n">
-        <v>0.0173</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="M192" s="6" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -12602,22 +12602,22 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>11.006</v>
+        <v>11.348</v>
       </c>
       <c r="H193" t="n">
-        <v>10.8659</v>
+        <v>11.0654</v>
       </c>
       <c r="I193" t="n">
-        <v>10.6606</v>
+        <v>10.8206</v>
       </c>
       <c r="J193" t="n">
-        <v>57.4</v>
+        <v>64.3</v>
       </c>
       <c r="K193" t="n">
-        <v>18.1</v>
+        <v>24.6</v>
       </c>
       <c r="L193" t="n">
-        <v>0.0231</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M193" s="6" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -12665,22 +12665,22 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>9.978999999999999</v>
+        <v>10.628</v>
       </c>
       <c r="H194" t="n">
-        <v>9.2523</v>
+        <v>9.868</v>
       </c>
       <c r="I194" t="n">
-        <v>9.2415</v>
+        <v>9.330399999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>67</v>
+        <v>69.2</v>
       </c>
       <c r="K194" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L194" t="n">
-        <v>0.1325</v>
+        <v>0.0781</v>
       </c>
       <c r="M194" s="6" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -12728,22 +12728,22 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>27.675</v>
+        <v>27.73</v>
       </c>
       <c r="H195" t="n">
-        <v>27.464</v>
+        <v>27.7547</v>
       </c>
       <c r="I195" t="n">
-        <v>29.7602</v>
+        <v>28.5974</v>
       </c>
       <c r="J195" t="n">
         <v>48.3</v>
       </c>
       <c r="K195" t="n">
-        <v>29.8</v>
+        <v>17.5</v>
       </c>
       <c r="L195" t="n">
-        <v>0.3127</v>
+        <v>0.0927</v>
       </c>
       <c r="M195" s="6" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -12791,22 +12791,22 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>4.9125</v>
+        <v>4.7945</v>
       </c>
       <c r="H196" t="n">
-        <v>4.9115</v>
+        <v>4.8363</v>
       </c>
       <c r="I196" t="n">
-        <v>4.8651</v>
+        <v>4.8706</v>
       </c>
       <c r="J196" t="n">
-        <v>51.1</v>
+        <v>40.6</v>
       </c>
       <c r="K196" t="n">
-        <v>9.9</v>
+        <v>20.2</v>
       </c>
       <c r="L196" t="n">
-        <v>-0.0022</v>
+        <v>-0.0098</v>
       </c>
       <c r="M196" s="6" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -12854,22 +12854,22 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>90.70999999999999</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="H197" t="n">
-        <v>88.44159999999999</v>
+        <v>86.7959</v>
       </c>
       <c r="I197" t="n">
-        <v>87.1504</v>
+        <v>86.1023</v>
       </c>
       <c r="J197" t="n">
-        <v>69.09999999999999</v>
+        <v>46.5</v>
       </c>
       <c r="K197" t="n">
-        <v>18.7</v>
+        <v>20.5</v>
       </c>
       <c r="L197" t="n">
-        <v>0.3278</v>
+        <v>-0.2995</v>
       </c>
       <c r="M197" s="6" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>149.8600006103516</v>
+        <v>149.99</v>
       </c>
       <c r="H198" t="n">
         <v>149.1741</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -12980,22 +12980,22 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>141.26</v>
+        <v>141.22</v>
       </c>
       <c r="H199" t="n">
-        <v>141.0994</v>
+        <v>141.1467</v>
       </c>
       <c r="I199" t="n">
-        <v>141.0348</v>
+        <v>141.1232</v>
       </c>
       <c r="J199" t="n">
-        <v>58.9</v>
+        <v>55.6</v>
       </c>
       <c r="K199" t="n">
-        <v>14</v>
+        <v>8.9</v>
       </c>
       <c r="L199" t="n">
-        <v>0.0352</v>
+        <v>-0.0051</v>
       </c>
       <c r="M199" s="6" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -13043,22 +13043,22 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>159.38</v>
+        <v>157.84</v>
       </c>
       <c r="H200" t="n">
-        <v>155.1749</v>
+        <v>157.4205</v>
       </c>
       <c r="I200" t="n">
-        <v>154.0671</v>
+        <v>155.2155</v>
       </c>
       <c r="J200" t="n">
-        <v>66.09999999999999</v>
+        <v>54.7</v>
       </c>
       <c r="K200" t="n">
-        <v>32.7</v>
+        <v>17.4</v>
       </c>
       <c r="L200" t="n">
-        <v>0.6955</v>
+        <v>-0.2498</v>
       </c>
       <c r="M200" s="6" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -13106,22 +13106,22 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>121.115</v>
+        <v>120.26</v>
       </c>
       <c r="H201" t="n">
-        <v>118.1311</v>
+        <v>119.7951</v>
       </c>
       <c r="I201" t="n">
-        <v>117.1431</v>
+        <v>118.1813</v>
       </c>
       <c r="J201" t="n">
-        <v>67.7</v>
+        <v>56.3</v>
       </c>
       <c r="K201" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
       </c>
       <c r="L201" t="n">
-        <v>0.4444</v>
+        <v>-0.1798</v>
       </c>
       <c r="M201" s="6" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -13169,22 +13169,22 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>362.17</v>
+        <v>382.46</v>
       </c>
       <c r="H202" t="n">
-        <v>346.2595</v>
+        <v>364.4348</v>
       </c>
       <c r="I202" t="n">
-        <v>348.548</v>
+        <v>351.0454</v>
       </c>
       <c r="J202" t="n">
-        <v>64.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K202" t="n">
-        <v>22.5</v>
+        <v>24.9</v>
       </c>
       <c r="L202" t="n">
-        <v>2.6085</v>
+        <v>2.4331</v>
       </c>
       <c r="M202" s="6" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -13232,22 +13232,22 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>6.489</v>
+        <v>7.914</v>
       </c>
       <c r="H203" t="n">
-        <v>6.4064</v>
+        <v>6.8428</v>
       </c>
       <c r="I203" t="n">
-        <v>6.3477</v>
+        <v>6.4381</v>
       </c>
       <c r="J203" t="n">
-        <v>53</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K203" t="n">
-        <v>11.9</v>
+        <v>24.9</v>
       </c>
       <c r="L203" t="n">
-        <v>0.013</v>
+        <v>0.1732</v>
       </c>
       <c r="M203" s="6" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -13295,22 +13295,22 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>28.265</v>
+        <v>29.335</v>
       </c>
       <c r="H204" t="n">
-        <v>28.1744</v>
+        <v>28.9936</v>
       </c>
       <c r="I204" t="n">
-        <v>27.8333</v>
+        <v>28.092</v>
       </c>
       <c r="J204" t="n">
-        <v>51.8</v>
+        <v>58.1</v>
       </c>
       <c r="K204" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="L204" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.0587</v>
       </c>
       <c r="M204" s="6" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -13358,22 +13358,22 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>126.48</v>
+        <v>121.46</v>
       </c>
       <c r="H205" t="n">
-        <v>121.7699</v>
+        <v>123.2747</v>
       </c>
       <c r="I205" t="n">
-        <v>122.2152</v>
+        <v>122.5208</v>
       </c>
       <c r="J205" t="n">
-        <v>62.4</v>
+        <v>45</v>
       </c>
       <c r="K205" t="n">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="L205" t="n">
-        <v>0.8355</v>
+        <v>-0.5746</v>
       </c>
       <c r="M205" s="6" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -13421,22 +13421,22 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>40.37</v>
+        <v>38.32</v>
       </c>
       <c r="H206" t="n">
-        <v>38.6369</v>
+        <v>39.459</v>
       </c>
       <c r="I206" t="n">
-        <v>37.4924</v>
+        <v>38.5713</v>
       </c>
       <c r="J206" t="n">
-        <v>61.6</v>
+        <v>43.8</v>
       </c>
       <c r="K206" t="n">
-        <v>22.6</v>
+        <v>17.2</v>
       </c>
       <c r="L206" t="n">
-        <v>0.1772</v>
+        <v>-0.3895</v>
       </c>
       <c r="M206" s="6" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -13484,22 +13484,22 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>9.631</v>
+        <v>9.391</v>
       </c>
       <c r="H207" t="n">
-        <v>9.340299999999999</v>
+        <v>9.485300000000001</v>
       </c>
       <c r="I207" t="n">
-        <v>9.5932</v>
+        <v>9.5662</v>
       </c>
       <c r="J207" t="n">
-        <v>56.4</v>
+        <v>47.5</v>
       </c>
       <c r="K207" t="n">
-        <v>16.2</v>
+        <v>13.3</v>
       </c>
       <c r="L207" t="n">
-        <v>0.08</v>
+        <v>-0.0297</v>
       </c>
       <c r="M207" s="6" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -13547,22 +13547,22 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>9.093999999999999</v>
+        <v>8.733000000000001</v>
       </c>
       <c r="H208" t="n">
-        <v>9.214600000000001</v>
+        <v>8.955299999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>9.893000000000001</v>
+        <v>9.4588</v>
       </c>
       <c r="J208" t="n">
-        <v>43.6</v>
+        <v>39</v>
       </c>
       <c r="K208" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="L208" t="n">
-        <v>0.0561</v>
+        <v>-0.0028</v>
       </c>
       <c r="M208" s="6" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -13610,22 +13610,22 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>84.39</v>
+        <v>89.9375</v>
       </c>
       <c r="H209" t="n">
-        <v>80.1062</v>
+        <v>85.10980000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>80.6541</v>
+        <v>81.2801</v>
       </c>
       <c r="J209" t="n">
-        <v>64.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K209" t="n">
-        <v>21.2</v>
+        <v>33.4</v>
       </c>
       <c r="L209" t="n">
-        <v>0.743</v>
+        <v>0.6645</v>
       </c>
       <c r="M209" s="6" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -13673,22 +13673,22 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>137.68</v>
+        <v>144.32</v>
       </c>
       <c r="H210" t="n">
-        <v>132.2221</v>
+        <v>138.635</v>
       </c>
       <c r="I210" t="n">
-        <v>133.301</v>
+        <v>132.9602</v>
       </c>
       <c r="J210" t="n">
-        <v>60.1</v>
+        <v>60.7</v>
       </c>
       <c r="K210" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="L210" t="n">
-        <v>1.4248</v>
+        <v>1.0221</v>
       </c>
       <c r="M210" s="6" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -13736,22 +13736,22 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>46.345</v>
+        <v>61.09</v>
       </c>
       <c r="H211" t="n">
-        <v>46.089</v>
+        <v>49.6676</v>
       </c>
       <c r="I211" t="n">
-        <v>45.8387</v>
+        <v>46.5277</v>
       </c>
       <c r="J211" t="n">
-        <v>51.1</v>
+        <v>86.2</v>
       </c>
       <c r="K211" t="n">
-        <v>9.1</v>
+        <v>24.4</v>
       </c>
       <c r="L211" t="n">
-        <v>0.0397</v>
+        <v>1.6972</v>
       </c>
       <c r="M211" s="6" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -13799,22 +13799,22 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>47.03</v>
+        <v>61.08</v>
       </c>
       <c r="H212" t="n">
-        <v>46.0067</v>
+        <v>53.3593</v>
       </c>
       <c r="I212" t="n">
-        <v>43.5215</v>
+        <v>48.9137</v>
       </c>
       <c r="J212" t="n">
-        <v>56.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K212" t="n">
-        <v>14.1</v>
+        <v>23.9</v>
       </c>
       <c r="L212" t="n">
-        <v>-0.0987</v>
+        <v>1.2513</v>
       </c>
       <c r="M212" s="6" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -13862,28 +13862,28 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>6.795</v>
+        <v>9.262</v>
       </c>
       <c r="H213" t="n">
-        <v>6.9911</v>
+        <v>7.4382</v>
       </c>
       <c r="J213" t="n">
-        <v>35.9</v>
+        <v>86</v>
       </c>
       <c r="K213" t="n">
-        <v>29.9</v>
+        <v>28.9</v>
       </c>
       <c r="L213" t="n">
-        <v>0.0237</v>
-      </c>
-      <c r="M213" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.2533</v>
+      </c>
+      <c r="M213" s="4" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -13922,22 +13922,22 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>49.704</v>
+        <v>59.97</v>
       </c>
       <c r="H214" t="n">
-        <v>49.4223</v>
+        <v>52.2255</v>
       </c>
       <c r="I214" t="n">
-        <v>49.0134</v>
+        <v>49.6351</v>
       </c>
       <c r="J214" t="n">
-        <v>51.1</v>
+        <v>80.3</v>
       </c>
       <c r="K214" t="n">
-        <v>14</v>
+        <v>25.9</v>
       </c>
       <c r="L214" t="n">
-        <v>0.0128</v>
+        <v>1.2579</v>
       </c>
       <c r="M214" s="6" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -13985,22 +13985,22 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>75.4952</v>
+        <v>98.69499999999999</v>
       </c>
       <c r="H215" t="n">
-        <v>75.3428</v>
+        <v>81.40170000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>74.6849</v>
+        <v>75.8429</v>
       </c>
       <c r="J215" t="n">
-        <v>50</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K215" t="n">
-        <v>27.8</v>
+        <v>13.9</v>
       </c>
       <c r="L215" t="n">
-        <v>-0.0064</v>
+        <v>2.6527</v>
       </c>
       <c r="M215" s="6" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -14048,22 +14048,22 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>36.08</v>
+        <v>29.25</v>
       </c>
       <c r="H216" t="n">
-        <v>29.6931</v>
+        <v>31.9151</v>
       </c>
       <c r="I216" t="n">
-        <v>30.0027</v>
+        <v>29.9639</v>
       </c>
       <c r="J216" t="n">
-        <v>64.90000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="K216" t="n">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="L216" t="n">
-        <v>1.0168</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="M216" s="6" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -14111,22 +14111,22 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.2334</v>
+        <v>29.25</v>
       </c>
       <c r="H217" t="n">
-        <v>0.3117</v>
+        <v>31.9151</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3352</v>
+        <v>29.9639</v>
       </c>
       <c r="J217" t="n">
-        <v>32.7</v>
+        <v>43.2</v>
       </c>
       <c r="K217" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="L217" t="n">
-        <v>-0.0107</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="M217" s="6" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -14174,22 +14174,22 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.9905</v>
+        <v>29.25</v>
       </c>
       <c r="H218" t="n">
-        <v>1.1993</v>
+        <v>31.9151</v>
       </c>
       <c r="I218" t="n">
-        <v>1.8097</v>
+        <v>29.9639</v>
       </c>
       <c r="J218" t="n">
-        <v>36.9</v>
+        <v>43.2</v>
       </c>
       <c r="K218" t="n">
-        <v>27.8</v>
+        <v>17.2</v>
       </c>
       <c r="L218" t="n">
-        <v>0.0122</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="M218" s="6" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -14237,22 +14237,22 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>24.5525</v>
+        <v>29.25</v>
       </c>
       <c r="H219" t="n">
-        <v>17.5473</v>
+        <v>31.9151</v>
       </c>
       <c r="I219" t="n">
-        <v>14.3816</v>
+        <v>29.9639</v>
       </c>
       <c r="J219" t="n">
-        <v>77.8</v>
+        <v>43.2</v>
       </c>
       <c r="K219" t="n">
-        <v>30.8</v>
+        <v>17.2</v>
       </c>
       <c r="L219" t="n">
-        <v>1.2888</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="M219" s="6" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -14300,22 +14300,22 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>45.155</v>
+        <v>29.25</v>
       </c>
       <c r="H220" t="n">
-        <v>47.9756</v>
+        <v>31.9151</v>
       </c>
       <c r="I220" t="n">
-        <v>46.0371</v>
+        <v>29.9639</v>
       </c>
       <c r="J220" t="n">
-        <v>46</v>
+        <v>43.2</v>
       </c>
       <c r="K220" t="n">
-        <v>25.6</v>
+        <v>17.2</v>
       </c>
       <c r="L220" t="n">
-        <v>-1.6245</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="M220" s="6" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -14363,22 +14363,22 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>362.53</v>
+        <v>29.25</v>
       </c>
       <c r="H221" t="n">
-        <v>450.6588</v>
+        <v>31.9151</v>
       </c>
       <c r="I221" t="n">
-        <v>552.1660000000001</v>
+        <v>29.9639</v>
       </c>
       <c r="J221" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="K221" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="L221" t="n">
-        <v>-7.9562</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="M221" s="6" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -14426,22 +14426,22 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>24.92</v>
+        <v>29.25</v>
       </c>
       <c r="H222" t="n">
-        <v>26.3708</v>
+        <v>31.9151</v>
       </c>
       <c r="I222" t="n">
-        <v>28.0544</v>
+        <v>29.9639</v>
       </c>
       <c r="J222" t="n">
-        <v>46.2</v>
+        <v>43.2</v>
       </c>
       <c r="K222" t="n">
-        <v>19.5</v>
+        <v>17.2</v>
       </c>
       <c r="L222" t="n">
-        <v>-0.4212</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="M222" s="6" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -14489,22 +14489,22 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>24.92</v>
+        <v>29.25</v>
       </c>
       <c r="H223" t="n">
-        <v>26.3687</v>
+        <v>31.9151</v>
       </c>
       <c r="I223" t="n">
-        <v>28.0544</v>
+        <v>29.9639</v>
       </c>
       <c r="J223" t="n">
-        <v>46.2</v>
+        <v>43.2</v>
       </c>
       <c r="K223" t="n">
-        <v>18.6</v>
+        <v>17.2</v>
       </c>
       <c r="L223" t="n">
-        <v>-0.4252</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="M223" s="6" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -14552,22 +14552,22 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>255.8</v>
+        <v>251.4</v>
       </c>
       <c r="H224" t="n">
-        <v>251.9604</v>
+        <v>251.6582</v>
       </c>
       <c r="I224" t="n">
-        <v>252.01</v>
+        <v>252.5145</v>
       </c>
       <c r="J224" t="n">
-        <v>58.9</v>
+        <v>49.3</v>
       </c>
       <c r="K224" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="L224" t="n">
-        <v>0.7578</v>
+        <v>-0.4621</v>
       </c>
       <c r="M224" s="6" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -14615,22 +14615,22 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>254.37</v>
+        <v>253.1</v>
       </c>
       <c r="H225" t="n">
-        <v>249.1886</v>
+        <v>252.027</v>
       </c>
       <c r="I225" t="n">
-        <v>246.2408</v>
+        <v>249.2362</v>
       </c>
       <c r="J225" t="n">
-        <v>80.3</v>
+        <v>60.4</v>
       </c>
       <c r="K225" t="n">
-        <v>26.7</v>
+        <v>31.6</v>
       </c>
       <c r="L225" t="n">
-        <v>0.4209</v>
+        <v>-0.3245</v>
       </c>
       <c r="M225" s="6" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -14678,22 +14678,22 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>125.9</v>
+        <v>124.82</v>
       </c>
       <c r="H226" t="n">
-        <v>125.712</v>
+        <v>125.3003</v>
       </c>
       <c r="I226" t="n">
-        <v>126.1992</v>
+        <v>125.9686</v>
       </c>
       <c r="J226" t="n">
-        <v>52.6</v>
+        <v>35.7</v>
       </c>
       <c r="K226" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="L226" t="n">
-        <v>0.1154</v>
+        <v>-0.0578</v>
       </c>
       <c r="M226" s="6" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -14741,22 +14741,22 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>109.7</v>
+        <v>109.82</v>
       </c>
       <c r="H227" t="n">
-        <v>109.5848</v>
+        <v>109.7151</v>
       </c>
       <c r="I227" t="n">
-        <v>109.4233</v>
+        <v>109.5512</v>
       </c>
       <c r="J227" t="n">
-        <v>84.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K227" t="n">
-        <v>65.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="L227" t="n">
-        <v>0.0009</v>
+        <v>0.0017</v>
       </c>
       <c r="M227" s="6" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -14804,22 +14804,22 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>10.574</v>
+        <v>10.542</v>
       </c>
       <c r="H228" t="n">
-        <v>10.3998</v>
+        <v>10.5326</v>
       </c>
       <c r="I228" t="n">
-        <v>10.2839</v>
+        <v>10.4129</v>
       </c>
       <c r="J228" t="n">
-        <v>63.1</v>
+        <v>53.4</v>
       </c>
       <c r="K228" t="n">
-        <v>20.2</v>
+        <v>18.3</v>
       </c>
       <c r="L228" t="n">
-        <v>0.0129</v>
+        <v>-0.0207</v>
       </c>
       <c r="M228" s="6" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -14867,22 +14867,22 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>9.922000000000001</v>
+        <v>9.891999999999999</v>
       </c>
       <c r="H229" t="n">
-        <v>9.93</v>
+        <v>9.9057</v>
       </c>
       <c r="I229" t="n">
-        <v>9.9413</v>
+        <v>9.9396</v>
       </c>
       <c r="J229" t="n">
-        <v>48</v>
+        <v>45.2</v>
       </c>
       <c r="K229" t="n">
-        <v>17.4</v>
+        <v>10.5</v>
       </c>
       <c r="L229" t="n">
-        <v>-0.0002</v>
+        <v>-0.0018</v>
       </c>
       <c r="M229" s="6" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -14930,22 +14930,22 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>5.985</v>
+        <v>5.843</v>
       </c>
       <c r="H230" t="n">
-        <v>5.9454</v>
+        <v>5.9884</v>
       </c>
       <c r="I230" t="n">
-        <v>6.3798</v>
+        <v>6.2367</v>
       </c>
       <c r="J230" t="n">
-        <v>49.3</v>
+        <v>45.2</v>
       </c>
       <c r="K230" t="n">
-        <v>18.4</v>
+        <v>11</v>
       </c>
       <c r="L230" t="n">
-        <v>0.0608</v>
+        <v>-0.0123</v>
       </c>
       <c r="M230" s="6" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -14993,22 +14993,22 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>217.1</v>
+        <v>217.05</v>
       </c>
       <c r="H231" t="n">
-        <v>211.0069</v>
+        <v>214.5442</v>
       </c>
       <c r="I231" t="n">
-        <v>207.2152</v>
+        <v>210.208</v>
       </c>
       <c r="J231" t="n">
-        <v>70.09999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="K231" t="n">
-        <v>20.1</v>
+        <v>21.3</v>
       </c>
       <c r="L231" t="n">
-        <v>0.877</v>
+        <v>-0.3727</v>
       </c>
       <c r="M231" s="6" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -15056,22 +15056,22 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>368.375</v>
+        <v>365</v>
       </c>
       <c r="H232" t="n">
-        <v>358.5662</v>
+        <v>363.7146</v>
       </c>
       <c r="I232" t="n">
-        <v>352.2025</v>
+        <v>358.057</v>
       </c>
       <c r="J232" t="n">
-        <v>68.7</v>
+        <v>56.3</v>
       </c>
       <c r="K232" t="n">
-        <v>12.6</v>
+        <v>13.9</v>
       </c>
       <c r="L232" t="n">
-        <v>1.2794</v>
+        <v>-0.8952</v>
       </c>
       <c r="M232" s="6" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -15119,22 +15119,22 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>6.746</v>
+        <v>6.548</v>
       </c>
       <c r="H233" t="n">
-        <v>6.565</v>
+        <v>6.6063</v>
       </c>
       <c r="I233" t="n">
-        <v>6.4008</v>
+        <v>6.5084</v>
       </c>
       <c r="J233" t="n">
-        <v>68.59999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="K233" t="n">
-        <v>24.5</v>
+        <v>19.6</v>
       </c>
       <c r="L233" t="n">
-        <v>0.0175</v>
+        <v>-0.0231</v>
       </c>
       <c r="M233" s="6" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -15182,22 +15182,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>143.2</v>
+        <v>143.15</v>
       </c>
       <c r="H234" t="n">
-        <v>142.74</v>
+        <v>142.9255</v>
       </c>
       <c r="I234" t="n">
-        <v>142.8028</v>
+        <v>142.8804</v>
       </c>
       <c r="J234" t="n">
-        <v>57.7</v>
+        <v>54.6</v>
       </c>
       <c r="K234" t="n">
-        <v>12.1</v>
+        <v>6.8</v>
       </c>
       <c r="L234" t="n">
-        <v>0.0742</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="M234" s="6" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -15245,22 +15245,22 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.6694</v>
+        <v>0.6407</v>
       </c>
       <c r="H235" t="n">
-        <v>0.6852</v>
+        <v>0.6646</v>
       </c>
       <c r="I235" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.6843</v>
       </c>
       <c r="J235" t="n">
-        <v>39.2</v>
+        <v>30.3</v>
       </c>
       <c r="K235" t="n">
-        <v>12</v>
+        <v>23.5</v>
       </c>
       <c r="L235" t="n">
-        <v>-0.0014</v>
+        <v>-0.0018</v>
       </c>
       <c r="M235" s="6" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -15308,22 +15308,22 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>723.21</v>
+        <v>710.8099999999999</v>
       </c>
       <c r="H236" t="n">
-        <v>709.0929</v>
+        <v>713.5093000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>703.2754</v>
+        <v>708.7354</v>
       </c>
       <c r="J236" t="n">
-        <v>63.1</v>
+        <v>48.2</v>
       </c>
       <c r="K236" t="n">
-        <v>17.4</v>
+        <v>14.1</v>
       </c>
       <c r="L236" t="n">
-        <v>1.9988</v>
+        <v>-1.8907</v>
       </c>
       <c r="M236" s="6" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -15371,22 +15371,22 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>6.416</v>
+        <v>6.327</v>
       </c>
       <c r="H237" t="n">
-        <v>6.2822</v>
+        <v>6.3382</v>
       </c>
       <c r="I237" t="n">
-        <v>6.2203</v>
+        <v>6.2794</v>
       </c>
       <c r="J237" t="n">
-        <v>66.3</v>
+        <v>50.3</v>
       </c>
       <c r="K237" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="L237" t="n">
-        <v>0.0171</v>
+        <v>-0.016</v>
       </c>
       <c r="M237" s="6" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>2026-08-09 21:35</t>
+          <t>2026-08-25 12:55</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -9641,22 +9641,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>118.54</v>
+        <v>118.36</v>
       </c>
       <c r="H146" t="n">
-        <v>118.15</v>
+        <v>118.17</v>
       </c>
       <c r="I146" t="n">
-        <v>117.4704</v>
+        <v>117.3876</v>
       </c>
       <c r="J146" t="n">
-        <v>52.7</v>
+        <v>52.1</v>
       </c>
       <c r="K146" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="L146" t="n">
-        <v>-0.0343</v>
+        <v>-0.1144</v>
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LU1954152853.SG</t>
+          <t>UST.PA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Stoccarda</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -14765,7 +14765,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>2026-08-25 12:55</t>
+          <t>2026-08-25 14:28</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -614,7 +614,7 @@
     <t>FMI.MI</t>
   </si>
   <si>
-    <t>Amundi IS MSCI EMU ESG Broad Transition UCITS ETF Dist</t>
+    <t>Amundi Italy MIB ESG UCITS ETF DR Acc</t>
   </si>
   <si>
     <t>LU0908501132</t>
@@ -1133,7 +1133,7 @@
     <t>EFRN.DE</t>
   </si>
   <si>
-    <t>Amundi IS EUR Float. Rate Corp. Bd ESG UCITS ETF</t>
+    <t>iShares EUR Floating Rate Bond Advanced UCITS ETF EUR (Dist)</t>
   </si>
   <si>
     <t>IE00BF5GB717</t>
@@ -1283,7 +1283,7 @@
     <t>IUSB.DE</t>
   </si>
   <si>
-    <t>iShares US Large Cap Deep Buffer UCITS ETF USD (Acc)</t>
+    <t>iShares Global Timber &amp; Forestry UCITS ETF USD (Dist)</t>
   </si>
   <si>
     <t>Volatilita / Strutturati</t>
@@ -1379,7 +1379,7 @@
     <t>IUSM.DE</t>
   </si>
   <si>
-    <t>iShares US Large Cap Max Buffer Sep UCITS ETF USD (Acc)</t>
+    <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
   </si>
   <si>
     <t>IE00B1FZS798</t>
@@ -1604,7 +1604,7 @@
     <t>UNIC.MI</t>
   </si>
   <si>
-    <t>Amundi MSCI Disruptive Technology UCITS ETF Acc</t>
+    <t>Amundi Global Memory Chips UCITS ETF Acc</t>
   </si>
   <si>
     <t>LU2023678282</t>
@@ -1835,10 +1835,10 @@
     <t>HLTH.DE</t>
   </si>
   <si>
-    <t>Amundi MSCI World Health Care UCITS ETF EUR (Acc)</t>
-  </si>
-  <si>
-    <t>IE00BWXC8680</t>
+    <t>SPDR MSCI Europe Health Care UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00BKWQ0H23</t>
   </si>
   <si>
     <t>IWMO.L</t>
@@ -1967,22 +1967,22 @@
     <t>IPRE.DE</t>
   </si>
   <si>
-    <t>iShares Listed Private Equity UCITS ETF USD (Dist)</t>
+    <t>iShares European Property Yield UCITS ETF EUR (Acc)</t>
   </si>
   <si>
     <t>Private Equity</t>
   </si>
   <si>
-    <t>IE00B1TXHL60</t>
+    <t>IE00BGDQ0L74</t>
   </si>
   <si>
     <t>DX2G.DE</t>
   </si>
   <si>
-    <t>Xtrackers LPX Private Equity Swap UCITS ETF 1C</t>
-  </si>
-  <si>
-    <t>IE00BYPMDN47</t>
+    <t>Xtrackers CAC 40 UCITS ETF 1D</t>
+  </si>
+  <si>
+    <t>LU0322250985</t>
   </si>
   <si>
     <t>XEON.DE</t>
@@ -2312,7 +2312,7 @@
     <t>EXS1.DE</t>
   </si>
   <si>
-    <t>Amundi DAX 50 ESG UCITS ETF - E</t>
+    <t>iShares Core DAX UCITS ETF (DE) EUR (Acc)</t>
   </si>
   <si>
     <t>Azionari Europa</t>
@@ -2321,16 +2321,16 @@
     <t>Singapur</t>
   </si>
   <si>
-    <t>LU2240851688</t>
+    <t>DE0005933931</t>
   </si>
   <si>
     <t>MSEU.L</t>
   </si>
   <si>
-    <t>Amundi Index MSCI EMU SRI PBA U</t>
-  </si>
-  <si>
-    <t>LU2109787635</t>
+    <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
+  </si>
+  <si>
+    <t>FR0012399806</t>
   </si>
   <si>
     <t>WATC.SW</t>
@@ -2891,148 +2891,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="26" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="0" fillId="6" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="11" fillId="7" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="12" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="13" fillId="8" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="14" fillId="9" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="15" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="17" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="26" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="26" fontId="20" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
         <v>81</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
         <v>84</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
         <v>96</v>
@@ -4568,7 +4568,7 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
         <v>105</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
         <v>112</v>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
         <v>128</v>
@@ -4944,7 +4944,7 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
         <v>131</v>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
         <v>148</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
         <v>163</v>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s">
         <v>191</v>
@@ -8422,7 +8422,7 @@
     </row>
     <row r="108" spans="1:15">
       <c r="A108" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B108" t="s">
         <v>367</v>
@@ -10349,7 +10349,7 @@
     </row>
     <row r="149" spans="1:15">
       <c r="A149" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B149" t="s">
         <v>494</v>
@@ -11101,7 +11101,7 @@
     </row>
     <row r="165" spans="1:15">
       <c r="A165" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B165" t="s">
         <v>541</v>
@@ -12041,7 +12041,7 @@
     </row>
     <row r="185" spans="1:15">
       <c r="A185" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B185" t="s">
         <v>610</v>
@@ -12088,7 +12088,7 @@
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B186" t="s">
         <v>613</v>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="784">
   <si>
     <t>Livello</t>
   </si>
@@ -1748,7 +1748,7 @@
     <t>IE00B1FZS350</t>
   </si>
   <si>
-    <t>INRG.SW</t>
+    <t>INRG.MI</t>
   </si>
   <si>
     <t>iShares Global Clean Energy UCITS ETF USD Dist</t>
@@ -2078,9 +2078,6 @@
     <t>IE000V0H6AD4</t>
   </si>
   <si>
-    <t>INRG.MI</t>
-  </si>
-  <si>
     <t>iShares Global Clean Energy Transition UCITS ETF</t>
   </si>
   <si>
@@ -2333,22 +2330,22 @@
     <t>FR0012399806</t>
   </si>
   <si>
-    <t>WATC.SW</t>
+    <t>WATC.PA</t>
   </si>
   <si>
     <t>Amundi MSCI Water UCITS ETF Acc</t>
   </si>
   <si>
+    <t>FR0014002CH1</t>
+  </si>
+  <si>
+    <t>CSBGU7.SW</t>
+  </si>
+  <si>
+    <t>iShares VII PLC - iShares VII PLC - iShares $ Trea</t>
+  </si>
+  <si>
     <t>Svizzera</t>
-  </si>
-  <si>
-    <t>FR0014002CH1</t>
-  </si>
-  <si>
-    <t>CSBGU7.SW</t>
-  </si>
-  <si>
-    <t>iShares VII PLC - iShares VII PLC - iShares $ Trea</t>
   </si>
   <si>
     <t>IE00B3VWN393</t>
@@ -3440,7 +3437,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -3816,7 +3813,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
         <v>52</v>
@@ -4803,7 +4800,7 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
         <v>122</v>
@@ -5132,7 +5129,7 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="s">
         <v>145</v>
@@ -5179,7 +5176,7 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B39" t="s">
         <v>148</v>
@@ -5414,7 +5411,7 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
         <v>163</v>
@@ -5837,7 +5834,7 @@
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
         <v>191</v>
@@ -5931,7 +5928,7 @@
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
         <v>197</v>
@@ -6307,7 +6304,7 @@
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" t="s">
         <v>222</v>
@@ -8422,7 +8419,7 @@
     </row>
     <row r="108" spans="1:15">
       <c r="A108" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B108" t="s">
         <v>367</v>
@@ -8704,7 +8701,7 @@
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B114" t="s">
         <v>385</v>
@@ -8751,7 +8748,7 @@
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B115" t="s">
         <v>388</v>
@@ -12088,7 +12085,7 @@
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B186" t="s">
         <v>613</v>
@@ -13125,10 +13122,10 @@
         <v>3</v>
       </c>
       <c r="B208" t="s">
+        <v>573</v>
+      </c>
+      <c r="C208" t="s">
         <v>683</v>
-      </c>
-      <c r="C208" t="s">
-        <v>684</v>
       </c>
       <c r="D208" t="s">
         <v>46</v>
@@ -13164,7 +13161,7 @@
         <v>21</v>
       </c>
       <c r="O208" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="209" spans="1:15">
@@ -13172,10 +13169,10 @@
         <v>3</v>
       </c>
       <c r="B209" t="s">
+        <v>685</v>
+      </c>
+      <c r="C209" t="s">
         <v>686</v>
-      </c>
-      <c r="C209" t="s">
-        <v>687</v>
       </c>
       <c r="D209" t="s">
         <v>555</v>
@@ -13211,7 +13208,7 @@
         <v>21</v>
       </c>
       <c r="O209" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="210" spans="1:15">
@@ -13219,13 +13216,13 @@
         <v>3</v>
       </c>
       <c r="B210" t="s">
+        <v>688</v>
+      </c>
+      <c r="C210" t="s">
         <v>689</v>
       </c>
-      <c r="C210" t="s">
+      <c r="D210" t="s">
         <v>690</v>
-      </c>
-      <c r="D210" t="s">
-        <v>691</v>
       </c>
       <c r="E210" t="s">
         <v>18</v>
@@ -13258,7 +13255,7 @@
         <v>21</v>
       </c>
       <c r="O210" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="211" spans="1:15">
@@ -13266,19 +13263,19 @@
         <v>3</v>
       </c>
       <c r="B211" t="s">
+        <v>692</v>
+      </c>
+      <c r="C211" t="s">
         <v>693</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211" t="s">
         <v>694</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>695</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>696</v>
-      </c>
-      <c r="F211" t="s">
-        <v>697</v>
       </c>
       <c r="G211">
         <v>61.09</v>
@@ -13305,7 +13302,7 @@
         <v>21</v>
       </c>
       <c r="O211" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="212" spans="1:15">
@@ -13313,19 +13310,19 @@
         <v>3</v>
       </c>
       <c r="B212" t="s">
+        <v>698</v>
+      </c>
+      <c r="C212" t="s">
         <v>699</v>
       </c>
-      <c r="C212" t="s">
-        <v>700</v>
-      </c>
       <c r="D212" t="s">
+        <v>694</v>
+      </c>
+      <c r="E212" t="s">
         <v>695</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>696</v>
-      </c>
-      <c r="F212" t="s">
-        <v>697</v>
       </c>
       <c r="G212">
         <v>61.08</v>
@@ -13352,7 +13349,7 @@
         <v>21</v>
       </c>
       <c r="O212" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="213" spans="1:15">
@@ -13360,19 +13357,19 @@
         <v>2</v>
       </c>
       <c r="B213" t="s">
+        <v>701</v>
+      </c>
+      <c r="C213" t="s">
         <v>702</v>
       </c>
-      <c r="C213" t="s">
-        <v>703</v>
-      </c>
       <c r="D213" t="s">
+        <v>694</v>
+      </c>
+      <c r="E213" t="s">
         <v>695</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>696</v>
-      </c>
-      <c r="F213" t="s">
-        <v>697</v>
       </c>
       <c r="G213">
         <v>9.262</v>
@@ -13396,7 +13393,7 @@
         <v>21</v>
       </c>
       <c r="O213" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="214" spans="1:15">
@@ -13404,16 +13401,16 @@
         <v>3</v>
       </c>
       <c r="B214" t="s">
+        <v>704</v>
+      </c>
+      <c r="C214" t="s">
         <v>705</v>
       </c>
-      <c r="C214" t="s">
+      <c r="D214" t="s">
+        <v>694</v>
+      </c>
+      <c r="E214" t="s">
         <v>706</v>
-      </c>
-      <c r="D214" t="s">
-        <v>695</v>
-      </c>
-      <c r="E214" t="s">
-        <v>707</v>
       </c>
       <c r="F214" t="s">
         <v>19</v>
@@ -13443,7 +13440,7 @@
         <v>21</v>
       </c>
       <c r="O214" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="215" spans="1:15">
@@ -13451,16 +13448,16 @@
         <v>3</v>
       </c>
       <c r="B215" t="s">
+        <v>708</v>
+      </c>
+      <c r="C215" t="s">
         <v>709</v>
       </c>
-      <c r="C215" t="s">
-        <v>710</v>
-      </c>
       <c r="D215" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E215" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F215" t="s">
         <v>557</v>
@@ -13490,7 +13487,7 @@
         <v>21</v>
       </c>
       <c r="O215" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="216" spans="1:15">
@@ -13498,13 +13495,13 @@
         <v>3</v>
       </c>
       <c r="B216" t="s">
+        <v>711</v>
+      </c>
+      <c r="C216" t="s">
         <v>712</v>
       </c>
-      <c r="C216" t="s">
+      <c r="D216" t="s">
         <v>713</v>
-      </c>
-      <c r="D216" t="s">
-        <v>714</v>
       </c>
       <c r="E216" t="s">
         <v>18</v>
@@ -13537,7 +13534,7 @@
         <v>21</v>
       </c>
       <c r="O216" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="217" spans="1:15">
@@ -13545,13 +13542,13 @@
         <v>3</v>
       </c>
       <c r="B217" t="s">
+        <v>715</v>
+      </c>
+      <c r="C217" t="s">
         <v>716</v>
       </c>
-      <c r="C217" t="s">
-        <v>717</v>
-      </c>
       <c r="D217" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E217" t="s">
         <v>18</v>
@@ -13584,7 +13581,7 @@
         <v>21</v>
       </c>
       <c r="O217" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="218" spans="1:15">
@@ -13592,13 +13589,13 @@
         <v>3</v>
       </c>
       <c r="B218" t="s">
+        <v>717</v>
+      </c>
+      <c r="C218" t="s">
         <v>718</v>
       </c>
-      <c r="C218" t="s">
-        <v>719</v>
-      </c>
       <c r="D218" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E218" t="s">
         <v>18</v>
@@ -13631,7 +13628,7 @@
         <v>21</v>
       </c>
       <c r="O218" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="219" spans="1:15">
@@ -13639,13 +13636,13 @@
         <v>3</v>
       </c>
       <c r="B219" t="s">
+        <v>719</v>
+      </c>
+      <c r="C219" t="s">
         <v>720</v>
       </c>
-      <c r="C219" t="s">
-        <v>721</v>
-      </c>
       <c r="D219" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E219" t="s">
         <v>556</v>
@@ -13678,7 +13675,7 @@
         <v>21</v>
       </c>
       <c r="O219" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="220" spans="1:15">
@@ -13686,13 +13683,13 @@
         <v>3</v>
       </c>
       <c r="B220" t="s">
+        <v>721</v>
+      </c>
+      <c r="C220" t="s">
         <v>722</v>
       </c>
-      <c r="C220" t="s">
-        <v>723</v>
-      </c>
       <c r="D220" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E220" t="s">
         <v>18</v>
@@ -13725,7 +13722,7 @@
         <v>21</v>
       </c>
       <c r="O220" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="221" spans="1:15">
@@ -13733,13 +13730,13 @@
         <v>3</v>
       </c>
       <c r="B221" t="s">
+        <v>723</v>
+      </c>
+      <c r="C221" t="s">
         <v>724</v>
       </c>
-      <c r="C221" t="s">
-        <v>725</v>
-      </c>
       <c r="D221" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E221" t="s">
         <v>18</v>
@@ -13772,7 +13769,7 @@
         <v>21</v>
       </c>
       <c r="O221" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="222" spans="1:15">
@@ -13780,13 +13777,13 @@
         <v>3</v>
       </c>
       <c r="B222" t="s">
+        <v>725</v>
+      </c>
+      <c r="C222" t="s">
         <v>726</v>
       </c>
-      <c r="C222" t="s">
-        <v>727</v>
-      </c>
       <c r="D222" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E222" t="s">
         <v>18</v>
@@ -13819,7 +13816,7 @@
         <v>21</v>
       </c>
       <c r="O222" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="223" spans="1:15">
@@ -13827,13 +13824,13 @@
         <v>3</v>
       </c>
       <c r="B223" t="s">
+        <v>727</v>
+      </c>
+      <c r="C223" t="s">
         <v>728</v>
       </c>
-      <c r="C223" t="s">
-        <v>729</v>
-      </c>
       <c r="D223" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E223" t="s">
         <v>18</v>
@@ -13866,7 +13863,7 @@
         <v>21</v>
       </c>
       <c r="O223" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="224" spans="1:15">
@@ -13874,16 +13871,16 @@
         <v>3</v>
       </c>
       <c r="B224" t="s">
+        <v>729</v>
+      </c>
+      <c r="C224" t="s">
         <v>730</v>
       </c>
-      <c r="C224" t="s">
+      <c r="D224" t="s">
         <v>731</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>732</v>
-      </c>
-      <c r="E224" t="s">
-        <v>733</v>
       </c>
       <c r="F224" t="s">
         <v>19</v>
@@ -13913,7 +13910,7 @@
         <v>21</v>
       </c>
       <c r="O224" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="225" spans="1:15">
@@ -13921,13 +13918,13 @@
         <v>3</v>
       </c>
       <c r="B225" t="s">
+        <v>734</v>
+      </c>
+      <c r="C225" t="s">
         <v>735</v>
       </c>
-      <c r="C225" t="s">
+      <c r="D225" t="s">
         <v>736</v>
-      </c>
-      <c r="D225" t="s">
-        <v>737</v>
       </c>
       <c r="E225" t="s">
         <v>18</v>
@@ -13960,7 +13957,7 @@
         <v>21</v>
       </c>
       <c r="O225" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="226" spans="1:15">
@@ -13968,13 +13965,13 @@
         <v>3</v>
       </c>
       <c r="B226" t="s">
+        <v>738</v>
+      </c>
+      <c r="C226" t="s">
         <v>739</v>
       </c>
-      <c r="C226" t="s">
+      <c r="D226" t="s">
         <v>740</v>
-      </c>
-      <c r="D226" t="s">
-        <v>741</v>
       </c>
       <c r="E226" t="s">
         <v>165</v>
@@ -14007,7 +14004,7 @@
         <v>21</v>
       </c>
       <c r="O226" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="227" spans="1:15">
@@ -14015,16 +14012,16 @@
         <v>3</v>
       </c>
       <c r="B227" t="s">
+        <v>742</v>
+      </c>
+      <c r="C227" t="s">
         <v>743</v>
       </c>
-      <c r="C227" t="s">
+      <c r="D227" t="s">
         <v>744</v>
       </c>
-      <c r="D227" t="s">
-        <v>745</v>
-      </c>
       <c r="E227" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F227" t="s">
         <v>19</v>
@@ -14054,7 +14051,7 @@
         <v>21</v>
       </c>
       <c r="O227" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="228" spans="1:15">
@@ -14062,13 +14059,13 @@
         <v>3</v>
       </c>
       <c r="B228" t="s">
+        <v>746</v>
+      </c>
+      <c r="C228" t="s">
         <v>747</v>
       </c>
-      <c r="C228" t="s">
+      <c r="D228" t="s">
         <v>748</v>
-      </c>
-      <c r="D228" t="s">
-        <v>749</v>
       </c>
       <c r="E228" t="s">
         <v>220</v>
@@ -14101,7 +14098,7 @@
         <v>21</v>
       </c>
       <c r="O228" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="229" spans="1:15">
@@ -14109,13 +14106,13 @@
         <v>3</v>
       </c>
       <c r="B229" t="s">
+        <v>750</v>
+      </c>
+      <c r="C229" t="s">
         <v>751</v>
       </c>
-      <c r="C229" t="s">
+      <c r="D229" t="s">
         <v>752</v>
-      </c>
-      <c r="D229" t="s">
-        <v>753</v>
       </c>
       <c r="E229" t="s">
         <v>165</v>
@@ -14148,7 +14145,7 @@
         <v>21</v>
       </c>
       <c r="O229" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="230" spans="1:15">
@@ -14156,16 +14153,16 @@
         <v>3</v>
       </c>
       <c r="B230" t="s">
+        <v>754</v>
+      </c>
+      <c r="C230" t="s">
         <v>755</v>
       </c>
-      <c r="C230" t="s">
+      <c r="D230" t="s">
         <v>756</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>757</v>
-      </c>
-      <c r="E230" t="s">
-        <v>758</v>
       </c>
       <c r="F230" t="s">
         <v>557</v>
@@ -14195,7 +14192,7 @@
         <v>21</v>
       </c>
       <c r="O230" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="231" spans="1:15">
@@ -14203,16 +14200,16 @@
         <v>3</v>
       </c>
       <c r="B231" t="s">
+        <v>759</v>
+      </c>
+      <c r="C231" t="s">
         <v>760</v>
       </c>
-      <c r="C231" t="s">
+      <c r="D231" t="s">
         <v>761</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
         <v>762</v>
-      </c>
-      <c r="E231" t="s">
-        <v>763</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -14242,7 +14239,7 @@
         <v>21</v>
       </c>
       <c r="O231" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="232" spans="1:15">
@@ -14250,16 +14247,16 @@
         <v>3</v>
       </c>
       <c r="B232" t="s">
+        <v>764</v>
+      </c>
+      <c r="C232" t="s">
         <v>765</v>
       </c>
-      <c r="C232" t="s">
-        <v>766</v>
-      </c>
       <c r="D232" t="s">
+        <v>761</v>
+      </c>
+      <c r="E232" t="s">
         <v>762</v>
-      </c>
-      <c r="E232" t="s">
-        <v>763</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -14289,7 +14286,7 @@
         <v>21</v>
       </c>
       <c r="O232" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="233" spans="1:15">
@@ -14297,16 +14294,16 @@
         <v>3</v>
       </c>
       <c r="B233" t="s">
+        <v>767</v>
+      </c>
+      <c r="C233" t="s">
         <v>768</v>
       </c>
-      <c r="C233" t="s">
-        <v>769</v>
-      </c>
       <c r="D233" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E233" t="s">
-        <v>770</v>
+        <v>165</v>
       </c>
       <c r="F233" t="s">
         <v>19</v>
@@ -14336,7 +14333,7 @@
         <v>21</v>
       </c>
       <c r="O233" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="234" spans="1:15">
@@ -14344,16 +14341,16 @@
         <v>3</v>
       </c>
       <c r="B234" t="s">
+        <v>770</v>
+      </c>
+      <c r="C234" t="s">
+        <v>771</v>
+      </c>
+      <c r="D234" t="s">
+        <v>740</v>
+      </c>
+      <c r="E234" t="s">
         <v>772</v>
-      </c>
-      <c r="C234" t="s">
-        <v>773</v>
-      </c>
-      <c r="D234" t="s">
-        <v>741</v>
-      </c>
-      <c r="E234" t="s">
-        <v>770</v>
       </c>
       <c r="F234" t="s">
         <v>557</v>
@@ -14383,7 +14380,7 @@
         <v>21</v>
       </c>
       <c r="O234" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="235" spans="1:15">
@@ -14391,13 +14388,13 @@
         <v>3</v>
       </c>
       <c r="B235" t="s">
+        <v>774</v>
+      </c>
+      <c r="C235" t="s">
         <v>775</v>
       </c>
-      <c r="C235" t="s">
+      <c r="D235" t="s">
         <v>776</v>
-      </c>
-      <c r="D235" t="s">
-        <v>777</v>
       </c>
       <c r="E235" t="s">
         <v>18</v>
@@ -14430,7 +14427,7 @@
         <v>21</v>
       </c>
       <c r="O235" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="236" spans="1:15">
@@ -14438,13 +14435,13 @@
         <v>3</v>
       </c>
       <c r="B236" t="s">
+        <v>778</v>
+      </c>
+      <c r="C236" t="s">
         <v>779</v>
       </c>
-      <c r="C236" t="s">
-        <v>780</v>
-      </c>
       <c r="D236" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E236" t="s">
         <v>18</v>
@@ -14477,7 +14474,7 @@
         <v>21</v>
       </c>
       <c r="O236" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="237" spans="1:15">
@@ -14485,13 +14482,13 @@
         <v>3</v>
       </c>
       <c r="B237" t="s">
+        <v>781</v>
+      </c>
+      <c r="C237" t="s">
         <v>782</v>
       </c>
-      <c r="C237" t="s">
-        <v>783</v>
-      </c>
       <c r="D237" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E237" t="s">
         <v>220</v>
@@ -14524,7 +14521,7 @@
         <v>21</v>
       </c>
       <c r="O237" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
   </sheetData>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="785">
   <si>
     <t>Livello</t>
   </si>
@@ -1748,336 +1748,342 @@
     <t>IE00B1FZS350</t>
   </si>
   <si>
+    <t>INRG.SW</t>
+  </si>
+  <si>
+    <t>iShares Global Clean Energy UCITS ETF USD Dist</t>
+  </si>
+  <si>
+    <t>Svizzera</t>
+  </si>
+  <si>
+    <t>IE00B1XNHC34</t>
+  </si>
+  <si>
+    <t>XAIX.DE</t>
+  </si>
+  <si>
+    <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+  </si>
+  <si>
+    <t>Settoriale - Tecnologia</t>
+  </si>
+  <si>
+    <t>IE00BGV5VN51</t>
+  </si>
+  <si>
+    <t>SXR2.DE</t>
+  </si>
+  <si>
+    <t>iShares MSCI Canada UCITS ETF USD Acc</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>IE00B52SF786</t>
+  </si>
+  <si>
+    <t>IQQI.DE</t>
+  </si>
+  <si>
+    <t>iShares Global Infrastructure UCITS ETF USD Dist</t>
+  </si>
+  <si>
+    <t>Infrastrutture</t>
+  </si>
+  <si>
+    <t>IE00B6QW5T61</t>
+  </si>
+  <si>
+    <t>IBGX.AS</t>
+  </si>
+  <si>
+    <t>iShares USD Treasury Bond 7-10yr UCITS ETF USD Dist</t>
+  </si>
+  <si>
+    <t>Obbligazionari - Governativi USD</t>
+  </si>
+  <si>
+    <t>IE00B1FZS681</t>
+  </si>
+  <si>
+    <t>IS3S.DE</t>
+  </si>
+  <si>
+    <t>iShares MSCI Europe Small Cap UCITS ETF EUR Acc</t>
+  </si>
+  <si>
+    <t>IE00B3VWMM18</t>
+  </si>
+  <si>
+    <t>WSML.L</t>
+  </si>
+  <si>
+    <t>iShares MSCI World Small Cap UCITS ETF USD (Acc)</t>
+  </si>
+  <si>
+    <t>IE00BDVWFV31</t>
+  </si>
+  <si>
+    <t>VHYL.MI</t>
+  </si>
+  <si>
+    <t>Vanguard FTSE All-World High Div Yield UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00B8GKDB10</t>
+  </si>
+  <si>
+    <t>HLTH.DE</t>
+  </si>
+  <si>
+    <t>SPDR MSCI Europe Health Care UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00BKWQ0H23</t>
+  </si>
+  <si>
+    <t>IWMO.L</t>
+  </si>
+  <si>
+    <t>iShares Edge MSCI World Momentum Factor UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00B0M63912</t>
+  </si>
+  <si>
+    <t>IWQU.L</t>
+  </si>
+  <si>
+    <t>iShares Edge MSCI World Quality Factor UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00B0M63961</t>
+  </si>
+  <si>
+    <t>MVOL.L</t>
+  </si>
+  <si>
+    <t>iShares Edge MSCI World Minimum Volatility UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00B0M63507</t>
+  </si>
+  <si>
+    <t>LTAM.MI</t>
+  </si>
+  <si>
+    <t>iShares MSCI EM Latin America UCITS ETF USD (Dist)</t>
+  </si>
+  <si>
+    <t>IE00B27YCK28</t>
+  </si>
+  <si>
+    <t>EMV.MI</t>
+  </si>
+  <si>
+    <t>iShares Edge MSCI EM Min Vol Factor UCITS ETF USD (Acc)</t>
+  </si>
+  <si>
+    <t>IE00B8KGV557</t>
+  </si>
+  <si>
+    <t>IS3T.DE</t>
+  </si>
+  <si>
+    <t>iShares MSCI World Mid-Cap Equal Weight UCITS ETF EUR</t>
+  </si>
+  <si>
+    <t>Azionario Mid Cap</t>
+  </si>
+  <si>
+    <t>IE00BP3QZD73</t>
+  </si>
+  <si>
+    <t>EMID.L</t>
+  </si>
+  <si>
+    <t>iShares MSCI Europe Mid Cap UCITS ETF EUR (Dist)</t>
+  </si>
+  <si>
+    <t>IE00BFXR5895</t>
+  </si>
+  <si>
+    <t>AIGI.MI</t>
+  </si>
+  <si>
+    <t>WisdomTree Industrial Metals ETC (Al+Cu+Zn+Ni+Pb)</t>
+  </si>
+  <si>
+    <t>Metalli Industriali</t>
+  </si>
+  <si>
+    <t>GB00B15KYG56</t>
+  </si>
+  <si>
+    <t>COPA.MI</t>
+  </si>
+  <si>
+    <t>WisdomTree Copper ETC</t>
+  </si>
+  <si>
+    <t>GB00B15KXQ89</t>
+  </si>
+  <si>
+    <t>ALUM.MI</t>
+  </si>
+  <si>
+    <t>WisdomTree Aluminium ETC</t>
+  </si>
+  <si>
+    <t>DE000A0Q4MJ7</t>
+  </si>
+  <si>
+    <t>ZINC.MI</t>
+  </si>
+  <si>
+    <t>WisdomTree Zinc ETC</t>
+  </si>
+  <si>
+    <t>DE000A0QLW44</t>
+  </si>
+  <si>
+    <t>COPM.MI</t>
+  </si>
+  <si>
+    <t>iShares Copper Miners UCITS ETF USD (Acc)</t>
+  </si>
+  <si>
+    <t>IE00063FT9K6</t>
+  </si>
+  <si>
+    <t>BATE.DE</t>
+  </si>
+  <si>
+    <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00BMDX3P59</t>
+  </si>
+  <si>
+    <t>IPRE.DE</t>
+  </si>
+  <si>
+    <t>iShares European Property Yield UCITS ETF EUR (Acc)</t>
+  </si>
+  <si>
+    <t>Private Equity</t>
+  </si>
+  <si>
+    <t>IE00BGDQ0L74</t>
+  </si>
+  <si>
+    <t>DX2G.DE</t>
+  </si>
+  <si>
+    <t>Xtrackers CAC 40 UCITS ETF 1D</t>
+  </si>
+  <si>
+    <t>LU0322250985</t>
+  </si>
+  <si>
+    <t>XEON.DE</t>
+  </si>
+  <si>
+    <t>Xtrackers II EUR Overnight Rate Swap UCITS ETF 1C</t>
+  </si>
+  <si>
+    <t>LU0290358497</t>
+  </si>
+  <si>
+    <t>IBGS.MI</t>
+  </si>
+  <si>
+    <t>iShares EUR Govt Bond 1-3yr UCITS ETF EUR (Dist)</t>
+  </si>
+  <si>
+    <t>Obbligazionari - Governativi EUR</t>
+  </si>
+  <si>
+    <t>IE00B14X4Q57</t>
+  </si>
+  <si>
+    <t>IUSE.L</t>
+  </si>
+  <si>
+    <t>iShares Core S&amp;P 500 UCITS ETF EUR Hedged (Acc)</t>
+  </si>
+  <si>
+    <t>IE00B3ZW0K18</t>
+  </si>
+  <si>
+    <t>IWDE.L</t>
+  </si>
+  <si>
+    <t>iShares MSCI World EUR Hedged UCITS ETF (Acc)</t>
+  </si>
+  <si>
+    <t>IE00B441G979</t>
+  </si>
+  <si>
+    <t>SGLD.MI</t>
+  </si>
+  <si>
+    <t>Invesco Physical Gold ETC</t>
+  </si>
+  <si>
+    <t>IE00B579F325</t>
+  </si>
+  <si>
+    <t>BTCN.AS</t>
+  </si>
+  <si>
+    <t>iShares Bitcoin ETP</t>
+  </si>
+  <si>
+    <t>XS2940466316</t>
+  </si>
+  <si>
+    <t>CMOD.MI</t>
+  </si>
+  <si>
+    <t>Invesco Bloomberg Commodity UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00BD6FVP32</t>
+  </si>
+  <si>
+    <t>XDWT.DE</t>
+  </si>
+  <si>
+    <t>Xtrackers MSCI World Information Technology UCITS ETF 1C</t>
+  </si>
+  <si>
+    <t>IE00BM67HT60</t>
+  </si>
+  <si>
+    <t>USPY.DE</t>
+  </si>
+  <si>
+    <t>L&amp;G Cyber Security UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE00BYPLS672</t>
+  </si>
+  <si>
+    <t>AIFS.DE</t>
+  </si>
+  <si>
+    <t>iShares AI Infrastructure UCITS ETF</t>
+  </si>
+  <si>
+    <t>IE000V0H6AD4</t>
+  </si>
+  <si>
     <t>INRG.MI</t>
   </si>
   <si>
-    <t>iShares Global Clean Energy UCITS ETF USD Dist</t>
-  </si>
-  <si>
-    <t>IE00B1XNHC34</t>
-  </si>
-  <si>
-    <t>XAIX.DE</t>
-  </si>
-  <si>
-    <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
-  </si>
-  <si>
-    <t>Settoriale - Tecnologia</t>
-  </si>
-  <si>
-    <t>IE00BGV5VN51</t>
-  </si>
-  <si>
-    <t>SXR2.DE</t>
-  </si>
-  <si>
-    <t>iShares MSCI Canada UCITS ETF USD Acc</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>IE00B52SF786</t>
-  </si>
-  <si>
-    <t>IQQI.DE</t>
-  </si>
-  <si>
-    <t>iShares Global Infrastructure UCITS ETF USD Dist</t>
-  </si>
-  <si>
-    <t>Infrastrutture</t>
-  </si>
-  <si>
-    <t>IE00B6QW5T61</t>
-  </si>
-  <si>
-    <t>IBGX.AS</t>
-  </si>
-  <si>
-    <t>iShares USD Treasury Bond 7-10yr UCITS ETF USD Dist</t>
-  </si>
-  <si>
-    <t>Obbligazionari - Governativi USD</t>
-  </si>
-  <si>
-    <t>IE00B1FZS681</t>
-  </si>
-  <si>
-    <t>IS3S.DE</t>
-  </si>
-  <si>
-    <t>iShares MSCI Europe Small Cap UCITS ETF EUR Acc</t>
-  </si>
-  <si>
-    <t>IE00B3VWMM18</t>
-  </si>
-  <si>
-    <t>WSML.L</t>
-  </si>
-  <si>
-    <t>iShares MSCI World Small Cap UCITS ETF USD (Acc)</t>
-  </si>
-  <si>
-    <t>IE00BDVWFV31</t>
-  </si>
-  <si>
-    <t>VHYL.MI</t>
-  </si>
-  <si>
-    <t>Vanguard FTSE All-World High Div Yield UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE00B8GKDB10</t>
-  </si>
-  <si>
-    <t>HLTH.DE</t>
-  </si>
-  <si>
-    <t>SPDR MSCI Europe Health Care UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE00BKWQ0H23</t>
-  </si>
-  <si>
-    <t>IWMO.L</t>
-  </si>
-  <si>
-    <t>iShares Edge MSCI World Momentum Factor UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE00B0M63912</t>
-  </si>
-  <si>
-    <t>IWQU.L</t>
-  </si>
-  <si>
-    <t>iShares Edge MSCI World Quality Factor UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE00B0M63961</t>
-  </si>
-  <si>
-    <t>MVOL.L</t>
-  </si>
-  <si>
-    <t>iShares Edge MSCI World Minimum Volatility UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE00B0M63507</t>
-  </si>
-  <si>
-    <t>LTAM.MI</t>
-  </si>
-  <si>
-    <t>iShares MSCI EM Latin America UCITS ETF USD (Dist)</t>
-  </si>
-  <si>
-    <t>IE00B27YCK28</t>
-  </si>
-  <si>
-    <t>EMV.MI</t>
-  </si>
-  <si>
-    <t>iShares Edge MSCI EM Min Vol Factor UCITS ETF USD (Acc)</t>
-  </si>
-  <si>
-    <t>IE00B8KGV557</t>
-  </si>
-  <si>
-    <t>IS3T.DE</t>
-  </si>
-  <si>
-    <t>iShares MSCI World Mid-Cap Equal Weight UCITS ETF EUR</t>
-  </si>
-  <si>
-    <t>Azionario Mid Cap</t>
-  </si>
-  <si>
-    <t>IE00BP3QZD73</t>
-  </si>
-  <si>
-    <t>EMID.L</t>
-  </si>
-  <si>
-    <t>iShares MSCI Europe Mid Cap UCITS ETF EUR (Dist)</t>
-  </si>
-  <si>
-    <t>IE00BFXR5895</t>
-  </si>
-  <si>
-    <t>AIGI.MI</t>
-  </si>
-  <si>
-    <t>WisdomTree Industrial Metals ETC (Al+Cu+Zn+Ni+Pb)</t>
-  </si>
-  <si>
-    <t>Metalli Industriali</t>
-  </si>
-  <si>
-    <t>GB00B15KYG56</t>
-  </si>
-  <si>
-    <t>COPA.MI</t>
-  </si>
-  <si>
-    <t>WisdomTree Copper ETC</t>
-  </si>
-  <si>
-    <t>GB00B15KXQ89</t>
-  </si>
-  <si>
-    <t>ALUM.MI</t>
-  </si>
-  <si>
-    <t>WisdomTree Aluminium ETC</t>
-  </si>
-  <si>
-    <t>DE000A0Q4MJ7</t>
-  </si>
-  <si>
-    <t>ZINC.MI</t>
-  </si>
-  <si>
-    <t>WisdomTree Zinc ETC</t>
-  </si>
-  <si>
-    <t>DE000A0QLW44</t>
-  </si>
-  <si>
-    <t>COPM.MI</t>
-  </si>
-  <si>
-    <t>iShares Copper Miners UCITS ETF USD (Acc)</t>
-  </si>
-  <si>
-    <t>IE00063FT9K6</t>
-  </si>
-  <si>
-    <t>BATE.DE</t>
-  </si>
-  <si>
-    <t>L&amp;G Battery Value-Chain UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE00BMDX3P59</t>
-  </si>
-  <si>
-    <t>IPRE.DE</t>
-  </si>
-  <si>
-    <t>iShares European Property Yield UCITS ETF EUR (Acc)</t>
-  </si>
-  <si>
-    <t>Private Equity</t>
-  </si>
-  <si>
-    <t>IE00BGDQ0L74</t>
-  </si>
-  <si>
-    <t>DX2G.DE</t>
-  </si>
-  <si>
-    <t>Xtrackers CAC 40 UCITS ETF 1D</t>
-  </si>
-  <si>
-    <t>LU0322250985</t>
-  </si>
-  <si>
-    <t>XEON.DE</t>
-  </si>
-  <si>
-    <t>Xtrackers II EUR Overnight Rate Swap UCITS ETF 1C</t>
-  </si>
-  <si>
-    <t>LU0290358497</t>
-  </si>
-  <si>
-    <t>IBGS.MI</t>
-  </si>
-  <si>
-    <t>iShares EUR Govt Bond 1-3yr UCITS ETF EUR (Dist)</t>
-  </si>
-  <si>
-    <t>Obbligazionari - Governativi EUR</t>
-  </si>
-  <si>
-    <t>IE00B14X4Q57</t>
-  </si>
-  <si>
-    <t>IUSE.L</t>
-  </si>
-  <si>
-    <t>iShares Core S&amp;P 500 UCITS ETF EUR Hedged (Acc)</t>
-  </si>
-  <si>
-    <t>IE00B3ZW0K18</t>
-  </si>
-  <si>
-    <t>IWDE.L</t>
-  </si>
-  <si>
-    <t>iShares MSCI World EUR Hedged UCITS ETF (Acc)</t>
-  </si>
-  <si>
-    <t>IE00B441G979</t>
-  </si>
-  <si>
-    <t>SGLD.MI</t>
-  </si>
-  <si>
-    <t>Invesco Physical Gold ETC</t>
-  </si>
-  <si>
-    <t>IE00B579F325</t>
-  </si>
-  <si>
-    <t>BTCN.AS</t>
-  </si>
-  <si>
-    <t>iShares Bitcoin ETP</t>
-  </si>
-  <si>
-    <t>XS2940466316</t>
-  </si>
-  <si>
-    <t>CMOD.MI</t>
-  </si>
-  <si>
-    <t>Invesco Bloomberg Commodity UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE00BD6FVP32</t>
-  </si>
-  <si>
-    <t>XDWT.DE</t>
-  </si>
-  <si>
-    <t>Xtrackers MSCI World Information Technology UCITS ETF 1C</t>
-  </si>
-  <si>
-    <t>IE00BM67HT60</t>
-  </si>
-  <si>
-    <t>USPY.DE</t>
-  </si>
-  <si>
-    <t>L&amp;G Cyber Security UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE00BYPLS672</t>
-  </si>
-  <si>
-    <t>AIFS.DE</t>
-  </si>
-  <si>
-    <t>iShares AI Infrastructure UCITS ETF</t>
-  </si>
-  <si>
-    <t>IE000V0H6AD4</t>
-  </si>
-  <si>
     <t>iShares Global Clean Energy Transition UCITS ETF</t>
   </si>
   <si>
@@ -2343,9 +2349,6 @@
   </si>
   <si>
     <t>iShares VII PLC - iShares VII PLC - iShares $ Trea</t>
-  </si>
-  <si>
-    <t>Svizzera</t>
   </si>
   <si>
     <t>IE00B3VWN393</t>
@@ -11533,10 +11536,10 @@
         <v>46</v>
       </c>
       <c r="E174" t="s">
-        <v>18</v>
+        <v>575</v>
       </c>
       <c r="F174" t="s">
-        <v>19</v>
+        <v>557</v>
       </c>
       <c r="G174">
         <v>10.174</v>
@@ -11563,7 +11566,7 @@
         <v>21</v>
       </c>
       <c r="O174" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="175" spans="1:15">
@@ -11571,13 +11574,13 @@
         <v>3</v>
       </c>
       <c r="B175" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C175" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D175" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E175" t="s">
         <v>220</v>
@@ -11610,7 +11613,7 @@
         <v>21</v>
       </c>
       <c r="O175" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="176" spans="1:15">
@@ -11618,13 +11621,13 @@
         <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C176" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D176" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E176" t="s">
         <v>18</v>
@@ -11657,7 +11660,7 @@
         <v>21</v>
       </c>
       <c r="O176" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="177" spans="1:15">
@@ -11665,13 +11668,13 @@
         <v>3</v>
       </c>
       <c r="B177" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C177" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D177" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E177" t="s">
         <v>18</v>
@@ -11704,7 +11707,7 @@
         <v>21</v>
       </c>
       <c r="O177" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="178" spans="1:15">
@@ -11712,13 +11715,13 @@
         <v>3</v>
       </c>
       <c r="B178" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C178" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D178" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E178" t="s">
         <v>18</v>
@@ -11751,7 +11754,7 @@
         <v>21</v>
       </c>
       <c r="O178" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="179" spans="1:15">
@@ -11759,10 +11762,10 @@
         <v>3</v>
       </c>
       <c r="B179" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C179" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D179" t="s">
         <v>54</v>
@@ -11798,7 +11801,7 @@
         <v>21</v>
       </c>
       <c r="O179" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="180" spans="1:15">
@@ -11806,10 +11809,10 @@
         <v>3</v>
       </c>
       <c r="B180" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C180" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D180" t="s">
         <v>564</v>
@@ -11845,7 +11848,7 @@
         <v>21</v>
       </c>
       <c r="O180" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="181" spans="1:15">
@@ -11853,10 +11856,10 @@
         <v>3</v>
       </c>
       <c r="B181" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C181" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D181" t="s">
         <v>564</v>
@@ -11892,7 +11895,7 @@
         <v>21</v>
       </c>
       <c r="O181" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="182" spans="1:15">
@@ -11900,10 +11903,10 @@
         <v>3</v>
       </c>
       <c r="B182" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C182" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D182" t="s">
         <v>258</v>
@@ -11939,7 +11942,7 @@
         <v>21</v>
       </c>
       <c r="O182" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="183" spans="1:15">
@@ -11947,10 +11950,10 @@
         <v>3</v>
       </c>
       <c r="B183" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C183" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D183" t="s">
         <v>564</v>
@@ -11986,7 +11989,7 @@
         <v>21</v>
       </c>
       <c r="O183" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="184" spans="1:15">
@@ -11994,10 +11997,10 @@
         <v>3</v>
       </c>
       <c r="B184" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C184" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D184" t="s">
         <v>564</v>
@@ -12033,7 +12036,7 @@
         <v>21</v>
       </c>
       <c r="O184" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="185" spans="1:15">
@@ -12041,10 +12044,10 @@
         <v>3</v>
       </c>
       <c r="B185" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C185" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D185" t="s">
         <v>564</v>
@@ -12080,7 +12083,7 @@
         <v>21</v>
       </c>
       <c r="O185" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="186" spans="1:15">
@@ -12088,10 +12091,10 @@
         <v>2</v>
       </c>
       <c r="B186" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C186" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D186" t="s">
         <v>37</v>
@@ -12127,7 +12130,7 @@
         <v>21</v>
       </c>
       <c r="O186" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="187" spans="1:15">
@@ -12135,10 +12138,10 @@
         <v>3</v>
       </c>
       <c r="B187" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C187" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D187" t="s">
         <v>17</v>
@@ -12174,7 +12177,7 @@
         <v>21</v>
       </c>
       <c r="O187" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="188" spans="1:15">
@@ -12182,13 +12185,13 @@
         <v>3</v>
       </c>
       <c r="B188" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C188" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D188" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E188" t="s">
         <v>220</v>
@@ -12221,7 +12224,7 @@
         <v>21</v>
       </c>
       <c r="O188" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="189" spans="1:15">
@@ -12229,13 +12232,13 @@
         <v>3</v>
       </c>
       <c r="B189" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C189" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D189" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E189" t="s">
         <v>18</v>
@@ -12268,7 +12271,7 @@
         <v>21</v>
       </c>
       <c r="O189" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="190" spans="1:15">
@@ -12276,13 +12279,13 @@
         <v>3</v>
       </c>
       <c r="B190" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C190" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D190" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E190" t="s">
         <v>18</v>
@@ -12315,7 +12318,7 @@
         <v>21</v>
       </c>
       <c r="O190" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="191" spans="1:15">
@@ -12323,13 +12326,13 @@
         <v>3</v>
       </c>
       <c r="B191" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C191" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D191" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E191" t="s">
         <v>18</v>
@@ -12362,7 +12365,7 @@
         <v>21</v>
       </c>
       <c r="O191" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="192" spans="1:15">
@@ -12370,13 +12373,13 @@
         <v>3</v>
       </c>
       <c r="B192" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C192" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D192" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E192" t="s">
         <v>18</v>
@@ -12409,7 +12412,7 @@
         <v>21</v>
       </c>
       <c r="O192" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="193" spans="1:15">
@@ -12417,13 +12420,13 @@
         <v>3</v>
       </c>
       <c r="B193" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C193" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D193" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E193" t="s">
         <v>18</v>
@@ -12456,7 +12459,7 @@
         <v>21</v>
       </c>
       <c r="O193" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="194" spans="1:15">
@@ -12464,13 +12467,13 @@
         <v>3</v>
       </c>
       <c r="B194" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C194" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D194" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E194" t="s">
         <v>18</v>
@@ -12503,7 +12506,7 @@
         <v>21</v>
       </c>
       <c r="O194" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="195" spans="1:15">
@@ -12511,13 +12514,13 @@
         <v>3</v>
       </c>
       <c r="B195" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C195" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D195" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E195" t="s">
         <v>220</v>
@@ -12550,7 +12553,7 @@
         <v>21</v>
       </c>
       <c r="O195" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="196" spans="1:15">
@@ -12558,13 +12561,13 @@
         <v>3</v>
       </c>
       <c r="B196" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C196" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D196" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E196" t="s">
         <v>220</v>
@@ -12597,7 +12600,7 @@
         <v>21</v>
       </c>
       <c r="O196" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="197" spans="1:15">
@@ -12605,13 +12608,13 @@
         <v>3</v>
       </c>
       <c r="B197" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C197" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D197" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E197" t="s">
         <v>220</v>
@@ -12644,7 +12647,7 @@
         <v>21</v>
       </c>
       <c r="O197" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="198" spans="1:15">
@@ -12652,10 +12655,10 @@
         <v>3</v>
       </c>
       <c r="B198" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C198" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D198" t="s">
         <v>409</v>
@@ -12691,7 +12694,7 @@
         <v>21</v>
       </c>
       <c r="O198" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="199" spans="1:15">
@@ -12699,13 +12702,13 @@
         <v>3</v>
       </c>
       <c r="B199" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C199" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D199" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E199" t="s">
         <v>18</v>
@@ -12738,7 +12741,7 @@
         <v>21</v>
       </c>
       <c r="O199" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="200" spans="1:15">
@@ -12746,10 +12749,10 @@
         <v>3</v>
       </c>
       <c r="B200" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C200" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D200" t="s">
         <v>50</v>
@@ -12785,7 +12788,7 @@
         <v>21</v>
       </c>
       <c r="O200" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="201" spans="1:15">
@@ -12793,10 +12796,10 @@
         <v>3</v>
       </c>
       <c r="B201" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C201" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D201" t="s">
         <v>564</v>
@@ -12832,7 +12835,7 @@
         <v>21</v>
       </c>
       <c r="O201" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="202" spans="1:15">
@@ -12840,10 +12843,10 @@
         <v>3</v>
       </c>
       <c r="B202" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C202" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D202" t="s">
         <v>555</v>
@@ -12879,7 +12882,7 @@
         <v>21</v>
       </c>
       <c r="O202" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="203" spans="1:15">
@@ -12887,13 +12890,13 @@
         <v>3</v>
       </c>
       <c r="B203" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C203" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D203" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E203" t="s">
         <v>18</v>
@@ -12926,7 +12929,7 @@
         <v>21</v>
       </c>
       <c r="O203" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="204" spans="1:15">
@@ -12934,10 +12937,10 @@
         <v>3</v>
       </c>
       <c r="B204" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C204" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D204" t="s">
         <v>110</v>
@@ -12973,7 +12976,7 @@
         <v>21</v>
       </c>
       <c r="O204" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="205" spans="1:15">
@@ -12981,13 +12984,13 @@
         <v>3</v>
       </c>
       <c r="B205" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C205" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D205" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E205" t="s">
         <v>220</v>
@@ -13020,7 +13023,7 @@
         <v>21</v>
       </c>
       <c r="O205" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="206" spans="1:15">
@@ -13028,13 +13031,13 @@
         <v>3</v>
       </c>
       <c r="B206" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C206" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D206" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E206" t="s">
         <v>220</v>
@@ -13067,7 +13070,7 @@
         <v>21</v>
       </c>
       <c r="O206" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="207" spans="1:15">
@@ -13075,13 +13078,13 @@
         <v>3</v>
       </c>
       <c r="B207" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C207" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D207" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E207" t="s">
         <v>220</v>
@@ -13114,7 +13117,7 @@
         <v>21</v>
       </c>
       <c r="O207" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="208" spans="1:15">
@@ -13122,10 +13125,10 @@
         <v>3</v>
       </c>
       <c r="B208" t="s">
-        <v>573</v>
+        <v>684</v>
       </c>
       <c r="C208" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D208" t="s">
         <v>46</v>
@@ -13161,7 +13164,7 @@
         <v>21</v>
       </c>
       <c r="O208" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="209" spans="1:15">
@@ -13169,10 +13172,10 @@
         <v>3</v>
       </c>
       <c r="B209" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C209" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D209" t="s">
         <v>555</v>
@@ -13208,7 +13211,7 @@
         <v>21</v>
       </c>
       <c r="O209" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="210" spans="1:15">
@@ -13216,13 +13219,13 @@
         <v>3</v>
       </c>
       <c r="B210" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C210" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D210" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E210" t="s">
         <v>18</v>
@@ -13255,7 +13258,7 @@
         <v>21</v>
       </c>
       <c r="O210" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="211" spans="1:15">
@@ -13263,19 +13266,19 @@
         <v>3</v>
       </c>
       <c r="B211" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C211" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D211" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E211" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F211" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G211">
         <v>61.09</v>
@@ -13302,7 +13305,7 @@
         <v>21</v>
       </c>
       <c r="O211" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="212" spans="1:15">
@@ -13310,19 +13313,19 @@
         <v>3</v>
       </c>
       <c r="B212" t="s">
+        <v>700</v>
+      </c>
+      <c r="C212" t="s">
+        <v>701</v>
+      </c>
+      <c r="D212" t="s">
+        <v>696</v>
+      </c>
+      <c r="E212" t="s">
+        <v>697</v>
+      </c>
+      <c r="F212" t="s">
         <v>698</v>
-      </c>
-      <c r="C212" t="s">
-        <v>699</v>
-      </c>
-      <c r="D212" t="s">
-        <v>694</v>
-      </c>
-      <c r="E212" t="s">
-        <v>695</v>
-      </c>
-      <c r="F212" t="s">
-        <v>696</v>
       </c>
       <c r="G212">
         <v>61.08</v>
@@ -13349,7 +13352,7 @@
         <v>21</v>
       </c>
       <c r="O212" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="213" spans="1:15">
@@ -13357,19 +13360,19 @@
         <v>2</v>
       </c>
       <c r="B213" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C213" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D213" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E213" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F213" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G213">
         <v>9.262</v>
@@ -13393,7 +13396,7 @@
         <v>21</v>
       </c>
       <c r="O213" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="214" spans="1:15">
@@ -13401,16 +13404,16 @@
         <v>3</v>
       </c>
       <c r="B214" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C214" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D214" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E214" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F214" t="s">
         <v>19</v>
@@ -13440,7 +13443,7 @@
         <v>21</v>
       </c>
       <c r="O214" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="215" spans="1:15">
@@ -13448,16 +13451,16 @@
         <v>3</v>
       </c>
       <c r="B215" t="s">
+        <v>710</v>
+      </c>
+      <c r="C215" t="s">
+        <v>711</v>
+      </c>
+      <c r="D215" t="s">
+        <v>696</v>
+      </c>
+      <c r="E215" t="s">
         <v>708</v>
-      </c>
-      <c r="C215" t="s">
-        <v>709</v>
-      </c>
-      <c r="D215" t="s">
-        <v>694</v>
-      </c>
-      <c r="E215" t="s">
-        <v>706</v>
       </c>
       <c r="F215" t="s">
         <v>557</v>
@@ -13487,7 +13490,7 @@
         <v>21</v>
       </c>
       <c r="O215" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="216" spans="1:15">
@@ -13495,13 +13498,13 @@
         <v>3</v>
       </c>
       <c r="B216" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C216" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D216" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E216" t="s">
         <v>18</v>
@@ -13534,7 +13537,7 @@
         <v>21</v>
       </c>
       <c r="O216" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="217" spans="1:15">
@@ -13542,13 +13545,13 @@
         <v>3</v>
       </c>
       <c r="B217" t="s">
+        <v>717</v>
+      </c>
+      <c r="C217" t="s">
+        <v>718</v>
+      </c>
+      <c r="D217" t="s">
         <v>715</v>
-      </c>
-      <c r="C217" t="s">
-        <v>716</v>
-      </c>
-      <c r="D217" t="s">
-        <v>713</v>
       </c>
       <c r="E217" t="s">
         <v>18</v>
@@ -13581,7 +13584,7 @@
         <v>21</v>
       </c>
       <c r="O217" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="218" spans="1:15">
@@ -13589,13 +13592,13 @@
         <v>3</v>
       </c>
       <c r="B218" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C218" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D218" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E218" t="s">
         <v>18</v>
@@ -13628,7 +13631,7 @@
         <v>21</v>
       </c>
       <c r="O218" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="219" spans="1:15">
@@ -13636,13 +13639,13 @@
         <v>3</v>
       </c>
       <c r="B219" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C219" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D219" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E219" t="s">
         <v>556</v>
@@ -13675,7 +13678,7 @@
         <v>21</v>
       </c>
       <c r="O219" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="220" spans="1:15">
@@ -13683,13 +13686,13 @@
         <v>3</v>
       </c>
       <c r="B220" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C220" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D220" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E220" t="s">
         <v>18</v>
@@ -13722,7 +13725,7 @@
         <v>21</v>
       </c>
       <c r="O220" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="221" spans="1:15">
@@ -13730,13 +13733,13 @@
         <v>3</v>
       </c>
       <c r="B221" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C221" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D221" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E221" t="s">
         <v>18</v>
@@ -13769,7 +13772,7 @@
         <v>21</v>
       </c>
       <c r="O221" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="222" spans="1:15">
@@ -13777,13 +13780,13 @@
         <v>3</v>
       </c>
       <c r="B222" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C222" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D222" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E222" t="s">
         <v>18</v>
@@ -13816,7 +13819,7 @@
         <v>21</v>
       </c>
       <c r="O222" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="223" spans="1:15">
@@ -13824,13 +13827,13 @@
         <v>3</v>
       </c>
       <c r="B223" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C223" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D223" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E223" t="s">
         <v>18</v>
@@ -13863,7 +13866,7 @@
         <v>21</v>
       </c>
       <c r="O223" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="224" spans="1:15">
@@ -13871,16 +13874,16 @@
         <v>3</v>
       </c>
       <c r="B224" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C224" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D224" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E224" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F224" t="s">
         <v>19</v>
@@ -13910,7 +13913,7 @@
         <v>21</v>
       </c>
       <c r="O224" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="225" spans="1:15">
@@ -13918,13 +13921,13 @@
         <v>3</v>
       </c>
       <c r="B225" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C225" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D225" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E225" t="s">
         <v>18</v>
@@ -13957,7 +13960,7 @@
         <v>21</v>
       </c>
       <c r="O225" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="226" spans="1:15">
@@ -13965,13 +13968,13 @@
         <v>3</v>
       </c>
       <c r="B226" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C226" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D226" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E226" t="s">
         <v>165</v>
@@ -14004,7 +14007,7 @@
         <v>21</v>
       </c>
       <c r="O226" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="227" spans="1:15">
@@ -14012,16 +14015,16 @@
         <v>3</v>
       </c>
       <c r="B227" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C227" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D227" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E227" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F227" t="s">
         <v>19</v>
@@ -14051,7 +14054,7 @@
         <v>21</v>
       </c>
       <c r="O227" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="228" spans="1:15">
@@ -14059,13 +14062,13 @@
         <v>3</v>
       </c>
       <c r="B228" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C228" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D228" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E228" t="s">
         <v>220</v>
@@ -14098,7 +14101,7 @@
         <v>21</v>
       </c>
       <c r="O228" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="229" spans="1:15">
@@ -14106,13 +14109,13 @@
         <v>3</v>
       </c>
       <c r="B229" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C229" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D229" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E229" t="s">
         <v>165</v>
@@ -14145,7 +14148,7 @@
         <v>21</v>
       </c>
       <c r="O229" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="230" spans="1:15">
@@ -14153,16 +14156,16 @@
         <v>3</v>
       </c>
       <c r="B230" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C230" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D230" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E230" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F230" t="s">
         <v>557</v>
@@ -14192,7 +14195,7 @@
         <v>21</v>
       </c>
       <c r="O230" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="231" spans="1:15">
@@ -14200,16 +14203,16 @@
         <v>3</v>
       </c>
       <c r="B231" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C231" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D231" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E231" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -14239,7 +14242,7 @@
         <v>21</v>
       </c>
       <c r="O231" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="232" spans="1:15">
@@ -14247,16 +14250,16 @@
         <v>3</v>
       </c>
       <c r="B232" t="s">
+        <v>766</v>
+      </c>
+      <c r="C232" t="s">
+        <v>767</v>
+      </c>
+      <c r="D232" t="s">
+        <v>763</v>
+      </c>
+      <c r="E232" t="s">
         <v>764</v>
-      </c>
-      <c r="C232" t="s">
-        <v>765</v>
-      </c>
-      <c r="D232" t="s">
-        <v>761</v>
-      </c>
-      <c r="E232" t="s">
-        <v>762</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -14286,7 +14289,7 @@
         <v>21</v>
       </c>
       <c r="O232" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="233" spans="1:15">
@@ -14294,13 +14297,13 @@
         <v>3</v>
       </c>
       <c r="B233" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C233" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D233" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E233" t="s">
         <v>165</v>
@@ -14333,7 +14336,7 @@
         <v>21</v>
       </c>
       <c r="O233" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="234" spans="1:15">
@@ -14341,16 +14344,16 @@
         <v>3</v>
       </c>
       <c r="B234" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C234" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D234" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E234" t="s">
-        <v>772</v>
+        <v>575</v>
       </c>
       <c r="F234" t="s">
         <v>557</v>
@@ -14380,7 +14383,7 @@
         <v>21</v>
       </c>
       <c r="O234" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="235" spans="1:15">
@@ -14388,13 +14391,13 @@
         <v>3</v>
       </c>
       <c r="B235" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C235" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D235" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E235" t="s">
         <v>18</v>
@@ -14427,7 +14430,7 @@
         <v>21</v>
       </c>
       <c r="O235" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="236" spans="1:15">
@@ -14435,13 +14438,13 @@
         <v>3</v>
       </c>
       <c r="B236" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C236" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D236" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E236" t="s">
         <v>18</v>
@@ -14474,7 +14477,7 @@
         <v>21</v>
       </c>
       <c r="O236" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="237" spans="1:15">
@@ -14482,13 +14485,13 @@
         <v>3</v>
       </c>
       <c r="B237" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C237" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D237" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E237" t="s">
         <v>220</v>
@@ -14521,7 +14524,7 @@
         <v>21</v>
       </c>
       <c r="O237" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1226,22 +1226,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>168.66</v>
+        <v>170.69</v>
       </c>
       <c r="H2" t="n">
-        <v>170.5231</v>
+        <v>170.8819</v>
       </c>
       <c r="I2" t="n">
-        <v>170.7972</v>
+        <v>170.425</v>
       </c>
       <c r="J2" t="n">
-        <v>48.6</v>
+        <v>50.2</v>
       </c>
       <c r="K2" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4481</v>
+        <v>0.3495</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>50.71</v>
+        <v>51.05</v>
       </c>
       <c r="H3" t="n">
-        <v>50.5978</v>
+        <v>50.6891</v>
       </c>
       <c r="I3" t="n">
-        <v>49.905</v>
+        <v>49.9144</v>
       </c>
       <c r="J3" t="n">
-        <v>52.2</v>
+        <v>54.4</v>
       </c>
       <c r="K3" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0674</v>
+        <v>0.0472</v>
       </c>
       <c r="M3" s="12" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1324,7 +1324,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1352,31 +1352,31 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>142.46</v>
+        <v>144.72</v>
       </c>
       <c r="H4" t="n">
-        <v>142.0164</v>
+        <v>142.448</v>
       </c>
       <c r="I4" t="n">
-        <v>135.1548</v>
+        <v>135.462</v>
       </c>
       <c r="J4" t="n">
-        <v>54.3</v>
+        <v>60.5</v>
       </c>
       <c r="K4" t="n">
-        <v>26.6</v>
+        <v>25.9</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1027</v>
-      </c>
-      <c r="M4" s="12" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>-0.109</v>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1415,22 +1415,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.969</v>
+        <v>2.9835</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9405</v>
+        <v>2.9464</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8592</v>
+        <v>2.8645</v>
       </c>
       <c r="J5" t="n">
-        <v>58.1</v>
+        <v>60.7</v>
       </c>
       <c r="K5" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1478,22 +1478,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>25.61</v>
+        <v>26.73</v>
       </c>
       <c r="H6" t="n">
-        <v>24.7672</v>
+        <v>24.9718</v>
       </c>
       <c r="I6" t="n">
-        <v>24.9056</v>
+        <v>24.9626</v>
       </c>
       <c r="J6" t="n">
-        <v>61.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>19.3</v>
+        <v>21.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1487</v>
+        <v>0.248</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1541,22 +1541,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>210.8</v>
+        <v>213.55</v>
       </c>
       <c r="H7" t="n">
-        <v>208.9862</v>
+        <v>209.5716</v>
       </c>
       <c r="I7" t="n">
-        <v>202.5722</v>
+        <v>202.943</v>
       </c>
       <c r="J7" t="n">
-        <v>56.9</v>
+        <v>63.3</v>
       </c>
       <c r="K7" t="n">
-        <v>30.8</v>
+        <v>32.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1854</v>
+        <v>0.2212</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1604,22 +1604,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>539.1</v>
+        <v>541.4</v>
       </c>
       <c r="H8" t="n">
-        <v>520.8521</v>
+        <v>522.6022</v>
       </c>
       <c r="I8" t="n">
-        <v>503.872</v>
+        <v>505.538</v>
       </c>
       <c r="J8" t="n">
-        <v>68.5</v>
+        <v>69.8</v>
       </c>
       <c r="K8" t="n">
-        <v>27.3</v>
+        <v>27.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3038</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1667,22 +1667,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>40.42</v>
+        <v>40.745</v>
       </c>
       <c r="H9" t="n">
-        <v>42.1368</v>
+        <v>42.0155</v>
       </c>
       <c r="I9" t="n">
-        <v>43.1394</v>
+        <v>43.0263</v>
       </c>
       <c r="J9" t="n">
-        <v>33.3</v>
+        <v>36.2</v>
       </c>
       <c r="K9" t="n">
-        <v>15.7</v>
+        <v>16.6</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1397</v>
+        <v>-0.1488</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1701,8 +1701,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>3</v>
+      <c r="A10" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1730,31 +1730,31 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>109.38</v>
+        <v>109.62</v>
       </c>
       <c r="H10" t="n">
-        <v>108.7561</v>
+        <v>108.8936</v>
       </c>
       <c r="I10" t="n">
-        <v>105.3026</v>
+        <v>105.5302</v>
       </c>
       <c r="J10" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="K10" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3518</v>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>-0.2967</v>
+      </c>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1793,22 +1793,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>47.07</v>
+        <v>47.295</v>
       </c>
       <c r="H11" t="n">
-        <v>47.2674</v>
+        <v>47.301</v>
       </c>
       <c r="I11" t="n">
-        <v>45.8149</v>
+        <v>45.9084</v>
       </c>
       <c r="J11" t="n">
-        <v>50.7</v>
+        <v>52.9</v>
       </c>
       <c r="K11" t="n">
-        <v>31.8</v>
+        <v>29.6</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1632</v>
+        <v>-0.1559</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>52</v>
+        <v>52.43</v>
       </c>
       <c r="H12" t="n">
-        <v>52.5377</v>
+        <v>52.5344</v>
       </c>
       <c r="I12" t="n">
-        <v>52.4368</v>
+        <v>52.3832</v>
       </c>
       <c r="J12" t="n">
-        <v>45.1</v>
+        <v>48.7</v>
       </c>
       <c r="K12" t="n">
-        <v>10.8</v>
+        <v>12.1</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0423</v>
+        <v>-0.0351</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1919,22 +1919,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>40.21</v>
+        <v>40.59</v>
       </c>
       <c r="H13" t="n">
-        <v>40.1494</v>
+        <v>40.2465</v>
       </c>
       <c r="I13" t="n">
-        <v>40.21</v>
+        <v>40.1851</v>
       </c>
       <c r="J13" t="n">
-        <v>50.9</v>
+        <v>53.3</v>
       </c>
       <c r="K13" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0915</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1982,22 +1982,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>99.75</v>
+        <v>100.68</v>
       </c>
       <c r="H14" t="n">
-        <v>102.0789</v>
+        <v>102.1674</v>
       </c>
       <c r="I14" t="n">
-        <v>103.9838</v>
+        <v>104.0024</v>
       </c>
       <c r="J14" t="n">
-        <v>36.1</v>
+        <v>39.6</v>
       </c>
       <c r="K14" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1137</v>
+        <v>-0.0544</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2045,22 +2045,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>217.44</v>
+        <v>222.94</v>
       </c>
       <c r="H15" t="n">
-        <v>218.8471</v>
+        <v>219.5644</v>
       </c>
       <c r="I15" t="n">
-        <v>216.9528</v>
+        <v>217.1954</v>
       </c>
       <c r="J15" t="n">
-        <v>47.8</v>
+        <v>59.5</v>
       </c>
       <c r="K15" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3482</v>
+        <v>0.0713</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2108,22 +2108,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>624.74</v>
+        <v>627.24</v>
       </c>
       <c r="H16" t="n">
-        <v>625.9739</v>
+        <v>626.7907</v>
       </c>
       <c r="I16" t="n">
-        <v>619.3194</v>
+        <v>619.8678</v>
       </c>
       <c r="J16" t="n">
-        <v>50.3</v>
+        <v>51.9</v>
       </c>
       <c r="K16" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5327</v>
+        <v>-0.3305</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2143,7 +2143,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2171,31 +2171,31 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>15.492</v>
+        <v>15.644</v>
       </c>
       <c r="H17" t="n">
-        <v>15.5604</v>
+        <v>15.5797</v>
       </c>
       <c r="I17" t="n">
-        <v>14.8066</v>
+        <v>14.8385</v>
       </c>
       <c r="J17" t="n">
-        <v>51.5</v>
+        <v>54.2</v>
       </c>
       <c r="K17" t="n">
-        <v>24.7</v>
+        <v>23.2</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0356</v>
-      </c>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>-0.0504</v>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2234,22 +2234,22 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>73.902</v>
+        <v>74.374</v>
       </c>
       <c r="H18" t="n">
-        <v>73.9974</v>
+        <v>74.1315</v>
       </c>
       <c r="I18" t="n">
-        <v>73.8661</v>
+        <v>73.8475</v>
       </c>
       <c r="J18" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="K18" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0708</v>
+        <v>0.0921</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2297,22 +2297,22 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>100.15</v>
+        <v>100.79</v>
       </c>
       <c r="H19" t="n">
-        <v>100.2874</v>
+        <v>100.474</v>
       </c>
       <c r="I19" t="n">
-        <v>100.1128</v>
+        <v>100.0882</v>
       </c>
       <c r="J19" t="n">
-        <v>49.9</v>
+        <v>51.9</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0989</v>
+        <v>0.1287</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2360,22 +2360,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7.5922</v>
+        <v>7.6386</v>
       </c>
       <c r="H20" t="n">
-        <v>7.5985</v>
+        <v>7.612</v>
       </c>
       <c r="I20" t="n">
-        <v>7.5828</v>
+        <v>7.5808</v>
       </c>
       <c r="J20" t="n">
-        <v>50.2</v>
+        <v>52</v>
       </c>
       <c r="K20" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0103</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>147.61</v>
+        <v>151.53</v>
       </c>
       <c r="H21" t="n">
-        <v>148.683</v>
+        <v>149.1541</v>
       </c>
       <c r="I21" t="n">
-        <v>147.43</v>
+        <v>147.5914</v>
       </c>
       <c r="J21" t="n">
-        <v>47.4</v>
+        <v>59.6</v>
       </c>
       <c r="K21" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2511</v>
+        <v>0.035</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2486,22 +2486,22 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>74.20999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>74.0219</v>
+        <v>74.0342</v>
       </c>
       <c r="I22" t="n">
-        <v>72.56480000000001</v>
+        <v>72.6748</v>
       </c>
       <c r="J22" t="n">
-        <v>53.6</v>
+        <v>54.6</v>
       </c>
       <c r="K22" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2246</v>
+        <v>-0.2015</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2549,22 +2549,22 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7.299</v>
+        <v>7.324</v>
       </c>
       <c r="H23" t="n">
-        <v>7.292</v>
+        <v>7.3028</v>
       </c>
       <c r="I23" t="n">
-        <v>7.2912</v>
+        <v>7.2876</v>
       </c>
       <c r="J23" t="n">
-        <v>50.7</v>
+        <v>51.6</v>
       </c>
       <c r="K23" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0095</v>
+        <v>0.0101</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2612,22 +2612,22 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>251.3</v>
+        <v>252.35</v>
       </c>
       <c r="H24" t="n">
-        <v>255.7239</v>
+        <v>255.8239</v>
       </c>
       <c r="I24" t="n">
-        <v>254.179</v>
+        <v>254.2</v>
       </c>
       <c r="J24" t="n">
-        <v>38.1</v>
+        <v>40.4</v>
       </c>
       <c r="K24" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7581</v>
+        <v>-0.6911</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2675,22 +2675,22 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>353.42</v>
+        <v>358.51</v>
       </c>
       <c r="H25" t="n">
-        <v>355.6501</v>
+        <v>356.087</v>
       </c>
       <c r="I25" t="n">
-        <v>356.544</v>
+        <v>356.5712</v>
       </c>
       <c r="J25" t="n">
-        <v>47.2</v>
+        <v>53.3</v>
       </c>
       <c r="K25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4634</v>
+        <v>-0.0631</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2738,22 +2738,22 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>98.40000000000001</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>98.8796</v>
+        <v>99.021</v>
       </c>
       <c r="I26" t="n">
-        <v>98.76779999999999</v>
+        <v>98.73439999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>48.5</v>
+        <v>50.4</v>
       </c>
       <c r="K26" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0425</v>
+        <v>0.0664</v>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>37.095</v>
+        <v>37.445</v>
       </c>
       <c r="H27" t="n">
-        <v>36.2864</v>
+        <v>36.3946</v>
       </c>
       <c r="I27" t="n">
-        <v>35.0184</v>
+        <v>35.1054</v>
       </c>
       <c r="J27" t="n">
-        <v>65.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0376</v>
+        <v>0.0523</v>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2864,22 +2864,22 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>126.67</v>
+        <v>127.6273</v>
       </c>
       <c r="H28" t="n">
-        <v>127.1974</v>
+        <v>127.4486</v>
       </c>
       <c r="I28" t="n">
-        <v>126.6753</v>
+        <v>126.6366</v>
       </c>
       <c r="J28" t="n">
-        <v>49.3</v>
+        <v>51.2</v>
       </c>
       <c r="K28" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1572</v>
+        <v>0.1613</v>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2927,22 +2927,22 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.24</v>
+        <v>57.6</v>
       </c>
       <c r="H29" t="n">
-        <v>57.2391</v>
+        <v>57.2829</v>
       </c>
       <c r="I29" t="n">
-        <v>56.2016</v>
+        <v>56.258</v>
       </c>
       <c r="J29" t="n">
-        <v>52.3</v>
+        <v>56.4</v>
       </c>
       <c r="K29" t="n">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.0756</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2990,22 +2990,22 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>472.5</v>
+        <v>473.25</v>
       </c>
       <c r="H30" t="n">
-        <v>474.3494</v>
+        <v>474.4213</v>
       </c>
       <c r="I30" t="n">
-        <v>469.335</v>
+        <v>469.782</v>
       </c>
       <c r="J30" t="n">
-        <v>48.1</v>
+        <v>49.5</v>
       </c>
       <c r="K30" t="n">
-        <v>24.2</v>
+        <v>23.2</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.9887</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3053,22 +3053,22 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>398.35</v>
+        <v>400.05</v>
       </c>
       <c r="H31" t="n">
-        <v>397.3512</v>
+        <v>397.5134</v>
       </c>
       <c r="I31" t="n">
-        <v>387.405</v>
+        <v>388.033</v>
       </c>
       <c r="J31" t="n">
-        <v>54.1</v>
+        <v>55.8</v>
       </c>
       <c r="K31" t="n">
-        <v>15.4</v>
+        <v>14.9</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.3609</v>
+        <v>-1.2299</v>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3116,22 +3116,22 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>25.1</v>
+        <v>25.05</v>
       </c>
       <c r="H32" t="n">
-        <v>24.9751</v>
+        <v>24.9891</v>
       </c>
       <c r="I32" t="n">
-        <v>24.3659</v>
+        <v>24.4011</v>
       </c>
       <c r="J32" t="n">
-        <v>58.5</v>
+        <v>56.1</v>
       </c>
       <c r="K32" t="n">
-        <v>29.2</v>
+        <v>26.9</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.0461</v>
+        <v>-0.0457</v>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3179,22 +3179,22 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>198.17</v>
+        <v>197.98</v>
       </c>
       <c r="H33" t="n">
-        <v>197.8697</v>
+        <v>198.0594</v>
       </c>
       <c r="I33" t="n">
-        <v>197.488</v>
+        <v>197.3768</v>
       </c>
       <c r="J33" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="K33" t="n">
         <v>8.9</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1913</v>
+        <v>0.1476</v>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3242,22 +3242,22 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>7.534</v>
+        <v>7.542</v>
       </c>
       <c r="H34" t="n">
-        <v>7.5346</v>
+        <v>7.5439</v>
       </c>
       <c r="I34" t="n">
-        <v>7.5409</v>
+        <v>7.536</v>
       </c>
       <c r="J34" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="K34" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3305,22 +3305,22 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>68.64</v>
+        <v>68.7</v>
       </c>
       <c r="H35" t="n">
-        <v>70.4558</v>
+        <v>70.33159999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>70.70780000000001</v>
+        <v>70.69159999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="K35" t="n">
-        <v>17.1</v>
+        <v>18.1</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2637</v>
+        <v>-0.2699</v>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3368,22 +3368,22 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>151.24</v>
+        <v>150.9</v>
       </c>
       <c r="H36" t="n">
-        <v>155.4262</v>
+        <v>155.0554</v>
       </c>
       <c r="I36" t="n">
-        <v>153.7212</v>
+        <v>153.7312</v>
       </c>
       <c r="J36" t="n">
-        <v>37.2</v>
+        <v>36.3</v>
       </c>
       <c r="K36" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.6681</v>
+        <v>-0.8032</v>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3431,22 +3431,22 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>94.16</v>
+        <v>93.42</v>
       </c>
       <c r="H37" t="n">
-        <v>94.66840000000001</v>
+        <v>94.5478</v>
       </c>
       <c r="I37" t="n">
-        <v>96.0444</v>
+        <v>95.9924</v>
       </c>
       <c r="J37" t="n">
-        <v>46.2</v>
+        <v>42.9</v>
       </c>
       <c r="K37" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.0131</v>
+        <v>-0.0327</v>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3494,22 +3494,22 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>69.7</v>
+        <v>70.39</v>
       </c>
       <c r="H38" t="n">
-        <v>69.7401</v>
+        <v>69.9235</v>
       </c>
       <c r="I38" t="n">
-        <v>69.7068</v>
+        <v>69.70959999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>50.2</v>
+        <v>53.4</v>
       </c>
       <c r="K38" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0854</v>
+        <v>0.1377</v>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="9" t="n">
         <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -3557,22 +3557,22 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>70.41</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>70.17</v>
+        <v>70.3005</v>
       </c>
       <c r="I39" t="n">
-        <v>69.90519999999999</v>
+        <v>69.8938</v>
       </c>
       <c r="J39" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="K39" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1203</v>
+        <v>0.1257</v>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3620,22 +3620,22 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H40" t="n">
-        <v>338.7556</v>
+        <v>337.7959</v>
       </c>
       <c r="I40" t="n">
-        <v>341.591</v>
+        <v>341.437</v>
       </c>
       <c r="J40" t="n">
-        <v>28.9</v>
+        <v>27.7</v>
       </c>
       <c r="K40" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.2995</v>
+        <v>-1.4295</v>
       </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3654,8 +3654,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>3</v>
+      <c r="A41" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3683,31 +3683,31 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>719.2</v>
+        <v>724.4</v>
       </c>
       <c r="H41" t="n">
-        <v>722.8797</v>
+        <v>723.5242</v>
       </c>
       <c r="I41" t="n">
-        <v>713.46</v>
+        <v>714.17</v>
       </c>
       <c r="J41" t="n">
-        <v>48.4</v>
+        <v>53.6</v>
       </c>
       <c r="K41" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.3764</v>
-      </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>-0.4005</v>
+      </c>
+      <c r="M41" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3746,22 +3746,22 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>438.65</v>
+        <v>441.65</v>
       </c>
       <c r="H42" t="n">
-        <v>444.8967</v>
+        <v>445.0398</v>
       </c>
       <c r="I42" t="n">
-        <v>442.314</v>
+        <v>442.43</v>
       </c>
       <c r="J42" t="n">
-        <v>41</v>
+        <v>44.6</v>
       </c>
       <c r="K42" t="n">
-        <v>17.3</v>
+        <v>16.5</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.4806</v>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3809,22 +3809,22 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>194.2</v>
+        <v>194.84</v>
       </c>
       <c r="H43" t="n">
-        <v>195.3727</v>
+        <v>195.3943</v>
       </c>
       <c r="I43" t="n">
-        <v>193.1788</v>
+        <v>193.3564</v>
       </c>
       <c r="J43" t="n">
-        <v>46.9</v>
+        <v>49.4</v>
       </c>
       <c r="K43" t="n">
-        <v>20.9</v>
+        <v>20.1</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.4223</v>
+        <v>-0.3823</v>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3872,22 +3872,22 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>246.7</v>
+        <v>247.3</v>
       </c>
       <c r="H44" t="n">
-        <v>249.5823</v>
+        <v>249.464</v>
       </c>
       <c r="I44" t="n">
-        <v>247.842</v>
+        <v>247.962</v>
       </c>
       <c r="J44" t="n">
-        <v>40.8</v>
+        <v>42.4</v>
       </c>
       <c r="K44" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.5897</v>
+        <v>-0.5991</v>
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3935,22 +3935,22 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>123.82</v>
+        <v>124.38</v>
       </c>
       <c r="H45" t="n">
-        <v>125.4059</v>
+        <v>125.3633</v>
       </c>
       <c r="I45" t="n">
-        <v>124.5936</v>
+        <v>124.6552</v>
       </c>
       <c r="J45" t="n">
-        <v>39.8</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.3031</v>
+        <v>-0.2928</v>
       </c>
       <c r="M45" s="10" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3998,22 +3998,22 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>52.86</v>
+        <v>53.03</v>
       </c>
       <c r="H46" t="n">
-        <v>53.9748</v>
+        <v>53.9089</v>
       </c>
       <c r="I46" t="n">
-        <v>53.7652</v>
+        <v>53.7752</v>
       </c>
       <c r="J46" t="n">
-        <v>36.6</v>
+        <v>38</v>
       </c>
       <c r="K46" t="n">
-        <v>13.9</v>
+        <v>14.8</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.1885</v>
+        <v>-0.1904</v>
       </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4064,19 +4064,19 @@
         <v>97.58</v>
       </c>
       <c r="H47" t="n">
-        <v>98.7929</v>
+        <v>98.68170000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>98.2758</v>
+        <v>98.28959999999999</v>
       </c>
       <c r="J47" t="n">
         <v>40.2</v>
       </c>
       <c r="K47" t="n">
-        <v>24.4</v>
+        <v>23.3</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.2311</v>
+        <v>-0.2655</v>
       </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4124,22 +4124,22 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>442</v>
+        <v>443.6</v>
       </c>
       <c r="H48" t="n">
-        <v>448.0021</v>
+        <v>447.7552</v>
       </c>
       <c r="I48" t="n">
-        <v>445.41</v>
+        <v>445.583</v>
       </c>
       <c r="J48" t="n">
-        <v>39.5</v>
+        <v>41.9</v>
       </c>
       <c r="K48" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.117</v>
+        <v>-1.112</v>
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4187,22 +4187,22 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>378.7</v>
+        <v>381.87</v>
       </c>
       <c r="H49" t="n">
-        <v>388.2362</v>
+        <v>387.7652</v>
       </c>
       <c r="I49" t="n">
-        <v>391.1068</v>
+        <v>390.8042</v>
       </c>
       <c r="J49" t="n">
-        <v>31.9</v>
+        <v>37.5</v>
       </c>
       <c r="K49" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.4349</v>
+        <v>-1.2944</v>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4250,22 +4250,22 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6.711</v>
+        <v>6.74</v>
       </c>
       <c r="H50" t="n">
-        <v>6.7912</v>
+        <v>6.7893</v>
       </c>
       <c r="I50" t="n">
-        <v>6.7367</v>
+        <v>6.7403</v>
       </c>
       <c r="J50" t="n">
-        <v>41.2</v>
+        <v>44.2</v>
       </c>
       <c r="K50" t="n">
-        <v>26.1</v>
+        <v>25.4</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.017</v>
+        <v>-0.0165</v>
       </c>
       <c r="M50" s="10" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4313,22 +4313,22 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>30.755</v>
+        <v>30.86</v>
       </c>
       <c r="H51" t="n">
-        <v>31.0531</v>
+        <v>31.039</v>
       </c>
       <c r="I51" t="n">
-        <v>31.0166</v>
+        <v>31.0207</v>
       </c>
       <c r="J51" t="n">
-        <v>42.3</v>
+        <v>45.1</v>
       </c>
       <c r="K51" t="n">
-        <v>20.8</v>
+        <v>19.7</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.0441</v>
+        <v>-0.0459</v>
       </c>
       <c r="M51" s="10" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>42.09</v>
+        <v>42.145</v>
       </c>
       <c r="H52" t="n">
-        <v>42.5106</v>
+        <v>42.4844</v>
       </c>
       <c r="I52" t="n">
-        <v>42.5235</v>
+        <v>42.5221</v>
       </c>
       <c r="J52" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="K52" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.0609</v>
+        <v>-0.0664</v>
       </c>
       <c r="M52" s="10" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4439,22 +4439,22 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>153.4</v>
+        <v>154.68</v>
       </c>
       <c r="H53" t="n">
-        <v>154.3476</v>
+        <v>154.3948</v>
       </c>
       <c r="I53" t="n">
-        <v>154.8852</v>
+        <v>154.9148</v>
       </c>
       <c r="J53" t="n">
-        <v>47.4</v>
+        <v>51</v>
       </c>
       <c r="K53" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.2002</v>
+        <v>-0.1316</v>
       </c>
       <c r="M53" s="10" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4502,22 +4502,22 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>126.64</v>
+        <v>127.46</v>
       </c>
       <c r="H54" t="n">
-        <v>129.6749</v>
+        <v>129.753</v>
       </c>
       <c r="I54" t="n">
-        <v>129.88</v>
+        <v>129.8964</v>
       </c>
       <c r="J54" t="n">
-        <v>36.3</v>
+        <v>38.9</v>
       </c>
       <c r="K54" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="L54" t="n">
-        <v>-0.4234</v>
+        <v>-0.3711</v>
       </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4565,22 +4565,22 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>124.46</v>
+        <v>124.48</v>
       </c>
       <c r="H55" t="n">
-        <v>126.0617</v>
+        <v>125.9301</v>
       </c>
       <c r="I55" t="n">
-        <v>125.2968</v>
+        <v>125.3248</v>
       </c>
       <c r="J55" t="n">
         <v>40.8</v>
       </c>
       <c r="K55" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.2937</v>
+        <v>-0.3442</v>
       </c>
       <c r="M55" s="10" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4628,22 +4628,22 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>105.89</v>
+        <v>107.54</v>
       </c>
       <c r="H56" t="n">
-        <v>108.4671</v>
+        <v>108.5141</v>
       </c>
       <c r="I56" t="n">
-        <v>110.9194</v>
+        <v>110.7284</v>
       </c>
       <c r="J56" t="n">
-        <v>44</v>
+        <v>46.9</v>
       </c>
       <c r="K56" t="n">
         <v>13.3</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.1481</v>
+        <v>-0.0308</v>
       </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4691,22 +4691,22 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>126.68</v>
+        <v>126.96</v>
       </c>
       <c r="H57" t="n">
-        <v>129.7143</v>
+        <v>129.5088</v>
       </c>
       <c r="I57" t="n">
-        <v>129.8876</v>
+        <v>129.8612</v>
       </c>
       <c r="J57" t="n">
-        <v>35.8</v>
+        <v>36.6</v>
       </c>
       <c r="K57" t="n">
-        <v>16.2</v>
+        <v>17.6</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.4261</v>
+        <v>-0.4469</v>
       </c>
       <c r="M57" s="10" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4754,22 +4754,22 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>72.23999999999999</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>73.28230000000001</v>
+        <v>73.2218</v>
       </c>
       <c r="I58" t="n">
-        <v>72.50539999999999</v>
+        <v>72.54559999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>42</v>
+        <v>43.3</v>
       </c>
       <c r="K58" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.2372</v>
+        <v>-0.2459</v>
       </c>
       <c r="M58" s="10" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4817,22 +4817,22 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>42.655</v>
+        <v>42.75</v>
       </c>
       <c r="H59" t="n">
-        <v>43.2776</v>
+        <v>43.2355</v>
       </c>
       <c r="I59" t="n">
-        <v>42.729</v>
+        <v>42.7489</v>
       </c>
       <c r="J59" t="n">
-        <v>42.4</v>
+        <v>43.5</v>
       </c>
       <c r="K59" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.1337</v>
+        <v>-0.1489</v>
       </c>
       <c r="M59" s="10" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4880,22 +4880,22 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>416.85</v>
+        <v>417.45</v>
       </c>
       <c r="H60" t="n">
-        <v>423.1107</v>
+        <v>422.662</v>
       </c>
       <c r="I60" t="n">
-        <v>422.127</v>
+        <v>422.083</v>
       </c>
       <c r="J60" t="n">
-        <v>39.8</v>
+        <v>40.6</v>
       </c>
       <c r="K60" t="n">
-        <v>15.6</v>
+        <v>16.8</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.0089</v>
+        <v>-1.1047</v>
       </c>
       <c r="M60" s="10" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4943,22 +4943,22 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>463</v>
+        <v>464.35</v>
       </c>
       <c r="H61" t="n">
-        <v>466.3336</v>
+        <v>466.2136</v>
       </c>
       <c r="I61" t="n">
-        <v>466.557</v>
+        <v>466.53</v>
       </c>
       <c r="J61" t="n">
-        <v>45.1</v>
+        <v>47.1</v>
       </c>
       <c r="K61" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.5764</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="M61" s="10" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5006,22 +5006,22 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.095</v>
+        <v>5.121</v>
       </c>
       <c r="H62" t="n">
-        <v>5.1262</v>
+        <v>5.1295</v>
       </c>
       <c r="I62" t="n">
-        <v>5.0948</v>
+        <v>5.0981</v>
       </c>
       <c r="J62" t="n">
-        <v>46</v>
+        <v>49.7</v>
       </c>
       <c r="K62" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.0091</v>
+        <v>-0.0062</v>
       </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5069,22 +5069,22 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>214.1</v>
+        <v>214.3</v>
       </c>
       <c r="H63" t="n">
-        <v>217.9835</v>
+        <v>217.6758</v>
       </c>
       <c r="I63" t="n">
-        <v>217.236</v>
+        <v>217.224</v>
       </c>
       <c r="J63" t="n">
-        <v>38.9</v>
+        <v>39.3</v>
       </c>
       <c r="K63" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.5784</v>
+        <v>-0.6783</v>
       </c>
       <c r="M63" s="10" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5132,22 +5132,22 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>91.34</v>
+        <v>91.72</v>
       </c>
       <c r="H64" t="n">
-        <v>92.57259999999999</v>
+        <v>92.54219999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>92.3648</v>
+        <v>92.3716</v>
       </c>
       <c r="J64" t="n">
-        <v>39.9</v>
+        <v>42.4</v>
       </c>
       <c r="K64" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.1542</v>
+        <v>-0.1597</v>
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5195,22 +5195,22 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>42.03</v>
+        <v>41.795</v>
       </c>
       <c r="H65" t="n">
-        <v>42.8181</v>
+        <v>42.7297</v>
       </c>
       <c r="I65" t="n">
-        <v>43.4155</v>
+        <v>43.3969</v>
       </c>
       <c r="J65" t="n">
-        <v>33.1</v>
+        <v>31.6</v>
       </c>
       <c r="K65" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.0794</v>
+        <v>-0.09</v>
       </c>
       <c r="M65" s="10" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5258,22 +5258,22 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>168.11</v>
+        <v>170.01</v>
       </c>
       <c r="H66" t="n">
-        <v>170.1865</v>
+        <v>170.3675</v>
       </c>
       <c r="I66" t="n">
-        <v>173.1734</v>
+        <v>173.2114</v>
       </c>
       <c r="J66" t="n">
-        <v>44</v>
+        <v>47.9</v>
       </c>
       <c r="K66" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0515</v>
+        <v>0.1728</v>
       </c>
       <c r="M66" s="10" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5321,22 +5321,22 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>71.89</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>72.07389999999999</v>
+        <v>72.0202</v>
       </c>
       <c r="I67" t="n">
-        <v>71.79600000000001</v>
+        <v>71.80119999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>48.2</v>
+        <v>42.3</v>
       </c>
       <c r="K67" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.0743</v>
+        <v>-0.1064</v>
       </c>
       <c r="M67" s="10" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5384,22 +5384,22 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>602.5</v>
+        <v>606.48</v>
       </c>
       <c r="H68" t="n">
-        <v>606.8861000000001</v>
+        <v>607.1697</v>
       </c>
       <c r="I68" t="n">
-        <v>603.5388</v>
+        <v>603.7334</v>
       </c>
       <c r="J68" t="n">
-        <v>45.5</v>
+        <v>50.1</v>
       </c>
       <c r="K68" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.869</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="M68" s="10" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5447,22 +5447,22 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>169.985</v>
+        <v>170.135</v>
       </c>
       <c r="H69" t="n">
-        <v>170.6959</v>
+        <v>170.6425</v>
       </c>
       <c r="I69" t="n">
-        <v>171.0366</v>
+        <v>171.0142</v>
       </c>
       <c r="J69" t="n">
-        <v>38</v>
+        <v>40.7</v>
       </c>
       <c r="K69" t="n">
-        <v>13.8</v>
+        <v>15.3</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.0489</v>
+        <v>-0.0584</v>
       </c>
       <c r="M69" s="10" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5510,22 +5510,22 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5.162</v>
+        <v>5.1646</v>
       </c>
       <c r="H70" t="n">
-        <v>5.1915</v>
+        <v>5.1895</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2053</v>
+        <v>5.2041</v>
       </c>
       <c r="J70" t="n">
-        <v>32.3</v>
+        <v>33</v>
       </c>
       <c r="K70" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.0029</v>
+        <v>-0.0031</v>
       </c>
       <c r="M70" s="10" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5573,22 +5573,22 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6.192</v>
+        <v>6.196</v>
       </c>
       <c r="H71" t="n">
-        <v>6.2039</v>
+        <v>6.204</v>
       </c>
       <c r="I71" t="n">
-        <v>6.1593</v>
+        <v>6.1657</v>
       </c>
       <c r="J71" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.0092</v>
+        <v>-0.0075</v>
       </c>
       <c r="M71" s="10" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5636,22 +5636,22 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>149.9</v>
+        <v>150.45</v>
       </c>
       <c r="H72" t="n">
-        <v>151.9817</v>
+        <v>151.9005</v>
       </c>
       <c r="I72" t="n">
-        <v>153.2276</v>
+        <v>153.1302</v>
       </c>
       <c r="J72" t="n">
-        <v>31.1</v>
+        <v>33.8</v>
       </c>
       <c r="K72" t="n">
-        <v>26.8</v>
+        <v>27.8</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.171</v>
+        <v>-0.1455</v>
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5699,22 +5699,22 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>526.3099999999999</v>
+        <v>529.61</v>
       </c>
       <c r="H73" t="n">
-        <v>523.1264</v>
+        <v>523.7103</v>
       </c>
       <c r="I73" t="n">
-        <v>514.6908</v>
+        <v>515.4462</v>
       </c>
       <c r="J73" t="n">
-        <v>55.7</v>
+        <v>58.5</v>
       </c>
       <c r="K73" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="L73" t="n">
-        <v>-0.9077</v>
+        <v>-0.7509</v>
       </c>
       <c r="M73" s="10" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5762,22 +5762,22 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>194.9</v>
+        <v>195.46</v>
       </c>
       <c r="H74" t="n">
-        <v>197.7474</v>
+        <v>197.6123</v>
       </c>
       <c r="I74" t="n">
-        <v>199.6606</v>
+        <v>199.5082</v>
       </c>
       <c r="J74" t="n">
-        <v>29.7</v>
+        <v>31.6</v>
       </c>
       <c r="K74" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="L74" t="n">
-        <v>-0.2038</v>
+        <v>-0.183</v>
       </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5825,22 +5825,22 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>4.9232</v>
+        <v>4.9045</v>
       </c>
       <c r="H75" t="n">
-        <v>4.9403</v>
+        <v>4.938</v>
       </c>
       <c r="I75" t="n">
-        <v>4.9457</v>
+        <v>4.9449</v>
       </c>
       <c r="J75" t="n">
-        <v>43.5</v>
+        <v>38.1</v>
       </c>
       <c r="K75" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="L75" t="n">
-        <v>-0.0012</v>
+        <v>-0.0026</v>
       </c>
       <c r="M75" s="10" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5888,22 +5888,22 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>126.04</v>
+        <v>126.81</v>
       </c>
       <c r="H76" t="n">
-        <v>126.9756</v>
+        <v>127.0063</v>
       </c>
       <c r="I76" t="n">
-        <v>126.2408</v>
+        <v>126.293</v>
       </c>
       <c r="J76" t="n">
-        <v>45.2</v>
+        <v>49.7</v>
       </c>
       <c r="K76" t="n">
-        <v>14.1</v>
+        <v>12.9</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.2163</v>
+        <v>-0.1733</v>
       </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5951,22 +5951,22 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>226.1</v>
+        <v>226.66</v>
       </c>
       <c r="H77" t="n">
-        <v>227.6776</v>
+        <v>227.6057</v>
       </c>
       <c r="I77" t="n">
-        <v>228.3032</v>
+        <v>228.2508</v>
       </c>
       <c r="J77" t="n">
-        <v>30.8</v>
+        <v>36.9</v>
       </c>
       <c r="K77" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.1595</v>
+        <v>-0.1464</v>
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6014,22 +6014,22 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>13.984</v>
+        <v>14.186</v>
       </c>
       <c r="H78" t="n">
-        <v>14.1417</v>
+        <v>14.1637</v>
       </c>
       <c r="I78" t="n">
-        <v>13.8796</v>
+        <v>13.8975</v>
       </c>
       <c r="J78" t="n">
-        <v>44</v>
+        <v>55.7</v>
       </c>
       <c r="K78" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.0355</v>
+        <v>-0.0261</v>
       </c>
       <c r="M78" s="10" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6077,22 +6077,22 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>266.1</v>
+        <v>267.1</v>
       </c>
       <c r="H79" t="n">
-        <v>267.7658</v>
+        <v>267.7584</v>
       </c>
       <c r="I79" t="n">
-        <v>264.718</v>
+        <v>264.884</v>
       </c>
       <c r="J79" t="n">
-        <v>46.6</v>
+        <v>49.6</v>
       </c>
       <c r="K79" t="n">
-        <v>16.3</v>
+        <v>15.2</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.5098</v>
+        <v>-0.5051</v>
       </c>
       <c r="M79" s="10" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6140,22 +6140,22 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>53.8</v>
+        <v>53.84</v>
       </c>
       <c r="H80" t="n">
-        <v>54.1555</v>
+        <v>54.1315</v>
       </c>
       <c r="I80" t="n">
-        <v>54.3072</v>
+        <v>54.2928</v>
       </c>
       <c r="J80" t="n">
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="K80" t="n">
-        <v>20.1</v>
+        <v>21.3</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.0373</v>
+        <v>-0.039</v>
       </c>
       <c r="M80" s="10" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6203,22 +6203,22 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>265.7</v>
+        <v>266.1</v>
       </c>
       <c r="H81" t="n">
-        <v>273.4548</v>
+        <v>273.1033</v>
       </c>
       <c r="I81" t="n">
-        <v>275.948</v>
+        <v>275.62</v>
       </c>
       <c r="J81" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="K81" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="L81" t="n">
-        <v>-0.6264</v>
+        <v>-0.61</v>
       </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6266,22 +6266,22 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>150.01</v>
+        <v>150.425</v>
       </c>
       <c r="H82" t="n">
-        <v>151.7365</v>
+        <v>151.6702</v>
       </c>
       <c r="I82" t="n">
-        <v>152.7714</v>
+        <v>152.6904</v>
       </c>
       <c r="J82" t="n">
-        <v>30.4</v>
+        <v>32.9</v>
       </c>
       <c r="K82" t="n">
-        <v>26.7</v>
+        <v>27.1</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.1287</v>
+        <v>-0.1119</v>
       </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6329,22 +6329,22 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>229</v>
+        <v>229.65</v>
       </c>
       <c r="H83" t="n">
-        <v>231.1344</v>
+        <v>231.0585</v>
       </c>
       <c r="I83" t="n">
-        <v>232.4256</v>
+        <v>232.3216</v>
       </c>
       <c r="J83" t="n">
-        <v>28.9</v>
+        <v>32.3</v>
       </c>
       <c r="K83" t="n">
-        <v>19</v>
+        <v>20.3</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.1652</v>
+        <v>-0.1371</v>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6392,22 +6392,22 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>136.29</v>
+        <v>135.99</v>
       </c>
       <c r="H84" t="n">
-        <v>136.8266</v>
+        <v>136.7469</v>
       </c>
       <c r="I84" t="n">
-        <v>137.1982</v>
+        <v>137.1614</v>
       </c>
       <c r="J84" t="n">
-        <v>36.3</v>
+        <v>31.9</v>
       </c>
       <c r="K84" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.0396</v>
+        <v>-0.0707</v>
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6455,22 +6455,22 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>45.015</v>
+        <v>45.115</v>
       </c>
       <c r="H85" t="n">
-        <v>45.381</v>
+        <v>45.3668</v>
       </c>
       <c r="I85" t="n">
-        <v>45.5929</v>
+        <v>45.5762</v>
       </c>
       <c r="J85" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K85" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.0297</v>
+        <v>-0.0256</v>
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6518,22 +6518,22 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>231.75</v>
+        <v>232.24</v>
       </c>
       <c r="H86" t="n">
-        <v>233.8199</v>
+        <v>233.7513</v>
       </c>
       <c r="I86" t="n">
-        <v>234.9052</v>
+        <v>234.821</v>
       </c>
       <c r="J86" t="n">
-        <v>30.5</v>
+        <v>32.9</v>
       </c>
       <c r="K86" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.1624</v>
+        <v>-0.1427</v>
       </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6581,22 +6581,22 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>685.3200000000001</v>
+        <v>689.5599999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>690.6161</v>
+        <v>690.7818</v>
       </c>
       <c r="I87" t="n">
-        <v>686.9068</v>
+        <v>687.1748</v>
       </c>
       <c r="J87" t="n">
-        <v>45</v>
+        <v>49.4</v>
       </c>
       <c r="K87" t="n">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="L87" t="n">
-        <v>-1.1816</v>
+        <v>-0.9376</v>
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6644,22 +6644,22 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>424.35</v>
+        <v>426.86</v>
       </c>
       <c r="H88" t="n">
-        <v>427.6995</v>
+        <v>427.791</v>
       </c>
       <c r="I88" t="n">
-        <v>425.2908</v>
+        <v>425.4596</v>
       </c>
       <c r="J88" t="n">
-        <v>44.7</v>
+        <v>49.1</v>
       </c>
       <c r="K88" t="n">
-        <v>15</v>
+        <v>13.7</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.7415</v>
+        <v>-0.6018</v>
       </c>
       <c r="M88" s="10" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6707,22 +6707,22 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>266.71</v>
+        <v>266.31</v>
       </c>
       <c r="H89" t="n">
-        <v>267.7491</v>
+        <v>267.6551</v>
       </c>
       <c r="I89" t="n">
-        <v>267.7654</v>
+        <v>267.7444</v>
       </c>
       <c r="J89" t="n">
-        <v>36.3</v>
+        <v>32.5</v>
       </c>
       <c r="K89" t="n">
-        <v>14.9</v>
+        <v>16.5</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.1295</v>
+        <v>-0.1749</v>
       </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6770,22 +6770,22 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>41</v>
+        <v>41.061</v>
       </c>
       <c r="H90" t="n">
-        <v>41.3578</v>
+        <v>41.3408</v>
       </c>
       <c r="I90" t="n">
-        <v>41.5956</v>
+        <v>41.5762</v>
       </c>
       <c r="J90" t="n">
-        <v>30.9</v>
+        <v>32.5</v>
       </c>
       <c r="K90" t="n">
-        <v>26.3</v>
+        <v>26.8</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.0264</v>
+        <v>-0.0241</v>
       </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6833,22 +6833,22 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>7.2108</v>
+        <v>7.2324</v>
       </c>
       <c r="H91" t="n">
-        <v>7.3069</v>
+        <v>7.3026</v>
       </c>
       <c r="I91" t="n">
-        <v>7.3782</v>
+        <v>7.3726</v>
       </c>
       <c r="J91" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="K91" t="n">
         <v>30.5</v>
       </c>
-      <c r="K91" t="n">
-        <v>29.9</v>
-      </c>
       <c r="L91" t="n">
-        <v>-0.0062</v>
+        <v>-0.0052</v>
       </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6896,22 +6896,22 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>18.806</v>
+        <v>18.914</v>
       </c>
       <c r="H92" t="n">
-        <v>18.9437</v>
+        <v>18.9473</v>
       </c>
       <c r="I92" t="n">
-        <v>18.8354</v>
+        <v>18.8428</v>
       </c>
       <c r="J92" t="n">
-        <v>45.2</v>
+        <v>49.5</v>
       </c>
       <c r="K92" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.0324</v>
+        <v>-0.0265</v>
       </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6959,22 +6959,22 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>216.7</v>
+        <v>217.32</v>
       </c>
       <c r="H93" t="n">
-        <v>218.8991</v>
+        <v>218.8478</v>
       </c>
       <c r="I93" t="n">
-        <v>220.206</v>
+        <v>220.1126</v>
       </c>
       <c r="J93" t="n">
-        <v>31.2</v>
+        <v>34.4</v>
       </c>
       <c r="K93" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="L93" t="n">
-        <v>-0.1549</v>
+        <v>-0.1189</v>
       </c>
       <c r="M93" s="10" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7022,22 +7022,22 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>48.35</v>
+        <v>48.385</v>
       </c>
       <c r="H94" t="n">
-        <v>48.7378</v>
+        <v>48.7133</v>
       </c>
       <c r="I94" t="n">
-        <v>49.036</v>
+        <v>49.0128</v>
       </c>
       <c r="J94" t="n">
-        <v>34.1</v>
+        <v>34.8</v>
       </c>
       <c r="K94" t="n">
-        <v>24.4</v>
+        <v>25.4</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.0292</v>
+        <v>-0.0281</v>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7085,22 +7085,22 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>54.97</v>
+        <v>54.98</v>
       </c>
       <c r="H95" t="n">
-        <v>55.1938</v>
+        <v>55.1821</v>
       </c>
       <c r="I95" t="n">
-        <v>55.2516</v>
+        <v>55.246</v>
       </c>
       <c r="J95" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="K95" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.0274</v>
+        <v>-0.0279</v>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7148,22 +7148,22 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>135.69</v>
+        <v>136.13</v>
       </c>
       <c r="H96" t="n">
-        <v>136.8191</v>
+        <v>136.7966</v>
       </c>
       <c r="I96" t="n">
-        <v>137.2798</v>
+        <v>137.2466</v>
       </c>
       <c r="J96" t="n">
-        <v>29.2</v>
+        <v>33.9</v>
       </c>
       <c r="K96" t="n">
-        <v>14.6</v>
+        <v>15.2</v>
       </c>
       <c r="L96" t="n">
-        <v>-0.1072</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7223,7 +7223,7 @@
         <v>46.9</v>
       </c>
       <c r="K97" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="L97" t="n">
         <v>-0.004</v>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="9" t="n">
         <v>3</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -7274,22 +7274,22 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>24.17</v>
+        <v>24.52</v>
       </c>
       <c r="H98" t="n">
-        <v>24.4766</v>
+        <v>24.52</v>
       </c>
       <c r="I98" t="n">
-        <v>24.609</v>
+        <v>24.5852</v>
       </c>
       <c r="J98" t="n">
-        <v>45.6</v>
+        <v>50</v>
       </c>
       <c r="K98" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="L98" t="n">
-        <v>-0.0111</v>
+        <v>0.0106</v>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7337,22 +7337,22 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>193.99</v>
+        <v>195.34</v>
       </c>
       <c r="H99" t="n">
-        <v>195.6532</v>
+        <v>195.6975</v>
       </c>
       <c r="I99" t="n">
-        <v>193.9348</v>
+        <v>194.0084</v>
       </c>
       <c r="J99" t="n">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="K99" t="n">
-        <v>17.3</v>
+        <v>16.5</v>
       </c>
       <c r="L99" t="n">
-        <v>-0.401</v>
+        <v>-0.3479</v>
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7400,22 +7400,22 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>48.64</v>
+        <v>48.76</v>
       </c>
       <c r="H100" t="n">
-        <v>49.1172</v>
+        <v>49.1</v>
       </c>
       <c r="I100" t="n">
-        <v>49.4052</v>
+        <v>49.3829</v>
       </c>
       <c r="J100" t="n">
-        <v>28.7</v>
+        <v>31.3</v>
       </c>
       <c r="K100" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="L100" t="n">
-        <v>-0.0346</v>
+        <v>-0.0295</v>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7463,22 +7463,22 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>130.225</v>
+        <v>130.285</v>
       </c>
       <c r="H101" t="n">
-        <v>130.8974</v>
+        <v>130.8589</v>
       </c>
       <c r="I101" t="n">
-        <v>131.2179</v>
+        <v>131.1885</v>
       </c>
       <c r="J101" t="n">
-        <v>32.8</v>
+        <v>33.5</v>
       </c>
       <c r="K101" t="n">
-        <v>19.6</v>
+        <v>20.3</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.0592</v>
+        <v>-0.0622</v>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7526,22 +7526,22 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>7.173</v>
+        <v>7.207</v>
       </c>
       <c r="H102" t="n">
-        <v>7.2275</v>
+        <v>7.2307</v>
       </c>
       <c r="I102" t="n">
-        <v>7.135</v>
+        <v>7.1356</v>
       </c>
       <c r="J102" t="n">
-        <v>45.6</v>
+        <v>49.3</v>
       </c>
       <c r="K102" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="L102" t="n">
-        <v>-0.0158</v>
+        <v>-0.0136</v>
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7589,22 +7589,22 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>136.895</v>
+        <v>137.185</v>
       </c>
       <c r="H103" t="n">
-        <v>139.4055</v>
+        <v>139.2617</v>
       </c>
       <c r="I103" t="n">
-        <v>141.5846</v>
+        <v>141.4093</v>
       </c>
       <c r="J103" t="n">
-        <v>32.2</v>
+        <v>33.4</v>
       </c>
       <c r="K103" t="n">
-        <v>30.3</v>
+        <v>30.7</v>
       </c>
       <c r="L103" t="n">
-        <v>-0.1419</v>
+        <v>-0.1265</v>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7652,22 +7652,22 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>104.48</v>
+        <v>104.58</v>
       </c>
       <c r="H104" t="n">
-        <v>104.7084</v>
+        <v>104.7091</v>
       </c>
       <c r="I104" t="n">
-        <v>104.7478</v>
+        <v>104.7448</v>
       </c>
       <c r="J104" t="n">
-        <v>36.9</v>
+        <v>41.1</v>
       </c>
       <c r="K104" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="L104" t="n">
-        <v>-0.0253</v>
+        <v>-0.0205</v>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>106.6</v>
+        <v>106.66</v>
       </c>
       <c r="H105" t="n">
-        <v>107.2921</v>
+        <v>107.2965</v>
       </c>
       <c r="I105" t="n">
-        <v>107.52</v>
+        <v>107.5082</v>
       </c>
       <c r="J105" t="n">
         <v>2.8</v>
@@ -7730,7 +7730,7 @@
         <v>38.4</v>
       </c>
       <c r="L105" t="n">
-        <v>-0.038</v>
+        <v>-0.0347</v>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7778,22 +7778,22 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>199.98</v>
+        <v>200.09</v>
       </c>
       <c r="H106" t="n">
-        <v>201.6973</v>
+        <v>201.5899</v>
       </c>
       <c r="I106" t="n">
-        <v>202.9668</v>
+        <v>202.8602</v>
       </c>
       <c r="J106" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="K106" t="n">
-        <v>27.2</v>
+        <v>28.2</v>
       </c>
       <c r="L106" t="n">
-        <v>-0.1185</v>
+        <v>-0.1178</v>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7812,8 +7812,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
-        <v>3</v>
+      <c r="A107" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -7841,31 +7841,31 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>113.1</v>
+        <v>113.18</v>
       </c>
       <c r="H107" t="n">
-        <v>112.9838</v>
+        <v>113.0016</v>
       </c>
       <c r="I107" t="n">
-        <v>112.8016</v>
+        <v>112.815</v>
       </c>
       <c r="J107" t="n">
-        <v>60.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K107" t="n">
-        <v>77.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="L107" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M107" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0048</v>
+      </c>
+      <c r="M107" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7904,22 +7904,22 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>5.0686</v>
+        <v>5.073</v>
       </c>
       <c r="H108" t="n">
-        <v>5.0646</v>
+        <v>5.0656</v>
       </c>
       <c r="I108" t="n">
-        <v>5.0565</v>
+        <v>5.0571</v>
       </c>
       <c r="J108" t="n">
-        <v>63.1</v>
+        <v>69</v>
       </c>
       <c r="K108" t="n">
-        <v>14</v>
+        <v>10.8</v>
       </c>
       <c r="L108" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7967,22 +7967,22 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>74.98</v>
+        <v>75.04600000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>75.1865</v>
+        <v>75.184</v>
       </c>
       <c r="I109" t="n">
-        <v>75.0544</v>
+        <v>75.0574</v>
       </c>
       <c r="J109" t="n">
-        <v>45.2</v>
+        <v>46.7</v>
       </c>
       <c r="K109" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="L109" t="n">
-        <v>-0.0142</v>
+        <v>-0.023</v>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8030,22 +8030,22 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>118.87</v>
+        <v>118.9</v>
       </c>
       <c r="H110" t="n">
-        <v>119.0988</v>
+        <v>119.0894</v>
       </c>
       <c r="I110" t="n">
-        <v>119.129</v>
+        <v>119.1234</v>
       </c>
       <c r="J110" t="n">
-        <v>36.3</v>
+        <v>37.3</v>
       </c>
       <c r="K110" t="n">
         <v>12.3</v>
       </c>
       <c r="L110" t="n">
-        <v>-0.0236</v>
+        <v>-0.0263</v>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8093,22 +8093,22 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>107.09</v>
+        <v>107.89</v>
       </c>
       <c r="H111" t="n">
-        <v>107.0585</v>
+        <v>107.2083</v>
       </c>
       <c r="I111" t="n">
-        <v>106.0506</v>
+        <v>106.1442</v>
       </c>
       <c r="J111" t="n">
-        <v>51.2</v>
+        <v>55.1</v>
       </c>
       <c r="K111" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="L111" t="n">
-        <v>-0.0808</v>
+        <v>-0.0098</v>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8156,22 +8156,22 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>127.71</v>
+        <v>127.79</v>
       </c>
       <c r="H112" t="n">
-        <v>127.943</v>
+        <v>127.9371</v>
       </c>
       <c r="I112" t="n">
-        <v>127.983</v>
+        <v>127.9776</v>
       </c>
       <c r="J112" t="n">
-        <v>37.9</v>
+        <v>41</v>
       </c>
       <c r="K112" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="L112" t="n">
-        <v>-0.0251</v>
+        <v>-0.0239</v>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8219,22 +8219,22 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>101.35</v>
+        <v>101.42</v>
       </c>
       <c r="H113" t="n">
-        <v>101.5262</v>
+        <v>101.5256</v>
       </c>
       <c r="I113" t="n">
-        <v>101.5866</v>
+        <v>101.5868</v>
       </c>
       <c r="J113" t="n">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="K113" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="L113" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8294,7 +8294,7 @@
         <v>42.2</v>
       </c>
       <c r="K114" t="n">
-        <v>20.7</v>
+        <v>14.6</v>
       </c>
       <c r="L114" t="n">
         <v>-0.0252</v>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8345,22 +8345,22 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>54.42</v>
+        <v>54.404</v>
       </c>
       <c r="H115" t="n">
-        <v>54.4609</v>
+        <v>54.4552</v>
       </c>
       <c r="I115" t="n">
-        <v>54.4382</v>
+        <v>54.4377</v>
       </c>
       <c r="J115" t="n">
-        <v>44.7</v>
+        <v>42.5</v>
       </c>
       <c r="K115" t="n">
-        <v>17.2</v>
+        <v>15.9</v>
       </c>
       <c r="L115" t="n">
-        <v>-0.0072</v>
+        <v>-0.0105</v>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8408,22 +8408,22 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>84.3</v>
+        <v>84.86</v>
       </c>
       <c r="H116" t="n">
-        <v>84.6592</v>
+        <v>84.67829999999999</v>
       </c>
       <c r="I116" t="n">
-        <v>85.3116</v>
+        <v>85.29219999999999</v>
       </c>
       <c r="J116" t="n">
-        <v>32.2</v>
+        <v>52.5</v>
       </c>
       <c r="K116" t="n">
-        <v>44.4</v>
+        <v>41.8</v>
       </c>
       <c r="L116" t="n">
-        <v>-0.0386</v>
+        <v>0.0103</v>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8471,22 +8471,22 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>407.5</v>
+        <v>410.81</v>
       </c>
       <c r="H117" t="n">
-        <v>408.906</v>
+        <v>409.1847</v>
       </c>
       <c r="I117" t="n">
-        <v>405.1512</v>
+        <v>405.6088</v>
       </c>
       <c r="J117" t="n">
-        <v>49.1</v>
+        <v>54.8</v>
       </c>
       <c r="K117" t="n">
-        <v>24.1</v>
+        <v>23.5</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.6885</v>
+        <v>-0.457</v>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -8534,22 +8534,22 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>41.795</v>
+        <v>41.9</v>
       </c>
       <c r="H118" t="n">
-        <v>42.851</v>
+        <v>42.785</v>
       </c>
       <c r="I118" t="n">
-        <v>42.8663</v>
+        <v>42.8611</v>
       </c>
       <c r="J118" t="n">
-        <v>33.9</v>
+        <v>34.8</v>
       </c>
       <c r="K118" t="n">
-        <v>26.7</v>
+        <v>28.5</v>
       </c>
       <c r="L118" t="n">
-        <v>-0.1975</v>
+        <v>-0.1834</v>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -8597,22 +8597,22 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>624.5</v>
+        <v>628.2</v>
       </c>
       <c r="H119" t="n">
-        <v>629.0497</v>
+        <v>629.2101</v>
       </c>
       <c r="I119" t="n">
-        <v>625.386</v>
+        <v>625.65</v>
       </c>
       <c r="J119" t="n">
-        <v>45.5</v>
+        <v>49.7</v>
       </c>
       <c r="K119" t="n">
-        <v>15.9</v>
+        <v>14.5</v>
       </c>
       <c r="L119" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.799</v>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8660,22 +8660,22 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>138.72</v>
+        <v>138.85</v>
       </c>
       <c r="H120" t="n">
-        <v>138.5688</v>
+        <v>138.6636</v>
       </c>
       <c r="I120" t="n">
-        <v>138.2428</v>
+        <v>138.2826</v>
       </c>
       <c r="J120" t="n">
-        <v>57.6</v>
+        <v>55.6</v>
       </c>
       <c r="K120" t="n">
-        <v>23.9</v>
+        <v>26.4</v>
       </c>
       <c r="L120" t="n">
-        <v>-0.0001</v>
+        <v>0.032</v>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>15.59710025787354</v>
+        <v>15.59780025482178</v>
       </c>
       <c r="H121" t="n">
         <v>15.4142</v>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>127.1399993896484</v>
+        <v>127.1699981689453</v>
       </c>
       <c r="H122" t="n">
         <v>126.4026</v>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>114.370002746582</v>
+        <v>114.379997253418</v>
       </c>
       <c r="H123" t="n">
         <v>113.6715</v>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -8912,22 +8912,22 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>20.665</v>
+        <v>20.805</v>
       </c>
       <c r="H124" t="n">
-        <v>20.8711</v>
+        <v>20.8829</v>
       </c>
       <c r="I124" t="n">
-        <v>20.5354</v>
+        <v>20.5568</v>
       </c>
       <c r="J124" t="n">
-        <v>45.1</v>
+        <v>49</v>
       </c>
       <c r="K124" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="L124" t="n">
-        <v>-0.0533</v>
+        <v>-0.0436</v>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -8975,22 +8975,22 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>48.51</v>
+        <v>48.615</v>
       </c>
       <c r="H125" t="n">
-        <v>48.7141</v>
+        <v>48.7094</v>
       </c>
       <c r="I125" t="n">
-        <v>49.0254</v>
+        <v>49.0068</v>
       </c>
       <c r="J125" t="n">
-        <v>37</v>
+        <v>42.1</v>
       </c>
       <c r="K125" t="n">
-        <v>22.1</v>
+        <v>21.4</v>
       </c>
       <c r="L125" t="n">
-        <v>0.0001</v>
+        <v>0.0073</v>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -9038,22 +9038,22 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>63.25</v>
+        <v>63.37</v>
       </c>
       <c r="H126" t="n">
-        <v>63.5267</v>
+        <v>63.5548</v>
       </c>
       <c r="I126" t="n">
-        <v>63.2264</v>
+        <v>63.2466</v>
       </c>
       <c r="J126" t="n">
-        <v>41.7</v>
+        <v>44.6</v>
       </c>
       <c r="K126" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="L126" t="n">
-        <v>-0.0278</v>
+        <v>-0.0254</v>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -9101,22 +9101,22 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>234.25</v>
+        <v>235.35</v>
       </c>
       <c r="H127" t="n">
-        <v>237.2978</v>
+        <v>237.1856</v>
       </c>
       <c r="I127" t="n">
-        <v>233.331</v>
+        <v>233.503</v>
       </c>
       <c r="J127" t="n">
-        <v>43.6</v>
+        <v>46.4</v>
       </c>
       <c r="K127" t="n">
-        <v>23.9</v>
+        <v>22.6</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.7178</v>
+        <v>-0.7625</v>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -9164,22 +9164,22 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>331.85</v>
+        <v>330.35</v>
       </c>
       <c r="H128" t="n">
-        <v>340.0864</v>
+        <v>339.1591</v>
       </c>
       <c r="I128" t="n">
-        <v>341.376</v>
+        <v>341.435</v>
       </c>
       <c r="J128" t="n">
-        <v>29.2</v>
+        <v>27.2</v>
       </c>
       <c r="K128" t="n">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="L128" t="n">
-        <v>-0.9401</v>
+        <v>-1.188</v>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -9227,22 +9227,22 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>42.785</v>
+        <v>43.04</v>
       </c>
       <c r="H129" t="n">
-        <v>41.8474</v>
+        <v>41.8717</v>
       </c>
       <c r="I129" t="n">
-        <v>40.1361</v>
+        <v>40.1412</v>
       </c>
       <c r="J129" t="n">
-        <v>65.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="K129" t="n">
         <v>28.2</v>
       </c>
       <c r="L129" t="n">
-        <v>0.0167</v>
+        <v>0.0329</v>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -9290,22 +9290,22 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>10.354</v>
+        <v>10.35</v>
       </c>
       <c r="H130" t="n">
-        <v>10.3617</v>
+        <v>10.3606</v>
       </c>
       <c r="I130" t="n">
-        <v>10.4229</v>
+        <v>10.4206</v>
       </c>
       <c r="J130" t="n">
-        <v>47.2</v>
+        <v>46.6</v>
       </c>
       <c r="K130" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="L130" t="n">
-        <v>0.0017</v>
+        <v>0.0026</v>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -9353,22 +9353,22 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>65.09</v>
+        <v>65.38</v>
       </c>
       <c r="H131" t="n">
-        <v>65.47969999999999</v>
+        <v>65.5073</v>
       </c>
       <c r="I131" t="n">
-        <v>65.6352</v>
+        <v>65.64100000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>39.5</v>
+        <v>45.8</v>
       </c>
       <c r="K131" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="L131" t="n">
-        <v>-0.0165</v>
+        <v>0.002</v>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -9416,22 +9416,22 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>154.7</v>
+        <v>154.81</v>
       </c>
       <c r="H132" t="n">
-        <v>155.4186</v>
+        <v>155.3831</v>
       </c>
       <c r="I132" t="n">
-        <v>155.5716</v>
+        <v>155.5402</v>
       </c>
       <c r="J132" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="K132" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="L132" t="n">
-        <v>0.0072</v>
+        <v>-0.0285</v>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -9479,22 +9479,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>7.246</v>
+        <v>7.219</v>
       </c>
       <c r="H133" t="n">
-        <v>7.247</v>
+        <v>7.2443</v>
       </c>
       <c r="I133" t="n">
-        <v>7.1346</v>
+        <v>7.1381</v>
       </c>
       <c r="J133" t="n">
-        <v>52.3</v>
+        <v>49.5</v>
       </c>
       <c r="K133" t="n">
-        <v>18.7</v>
+        <v>17.5</v>
       </c>
       <c r="L133" t="n">
-        <v>-0.0109</v>
+        <v>-0.0143</v>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -9542,22 +9542,22 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>145.335</v>
+        <v>145.43</v>
       </c>
       <c r="H134" t="n">
-        <v>146.2156</v>
+        <v>146.1636</v>
       </c>
       <c r="I134" t="n">
-        <v>147.8598</v>
+        <v>147.7544</v>
       </c>
       <c r="J134" t="n">
-        <v>36.9</v>
+        <v>38.5</v>
       </c>
       <c r="K134" t="n">
         <v>24.3</v>
       </c>
       <c r="L134" t="n">
-        <v>0.0215</v>
+        <v>0.0351</v>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -9605,22 +9605,22 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>179.5</v>
+        <v>180.82</v>
       </c>
       <c r="H135" t="n">
-        <v>180.9149</v>
+        <v>180.986</v>
       </c>
       <c r="I135" t="n">
-        <v>178.7356</v>
+        <v>178.8666</v>
       </c>
       <c r="J135" t="n">
-        <v>45.8</v>
+        <v>51</v>
       </c>
       <c r="K135" t="n">
-        <v>18.7</v>
+        <v>17.4</v>
       </c>
       <c r="L135" t="n">
-        <v>-0.3696</v>
+        <v>-0.3224</v>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -9668,22 +9668,22 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>69.51000000000001</v>
+        <v>69.59</v>
       </c>
       <c r="H136" t="n">
-        <v>69.7435</v>
+        <v>69.7289</v>
       </c>
       <c r="I136" t="n">
-        <v>70.4744</v>
+        <v>70.43680000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>40.9</v>
+        <v>43.3</v>
       </c>
       <c r="K136" t="n">
-        <v>22.8</v>
+        <v>22</v>
       </c>
       <c r="L136" t="n">
-        <v>0.0185</v>
+        <v>0.0301</v>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -9731,22 +9731,22 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>131.43</v>
+        <v>132.12</v>
       </c>
       <c r="H137" t="n">
-        <v>132.2418</v>
+        <v>132.2751</v>
       </c>
       <c r="I137" t="n">
-        <v>131.629</v>
+        <v>131.6736</v>
       </c>
       <c r="J137" t="n">
-        <v>46.4</v>
+        <v>49.8</v>
       </c>
       <c r="K137" t="n">
-        <v>14.7</v>
+        <v>14</v>
       </c>
       <c r="L137" t="n">
-        <v>-0.1904</v>
+        <v>-0.1469</v>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -9794,22 +9794,22 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>72.65000000000001</v>
+        <v>72.67</v>
       </c>
       <c r="H138" t="n">
-        <v>72.9362</v>
+        <v>72.9255</v>
       </c>
       <c r="I138" t="n">
-        <v>73.2586</v>
+        <v>73.2274</v>
       </c>
       <c r="J138" t="n">
-        <v>38.5</v>
+        <v>39.9</v>
       </c>
       <c r="K138" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0133</v>
+        <v>0.0067</v>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -9857,22 +9857,22 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18.381</v>
+        <v>18.403</v>
       </c>
       <c r="H139" t="n">
-        <v>18.477</v>
+        <v>18.4737</v>
       </c>
       <c r="I139" t="n">
-        <v>18.7189</v>
+        <v>18.7025</v>
       </c>
       <c r="J139" t="n">
-        <v>39.6</v>
+        <v>41.3</v>
       </c>
       <c r="K139" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="L139" t="n">
-        <v>0.0136</v>
+        <v>0.0151</v>
       </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -9920,22 +9920,22 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>45.83</v>
+        <v>46.08</v>
       </c>
       <c r="H140" t="n">
-        <v>46.174</v>
+        <v>46.175</v>
       </c>
       <c r="I140" t="n">
-        <v>46.3532</v>
+        <v>46.3394</v>
       </c>
       <c r="J140" t="n">
-        <v>32.4</v>
+        <v>43.8</v>
       </c>
       <c r="K140" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="L140" t="n">
-        <v>-0.0235</v>
+        <v>-0.0126</v>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9983,22 +9983,22 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>80.56</v>
+        <v>80.8</v>
       </c>
       <c r="H141" t="n">
-        <v>80.8877</v>
+        <v>80.8793</v>
       </c>
       <c r="I141" t="n">
-        <v>81.8558</v>
+        <v>81.8058</v>
       </c>
       <c r="J141" t="n">
-        <v>40</v>
+        <v>45.4</v>
       </c>
       <c r="K141" t="n">
-        <v>20.6</v>
+        <v>19.4</v>
       </c>
       <c r="L141" t="n">
-        <v>0.0393</v>
+        <v>0.0584</v>
       </c>
       <c r="M141" s="10" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -10046,22 +10046,22 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>44.48</v>
+        <v>44.635</v>
       </c>
       <c r="H142" t="n">
-        <v>44.7331</v>
+        <v>44.7277</v>
       </c>
       <c r="I142" t="n">
-        <v>45.0791</v>
+        <v>45.0566</v>
       </c>
       <c r="J142" t="n">
-        <v>31.9</v>
+        <v>41.2</v>
       </c>
       <c r="K142" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
       <c r="L142" t="n">
-        <v>-0.0111</v>
+        <v>0.0012</v>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -10109,22 +10109,22 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>8.664</v>
+        <v>8.666</v>
       </c>
       <c r="H143" t="n">
-        <v>8.695399999999999</v>
+        <v>8.692600000000001</v>
       </c>
       <c r="I143" t="n">
-        <v>8.8011</v>
+        <v>8.7956</v>
       </c>
       <c r="J143" t="n">
-        <v>37.6</v>
+        <v>38.2</v>
       </c>
       <c r="K143" t="n">
-        <v>31.2</v>
+        <v>30.4</v>
       </c>
       <c r="L143" t="n">
-        <v>0.0051</v>
+        <v>0.0057</v>
       </c>
       <c r="M143" s="10" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -10172,22 +10172,22 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>91.98</v>
+        <v>89.77</v>
       </c>
       <c r="H144" t="n">
-        <v>91.31319999999999</v>
+        <v>91.1065</v>
       </c>
       <c r="I144" t="n">
-        <v>89.02460000000001</v>
+        <v>89.173</v>
       </c>
       <c r="J144" t="n">
-        <v>57.1</v>
+        <v>45</v>
       </c>
       <c r="K144" t="n">
-        <v>32.5</v>
+        <v>28.6</v>
       </c>
       <c r="L144" t="n">
-        <v>-0.0508</v>
+        <v>-0.3385</v>
       </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -10235,22 +10235,22 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>122.1</v>
+        <v>121.3</v>
       </c>
       <c r="H145" t="n">
-        <v>123.2795</v>
+        <v>123.0781</v>
       </c>
       <c r="I145" t="n">
-        <v>121.3915</v>
+        <v>121.4209</v>
       </c>
       <c r="J145" t="n">
-        <v>46.9</v>
+        <v>44</v>
       </c>
       <c r="K145" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L145" t="n">
-        <v>-0.237</v>
+        <v>-0.4002</v>
       </c>
       <c r="M145" s="10" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -10298,22 +10298,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>114.96</v>
+        <v>115.72</v>
       </c>
       <c r="H146" t="n">
-        <v>117.8749</v>
+        <v>117.7196</v>
       </c>
       <c r="I146" t="n">
-        <v>116.944</v>
+        <v>116.9164</v>
       </c>
       <c r="J146" t="n">
-        <v>41.6</v>
+        <v>43.7</v>
       </c>
       <c r="K146" t="n">
-        <v>18.7</v>
+        <v>17.8</v>
       </c>
       <c r="L146" t="n">
-        <v>-0.4193</v>
+        <v>-0.4655</v>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -10361,22 +10361,22 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>23.255</v>
+        <v>23.02</v>
       </c>
       <c r="H147" t="n">
-        <v>23.6691</v>
+        <v>23.6163</v>
       </c>
       <c r="I147" t="n">
-        <v>23.4081</v>
+        <v>23.4232</v>
       </c>
       <c r="J147" t="n">
-        <v>42.1</v>
+        <v>38.6</v>
       </c>
       <c r="K147" t="n">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
       <c r="L147" t="n">
-        <v>-0.0882</v>
+        <v>-0.0985</v>
       </c>
       <c r="M147" s="10" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -10424,22 +10424,22 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>100.81</v>
+        <v>100</v>
       </c>
       <c r="H148" t="n">
-        <v>102.7646</v>
+        <v>102.5599</v>
       </c>
       <c r="I148" t="n">
-        <v>101.6502</v>
+        <v>101.7204</v>
       </c>
       <c r="J148" t="n">
-        <v>41.5</v>
+        <v>38.6</v>
       </c>
       <c r="K148" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="L148" t="n">
-        <v>-0.3922</v>
+        <v>-0.4224</v>
       </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -10487,22 +10487,22 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>61.24</v>
+        <v>61.68</v>
       </c>
       <c r="H149" t="n">
-        <v>61.7989</v>
+        <v>61.8074</v>
       </c>
       <c r="I149" t="n">
-        <v>60.5547</v>
+        <v>60.6251</v>
       </c>
       <c r="J149" t="n">
-        <v>46.9</v>
+        <v>51</v>
       </c>
       <c r="K149" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="L149" t="n">
-        <v>-0.1571</v>
+        <v>-0.1631</v>
       </c>
       <c r="M149" s="10" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -10550,22 +10550,22 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>6.335</v>
+        <v>6.356</v>
       </c>
       <c r="H150" t="n">
-        <v>6.3677</v>
+        <v>6.3697</v>
       </c>
       <c r="I150" t="n">
-        <v>6.3274</v>
+        <v>6.3278</v>
       </c>
       <c r="J150" t="n">
-        <v>47.3</v>
+        <v>49.5</v>
       </c>
       <c r="K150" t="n">
         <v>16.3</v>
       </c>
       <c r="L150" t="n">
-        <v>-0.0105</v>
+        <v>-0.0091</v>
       </c>
       <c r="M150" s="10" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -10613,22 +10613,22 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>137.75</v>
+        <v>138.14</v>
       </c>
       <c r="H151" t="n">
-        <v>139.1702</v>
+        <v>139.234</v>
       </c>
       <c r="I151" t="n">
-        <v>137.0548</v>
+        <v>137.1532</v>
       </c>
       <c r="J151" t="n">
-        <v>45.4</v>
+        <v>46.5</v>
       </c>
       <c r="K151" t="n">
-        <v>23.9</v>
+        <v>22.9</v>
       </c>
       <c r="L151" t="n">
-        <v>-0.3051</v>
+        <v>-0.3193</v>
       </c>
       <c r="M151" s="10" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10676,22 +10676,22 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>4.9805</v>
+        <v>4.9945</v>
       </c>
       <c r="H152" t="n">
-        <v>5.0102</v>
+        <v>5.0089</v>
       </c>
       <c r="I152" t="n">
-        <v>4.9811</v>
+        <v>4.9825</v>
       </c>
       <c r="J152" t="n">
-        <v>46.3</v>
+        <v>48.5</v>
       </c>
       <c r="K152" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="L152" t="n">
-        <v>-0.0081</v>
+        <v>-0.0078</v>
       </c>
       <c r="M152" s="10" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -10739,22 +10739,22 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>25.26</v>
+        <v>25.365</v>
       </c>
       <c r="H153" t="n">
-        <v>25.4314</v>
+        <v>25.4319</v>
       </c>
       <c r="I153" t="n">
-        <v>25.5651</v>
+        <v>25.5531</v>
       </c>
       <c r="J153" t="n">
-        <v>43.9</v>
+        <v>47.1</v>
       </c>
       <c r="K153" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
       <c r="L153" t="n">
-        <v>-0.0262</v>
+        <v>-0.0143</v>
       </c>
       <c r="M153" s="10" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -10802,22 +10802,22 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>98.22</v>
+        <v>97.94</v>
       </c>
       <c r="H154" t="n">
-        <v>97.34399999999999</v>
+        <v>97.3844</v>
       </c>
       <c r="I154" t="n">
-        <v>96.301</v>
+        <v>96.42</v>
       </c>
       <c r="J154" t="n">
-        <v>58.9</v>
+        <v>56.9</v>
       </c>
       <c r="K154" t="n">
-        <v>21.5</v>
+        <v>20.3</v>
       </c>
       <c r="L154" t="n">
-        <v>-0.0206</v>
+        <v>-0.0278</v>
       </c>
       <c r="M154" s="10" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -10865,22 +10865,22 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>799.8099999999999</v>
+        <v>801.1</v>
       </c>
       <c r="H155" t="n">
-        <v>804.8158</v>
+        <v>804.6944999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>808.1052</v>
+        <v>807.7592</v>
       </c>
       <c r="J155" t="n">
-        <v>44.5</v>
+        <v>45.7</v>
       </c>
       <c r="K155" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="L155" t="n">
-        <v>-0.9356</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="M155" s="10" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n">
+      <c r="A156" s="9" t="n">
         <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -10928,22 +10928,22 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>197</v>
+        <v>195.82</v>
       </c>
       <c r="H156" t="n">
-        <v>204.0414</v>
+        <v>203.3282</v>
       </c>
       <c r="I156" t="n">
-        <v>206.822</v>
+        <v>206.5314</v>
       </c>
       <c r="J156" t="n">
-        <v>32.7</v>
+        <v>31</v>
       </c>
       <c r="K156" t="n">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="L156" t="n">
-        <v>-0.6566</v>
+        <v>-0.8287</v>
       </c>
       <c r="M156" s="10" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -10991,22 +10991,22 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>651.5</v>
+        <v>657</v>
       </c>
       <c r="H157" t="n">
-        <v>661.4816</v>
+        <v>661.6235</v>
       </c>
       <c r="I157" t="n">
-        <v>660.208</v>
+        <v>660.162</v>
       </c>
       <c r="J157" t="n">
-        <v>43.8</v>
+        <v>46.8</v>
       </c>
       <c r="K157" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="L157" t="n">
-        <v>-1.0965</v>
+        <v>-0.9408</v>
       </c>
       <c r="M157" s="10" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>UST.PA</t>
+          <t>USTH.MI</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11054,22 +11054,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>101.73</v>
+        <v>20.465</v>
       </c>
       <c r="H158" t="n">
-        <v>102.965</v>
+        <v>20.5909</v>
       </c>
       <c r="I158" t="n">
-        <v>103.5428</v>
+        <v>20.5431</v>
       </c>
       <c r="J158" t="n">
-        <v>44.6</v>
+        <v>47.3</v>
       </c>
       <c r="K158" t="n">
-        <v>13.2</v>
+        <v>10.8</v>
       </c>
       <c r="L158" t="n">
-        <v>-0.1016</v>
+        <v>-0.0277</v>
       </c>
       <c r="M158" s="10" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -11117,22 +11117,22 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>19.048</v>
+        <v>19.484</v>
       </c>
       <c r="H159" t="n">
-        <v>19.5219</v>
+        <v>19.5634</v>
       </c>
       <c r="I159" t="n">
-        <v>19.2958</v>
+        <v>19.3045</v>
       </c>
       <c r="J159" t="n">
-        <v>47.2</v>
+        <v>49.9</v>
       </c>
       <c r="K159" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="L159" t="n">
-        <v>-0.0838</v>
+        <v>-0.056</v>
       </c>
       <c r="M159" s="10" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -11180,22 +11180,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>101.73</v>
+        <v>102.28</v>
       </c>
       <c r="H160" t="n">
-        <v>102.965</v>
+        <v>102.9635</v>
       </c>
       <c r="I160" t="n">
-        <v>103.5428</v>
+        <v>103.4872</v>
       </c>
       <c r="J160" t="n">
-        <v>44.6</v>
+        <v>46.5</v>
       </c>
       <c r="K160" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="L160" t="n">
-        <v>-0.1016</v>
+        <v>-0.075</v>
       </c>
       <c r="M160" s="10" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -11243,22 +11243,22 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>286.4</v>
+        <v>287.7</v>
       </c>
       <c r="H161" t="n">
-        <v>289.9178</v>
+        <v>289.8962</v>
       </c>
       <c r="I161" t="n">
-        <v>291.52</v>
+        <v>291.373</v>
       </c>
       <c r="J161" t="n">
-        <v>44.6</v>
+        <v>46.1</v>
       </c>
       <c r="K161" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="L161" t="n">
-        <v>-0.2937</v>
+        <v>-0.2307</v>
       </c>
       <c r="M161" s="10" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -11306,22 +11306,22 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>26.25</v>
+        <v>26</v>
       </c>
       <c r="H162" t="n">
-        <v>26.8062</v>
+        <v>26.7484</v>
       </c>
       <c r="I162" t="n">
-        <v>26.9796</v>
+        <v>26.964</v>
       </c>
       <c r="J162" t="n">
-        <v>40.6</v>
+        <v>37.4</v>
       </c>
       <c r="K162" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="L162" t="n">
-        <v>-0.0326</v>
+        <v>-0.0581</v>
       </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -11369,22 +11369,22 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>15.988</v>
+        <v>16.154</v>
       </c>
       <c r="H163" t="n">
-        <v>16.1582</v>
+        <v>16.1731</v>
       </c>
       <c r="I163" t="n">
-        <v>16.0755</v>
+        <v>16.0849</v>
       </c>
       <c r="J163" t="n">
-        <v>44.5</v>
+        <v>50</v>
       </c>
       <c r="K163" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L163" t="n">
-        <v>-0.0307</v>
+        <v>-0.0187</v>
       </c>
       <c r="M163" s="10" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -11432,22 +11432,22 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>138.96</v>
+        <v>138.12</v>
       </c>
       <c r="H164" t="n">
-        <v>141.2098</v>
+        <v>141.0267</v>
       </c>
       <c r="I164" t="n">
-        <v>140.1056</v>
+        <v>140.096</v>
       </c>
       <c r="J164" t="n">
-        <v>45.7</v>
+        <v>44</v>
       </c>
       <c r="K164" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="L164" t="n">
-        <v>-0.2743</v>
+        <v>-0.3861</v>
       </c>
       <c r="M164" s="10" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -11495,22 +11495,22 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>73.34</v>
+        <v>74.02</v>
       </c>
       <c r="H165" t="n">
-        <v>72.6443</v>
+        <v>72.815</v>
       </c>
       <c r="I165" t="n">
-        <v>71.5626</v>
+        <v>71.67359999999999</v>
       </c>
       <c r="J165" t="n">
-        <v>53.4</v>
+        <v>55.8</v>
       </c>
       <c r="K165" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="L165" t="n">
-        <v>-0.1175</v>
+        <v>-0.0023</v>
       </c>
       <c r="M165" s="10" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -11558,22 +11558,22 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1172.5</v>
+        <v>1180.36</v>
       </c>
       <c r="H166" t="n">
-        <v>1178.4709</v>
+        <v>1179.4772</v>
       </c>
       <c r="I166" t="n">
-        <v>1168.8446</v>
+        <v>1169.1894</v>
       </c>
       <c r="J166" t="n">
-        <v>48.9</v>
+        <v>50.9</v>
       </c>
       <c r="K166" t="n">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="L166" t="n">
-        <v>-1.274</v>
+        <v>-0.7855</v>
       </c>
       <c r="M166" s="10" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -11592,8 +11592,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="n">
-        <v>3</v>
+      <c r="A167" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -11621,31 +11621,31 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>20.83</v>
+        <v>21.09</v>
       </c>
       <c r="H167" t="n">
-        <v>20.9658</v>
+        <v>20.9905</v>
       </c>
       <c r="I167" t="n">
-        <v>20.4769</v>
+        <v>20.4821</v>
       </c>
       <c r="J167" t="n">
-        <v>49.4</v>
+        <v>53.8</v>
       </c>
       <c r="K167" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
       <c r="L167" t="n">
-        <v>-0.0237</v>
-      </c>
-      <c r="M167" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>-0.0071</v>
+      </c>
+      <c r="M167" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -11684,22 +11684,22 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>5.878</v>
+        <v>5.874</v>
       </c>
       <c r="H168" t="n">
-        <v>6.214</v>
+        <v>6.1861</v>
       </c>
       <c r="I168" t="n">
-        <v>6.0513</v>
+        <v>6.0581</v>
       </c>
       <c r="J168" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="K168" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="L168" t="n">
-        <v>-0.0755</v>
+        <v>-0.0779</v>
       </c>
       <c r="M168" s="10" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11747,22 +11747,22 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>399</v>
+        <v>410.53</v>
       </c>
       <c r="H169" t="n">
-        <v>410.4865</v>
+        <v>410.9533</v>
       </c>
       <c r="I169" t="n">
-        <v>390.768</v>
+        <v>391.415</v>
       </c>
       <c r="J169" t="n">
-        <v>45</v>
+        <v>52.2</v>
       </c>
       <c r="K169" t="n">
-        <v>31.3</v>
+        <v>29.3</v>
       </c>
       <c r="L169" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-1.368</v>
       </c>
       <c r="M169" s="10" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -11810,22 +11810,22 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>50</v>
+        <v>51.61</v>
       </c>
       <c r="H170" t="n">
-        <v>51.4397</v>
+        <v>51.5412</v>
       </c>
       <c r="I170" t="n">
-        <v>48.7714</v>
+        <v>48.8773</v>
       </c>
       <c r="J170" t="n">
-        <v>46.3</v>
+        <v>51.9</v>
       </c>
       <c r="K170" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="L170" t="n">
-        <v>-0.1575</v>
+        <v>-0.1798</v>
       </c>
       <c r="M170" s="10" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -11873,22 +11873,22 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>165.57</v>
+        <v>166.63</v>
       </c>
       <c r="H171" t="n">
-        <v>166.6883</v>
+        <v>166.7715</v>
       </c>
       <c r="I171" t="n">
-        <v>165.7896</v>
+        <v>165.8478</v>
       </c>
       <c r="J171" t="n">
-        <v>46</v>
+        <v>50.4</v>
       </c>
       <c r="K171" t="n">
-        <v>13.1</v>
+        <v>11.8</v>
       </c>
       <c r="L171" t="n">
-        <v>-0.2251</v>
+        <v>-0.1669</v>
       </c>
       <c r="M171" s="10" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -11939,10 +11939,10 @@
         <v>20.035</v>
       </c>
       <c r="H172" t="n">
-        <v>19.9651</v>
+        <v>19.9717</v>
       </c>
       <c r="I172" t="n">
-        <v>19.9044</v>
+        <v>19.9075</v>
       </c>
       <c r="J172" t="n">
         <v>100</v>
@@ -11951,7 +11951,7 @@
         <v>99.8</v>
       </c>
       <c r="L172" t="n">
-        <v>0.0118</v>
+        <v>0.0094</v>
       </c>
       <c r="M172" s="10" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -11999,22 +11999,22 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>28.85</v>
+        <v>28.845</v>
       </c>
       <c r="H173" t="n">
-        <v>29.7807</v>
+        <v>29.6989</v>
       </c>
       <c r="I173" t="n">
-        <v>30.2842</v>
+        <v>30.2572</v>
       </c>
       <c r="J173" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="K173" t="n">
-        <v>28.4</v>
+        <v>30.6</v>
       </c>
       <c r="L173" t="n">
-        <v>-0.1069</v>
+        <v>-0.1077</v>
       </c>
       <c r="M173" s="10" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -12062,22 +12062,22 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>9.83</v>
+        <v>9.988</v>
       </c>
       <c r="H174" t="n">
-        <v>10.2393</v>
+        <v>10.2231</v>
       </c>
       <c r="I174" t="n">
-        <v>10.6482</v>
+        <v>10.6097</v>
       </c>
       <c r="J174" t="n">
-        <v>35</v>
+        <v>39.4</v>
       </c>
       <c r="K174" t="n">
-        <v>15.8</v>
+        <v>16.3</v>
       </c>
       <c r="L174" t="n">
-        <v>-0.0094</v>
+        <v>-0.0027</v>
       </c>
       <c r="M174" s="10" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -12125,22 +12125,22 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>202.7</v>
+        <v>203.8</v>
       </c>
       <c r="H175" t="n">
-        <v>203.452</v>
+        <v>203.6575</v>
       </c>
       <c r="I175" t="n">
-        <v>202.3598</v>
+        <v>202.2688</v>
       </c>
       <c r="J175" t="n">
-        <v>49.4</v>
+        <v>50.9</v>
       </c>
       <c r="K175" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="L175" t="n">
-        <v>0.0028</v>
+        <v>0.0165</v>
       </c>
       <c r="M175" s="10" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -12188,22 +12188,22 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>270.7</v>
+        <v>274.05</v>
       </c>
       <c r="H176" t="n">
-        <v>274.6131</v>
+        <v>274.6628</v>
       </c>
       <c r="I176" t="n">
-        <v>270.26</v>
+        <v>270.522</v>
       </c>
       <c r="J176" t="n">
-        <v>41.6</v>
+        <v>50.4</v>
       </c>
       <c r="K176" t="n">
-        <v>31.2</v>
+        <v>28.8</v>
       </c>
       <c r="L176" t="n">
-        <v>-0.8579</v>
+        <v>-0.7786</v>
       </c>
       <c r="M176" s="10" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -12251,22 +12251,22 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>33.12</v>
+        <v>33.04</v>
       </c>
       <c r="H177" t="n">
-        <v>33.515</v>
+        <v>33.4616</v>
       </c>
       <c r="I177" t="n">
-        <v>34.0833</v>
+        <v>34.0588</v>
       </c>
       <c r="J177" t="n">
-        <v>41.3</v>
+        <v>40.3</v>
       </c>
       <c r="K177" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="L177" t="n">
-        <v>-0.0165</v>
+        <v>-0.023</v>
       </c>
       <c r="M177" s="10" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -12314,22 +12314,22 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>157.79</v>
+        <v>158.06</v>
       </c>
       <c r="H178" t="n">
-        <v>158.6796</v>
+        <v>158.6551</v>
       </c>
       <c r="I178" t="n">
-        <v>159.094</v>
+        <v>159.0628</v>
       </c>
       <c r="J178" t="n">
-        <v>31</v>
+        <v>34.3</v>
       </c>
       <c r="K178" t="n">
-        <v>15.9</v>
+        <v>17.3</v>
       </c>
       <c r="L178" t="n">
-        <v>-0.0764</v>
+        <v>-0.0653</v>
       </c>
       <c r="M178" s="10" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -12377,22 +12377,22 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>69.91</v>
+        <v>70.63</v>
       </c>
       <c r="H179" t="n">
-        <v>69.8245</v>
+        <v>69.9538</v>
       </c>
       <c r="I179" t="n">
-        <v>69.1844</v>
+        <v>69.2212</v>
       </c>
       <c r="J179" t="n">
-        <v>52.2</v>
+        <v>57.7</v>
       </c>
       <c r="K179" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="L179" t="n">
-        <v>-0.0605</v>
+        <v>-0.0021</v>
       </c>
       <c r="M179" s="10" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -12440,22 +12440,22 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>10.43</v>
+        <v>10.564</v>
       </c>
       <c r="H180" t="n">
-        <v>10.6192</v>
+        <v>10.6222</v>
       </c>
       <c r="I180" t="n">
-        <v>10.4953</v>
+        <v>10.5018</v>
       </c>
       <c r="J180" t="n">
-        <v>40.7</v>
+        <v>47.9</v>
       </c>
       <c r="K180" t="n">
-        <v>19.6</v>
+        <v>18.1</v>
       </c>
       <c r="L180" t="n">
-        <v>-0.0289</v>
+        <v>-0.0272</v>
       </c>
       <c r="M180" s="10" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -12503,22 +12503,22 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>81.29000000000001</v>
+        <v>81.75</v>
       </c>
       <c r="H181" t="n">
-        <v>81.27549999999999</v>
+        <v>81.3439</v>
       </c>
       <c r="I181" t="n">
-        <v>80.56059999999999</v>
+        <v>80.6242</v>
       </c>
       <c r="J181" t="n">
-        <v>52.8</v>
+        <v>59.1</v>
       </c>
       <c r="K181" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="L181" t="n">
-        <v>-0.0847</v>
+        <v>-0.0485</v>
       </c>
       <c r="M181" s="10" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -12566,22 +12566,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>227.9</v>
+        <v>229.55</v>
       </c>
       <c r="H182" t="n">
-        <v>231.1497</v>
+        <v>230.9974</v>
       </c>
       <c r="I182" t="n">
-        <v>231.39</v>
+        <v>231.544</v>
       </c>
       <c r="J182" t="n">
-        <v>44.2</v>
+        <v>47.5</v>
       </c>
       <c r="K182" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="L182" t="n">
-        <v>-0.2652</v>
+        <v>-0.3305</v>
       </c>
       <c r="M182" s="10" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -12629,22 +12629,22 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>112.83</v>
+        <v>114.08</v>
       </c>
       <c r="H183" t="n">
-        <v>115.6938</v>
+        <v>115.6117</v>
       </c>
       <c r="I183" t="n">
-        <v>116.443</v>
+        <v>116.334</v>
       </c>
       <c r="J183" t="n">
-        <v>41</v>
+        <v>44.5</v>
       </c>
       <c r="K183" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L183" t="n">
-        <v>-0.3322</v>
+        <v>-0.3092</v>
       </c>
       <c r="M183" s="10" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -12692,22 +12692,22 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>88.92</v>
+        <v>89.64</v>
       </c>
       <c r="H184" t="n">
-        <v>90.0667</v>
+        <v>90.07259999999999</v>
       </c>
       <c r="I184" t="n">
-        <v>88.803</v>
+        <v>88.8934</v>
       </c>
       <c r="J184" t="n">
-        <v>42.3</v>
+        <v>48.1</v>
       </c>
       <c r="K184" t="n">
-        <v>29.9</v>
+        <v>27.5</v>
       </c>
       <c r="L184" t="n">
-        <v>-0.1973</v>
+        <v>-0.2019</v>
       </c>
       <c r="M184" s="10" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -12727,7 +12727,7 @@
     </row>
     <row r="185">
       <c r="A185" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -12755,31 +12755,31 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>78.06999999999999</v>
+        <v>78.39</v>
       </c>
       <c r="H185" t="n">
-        <v>77.9145</v>
+        <v>77.98</v>
       </c>
       <c r="I185" t="n">
-        <v>76.25749999999999</v>
+        <v>76.372</v>
       </c>
       <c r="J185" t="n">
-        <v>57.7</v>
+        <v>63</v>
       </c>
       <c r="K185" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="L185" t="n">
-        <v>-0.0965</v>
-      </c>
-      <c r="M185" s="12" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>-0.0992</v>
+      </c>
+      <c r="M185" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -12790,7 +12790,7 @@
     </row>
     <row r="186">
       <c r="A186" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -12818,31 +12818,31 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>18.322</v>
+        <v>18.884</v>
       </c>
       <c r="H186" t="n">
-        <v>18.0366</v>
+        <v>18.1304</v>
       </c>
       <c r="I186" t="n">
-        <v>18.0442</v>
+        <v>18.0734</v>
       </c>
       <c r="J186" t="n">
-        <v>58.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K186" t="n">
-        <v>17.6</v>
+        <v>19.3</v>
       </c>
       <c r="L186" t="n">
-        <v>0.0617</v>
-      </c>
-      <c r="M186" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.1056</v>
+      </c>
+      <c r="M186" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -12881,22 +12881,22 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>39.98</v>
+        <v>39.865</v>
       </c>
       <c r="H187" t="n">
-        <v>39.4661</v>
+        <v>39.576</v>
       </c>
       <c r="I187" t="n">
-        <v>39.2109</v>
+        <v>39.2076</v>
       </c>
       <c r="J187" t="n">
-        <v>58.2</v>
+        <v>55.1</v>
       </c>
       <c r="K187" t="n">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="L187" t="n">
-        <v>0.0655</v>
+        <v>0.0538</v>
       </c>
       <c r="M187" s="10" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -12944,22 +12944,22 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>52.3</v>
+        <v>52.57</v>
       </c>
       <c r="H188" t="n">
-        <v>52.9815</v>
+        <v>52.9733</v>
       </c>
       <c r="I188" t="n">
-        <v>52.4336</v>
+        <v>52.4684</v>
       </c>
       <c r="J188" t="n">
-        <v>39.9</v>
+        <v>43.7</v>
       </c>
       <c r="K188" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="L188" t="n">
-        <v>-0.1331</v>
+        <v>-0.1307</v>
       </c>
       <c r="M188" s="10" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -13007,22 +13007,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>8.4</v>
+        <v>8.445</v>
       </c>
       <c r="H189" t="n">
-        <v>8.4468</v>
+        <v>8.4511</v>
       </c>
       <c r="I189" t="n">
-        <v>8.337400000000001</v>
+        <v>8.3383</v>
       </c>
       <c r="J189" t="n">
-        <v>47.3</v>
+        <v>52.3</v>
       </c>
       <c r="K189" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="L189" t="n">
-        <v>-0.0132</v>
+        <v>-0.0103</v>
       </c>
       <c r="M189" s="10" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -13070,22 +13070,22 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>17.008</v>
+        <v>17.094</v>
       </c>
       <c r="H190" t="n">
-        <v>17.0586</v>
+        <v>17.0732</v>
       </c>
       <c r="I190" t="n">
-        <v>16.8729</v>
+        <v>16.8896</v>
       </c>
       <c r="J190" t="n">
-        <v>48.7</v>
+        <v>51.7</v>
       </c>
       <c r="K190" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="L190" t="n">
-        <v>-0.0046</v>
+        <v>0.0005</v>
       </c>
       <c r="M190" s="10" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -13133,22 +13133,22 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>48.05</v>
+        <v>48.235</v>
       </c>
       <c r="H191" t="n">
-        <v>48.7149</v>
+        <v>48.6994</v>
       </c>
       <c r="I191" t="n">
-        <v>48.095</v>
+        <v>48.1534</v>
       </c>
       <c r="J191" t="n">
-        <v>44.4</v>
+        <v>45.8</v>
       </c>
       <c r="K191" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="L191" t="n">
-        <v>-0.1045</v>
+        <v>-0.1056</v>
       </c>
       <c r="M191" s="10" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -13196,22 +13196,22 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>3.776</v>
+        <v>3.808</v>
       </c>
       <c r="H192" t="n">
-        <v>3.7547</v>
+        <v>3.7622</v>
       </c>
       <c r="I192" t="n">
-        <v>3.7287</v>
+        <v>3.7317</v>
       </c>
       <c r="J192" t="n">
-        <v>52.8</v>
+        <v>57</v>
       </c>
       <c r="K192" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="L192" t="n">
-        <v>0.0022</v>
+        <v>0.0066</v>
       </c>
       <c r="M192" s="12" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -13259,22 +13259,22 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>11.5</v>
+        <v>11.486</v>
       </c>
       <c r="H193" t="n">
-        <v>11.2537</v>
+        <v>11.2923</v>
       </c>
       <c r="I193" t="n">
-        <v>10.9124</v>
+        <v>10.939</v>
       </c>
       <c r="J193" t="n">
-        <v>65.8</v>
+        <v>61.1</v>
       </c>
       <c r="K193" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="L193" t="n">
-        <v>0.0264</v>
+        <v>0.0254</v>
       </c>
       <c r="M193" s="10" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -13322,22 +13322,22 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>10.15</v>
+        <v>10.254</v>
       </c>
       <c r="H194" t="n">
-        <v>10.1253</v>
+        <v>10.1352</v>
       </c>
       <c r="I194" t="n">
-        <v>9.4185</v>
+        <v>9.4206</v>
       </c>
       <c r="J194" t="n">
-        <v>53.8</v>
+        <v>56.3</v>
       </c>
       <c r="K194" t="n">
-        <v>26.7</v>
+        <v>27</v>
       </c>
       <c r="L194" t="n">
-        <v>-0.0035</v>
+        <v>0.0032</v>
       </c>
       <c r="M194" s="10" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -13385,22 +13385,22 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>26.385</v>
+        <v>26.83</v>
       </c>
       <c r="H195" t="n">
-        <v>27.5667</v>
+        <v>27.5534</v>
       </c>
       <c r="I195" t="n">
-        <v>28.0554</v>
+        <v>27.9788</v>
       </c>
       <c r="J195" t="n">
-        <v>37</v>
+        <v>40.2</v>
       </c>
       <c r="K195" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="L195" t="n">
-        <v>-0.0397</v>
+        <v>-0.0347</v>
       </c>
       <c r="M195" s="10" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -13448,22 +13448,22 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>4.6305</v>
+        <v>4.619</v>
       </c>
       <c r="H196" t="n">
-        <v>4.7796</v>
+        <v>4.7656</v>
       </c>
       <c r="I196" t="n">
-        <v>4.8608</v>
+        <v>4.8564</v>
       </c>
       <c r="J196" t="n">
-        <v>25.5</v>
+        <v>24.6</v>
       </c>
       <c r="K196" t="n">
-        <v>28.6</v>
+        <v>30.9</v>
       </c>
       <c r="L196" t="n">
-        <v>-0.0171</v>
+        <v>-0.0179</v>
       </c>
       <c r="M196" s="10" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -13511,22 +13511,22 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>83.90000000000001</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="H197" t="n">
-        <v>86.003</v>
+        <v>85.8818</v>
       </c>
       <c r="I197" t="n">
-        <v>86.03749999999999</v>
+        <v>86.0277</v>
       </c>
       <c r="J197" t="n">
-        <v>34.2</v>
+        <v>35.9</v>
       </c>
       <c r="K197" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="L197" t="n">
-        <v>-0.4003</v>
+        <v>-0.3627</v>
       </c>
       <c r="M197" s="10" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>150.0749969482422</v>
+        <v>150.0950012207031</v>
       </c>
       <c r="H198" t="n">
         <v>149.1741</v>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -13637,22 +13637,22 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>140.95</v>
+        <v>141.03</v>
       </c>
       <c r="H199" t="n">
-        <v>141.1293</v>
+        <v>141.1302</v>
       </c>
       <c r="I199" t="n">
-        <v>141.129</v>
+        <v>141.1284</v>
       </c>
       <c r="J199" t="n">
-        <v>40.4</v>
+        <v>44</v>
       </c>
       <c r="K199" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="L199" t="n">
-        <v>-0.0249</v>
+        <v>-0.0213</v>
       </c>
       <c r="M199" s="10" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -13700,22 +13700,22 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>156.24</v>
+        <v>157.48</v>
       </c>
       <c r="H200" t="n">
-        <v>157.5224</v>
+        <v>157.5864</v>
       </c>
       <c r="I200" t="n">
-        <v>155.5094</v>
+        <v>155.6416</v>
       </c>
       <c r="J200" t="n">
-        <v>46.1</v>
+        <v>51.3</v>
       </c>
       <c r="K200" t="n">
-        <v>38.3</v>
+        <v>37.4</v>
       </c>
       <c r="L200" t="n">
-        <v>-0.2893</v>
+        <v>-0.262</v>
       </c>
       <c r="M200" s="10" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -13763,22 +13763,22 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>118.69</v>
+        <v>119.61</v>
       </c>
       <c r="H201" t="n">
-        <v>119.8406</v>
+        <v>119.8859</v>
       </c>
       <c r="I201" t="n">
-        <v>118.3959</v>
+        <v>118.4907</v>
       </c>
       <c r="J201" t="n">
-        <v>44.5</v>
+        <v>50</v>
       </c>
       <c r="K201" t="n">
-        <v>21.9</v>
+        <v>20.5</v>
       </c>
       <c r="L201" t="n">
-        <v>-0.2381</v>
+        <v>-0.2161</v>
       </c>
       <c r="M201" s="10" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -13826,22 +13826,22 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>357.73</v>
+        <v>366.86</v>
       </c>
       <c r="H202" t="n">
-        <v>367.2204</v>
+        <v>367.5635</v>
       </c>
       <c r="I202" t="n">
-        <v>353.0022</v>
+        <v>353.634</v>
       </c>
       <c r="J202" t="n">
-        <v>44.1</v>
+        <v>51.6</v>
       </c>
       <c r="K202" t="n">
-        <v>28.1</v>
+        <v>26.1</v>
       </c>
       <c r="L202" t="n">
-        <v>-1.45</v>
+        <v>-1.556</v>
       </c>
       <c r="M202" s="10" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -13889,22 +13889,22 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>7.64</v>
+        <v>7.773</v>
       </c>
       <c r="H203" t="n">
-        <v>7.2453</v>
+        <v>7.3064</v>
       </c>
       <c r="I203" t="n">
-        <v>6.5911</v>
+        <v>6.6279</v>
       </c>
       <c r="J203" t="n">
-        <v>63.8</v>
+        <v>68</v>
       </c>
       <c r="K203" t="n">
-        <v>34.9</v>
+        <v>36.9</v>
       </c>
       <c r="L203" t="n">
-        <v>0.0838</v>
+        <v>0.0653</v>
       </c>
       <c r="M203" s="10" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -13955,19 +13955,19 @@
         <v>30.56</v>
       </c>
       <c r="H204" t="n">
-        <v>29.4046</v>
+        <v>29.5112</v>
       </c>
       <c r="I204" t="n">
-        <v>28.3785</v>
+        <v>28.4572</v>
       </c>
       <c r="J204" t="n">
         <v>71.8</v>
       </c>
       <c r="K204" t="n">
-        <v>26</v>
+        <v>27.1</v>
       </c>
       <c r="L204" t="n">
-        <v>0.09</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="M204" s="10" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -14015,22 +14015,22 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>122.74</v>
+        <v>123.7</v>
       </c>
       <c r="H205" t="n">
-        <v>123.4566</v>
+        <v>123.5745</v>
       </c>
       <c r="I205" t="n">
-        <v>122.4244</v>
+        <v>122.4608</v>
       </c>
       <c r="J205" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="K205" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="L205" t="n">
-        <v>-0.1502</v>
+        <v>-0.0885</v>
       </c>
       <c r="M205" s="10" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -14078,22 +14078,22 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>38.67</v>
+        <v>37.955</v>
       </c>
       <c r="H206" t="n">
-        <v>39.4407</v>
+        <v>39.3367</v>
       </c>
       <c r="I206" t="n">
-        <v>39.0461</v>
+        <v>39.1081</v>
       </c>
       <c r="J206" t="n">
-        <v>46.4</v>
+        <v>42.8</v>
       </c>
       <c r="K206" t="n">
-        <v>17.5</v>
+        <v>17.1</v>
       </c>
       <c r="L206" t="n">
-        <v>-0.1372</v>
+        <v>-0.1957</v>
       </c>
       <c r="M206" s="10" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -14141,22 +14141,22 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>9.278</v>
+        <v>9.353</v>
       </c>
       <c r="H207" t="n">
-        <v>9.461</v>
+        <v>9.4611</v>
       </c>
       <c r="I207" t="n">
-        <v>9.5001</v>
+        <v>9.4922</v>
       </c>
       <c r="J207" t="n">
-        <v>44.9</v>
+        <v>46.6</v>
       </c>
       <c r="K207" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="L207" t="n">
-        <v>-0.0206</v>
+        <v>-0.0177</v>
       </c>
       <c r="M207" s="10" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -14204,22 +14204,22 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>8.493</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="H208" t="n">
-        <v>8.833600000000001</v>
+        <v>8.820499999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>9.265599999999999</v>
+        <v>9.229100000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>34.4</v>
+        <v>38.3</v>
       </c>
       <c r="K208" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="L208" t="n">
-        <v>-0.0007</v>
+        <v>0.0066</v>
       </c>
       <c r="M208" s="10" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -14267,22 +14267,22 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>83.495</v>
+        <v>85.8925</v>
       </c>
       <c r="H209" t="n">
-        <v>85.8947</v>
+        <v>85.99039999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>81.73309999999999</v>
+        <v>81.869</v>
       </c>
       <c r="J209" t="n">
-        <v>45</v>
+        <v>52.2</v>
       </c>
       <c r="K209" t="n">
-        <v>32.6</v>
+        <v>30.5</v>
       </c>
       <c r="L209" t="n">
-        <v>-0.1913</v>
+        <v>-0.2908</v>
       </c>
       <c r="M209" s="10" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -14330,22 +14330,22 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>135.15</v>
+        <v>139.25</v>
       </c>
       <c r="H210" t="n">
-        <v>139.8556</v>
+        <v>140.1547</v>
       </c>
       <c r="I210" t="n">
-        <v>133.6678</v>
+        <v>133.9866</v>
       </c>
       <c r="J210" t="n">
-        <v>45.1</v>
+        <v>50.1</v>
       </c>
       <c r="K210" t="n">
-        <v>20.2</v>
+        <v>18.8</v>
       </c>
       <c r="L210" t="n">
-        <v>-0.465</v>
+        <v>-0.4768</v>
       </c>
       <c r="M210" s="10" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -14393,22 +14393,22 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>60.51</v>
+        <v>55.42</v>
       </c>
       <c r="H211" t="n">
-        <v>52.1159</v>
+        <v>51.6312</v>
       </c>
       <c r="I211" t="n">
-        <v>47.4114</v>
+        <v>47.3096</v>
       </c>
       <c r="J211" t="n">
-        <v>80.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K211" t="n">
-        <v>32.7</v>
+        <v>31.4</v>
       </c>
       <c r="L211" t="n">
-        <v>1.0262</v>
+        <v>0.7014</v>
       </c>
       <c r="M211" s="10" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -14456,22 +14456,22 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>58.7</v>
+        <v>64.08</v>
       </c>
       <c r="H212" t="n">
-        <v>57.6609</v>
+        <v>58.1733</v>
       </c>
       <c r="I212" t="n">
-        <v>50.8852</v>
+        <v>50.9928</v>
       </c>
       <c r="J212" t="n">
-        <v>56.4</v>
+        <v>75</v>
       </c>
       <c r="K212" t="n">
-        <v>34.7</v>
+        <v>37.3</v>
       </c>
       <c r="L212" t="n">
-        <v>0.6055</v>
+        <v>0.9488</v>
       </c>
       <c r="M212" s="10" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -14519,19 +14519,19 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>9.507999999999999</v>
+        <v>9.444000000000001</v>
       </c>
       <c r="H213" t="n">
-        <v>8.212999999999999</v>
+        <v>8.3302</v>
       </c>
       <c r="J213" t="n">
-        <v>73.2</v>
+        <v>71.8</v>
       </c>
       <c r="K213" t="n">
-        <v>37.9</v>
+        <v>38.3</v>
       </c>
       <c r="L213" t="n">
-        <v>0.2735</v>
+        <v>0.2311</v>
       </c>
       <c r="M213" s="12" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -14579,22 +14579,22 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>58.43</v>
+        <v>59.245</v>
       </c>
       <c r="H214" t="n">
-        <v>55.2149</v>
+        <v>55.6672</v>
       </c>
       <c r="I214" t="n">
-        <v>50.7135</v>
+        <v>50.9684</v>
       </c>
       <c r="J214" t="n">
-        <v>65.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K214" t="n">
-        <v>35.6</v>
+        <v>37.4</v>
       </c>
       <c r="L214" t="n">
-        <v>0.6846</v>
+        <v>0.5461</v>
       </c>
       <c r="M214" s="10" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -14642,22 +14642,22 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>93.94</v>
+        <v>94.48</v>
       </c>
       <c r="H215" t="n">
-        <v>86.9362</v>
+        <v>87.7599</v>
       </c>
       <c r="I215" t="n">
-        <v>77.9825</v>
+        <v>78.4885</v>
       </c>
       <c r="J215" t="n">
-        <v>67.5</v>
+        <v>68.2</v>
       </c>
       <c r="K215" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="L215" t="n">
-        <v>1.3418</v>
+        <v>1.0298</v>
       </c>
       <c r="M215" s="10" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -14705,22 +14705,22 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>30.99</v>
+        <v>34.85</v>
       </c>
       <c r="H216" t="n">
-        <v>32.0677</v>
+        <v>32.4034</v>
       </c>
       <c r="I216" t="n">
-        <v>30.0436</v>
+        <v>30.1817</v>
       </c>
       <c r="J216" t="n">
-        <v>48</v>
+        <v>56.3</v>
       </c>
       <c r="K216" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="L216" t="n">
-        <v>-0.2327</v>
+        <v>-0.0125</v>
       </c>
       <c r="M216" s="10" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -14768,22 +14768,22 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.2302</v>
+        <v>0.228</v>
       </c>
       <c r="H217" t="n">
-        <v>0.2522</v>
+        <v>0.252</v>
       </c>
       <c r="I217" t="n">
         <v>0.3056</v>
       </c>
       <c r="J217" t="n">
-        <v>41</v>
+        <v>40.3</v>
       </c>
       <c r="K217" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="L217" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="M217" s="10" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -14831,22 +14831,22 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.2302</v>
+        <v>1.185</v>
       </c>
       <c r="H218" t="n">
-        <v>1.1238</v>
+        <v>1.1296</v>
       </c>
       <c r="I218" t="n">
-        <v>1.4237</v>
+        <v>1.4092</v>
       </c>
       <c r="J218" t="n">
-        <v>53.2</v>
+        <v>50.7</v>
       </c>
       <c r="K218" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="L218" t="n">
-        <v>0.0522</v>
+        <v>0.0492</v>
       </c>
       <c r="M218" s="10" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -14894,22 +14894,22 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>23.5</v>
+        <v>24.005</v>
       </c>
       <c r="H219" t="n">
-        <v>22.0953</v>
+        <v>22.3358</v>
       </c>
       <c r="I219" t="n">
-        <v>17.0406</v>
+        <v>17.3012</v>
       </c>
       <c r="J219" t="n">
-        <v>58.1</v>
+        <v>60</v>
       </c>
       <c r="K219" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="L219" t="n">
-        <v>-0.1466</v>
+        <v>-0.143</v>
       </c>
       <c r="M219" s="10" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -14957,22 +14957,22 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>44.985</v>
+        <v>49.34</v>
       </c>
       <c r="H220" t="n">
-        <v>44.7193</v>
+        <v>45.1594</v>
       </c>
       <c r="I220" t="n">
-        <v>45.9082</v>
+        <v>46.0449</v>
       </c>
       <c r="J220" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="K220" t="n">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="L220" t="n">
-        <v>0.4298</v>
+        <v>0.6868</v>
       </c>
       <c r="M220" s="10" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -15020,22 +15020,22 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>287.05</v>
+        <v>295.08</v>
       </c>
       <c r="H221" t="n">
-        <v>354.2134</v>
+        <v>354.9782</v>
       </c>
       <c r="I221" t="n">
-        <v>463.853</v>
+        <v>464.0136</v>
       </c>
       <c r="J221" t="n">
-        <v>39.9</v>
+        <v>40.6</v>
       </c>
       <c r="K221" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L221" t="n">
-        <v>1.8972</v>
+        <v>2.4097</v>
       </c>
       <c r="M221" s="10" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -15083,22 +15083,22 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>21.53</v>
+        <v>22.035</v>
       </c>
       <c r="H222" t="n">
-        <v>22.3117</v>
+        <v>22.3598</v>
       </c>
       <c r="I222" t="n">
-        <v>25.9116</v>
+        <v>25.9217</v>
       </c>
       <c r="J222" t="n">
-        <v>45.8</v>
+        <v>47.2</v>
       </c>
       <c r="K222" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="L222" t="n">
-        <v>0.3305</v>
+        <v>0.3627</v>
       </c>
       <c r="M222" s="10" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -15209,22 +15209,22 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>248.35</v>
+        <v>247.05</v>
       </c>
       <c r="H224" t="n">
-        <v>251.3995</v>
+        <v>250.9853</v>
       </c>
       <c r="I224" t="n">
-        <v>251.8755</v>
+        <v>251.7785</v>
       </c>
       <c r="J224" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="K224" t="n">
-        <v>13.9</v>
+        <v>15.5</v>
       </c>
       <c r="L224" t="n">
-        <v>-0.238</v>
+        <v>-0.4281</v>
       </c>
       <c r="M224" s="10" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -15272,22 +15272,22 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>250.18</v>
+        <v>250.25</v>
       </c>
       <c r="H225" t="n">
-        <v>252.0325</v>
+        <v>252.0391</v>
       </c>
       <c r="I225" t="n">
-        <v>249.881</v>
+        <v>249.8824</v>
       </c>
       <c r="J225" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="K225" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="L225" t="n">
-        <v>-0.4466</v>
+        <v>-0.4421</v>
       </c>
       <c r="M225" s="10" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -15335,22 +15335,22 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>123.95</v>
+        <v>124.06</v>
       </c>
       <c r="H226" t="n">
-        <v>125.0243</v>
+        <v>124.9549</v>
       </c>
       <c r="I226" t="n">
-        <v>125.736</v>
+        <v>125.6742</v>
       </c>
       <c r="J226" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K226" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="L226" t="n">
-        <v>-0.09</v>
+        <v>-0.0896</v>
       </c>
       <c r="M226" s="10" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -15369,8 +15369,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
-        <v>3</v>
+      <c r="A227" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -15398,31 +15398,31 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>109.86</v>
+        <v>109.9</v>
       </c>
       <c r="H227" t="n">
-        <v>109.77</v>
+        <v>109.7841</v>
       </c>
       <c r="I227" t="n">
-        <v>109.6067</v>
+        <v>109.6185</v>
       </c>
       <c r="J227" t="n">
-        <v>87.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K227" t="n">
-        <v>72</v>
+        <v>72.5</v>
       </c>
       <c r="L227" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="M227" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0015</v>
+      </c>
+      <c r="M227" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -15461,22 +15461,22 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>10.436</v>
+        <v>10.45</v>
       </c>
       <c r="H228" t="n">
-        <v>10.5286</v>
+        <v>10.522</v>
       </c>
       <c r="I228" t="n">
-        <v>10.444</v>
+        <v>10.4463</v>
       </c>
       <c r="J228" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
       <c r="K228" t="n">
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="L228" t="n">
-        <v>-0.0236</v>
+        <v>-0.0255</v>
       </c>
       <c r="M228" s="10" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -15524,22 +15524,22 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>9.865</v>
+        <v>9.895</v>
       </c>
       <c r="H229" t="n">
-        <v>9.892300000000001</v>
+        <v>9.8909</v>
       </c>
       <c r="I229" t="n">
-        <v>9.929399999999999</v>
+        <v>9.926500000000001</v>
       </c>
       <c r="J229" t="n">
-        <v>40.9</v>
+        <v>49.5</v>
       </c>
       <c r="K229" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="L229" t="n">
-        <v>-0.0025</v>
+        <v>-0.0011</v>
       </c>
       <c r="M229" s="10" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -15587,22 +15587,22 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>5.719</v>
+        <v>5.804</v>
       </c>
       <c r="H230" t="n">
-        <v>5.9463</v>
+        <v>5.9432</v>
       </c>
       <c r="I230" t="n">
-        <v>6.1303</v>
+        <v>6.1109</v>
       </c>
       <c r="J230" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="K230" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="L230" t="n">
-        <v>-0.0114</v>
+        <v>-0.008</v>
       </c>
       <c r="M230" s="10" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -15650,22 +15650,22 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>212.35</v>
+        <v>213.15</v>
       </c>
       <c r="H231" t="n">
-        <v>215.1686</v>
+        <v>215.1185</v>
       </c>
       <c r="I231" t="n">
-        <v>211.23</v>
+        <v>211.445</v>
       </c>
       <c r="J231" t="n">
-        <v>44</v>
+        <v>45.8</v>
       </c>
       <c r="K231" t="n">
-        <v>24.5</v>
+        <v>22.6</v>
       </c>
       <c r="L231" t="n">
-        <v>-0.5225</v>
+        <v>-0.6004</v>
       </c>
       <c r="M231" s="10" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -15713,22 +15713,22 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>358.2</v>
+        <v>359.25</v>
       </c>
       <c r="H232" t="n">
-        <v>363.4134</v>
+        <v>363.5134</v>
       </c>
       <c r="I232" t="n">
-        <v>358.7505</v>
+        <v>358.7715</v>
       </c>
       <c r="J232" t="n">
-        <v>42.7</v>
+        <v>44.2</v>
       </c>
       <c r="K232" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="L232" t="n">
-        <v>-1.1545</v>
+        <v>-1.0875</v>
       </c>
       <c r="M232" s="10" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -15776,22 +15776,22 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>6.828</v>
+        <v>6.848</v>
       </c>
       <c r="H233" t="n">
-        <v>7.0117</v>
+        <v>6.9993</v>
       </c>
       <c r="I233" t="n">
-        <v>7.0329</v>
+        <v>7.0315</v>
       </c>
       <c r="J233" t="n">
-        <v>31.4</v>
+        <v>32.5</v>
       </c>
       <c r="K233" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="L233" t="n">
-        <v>-0.0266</v>
+        <v>-0.0271</v>
       </c>
       <c r="M233" s="10" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -15839,22 +15839,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>142.22</v>
+        <v>142.415</v>
       </c>
       <c r="H234" t="n">
-        <v>142.8393</v>
+        <v>142.8578</v>
       </c>
       <c r="I234" t="n">
-        <v>142.8805</v>
+        <v>142.8844</v>
       </c>
       <c r="J234" t="n">
-        <v>38.9</v>
+        <v>41.6</v>
       </c>
       <c r="K234" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="L234" t="n">
-        <v>-0.08</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="M234" s="10" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -15902,22 +15902,22 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.6323</v>
+        <v>0.625</v>
       </c>
       <c r="H235" t="n">
-        <v>0.6518</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>0.676</v>
+        <v>0.674</v>
       </c>
       <c r="J235" t="n">
-        <v>29.6</v>
+        <v>24.4</v>
       </c>
       <c r="K235" t="n">
-        <v>21.4</v>
+        <v>23.4</v>
       </c>
       <c r="L235" t="n">
-        <v>-0.0018</v>
+        <v>-0.0019</v>
       </c>
       <c r="M235" s="10" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -15965,22 +15965,22 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>709.1900000000001</v>
+        <v>712.5700000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>713.2285000000001</v>
+        <v>713.3795</v>
       </c>
       <c r="I236" t="n">
-        <v>709.9194</v>
+        <v>710.151</v>
       </c>
       <c r="J236" t="n">
-        <v>46.7</v>
+        <v>49.9</v>
       </c>
       <c r="K236" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="L236" t="n">
-        <v>-0.9993</v>
+        <v>-0.7854</v>
       </c>
       <c r="M236" s="10" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -16028,22 +16028,22 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>6.297</v>
+        <v>6.334</v>
       </c>
       <c r="H237" t="n">
-        <v>6.3366</v>
+        <v>6.3386</v>
       </c>
       <c r="I237" t="n">
-        <v>6.2916</v>
+        <v>6.2945</v>
       </c>
       <c r="J237" t="n">
-        <v>46.3</v>
+        <v>50.6</v>
       </c>
       <c r="K237" t="n">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="L237" t="n">
-        <v>-0.0112</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="M237" s="10" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>2026-09-02 10:29</t>
+          <t>2026-09-03 07:48</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -15122,12 +15122,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>3MIB.MI</t>
+          <t>3ITL.MI</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>GraniteShares 3x Long FTSE MIB Daily ETP</t>
+          <t>WisdomTree FTSE MIB 3x Daily Leveraged</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1702,7 +1702,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
     </row>
     <row r="167">
       <c r="A167" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1229,19 +1229,19 @@
         <v>170.69</v>
       </c>
       <c r="H2" t="n">
-        <v>170.8819</v>
+        <v>171.0127</v>
       </c>
       <c r="I2" t="n">
-        <v>170.425</v>
+        <v>169.8794</v>
       </c>
       <c r="J2" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="K2" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3495</v>
+        <v>0.1625</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1292,19 +1292,19 @@
         <v>51.05</v>
       </c>
       <c r="H3" t="n">
-        <v>50.6891</v>
+        <v>50.6959</v>
       </c>
       <c r="I3" t="n">
-        <v>49.9144</v>
+        <v>49.9174</v>
       </c>
       <c r="J3" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="K3" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0472</v>
+        <v>-0.0066</v>
       </c>
       <c r="M3" s="12" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1418,19 +1418,19 @@
         <v>2.9835</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9464</v>
+        <v>2.95</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8645</v>
+        <v>2.8697</v>
       </c>
       <c r="J5" t="n">
         <v>60.7</v>
       </c>
       <c r="K5" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0014</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1481,19 +1481,19 @@
         <v>26.73</v>
       </c>
       <c r="H6" t="n">
-        <v>24.9718</v>
+        <v>25.1431</v>
       </c>
       <c r="I6" t="n">
-        <v>24.9626</v>
+        <v>25.0089</v>
       </c>
       <c r="J6" t="n">
-        <v>70.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>21.5</v>
+        <v>23.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.248</v>
+        <v>0.2912</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1544,19 +1544,19 @@
         <v>213.55</v>
       </c>
       <c r="H7" t="n">
-        <v>209.5716</v>
+        <v>209.8385</v>
       </c>
       <c r="I7" t="n">
-        <v>202.943</v>
+        <v>203.2264</v>
       </c>
       <c r="J7" t="n">
-        <v>63.3</v>
+        <v>63.1</v>
       </c>
       <c r="K7" t="n">
-        <v>32.6</v>
+        <v>31.3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2212</v>
+        <v>0.0893</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1607,19 +1607,19 @@
         <v>541.4</v>
       </c>
       <c r="H8" t="n">
-        <v>522.6022</v>
+        <v>524.3149</v>
       </c>
       <c r="I8" t="n">
-        <v>505.538</v>
+        <v>507.089</v>
       </c>
       <c r="J8" t="n">
         <v>69.8</v>
       </c>
       <c r="K8" t="n">
-        <v>27.9</v>
+        <v>28.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.9727</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1670,19 +1670,19 @@
         <v>40.745</v>
       </c>
       <c r="H9" t="n">
-        <v>42.0155</v>
+        <v>41.885</v>
       </c>
       <c r="I9" t="n">
-        <v>43.0263</v>
+        <v>42.9108</v>
       </c>
       <c r="J9" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="K9" t="n">
-        <v>16.6</v>
+        <v>17.8</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1488</v>
+        <v>-0.1525</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1733,28 +1733,28 @@
         <v>109.62</v>
       </c>
       <c r="H10" t="n">
-        <v>108.8936</v>
+        <v>108.9869</v>
       </c>
       <c r="I10" t="n">
-        <v>105.5302</v>
+        <v>105.7468</v>
       </c>
       <c r="J10" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
-        <v>18.2</v>
+        <v>17.1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2967</v>
-      </c>
-      <c r="M10" s="12" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>-0.2737</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1796,19 +1796,19 @@
         <v>47.295</v>
       </c>
       <c r="H11" t="n">
-        <v>47.301</v>
+        <v>47.3078</v>
       </c>
       <c r="I11" t="n">
-        <v>45.9084</v>
+        <v>45.9903</v>
       </c>
       <c r="J11" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="K11" t="n">
-        <v>29.6</v>
+        <v>27.8</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1559</v>
+        <v>-0.1597</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1827,8 +1827,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>3</v>
+      <c r="A12" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1859,28 +1859,28 @@
         <v>52.43</v>
       </c>
       <c r="H12" t="n">
-        <v>52.5344</v>
+        <v>52.4908</v>
       </c>
       <c r="I12" t="n">
-        <v>52.3832</v>
+        <v>52.3264</v>
       </c>
       <c r="J12" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="K12" t="n">
-        <v>12.1</v>
+        <v>8.1</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0351</v>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>-0.0461</v>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>L0 RECOVERY</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1922,19 +1922,19 @@
         <v>40.59</v>
       </c>
       <c r="H13" t="n">
-        <v>40.2465</v>
+        <v>40.288</v>
       </c>
       <c r="I13" t="n">
-        <v>40.1851</v>
+        <v>40.1394</v>
       </c>
       <c r="J13" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="K13" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0915</v>
+        <v>0.0726</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1982,22 +1982,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>100.68</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>102.1674</v>
+        <v>101.5836</v>
       </c>
       <c r="I14" t="n">
-        <v>104.0024</v>
+        <v>103.816</v>
       </c>
       <c r="J14" t="n">
-        <v>39.6</v>
+        <v>32.3</v>
       </c>
       <c r="K14" t="n">
-        <v>21.5</v>
+        <v>19.2</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0544</v>
+        <v>-0.226</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2048,19 +2048,19 @@
         <v>222.94</v>
       </c>
       <c r="H15" t="n">
-        <v>219.5644</v>
+        <v>219.6532</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1954</v>
+        <v>217.2928</v>
       </c>
       <c r="J15" t="n">
-        <v>59.5</v>
+        <v>59.1</v>
       </c>
       <c r="K15" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0713</v>
+        <v>0.0706</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2111,19 +2111,19 @@
         <v>627.24</v>
       </c>
       <c r="H16" t="n">
-        <v>626.7907</v>
+        <v>626.7585</v>
       </c>
       <c r="I16" t="n">
-        <v>619.8678</v>
+        <v>620.1684</v>
       </c>
       <c r="J16" t="n">
         <v>51.9</v>
       </c>
       <c r="K16" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3305</v>
+        <v>-0.574</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2174,19 +2174,19 @@
         <v>15.644</v>
       </c>
       <c r="H17" t="n">
-        <v>15.5797</v>
+        <v>15.5896</v>
       </c>
       <c r="I17" t="n">
-        <v>14.8385</v>
+        <v>14.8661</v>
       </c>
       <c r="J17" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="K17" t="n">
-        <v>23.2</v>
+        <v>20.7</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0504</v>
+        <v>-0.0639</v>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2237,19 +2237,19 @@
         <v>74.374</v>
       </c>
       <c r="H18" t="n">
-        <v>74.1315</v>
+        <v>74.18559999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>73.8475</v>
+        <v>73.8034</v>
       </c>
       <c r="J18" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="K18" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0921</v>
+        <v>0.0658</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2300,19 +2300,19 @@
         <v>100.79</v>
       </c>
       <c r="H19" t="n">
-        <v>100.474</v>
+        <v>100.5497</v>
       </c>
       <c r="I19" t="n">
-        <v>100.0882</v>
+        <v>100.0296</v>
       </c>
       <c r="J19" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="K19" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1287</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2363,19 +2363,19 @@
         <v>7.6386</v>
       </c>
       <c r="H20" t="n">
-        <v>7.612</v>
+        <v>7.6179</v>
       </c>
       <c r="I20" t="n">
-        <v>7.5808</v>
+        <v>7.5762</v>
       </c>
       <c r="J20" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0103</v>
+        <v>0.0073</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2426,10 +2426,10 @@
         <v>151.53</v>
       </c>
       <c r="H21" t="n">
-        <v>149.1541</v>
+        <v>149.2175</v>
       </c>
       <c r="I21" t="n">
-        <v>147.5914</v>
+        <v>147.6612</v>
       </c>
       <c r="J21" t="n">
         <v>59.6</v>
@@ -2438,7 +2438,7 @@
         <v>10.3</v>
       </c>
       <c r="L21" t="n">
-        <v>0.035</v>
+        <v>0.0446</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2489,19 +2489,19 @@
         <v>74.34999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>74.0342</v>
+        <v>74.0642</v>
       </c>
       <c r="I22" t="n">
-        <v>72.6748</v>
+        <v>72.7762</v>
       </c>
       <c r="J22" t="n">
         <v>54.6</v>
       </c>
       <c r="K22" t="n">
-        <v>13.6</v>
+        <v>15.8</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2015</v>
+        <v>-0.1731</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2552,19 +2552,19 @@
         <v>7.324</v>
       </c>
       <c r="H23" t="n">
-        <v>7.3028</v>
+        <v>7.3085</v>
       </c>
       <c r="I23" t="n">
-        <v>7.2876</v>
+        <v>7.2821</v>
       </c>
       <c r="J23" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="K23" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0101</v>
+        <v>0.0078</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2678,19 +2678,19 @@
         <v>358.51</v>
       </c>
       <c r="H25" t="n">
-        <v>356.087</v>
+        <v>356.0584</v>
       </c>
       <c r="I25" t="n">
-        <v>356.5712</v>
+        <v>356.4476</v>
       </c>
       <c r="J25" t="n">
-        <v>53.3</v>
+        <v>53.6</v>
       </c>
       <c r="K25" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0631</v>
+        <v>0.0047</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2741,19 +2741,19 @@
         <v>98.98999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>99.021</v>
+        <v>99.0569</v>
       </c>
       <c r="I26" t="n">
-        <v>98.73439999999999</v>
+        <v>98.6716</v>
       </c>
       <c r="J26" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="K26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0664</v>
+        <v>0.0309</v>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2804,19 +2804,19 @@
         <v>37.445</v>
       </c>
       <c r="H27" t="n">
-        <v>36.3946</v>
+        <v>36.4925</v>
       </c>
       <c r="I27" t="n">
-        <v>35.1054</v>
+        <v>35.188</v>
       </c>
       <c r="J27" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0523</v>
+        <v>0.0544</v>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2867,19 +2867,19 @@
         <v>127.6273</v>
       </c>
       <c r="H28" t="n">
-        <v>127.4486</v>
+        <v>127.5111</v>
       </c>
       <c r="I28" t="n">
-        <v>126.6366</v>
+        <v>126.5599</v>
       </c>
       <c r="J28" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="K28" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1613</v>
+        <v>0.0708</v>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2930,19 +2930,19 @@
         <v>57.6</v>
       </c>
       <c r="H29" t="n">
-        <v>57.2829</v>
+        <v>57.2985</v>
       </c>
       <c r="I29" t="n">
-        <v>56.258</v>
+        <v>56.3106</v>
       </c>
       <c r="J29" t="n">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
       <c r="K29" t="n">
-        <v>16.6</v>
+        <v>15.3</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2993,19 +2993,19 @@
         <v>473.25</v>
       </c>
       <c r="H30" t="n">
-        <v>474.4213</v>
+        <v>474.3098</v>
       </c>
       <c r="I30" t="n">
-        <v>469.782</v>
+        <v>470.112</v>
       </c>
       <c r="J30" t="n">
         <v>49.5</v>
       </c>
       <c r="K30" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.862</v>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3056,19 +3056,19 @@
         <v>400.05</v>
       </c>
       <c r="H31" t="n">
-        <v>397.5134</v>
+        <v>397.6861</v>
       </c>
       <c r="I31" t="n">
-        <v>388.033</v>
+        <v>388.624</v>
       </c>
       <c r="J31" t="n">
         <v>55.8</v>
       </c>
       <c r="K31" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.2299</v>
+        <v>-1.1068</v>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3119,19 +3119,19 @@
         <v>25.05</v>
       </c>
       <c r="H32" t="n">
-        <v>24.9891</v>
+        <v>24.9984</v>
       </c>
       <c r="I32" t="n">
-        <v>24.4011</v>
+        <v>24.4336</v>
       </c>
       <c r="J32" t="n">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="K32" t="n">
-        <v>26.9</v>
+        <v>25.1</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.0457</v>
+        <v>-0.0467</v>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3182,19 +3182,19 @@
         <v>197.98</v>
       </c>
       <c r="H33" t="n">
-        <v>198.0594</v>
+        <v>198.1656</v>
       </c>
       <c r="I33" t="n">
-        <v>197.3768</v>
+        <v>197.2354</v>
       </c>
       <c r="J33" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="K33" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1476</v>
+        <v>0.0709</v>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3245,19 +3245,19 @@
         <v>7.542</v>
       </c>
       <c r="H34" t="n">
-        <v>7.5439</v>
+        <v>7.5478</v>
       </c>
       <c r="I34" t="n">
-        <v>7.536</v>
+        <v>7.529</v>
       </c>
       <c r="J34" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="K34" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="L34" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0055</v>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3308,19 +3308,19 @@
         <v>68.7</v>
       </c>
       <c r="H35" t="n">
-        <v>70.33159999999999</v>
+        <v>70.1823</v>
       </c>
       <c r="I35" t="n">
-        <v>70.69159999999999</v>
+        <v>70.6478</v>
       </c>
       <c r="J35" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="K35" t="n">
-        <v>18.1</v>
+        <v>20.2</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2699</v>
+        <v>-0.2761</v>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3371,19 +3371,19 @@
         <v>150.9</v>
       </c>
       <c r="H36" t="n">
-        <v>155.0554</v>
+        <v>154.7286</v>
       </c>
       <c r="I36" t="n">
-        <v>153.7312</v>
+        <v>153.7388</v>
       </c>
       <c r="J36" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="K36" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.8032</v>
+        <v>-0.8504</v>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3434,19 +3434,19 @@
         <v>93.42</v>
       </c>
       <c r="H37" t="n">
-        <v>94.5478</v>
+        <v>94.4524</v>
       </c>
       <c r="I37" t="n">
-        <v>95.9924</v>
+        <v>95.941</v>
       </c>
       <c r="J37" t="n">
         <v>42.9</v>
       </c>
       <c r="K37" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.0327</v>
+        <v>-0.0321</v>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3497,19 +3497,19 @@
         <v>70.39</v>
       </c>
       <c r="H38" t="n">
-        <v>69.9235</v>
+        <v>69.9843</v>
       </c>
       <c r="I38" t="n">
-        <v>69.70959999999999</v>
+        <v>69.6996</v>
       </c>
       <c r="J38" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="K38" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1377</v>
+        <v>0.1121</v>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3560,19 +3560,19 @@
         <v>70.59999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>70.3005</v>
+        <v>70.3592</v>
       </c>
       <c r="I39" t="n">
-        <v>69.8938</v>
+        <v>69.874</v>
       </c>
       <c r="J39" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="K39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1257</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3623,19 +3623,19 @@
         <v>328</v>
       </c>
       <c r="H40" t="n">
-        <v>337.7959</v>
+        <v>336.7682</v>
       </c>
       <c r="I40" t="n">
-        <v>341.437</v>
+        <v>341.204</v>
       </c>
       <c r="J40" t="n">
-        <v>27.7</v>
+        <v>29.7</v>
       </c>
       <c r="K40" t="n">
-        <v>23.3</v>
+        <v>21.2</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.4295</v>
+        <v>-1.4919</v>
       </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3686,28 +3686,28 @@
         <v>724.4</v>
       </c>
       <c r="H41" t="n">
-        <v>723.5242</v>
+        <v>723.4353</v>
       </c>
       <c r="I41" t="n">
-        <v>714.17</v>
+        <v>714.64</v>
       </c>
       <c r="J41" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
       <c r="K41" t="n">
-        <v>29.1</v>
+        <v>26.3</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4005</v>
-      </c>
-      <c r="M41" s="12" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>-0.7417</v>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3749,19 +3749,19 @@
         <v>441.65</v>
       </c>
       <c r="H42" t="n">
-        <v>445.0398</v>
+        <v>444.5662</v>
       </c>
       <c r="I42" t="n">
-        <v>442.43</v>
+        <v>442.422</v>
       </c>
       <c r="J42" t="n">
-        <v>44.6</v>
+        <v>45.4</v>
       </c>
       <c r="K42" t="n">
-        <v>16.5</v>
+        <v>17.7</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.4806</v>
+        <v>-0.7028</v>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3812,19 +3812,19 @@
         <v>194.84</v>
       </c>
       <c r="H43" t="n">
-        <v>195.3943</v>
+        <v>195.3088</v>
       </c>
       <c r="I43" t="n">
-        <v>193.3564</v>
+        <v>193.484</v>
       </c>
       <c r="J43" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="K43" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.3823</v>
+        <v>-0.3926</v>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3875,19 +3875,19 @@
         <v>247.3</v>
       </c>
       <c r="H44" t="n">
-        <v>249.464</v>
+        <v>249.2536</v>
       </c>
       <c r="I44" t="n">
-        <v>247.962</v>
+        <v>248.014</v>
       </c>
       <c r="J44" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="K44" t="n">
-        <v>24.1</v>
+        <v>25</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.5991</v>
+        <v>-0.6289</v>
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3938,19 +3938,19 @@
         <v>124.38</v>
       </c>
       <c r="H45" t="n">
-        <v>125.3633</v>
+        <v>125.2628</v>
       </c>
       <c r="I45" t="n">
-        <v>124.6552</v>
+        <v>124.684</v>
       </c>
       <c r="J45" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="K45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.2928</v>
+        <v>-0.303</v>
       </c>
       <c r="M45" s="10" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4001,19 +4001,19 @@
         <v>53.03</v>
       </c>
       <c r="H46" t="n">
-        <v>53.9089</v>
+        <v>53.8252</v>
       </c>
       <c r="I46" t="n">
-        <v>53.7752</v>
+        <v>53.7764</v>
       </c>
       <c r="J46" t="n">
         <v>38</v>
       </c>
       <c r="K46" t="n">
-        <v>14.8</v>
+        <v>16.3</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.1904</v>
+        <v>-0.1934</v>
       </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4064,19 +4064,19 @@
         <v>97.58</v>
       </c>
       <c r="H47" t="n">
-        <v>98.68170000000001</v>
+        <v>98.5656</v>
       </c>
       <c r="I47" t="n">
-        <v>98.28959999999999</v>
+        <v>98.28400000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
       <c r="K47" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.2655</v>
+        <v>-0.2823</v>
       </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4127,19 +4127,19 @@
         <v>443.6</v>
       </c>
       <c r="H48" t="n">
-        <v>447.7552</v>
+        <v>447.325</v>
       </c>
       <c r="I48" t="n">
-        <v>445.583</v>
+        <v>445.647</v>
       </c>
       <c r="J48" t="n">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="K48" t="n">
-        <v>20.8</v>
+        <v>22</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.112</v>
+        <v>-1.1559</v>
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4190,19 +4190,19 @@
         <v>381.87</v>
       </c>
       <c r="H49" t="n">
-        <v>387.7652</v>
+        <v>387.1693</v>
       </c>
       <c r="I49" t="n">
-        <v>390.8042</v>
+        <v>390.4262</v>
       </c>
       <c r="J49" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="K49" t="n">
-        <v>13.4</v>
+        <v>14.5</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.2944</v>
+        <v>-1.2094</v>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4253,19 +4253,19 @@
         <v>6.74</v>
       </c>
       <c r="H50" t="n">
-        <v>6.7893</v>
+        <v>6.7823</v>
       </c>
       <c r="I50" t="n">
-        <v>6.7403</v>
+        <v>6.7415</v>
       </c>
       <c r="J50" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
       <c r="K50" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.0165</v>
+        <v>-0.0179</v>
       </c>
       <c r="M50" s="10" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4316,19 +4316,19 @@
         <v>30.86</v>
       </c>
       <c r="H51" t="n">
-        <v>31.039</v>
+        <v>31.0177</v>
       </c>
       <c r="I51" t="n">
-        <v>31.0207</v>
+        <v>31.0228</v>
       </c>
       <c r="J51" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="K51" t="n">
         <v>19.7</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.0459</v>
+        <v>-0.0488</v>
       </c>
       <c r="M51" s="10" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4379,19 +4379,19 @@
         <v>42.145</v>
       </c>
       <c r="H52" t="n">
-        <v>42.4844</v>
+        <v>42.4465</v>
       </c>
       <c r="I52" t="n">
-        <v>42.5221</v>
+        <v>42.5113</v>
       </c>
       <c r="J52" t="n">
-        <v>42.7</v>
+        <v>43.2</v>
       </c>
       <c r="K52" t="n">
-        <v>15</v>
+        <v>16.4</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.0664</v>
+        <v>-0.073</v>
       </c>
       <c r="M52" s="10" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4442,19 +4442,19 @@
         <v>154.68</v>
       </c>
       <c r="H53" t="n">
-        <v>154.3948</v>
+        <v>154.3599</v>
       </c>
       <c r="I53" t="n">
-        <v>154.9148</v>
+        <v>154.8832</v>
       </c>
       <c r="J53" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="K53" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.1316</v>
+        <v>-0.117</v>
       </c>
       <c r="M53" s="10" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4502,22 +4502,22 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>127.46</v>
+        <v>127.38</v>
       </c>
       <c r="H54" t="n">
-        <v>129.753</v>
+        <v>129.2932</v>
       </c>
       <c r="I54" t="n">
-        <v>129.8964</v>
+        <v>129.816</v>
       </c>
       <c r="J54" t="n">
-        <v>38.9</v>
+        <v>39.5</v>
       </c>
       <c r="K54" t="n">
-        <v>16.4</v>
+        <v>19.5</v>
       </c>
       <c r="L54" t="n">
-        <v>-0.3711</v>
+        <v>-0.4217</v>
       </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4568,19 +4568,19 @@
         <v>124.48</v>
       </c>
       <c r="H55" t="n">
-        <v>125.9301</v>
+        <v>125.7833</v>
       </c>
       <c r="I55" t="n">
-        <v>125.3248</v>
+        <v>125.3296</v>
       </c>
       <c r="J55" t="n">
-        <v>40.8</v>
+        <v>41.1</v>
       </c>
       <c r="K55" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.3442</v>
+        <v>-0.3741</v>
       </c>
       <c r="M55" s="10" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4631,19 +4631,19 @@
         <v>107.54</v>
       </c>
       <c r="H56" t="n">
-        <v>108.5141</v>
+        <v>108.4678</v>
       </c>
       <c r="I56" t="n">
-        <v>110.7284</v>
+        <v>110.4852</v>
       </c>
       <c r="J56" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="K56" t="n">
-        <v>13.3</v>
+        <v>8.4</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.0308</v>
+        <v>0.008</v>
       </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4694,19 +4694,19 @@
         <v>126.96</v>
       </c>
       <c r="H57" t="n">
-        <v>129.5088</v>
+        <v>129.273</v>
       </c>
       <c r="I57" t="n">
-        <v>129.8612</v>
+        <v>129.8148</v>
       </c>
       <c r="J57" t="n">
         <v>36.6</v>
       </c>
       <c r="K57" t="n">
-        <v>17.6</v>
+        <v>15.1</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.4469</v>
+        <v>-0.4594</v>
       </c>
       <c r="M57" s="10" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4757,19 +4757,19 @@
         <v>72.43000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>73.2218</v>
+        <v>73.1455</v>
       </c>
       <c r="I58" t="n">
-        <v>72.54559999999999</v>
+        <v>72.5692</v>
       </c>
       <c r="J58" t="n">
         <v>43.3</v>
       </c>
       <c r="K58" t="n">
-        <v>17.4</v>
+        <v>18.7</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.2459</v>
+        <v>-0.2514</v>
       </c>
       <c r="M58" s="10" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4820,19 +4820,19 @@
         <v>42.75</v>
       </c>
       <c r="H59" t="n">
-        <v>43.2355</v>
+        <v>43.1819</v>
       </c>
       <c r="I59" t="n">
-        <v>42.7489</v>
+        <v>42.7596</v>
       </c>
       <c r="J59" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="K59" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.1489</v>
+        <v>-0.1597</v>
       </c>
       <c r="M59" s="10" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4883,19 +4883,19 @@
         <v>417.45</v>
       </c>
       <c r="H60" t="n">
-        <v>422.662</v>
+        <v>422.1226</v>
       </c>
       <c r="I60" t="n">
-        <v>422.083</v>
+        <v>421.953</v>
       </c>
       <c r="J60" t="n">
-        <v>40.6</v>
+        <v>41</v>
       </c>
       <c r="K60" t="n">
-        <v>16.8</v>
+        <v>18.2</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.1047</v>
+        <v>-1.1732</v>
       </c>
       <c r="M60" s="10" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4946,19 +4946,19 @@
         <v>464.35</v>
       </c>
       <c r="H61" t="n">
-        <v>466.2136</v>
+        <v>466.0577</v>
       </c>
       <c r="I61" t="n">
-        <v>466.53</v>
+        <v>466.504</v>
       </c>
       <c r="J61" t="n">
         <v>47.1</v>
       </c>
       <c r="K61" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.4734</v>
       </c>
       <c r="M61" s="10" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5009,19 +5009,19 @@
         <v>5.121</v>
       </c>
       <c r="H62" t="n">
-        <v>5.1295</v>
+        <v>5.1307</v>
       </c>
       <c r="I62" t="n">
-        <v>5.0981</v>
+        <v>5.1009</v>
       </c>
       <c r="J62" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="K62" t="n">
-        <v>12.7</v>
+        <v>11.5</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.0062</v>
+        <v>-0.005</v>
       </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5072,19 +5072,19 @@
         <v>214.3</v>
       </c>
       <c r="H63" t="n">
-        <v>217.6758</v>
+        <v>217.3327</v>
       </c>
       <c r="I63" t="n">
-        <v>217.224</v>
+        <v>217.155</v>
       </c>
       <c r="J63" t="n">
-        <v>39.3</v>
+        <v>39.6</v>
       </c>
       <c r="K63" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.6783</v>
+        <v>-0.7389</v>
       </c>
       <c r="M63" s="10" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5135,19 +5135,19 @@
         <v>91.72</v>
       </c>
       <c r="H64" t="n">
-        <v>92.54219999999999</v>
+        <v>92.4579</v>
       </c>
       <c r="I64" t="n">
-        <v>92.3716</v>
+        <v>92.361</v>
       </c>
       <c r="J64" t="n">
-        <v>42.4</v>
+        <v>42.7</v>
       </c>
       <c r="K64" t="n">
-        <v>14.4</v>
+        <v>15.9</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.1597</v>
+        <v>-0.1826</v>
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5198,19 +5198,19 @@
         <v>41.795</v>
       </c>
       <c r="H65" t="n">
-        <v>42.7297</v>
+        <v>42.6386</v>
       </c>
       <c r="I65" t="n">
-        <v>43.3969</v>
+        <v>43.3715</v>
       </c>
       <c r="J65" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="K65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.09</v>
+        <v>-0.0944</v>
       </c>
       <c r="M65" s="10" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5258,22 +5258,22 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>170.01</v>
+        <v>168.26</v>
       </c>
       <c r="H66" t="n">
-        <v>170.3675</v>
+        <v>169.9628</v>
       </c>
       <c r="I66" t="n">
-        <v>173.2114</v>
+        <v>172.5788</v>
       </c>
       <c r="J66" t="n">
-        <v>47.9</v>
+        <v>44.2</v>
       </c>
       <c r="K66" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>0.1728</v>
+        <v>0.016</v>
       </c>
       <c r="M66" s="10" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5387,19 +5387,19 @@
         <v>606.48</v>
       </c>
       <c r="H68" t="n">
-        <v>607.1697</v>
+        <v>607.1626</v>
       </c>
       <c r="I68" t="n">
-        <v>603.7334</v>
+        <v>603.9362</v>
       </c>
       <c r="J68" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="K68" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6294</v>
       </c>
       <c r="M68" s="10" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5513,19 +5513,19 @@
         <v>5.1646</v>
       </c>
       <c r="H70" t="n">
-        <v>5.1895</v>
+        <v>5.1867</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2041</v>
+        <v>5.2026</v>
       </c>
       <c r="J70" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K70" t="n">
-        <v>13.1</v>
+        <v>14.7</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="M70" s="10" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5585,10 +5585,10 @@
         <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.0075</v>
+        <v>-0.0074</v>
       </c>
       <c r="M71" s="10" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5639,19 +5639,19 @@
         <v>150.45</v>
       </c>
       <c r="H72" t="n">
-        <v>151.9005</v>
+        <v>151.7425</v>
       </c>
       <c r="I72" t="n">
-        <v>153.1302</v>
+        <v>153.011</v>
       </c>
       <c r="J72" t="n">
-        <v>33.8</v>
+        <v>35.2</v>
       </c>
       <c r="K72" t="n">
-        <v>27.8</v>
+        <v>29.2</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.1455</v>
+        <v>-0.1561</v>
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5702,19 +5702,19 @@
         <v>529.61</v>
       </c>
       <c r="H73" t="n">
-        <v>523.7103</v>
+        <v>524.2308</v>
       </c>
       <c r="I73" t="n">
-        <v>515.4462</v>
+        <v>516.046</v>
       </c>
       <c r="J73" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="K73" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="L73" t="n">
-        <v>-0.7509</v>
+        <v>-0.6631</v>
       </c>
       <c r="M73" s="10" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5765,19 +5765,19 @@
         <v>195.46</v>
       </c>
       <c r="H74" t="n">
-        <v>197.6123</v>
+        <v>197.3771</v>
       </c>
       <c r="I74" t="n">
-        <v>199.5082</v>
+        <v>199.3248</v>
       </c>
       <c r="J74" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="K74" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="L74" t="n">
-        <v>-0.183</v>
+        <v>-0.2049</v>
       </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5828,19 +5828,19 @@
         <v>4.9045</v>
       </c>
       <c r="H75" t="n">
-        <v>4.938</v>
+        <v>4.9366</v>
       </c>
       <c r="I75" t="n">
-        <v>4.9449</v>
+        <v>4.9442</v>
       </c>
       <c r="J75" t="n">
-        <v>38.1</v>
+        <v>37.7</v>
       </c>
       <c r="K75" t="n">
-        <v>25.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>-0.0026</v>
+        <v>-0.0031</v>
       </c>
       <c r="M75" s="10" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5891,19 +5891,19 @@
         <v>126.81</v>
       </c>
       <c r="H76" t="n">
-        <v>127.0063</v>
+        <v>126.9862</v>
       </c>
       <c r="I76" t="n">
-        <v>126.293</v>
+        <v>126.347</v>
       </c>
       <c r="J76" t="n">
         <v>49.7</v>
       </c>
       <c r="K76" t="n">
-        <v>12.9</v>
+        <v>10.7</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.1733</v>
+        <v>-0.1616</v>
       </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5954,19 +5954,19 @@
         <v>226.66</v>
       </c>
       <c r="H77" t="n">
-        <v>227.6057</v>
+        <v>227.4881</v>
       </c>
       <c r="I77" t="n">
-        <v>228.2508</v>
+        <v>228.1808</v>
       </c>
       <c r="J77" t="n">
-        <v>36.9</v>
+        <v>37.5</v>
       </c>
       <c r="K77" t="n">
-        <v>16</v>
+        <v>16.9</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.1464</v>
+        <v>-0.1518</v>
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6017,19 +6017,19 @@
         <v>14.186</v>
       </c>
       <c r="H78" t="n">
-        <v>14.1637</v>
+        <v>14.1587</v>
       </c>
       <c r="I78" t="n">
-        <v>13.8975</v>
+        <v>13.9108</v>
       </c>
       <c r="J78" t="n">
-        <v>55.7</v>
+        <v>54.9</v>
       </c>
       <c r="K78" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.0261</v>
+        <v>-0.0311</v>
       </c>
       <c r="M78" s="10" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6080,19 +6080,19 @@
         <v>267.1</v>
       </c>
       <c r="H79" t="n">
-        <v>267.7584</v>
+        <v>267.6914</v>
       </c>
       <c r="I79" t="n">
-        <v>264.884</v>
+        <v>265.059</v>
       </c>
       <c r="J79" t="n">
         <v>49.6</v>
       </c>
       <c r="K79" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.5051</v>
+        <v>-0.5153</v>
       </c>
       <c r="M79" s="10" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6143,19 +6143,19 @@
         <v>53.84</v>
       </c>
       <c r="H80" t="n">
-        <v>54.1315</v>
+        <v>54.1037</v>
       </c>
       <c r="I80" t="n">
-        <v>54.2928</v>
+        <v>54.276</v>
       </c>
       <c r="J80" t="n">
         <v>33</v>
       </c>
       <c r="K80" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.039</v>
+        <v>-0.0404</v>
       </c>
       <c r="M80" s="10" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6206,19 +6206,19 @@
         <v>266.1</v>
       </c>
       <c r="H81" t="n">
-        <v>273.1033</v>
+        <v>272.4751</v>
       </c>
       <c r="I81" t="n">
-        <v>275.62</v>
+        <v>275.261</v>
       </c>
       <c r="J81" t="n">
         <v>36.6</v>
       </c>
       <c r="K81" t="n">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="L81" t="n">
-        <v>-0.61</v>
+        <v>-0.6988</v>
       </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6269,19 +6269,19 @@
         <v>150.425</v>
       </c>
       <c r="H82" t="n">
-        <v>151.6702</v>
+        <v>151.5326</v>
       </c>
       <c r="I82" t="n">
-        <v>152.6904</v>
+        <v>152.5893</v>
       </c>
       <c r="J82" t="n">
-        <v>32.9</v>
+        <v>34.6</v>
       </c>
       <c r="K82" t="n">
-        <v>27.1</v>
+        <v>28.6</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.1119</v>
+        <v>-0.1273</v>
       </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6332,19 +6332,19 @@
         <v>229.65</v>
       </c>
       <c r="H83" t="n">
-        <v>231.0585</v>
+        <v>230.8899</v>
       </c>
       <c r="I83" t="n">
-        <v>232.3216</v>
+        <v>232.193</v>
       </c>
       <c r="J83" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="K83" t="n">
-        <v>20.3</v>
+        <v>21.8</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.1371</v>
+        <v>-0.153</v>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6392,22 +6392,22 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>135.99</v>
+        <v>136.09</v>
       </c>
       <c r="H84" t="n">
-        <v>136.7469</v>
+        <v>136.6843</v>
       </c>
       <c r="I84" t="n">
-        <v>137.1614</v>
+        <v>137.1218</v>
       </c>
       <c r="J84" t="n">
-        <v>31.9</v>
+        <v>34.7</v>
       </c>
       <c r="K84" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.0707</v>
+        <v>-0.0789</v>
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6458,19 +6458,19 @@
         <v>45.115</v>
       </c>
       <c r="H85" t="n">
-        <v>45.3668</v>
+        <v>45.3351</v>
       </c>
       <c r="I85" t="n">
-        <v>45.5762</v>
+        <v>45.554</v>
       </c>
       <c r="J85" t="n">
-        <v>33</v>
+        <v>36.1</v>
       </c>
       <c r="K85" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.0256</v>
+        <v>-0.0294</v>
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6521,19 +6521,19 @@
         <v>232.24</v>
       </c>
       <c r="H86" t="n">
-        <v>233.7513</v>
+        <v>233.5841</v>
       </c>
       <c r="I86" t="n">
-        <v>234.821</v>
+        <v>234.71</v>
       </c>
       <c r="J86" t="n">
-        <v>32.9</v>
+        <v>34.6</v>
       </c>
       <c r="K86" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.1427</v>
+        <v>-0.1671</v>
       </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6584,19 +6584,19 @@
         <v>689.5599999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>690.7818</v>
+        <v>690.6809</v>
       </c>
       <c r="I87" t="n">
-        <v>687.1748</v>
+        <v>687.4616</v>
       </c>
       <c r="J87" t="n">
         <v>49.4</v>
       </c>
       <c r="K87" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="L87" t="n">
-        <v>-0.9376</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6647,19 +6647,19 @@
         <v>426.86</v>
       </c>
       <c r="H88" t="n">
-        <v>427.791</v>
+        <v>427.7291</v>
       </c>
       <c r="I88" t="n">
-        <v>425.4596</v>
+        <v>425.641</v>
       </c>
       <c r="J88" t="n">
         <v>49.1</v>
       </c>
       <c r="K88" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.6018</v>
+        <v>-0.5607</v>
       </c>
       <c r="M88" s="10" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6710,19 +6710,19 @@
         <v>266.31</v>
       </c>
       <c r="H89" t="n">
-        <v>267.6551</v>
+        <v>267.5959</v>
       </c>
       <c r="I89" t="n">
-        <v>267.7444</v>
+        <v>267.7364</v>
       </c>
       <c r="J89" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="K89" t="n">
-        <v>16.5</v>
+        <v>18.1</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.1749</v>
+        <v>-0.1857</v>
       </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6773,19 +6773,19 @@
         <v>41.061</v>
       </c>
       <c r="H90" t="n">
-        <v>41.3408</v>
+        <v>41.3098</v>
       </c>
       <c r="I90" t="n">
-        <v>41.5762</v>
+        <v>41.5527</v>
       </c>
       <c r="J90" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="K90" t="n">
-        <v>26.8</v>
+        <v>28</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.0241</v>
+        <v>-0.0275</v>
       </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6836,19 +6836,19 @@
         <v>7.2324</v>
       </c>
       <c r="H91" t="n">
-        <v>7.3026</v>
+        <v>7.2946</v>
       </c>
       <c r="I91" t="n">
-        <v>7.3726</v>
+        <v>7.366</v>
       </c>
       <c r="J91" t="n">
-        <v>32.8</v>
+        <v>34.8</v>
       </c>
       <c r="K91" t="n">
-        <v>30.5</v>
+        <v>31.4</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.0052</v>
+        <v>-0.0059</v>
       </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6899,19 +6899,19 @@
         <v>18.914</v>
       </c>
       <c r="H92" t="n">
-        <v>18.9473</v>
+        <v>18.9448</v>
       </c>
       <c r="I92" t="n">
-        <v>18.8428</v>
+        <v>18.8508</v>
       </c>
       <c r="J92" t="n">
         <v>49.5</v>
       </c>
       <c r="K92" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.0265</v>
+        <v>-0.0245</v>
       </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6962,19 +6962,19 @@
         <v>217.32</v>
       </c>
       <c r="H93" t="n">
-        <v>218.8478</v>
+        <v>218.6816</v>
       </c>
       <c r="I93" t="n">
-        <v>220.1126</v>
+        <v>219.9874</v>
       </c>
       <c r="J93" t="n">
-        <v>34.4</v>
+        <v>35.7</v>
       </c>
       <c r="K93" t="n">
-        <v>21.9</v>
+        <v>23.4</v>
       </c>
       <c r="L93" t="n">
-        <v>-0.1189</v>
+        <v>-0.1404</v>
       </c>
       <c r="M93" s="10" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7025,19 +7025,19 @@
         <v>48.385</v>
       </c>
       <c r="H94" t="n">
-        <v>48.7133</v>
+        <v>48.6738</v>
       </c>
       <c r="I94" t="n">
-        <v>49.0128</v>
+        <v>48.9852</v>
       </c>
       <c r="J94" t="n">
-        <v>34.8</v>
+        <v>36.9</v>
       </c>
       <c r="K94" t="n">
-        <v>25.4</v>
+        <v>26.9</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.0281</v>
+        <v>-0.0326</v>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7088,19 +7088,19 @@
         <v>54.98</v>
       </c>
       <c r="H95" t="n">
-        <v>55.1821</v>
+        <v>55.1663</v>
       </c>
       <c r="I95" t="n">
-        <v>55.246</v>
+        <v>55.238</v>
       </c>
       <c r="J95" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="K95" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.0279</v>
+        <v>-0.0292</v>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7151,19 +7151,19 @@
         <v>136.13</v>
       </c>
       <c r="H96" t="n">
-        <v>136.7966</v>
+        <v>136.7142</v>
       </c>
       <c r="I96" t="n">
-        <v>137.2466</v>
+        <v>137.1962</v>
       </c>
       <c r="J96" t="n">
-        <v>33.9</v>
+        <v>36.7</v>
       </c>
       <c r="K96" t="n">
-        <v>15.2</v>
+        <v>17.5</v>
       </c>
       <c r="L96" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0965</v>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7211,22 +7211,22 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>22.66</v>
+        <v>22.69</v>
       </c>
       <c r="H97" t="n">
-        <v>22.7039</v>
+        <v>22.6984</v>
       </c>
       <c r="I97" t="n">
-        <v>22.68</v>
+        <v>22.6779</v>
       </c>
       <c r="J97" t="n">
-        <v>46.9</v>
+        <v>49.8</v>
       </c>
       <c r="K97" t="n">
-        <v>10.9</v>
+        <v>7.3</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.004</v>
+        <v>-0.0081</v>
       </c>
       <c r="M97" s="10" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7277,19 +7277,19 @@
         <v>24.52</v>
       </c>
       <c r="H98" t="n">
-        <v>24.52</v>
+        <v>24.5183</v>
       </c>
       <c r="I98" t="n">
-        <v>24.5852</v>
+        <v>24.5576</v>
       </c>
       <c r="J98" t="n">
         <v>50</v>
       </c>
       <c r="K98" t="n">
-        <v>13.2</v>
+        <v>9.5</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0106</v>
+        <v>0.0046</v>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7340,19 +7340,19 @@
         <v>195.34</v>
       </c>
       <c r="H99" t="n">
-        <v>195.6975</v>
+        <v>195.7109</v>
       </c>
       <c r="I99" t="n">
-        <v>194.0084</v>
+        <v>194.085</v>
       </c>
       <c r="J99" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="K99" t="n">
-        <v>16.5</v>
+        <v>15.3</v>
       </c>
       <c r="L99" t="n">
-        <v>-0.3479</v>
+        <v>-0.318</v>
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7403,19 +7403,19 @@
         <v>48.76</v>
       </c>
       <c r="H100" t="n">
-        <v>49.1</v>
+        <v>49.0641</v>
       </c>
       <c r="I100" t="n">
-        <v>49.3829</v>
+        <v>49.3545</v>
       </c>
       <c r="J100" t="n">
-        <v>31.3</v>
+        <v>32.7</v>
       </c>
       <c r="K100" t="n">
-        <v>24.7</v>
+        <v>26.1</v>
       </c>
       <c r="L100" t="n">
-        <v>-0.0295</v>
+        <v>-0.0331</v>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7466,19 +7466,19 @@
         <v>130.285</v>
       </c>
       <c r="H101" t="n">
-        <v>130.8589</v>
+        <v>130.8021</v>
       </c>
       <c r="I101" t="n">
-        <v>131.1885</v>
+        <v>131.1525</v>
       </c>
       <c r="J101" t="n">
-        <v>33.5</v>
+        <v>33.9</v>
       </c>
       <c r="K101" t="n">
-        <v>20.3</v>
+        <v>21.8</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.0622</v>
+        <v>-0.0699</v>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7526,22 +7526,22 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>7.207</v>
+        <v>7.287</v>
       </c>
       <c r="H102" t="n">
-        <v>7.2307</v>
+        <v>7.2355</v>
       </c>
       <c r="I102" t="n">
-        <v>7.1356</v>
+        <v>7.1469</v>
       </c>
       <c r="J102" t="n">
-        <v>49.3</v>
+        <v>58.3</v>
       </c>
       <c r="K102" t="n">
-        <v>13.9</v>
+        <v>13.1</v>
       </c>
       <c r="L102" t="n">
-        <v>-0.0136</v>
+        <v>-0.0097</v>
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7592,19 +7592,19 @@
         <v>137.185</v>
       </c>
       <c r="H103" t="n">
-        <v>139.2617</v>
+        <v>139.0488</v>
       </c>
       <c r="I103" t="n">
-        <v>141.4093</v>
+        <v>141.2105</v>
       </c>
       <c r="J103" t="n">
-        <v>33.4</v>
+        <v>34.2</v>
       </c>
       <c r="K103" t="n">
-        <v>30.7</v>
+        <v>31.5</v>
       </c>
       <c r="L103" t="n">
-        <v>-0.1265</v>
+        <v>-0.1398</v>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7655,19 +7655,19 @@
         <v>104.58</v>
       </c>
       <c r="H104" t="n">
-        <v>104.7091</v>
+        <v>104.6925</v>
       </c>
       <c r="I104" t="n">
-        <v>104.7448</v>
+        <v>104.7368</v>
       </c>
       <c r="J104" t="n">
-        <v>41.1</v>
+        <v>42.3</v>
       </c>
       <c r="K104" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="L104" t="n">
-        <v>-0.0205</v>
+        <v>-0.0242</v>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7718,19 +7718,19 @@
         <v>106.66</v>
       </c>
       <c r="H105" t="n">
-        <v>107.2965</v>
+        <v>107.2282</v>
       </c>
       <c r="I105" t="n">
-        <v>107.5082</v>
+        <v>107.4778</v>
       </c>
       <c r="J105" t="n">
-        <v>2.8</v>
+        <v>12.5</v>
       </c>
       <c r="K105" t="n">
-        <v>38.4</v>
+        <v>41.3</v>
       </c>
       <c r="L105" t="n">
-        <v>-0.0347</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7781,19 +7781,19 @@
         <v>200.09</v>
       </c>
       <c r="H106" t="n">
-        <v>201.5899</v>
+        <v>201.4367</v>
       </c>
       <c r="I106" t="n">
-        <v>202.8602</v>
+        <v>202.739</v>
       </c>
       <c r="J106" t="n">
-        <v>28</v>
+        <v>29.3</v>
       </c>
       <c r="K106" t="n">
-        <v>28.2</v>
+        <v>29.3</v>
       </c>
       <c r="L106" t="n">
-        <v>-0.1178</v>
+        <v>-0.1322</v>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7844,19 +7844,19 @@
         <v>113.18</v>
       </c>
       <c r="H107" t="n">
-        <v>113.0016</v>
+        <v>113.0178</v>
       </c>
       <c r="I107" t="n">
-        <v>112.815</v>
+        <v>112.829</v>
       </c>
       <c r="J107" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="K107" t="n">
-        <v>78.2</v>
+        <v>78.7</v>
       </c>
       <c r="L107" t="n">
-        <v>0.0048</v>
+        <v>0.0062</v>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7907,19 +7907,19 @@
         <v>5.073</v>
       </c>
       <c r="H108" t="n">
-        <v>5.0656</v>
+        <v>5.0659</v>
       </c>
       <c r="I108" t="n">
-        <v>5.0571</v>
+        <v>5.0575</v>
       </c>
       <c r="J108" t="n">
-        <v>69</v>
+        <v>67.3</v>
       </c>
       <c r="K108" t="n">
-        <v>10.8</v>
+        <v>31</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7970,19 +7970,19 @@
         <v>75.04600000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>75.184</v>
+        <v>75.1734</v>
       </c>
       <c r="I109" t="n">
-        <v>75.0574</v>
+        <v>75.059</v>
       </c>
       <c r="J109" t="n">
         <v>46.7</v>
       </c>
       <c r="K109" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="L109" t="n">
-        <v>-0.023</v>
+        <v>-0.032</v>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8033,19 +8033,19 @@
         <v>118.9</v>
       </c>
       <c r="H110" t="n">
-        <v>119.0894</v>
+        <v>119.0696</v>
       </c>
       <c r="I110" t="n">
-        <v>119.1234</v>
+        <v>119.1142</v>
       </c>
       <c r="J110" t="n">
-        <v>37.3</v>
+        <v>38</v>
       </c>
       <c r="K110" t="n">
-        <v>12.3</v>
+        <v>13.7</v>
       </c>
       <c r="L110" t="n">
-        <v>-0.0263</v>
+        <v>-0.0319</v>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8096,19 +8096,19 @@
         <v>107.89</v>
       </c>
       <c r="H111" t="n">
-        <v>107.2083</v>
+        <v>107.2724</v>
       </c>
       <c r="I111" t="n">
-        <v>106.1442</v>
+        <v>106.2534</v>
       </c>
       <c r="J111" t="n">
         <v>55.1</v>
       </c>
       <c r="K111" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="L111" t="n">
-        <v>-0.0098</v>
+        <v>-0.0016</v>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8159,19 +8159,19 @@
         <v>127.79</v>
       </c>
       <c r="H112" t="n">
-        <v>127.9371</v>
+        <v>127.9162</v>
       </c>
       <c r="I112" t="n">
-        <v>127.9776</v>
+        <v>127.9678</v>
       </c>
       <c r="J112" t="n">
-        <v>41</v>
+        <v>42.6</v>
       </c>
       <c r="K112" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="L112" t="n">
-        <v>-0.0239</v>
+        <v>-0.0288</v>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8222,19 +8222,19 @@
         <v>101.42</v>
       </c>
       <c r="H113" t="n">
-        <v>101.5256</v>
+        <v>101.5104</v>
       </c>
       <c r="I113" t="n">
-        <v>101.5868</v>
+        <v>101.579</v>
       </c>
       <c r="J113" t="n">
-        <v>30.4</v>
+        <v>36.7</v>
       </c>
       <c r="K113" t="n">
-        <v>25.4</v>
+        <v>26</v>
       </c>
       <c r="L113" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0146</v>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8348,10 +8348,10 @@
         <v>54.404</v>
       </c>
       <c r="H115" t="n">
-        <v>54.4552</v>
+        <v>54.4515</v>
       </c>
       <c r="I115" t="n">
-        <v>54.4377</v>
+        <v>54.4372</v>
       </c>
       <c r="J115" t="n">
         <v>42.5</v>
@@ -8360,7 +8360,7 @@
         <v>15.9</v>
       </c>
       <c r="L115" t="n">
-        <v>-0.0105</v>
+        <v>-0.0115</v>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8474,19 +8474,19 @@
         <v>410.81</v>
       </c>
       <c r="H117" t="n">
-        <v>409.1847</v>
+        <v>409.1474</v>
       </c>
       <c r="I117" t="n">
-        <v>405.6088</v>
+        <v>405.9928</v>
       </c>
       <c r="J117" t="n">
-        <v>54.8</v>
+        <v>55</v>
       </c>
       <c r="K117" t="n">
-        <v>23.5</v>
+        <v>16.9</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.457</v>
+        <v>-0.4287</v>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -8537,19 +8537,19 @@
         <v>41.9</v>
       </c>
       <c r="H118" t="n">
-        <v>42.785</v>
+        <v>42.7063</v>
       </c>
       <c r="I118" t="n">
-        <v>42.8611</v>
+        <v>42.8464</v>
       </c>
       <c r="J118" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="K118" t="n">
-        <v>28.5</v>
+        <v>30.6</v>
       </c>
       <c r="L118" t="n">
-        <v>-0.1834</v>
+        <v>-0.1735</v>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -8600,19 +8600,19 @@
         <v>628.2</v>
       </c>
       <c r="H119" t="n">
-        <v>629.2101</v>
+        <v>629.1396999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>625.65</v>
+        <v>625.936</v>
       </c>
       <c r="J119" t="n">
         <v>49.7</v>
       </c>
       <c r="K119" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="L119" t="n">
-        <v>-0.799</v>
+        <v>-0.7564</v>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8663,19 +8663,19 @@
         <v>138.85</v>
       </c>
       <c r="H120" t="n">
-        <v>138.6636</v>
+        <v>138.6762</v>
       </c>
       <c r="I120" t="n">
-        <v>138.2826</v>
+        <v>138.3038</v>
       </c>
       <c r="J120" t="n">
-        <v>55.6</v>
+        <v>55.4</v>
       </c>
       <c r="K120" t="n">
-        <v>26.4</v>
+        <v>29.9</v>
       </c>
       <c r="L120" t="n">
-        <v>0.032</v>
+        <v>0.0151</v>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>15.59780025482178</v>
+        <v>15.5978</v>
       </c>
       <c r="H121" t="n">
         <v>15.4142</v>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>127.1699981689453</v>
+        <v>127.17</v>
       </c>
       <c r="H122" t="n">
         <v>126.4026</v>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>114.379997253418</v>
+        <v>114.38</v>
       </c>
       <c r="H123" t="n">
         <v>113.6715</v>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -8915,19 +8915,19 @@
         <v>20.805</v>
       </c>
       <c r="H124" t="n">
-        <v>20.8829</v>
+        <v>20.8833</v>
       </c>
       <c r="I124" t="n">
-        <v>20.5568</v>
+        <v>20.5731</v>
       </c>
       <c r="J124" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="K124" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="L124" t="n">
-        <v>-0.0436</v>
+        <v>-0.0413</v>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -8978,19 +8978,19 @@
         <v>48.615</v>
       </c>
       <c r="H125" t="n">
-        <v>48.7094</v>
+        <v>48.6918</v>
       </c>
       <c r="I125" t="n">
-        <v>49.0068</v>
+        <v>48.9834</v>
       </c>
       <c r="J125" t="n">
-        <v>42.1</v>
+        <v>43.2</v>
       </c>
       <c r="K125" t="n">
-        <v>21.4</v>
+        <v>19.3</v>
       </c>
       <c r="L125" t="n">
-        <v>0.0073</v>
+        <v>0.0067</v>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -9041,19 +9041,19 @@
         <v>63.37</v>
       </c>
       <c r="H126" t="n">
-        <v>63.5548</v>
+        <v>63.5389</v>
       </c>
       <c r="I126" t="n">
-        <v>63.2466</v>
+        <v>63.2572</v>
       </c>
       <c r="J126" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="K126" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="L126" t="n">
-        <v>-0.0254</v>
+        <v>-0.0433</v>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -9164,22 +9164,22 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>330.35</v>
+        <v>330.65</v>
       </c>
       <c r="H128" t="n">
-        <v>339.1591</v>
+        <v>337.3613</v>
       </c>
       <c r="I128" t="n">
-        <v>341.435</v>
+        <v>341.28</v>
       </c>
       <c r="J128" t="n">
-        <v>27.2</v>
+        <v>33.2</v>
       </c>
       <c r="K128" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="L128" t="n">
-        <v>-1.188</v>
+        <v>-1.3223</v>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -9227,22 +9227,22 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>43.04</v>
+        <v>43.225</v>
       </c>
       <c r="H129" t="n">
-        <v>41.8717</v>
+        <v>42.0006</v>
       </c>
       <c r="I129" t="n">
-        <v>40.1412</v>
+        <v>40.2513</v>
       </c>
       <c r="J129" t="n">
-        <v>67.8</v>
+        <v>69.2</v>
       </c>
       <c r="K129" t="n">
-        <v>28.2</v>
+        <v>29.4</v>
       </c>
       <c r="L129" t="n">
-        <v>0.0329</v>
+        <v>0.044</v>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -9290,22 +9290,22 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>10.35</v>
+        <v>10.344</v>
       </c>
       <c r="H130" t="n">
-        <v>10.3606</v>
+        <v>10.359</v>
       </c>
       <c r="I130" t="n">
-        <v>10.4206</v>
+        <v>10.4169</v>
       </c>
       <c r="J130" t="n">
-        <v>46.6</v>
+        <v>45.6</v>
       </c>
       <c r="K130" t="n">
-        <v>19.1</v>
+        <v>11.7</v>
       </c>
       <c r="L130" t="n">
-        <v>0.0026</v>
+        <v>0.0029</v>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -9419,19 +9419,19 @@
         <v>154.81</v>
       </c>
       <c r="H132" t="n">
-        <v>155.3831</v>
+        <v>155.3251</v>
       </c>
       <c r="I132" t="n">
-        <v>155.5402</v>
+        <v>155.4966</v>
       </c>
       <c r="J132" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="K132" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="L132" t="n">
-        <v>-0.0285</v>
+        <v>-0.0615</v>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -9479,22 +9479,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>7.219</v>
+        <v>7.239</v>
       </c>
       <c r="H133" t="n">
-        <v>7.2443</v>
+        <v>7.2441</v>
       </c>
       <c r="I133" t="n">
-        <v>7.1381</v>
+        <v>7.1482</v>
       </c>
       <c r="J133" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="K133" t="n">
-        <v>17.5</v>
+        <v>16.7</v>
       </c>
       <c r="L133" t="n">
-        <v>-0.0143</v>
+        <v>-0.0145</v>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -9545,19 +9545,19 @@
         <v>145.43</v>
       </c>
       <c r="H134" t="n">
-        <v>146.1636</v>
+        <v>146.0864</v>
       </c>
       <c r="I134" t="n">
-        <v>147.7544</v>
+        <v>147.6443</v>
       </c>
       <c r="J134" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="K134" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="L134" t="n">
-        <v>0.0351</v>
+        <v>0.0337</v>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -9608,19 +9608,19 @@
         <v>180.82</v>
       </c>
       <c r="H135" t="n">
-        <v>180.986</v>
+        <v>180.9779</v>
       </c>
       <c r="I135" t="n">
-        <v>178.8666</v>
+        <v>179.0004</v>
       </c>
       <c r="J135" t="n">
         <v>51</v>
       </c>
       <c r="K135" t="n">
-        <v>17.4</v>
+        <v>16.4</v>
       </c>
       <c r="L135" t="n">
-        <v>-0.3224</v>
+        <v>-0.3182</v>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -9668,22 +9668,22 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>69.59</v>
+        <v>69.52</v>
       </c>
       <c r="H136" t="n">
-        <v>69.7289</v>
+        <v>69.68940000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>70.43680000000001</v>
+        <v>70.3472</v>
       </c>
       <c r="J136" t="n">
-        <v>43.3</v>
+        <v>42</v>
       </c>
       <c r="K136" t="n">
-        <v>22</v>
+        <v>18.7</v>
       </c>
       <c r="L136" t="n">
-        <v>0.0301</v>
+        <v>0.0364</v>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -9734,19 +9734,19 @@
         <v>132.12</v>
       </c>
       <c r="H137" t="n">
-        <v>132.2751</v>
+        <v>132.2818</v>
       </c>
       <c r="I137" t="n">
-        <v>131.6736</v>
+        <v>131.736</v>
       </c>
       <c r="J137" t="n">
         <v>49.8</v>
       </c>
       <c r="K137" t="n">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="L137" t="n">
-        <v>-0.1469</v>
+        <v>-0.1259</v>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -9797,19 +9797,19 @@
         <v>72.67</v>
       </c>
       <c r="H138" t="n">
-        <v>72.9255</v>
+        <v>72.896</v>
       </c>
       <c r="I138" t="n">
-        <v>73.2274</v>
+        <v>73.19159999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>39.9</v>
+        <v>40.7</v>
       </c>
       <c r="K138" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0067</v>
+        <v>-0.006</v>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -9860,19 +9860,19 @@
         <v>18.403</v>
       </c>
       <c r="H139" t="n">
-        <v>18.4737</v>
+        <v>18.4646</v>
       </c>
       <c r="I139" t="n">
-        <v>18.7025</v>
+        <v>18.6858</v>
       </c>
       <c r="J139" t="n">
-        <v>41.3</v>
+        <v>42.1</v>
       </c>
       <c r="K139" t="n">
-        <v>19.8</v>
+        <v>22.9</v>
       </c>
       <c r="L139" t="n">
-        <v>0.0151</v>
+        <v>0.0133</v>
       </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -9923,19 +9923,19 @@
         <v>46.08</v>
       </c>
       <c r="H140" t="n">
-        <v>46.175</v>
+        <v>46.1513</v>
       </c>
       <c r="I140" t="n">
-        <v>46.3394</v>
+        <v>46.3195</v>
       </c>
       <c r="J140" t="n">
-        <v>43.8</v>
+        <v>44.8</v>
       </c>
       <c r="K140" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="L140" t="n">
-        <v>-0.0126</v>
+        <v>-0.0154</v>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9983,22 +9983,22 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>80.8</v>
+        <v>80.55</v>
       </c>
       <c r="H141" t="n">
-        <v>80.8793</v>
+        <v>80.8146</v>
       </c>
       <c r="I141" t="n">
-        <v>81.8058</v>
+        <v>81.68219999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>45.4</v>
+        <v>41.8</v>
       </c>
       <c r="K141" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="L141" t="n">
-        <v>0.0584</v>
+        <v>0.0509</v>
       </c>
       <c r="M141" s="10" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -10049,19 +10049,19 @@
         <v>44.635</v>
       </c>
       <c r="H142" t="n">
-        <v>44.7277</v>
+        <v>44.7072</v>
       </c>
       <c r="I142" t="n">
-        <v>45.0566</v>
+        <v>45.0312</v>
       </c>
       <c r="J142" t="n">
-        <v>41.2</v>
+        <v>42.3</v>
       </c>
       <c r="K142" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="L142" t="n">
-        <v>0.0012</v>
+        <v>0.0034</v>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -10175,19 +10175,19 @@
         <v>89.77</v>
       </c>
       <c r="H144" t="n">
-        <v>91.1065</v>
+        <v>90.98520000000001</v>
       </c>
       <c r="I144" t="n">
-        <v>89.173</v>
+        <v>89.2256</v>
       </c>
       <c r="J144" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="K144" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="L144" t="n">
-        <v>-0.3385</v>
+        <v>-0.4182</v>
       </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -10238,19 +10238,19 @@
         <v>121.3</v>
       </c>
       <c r="H145" t="n">
-        <v>123.0781</v>
+        <v>122.926</v>
       </c>
       <c r="I145" t="n">
-        <v>121.4209</v>
+        <v>121.4541</v>
       </c>
       <c r="J145" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="K145" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="L145" t="n">
-        <v>-0.4002</v>
+        <v>-0.4772</v>
       </c>
       <c r="M145" s="10" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -10301,19 +10301,19 @@
         <v>115.72</v>
       </c>
       <c r="H146" t="n">
-        <v>117.7196</v>
+        <v>117.4947</v>
       </c>
       <c r="I146" t="n">
-        <v>116.9164</v>
+        <v>116.8492</v>
       </c>
       <c r="J146" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="K146" t="n">
-        <v>17.8</v>
+        <v>11.9</v>
       </c>
       <c r="L146" t="n">
-        <v>-0.4655</v>
+        <v>-0.5125</v>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -10364,19 +10364,19 @@
         <v>23.02</v>
       </c>
       <c r="H147" t="n">
-        <v>23.6163</v>
+        <v>23.591</v>
       </c>
       <c r="I147" t="n">
-        <v>23.4232</v>
+        <v>23.4558</v>
       </c>
       <c r="J147" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="K147" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="L147" t="n">
-        <v>-0.0985</v>
+        <v>-0.0905</v>
       </c>
       <c r="M147" s="10" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -10427,19 +10427,19 @@
         <v>100</v>
       </c>
       <c r="H148" t="n">
-        <v>102.5599</v>
+        <v>102.4479</v>
       </c>
       <c r="I148" t="n">
-        <v>101.7204</v>
+        <v>101.8634</v>
       </c>
       <c r="J148" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="K148" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="L148" t="n">
-        <v>-0.4224</v>
+        <v>-0.39</v>
       </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -10490,19 +10490,19 @@
         <v>61.68</v>
       </c>
       <c r="H149" t="n">
-        <v>61.8074</v>
+        <v>61.7918</v>
       </c>
       <c r="I149" t="n">
-        <v>60.6251</v>
+        <v>60.6908</v>
       </c>
       <c r="J149" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="K149" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="L149" t="n">
-        <v>-0.1631</v>
+        <v>-0.1738</v>
       </c>
       <c r="M149" s="10" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -10550,22 +10550,22 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>6.356</v>
+        <v>6.37</v>
       </c>
       <c r="H150" t="n">
-        <v>6.3697</v>
+        <v>6.3699</v>
       </c>
       <c r="I150" t="n">
-        <v>6.3278</v>
+        <v>6.3333</v>
       </c>
       <c r="J150" t="n">
-        <v>49.5</v>
+        <v>51.1</v>
       </c>
       <c r="K150" t="n">
-        <v>16.3</v>
+        <v>11.6</v>
       </c>
       <c r="L150" t="n">
-        <v>-0.0091</v>
+        <v>-0.0072</v>
       </c>
       <c r="M150" s="10" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -10616,19 +10616,19 @@
         <v>138.14</v>
       </c>
       <c r="H151" t="n">
-        <v>139.234</v>
+        <v>139.1436</v>
       </c>
       <c r="I151" t="n">
-        <v>137.1532</v>
+        <v>137.2224</v>
       </c>
       <c r="J151" t="n">
         <v>46.5</v>
       </c>
       <c r="K151" t="n">
-        <v>22.9</v>
+        <v>21.8</v>
       </c>
       <c r="L151" t="n">
-        <v>-0.3193</v>
+        <v>-0.3908</v>
       </c>
       <c r="M151" s="10" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10679,19 +10679,19 @@
         <v>4.9945</v>
       </c>
       <c r="H152" t="n">
-        <v>5.0089</v>
+        <v>5.0078</v>
       </c>
       <c r="I152" t="n">
-        <v>4.9825</v>
+        <v>4.9838</v>
       </c>
       <c r="J152" t="n">
         <v>48.5</v>
       </c>
       <c r="K152" t="n">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="L152" t="n">
-        <v>-0.0078</v>
+        <v>-0.0073</v>
       </c>
       <c r="M152" s="10" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -10742,19 +10742,19 @@
         <v>25.365</v>
       </c>
       <c r="H153" t="n">
-        <v>25.4319</v>
+        <v>25.429</v>
       </c>
       <c r="I153" t="n">
-        <v>25.5531</v>
+        <v>25.5447</v>
       </c>
       <c r="J153" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="K153" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="L153" t="n">
-        <v>-0.0143</v>
+        <v>-0.0074</v>
       </c>
       <c r="M153" s="10" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -10805,19 +10805,19 @@
         <v>97.94</v>
       </c>
       <c r="H154" t="n">
-        <v>97.3844</v>
+        <v>97.4106</v>
       </c>
       <c r="I154" t="n">
-        <v>96.42</v>
+        <v>96.527</v>
       </c>
       <c r="J154" t="n">
-        <v>56.9</v>
+        <v>56.5</v>
       </c>
       <c r="K154" t="n">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="L154" t="n">
-        <v>-0.0278</v>
+        <v>-0.0389</v>
       </c>
       <c r="M154" s="10" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -10868,19 +10868,19 @@
         <v>801.1</v>
       </c>
       <c r="H155" t="n">
-        <v>804.6944999999999</v>
+        <v>804.6072</v>
       </c>
       <c r="I155" t="n">
-        <v>807.7592</v>
+        <v>807.5454</v>
       </c>
       <c r="J155" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="K155" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="L155" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.4188</v>
       </c>
       <c r="M155" s="10" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -10931,19 +10931,19 @@
         <v>195.82</v>
       </c>
       <c r="H156" t="n">
-        <v>203.3282</v>
+        <v>202.7924</v>
       </c>
       <c r="I156" t="n">
-        <v>206.5314</v>
+        <v>206.278</v>
       </c>
       <c r="J156" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="K156" t="n">
-        <v>14.3</v>
+        <v>17.7</v>
       </c>
       <c r="L156" t="n">
-        <v>-0.8287</v>
+        <v>-0.8369</v>
       </c>
       <c r="M156" s="10" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -10994,19 +10994,19 @@
         <v>657</v>
       </c>
       <c r="H157" t="n">
-        <v>661.6235</v>
+        <v>661.1573</v>
       </c>
       <c r="I157" t="n">
-        <v>660.162</v>
+        <v>660.03</v>
       </c>
       <c r="J157" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="K157" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="L157" t="n">
-        <v>-0.9408</v>
+        <v>-1.0801</v>
       </c>
       <c r="M157" s="10" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -11054,22 +11054,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>20.465</v>
+        <v>20.49</v>
       </c>
       <c r="H158" t="n">
-        <v>20.5909</v>
+        <v>20.5933</v>
       </c>
       <c r="I158" t="n">
-        <v>20.5431</v>
+        <v>20.5436</v>
       </c>
       <c r="J158" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="K158" t="n">
         <v>10.8</v>
       </c>
       <c r="L158" t="n">
-        <v>-0.0277</v>
+        <v>-0.0261</v>
       </c>
       <c r="M158" s="10" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -11117,22 +11117,22 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>19.484</v>
+        <v>19.16</v>
       </c>
       <c r="H159" t="n">
-        <v>19.5634</v>
+        <v>19.4998</v>
       </c>
       <c r="I159" t="n">
-        <v>19.3045</v>
+        <v>19.3064</v>
       </c>
       <c r="J159" t="n">
-        <v>49.9</v>
+        <v>47.7</v>
       </c>
       <c r="K159" t="n">
-        <v>10.2</v>
+        <v>7.7</v>
       </c>
       <c r="L159" t="n">
-        <v>-0.056</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="M159" s="10" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -11246,19 +11246,19 @@
         <v>287.7</v>
       </c>
       <c r="H161" t="n">
-        <v>289.8962</v>
+        <v>289.7215</v>
       </c>
       <c r="I161" t="n">
-        <v>291.373</v>
+        <v>291.227</v>
       </c>
       <c r="J161" t="n">
         <v>46.1</v>
       </c>
       <c r="K161" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="L161" t="n">
-        <v>-0.2307</v>
+        <v>-0.2491</v>
       </c>
       <c r="M161" s="10" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -11309,19 +11309,19 @@
         <v>26</v>
       </c>
       <c r="H162" t="n">
-        <v>26.7484</v>
+        <v>26.7069</v>
       </c>
       <c r="I162" t="n">
-        <v>26.964</v>
+        <v>26.9481</v>
       </c>
       <c r="J162" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="K162" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="L162" t="n">
-        <v>-0.0581</v>
+        <v>-0.0664</v>
       </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -11372,19 +11372,19 @@
         <v>16.154</v>
       </c>
       <c r="H163" t="n">
-        <v>16.1731</v>
+        <v>16.1662</v>
       </c>
       <c r="I163" t="n">
-        <v>16.0849</v>
+        <v>16.0941</v>
       </c>
       <c r="J163" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="K163" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="L163" t="n">
-        <v>-0.0187</v>
+        <v>-0.0198</v>
       </c>
       <c r="M163" s="10" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -11435,19 +11435,19 @@
         <v>138.12</v>
       </c>
       <c r="H164" t="n">
-        <v>141.0267</v>
+        <v>140.7714</v>
       </c>
       <c r="I164" t="n">
-        <v>140.096</v>
+        <v>140.0976</v>
       </c>
       <c r="J164" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="K164" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="L164" t="n">
-        <v>-0.3861</v>
+        <v>-0.4823</v>
       </c>
       <c r="M164" s="10" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -11498,28 +11498,28 @@
         <v>74.02</v>
       </c>
       <c r="H165" t="n">
-        <v>72.815</v>
+        <v>72.8944</v>
       </c>
       <c r="I165" t="n">
-        <v>71.67359999999999</v>
+        <v>71.756</v>
       </c>
       <c r="J165" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="K165" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="L165" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="M165" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0342</v>
+      </c>
+      <c r="M165" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -11561,19 +11561,19 @@
         <v>1180.36</v>
       </c>
       <c r="H166" t="n">
-        <v>1179.4772</v>
+        <v>1179.7008</v>
       </c>
       <c r="I166" t="n">
-        <v>1169.1894</v>
+        <v>1169.7084</v>
       </c>
       <c r="J166" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="K166" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="L166" t="n">
-        <v>-0.7855</v>
+        <v>-0.7988</v>
       </c>
       <c r="M166" s="10" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -11621,31 +11621,31 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>21.09</v>
+        <v>20.925</v>
       </c>
       <c r="H167" t="n">
-        <v>20.9905</v>
+        <v>20.9697</v>
       </c>
       <c r="I167" t="n">
-        <v>20.4821</v>
+        <v>20.5298</v>
       </c>
       <c r="J167" t="n">
-        <v>53.8</v>
+        <v>50.8</v>
       </c>
       <c r="K167" t="n">
-        <v>18.5</v>
+        <v>13.8</v>
       </c>
       <c r="L167" t="n">
-        <v>-0.0071</v>
-      </c>
-      <c r="M167" s="12" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>-0.0483</v>
+      </c>
+      <c r="M167" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -11687,19 +11687,19 @@
         <v>5.874</v>
       </c>
       <c r="H168" t="n">
-        <v>6.1861</v>
+        <v>6.1599</v>
       </c>
       <c r="I168" t="n">
-        <v>6.0581</v>
+        <v>6.0656</v>
       </c>
       <c r="J168" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="K168" t="n">
-        <v>27.4</v>
+        <v>27.8</v>
       </c>
       <c r="L168" t="n">
-        <v>-0.0779</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="M168" s="10" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11750,19 +11750,19 @@
         <v>410.53</v>
       </c>
       <c r="H169" t="n">
-        <v>410.9533</v>
+        <v>410.4549</v>
       </c>
       <c r="I169" t="n">
-        <v>391.415</v>
+        <v>392.0822</v>
       </c>
       <c r="J169" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="K169" t="n">
-        <v>29.3</v>
+        <v>21.6</v>
       </c>
       <c r="L169" t="n">
-        <v>-1.368</v>
+        <v>-2.0906</v>
       </c>
       <c r="M169" s="10" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -11813,19 +11813,19 @@
         <v>51.61</v>
       </c>
       <c r="H170" t="n">
-        <v>51.5412</v>
+        <v>51.4979</v>
       </c>
       <c r="I170" t="n">
-        <v>48.8773</v>
+        <v>48.9662</v>
       </c>
       <c r="J170" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="K170" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="L170" t="n">
-        <v>-0.1798</v>
+        <v>-0.2551</v>
       </c>
       <c r="M170" s="10" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -11876,19 +11876,19 @@
         <v>166.63</v>
       </c>
       <c r="H171" t="n">
-        <v>166.7715</v>
+        <v>166.6662</v>
       </c>
       <c r="I171" t="n">
-        <v>165.8478</v>
+        <v>165.8752</v>
       </c>
       <c r="J171" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="K171" t="n">
-        <v>11.8</v>
+        <v>10.2</v>
       </c>
       <c r="L171" t="n">
-        <v>-0.1669</v>
+        <v>-0.2048</v>
       </c>
       <c r="M171" s="10" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -12002,19 +12002,19 @@
         <v>28.845</v>
       </c>
       <c r="H173" t="n">
-        <v>29.6989</v>
+        <v>29.6038</v>
       </c>
       <c r="I173" t="n">
-        <v>30.2572</v>
+        <v>30.2213</v>
       </c>
       <c r="J173" t="n">
-        <v>25.3</v>
+        <v>28.9</v>
       </c>
       <c r="K173" t="n">
-        <v>30.6</v>
+        <v>25.7</v>
       </c>
       <c r="L173" t="n">
-        <v>-0.1077</v>
+        <v>-0.1096</v>
       </c>
       <c r="M173" s="10" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -12065,19 +12065,19 @@
         <v>9.988</v>
       </c>
       <c r="H174" t="n">
-        <v>10.2231</v>
+        <v>10.1871</v>
       </c>
       <c r="I174" t="n">
-        <v>10.6097</v>
+        <v>10.5736</v>
       </c>
       <c r="J174" t="n">
-        <v>39.4</v>
+        <v>40.8</v>
       </c>
       <c r="K174" t="n">
-        <v>16.3</v>
+        <v>15.6</v>
       </c>
       <c r="L174" t="n">
-        <v>-0.0027</v>
+        <v>-0.0062</v>
       </c>
       <c r="M174" s="10" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -12128,19 +12128,19 @@
         <v>203.8</v>
       </c>
       <c r="H175" t="n">
-        <v>203.6575</v>
+        <v>203.6372</v>
       </c>
       <c r="I175" t="n">
-        <v>202.2688</v>
+        <v>202.1248</v>
       </c>
       <c r="J175" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="K175" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="L175" t="n">
-        <v>0.0165</v>
+        <v>-0.0766</v>
       </c>
       <c r="M175" s="10" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -12191,19 +12191,19 @@
         <v>274.05</v>
       </c>
       <c r="H176" t="n">
-        <v>274.6628</v>
+        <v>274.4924</v>
       </c>
       <c r="I176" t="n">
-        <v>270.522</v>
+        <v>270.71</v>
       </c>
       <c r="J176" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="K176" t="n">
-        <v>28.8</v>
+        <v>27.4</v>
       </c>
       <c r="L176" t="n">
-        <v>-0.7786</v>
+        <v>-0.8004</v>
       </c>
       <c r="M176" s="10" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -12254,19 +12254,19 @@
         <v>33.04</v>
       </c>
       <c r="H177" t="n">
-        <v>33.4616</v>
+        <v>33.415</v>
       </c>
       <c r="I177" t="n">
-        <v>34.0588</v>
+        <v>34.0324</v>
       </c>
       <c r="J177" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="K177" t="n">
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="L177" t="n">
-        <v>-0.023</v>
+        <v>-0.0227</v>
       </c>
       <c r="M177" s="10" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -12317,19 +12317,19 @@
         <v>158.06</v>
       </c>
       <c r="H178" t="n">
-        <v>158.6551</v>
+        <v>158.5812</v>
       </c>
       <c r="I178" t="n">
-        <v>159.0628</v>
+        <v>159.0172</v>
       </c>
       <c r="J178" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
       <c r="K178" t="n">
-        <v>17.3</v>
+        <v>16.1</v>
       </c>
       <c r="L178" t="n">
-        <v>-0.0653</v>
+        <v>-0.077</v>
       </c>
       <c r="M178" s="10" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -12380,19 +12380,19 @@
         <v>70.63</v>
       </c>
       <c r="H179" t="n">
-        <v>69.9538</v>
+        <v>70.00700000000001</v>
       </c>
       <c r="I179" t="n">
-        <v>69.2212</v>
+        <v>69.2154</v>
       </c>
       <c r="J179" t="n">
         <v>57.7</v>
       </c>
       <c r="K179" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="L179" t="n">
-        <v>-0.0021</v>
+        <v>0.0021</v>
       </c>
       <c r="M179" s="10" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -12443,19 +12443,19 @@
         <v>10.564</v>
       </c>
       <c r="H180" t="n">
-        <v>10.6222</v>
+        <v>10.6146</v>
       </c>
       <c r="I180" t="n">
-        <v>10.5018</v>
+        <v>10.505</v>
       </c>
       <c r="J180" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="K180" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="L180" t="n">
-        <v>-0.0272</v>
+        <v>-0.03</v>
       </c>
       <c r="M180" s="10" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -12506,19 +12506,19 @@
         <v>81.75</v>
       </c>
       <c r="H181" t="n">
-        <v>81.3439</v>
+        <v>81.343</v>
       </c>
       <c r="I181" t="n">
-        <v>80.6242</v>
+        <v>80.66759999999999</v>
       </c>
       <c r="J181" t="n">
-        <v>59.1</v>
+        <v>58.2</v>
       </c>
       <c r="K181" t="n">
-        <v>20.8</v>
+        <v>19.7</v>
       </c>
       <c r="L181" t="n">
-        <v>-0.0485</v>
+        <v>-0.0538</v>
       </c>
       <c r="M181" s="10" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -12632,19 +12632,19 @@
         <v>114.08</v>
       </c>
       <c r="H183" t="n">
-        <v>115.6117</v>
+        <v>115.4348</v>
       </c>
       <c r="I183" t="n">
-        <v>116.334</v>
+        <v>116.2074</v>
       </c>
       <c r="J183" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="K183" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L183" t="n">
-        <v>-0.3092</v>
+        <v>-0.3249</v>
       </c>
       <c r="M183" s="10" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -12695,19 +12695,19 @@
         <v>89.64</v>
       </c>
       <c r="H184" t="n">
-        <v>90.07259999999999</v>
+        <v>90.0288</v>
       </c>
       <c r="I184" t="n">
-        <v>88.8934</v>
+        <v>88.96339999999999</v>
       </c>
       <c r="J184" t="n">
         <v>48.1</v>
       </c>
       <c r="K184" t="n">
-        <v>27.5</v>
+        <v>26.3</v>
       </c>
       <c r="L184" t="n">
-        <v>-0.2019</v>
+        <v>-0.2221</v>
       </c>
       <c r="M184" s="10" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -12758,19 +12758,19 @@
         <v>78.39</v>
       </c>
       <c r="H185" t="n">
-        <v>77.98</v>
+        <v>78.0104</v>
       </c>
       <c r="I185" t="n">
-        <v>76.372</v>
+        <v>76.4682</v>
       </c>
       <c r="J185" t="n">
         <v>63</v>
       </c>
       <c r="K185" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="L185" t="n">
-        <v>-0.0992</v>
+        <v>-0.1153</v>
       </c>
       <c r="M185" s="10" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -12821,19 +12821,19 @@
         <v>18.884</v>
       </c>
       <c r="H186" t="n">
-        <v>18.1304</v>
+        <v>18.1537</v>
       </c>
       <c r="I186" t="n">
-        <v>18.0734</v>
+        <v>18.084</v>
       </c>
       <c r="J186" t="n">
-        <v>68.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="K186" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="L186" t="n">
-        <v>0.1056</v>
+        <v>0.101</v>
       </c>
       <c r="M186" s="12" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -12884,19 +12884,19 @@
         <v>39.865</v>
       </c>
       <c r="H187" t="n">
-        <v>39.576</v>
+        <v>39.6186</v>
       </c>
       <c r="I187" t="n">
-        <v>39.2076</v>
+        <v>39.2032</v>
       </c>
       <c r="J187" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
       <c r="K187" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="L187" t="n">
-        <v>0.0538</v>
+        <v>0.0395</v>
       </c>
       <c r="M187" s="10" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -12947,19 +12947,19 @@
         <v>52.57</v>
       </c>
       <c r="H188" t="n">
-        <v>52.9733</v>
+        <v>52.9368</v>
       </c>
       <c r="I188" t="n">
-        <v>52.4684</v>
+        <v>52.4926</v>
       </c>
       <c r="J188" t="n">
         <v>43.7</v>
       </c>
       <c r="K188" t="n">
-        <v>15.1</v>
+        <v>17.1</v>
       </c>
       <c r="L188" t="n">
-        <v>-0.1307</v>
+        <v>-0.1378</v>
       </c>
       <c r="M188" s="10" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -13007,22 +13007,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>8.445</v>
+        <v>8.448</v>
       </c>
       <c r="H189" t="n">
-        <v>8.4511</v>
+        <v>8.445399999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>8.3383</v>
+        <v>8.349600000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
       <c r="K189" t="n">
-        <v>15.9</v>
+        <v>16.6</v>
       </c>
       <c r="L189" t="n">
-        <v>-0.0103</v>
+        <v>-0.0157</v>
       </c>
       <c r="M189" s="10" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -13073,19 +13073,19 @@
         <v>17.094</v>
       </c>
       <c r="H190" t="n">
-        <v>17.0732</v>
+        <v>17.0792</v>
       </c>
       <c r="I190" t="n">
-        <v>16.8896</v>
+        <v>16.9027</v>
       </c>
       <c r="J190" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="K190" t="n">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
       <c r="L190" t="n">
-        <v>0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="M190" s="10" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -13136,19 +13136,19 @@
         <v>48.235</v>
       </c>
       <c r="H191" t="n">
-        <v>48.6994</v>
+        <v>48.6768</v>
       </c>
       <c r="I191" t="n">
-        <v>48.1534</v>
+        <v>48.1979</v>
       </c>
       <c r="J191" t="n">
         <v>45.8</v>
       </c>
       <c r="K191" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L191" t="n">
-        <v>-0.1056</v>
+        <v>-0.1067</v>
       </c>
       <c r="M191" s="10" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -13199,19 +13199,19 @@
         <v>3.808</v>
       </c>
       <c r="H192" t="n">
-        <v>3.7622</v>
+        <v>3.7665</v>
       </c>
       <c r="I192" t="n">
-        <v>3.7317</v>
+        <v>3.7334</v>
       </c>
       <c r="J192" t="n">
         <v>57</v>
       </c>
       <c r="K192" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="L192" t="n">
-        <v>0.0066</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M192" s="12" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -13262,19 +13262,19 @@
         <v>11.486</v>
       </c>
       <c r="H193" t="n">
-        <v>11.2923</v>
+        <v>11.3141</v>
       </c>
       <c r="I193" t="n">
-        <v>10.939</v>
+        <v>10.9632</v>
       </c>
       <c r="J193" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="K193" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="L193" t="n">
-        <v>0.0254</v>
+        <v>0.0156</v>
       </c>
       <c r="M193" s="10" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -13322,22 +13322,22 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>10.254</v>
+        <v>10.36</v>
       </c>
       <c r="H194" t="n">
-        <v>10.1352</v>
+        <v>10.1677</v>
       </c>
       <c r="I194" t="n">
-        <v>9.4206</v>
+        <v>9.4754</v>
       </c>
       <c r="J194" t="n">
-        <v>56.3</v>
+        <v>58.6</v>
       </c>
       <c r="K194" t="n">
-        <v>27</v>
+        <v>22.6</v>
       </c>
       <c r="L194" t="n">
-        <v>0.0032</v>
+        <v>-0.0319</v>
       </c>
       <c r="M194" s="10" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -13388,19 +13388,19 @@
         <v>26.83</v>
       </c>
       <c r="H195" t="n">
-        <v>27.5534</v>
+        <v>27.469</v>
       </c>
       <c r="I195" t="n">
-        <v>27.9788</v>
+        <v>27.8999</v>
       </c>
       <c r="J195" t="n">
-        <v>40.2</v>
+        <v>41</v>
       </c>
       <c r="K195" t="n">
-        <v>15.4</v>
+        <v>16.7</v>
       </c>
       <c r="L195" t="n">
-        <v>-0.0347</v>
+        <v>-0.0611</v>
       </c>
       <c r="M195" s="10" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -13451,19 +13451,19 @@
         <v>4.619</v>
       </c>
       <c r="H196" t="n">
-        <v>4.7656</v>
+        <v>4.7526</v>
       </c>
       <c r="I196" t="n">
-        <v>4.8564</v>
+        <v>4.8511</v>
       </c>
       <c r="J196" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="K196" t="n">
-        <v>30.9</v>
+        <v>33</v>
       </c>
       <c r="L196" t="n">
-        <v>-0.0179</v>
+        <v>-0.0172</v>
       </c>
       <c r="M196" s="10" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -13514,19 +13514,19 @@
         <v>84.26000000000001</v>
       </c>
       <c r="H197" t="n">
-        <v>85.8818</v>
+        <v>85.69629999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>86.0277</v>
+        <v>85.9927</v>
       </c>
       <c r="J197" t="n">
-        <v>35.9</v>
+        <v>37.5</v>
       </c>
       <c r="K197" t="n">
-        <v>29.6</v>
+        <v>31.8</v>
       </c>
       <c r="L197" t="n">
-        <v>-0.3627</v>
+        <v>-0.353</v>
       </c>
       <c r="M197" s="10" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>150.0950012207031</v>
+        <v>150.095</v>
       </c>
       <c r="H198" t="n">
         <v>149.1741</v>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -13640,19 +13640,19 @@
         <v>141.03</v>
       </c>
       <c r="H199" t="n">
-        <v>141.1302</v>
+        <v>141.1138</v>
       </c>
       <c r="I199" t="n">
-        <v>141.1284</v>
+        <v>141.1226</v>
       </c>
       <c r="J199" t="n">
-        <v>44</v>
+        <v>45.3</v>
       </c>
       <c r="K199" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="L199" t="n">
-        <v>-0.0213</v>
+        <v>-0.0258</v>
       </c>
       <c r="M199" s="10" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -13703,19 +13703,19 @@
         <v>157.48</v>
       </c>
       <c r="H200" t="n">
-        <v>157.5864</v>
+        <v>157.5853</v>
       </c>
       <c r="I200" t="n">
-        <v>155.6416</v>
+        <v>155.7426</v>
       </c>
       <c r="J200" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="K200" t="n">
-        <v>37.4</v>
+        <v>13.8</v>
       </c>
       <c r="L200" t="n">
-        <v>-0.262</v>
+        <v>-0.2661</v>
       </c>
       <c r="M200" s="10" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -13766,19 +13766,19 @@
         <v>119.61</v>
       </c>
       <c r="H201" t="n">
-        <v>119.8859</v>
+        <v>119.8616</v>
       </c>
       <c r="I201" t="n">
-        <v>118.4907</v>
+        <v>118.5611</v>
       </c>
       <c r="J201" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="K201" t="n">
-        <v>20.5</v>
+        <v>14.5</v>
       </c>
       <c r="L201" t="n">
-        <v>-0.2161</v>
+        <v>-0.2266</v>
       </c>
       <c r="M201" s="10" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -13829,19 +13829,19 @@
         <v>366.86</v>
       </c>
       <c r="H202" t="n">
-        <v>367.5635</v>
+        <v>367.1397</v>
       </c>
       <c r="I202" t="n">
-        <v>353.634</v>
+        <v>354.0886</v>
       </c>
       <c r="J202" t="n">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="K202" t="n">
-        <v>26.1</v>
+        <v>20.3</v>
       </c>
       <c r="L202" t="n">
-        <v>-1.556</v>
+        <v>-1.9259</v>
       </c>
       <c r="M202" s="10" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -13892,19 +13892,19 @@
         <v>7.773</v>
       </c>
       <c r="H203" t="n">
-        <v>7.3064</v>
+        <v>7.3428</v>
       </c>
       <c r="I203" t="n">
-        <v>6.6279</v>
+        <v>6.6634</v>
       </c>
       <c r="J203" t="n">
-        <v>68</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K203" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="L203" t="n">
-        <v>0.0653</v>
+        <v>0.0389</v>
       </c>
       <c r="M203" s="10" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -13955,19 +13955,19 @@
         <v>30.56</v>
       </c>
       <c r="H204" t="n">
-        <v>29.5112</v>
+        <v>29.6275</v>
       </c>
       <c r="I204" t="n">
-        <v>28.4572</v>
+        <v>28.5372</v>
       </c>
       <c r="J204" t="n">
-        <v>71.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K204" t="n">
-        <v>27.1</v>
+        <v>26.3</v>
       </c>
       <c r="L204" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0999</v>
       </c>
       <c r="M204" s="10" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -14018,19 +14018,19 @@
         <v>123.7</v>
       </c>
       <c r="H205" t="n">
-        <v>123.5745</v>
+        <v>123.6003</v>
       </c>
       <c r="I205" t="n">
-        <v>122.4608</v>
+        <v>122.5164</v>
       </c>
       <c r="J205" t="n">
         <v>51</v>
       </c>
       <c r="K205" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="L205" t="n">
-        <v>-0.0885</v>
+        <v>-0.0873</v>
       </c>
       <c r="M205" s="10" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -14081,19 +14081,19 @@
         <v>37.955</v>
       </c>
       <c r="H206" t="n">
-        <v>39.3367</v>
+        <v>39.2052</v>
       </c>
       <c r="I206" t="n">
-        <v>39.1081</v>
+        <v>39.1562</v>
       </c>
       <c r="J206" t="n">
         <v>42.8</v>
       </c>
       <c r="K206" t="n">
-        <v>17.1</v>
+        <v>15.6</v>
       </c>
       <c r="L206" t="n">
-        <v>-0.1957</v>
+        <v>-0.2412</v>
       </c>
       <c r="M206" s="10" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -14144,19 +14144,19 @@
         <v>9.353</v>
       </c>
       <c r="H207" t="n">
-        <v>9.4611</v>
+        <v>9.4472</v>
       </c>
       <c r="I207" t="n">
-        <v>9.4922</v>
+        <v>9.482100000000001</v>
       </c>
       <c r="J207" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="K207" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="L207" t="n">
-        <v>-0.0177</v>
+        <v>-0.0213</v>
       </c>
       <c r="M207" s="10" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -14207,19 +14207,19 @@
         <v>8.617000000000001</v>
       </c>
       <c r="H208" t="n">
-        <v>8.820499999999999</v>
+        <v>8.794499999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>9.229100000000001</v>
+        <v>9.196099999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>38.3</v>
+        <v>39.1</v>
       </c>
       <c r="K208" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="L208" t="n">
-        <v>0.0066</v>
+        <v>0.0062</v>
       </c>
       <c r="M208" s="10" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -14270,19 +14270,19 @@
         <v>85.8925</v>
       </c>
       <c r="H209" t="n">
-        <v>85.99039999999999</v>
+        <v>85.8867</v>
       </c>
       <c r="I209" t="n">
-        <v>81.869</v>
+        <v>82.0097</v>
       </c>
       <c r="J209" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="K209" t="n">
-        <v>30.5</v>
+        <v>28.7</v>
       </c>
       <c r="L209" t="n">
-        <v>-0.2908</v>
+        <v>-0.4402</v>
       </c>
       <c r="M209" s="10" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -14333,19 +14333,19 @@
         <v>139.25</v>
       </c>
       <c r="H210" t="n">
-        <v>140.1547</v>
+        <v>140.0082</v>
       </c>
       <c r="I210" t="n">
-        <v>133.9866</v>
+        <v>134.1894</v>
       </c>
       <c r="J210" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="K210" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="L210" t="n">
-        <v>-0.4768</v>
+        <v>-0.6744</v>
       </c>
       <c r="M210" s="10" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -14393,22 +14393,22 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>55.42</v>
+        <v>62.6</v>
       </c>
       <c r="H211" t="n">
-        <v>51.6312</v>
+        <v>53.3935</v>
       </c>
       <c r="I211" t="n">
-        <v>47.3096</v>
+        <v>48.0007</v>
       </c>
       <c r="J211" t="n">
-        <v>71.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K211" t="n">
-        <v>31.4</v>
+        <v>35.8</v>
       </c>
       <c r="L211" t="n">
-        <v>0.7014</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="M211" s="10" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -14456,22 +14456,22 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>64.08</v>
+        <v>59.14</v>
       </c>
       <c r="H212" t="n">
-        <v>58.1733</v>
+        <v>58.3211</v>
       </c>
       <c r="I212" t="n">
-        <v>50.9928</v>
+        <v>51.6433</v>
       </c>
       <c r="J212" t="n">
-        <v>75</v>
+        <v>56.4</v>
       </c>
       <c r="K212" t="n">
-        <v>37.3</v>
+        <v>34.3</v>
       </c>
       <c r="L212" t="n">
-        <v>0.9488</v>
+        <v>-0.0234</v>
       </c>
       <c r="M212" s="10" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -14582,19 +14582,19 @@
         <v>59.245</v>
       </c>
       <c r="H214" t="n">
-        <v>55.6672</v>
+        <v>55.9644</v>
       </c>
       <c r="I214" t="n">
-        <v>50.9684</v>
+        <v>51.2217</v>
       </c>
       <c r="J214" t="n">
-        <v>68.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K214" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="L214" t="n">
-        <v>0.5461</v>
+        <v>0.3596</v>
       </c>
       <c r="M214" s="10" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -14645,19 +14645,19 @@
         <v>94.48</v>
       </c>
       <c r="H215" t="n">
-        <v>87.7599</v>
+        <v>88.2771</v>
       </c>
       <c r="I215" t="n">
-        <v>78.4885</v>
+        <v>78.9953</v>
       </c>
       <c r="J215" t="n">
-        <v>68.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K215" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="L215" t="n">
-        <v>1.0298</v>
+        <v>0.6381</v>
       </c>
       <c r="M215" s="10" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -14705,22 +14705,22 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>34.85</v>
+        <v>35.6</v>
       </c>
       <c r="H216" t="n">
-        <v>32.4034</v>
+        <v>32.4748</v>
       </c>
       <c r="I216" t="n">
-        <v>30.1817</v>
+        <v>30.1967</v>
       </c>
       <c r="J216" t="n">
-        <v>56.3</v>
+        <v>57.7</v>
       </c>
       <c r="K216" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="L216" t="n">
-        <v>-0.0125</v>
+        <v>0.0353</v>
       </c>
       <c r="M216" s="10" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -14768,22 +14768,22 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.228</v>
+        <v>0.2003</v>
       </c>
       <c r="H217" t="n">
-        <v>0.252</v>
+        <v>0.2471</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3056</v>
+        <v>0.3023</v>
       </c>
       <c r="J217" t="n">
-        <v>40.3</v>
+        <v>34.7</v>
       </c>
       <c r="K217" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="L217" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0009</v>
       </c>
       <c r="M217" s="10" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -14831,22 +14831,22 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.185</v>
+        <v>1.3916</v>
       </c>
       <c r="H218" t="n">
-        <v>1.1296</v>
+        <v>1.1545</v>
       </c>
       <c r="I218" t="n">
-        <v>1.4092</v>
+        <v>1.3997</v>
       </c>
       <c r="J218" t="n">
-        <v>50.7</v>
+        <v>59.8</v>
       </c>
       <c r="K218" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="L218" t="n">
-        <v>0.0492</v>
+        <v>0.0587</v>
       </c>
       <c r="M218" s="10" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -14894,22 +14894,22 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>24.005</v>
+        <v>25.745</v>
       </c>
       <c r="H219" t="n">
-        <v>22.3358</v>
+        <v>22.5015</v>
       </c>
       <c r="I219" t="n">
-        <v>17.3012</v>
+        <v>17.336</v>
       </c>
       <c r="J219" t="n">
-        <v>60</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K219" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="L219" t="n">
-        <v>-0.143</v>
+        <v>-0.032</v>
       </c>
       <c r="M219" s="10" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -14957,22 +14957,22 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>49.34</v>
+        <v>51.35</v>
       </c>
       <c r="H220" t="n">
-        <v>45.1594</v>
+        <v>45.7489</v>
       </c>
       <c r="I220" t="n">
-        <v>46.0449</v>
+        <v>46.2177</v>
       </c>
       <c r="J220" t="n">
-        <v>57.5</v>
+        <v>60.4</v>
       </c>
       <c r="K220" t="n">
-        <v>15.1</v>
+        <v>16.2</v>
       </c>
       <c r="L220" t="n">
-        <v>0.6868</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="M220" s="10" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -15020,22 +15020,22 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>295.08</v>
+        <v>290.48</v>
       </c>
       <c r="H221" t="n">
-        <v>354.9782</v>
+        <v>348.8355</v>
       </c>
       <c r="I221" t="n">
-        <v>464.0136</v>
+        <v>457.951</v>
       </c>
       <c r="J221" t="n">
-        <v>40.6</v>
+        <v>40.2</v>
       </c>
       <c r="K221" t="n">
-        <v>9.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="L221" t="n">
-        <v>2.4097</v>
+        <v>1.5217</v>
       </c>
       <c r="M221" s="10" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -15083,22 +15083,22 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>22.035</v>
+        <v>26.5</v>
       </c>
       <c r="H222" t="n">
-        <v>22.3598</v>
+        <v>22.7541</v>
       </c>
       <c r="I222" t="n">
-        <v>25.9217</v>
+        <v>25.9606</v>
       </c>
       <c r="J222" t="n">
-        <v>47.2</v>
+        <v>57.4</v>
       </c>
       <c r="K222" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="L222" t="n">
-        <v>0.3627</v>
+        <v>0.6821</v>
       </c>
       <c r="M222" s="10" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -15146,22 +15146,22 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>29.25</v>
+        <v>566.85</v>
       </c>
       <c r="H223" t="n">
-        <v>31.9151</v>
+        <v>584.1635</v>
       </c>
       <c r="I223" t="n">
-        <v>29.9639</v>
+        <v>582.1614</v>
       </c>
       <c r="J223" t="n">
-        <v>43.2</v>
+        <v>42.8</v>
       </c>
       <c r="K223" t="n">
-        <v>17.2</v>
+        <v>15.7</v>
       </c>
       <c r="L223" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-4.9254</v>
       </c>
       <c r="M223" s="10" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -15209,22 +15209,22 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>247.05</v>
+        <v>246.2</v>
       </c>
       <c r="H224" t="n">
-        <v>250.9853</v>
+        <v>250.5295</v>
       </c>
       <c r="I224" t="n">
-        <v>251.7785</v>
+        <v>251.6725</v>
       </c>
       <c r="J224" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="K224" t="n">
-        <v>15.5</v>
+        <v>17.1</v>
       </c>
       <c r="L224" t="n">
-        <v>-0.4281</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="M224" s="10" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -15338,19 +15338,19 @@
         <v>124.06</v>
       </c>
       <c r="H226" t="n">
-        <v>124.9549</v>
+        <v>124.8559</v>
       </c>
       <c r="I226" t="n">
-        <v>125.6742</v>
+        <v>125.6002</v>
       </c>
       <c r="J226" t="n">
-        <v>28</v>
+        <v>30.7</v>
       </c>
       <c r="K226" t="n">
-        <v>15.2</v>
+        <v>16.2</v>
       </c>
       <c r="L226" t="n">
-        <v>-0.0896</v>
+        <v>-0.0984</v>
       </c>
       <c r="M226" s="10" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -15407,7 +15407,7 @@
         <v>109.6185</v>
       </c>
       <c r="J227" t="n">
-        <v>91.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="K227" t="n">
         <v>72.5</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -15464,19 +15464,19 @@
         <v>10.45</v>
       </c>
       <c r="H228" t="n">
-        <v>10.522</v>
+        <v>10.5148</v>
       </c>
       <c r="I228" t="n">
-        <v>10.4463</v>
+        <v>10.4481</v>
       </c>
       <c r="J228" t="n">
         <v>45.2</v>
       </c>
       <c r="K228" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="L228" t="n">
-        <v>-0.0255</v>
+        <v>-0.0262</v>
       </c>
       <c r="M228" s="10" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -15590,19 +15590,19 @@
         <v>5.804</v>
       </c>
       <c r="H230" t="n">
-        <v>5.9432</v>
+        <v>5.9267</v>
       </c>
       <c r="I230" t="n">
-        <v>6.1109</v>
+        <v>6.0886</v>
       </c>
       <c r="J230" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="K230" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="L230" t="n">
-        <v>-0.008</v>
+        <v>-0.0112</v>
       </c>
       <c r="M230" s="10" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -15653,19 +15653,19 @@
         <v>213.15</v>
       </c>
       <c r="H231" t="n">
-        <v>215.1185</v>
+        <v>214.8621</v>
       </c>
       <c r="I231" t="n">
-        <v>211.445</v>
+        <v>211.566</v>
       </c>
       <c r="J231" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="K231" t="n">
-        <v>22.6</v>
+        <v>19.8</v>
       </c>
       <c r="L231" t="n">
-        <v>-0.6004</v>
+        <v>-0.7281</v>
       </c>
       <c r="M231" s="10" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -15713,22 +15713,22 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>359.25</v>
+        <v>359.15</v>
       </c>
       <c r="H232" t="n">
-        <v>363.5134</v>
+        <v>362.64</v>
       </c>
       <c r="I232" t="n">
-        <v>358.7715</v>
+        <v>359.1205</v>
       </c>
       <c r="J232" t="n">
-        <v>44.2</v>
+        <v>44.6</v>
       </c>
       <c r="K232" t="n">
-        <v>14.6</v>
+        <v>16.8</v>
       </c>
       <c r="L232" t="n">
-        <v>-1.0875</v>
+        <v>-1.3482</v>
       </c>
       <c r="M232" s="10" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -15779,19 +15779,19 @@
         <v>6.848</v>
       </c>
       <c r="H233" t="n">
-        <v>6.9993</v>
+        <v>6.9832</v>
       </c>
       <c r="I233" t="n">
-        <v>7.0315</v>
+        <v>7.0271</v>
       </c>
       <c r="J233" t="n">
-        <v>32.5</v>
+        <v>34.1</v>
       </c>
       <c r="K233" t="n">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="L233" t="n">
-        <v>-0.0271</v>
+        <v>-0.0282</v>
       </c>
       <c r="M233" s="10" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -15839,22 +15839,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>142.415</v>
+        <v>142.405</v>
       </c>
       <c r="H234" t="n">
-        <v>142.8578</v>
+        <v>142.7619</v>
       </c>
       <c r="I234" t="n">
-        <v>142.8844</v>
+        <v>142.8456</v>
       </c>
       <c r="J234" t="n">
-        <v>41.6</v>
+        <v>42.6</v>
       </c>
       <c r="K234" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="L234" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0893</v>
       </c>
       <c r="M234" s="10" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -15905,19 +15905,19 @@
         <v>0.625</v>
       </c>
       <c r="H235" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6466</v>
       </c>
       <c r="I235" t="n">
-        <v>0.674</v>
+        <v>0.6724</v>
       </c>
       <c r="J235" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="K235" t="n">
-        <v>23.4</v>
+        <v>24.3</v>
       </c>
       <c r="L235" t="n">
-        <v>-0.0019</v>
+        <v>-0.0015</v>
       </c>
       <c r="M235" s="10" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -15968,19 +15968,19 @@
         <v>712.5700000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>713.3795</v>
+        <v>713.4231</v>
       </c>
       <c r="I236" t="n">
-        <v>710.151</v>
+        <v>710.4836</v>
       </c>
       <c r="J236" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="K236" t="n">
-        <v>13.8</v>
+        <v>10.5</v>
       </c>
       <c r="L236" t="n">
-        <v>-0.7854</v>
+        <v>-0.6667</v>
       </c>
       <c r="M236" s="10" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -16031,19 +16031,19 @@
         <v>6.334</v>
       </c>
       <c r="H237" t="n">
-        <v>6.3386</v>
+        <v>6.3384</v>
       </c>
       <c r="I237" t="n">
-        <v>6.2945</v>
+        <v>6.2976</v>
       </c>
       <c r="J237" t="n">
         <v>50.6</v>
       </c>
       <c r="K237" t="n">
-        <v>13.6</v>
+        <v>11.7</v>
       </c>
       <c r="L237" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0081</v>
       </c>
       <c r="M237" s="10" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>2026-09-03 07:48</t>
+          <t>2026-09-03 19:49</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>31</v>
       </c>
       <c r="L108" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1828,7 +1828,7 @@
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1116,7 +1116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O237"/>
+  <dimension ref="A1:R237"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1195,21 @@
           <t>ISIN</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Settore</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="n">
@@ -1250,12 +1265,27 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>LU1900066975</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1343,27 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>LU1900067601</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1421,27 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>LU1834983550</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Materiali</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1499,27 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>FR0010405431</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1577,27 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>LU1900066207</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1655,27 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>LU1834983634</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Materiali</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1733,27 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>LU1681046006</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Clean Energy &amp; Battery</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1811,27 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>FR0010524777</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Clean Energy &amp; Battery</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1889,27 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>LU1834988278</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Energia</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1967,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1825,10 +1975,25 @@
           <t>LU1900066462</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Broad</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>0</v>
+      <c r="A12" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1873,19 +2038,34 @@
       <c r="L12" t="n">
         <v>-0.0461</v>
       </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>L0 RECOVERY</t>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>LU1834988609</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Telecom</t>
         </is>
       </c>
     </row>
@@ -1943,12 +2123,27 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>LU2009202107</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2201,27 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>LU1834988864</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Water</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2279,27 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>FR0010245514</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Giappone</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2357,27 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>LU1681037864</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Giappone</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2435,27 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>LU1287022708</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2513,27 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>LU1737652583</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2591,27 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>LU1437017350</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2669,27 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>LU1681045370</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2747,27 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>LU1681037609</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Giappone</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2825,27 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>LU1834983477</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Finanza</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2903,27 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>IE000OVF8Q66</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2612,22 +2957,22 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>252.35</v>
+        <v>252.2</v>
       </c>
       <c r="H24" t="n">
-        <v>255.8239</v>
+        <v>255.4788</v>
       </c>
       <c r="I24" t="n">
-        <v>254.2</v>
+        <v>254.221</v>
       </c>
       <c r="J24" t="n">
-        <v>40.4</v>
+        <v>40</v>
       </c>
       <c r="K24" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6911</v>
+        <v>-0.7907</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -2636,12 +2981,27 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>LU2469335371</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2699,12 +3059,27 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>LU1602144732</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Giappone</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2762,12 +3137,27 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>LU1900068328</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2825,12 +3215,27 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>LU1829218749</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Commodity Broad</t>
         </is>
       </c>
     </row>
@@ -2888,12 +3293,27 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>IE00B466KX20</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -2951,12 +3371,27 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>LU0496786905</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Asia Sviluppata</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3449,27 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>LU1681042518</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3077,12 +3527,27 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>LU1829219390</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Finanza</t>
         </is>
       </c>
     </row>
@@ -3140,12 +3605,27 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>LU1812092168</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3683,27 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>LU1900068161</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3761,27 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>IE000D5R9C23</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3839,27 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>FR0010527275</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Water</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3917,27 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>LU1834987890</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Industria</t>
         </is>
       </c>
     </row>
@@ -3455,12 +3995,27 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>LU1834985845</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Consumi</t>
         </is>
       </c>
     </row>
@@ -3518,12 +4073,27 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>LU1861138961</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3581,12 +4151,27 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>LU2109787551</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3644,12 +4229,27 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>LU1681039480</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -3707,12 +4307,27 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>LU1681044647</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3770,12 +4385,27 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>LU1598689153</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3833,12 +4463,27 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>LU1598690169</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3896,12 +4541,27 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>FR0010261198</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -3959,12 +4619,27 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>LU1437015735</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4697,27 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>FR0010010827</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4085,12 +4775,27 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>LU2130768844</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4853,27 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>LU1681042609</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4211,12 +4931,27 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>LU1681038672</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4274,12 +5009,27 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>IE00000EF730</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4337,12 +5087,27 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>LU1940199984</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4400,12 +5165,27 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>LU1940199711</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4463,12 +5243,27 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>LU1834986900</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4526,12 +5321,27 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>LU0908501132</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4589,12 +5399,27 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>LU1681041890</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4652,12 +5477,27 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>LU1900066033</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
         </is>
       </c>
     </row>
@@ -4715,12 +5555,27 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>LU1681037518</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4778,12 +5633,27 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>FR0007054358</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4841,12 +5711,27 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>LU2195226068</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4904,12 +5789,27 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>LU1602144575</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -4967,12 +5867,27 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>FR0007056841</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Industria</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5945,27 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>IE000KJPDY61</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -5093,12 +6023,27 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>LU1598688189</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -5156,12 +6101,27 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>LU1861137484</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -5219,12 +6179,27 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>LU1832418773</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -5282,12 +6257,27 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>FR0011720911</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -5324,19 +6314,19 @@
         <v>71.51000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>72.0202</v>
+        <v>71.9716</v>
       </c>
       <c r="I67" t="n">
-        <v>71.80119999999999</v>
+        <v>71.8036</v>
       </c>
       <c r="J67" t="n">
         <v>42.3</v>
       </c>
       <c r="K67" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.1064</v>
+        <v>-0.1225</v>
       </c>
       <c r="M67" s="10" t="inlineStr">
         <is>
@@ -5345,12 +6335,27 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>LU2059756598</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -5408,12 +6413,27 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>LU1829220216</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -5447,22 +6467,22 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>170.135</v>
+        <v>169.81</v>
       </c>
       <c r="H69" t="n">
-        <v>170.6425</v>
+        <v>170.5632</v>
       </c>
       <c r="I69" t="n">
-        <v>171.0142</v>
+        <v>170.9807</v>
       </c>
       <c r="J69" t="n">
-        <v>40.7</v>
+        <v>37</v>
       </c>
       <c r="K69" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.0584</v>
+        <v>-0.0808</v>
       </c>
       <c r="M69" s="10" t="inlineStr">
         <is>
@@ -5471,12 +6491,27 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>LU1650491282</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5534,12 +6569,27 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>IE000BUIVY49</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5597,12 +6647,27 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>IE0007FM00T9</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -5660,12 +6725,27 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>LU1598691217</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5723,12 +6803,27 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>LU0533033238</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5786,12 +6881,27 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>LU1650489385</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5849,12 +6959,27 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>IE000NHAIBN0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5912,12 +7037,27 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>IE00B4L5Y983</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -5975,12 +7115,27 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>LU1681039647</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6038,12 +7193,27 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>IE00085PWS28</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -6101,12 +7271,27 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>FR0011660927</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -6164,12 +7349,27 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>LU1437018168</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6227,12 +7427,27 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>LU1681043912</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -6290,12 +7505,27 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>LU0290357259</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6353,12 +7583,27 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>LU1681046774</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6416,12 +7661,27 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>LU1829219127</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6479,12 +7739,27 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
           <t>LU2182388236</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6542,12 +7817,27 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>LU0290357176</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6605,12 +7895,27 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
           <t>LU1681043599</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -6668,12 +7973,27 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
           <t>FR0010315770</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -6731,12 +8051,27 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>LU1681040496</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6794,12 +8129,27 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>LU1737653714</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6857,12 +8207,27 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
           <t>LU2356220926</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6920,12 +8285,27 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>FR0014003IY1</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -6983,12 +8363,27 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>LU1681046261</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7046,12 +8441,27 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>LU1563454310</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7109,12 +8519,27 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>LU1525418643</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7172,12 +8597,27 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>LU1829218822</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7235,12 +8675,27 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>LU2099295466</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7298,12 +8753,27 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
           <t>LU2023679090</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -7361,12 +8831,27 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>IE000KXCEXR3</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -7424,12 +8909,27 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>LU1437018598</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7487,12 +8987,27 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>LU1650488494</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7550,12 +9065,27 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>IE000P1IQS65</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -7613,12 +9143,27 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>LU1287023268</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7676,12 +9221,27 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>LU1598691050</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7739,12 +9299,27 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>LU1829219713</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7802,12 +9377,27 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>LU1681046691</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7865,12 +9455,27 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>LU1681041114</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7928,12 +9533,27 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>IE00BF5GB717</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7991,12 +9611,27 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>LU1435356495</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8054,12 +9689,27 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>LU1681046345</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8117,12 +9767,27 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>FR0007075494</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -8180,12 +9845,27 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>LU1650487413</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8243,12 +9923,27 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>LU1829219556</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8282,22 +9977,22 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>107.69</v>
+        <v>107.57</v>
       </c>
       <c r="H114" t="n">
-        <v>107.9401</v>
+        <v>107.9049</v>
       </c>
       <c r="I114" t="n">
-        <v>107.9346</v>
+        <v>107.9276</v>
       </c>
       <c r="J114" t="n">
-        <v>42.2</v>
+        <v>39.1</v>
       </c>
       <c r="K114" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="L114" t="n">
-        <v>-0.0252</v>
+        <v>-0.0458</v>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
@@ -8306,12 +10001,27 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>LU1812090543</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8369,12 +10079,27 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>LU2037748774</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8408,22 +10133,22 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>84.86</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="H116" t="n">
-        <v>84.67829999999999</v>
+        <v>84.6861</v>
       </c>
       <c r="I116" t="n">
-        <v>85.29219999999999</v>
+        <v>85.26300000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>52.5</v>
+        <v>49.6</v>
       </c>
       <c r="K116" t="n">
-        <v>41.8</v>
+        <v>39.5</v>
       </c>
       <c r="L116" t="n">
-        <v>0.0103</v>
+        <v>0.0361</v>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
@@ -8432,12 +10157,27 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>LU1435356149</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8495,12 +10235,27 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>LU0533032859</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Finanza</t>
         </is>
       </c>
     </row>
@@ -8558,12 +10313,27 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>FR0013380607</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -8621,12 +10391,27 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>IE0001GSQ2O9</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -8684,12 +10469,27 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>LU1681040900</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8747,12 +10547,27 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>IE000JJPY166</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8810,12 +10625,27 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>FR0010754200</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8873,12 +10703,27 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>FR0010510800</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8936,12 +10781,27 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>IE00B27YCF74</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Materiali</t>
         </is>
       </c>
     </row>
@@ -8999,12 +10859,27 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>LU1437024729</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9062,12 +10937,27 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>LU1525418726</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9125,12 +11015,27 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
           <t>LU0252633754</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -9188,12 +11093,27 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
           <t>LU1812091194</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -9251,12 +11171,27 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
           <t>LU1900069219</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Commodity Broad</t>
         </is>
       </c>
     </row>
@@ -9314,12 +11249,27 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
           <t>LU1435356065</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9353,22 +11303,22 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>65.38</v>
+        <v>65.23</v>
       </c>
       <c r="H131" t="n">
-        <v>65.5073</v>
+        <v>65.48090000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>65.64100000000001</v>
+        <v>65.626</v>
       </c>
       <c r="J131" t="n">
-        <v>45.8</v>
+        <v>42.1</v>
       </c>
       <c r="K131" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="L131" t="n">
-        <v>0.002</v>
+        <v>-0.0144</v>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
@@ -9377,12 +11327,27 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>LU1686831030</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9440,12 +11405,27 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>LU1681041205</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9503,12 +11483,27 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
           <t>IE000R7HJVO6</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -9566,12 +11561,27 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>IE00B1FZS798</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9629,12 +11639,27 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
           <t>LU1681049109</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -9692,12 +11717,27 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>LU1686830909</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9755,12 +11795,27 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
           <t>LU1681048804</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -9818,12 +11873,27 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>LU1285960032</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9881,12 +11951,27 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>LU2089239276</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9944,12 +12029,27 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>LU1708330235</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10007,12 +12107,27 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
           <t>LU1285959703</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10070,12 +12185,27 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>LU1437016204</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10112,19 +12242,19 @@
         <v>8.666</v>
       </c>
       <c r="H143" t="n">
-        <v>8.692600000000001</v>
+        <v>8.690099999999999</v>
       </c>
       <c r="I143" t="n">
-        <v>8.7956</v>
+        <v>8.7888</v>
       </c>
       <c r="J143" t="n">
         <v>38.2</v>
       </c>
       <c r="K143" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
       <c r="L143" t="n">
-        <v>0.0057</v>
+        <v>0.0061</v>
       </c>
       <c r="M143" s="10" t="inlineStr">
         <is>
@@ -10133,12 +12263,27 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
           <t>LU1285959885</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10196,12 +12341,27 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
           <t>IE0000U24AJ9</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10259,12 +12419,27 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>IE000R85HL30</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10322,12 +12497,27 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>LU1834988518</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -10385,12 +12575,27 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>LU1900067940</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10448,12 +12653,27 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>LU1900068914</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10511,12 +12731,27 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>IE0008TKP6O7</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10574,12 +12809,27 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>IE0009VWHAE6</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10637,12 +12887,27 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>IE000PEAJOT0</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10700,12 +12965,27 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>IE000QWCYQT0</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10763,12 +13043,27 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>FR0010361683</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10826,12 +13121,27 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
           <t>LU1834987973</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Finanza</t>
         </is>
       </c>
     </row>
@@ -10889,12 +13199,27 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>LU1681043086</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -10952,12 +13277,27 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>LU1681048630</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Consumi</t>
         </is>
       </c>
     </row>
@@ -11015,12 +13355,27 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>LU1681038599</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -11078,12 +13433,27 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>LU1954152853</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -11141,12 +13511,27 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>LU2023678282</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
         </is>
       </c>
     </row>
@@ -11204,12 +13589,27 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
           <t>LU1829221024</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -11267,12 +13667,27 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>LU1681038243</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -11330,12 +13745,27 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>LU1834988781</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Consumi</t>
         </is>
       </c>
     </row>
@@ -11393,12 +13823,27 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>LU2023678449</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -11456,12 +13901,27 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>LU1861132840</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>AI &amp; Robotics</t>
         </is>
       </c>
     </row>
@@ -11519,12 +13979,27 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>LU1900065811</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -11582,12 +14057,27 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>LU0533033667</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -11645,12 +14135,27 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>LU2023678878</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -11708,12 +14213,27 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
           <t>LU3038520774</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Difesa</t>
         </is>
       </c>
     </row>
@@ -11771,12 +14291,27 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>JE00B1VS3770</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Oro &amp; Metalli Preziosi</t>
         </is>
       </c>
     </row>
@@ -11834,12 +14369,27 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>JE00B1VS3333</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Oro &amp; Metalli Preziosi</t>
         </is>
       </c>
     </row>
@@ -11897,12 +14447,27 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>IE00BK5BQT80</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -11939,10 +14504,10 @@
         <v>20.035</v>
       </c>
       <c r="H172" t="n">
-        <v>19.9717</v>
+        <v>19.9778</v>
       </c>
       <c r="I172" t="n">
-        <v>19.9075</v>
+        <v>19.9107</v>
       </c>
       <c r="J172" t="n">
         <v>100</v>
@@ -11951,7 +14516,7 @@
         <v>99.8</v>
       </c>
       <c r="L172" t="n">
-        <v>0.0094</v>
+        <v>0.0072</v>
       </c>
       <c r="M172" s="10" t="inlineStr">
         <is>
@@ -11960,12 +14525,27 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>IE00B1FZS244</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -12023,12 +14603,27 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
           <t>IE00B1FZS350</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -12086,12 +14681,27 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>IE00B1XNHC34</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Clean Energy &amp; Battery</t>
         </is>
       </c>
     </row>
@@ -12149,12 +14759,27 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>IE00BGV5VN51</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>AI &amp; Robotics</t>
         </is>
       </c>
     </row>
@@ -12212,12 +14837,27 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
           <t>IE00B52SF786</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12275,12 +14915,27 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
           <t>IE00B6QW5T61</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Infrastrutture</t>
         </is>
       </c>
     </row>
@@ -12338,12 +14993,27 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>IE00B1FZS681</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12401,12 +15071,27 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>IE00B3VWMM18</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12464,12 +15149,27 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
           <t>IE00BDVWFV31</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12527,12 +15227,27 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>IE00B8GKDB10</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12566,22 +15281,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>229.55</v>
+        <v>230.6</v>
       </c>
       <c r="H182" t="n">
-        <v>230.9974</v>
+        <v>230.9595</v>
       </c>
       <c r="I182" t="n">
-        <v>231.544</v>
+        <v>231.628</v>
       </c>
       <c r="J182" t="n">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
       <c r="K182" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="L182" t="n">
-        <v>-0.3305</v>
+        <v>-0.2906</v>
       </c>
       <c r="M182" s="10" t="inlineStr">
         <is>
@@ -12590,12 +15305,27 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>IE00BKWQ0H23</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -12653,12 +15383,27 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>IE00B0M63912</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12716,12 +15461,27 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>IE00B0M63961</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12779,12 +15539,27 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
           <t>IE00B0M63507</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12842,12 +15617,27 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
           <t>IE00B27YCK28</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12905,12 +15695,27 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
           <t>IE00B8KGV557</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -12968,12 +15773,27 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>IE00BP3QZD73</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -13031,12 +15851,27 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
           <t>IE00BFXR5895</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -13094,12 +15929,27 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
           <t>GB00B15KYG56</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
         </is>
       </c>
     </row>
@@ -13157,12 +16007,27 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>GB00B15KXQ89</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
         </is>
       </c>
     </row>
@@ -13220,12 +16085,27 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
           <t>DE000A0Q4MJ7</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
         </is>
       </c>
     </row>
@@ -13283,12 +16163,27 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
           <t>DE000A0QLW44</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
         </is>
       </c>
     </row>
@@ -13346,12 +16241,27 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
           <t>IE00063FT9K6</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Metalli Industriali</t>
         </is>
       </c>
     </row>
@@ -13409,12 +16319,27 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
           <t>IE00BMDX3P59</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Clean Energy &amp; Battery</t>
         </is>
       </c>
     </row>
@@ -13472,12 +16397,27 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
           <t>IE00BGDQ0L74</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -13535,12 +16475,27 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
           <t>LU0322250985</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -13598,12 +16553,27 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
           <t>LU0290358497</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13661,12 +16631,27 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
           <t>IE00B14X4Q57</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13724,12 +16709,27 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
           <t>IE00B3ZW0K18</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -13787,12 +16787,27 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
           <t>IE00B441G979</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -13850,12 +16865,27 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
           <t>IE00B579F325</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Oro &amp; Metalli Preziosi</t>
         </is>
       </c>
     </row>
@@ -13913,12 +16943,27 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
           <t>XS2940466316</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Crypto</t>
         </is>
       </c>
     </row>
@@ -13976,12 +17021,27 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
           <t>IE00BD6FVP32</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Commodity Broad</t>
         </is>
       </c>
     </row>
@@ -14039,12 +17099,27 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
           <t>IE00BM67HT60</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -14102,12 +17177,27 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
           <t>IE00BYPLS672</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
         </is>
       </c>
     </row>
@@ -14165,12 +17255,27 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
           <t>IE000V0H6AD4</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>AI &amp; Robotics</t>
         </is>
       </c>
     </row>
@@ -14228,12 +17333,27 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
           <t>IE00B1W57M07</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Clean Energy &amp; Battery</t>
         </is>
       </c>
     </row>
@@ -14291,12 +17411,27 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
           <t>DE000A1RX996</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Oro &amp; Metalli Preziosi</t>
         </is>
       </c>
     </row>
@@ -14354,12 +17489,27 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
           <t>DE000A0N62E5</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Oro &amp; Metalli Preziosi</t>
         </is>
       </c>
     </row>
@@ -14417,12 +17567,27 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
           <t>GB00BLD4ZL17</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Crypto</t>
         </is>
       </c>
     </row>
@@ -14480,12 +17645,27 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
           <t>GB00BLD4ZM24</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Crypto</t>
         </is>
       </c>
     </row>
@@ -14519,19 +17699,19 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>9.444000000000001</v>
+        <v>9.212</v>
       </c>
       <c r="H213" t="n">
-        <v>8.3302</v>
+        <v>8.414199999999999</v>
       </c>
       <c r="J213" t="n">
-        <v>71.8</v>
+        <v>66.7</v>
       </c>
       <c r="K213" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="L213" t="n">
-        <v>0.2311</v>
+        <v>0.1738</v>
       </c>
       <c r="M213" s="12" t="inlineStr">
         <is>
@@ -14540,12 +17720,27 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
           <t>GB00BKJG2L22</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Crypto</t>
         </is>
       </c>
     </row>
@@ -14603,12 +17798,27 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
           <t>DE000A27Z304</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Crypto</t>
         </is>
       </c>
     </row>
@@ -14666,12 +17876,27 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
           <t>DE000A3G3ZL3</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Crypto</t>
         </is>
       </c>
     </row>
@@ -14705,22 +17930,22 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>35.6</v>
+        <v>34.975</v>
       </c>
       <c r="H216" t="n">
-        <v>32.4748</v>
+        <v>32.4153</v>
       </c>
       <c r="I216" t="n">
-        <v>30.1967</v>
+        <v>30.1842</v>
       </c>
       <c r="J216" t="n">
-        <v>57.7</v>
+        <v>56.6</v>
       </c>
       <c r="K216" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="L216" t="n">
-        <v>0.0353</v>
+        <v>-0.0046</v>
       </c>
       <c r="M216" s="10" t="inlineStr">
         <is>
@@ -14729,12 +17954,27 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Leva Titolo Singolo</t>
         </is>
       </c>
     </row>
@@ -14768,22 +18008,22 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.2003</v>
+        <v>0.2035</v>
       </c>
       <c r="H217" t="n">
-        <v>0.2471</v>
+        <v>0.2474</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3023</v>
+        <v>0.3024</v>
       </c>
       <c r="J217" t="n">
-        <v>34.7</v>
+        <v>35.3</v>
       </c>
       <c r="K217" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="L217" t="n">
-        <v>-0.0009</v>
+        <v>-0.0007</v>
       </c>
       <c r="M217" s="10" t="inlineStr">
         <is>
@@ -14792,12 +18032,27 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Leva Titolo Singolo</t>
         </is>
       </c>
     </row>
@@ -14831,22 +18086,22 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.3916</v>
+        <v>1.1284</v>
       </c>
       <c r="H218" t="n">
-        <v>1.1545</v>
+        <v>1.1295</v>
       </c>
       <c r="I218" t="n">
-        <v>1.3997</v>
+        <v>1.3945</v>
       </c>
       <c r="J218" t="n">
-        <v>59.8</v>
+        <v>47.7</v>
       </c>
       <c r="K218" t="n">
-        <v>17</v>
+        <v>14.9</v>
       </c>
       <c r="L218" t="n">
-        <v>0.0587</v>
+        <v>0.0419</v>
       </c>
       <c r="M218" s="10" t="inlineStr">
         <is>
@@ -14855,12 +18110,27 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Leva Titolo Singolo</t>
         </is>
       </c>
     </row>
@@ -14897,19 +18167,19 @@
         <v>25.745</v>
       </c>
       <c r="H219" t="n">
-        <v>22.5015</v>
+        <v>22.6191</v>
       </c>
       <c r="I219" t="n">
-        <v>17.336</v>
+        <v>17.5779</v>
       </c>
       <c r="J219" t="n">
-        <v>64.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K219" t="n">
-        <v>32.8</v>
+        <v>33.1</v>
       </c>
       <c r="L219" t="n">
-        <v>-0.032</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="M219" s="10" t="inlineStr">
         <is>
@@ -14918,12 +18188,27 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Leva Titolo Singolo</t>
         </is>
       </c>
     </row>
@@ -14957,22 +18242,22 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>51.35</v>
+        <v>49.94</v>
       </c>
       <c r="H220" t="n">
-        <v>45.7489</v>
+        <v>45.6147</v>
       </c>
       <c r="I220" t="n">
-        <v>46.2177</v>
+        <v>46.1895</v>
       </c>
       <c r="J220" t="n">
-        <v>60.4</v>
+        <v>58.4</v>
       </c>
       <c r="K220" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="L220" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.8572</v>
       </c>
       <c r="M220" s="10" t="inlineStr">
         <is>
@@ -14981,12 +18266,27 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Leva Titolo Singolo</t>
         </is>
       </c>
     </row>
@@ -15020,22 +18320,22 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>290.48</v>
+        <v>295.11</v>
       </c>
       <c r="H221" t="n">
-        <v>348.8355</v>
+        <v>349.2764</v>
       </c>
       <c r="I221" t="n">
-        <v>457.951</v>
+        <v>458.0436</v>
       </c>
       <c r="J221" t="n">
-        <v>40.2</v>
+        <v>40.6</v>
       </c>
       <c r="K221" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="L221" t="n">
-        <v>1.5217</v>
+        <v>1.8172</v>
       </c>
       <c r="M221" s="10" t="inlineStr">
         <is>
@@ -15044,12 +18344,27 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Leva Titolo Singolo</t>
         </is>
       </c>
     </row>
@@ -15083,22 +18398,22 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>26.5</v>
+        <v>24.28</v>
       </c>
       <c r="H222" t="n">
-        <v>22.7541</v>
+        <v>22.5427</v>
       </c>
       <c r="I222" t="n">
-        <v>25.9606</v>
+        <v>25.9162</v>
       </c>
       <c r="J222" t="n">
-        <v>57.4</v>
+        <v>52.9</v>
       </c>
       <c r="K222" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="L222" t="n">
-        <v>0.6821</v>
+        <v>0.5404</v>
       </c>
       <c r="M222" s="10" t="inlineStr">
         <is>
@@ -15107,12 +18422,27 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Leva Titolo Singolo</t>
         </is>
       </c>
     </row>
@@ -15146,22 +18476,22 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>566.85</v>
+        <v>553.98</v>
       </c>
       <c r="H223" t="n">
-        <v>584.1635</v>
+        <v>582.9378</v>
       </c>
       <c r="I223" t="n">
-        <v>582.1614</v>
+        <v>581.904</v>
       </c>
       <c r="J223" t="n">
-        <v>42.8</v>
+        <v>37.5</v>
       </c>
       <c r="K223" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="L223" t="n">
-        <v>-4.9254</v>
+        <v>-5.7467</v>
       </c>
       <c r="M223" s="10" t="inlineStr">
         <is>
@@ -15170,12 +18500,27 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -15233,12 +18578,27 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
           <t>FR0011758085</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -15272,22 +18632,22 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>250.25</v>
+        <v>250.23</v>
       </c>
       <c r="H225" t="n">
-        <v>252.0391</v>
+        <v>251.8668</v>
       </c>
       <c r="I225" t="n">
-        <v>249.8824</v>
+        <v>249.978</v>
       </c>
       <c r="J225" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="K225" t="n">
-        <v>24.1</v>
+        <v>22.7</v>
       </c>
       <c r="L225" t="n">
-        <v>-0.4421</v>
+        <v>-0.5261</v>
       </c>
       <c r="M225" s="10" t="inlineStr">
         <is>
@@ -15296,12 +18656,27 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
           <t>FR0013209921</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -15359,12 +18734,27 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
           <t>LU1287023342</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -15422,12 +18812,27 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
           <t>LU1190417599</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -15485,12 +18890,27 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
           <t>IE000XL4IXU1</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -15548,12 +18968,27 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
           <t>LU2370241684</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -15611,12 +19046,27 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
           <t>IE000G0E83X3</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>AI &amp; Robotics</t>
         </is>
       </c>
     </row>
@@ -15674,12 +19124,27 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
           <t>DE0005933931</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -15737,12 +19202,27 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
           <t>FR0012399806</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -15800,12 +19280,27 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
           <t>FR0014002CH1</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Water</t>
         </is>
       </c>
     </row>
@@ -15863,12 +19358,27 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
           <t>IE00B3VWN393</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -15926,12 +19436,27 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
           <t>LU0832435464</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Volatilità</t>
         </is>
       </c>
     </row>
@@ -15989,12 +19514,27 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
           <t>IE00B5BMR087</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>
@@ -16052,12 +19592,27 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>2026-09-03 19:49</t>
+          <t>2026-09-03 22:22</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
         <is>
           <t>IE000D8XC064</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Globale</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>Broad</t>
         </is>
       </c>
     </row>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ETF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1212,8 +1212,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
-        <v>3</v>
+      <c r="A2" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1241,31 +1241,31 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>170.69</v>
+        <v>175.4</v>
       </c>
       <c r="H2" t="n">
-        <v>171.0127</v>
+        <v>171.4613</v>
       </c>
       <c r="I2" t="n">
-        <v>169.8794</v>
+        <v>169.9736</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>54.7</v>
       </c>
       <c r="K2" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1625</v>
-      </c>
-      <c r="M2" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.463</v>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>51.05</v>
+        <v>50.67</v>
       </c>
       <c r="H3" t="n">
-        <v>50.6959</v>
+        <v>50.6597</v>
       </c>
       <c r="I3" t="n">
-        <v>49.9174</v>
+        <v>49.9098</v>
       </c>
       <c r="J3" t="n">
-        <v>54.2</v>
+        <v>51.6</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0066</v>
+        <v>-0.0308</v>
       </c>
       <c r="M3" s="12" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1397,22 +1397,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>144.72</v>
+        <v>146.24</v>
       </c>
       <c r="H4" t="n">
-        <v>142.448</v>
+        <v>142.9487</v>
       </c>
       <c r="I4" t="n">
-        <v>135.462</v>
+        <v>135.812</v>
       </c>
       <c r="J4" t="n">
-        <v>60.5</v>
+        <v>63.4</v>
       </c>
       <c r="K4" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.109</v>
+        <v>-0.0583</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1475,22 +1475,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.9835</v>
+        <v>3.032</v>
       </c>
       <c r="H5" t="n">
-        <v>2.95</v>
+        <v>2.9546</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8697</v>
+        <v>2.8706</v>
       </c>
       <c r="J5" t="n">
-        <v>60.7</v>
+        <v>66.8</v>
       </c>
       <c r="K5" t="n">
-        <v>30.1</v>
+        <v>31.2</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0014</v>
+        <v>0.0017</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1553,22 +1553,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>26.73</v>
+        <v>26.745</v>
       </c>
       <c r="H6" t="n">
-        <v>25.1431</v>
+        <v>25.1446</v>
       </c>
       <c r="I6" t="n">
-        <v>25.0089</v>
+        <v>25.0092</v>
       </c>
       <c r="J6" t="n">
-        <v>70.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>23.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2912</v>
+        <v>0.2921</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1631,22 +1631,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>213.55</v>
+        <v>213.6</v>
       </c>
       <c r="H7" t="n">
-        <v>209.8385</v>
+        <v>209.8433</v>
       </c>
       <c r="I7" t="n">
-        <v>203.2264</v>
+        <v>203.2274</v>
       </c>
       <c r="J7" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="K7" t="n">
         <v>31.3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0893</v>
+        <v>0.0925</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1709,22 +1709,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>541.4</v>
+        <v>538</v>
       </c>
       <c r="H8" t="n">
-        <v>524.3149</v>
+        <v>523.9911</v>
       </c>
       <c r="I8" t="n">
-        <v>507.089</v>
+        <v>507.021</v>
       </c>
       <c r="J8" t="n">
-        <v>69.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9727</v>
+        <v>0.7557</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1787,22 +1787,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>40.745</v>
+        <v>41.31</v>
       </c>
       <c r="H9" t="n">
-        <v>41.885</v>
+        <v>41.9388</v>
       </c>
       <c r="I9" t="n">
-        <v>42.9108</v>
+        <v>42.9221</v>
       </c>
       <c r="J9" t="n">
-        <v>36.3</v>
+        <v>42.3</v>
       </c>
       <c r="K9" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1525</v>
+        <v>-0.1164</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1865,22 +1865,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>109.62</v>
+        <v>110.32</v>
       </c>
       <c r="H10" t="n">
-        <v>108.9869</v>
+        <v>109.0535</v>
       </c>
       <c r="I10" t="n">
-        <v>105.7468</v>
+        <v>105.7608</v>
       </c>
       <c r="J10" t="n">
-        <v>56</v>
+        <v>59.3</v>
       </c>
       <c r="K10" t="n">
-        <v>17.1</v>
+        <v>18.4</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2737</v>
+        <v>-0.2291</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>47.295</v>
+        <v>48.275</v>
       </c>
       <c r="H11" t="n">
-        <v>47.3078</v>
+        <v>47.4011</v>
       </c>
       <c r="I11" t="n">
-        <v>45.9903</v>
+        <v>46.0099</v>
       </c>
       <c r="J11" t="n">
-        <v>52.8</v>
+        <v>61.8</v>
       </c>
       <c r="K11" t="n">
-        <v>27.8</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1597</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2021,109 +2021,109 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>52.43</v>
+        <v>52.25</v>
       </c>
       <c r="H12" t="n">
-        <v>52.4908</v>
+        <v>52.4737</v>
       </c>
       <c r="I12" t="n">
-        <v>52.3264</v>
+        <v>52.3228</v>
       </c>
       <c r="J12" t="n">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="K12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.0576</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:46</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>LU1834988609</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EMXC.MI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Asia - Paesi Sviluppati</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="H13" t="n">
+        <v>40.3469</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40.1518</v>
+      </c>
+      <c r="J13" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="K13" t="n">
         <v>8.1</v>
       </c>
-      <c r="L12" t="n">
-        <v>-0.0461</v>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-09-03 22:22</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>LU1834988609</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>EMXC.MI</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Asia - Paesi Sviluppati</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>40.59</v>
-      </c>
-      <c r="H13" t="n">
-        <v>40.288</v>
-      </c>
-      <c r="I13" t="n">
-        <v>40.1394</v>
-      </c>
-      <c r="J13" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>9</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.0726</v>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.1119</v>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2177,22 +2177,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>98.73999999999999</v>
+        <v>99.23</v>
       </c>
       <c r="H14" t="n">
-        <v>101.5836</v>
+        <v>101.6303</v>
       </c>
       <c r="I14" t="n">
-        <v>103.816</v>
+        <v>103.8258</v>
       </c>
       <c r="J14" t="n">
-        <v>32.3</v>
+        <v>34.2</v>
       </c>
       <c r="K14" t="n">
-        <v>19.2</v>
+        <v>24.5</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.226</v>
+        <v>-0.1948</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2255,22 +2255,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>222.94</v>
+        <v>222.64</v>
       </c>
       <c r="H15" t="n">
-        <v>219.6532</v>
+        <v>219.6246</v>
       </c>
       <c r="I15" t="n">
-        <v>217.2928</v>
+        <v>217.2868</v>
       </c>
       <c r="J15" t="n">
-        <v>59.1</v>
+        <v>58.6</v>
       </c>
       <c r="K15" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0706</v>
+        <v>0.0515</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2333,22 +2333,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>627.24</v>
+        <v>626.83</v>
       </c>
       <c r="H16" t="n">
-        <v>626.7585</v>
+        <v>626.7195</v>
       </c>
       <c r="I16" t="n">
-        <v>620.1684</v>
+        <v>620.1602</v>
       </c>
       <c r="J16" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="K16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.574</v>
+        <v>-0.6001</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2382,294 +2382,294 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LGQM.DE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Africa &amp; Middle East</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>16.024</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15.6258</v>
+      </c>
+      <c r="I17" t="n">
+        <v>14.8737</v>
+      </c>
+      <c r="J17" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.0396</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:46</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>LU1287022708</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Broad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LGQM.DE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Africa &amp; Middle East</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AEMD.DE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Amundi IS Core MSCI Emerging Markets UCITS ETF EUR Dist</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Asia - Emergente</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Milano</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>15.644</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15.5896</v>
-      </c>
-      <c r="I17" t="n">
-        <v>14.8661</v>
-      </c>
-      <c r="J17" t="n">
-        <v>54</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-0.0639</v>
-      </c>
-      <c r="M17" s="12" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>75.578</v>
+      </c>
+      <c r="H18" t="n">
+        <v>74.3002</v>
+      </c>
+      <c r="I18" t="n">
+        <v>73.8275</v>
+      </c>
+      <c r="J18" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
         <is>
           <t>L2 WATCH</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2026-09-03 22:22</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>LU1287022708</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:46</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>LU1737652583</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>EM</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Broad</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>AEMD.DE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Amundi IS Core MSCI Emerging Markets UCITS ETF EUR Dist</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AEME.PA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Amundi IS Core MSCI Emerging Markets UCITS ETF Acc</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Asia - Emergente</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Milano</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>74.374</v>
-      </c>
-      <c r="H18" t="n">
-        <v>74.18559999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>73.8034</v>
-      </c>
-      <c r="J18" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="K18" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.0658</v>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2026-09-03 22:22</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>LU1737652583</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="H19" t="n">
+        <v>100.7021</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100.0616</v>
+      </c>
+      <c r="J19" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1944</v>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:46</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>LU1437017350</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>EM</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Broad</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>AEME.PA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Amundi IS Core MSCI Emerging Markets UCITS ETF Acc</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AMEM.DE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Emerging Markets Swap II UCITS ETF EUR Acc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Asia - Emergente</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Milano</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>100.79</v>
-      </c>
-      <c r="H19" t="n">
-        <v>100.5497</v>
-      </c>
-      <c r="I19" t="n">
-        <v>100.0296</v>
-      </c>
-      <c r="J19" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.09229999999999999</v>
-      </c>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-09-03 22:22</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>LU1437017350</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>EM</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Broad</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AMEM.DE</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Emerging Markets Swap II UCITS ETF EUR Acc</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Asia - Emergente</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7.6386</v>
+        <v>7.7604</v>
       </c>
       <c r="H20" t="n">
-        <v>7.6179</v>
+        <v>7.6295</v>
       </c>
       <c r="I20" t="n">
-        <v>7.5762</v>
+        <v>7.5786</v>
       </c>
       <c r="J20" t="n">
-        <v>51.9</v>
+        <v>57.8</v>
       </c>
       <c r="K20" t="n">
         <v>7.4</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0151</v>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2723,22 +2723,22 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>151.53</v>
+        <v>151.55</v>
       </c>
       <c r="H21" t="n">
-        <v>149.2175</v>
+        <v>149.2194</v>
       </c>
       <c r="I21" t="n">
-        <v>147.6612</v>
+        <v>147.6616</v>
       </c>
       <c r="J21" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="K21" t="n">
         <v>10.3</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0446</v>
+        <v>0.0459</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>74.34999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="H22" t="n">
-        <v>74.0642</v>
+        <v>74.1309</v>
       </c>
       <c r="I22" t="n">
-        <v>72.7762</v>
+        <v>72.7902</v>
       </c>
       <c r="J22" t="n">
-        <v>54.6</v>
+        <v>58.9</v>
       </c>
       <c r="K22" t="n">
-        <v>15.8</v>
+        <v>12.9</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1731</v>
+        <v>-0.1284</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2850,8 +2850,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n">
-        <v>3</v>
+      <c r="A23" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2879,31 +2879,31 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7.324</v>
+        <v>7.444</v>
       </c>
       <c r="H23" t="n">
-        <v>7.3085</v>
+        <v>7.3199</v>
       </c>
       <c r="I23" t="n">
-        <v>7.2821</v>
+        <v>7.2845</v>
       </c>
       <c r="J23" t="n">
-        <v>51.4</v>
+        <v>57.4</v>
       </c>
       <c r="K23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0154</v>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3035,22 +3035,22 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>358.51</v>
+        <v>360.17</v>
       </c>
       <c r="H25" t="n">
-        <v>356.0584</v>
+        <v>356.2165</v>
       </c>
       <c r="I25" t="n">
-        <v>356.4476</v>
+        <v>356.4808</v>
       </c>
       <c r="J25" t="n">
-        <v>53.6</v>
+        <v>55.5</v>
       </c>
       <c r="K25" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0047</v>
+        <v>0.1106</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3113,22 +3113,22 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>98.98999999999999</v>
+        <v>100.34</v>
       </c>
       <c r="H26" t="n">
-        <v>99.0569</v>
+        <v>99.1854</v>
       </c>
       <c r="I26" t="n">
-        <v>98.6716</v>
+        <v>98.6986</v>
       </c>
       <c r="J26" t="n">
-        <v>50.2</v>
+        <v>55.5</v>
       </c>
       <c r="K26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0309</v>
+        <v>0.1171</v>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3191,22 +3191,22 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>37.445</v>
+        <v>37.615</v>
       </c>
       <c r="H27" t="n">
-        <v>36.4925</v>
+        <v>36.5087</v>
       </c>
       <c r="I27" t="n">
-        <v>35.188</v>
+        <v>35.1914</v>
       </c>
       <c r="J27" t="n">
-        <v>68.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0544</v>
+        <v>0.0653</v>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3240,8 +3240,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n">
-        <v>3</v>
+      <c r="A28" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3269,31 +3269,31 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>127.6273</v>
+        <v>130.14</v>
       </c>
       <c r="H28" t="n">
-        <v>127.5111</v>
+        <v>127.7504</v>
       </c>
       <c r="I28" t="n">
-        <v>126.5599</v>
+        <v>126.6102</v>
       </c>
       <c r="J28" t="n">
-        <v>51.1</v>
+        <v>56.9</v>
       </c>
       <c r="K28" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0708</v>
-      </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.2312</v>
+      </c>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3347,22 +3347,22 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="H29" t="n">
-        <v>57.2985</v>
+        <v>57.3175</v>
       </c>
       <c r="I29" t="n">
-        <v>56.3106</v>
+        <v>56.3146</v>
       </c>
       <c r="J29" t="n">
-        <v>56.6</v>
+        <v>58.7</v>
       </c>
       <c r="K29" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.067</v>
+        <v>-0.0543</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3425,22 +3425,22 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>473.25</v>
+        <v>475.7</v>
       </c>
       <c r="H30" t="n">
-        <v>474.3098</v>
+        <v>474.5431</v>
       </c>
       <c r="I30" t="n">
-        <v>470.112</v>
+        <v>470.161</v>
       </c>
       <c r="J30" t="n">
-        <v>49.5</v>
+        <v>54.7</v>
       </c>
       <c r="K30" t="n">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.862</v>
+        <v>-0.7056</v>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3503,22 +3503,22 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>400.05</v>
+        <v>402</v>
       </c>
       <c r="H31" t="n">
-        <v>397.6861</v>
+        <v>397.8718</v>
       </c>
       <c r="I31" t="n">
-        <v>388.624</v>
+        <v>388.663</v>
       </c>
       <c r="J31" t="n">
-        <v>55.8</v>
+        <v>57.9</v>
       </c>
       <c r="K31" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.1068</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3581,22 +3581,22 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>25.05</v>
+        <v>25.32</v>
       </c>
       <c r="H32" t="n">
-        <v>24.9984</v>
+        <v>25.0241</v>
       </c>
       <c r="I32" t="n">
-        <v>24.4336</v>
+        <v>24.439</v>
       </c>
       <c r="J32" t="n">
-        <v>55.9</v>
+        <v>63.9</v>
       </c>
       <c r="K32" t="n">
-        <v>25.1</v>
+        <v>25.7</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.0467</v>
+        <v>-0.0295</v>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3659,22 +3659,22 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>197.98</v>
+        <v>201.13</v>
       </c>
       <c r="H33" t="n">
-        <v>198.1656</v>
+        <v>198.4656</v>
       </c>
       <c r="I33" t="n">
-        <v>197.2354</v>
+        <v>197.2984</v>
       </c>
       <c r="J33" t="n">
-        <v>50.2</v>
+        <v>55.5</v>
       </c>
       <c r="K33" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0709</v>
+        <v>0.2719</v>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3708,8 +3708,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
-        <v>3</v>
+      <c r="A34" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3737,31 +3737,31 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>7.542</v>
+        <v>7.68</v>
       </c>
       <c r="H34" t="n">
-        <v>7.5478</v>
+        <v>7.5609</v>
       </c>
       <c r="I34" t="n">
-        <v>7.529</v>
+        <v>7.5317</v>
       </c>
       <c r="J34" t="n">
-        <v>50.1</v>
+        <v>56.2</v>
       </c>
       <c r="K34" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0143</v>
+      </c>
+      <c r="M34" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3815,22 +3815,22 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>68.7</v>
+        <v>69.16</v>
       </c>
       <c r="H35" t="n">
-        <v>70.1823</v>
+        <v>70.2261</v>
       </c>
       <c r="I35" t="n">
-        <v>70.6478</v>
+        <v>70.657</v>
       </c>
       <c r="J35" t="n">
-        <v>30.4</v>
+        <v>36.6</v>
       </c>
       <c r="K35" t="n">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2761</v>
+        <v>-0.2467</v>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3893,22 +3893,22 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>150.9</v>
+        <v>151.96</v>
       </c>
       <c r="H36" t="n">
-        <v>154.7286</v>
+        <v>154.8296</v>
       </c>
       <c r="I36" t="n">
-        <v>153.7388</v>
+        <v>153.76</v>
       </c>
       <c r="J36" t="n">
-        <v>36.1</v>
+        <v>39.4</v>
       </c>
       <c r="K36" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.8504</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3971,22 +3971,22 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>93.42</v>
+        <v>92.77</v>
       </c>
       <c r="H37" t="n">
-        <v>94.4524</v>
+        <v>94.3905</v>
       </c>
       <c r="I37" t="n">
-        <v>95.941</v>
+        <v>95.928</v>
       </c>
       <c r="J37" t="n">
-        <v>42.9</v>
+        <v>40.1</v>
       </c>
       <c r="K37" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.0321</v>
+        <v>-0.0736</v>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4049,22 +4049,22 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>70.39</v>
+        <v>71.63</v>
       </c>
       <c r="H38" t="n">
-        <v>69.9843</v>
+        <v>70.1024</v>
       </c>
       <c r="I38" t="n">
-        <v>69.6996</v>
+        <v>69.7244</v>
       </c>
       <c r="J38" t="n">
-        <v>53.3</v>
+        <v>59.6</v>
       </c>
       <c r="K38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1121</v>
+        <v>0.1912</v>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4098,8 +4098,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n">
-        <v>3</v>
+      <c r="A39" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4127,31 +4127,31 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>70.59999999999999</v>
+        <v>72.06</v>
       </c>
       <c r="H39" t="n">
-        <v>70.3592</v>
+        <v>70.4983</v>
       </c>
       <c r="I39" t="n">
-        <v>69.874</v>
+        <v>69.9032</v>
       </c>
       <c r="J39" t="n">
-        <v>52.1</v>
+        <v>59</v>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="L39" t="n">
-        <v>0.09130000000000001</v>
-      </c>
-      <c r="M39" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.1844</v>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>328</v>
+        <v>330.55</v>
       </c>
       <c r="H40" t="n">
-        <v>336.7682</v>
+        <v>337.011</v>
       </c>
       <c r="I40" t="n">
-        <v>341.204</v>
+        <v>341.255</v>
       </c>
       <c r="J40" t="n">
-        <v>29.7</v>
+        <v>35.9</v>
       </c>
       <c r="K40" t="n">
-        <v>21.2</v>
+        <v>24.7</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.4919</v>
+        <v>-1.3291</v>
       </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4283,22 +4283,22 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>724.4</v>
+        <v>728.8</v>
       </c>
       <c r="H41" t="n">
-        <v>723.4353</v>
+        <v>723.8543</v>
       </c>
       <c r="I41" t="n">
-        <v>714.64</v>
+        <v>714.728</v>
       </c>
       <c r="J41" t="n">
-        <v>53.5</v>
+        <v>57.6</v>
       </c>
       <c r="K41" t="n">
-        <v>26.3</v>
+        <v>27.1</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.7417</v>
+        <v>-0.4609</v>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4361,22 +4361,22 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>441.65</v>
+        <v>444.7</v>
       </c>
       <c r="H42" t="n">
-        <v>444.5662</v>
+        <v>444.8567</v>
       </c>
       <c r="I42" t="n">
-        <v>442.422</v>
+        <v>442.483</v>
       </c>
       <c r="J42" t="n">
-        <v>45.4</v>
+        <v>50.2</v>
       </c>
       <c r="K42" t="n">
-        <v>17.7</v>
+        <v>16.7</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.7028</v>
+        <v>-0.5081</v>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4439,22 +4439,22 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>194.84</v>
+        <v>195.24</v>
       </c>
       <c r="H43" t="n">
-        <v>195.3088</v>
+        <v>195.3469</v>
       </c>
       <c r="I43" t="n">
-        <v>193.484</v>
+        <v>193.492</v>
       </c>
       <c r="J43" t="n">
-        <v>49.5</v>
+        <v>51.3</v>
       </c>
       <c r="K43" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.3926</v>
+        <v>-0.3671</v>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4517,22 +4517,22 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>247.3</v>
+        <v>248.2</v>
       </c>
       <c r="H44" t="n">
-        <v>249.2536</v>
+        <v>249.3393</v>
       </c>
       <c r="I44" t="n">
-        <v>248.014</v>
+        <v>248.032</v>
       </c>
       <c r="J44" t="n">
-        <v>42.5</v>
+        <v>46.4</v>
       </c>
       <c r="K44" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.6289</v>
+        <v>-0.5714</v>
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4595,22 +4595,22 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>124.38</v>
+        <v>124.64</v>
       </c>
       <c r="H45" t="n">
-        <v>125.2628</v>
+        <v>125.2875</v>
       </c>
       <c r="I45" t="n">
-        <v>124.684</v>
+        <v>124.6892</v>
       </c>
       <c r="J45" t="n">
-        <v>43.2</v>
+        <v>45.5</v>
       </c>
       <c r="K45" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.303</v>
+        <v>-0.2865</v>
       </c>
       <c r="M45" s="10" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4673,22 +4673,22 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>53.03</v>
+        <v>53.22</v>
       </c>
       <c r="H46" t="n">
-        <v>53.8252</v>
+        <v>53.8433</v>
       </c>
       <c r="I46" t="n">
-        <v>53.7764</v>
+        <v>53.7802</v>
       </c>
       <c r="J46" t="n">
-        <v>38</v>
+        <v>41.1</v>
       </c>
       <c r="K46" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.1934</v>
+        <v>-0.1813</v>
       </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4751,22 +4751,22 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>97.58</v>
+        <v>97.77</v>
       </c>
       <c r="H47" t="n">
-        <v>98.5656</v>
+        <v>98.5992</v>
       </c>
       <c r="I47" t="n">
-        <v>98.28400000000001</v>
+        <v>98.2914</v>
       </c>
       <c r="J47" t="n">
-        <v>40.7</v>
+        <v>42.1</v>
       </c>
       <c r="K47" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.2823</v>
+        <v>-0.2636</v>
       </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4829,22 +4829,22 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>443.6</v>
+        <v>445.25</v>
       </c>
       <c r="H48" t="n">
-        <v>447.325</v>
+        <v>447.4821</v>
       </c>
       <c r="I48" t="n">
-        <v>445.647</v>
+        <v>445.68</v>
       </c>
       <c r="J48" t="n">
-        <v>42.2</v>
+        <v>46</v>
       </c>
       <c r="K48" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.1559</v>
+        <v>-1.0506</v>
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4907,22 +4907,22 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>381.87</v>
+        <v>383.63</v>
       </c>
       <c r="H49" t="n">
-        <v>387.1693</v>
+        <v>387.3369</v>
       </c>
       <c r="I49" t="n">
-        <v>390.4262</v>
+        <v>390.4614</v>
       </c>
       <c r="J49" t="n">
-        <v>37.6</v>
+        <v>41.6</v>
       </c>
       <c r="K49" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.2094</v>
+        <v>-1.0971</v>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4985,22 +4985,22 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6.74</v>
+        <v>6.759</v>
       </c>
       <c r="H50" t="n">
-        <v>6.7823</v>
+        <v>6.7841</v>
       </c>
       <c r="I50" t="n">
-        <v>6.7415</v>
+        <v>6.7419</v>
       </c>
       <c r="J50" t="n">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="K50" t="n">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.0179</v>
+        <v>-0.0167</v>
       </c>
       <c r="M50" s="10" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5063,22 +5063,22 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>30.86</v>
+        <v>30.91</v>
       </c>
       <c r="H51" t="n">
-        <v>31.0177</v>
+        <v>31.0224</v>
       </c>
       <c r="I51" t="n">
-        <v>31.0228</v>
+        <v>31.0238</v>
       </c>
       <c r="J51" t="n">
-        <v>45.3</v>
+        <v>46.8</v>
       </c>
       <c r="K51" t="n">
-        <v>19.7</v>
+        <v>18.7</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.0488</v>
+        <v>-0.0456</v>
       </c>
       <c r="M51" s="10" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5141,22 +5141,22 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>42.145</v>
+        <v>42.275</v>
       </c>
       <c r="H52" t="n">
-        <v>42.4465</v>
+        <v>42.4589</v>
       </c>
       <c r="I52" t="n">
-        <v>42.5113</v>
+        <v>42.5139</v>
       </c>
       <c r="J52" t="n">
-        <v>43.2</v>
+        <v>46.1</v>
       </c>
       <c r="K52" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.073</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="M52" s="10" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>154.68</v>
+        <v>153.86</v>
       </c>
       <c r="H53" t="n">
-        <v>154.3599</v>
+        <v>154.2818</v>
       </c>
       <c r="I53" t="n">
-        <v>154.8832</v>
+        <v>154.8668</v>
       </c>
       <c r="J53" t="n">
-        <v>51.2</v>
+        <v>48.8</v>
       </c>
       <c r="K53" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.117</v>
+        <v>-0.1693</v>
       </c>
       <c r="M53" s="10" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5297,22 +5297,22 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>127.38</v>
+        <v>127.74</v>
       </c>
       <c r="H54" t="n">
-        <v>129.2932</v>
+        <v>129.3275</v>
       </c>
       <c r="I54" t="n">
-        <v>129.816</v>
+        <v>129.8232</v>
       </c>
       <c r="J54" t="n">
-        <v>39.5</v>
+        <v>41.5</v>
       </c>
       <c r="K54" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="L54" t="n">
-        <v>-0.4217</v>
+        <v>-0.3988</v>
       </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5375,22 +5375,22 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>124.48</v>
+        <v>124.72</v>
       </c>
       <c r="H55" t="n">
-        <v>125.7833</v>
+        <v>125.8062</v>
       </c>
       <c r="I55" t="n">
-        <v>125.3296</v>
+        <v>125.3344</v>
       </c>
       <c r="J55" t="n">
-        <v>41.1</v>
+        <v>43</v>
       </c>
       <c r="K55" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.3741</v>
+        <v>-0.3588</v>
       </c>
       <c r="M55" s="10" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5453,22 +5453,22 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>107.54</v>
+        <v>109.36</v>
       </c>
       <c r="H56" t="n">
-        <v>108.4678</v>
+        <v>108.6412</v>
       </c>
       <c r="I56" t="n">
-        <v>110.4852</v>
+        <v>110.5216</v>
       </c>
       <c r="J56" t="n">
-        <v>47</v>
+        <v>50.9</v>
       </c>
       <c r="K56" t="n">
-        <v>8.4</v>
+        <v>13.1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.008</v>
+        <v>0.1241</v>
       </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5531,22 +5531,22 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>126.96</v>
+        <v>127.76</v>
       </c>
       <c r="H57" t="n">
-        <v>129.273</v>
+        <v>129.3492</v>
       </c>
       <c r="I57" t="n">
-        <v>129.8148</v>
+        <v>129.8308</v>
       </c>
       <c r="J57" t="n">
-        <v>36.6</v>
+        <v>41.2</v>
       </c>
       <c r="K57" t="n">
-        <v>15.1</v>
+        <v>18.7</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.4594</v>
+        <v>-0.4083</v>
       </c>
       <c r="M57" s="10" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5609,22 +5609,22 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>72.43000000000001</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>73.1455</v>
+        <v>73.1665</v>
       </c>
       <c r="I58" t="n">
-        <v>72.5692</v>
+        <v>72.5736</v>
       </c>
       <c r="J58" t="n">
-        <v>43.3</v>
+        <v>45.7</v>
       </c>
       <c r="K58" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.2514</v>
+        <v>-0.2374</v>
       </c>
       <c r="M58" s="10" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5687,22 +5687,22 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>42.75</v>
+        <v>42.865</v>
       </c>
       <c r="H59" t="n">
-        <v>43.1819</v>
+        <v>43.1929</v>
       </c>
       <c r="I59" t="n">
-        <v>42.7596</v>
+        <v>42.7619</v>
       </c>
       <c r="J59" t="n">
-        <v>43.9</v>
+        <v>45.9</v>
       </c>
       <c r="K59" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.1597</v>
+        <v>-0.1524</v>
       </c>
       <c r="M59" s="10" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5765,22 +5765,22 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>417.45</v>
+        <v>417.5</v>
       </c>
       <c r="H60" t="n">
-        <v>422.1226</v>
+        <v>422.1273</v>
       </c>
       <c r="I60" t="n">
-        <v>421.953</v>
+        <v>421.954</v>
       </c>
       <c r="J60" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="K60" t="n">
         <v>18.2</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.1732</v>
+        <v>-1.17</v>
       </c>
       <c r="M60" s="10" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5843,22 +5843,22 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>464.35</v>
+        <v>469</v>
       </c>
       <c r="H61" t="n">
-        <v>466.0577</v>
+        <v>466.5005</v>
       </c>
       <c r="I61" t="n">
-        <v>466.504</v>
+        <v>466.597</v>
       </c>
       <c r="J61" t="n">
-        <v>47.1</v>
+        <v>54.3</v>
       </c>
       <c r="K61" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.4734</v>
+        <v>-0.1767</v>
       </c>
       <c r="M61" s="10" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5921,22 +5921,22 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.121</v>
+        <v>5.161</v>
       </c>
       <c r="H62" t="n">
-        <v>5.1307</v>
+        <v>5.1345</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1009</v>
+        <v>5.1017</v>
       </c>
       <c r="J62" t="n">
-        <v>49.4</v>
+        <v>55.7</v>
       </c>
       <c r="K62" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.005</v>
+        <v>-0.0025</v>
       </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5999,22 +5999,22 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>214.3</v>
+        <v>214.9</v>
       </c>
       <c r="H63" t="n">
-        <v>217.3327</v>
+        <v>217.3899</v>
       </c>
       <c r="I63" t="n">
-        <v>217.155</v>
+        <v>217.167</v>
       </c>
       <c r="J63" t="n">
-        <v>39.6</v>
+        <v>41.9</v>
       </c>
       <c r="K63" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.7389</v>
+        <v>-0.7006</v>
       </c>
       <c r="M63" s="10" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6077,22 +6077,22 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>91.72</v>
+        <v>91.84</v>
       </c>
       <c r="H64" t="n">
-        <v>92.4579</v>
+        <v>92.4693</v>
       </c>
       <c r="I64" t="n">
-        <v>92.361</v>
+        <v>92.3634</v>
       </c>
       <c r="J64" t="n">
-        <v>42.7</v>
+        <v>44</v>
       </c>
       <c r="K64" t="n">
         <v>15.9</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.1826</v>
+        <v>-0.175</v>
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6155,22 +6155,22 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>41.795</v>
+        <v>42.075</v>
       </c>
       <c r="H65" t="n">
-        <v>42.6386</v>
+        <v>42.6652</v>
       </c>
       <c r="I65" t="n">
-        <v>43.3715</v>
+        <v>43.3771</v>
       </c>
       <c r="J65" t="n">
-        <v>31.9</v>
+        <v>37.8</v>
       </c>
       <c r="K65" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.0944</v>
+        <v>-0.0766</v>
       </c>
       <c r="M65" s="10" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6233,22 +6233,22 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>168.26</v>
+        <v>167.51</v>
       </c>
       <c r="H66" t="n">
-        <v>169.9628</v>
+        <v>169.8913</v>
       </c>
       <c r="I66" t="n">
-        <v>172.5788</v>
+        <v>172.5638</v>
       </c>
       <c r="J66" t="n">
-        <v>44.2</v>
+        <v>42.5</v>
       </c>
       <c r="K66" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>0.016</v>
+        <v>-0.0319</v>
       </c>
       <c r="M66" s="10" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6389,22 +6389,22 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>606.48</v>
+        <v>612.11</v>
       </c>
       <c r="H68" t="n">
-        <v>607.1626</v>
+        <v>607.6988</v>
       </c>
       <c r="I68" t="n">
-        <v>603.9362</v>
+        <v>604.0488</v>
       </c>
       <c r="J68" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K68" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.6294</v>
+        <v>-0.2701</v>
       </c>
       <c r="M68" s="10" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6545,22 +6545,22 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5.1646</v>
+        <v>5.168</v>
       </c>
       <c r="H70" t="n">
-        <v>5.1867</v>
+        <v>5.187</v>
       </c>
       <c r="I70" t="n">
-        <v>5.2026</v>
+        <v>5.2027</v>
       </c>
       <c r="J70" t="n">
-        <v>35</v>
+        <v>37.3</v>
       </c>
       <c r="K70" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.0035</v>
+        <v>-0.0032</v>
       </c>
       <c r="M70" s="10" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6623,22 +6623,22 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6.196</v>
+        <v>6.214</v>
       </c>
       <c r="H71" t="n">
-        <v>6.204</v>
+        <v>6.2058</v>
       </c>
       <c r="I71" t="n">
-        <v>6.1657</v>
+        <v>6.166</v>
       </c>
       <c r="J71" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="K71" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.0074</v>
+        <v>-0.0063</v>
       </c>
       <c r="M71" s="10" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6701,22 +6701,22 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>150.45</v>
+        <v>150.73</v>
       </c>
       <c r="H72" t="n">
-        <v>151.7425</v>
+        <v>151.7692</v>
       </c>
       <c r="I72" t="n">
-        <v>153.011</v>
+        <v>153.0166</v>
       </c>
       <c r="J72" t="n">
-        <v>35.2</v>
+        <v>38.2</v>
       </c>
       <c r="K72" t="n">
-        <v>29.2</v>
+        <v>28.5</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.1561</v>
+        <v>-0.1382</v>
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6779,22 +6779,22 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>529.61</v>
+        <v>527.33</v>
       </c>
       <c r="H73" t="n">
-        <v>524.2308</v>
+        <v>524.0136</v>
       </c>
       <c r="I73" t="n">
-        <v>516.046</v>
+        <v>516.0004</v>
       </c>
       <c r="J73" t="n">
-        <v>58.6</v>
+        <v>56.1</v>
       </c>
       <c r="K73" t="n">
         <v>12</v>
       </c>
       <c r="L73" t="n">
-        <v>-0.6631</v>
+        <v>-0.8086</v>
       </c>
       <c r="M73" s="10" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6857,22 +6857,22 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>195.46</v>
+        <v>195.95</v>
       </c>
       <c r="H74" t="n">
-        <v>197.3771</v>
+        <v>197.4238</v>
       </c>
       <c r="I74" t="n">
-        <v>199.3248</v>
+        <v>199.3346</v>
       </c>
       <c r="J74" t="n">
-        <v>33.4</v>
+        <v>37.5</v>
       </c>
       <c r="K74" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="L74" t="n">
-        <v>-0.2049</v>
+        <v>-0.1736</v>
       </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6935,22 +6935,22 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>4.9045</v>
+        <v>4.9337</v>
       </c>
       <c r="H75" t="n">
-        <v>4.9366</v>
+        <v>4.9394</v>
       </c>
       <c r="I75" t="n">
-        <v>4.9442</v>
+        <v>4.9448</v>
       </c>
       <c r="J75" t="n">
-        <v>37.7</v>
+        <v>47.4</v>
       </c>
       <c r="K75" t="n">
-        <v>8.800000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="L75" t="n">
-        <v>-0.0031</v>
+        <v>-0.0012</v>
       </c>
       <c r="M75" s="10" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7013,22 +7013,22 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>126.81</v>
+        <v>127.89</v>
       </c>
       <c r="H76" t="n">
-        <v>126.9862</v>
+        <v>127.0888</v>
       </c>
       <c r="I76" t="n">
-        <v>126.347</v>
+        <v>126.3686</v>
       </c>
       <c r="J76" t="n">
-        <v>49.7</v>
+        <v>56.2</v>
       </c>
       <c r="K76" t="n">
-        <v>10.7</v>
+        <v>12.9</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.1616</v>
+        <v>-0.0936</v>
       </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7091,22 +7091,22 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>226.66</v>
+        <v>226.7</v>
       </c>
       <c r="H77" t="n">
-        <v>227.4881</v>
+        <v>227.4919</v>
       </c>
       <c r="I77" t="n">
-        <v>228.1808</v>
+        <v>228.1816</v>
       </c>
       <c r="J77" t="n">
-        <v>37.5</v>
+        <v>38.1</v>
       </c>
       <c r="K77" t="n">
-        <v>16.9</v>
+        <v>15.7</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.1518</v>
+        <v>-0.1492</v>
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7169,22 +7169,22 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>14.186</v>
+        <v>14.276</v>
       </c>
       <c r="H78" t="n">
-        <v>14.1587</v>
+        <v>14.1679</v>
       </c>
       <c r="I78" t="n">
-        <v>13.9108</v>
+        <v>13.9128</v>
       </c>
       <c r="J78" t="n">
-        <v>54.9</v>
+        <v>59.5</v>
       </c>
       <c r="K78" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.0311</v>
+        <v>-0.0251</v>
       </c>
       <c r="M78" s="10" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7247,22 +7247,22 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>267.1</v>
+        <v>269.5</v>
       </c>
       <c r="H79" t="n">
-        <v>267.6914</v>
+        <v>267.92</v>
       </c>
       <c r="I79" t="n">
-        <v>265.059</v>
+        <v>265.107</v>
       </c>
       <c r="J79" t="n">
-        <v>49.6</v>
+        <v>56.7</v>
       </c>
       <c r="K79" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.5153</v>
+        <v>-0.3621</v>
       </c>
       <c r="M79" s="10" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7325,22 +7325,22 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>53.84</v>
+        <v>53.95</v>
       </c>
       <c r="H80" t="n">
-        <v>54.1037</v>
+        <v>54.1142</v>
       </c>
       <c r="I80" t="n">
-        <v>54.276</v>
+        <v>54.2782</v>
       </c>
       <c r="J80" t="n">
-        <v>33</v>
+        <v>39.9</v>
       </c>
       <c r="K80" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.0404</v>
+        <v>-0.0334</v>
       </c>
       <c r="M80" s="10" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7403,22 +7403,22 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>266.1</v>
+        <v>267.95</v>
       </c>
       <c r="H81" t="n">
-        <v>272.4751</v>
+        <v>272.6513</v>
       </c>
       <c r="I81" t="n">
-        <v>275.261</v>
+        <v>275.298</v>
       </c>
       <c r="J81" t="n">
-        <v>36.6</v>
+        <v>40</v>
       </c>
       <c r="K81" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="L81" t="n">
-        <v>-0.6988</v>
+        <v>-0.5807</v>
       </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7481,22 +7481,22 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>150.425</v>
+        <v>150.68</v>
       </c>
       <c r="H82" t="n">
-        <v>151.5326</v>
+        <v>151.5569</v>
       </c>
       <c r="I82" t="n">
-        <v>152.5893</v>
+        <v>152.5944</v>
       </c>
       <c r="J82" t="n">
-        <v>34.6</v>
+        <v>38</v>
       </c>
       <c r="K82" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.1273</v>
+        <v>-0.111</v>
       </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7559,22 +7559,22 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>229.65</v>
+        <v>229.68</v>
       </c>
       <c r="H83" t="n">
-        <v>230.8899</v>
+        <v>230.8927</v>
       </c>
       <c r="I83" t="n">
-        <v>232.193</v>
+        <v>232.1936</v>
       </c>
       <c r="J83" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="K83" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.153</v>
+        <v>-0.1511</v>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7637,22 +7637,22 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>136.09</v>
+        <v>135.99</v>
       </c>
       <c r="H84" t="n">
-        <v>136.6843</v>
+        <v>136.6748</v>
       </c>
       <c r="I84" t="n">
-        <v>137.1218</v>
+        <v>137.1198</v>
       </c>
       <c r="J84" t="n">
-        <v>34.7</v>
+        <v>31.9</v>
       </c>
       <c r="K84" t="n">
         <v>15.3</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.0789</v>
+        <v>-0.0853</v>
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7793,22 +7793,22 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>232.24</v>
+        <v>232.55</v>
       </c>
       <c r="H86" t="n">
-        <v>233.5841</v>
+        <v>233.6136</v>
       </c>
       <c r="I86" t="n">
-        <v>234.71</v>
+        <v>234.7162</v>
       </c>
       <c r="J86" t="n">
-        <v>34.6</v>
+        <v>38.1</v>
       </c>
       <c r="K86" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.1671</v>
+        <v>-0.1474</v>
       </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7871,22 +7871,22 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>689.5599999999999</v>
+        <v>695.3200000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>690.6809</v>
+        <v>691.2295</v>
       </c>
       <c r="I87" t="n">
-        <v>687.4616</v>
+        <v>687.5768</v>
       </c>
       <c r="J87" t="n">
-        <v>49.4</v>
+        <v>55.8</v>
       </c>
       <c r="K87" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="L87" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-0.4998</v>
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7949,22 +7949,22 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>426.86</v>
+        <v>430.35</v>
       </c>
       <c r="H88" t="n">
-        <v>427.7291</v>
+        <v>428.0615</v>
       </c>
       <c r="I88" t="n">
-        <v>425.641</v>
+        <v>425.7108</v>
       </c>
       <c r="J88" t="n">
-        <v>49.1</v>
+        <v>55.5</v>
       </c>
       <c r="K88" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.5607</v>
+        <v>-0.3379</v>
       </c>
       <c r="M88" s="10" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8027,22 +8027,22 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>266.31</v>
+        <v>267</v>
       </c>
       <c r="H89" t="n">
-        <v>267.5959</v>
+        <v>267.6617</v>
       </c>
       <c r="I89" t="n">
-        <v>267.7364</v>
+        <v>267.7502</v>
       </c>
       <c r="J89" t="n">
-        <v>32</v>
+        <v>38.9</v>
       </c>
       <c r="K89" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.1857</v>
+        <v>-0.1417</v>
       </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8105,22 +8105,22 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>41.061</v>
+        <v>41.105</v>
       </c>
       <c r="H90" t="n">
-        <v>41.3098</v>
+        <v>41.314</v>
       </c>
       <c r="I90" t="n">
-        <v>41.5527</v>
+        <v>41.5536</v>
       </c>
       <c r="J90" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
       <c r="K90" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.0275</v>
+        <v>-0.0247</v>
       </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8183,22 +8183,22 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>7.2324</v>
+        <v>7.235</v>
       </c>
       <c r="H91" t="n">
-        <v>7.2946</v>
+        <v>7.2948</v>
       </c>
       <c r="I91" t="n">
         <v>7.366</v>
       </c>
       <c r="J91" t="n">
-        <v>34.8</v>
+        <v>35.4</v>
       </c>
       <c r="K91" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.0059</v>
+        <v>-0.0057</v>
       </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8261,22 +8261,22 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>18.914</v>
+        <v>19.064</v>
       </c>
       <c r="H92" t="n">
-        <v>18.9448</v>
+        <v>18.9591</v>
       </c>
       <c r="I92" t="n">
-        <v>18.8508</v>
+        <v>18.8538</v>
       </c>
       <c r="J92" t="n">
-        <v>49.5</v>
+        <v>55.6</v>
       </c>
       <c r="K92" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.0245</v>
+        <v>-0.0149</v>
       </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8339,22 +8339,22 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>217.32</v>
+        <v>217.7</v>
       </c>
       <c r="H93" t="n">
-        <v>218.6816</v>
+        <v>218.7178</v>
       </c>
       <c r="I93" t="n">
-        <v>219.9874</v>
+        <v>219.995</v>
       </c>
       <c r="J93" t="n">
-        <v>35.7</v>
+        <v>39.4</v>
       </c>
       <c r="K93" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="L93" t="n">
-        <v>-0.1404</v>
+        <v>-0.1161</v>
       </c>
       <c r="M93" s="10" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8417,22 +8417,22 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>48.385</v>
+        <v>48.55</v>
       </c>
       <c r="H94" t="n">
-        <v>48.6738</v>
+        <v>48.6895</v>
       </c>
       <c r="I94" t="n">
-        <v>48.9852</v>
+        <v>48.9885</v>
       </c>
       <c r="J94" t="n">
-        <v>36.9</v>
+        <v>43.3</v>
       </c>
       <c r="K94" t="n">
-        <v>26.9</v>
+        <v>26.2</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.0326</v>
+        <v>-0.0221</v>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -8495,22 +8495,22 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>54.98</v>
+        <v>55.09</v>
       </c>
       <c r="H95" t="n">
-        <v>55.1663</v>
+        <v>55.1767</v>
       </c>
       <c r="I95" t="n">
-        <v>55.238</v>
+        <v>55.2402</v>
       </c>
       <c r="J95" t="n">
-        <v>31.1</v>
+        <v>41.1</v>
       </c>
       <c r="K95" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.0292</v>
+        <v>-0.0222</v>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8573,22 +8573,22 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>136.13</v>
+        <v>136.06</v>
       </c>
       <c r="H96" t="n">
-        <v>136.7142</v>
+        <v>136.7075</v>
       </c>
       <c r="I96" t="n">
-        <v>137.1962</v>
+        <v>137.1948</v>
       </c>
       <c r="J96" t="n">
-        <v>36.7</v>
+        <v>35</v>
       </c>
       <c r="K96" t="n">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="L96" t="n">
-        <v>-0.0965</v>
+        <v>-0.1009</v>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8651,19 +8651,19 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>22.69</v>
+        <v>22.655</v>
       </c>
       <c r="H97" t="n">
-        <v>22.6984</v>
+        <v>22.6993</v>
       </c>
       <c r="I97" t="n">
-        <v>22.6779</v>
+        <v>22.6794</v>
       </c>
       <c r="J97" t="n">
-        <v>49.8</v>
+        <v>46.5</v>
       </c>
       <c r="K97" t="n">
-        <v>7.3</v>
+        <v>11.2</v>
       </c>
       <c r="L97" t="n">
         <v>-0.0081</v>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8729,22 +8729,22 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>24.52</v>
+        <v>24.835</v>
       </c>
       <c r="H98" t="n">
-        <v>24.5183</v>
+        <v>24.5483</v>
       </c>
       <c r="I98" t="n">
-        <v>24.5576</v>
+        <v>24.5639</v>
       </c>
       <c r="J98" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="K98" t="n">
-        <v>9.5</v>
+        <v>12.4</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0046</v>
+        <v>0.0247</v>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8807,22 +8807,22 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>195.34</v>
+        <v>197.44</v>
       </c>
       <c r="H99" t="n">
-        <v>195.7109</v>
+        <v>195.9109</v>
       </c>
       <c r="I99" t="n">
-        <v>194.085</v>
+        <v>194.127</v>
       </c>
       <c r="J99" t="n">
-        <v>49.8</v>
+        <v>56.4</v>
       </c>
       <c r="K99" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="L99" t="n">
-        <v>-0.318</v>
+        <v>-0.1839</v>
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8885,22 +8885,22 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>48.76</v>
+        <v>48.885</v>
       </c>
       <c r="H100" t="n">
-        <v>49.0641</v>
+        <v>49.076</v>
       </c>
       <c r="I100" t="n">
-        <v>49.3545</v>
+        <v>49.357</v>
       </c>
       <c r="J100" t="n">
-        <v>32.7</v>
+        <v>39.3</v>
       </c>
       <c r="K100" t="n">
-        <v>26.1</v>
+        <v>25.3</v>
       </c>
       <c r="L100" t="n">
-        <v>-0.0331</v>
+        <v>-0.0251</v>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8963,22 +8963,22 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>130.285</v>
+        <v>130.465</v>
       </c>
       <c r="H101" t="n">
-        <v>130.8021</v>
+        <v>130.8192</v>
       </c>
       <c r="I101" t="n">
-        <v>131.1525</v>
+        <v>131.1561</v>
       </c>
       <c r="J101" t="n">
-        <v>33.9</v>
+        <v>39.4</v>
       </c>
       <c r="K101" t="n">
-        <v>21.8</v>
+        <v>20.9</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.0699</v>
+        <v>-0.0585</v>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -9041,22 +9041,22 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>7.287</v>
+        <v>7.297</v>
       </c>
       <c r="H102" t="n">
-        <v>7.2355</v>
+        <v>7.2364</v>
       </c>
       <c r="I102" t="n">
-        <v>7.1469</v>
+        <v>7.1471</v>
       </c>
       <c r="J102" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K102" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="L102" t="n">
-        <v>-0.0097</v>
+        <v>-0.0091</v>
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9119,22 +9119,22 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>137.185</v>
+        <v>137.32</v>
       </c>
       <c r="H103" t="n">
-        <v>139.0488</v>
+        <v>139.0617</v>
       </c>
       <c r="I103" t="n">
-        <v>141.2105</v>
+        <v>141.2132</v>
       </c>
       <c r="J103" t="n">
-        <v>34.2</v>
+        <v>35.3</v>
       </c>
       <c r="K103" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="L103" t="n">
-        <v>-0.1398</v>
+        <v>-0.1312</v>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -9197,22 +9197,22 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>104.58</v>
+        <v>104.61</v>
       </c>
       <c r="H104" t="n">
-        <v>104.6925</v>
+        <v>104.6953</v>
       </c>
       <c r="I104" t="n">
-        <v>104.7368</v>
+        <v>104.7374</v>
       </c>
       <c r="J104" t="n">
-        <v>42.3</v>
+        <v>44.3</v>
       </c>
       <c r="K104" t="n">
-        <v>17.4</v>
+        <v>16.4</v>
       </c>
       <c r="L104" t="n">
-        <v>-0.0242</v>
+        <v>-0.0223</v>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9275,22 +9275,22 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>106.66</v>
+        <v>106.72</v>
       </c>
       <c r="H105" t="n">
-        <v>107.2282</v>
+        <v>107.3011</v>
       </c>
       <c r="I105" t="n">
-        <v>107.4778</v>
+        <v>107.4946</v>
       </c>
       <c r="J105" t="n">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="K105" t="n">
-        <v>41.3</v>
+        <v>38.3</v>
       </c>
       <c r="L105" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0313</v>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -9353,22 +9353,22 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>200.09</v>
+        <v>200.36</v>
       </c>
       <c r="H106" t="n">
-        <v>201.4367</v>
+        <v>201.5089</v>
       </c>
       <c r="I106" t="n">
-        <v>202.739</v>
+        <v>202.7552</v>
       </c>
       <c r="J106" t="n">
-        <v>29.3</v>
+        <v>29.8</v>
       </c>
       <c r="K106" t="n">
-        <v>29.3</v>
+        <v>28.9</v>
       </c>
       <c r="L106" t="n">
-        <v>-0.1322</v>
+        <v>-0.0953</v>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -9402,8 +9402,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="n">
-        <v>2</v>
+      <c r="A107" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -9431,31 +9431,31 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>113.18</v>
+        <v>113.1</v>
       </c>
       <c r="H107" t="n">
-        <v>113.0178</v>
+        <v>113.0102</v>
       </c>
       <c r="I107" t="n">
-        <v>112.829</v>
+        <v>112.8274</v>
       </c>
       <c r="J107" t="n">
-        <v>64.2</v>
+        <v>58.5</v>
       </c>
       <c r="K107" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="L107" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="M107" s="12" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.0011</v>
+      </c>
+      <c r="M107" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -9509,22 +9509,22 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>5.073</v>
+        <v>5.0718</v>
       </c>
       <c r="H108" t="n">
-        <v>5.0659</v>
+        <v>5.0658</v>
       </c>
       <c r="I108" t="n">
         <v>5.0575</v>
       </c>
       <c r="J108" t="n">
-        <v>67.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K108" t="n">
-        <v>31</v>
+        <v>16.5</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9587,22 +9587,22 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>75.04600000000001</v>
+        <v>75.122</v>
       </c>
       <c r="H109" t="n">
-        <v>75.1734</v>
+        <v>75.1807</v>
       </c>
       <c r="I109" t="n">
-        <v>75.059</v>
+        <v>75.0605</v>
       </c>
       <c r="J109" t="n">
-        <v>46.7</v>
+        <v>49.1</v>
       </c>
       <c r="K109" t="n">
         <v>10.4</v>
       </c>
       <c r="L109" t="n">
-        <v>-0.032</v>
+        <v>-0.0272</v>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -9665,22 +9665,22 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>118.9</v>
+        <v>119.01</v>
       </c>
       <c r="H110" t="n">
-        <v>119.0696</v>
+        <v>119.0801</v>
       </c>
       <c r="I110" t="n">
-        <v>119.1142</v>
+        <v>119.1164</v>
       </c>
       <c r="J110" t="n">
-        <v>38</v>
+        <v>45.6</v>
       </c>
       <c r="K110" t="n">
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="L110" t="n">
-        <v>-0.0319</v>
+        <v>-0.0248</v>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9743,22 +9743,22 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>107.89</v>
+        <v>108.89</v>
       </c>
       <c r="H111" t="n">
-        <v>107.2724</v>
+        <v>107.3676</v>
       </c>
       <c r="I111" t="n">
-        <v>106.2534</v>
+        <v>106.2734</v>
       </c>
       <c r="J111" t="n">
-        <v>55.1</v>
+        <v>59.7</v>
       </c>
       <c r="K111" t="n">
-        <v>16.3</v>
+        <v>17.1</v>
       </c>
       <c r="L111" t="n">
-        <v>-0.0016</v>
+        <v>0.0622</v>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9821,22 +9821,22 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>127.79</v>
+        <v>127.81</v>
       </c>
       <c r="H112" t="n">
-        <v>127.9162</v>
+        <v>127.9181</v>
       </c>
       <c r="I112" t="n">
-        <v>127.9678</v>
+        <v>127.9682</v>
       </c>
       <c r="J112" t="n">
-        <v>42.6</v>
+        <v>43.8</v>
       </c>
       <c r="K112" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="L112" t="n">
-        <v>-0.0288</v>
+        <v>-0.0275</v>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9899,22 +9899,22 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>101.42</v>
+        <v>101.43</v>
       </c>
       <c r="H113" t="n">
-        <v>101.5104</v>
+        <v>101.5199</v>
       </c>
       <c r="I113" t="n">
-        <v>101.579</v>
+        <v>101.5812</v>
       </c>
       <c r="J113" t="n">
-        <v>36.7</v>
+        <v>31.2</v>
       </c>
       <c r="K113" t="n">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="L113" t="n">
-        <v>-0.0146</v>
+        <v>-0.0103</v>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9977,22 +9977,22 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>107.57</v>
+        <v>107.51</v>
       </c>
       <c r="H114" t="n">
-        <v>107.9049</v>
+        <v>107.8673</v>
       </c>
       <c r="I114" t="n">
-        <v>107.9276</v>
+        <v>107.9206</v>
       </c>
       <c r="J114" t="n">
-        <v>39.1</v>
+        <v>37.6</v>
       </c>
       <c r="K114" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="L114" t="n">
-        <v>-0.0458</v>
+        <v>-0.0606</v>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -10055,22 +10055,22 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>54.404</v>
+        <v>54.432</v>
       </c>
       <c r="H115" t="n">
-        <v>54.4515</v>
+        <v>54.4542</v>
       </c>
       <c r="I115" t="n">
-        <v>54.4372</v>
+        <v>54.4377</v>
       </c>
       <c r="J115" t="n">
-        <v>42.5</v>
+        <v>47</v>
       </c>
       <c r="K115" t="n">
-        <v>15.9</v>
+        <v>15.4</v>
       </c>
       <c r="L115" t="n">
-        <v>-0.0115</v>
+        <v>-0.0098</v>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -10211,22 +10211,22 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>410.81</v>
+        <v>415.48</v>
       </c>
       <c r="H117" t="n">
-        <v>409.1474</v>
+        <v>409.5921</v>
       </c>
       <c r="I117" t="n">
-        <v>405.9928</v>
+        <v>406.0862</v>
       </c>
       <c r="J117" t="n">
-        <v>55</v>
+        <v>61.7</v>
       </c>
       <c r="K117" t="n">
-        <v>16.9</v>
+        <v>23.8</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.4287</v>
+        <v>-0.1306</v>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -10289,22 +10289,22 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>41.9</v>
+        <v>41.955</v>
       </c>
       <c r="H118" t="n">
-        <v>42.7063</v>
+        <v>42.7115</v>
       </c>
       <c r="I118" t="n">
-        <v>42.8464</v>
+        <v>42.8475</v>
       </c>
       <c r="J118" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="K118" t="n">
         <v>30.6</v>
       </c>
       <c r="L118" t="n">
-        <v>-0.1735</v>
+        <v>-0.1699</v>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -10367,22 +10367,22 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>628.2</v>
+        <v>633</v>
       </c>
       <c r="H119" t="n">
-        <v>629.1396999999999</v>
+        <v>629.5968</v>
       </c>
       <c r="I119" t="n">
-        <v>625.936</v>
+        <v>626.032</v>
       </c>
       <c r="J119" t="n">
-        <v>49.7</v>
+        <v>55.5</v>
       </c>
       <c r="K119" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="L119" t="n">
-        <v>-0.7564</v>
+        <v>-0.45</v>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -10445,22 +10445,22 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>138.85</v>
+        <v>138.77</v>
       </c>
       <c r="H120" t="n">
-        <v>138.6762</v>
+        <v>138.6686</v>
       </c>
       <c r="I120" t="n">
-        <v>138.3038</v>
+        <v>138.3022</v>
       </c>
       <c r="J120" t="n">
-        <v>55.4</v>
+        <v>54</v>
       </c>
       <c r="K120" t="n">
-        <v>29.9</v>
+        <v>27.8</v>
       </c>
       <c r="L120" t="n">
-        <v>0.0151</v>
+        <v>0.01</v>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>15.5978</v>
+        <v>15.59879970550537</v>
       </c>
       <c r="H121" t="n">
         <v>15.4142</v>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -10601,7 +10601,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>127.17</v>
+        <v>127.129997253418</v>
       </c>
       <c r="H122" t="n">
         <v>126.4026</v>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -10679,7 +10679,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>114.38</v>
+        <v>114.4000015258789</v>
       </c>
       <c r="H123" t="n">
         <v>113.6715</v>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10757,22 +10757,22 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>20.805</v>
+        <v>20.64</v>
       </c>
       <c r="H124" t="n">
-        <v>20.8833</v>
+        <v>20.8675</v>
       </c>
       <c r="I124" t="n">
-        <v>20.5731</v>
+        <v>20.5698</v>
       </c>
       <c r="J124" t="n">
-        <v>48.8</v>
+        <v>43.7</v>
       </c>
       <c r="K124" t="n">
         <v>19.3</v>
       </c>
       <c r="L124" t="n">
-        <v>-0.0413</v>
+        <v>-0.0518</v>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10835,22 +10835,22 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>48.615</v>
+        <v>48.675</v>
       </c>
       <c r="H125" t="n">
-        <v>48.6918</v>
+        <v>48.6945</v>
       </c>
       <c r="I125" t="n">
-        <v>48.9834</v>
+        <v>48.9839</v>
       </c>
       <c r="J125" t="n">
-        <v>43.2</v>
+        <v>46.7</v>
       </c>
       <c r="K125" t="n">
-        <v>19.3</v>
+        <v>20.8</v>
       </c>
       <c r="L125" t="n">
-        <v>0.0067</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10913,22 +10913,22 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>63.37</v>
+        <v>63.53</v>
       </c>
       <c r="H126" t="n">
-        <v>63.5389</v>
+        <v>63.5542</v>
       </c>
       <c r="I126" t="n">
-        <v>63.2572</v>
+        <v>63.2604</v>
       </c>
       <c r="J126" t="n">
-        <v>44.5</v>
+        <v>51.3</v>
       </c>
       <c r="K126" t="n">
-        <v>20.1</v>
+        <v>19.2</v>
       </c>
       <c r="L126" t="n">
-        <v>-0.0433</v>
+        <v>-0.0331</v>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10991,22 +10991,22 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>235.35</v>
+        <v>237.05</v>
       </c>
       <c r="H127" t="n">
-        <v>237.1856</v>
+        <v>237.2847</v>
       </c>
       <c r="I127" t="n">
-        <v>233.503</v>
+        <v>233.78</v>
       </c>
       <c r="J127" t="n">
-        <v>46.4</v>
+        <v>51.2</v>
       </c>
       <c r="K127" t="n">
-        <v>22.6</v>
+        <v>20.7</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.7625</v>
+        <v>-0.6435</v>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -11069,22 +11069,22 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>330.65</v>
+        <v>329.65</v>
       </c>
       <c r="H128" t="n">
-        <v>337.3613</v>
+        <v>337.266</v>
       </c>
       <c r="I128" t="n">
-        <v>341.28</v>
+        <v>341.26</v>
       </c>
       <c r="J128" t="n">
-        <v>33.2</v>
+        <v>30.4</v>
       </c>
       <c r="K128" t="n">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="L128" t="n">
-        <v>-1.3223</v>
+        <v>-1.3861</v>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -11147,22 +11147,22 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>43.225</v>
+        <v>43.37</v>
       </c>
       <c r="H129" t="n">
-        <v>42.0006</v>
+        <v>42.1629</v>
       </c>
       <c r="I129" t="n">
-        <v>40.2513</v>
+        <v>40.3721</v>
       </c>
       <c r="J129" t="n">
-        <v>69.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K129" t="n">
-        <v>29.4</v>
+        <v>31</v>
       </c>
       <c r="L129" t="n">
-        <v>0.044</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -11225,22 +11225,22 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>10.344</v>
+        <v>10.35</v>
       </c>
       <c r="H130" t="n">
-        <v>10.359</v>
+        <v>10.3595</v>
       </c>
       <c r="I130" t="n">
-        <v>10.4169</v>
+        <v>10.417</v>
       </c>
       <c r="J130" t="n">
-        <v>45.6</v>
+        <v>46.6</v>
       </c>
       <c r="K130" t="n">
-        <v>11.7</v>
+        <v>18.6</v>
       </c>
       <c r="L130" t="n">
-        <v>0.0029</v>
+        <v>0.0032</v>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -11381,22 +11381,22 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>154.81</v>
+        <v>155.08</v>
       </c>
       <c r="H132" t="n">
-        <v>155.3251</v>
+        <v>155.3508</v>
       </c>
       <c r="I132" t="n">
-        <v>155.4966</v>
+        <v>155.502</v>
       </c>
       <c r="J132" t="n">
-        <v>42.4</v>
+        <v>46.3</v>
       </c>
       <c r="K132" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="L132" t="n">
-        <v>-0.0615</v>
+        <v>-0.0443</v>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -11459,22 +11459,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>7.239</v>
+        <v>7.248</v>
       </c>
       <c r="H133" t="n">
-        <v>7.2441</v>
+        <v>7.2447</v>
       </c>
       <c r="I133" t="n">
-        <v>7.1482</v>
+        <v>7.1421</v>
       </c>
       <c r="J133" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="K133" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="L133" t="n">
-        <v>-0.0145</v>
+        <v>-0.0143</v>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -11537,22 +11537,22 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>145.43</v>
+        <v>145.245</v>
       </c>
       <c r="H134" t="n">
-        <v>146.0864</v>
+        <v>146.0688</v>
       </c>
       <c r="I134" t="n">
-        <v>147.6443</v>
+        <v>147.6406</v>
       </c>
       <c r="J134" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K134" t="n">
         <v>24.7</v>
       </c>
       <c r="L134" t="n">
-        <v>0.0337</v>
+        <v>0.0219</v>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -11615,22 +11615,22 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>180.82</v>
+        <v>182.64</v>
       </c>
       <c r="H135" t="n">
-        <v>180.9779</v>
+        <v>181.1512</v>
       </c>
       <c r="I135" t="n">
-        <v>179.0004</v>
+        <v>179.0368</v>
       </c>
       <c r="J135" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K135" t="n">
-        <v>16.4</v>
+        <v>17.1</v>
       </c>
       <c r="L135" t="n">
-        <v>-0.3182</v>
+        <v>-0.2021</v>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -11693,22 +11693,22 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>69.52</v>
+        <v>69.5</v>
       </c>
       <c r="H136" t="n">
-        <v>69.68940000000001</v>
+        <v>69.7071</v>
       </c>
       <c r="I136" t="n">
-        <v>70.3472</v>
+        <v>70.39060000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>42</v>
+        <v>41.3</v>
       </c>
       <c r="K136" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="L136" t="n">
-        <v>0.0364</v>
+        <v>0.0325</v>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -11771,22 +11771,22 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>132.12</v>
+        <v>133.38</v>
       </c>
       <c r="H137" t="n">
-        <v>132.2818</v>
+        <v>132.4018</v>
       </c>
       <c r="I137" t="n">
-        <v>131.736</v>
+        <v>131.7612</v>
       </c>
       <c r="J137" t="n">
-        <v>49.8</v>
+        <v>56.3</v>
       </c>
       <c r="K137" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="L137" t="n">
-        <v>-0.1259</v>
+        <v>-0.0455</v>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -11849,22 +11849,22 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>72.67</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="H138" t="n">
-        <v>72.896</v>
+        <v>72.91030000000001</v>
       </c>
       <c r="I138" t="n">
-        <v>73.19159999999999</v>
+        <v>73.19459999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>40.7</v>
+        <v>45.8</v>
       </c>
       <c r="K138" t="n">
-        <v>23.7</v>
+        <v>22.8</v>
       </c>
       <c r="L138" t="n">
-        <v>-0.006</v>
+        <v>0.0035</v>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -11927,22 +11927,22 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18.403</v>
+        <v>18.3745</v>
       </c>
       <c r="H139" t="n">
-        <v>18.4646</v>
+        <v>18.4619</v>
       </c>
       <c r="I139" t="n">
-        <v>18.6858</v>
+        <v>18.6853</v>
       </c>
       <c r="J139" t="n">
-        <v>42.1</v>
+        <v>39.6</v>
       </c>
       <c r="K139" t="n">
-        <v>22.9</v>
+        <v>19.5</v>
       </c>
       <c r="L139" t="n">
-        <v>0.0133</v>
+        <v>0.0115</v>
       </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -12005,22 +12005,22 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>46.08</v>
+        <v>46.05</v>
       </c>
       <c r="H140" t="n">
-        <v>46.1513</v>
+        <v>46.1484</v>
       </c>
       <c r="I140" t="n">
-        <v>46.3195</v>
+        <v>46.3189</v>
       </c>
       <c r="J140" t="n">
-        <v>44.8</v>
+        <v>43.2</v>
       </c>
       <c r="K140" t="n">
         <v>21.5</v>
       </c>
       <c r="L140" t="n">
-        <v>-0.0154</v>
+        <v>-0.0173</v>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -12083,22 +12083,22 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>80.55</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H141" t="n">
-        <v>80.8146</v>
+        <v>80.84220000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>81.68219999999999</v>
+        <v>81.74079999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>41.8</v>
+        <v>40.3</v>
       </c>
       <c r="K141" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="L141" t="n">
-        <v>0.0509</v>
+        <v>0.0508</v>
       </c>
       <c r="M141" s="10" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -12161,22 +12161,22 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>44.635</v>
+        <v>44.71</v>
       </c>
       <c r="H142" t="n">
-        <v>44.7072</v>
+        <v>44.7165</v>
       </c>
       <c r="I142" t="n">
-        <v>45.0312</v>
+        <v>45.0332</v>
       </c>
       <c r="J142" t="n">
-        <v>42.3</v>
+        <v>46.3</v>
       </c>
       <c r="K142" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="L142" t="n">
-        <v>0.0034</v>
+        <v>0.0091</v>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -12317,22 +12317,22 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>89.77</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="H144" t="n">
-        <v>90.98520000000001</v>
+        <v>91.0776</v>
       </c>
       <c r="I144" t="n">
-        <v>89.2256</v>
+        <v>89.245</v>
       </c>
       <c r="J144" t="n">
-        <v>44.9</v>
+        <v>50.2</v>
       </c>
       <c r="K144" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="L144" t="n">
-        <v>-0.4182</v>
+        <v>-0.3563</v>
       </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -12395,22 +12395,22 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>121.3</v>
+        <v>122.44</v>
       </c>
       <c r="H145" t="n">
-        <v>122.926</v>
+        <v>123.0201</v>
       </c>
       <c r="I145" t="n">
-        <v>121.4541</v>
+        <v>121.4735</v>
       </c>
       <c r="J145" t="n">
-        <v>43.9</v>
+        <v>49</v>
       </c>
       <c r="K145" t="n">
         <v>7.7</v>
       </c>
       <c r="L145" t="n">
-        <v>-0.4772</v>
+        <v>-0.4105</v>
       </c>
       <c r="M145" s="10" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -12473,22 +12473,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>115.72</v>
+        <v>116.68</v>
       </c>
       <c r="H146" t="n">
-        <v>117.4947</v>
+        <v>117.5862</v>
       </c>
       <c r="I146" t="n">
-        <v>116.8492</v>
+        <v>116.8684</v>
       </c>
       <c r="J146" t="n">
-        <v>43.9</v>
+        <v>47.3</v>
       </c>
       <c r="K146" t="n">
-        <v>11.9</v>
+        <v>17</v>
       </c>
       <c r="L146" t="n">
-        <v>-0.5125</v>
+        <v>-0.4513</v>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -12551,22 +12551,22 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>23.02</v>
+        <v>23.43</v>
       </c>
       <c r="H147" t="n">
-        <v>23.591</v>
+        <v>23.63</v>
       </c>
       <c r="I147" t="n">
-        <v>23.4558</v>
+        <v>23.464</v>
       </c>
       <c r="J147" t="n">
-        <v>38.4</v>
+        <v>45.3</v>
       </c>
       <c r="K147" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="L147" t="n">
-        <v>-0.0905</v>
+        <v>-0.0643</v>
       </c>
       <c r="M147" s="10" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -12629,22 +12629,22 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>100</v>
+        <v>101.65</v>
       </c>
       <c r="H148" t="n">
-        <v>102.4479</v>
+        <v>102.605</v>
       </c>
       <c r="I148" t="n">
-        <v>101.8634</v>
+        <v>101.8964</v>
       </c>
       <c r="J148" t="n">
-        <v>38.3</v>
+        <v>44.7</v>
       </c>
       <c r="K148" t="n">
-        <v>14.6</v>
+        <v>13.8</v>
       </c>
       <c r="L148" t="n">
-        <v>-0.39</v>
+        <v>-0.2847</v>
       </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -12707,22 +12707,22 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>61.68</v>
+        <v>62.45</v>
       </c>
       <c r="H149" t="n">
-        <v>61.7918</v>
+        <v>61.8651</v>
       </c>
       <c r="I149" t="n">
-        <v>60.6908</v>
+        <v>60.7062</v>
       </c>
       <c r="J149" t="n">
-        <v>51.1</v>
+        <v>57.9</v>
       </c>
       <c r="K149" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="L149" t="n">
-        <v>-0.1738</v>
+        <v>-0.1246</v>
       </c>
       <c r="M149" s="10" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>6.37</v>
+        <v>6.422</v>
       </c>
       <c r="H150" t="n">
-        <v>6.3699</v>
+        <v>6.3748</v>
       </c>
       <c r="I150" t="n">
-        <v>6.3333</v>
+        <v>6.3344</v>
       </c>
       <c r="J150" t="n">
-        <v>51.1</v>
+        <v>56.6</v>
       </c>
       <c r="K150" t="n">
-        <v>11.6</v>
+        <v>15.8</v>
       </c>
       <c r="L150" t="n">
-        <v>-0.0072</v>
+        <v>-0.0038</v>
       </c>
       <c r="M150" s="10" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -12863,22 +12863,22 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>138.14</v>
+        <v>139.6</v>
       </c>
       <c r="H151" t="n">
-        <v>139.1436</v>
+        <v>139.3973</v>
       </c>
       <c r="I151" t="n">
-        <v>137.2224</v>
+        <v>137.2782</v>
       </c>
       <c r="J151" t="n">
-        <v>46.5</v>
+        <v>54.4</v>
       </c>
       <c r="K151" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="L151" t="n">
-        <v>-0.3908</v>
+        <v>-0.2491</v>
       </c>
       <c r="M151" s="10" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -12941,22 +12941,22 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>4.9945</v>
+        <v>5.041</v>
       </c>
       <c r="H152" t="n">
-        <v>5.0078</v>
+        <v>5.0122</v>
       </c>
       <c r="I152" t="n">
-        <v>4.9838</v>
+        <v>4.9848</v>
       </c>
       <c r="J152" t="n">
-        <v>48.5</v>
+        <v>55.4</v>
       </c>
       <c r="K152" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="L152" t="n">
-        <v>-0.0073</v>
+        <v>-0.0044</v>
       </c>
       <c r="M152" s="10" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -13019,22 +13019,22 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>25.365</v>
+        <v>25.335</v>
       </c>
       <c r="H153" t="n">
-        <v>25.429</v>
+        <v>25.4262</v>
       </c>
       <c r="I153" t="n">
-        <v>25.5447</v>
+        <v>25.5441</v>
       </c>
       <c r="J153" t="n">
-        <v>47.2</v>
+        <v>46.3</v>
       </c>
       <c r="K153" t="n">
         <v>13</v>
       </c>
       <c r="L153" t="n">
-        <v>-0.0074</v>
+        <v>-0.0094</v>
       </c>
       <c r="M153" s="10" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -13097,22 +13097,22 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>97.94</v>
+        <v>98.72</v>
       </c>
       <c r="H154" t="n">
-        <v>97.4106</v>
+        <v>97.4849</v>
       </c>
       <c r="I154" t="n">
-        <v>96.527</v>
+        <v>96.54259999999999</v>
       </c>
       <c r="J154" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="K154" t="n">
-        <v>19.6</v>
+        <v>20.6</v>
       </c>
       <c r="L154" t="n">
-        <v>-0.0389</v>
+        <v>0.0109</v>
       </c>
       <c r="M154" s="10" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -13175,22 +13175,22 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>801.1</v>
+        <v>800.17</v>
       </c>
       <c r="H155" t="n">
-        <v>804.6072</v>
+        <v>804.5187</v>
       </c>
       <c r="I155" t="n">
-        <v>807.5454</v>
+        <v>807.5268</v>
       </c>
       <c r="J155" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="K155" t="n">
         <v>12.8</v>
       </c>
       <c r="L155" t="n">
-        <v>-0.4188</v>
+        <v>-0.4782</v>
       </c>
       <c r="M155" s="10" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -13253,22 +13253,22 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>195.82</v>
+        <v>196.51</v>
       </c>
       <c r="H156" t="n">
-        <v>202.7924</v>
+        <v>202.8581</v>
       </c>
       <c r="I156" t="n">
-        <v>206.278</v>
+        <v>206.2918</v>
       </c>
       <c r="J156" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="K156" t="n">
-        <v>17.7</v>
+        <v>15.6</v>
       </c>
       <c r="L156" t="n">
-        <v>-0.8369</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="M156" s="10" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -13331,22 +13331,22 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>657</v>
+        <v>667.2</v>
       </c>
       <c r="H157" t="n">
-        <v>661.1573</v>
+        <v>662.1288</v>
       </c>
       <c r="I157" t="n">
-        <v>660.03</v>
+        <v>660.234</v>
       </c>
       <c r="J157" t="n">
-        <v>46.9</v>
+        <v>53.7</v>
       </c>
       <c r="K157" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
       <c r="L157" t="n">
-        <v>-1.0801</v>
+        <v>-0.4292</v>
       </c>
       <c r="M157" s="10" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -13409,22 +13409,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>20.49</v>
+        <v>20.785</v>
       </c>
       <c r="H158" t="n">
-        <v>20.5933</v>
+        <v>20.6086</v>
       </c>
       <c r="I158" t="n">
-        <v>20.5436</v>
+        <v>20.546</v>
       </c>
       <c r="J158" t="n">
-        <v>47.9</v>
+        <v>54</v>
       </c>
       <c r="K158" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="L158" t="n">
-        <v>-0.0261</v>
+        <v>-0.011</v>
       </c>
       <c r="M158" s="10" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -13487,22 +13487,22 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>19.16</v>
+        <v>19.754</v>
       </c>
       <c r="H159" t="n">
-        <v>19.4998</v>
+        <v>19.5563</v>
       </c>
       <c r="I159" t="n">
-        <v>19.3064</v>
+        <v>19.3183</v>
       </c>
       <c r="J159" t="n">
-        <v>47.7</v>
+        <v>51.9</v>
       </c>
       <c r="K159" t="n">
-        <v>7.7</v>
+        <v>9.1</v>
       </c>
       <c r="L159" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0556</v>
       </c>
       <c r="M159" s="10" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -13565,22 +13565,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>102.28</v>
+        <v>103.67</v>
       </c>
       <c r="H160" t="n">
-        <v>102.9635</v>
+        <v>103.0369</v>
       </c>
       <c r="I160" t="n">
-        <v>103.4872</v>
+        <v>103.46</v>
       </c>
       <c r="J160" t="n">
-        <v>46.5</v>
+        <v>52.6</v>
       </c>
       <c r="K160" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="L160" t="n">
-        <v>-0.075</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="M160" s="10" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -13643,22 +13643,22 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>287.7</v>
+        <v>291.8</v>
       </c>
       <c r="H161" t="n">
-        <v>289.7215</v>
+        <v>290.112</v>
       </c>
       <c r="I161" t="n">
-        <v>291.227</v>
+        <v>291.309</v>
       </c>
       <c r="J161" t="n">
-        <v>46.1</v>
+        <v>52.4</v>
       </c>
       <c r="K161" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="L161" t="n">
-        <v>-0.2491</v>
+        <v>0.0125</v>
       </c>
       <c r="M161" s="10" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -13721,22 +13721,22 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>26</v>
+        <v>26.255</v>
       </c>
       <c r="H162" t="n">
-        <v>26.7069</v>
+        <v>26.7311</v>
       </c>
       <c r="I162" t="n">
-        <v>26.9481</v>
+        <v>26.9532</v>
       </c>
       <c r="J162" t="n">
-        <v>37.1</v>
+        <v>40.4</v>
       </c>
       <c r="K162" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="L162" t="n">
-        <v>-0.0664</v>
+        <v>-0.0502</v>
       </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -13799,22 +13799,22 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>16.154</v>
+        <v>16.17</v>
       </c>
       <c r="H163" t="n">
-        <v>16.1662</v>
+        <v>16.1677</v>
       </c>
       <c r="I163" t="n">
-        <v>16.0941</v>
+        <v>16.0944</v>
       </c>
       <c r="J163" t="n">
-        <v>50.1</v>
+        <v>50.7</v>
       </c>
       <c r="K163" t="n">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="L163" t="n">
-        <v>-0.0198</v>
+        <v>-0.0189</v>
       </c>
       <c r="M163" s="10" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -13877,22 +13877,22 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>138.12</v>
+        <v>140.61</v>
       </c>
       <c r="H164" t="n">
-        <v>140.7714</v>
+        <v>141.0085</v>
       </c>
       <c r="I164" t="n">
-        <v>140.0976</v>
+        <v>140.1474</v>
       </c>
       <c r="J164" t="n">
-        <v>43.9</v>
+        <v>49.4</v>
       </c>
       <c r="K164" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="L164" t="n">
-        <v>-0.4823</v>
+        <v>-0.3234</v>
       </c>
       <c r="M164" s="10" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -13955,22 +13955,22 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>74.02</v>
+        <v>74.05</v>
       </c>
       <c r="H165" t="n">
-        <v>72.8944</v>
+        <v>72.8973</v>
       </c>
       <c r="I165" t="n">
-        <v>71.756</v>
+        <v>71.75660000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="K165" t="n">
         <v>14.1</v>
       </c>
       <c r="L165" t="n">
-        <v>0.0342</v>
+        <v>0.0361</v>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -14004,8 +14004,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="n">
-        <v>3</v>
+      <c r="A166" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -14033,31 +14033,31 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1180.36</v>
+        <v>1199.3199</v>
       </c>
       <c r="H166" t="n">
-        <v>1179.7008</v>
+        <v>1181.5065</v>
       </c>
       <c r="I166" t="n">
-        <v>1169.7084</v>
+        <v>1170.0876</v>
       </c>
       <c r="J166" t="n">
-        <v>50.8</v>
+        <v>56.1</v>
       </c>
       <c r="K166" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="L166" t="n">
-        <v>-0.7988</v>
-      </c>
-      <c r="M166" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.4112</v>
+      </c>
+      <c r="M166" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -14111,22 +14111,22 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>20.925</v>
+        <v>21.205</v>
       </c>
       <c r="H167" t="n">
-        <v>20.9697</v>
+        <v>20.9963</v>
       </c>
       <c r="I167" t="n">
-        <v>20.5298</v>
+        <v>20.5354</v>
       </c>
       <c r="J167" t="n">
-        <v>50.8</v>
+        <v>55.2</v>
       </c>
       <c r="K167" t="n">
-        <v>13.8</v>
+        <v>16.5</v>
       </c>
       <c r="L167" t="n">
-        <v>-0.0483</v>
+        <v>-0.0306</v>
       </c>
       <c r="M167" s="10" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -14189,22 +14189,22 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>5.874</v>
+        <v>5.879</v>
       </c>
       <c r="H168" t="n">
-        <v>6.1599</v>
+        <v>6.1604</v>
       </c>
       <c r="I168" t="n">
-        <v>6.0656</v>
+        <v>6.0657</v>
       </c>
       <c r="J168" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="K168" t="n">
         <v>27.8</v>
       </c>
       <c r="L168" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.076</v>
       </c>
       <c r="M168" s="10" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -14267,22 +14267,22 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>410.53</v>
+        <v>414.1</v>
       </c>
       <c r="H169" t="n">
-        <v>410.4549</v>
+        <v>410.8006</v>
       </c>
       <c r="I169" t="n">
-        <v>392.0822</v>
+        <v>392.1536</v>
       </c>
       <c r="J169" t="n">
-        <v>52.4</v>
+        <v>54.6</v>
       </c>
       <c r="K169" t="n">
-        <v>21.6</v>
+        <v>27.7</v>
       </c>
       <c r="L169" t="n">
-        <v>-2.0906</v>
+        <v>-1.8505</v>
       </c>
       <c r="M169" s="10" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -14345,22 +14345,22 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>51.61</v>
+        <v>52.15</v>
       </c>
       <c r="H170" t="n">
-        <v>51.4979</v>
+        <v>51.5492</v>
       </c>
       <c r="I170" t="n">
-        <v>48.9662</v>
+        <v>48.977</v>
       </c>
       <c r="J170" t="n">
-        <v>52.1</v>
+        <v>54.1</v>
       </c>
       <c r="K170" t="n">
-        <v>15.6</v>
+        <v>19</v>
       </c>
       <c r="L170" t="n">
-        <v>-0.2551</v>
+        <v>-0.221</v>
       </c>
       <c r="M170" s="10" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -14423,22 +14423,22 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>166.63</v>
+        <v>168.15</v>
       </c>
       <c r="H171" t="n">
-        <v>166.6662</v>
+        <v>166.9192</v>
       </c>
       <c r="I171" t="n">
-        <v>165.8752</v>
+        <v>165.9308</v>
       </c>
       <c r="J171" t="n">
-        <v>50.6</v>
+        <v>57.1</v>
       </c>
       <c r="K171" t="n">
-        <v>10.2</v>
+        <v>11.9</v>
       </c>
       <c r="L171" t="n">
-        <v>-0.2048</v>
+        <v>-0.063</v>
       </c>
       <c r="M171" s="10" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -14579,22 +14579,22 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>28.845</v>
+        <v>29.065</v>
       </c>
       <c r="H173" t="n">
-        <v>29.6038</v>
+        <v>29.6247</v>
       </c>
       <c r="I173" t="n">
-        <v>30.2213</v>
+        <v>30.2257</v>
       </c>
       <c r="J173" t="n">
-        <v>28.9</v>
+        <v>35</v>
       </c>
       <c r="K173" t="n">
-        <v>25.7</v>
+        <v>32</v>
       </c>
       <c r="L173" t="n">
-        <v>-0.1096</v>
+        <v>-0.0955</v>
       </c>
       <c r="M173" s="10" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -14657,22 +14657,22 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>9.988</v>
+        <v>10.19</v>
       </c>
       <c r="H174" t="n">
-        <v>10.1871</v>
+        <v>10.2123</v>
       </c>
       <c r="I174" t="n">
-        <v>10.5736</v>
+        <v>10.579</v>
       </c>
       <c r="J174" t="n">
-        <v>40.8</v>
+        <v>46.7</v>
       </c>
       <c r="K174" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="L174" t="n">
-        <v>-0.0062</v>
+        <v>0.0092</v>
       </c>
       <c r="M174" s="10" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -14735,22 +14735,22 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>203.8</v>
+        <v>207.95</v>
       </c>
       <c r="H175" t="n">
-        <v>203.6372</v>
+        <v>204.0319</v>
       </c>
       <c r="I175" t="n">
-        <v>202.1248</v>
+        <v>202.2078</v>
       </c>
       <c r="J175" t="n">
-        <v>51</v>
+        <v>57.2</v>
       </c>
       <c r="K175" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="L175" t="n">
-        <v>-0.0766</v>
+        <v>0.1866</v>
       </c>
       <c r="M175" s="10" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -14813,22 +14813,22 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>274.05</v>
+        <v>278.65</v>
       </c>
       <c r="H176" t="n">
-        <v>274.4924</v>
+        <v>274.9305</v>
       </c>
       <c r="I176" t="n">
-        <v>270.71</v>
+        <v>270.802</v>
       </c>
       <c r="J176" t="n">
-        <v>50.7</v>
+        <v>60.6</v>
       </c>
       <c r="K176" t="n">
-        <v>27.4</v>
+        <v>28.3</v>
       </c>
       <c r="L176" t="n">
-        <v>-0.8004</v>
+        <v>-0.5068</v>
       </c>
       <c r="M176" s="10" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -14891,22 +14891,22 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>33.04</v>
+        <v>33.1</v>
       </c>
       <c r="H177" t="n">
-        <v>33.415</v>
+        <v>33.4207</v>
       </c>
       <c r="I177" t="n">
-        <v>34.0324</v>
+        <v>34.0336</v>
       </c>
       <c r="J177" t="n">
-        <v>40.8</v>
+        <v>42</v>
       </c>
       <c r="K177" t="n">
         <v>22.6</v>
       </c>
       <c r="L177" t="n">
-        <v>-0.0227</v>
+        <v>-0.0189</v>
       </c>
       <c r="M177" s="10" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -14969,22 +14969,22 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>158.06</v>
+        <v>158.22</v>
       </c>
       <c r="H178" t="n">
-        <v>158.5812</v>
+        <v>158.5964</v>
       </c>
       <c r="I178" t="n">
-        <v>159.0172</v>
+        <v>159.0204</v>
       </c>
       <c r="J178" t="n">
-        <v>37</v>
+        <v>40.7</v>
       </c>
       <c r="K178" t="n">
         <v>16.1</v>
       </c>
       <c r="L178" t="n">
-        <v>-0.077</v>
+        <v>-0.0668</v>
       </c>
       <c r="M178" s="10" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -15047,22 +15047,22 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>70.63</v>
+        <v>71.3</v>
       </c>
       <c r="H179" t="n">
-        <v>70.00700000000001</v>
+        <v>70.07080000000001</v>
       </c>
       <c r="I179" t="n">
-        <v>69.2154</v>
+        <v>69.22880000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>57.7</v>
+        <v>62.2</v>
       </c>
       <c r="K179" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L179" t="n">
-        <v>0.0021</v>
+        <v>0.0449</v>
       </c>
       <c r="M179" s="10" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -15125,22 +15125,22 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>10.564</v>
+        <v>10.6273</v>
       </c>
       <c r="H180" t="n">
-        <v>10.6146</v>
+        <v>10.6206</v>
       </c>
       <c r="I180" t="n">
-        <v>10.505</v>
+        <v>10.5062</v>
       </c>
       <c r="J180" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K180" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="L180" t="n">
-        <v>-0.03</v>
+        <v>-0.026</v>
       </c>
       <c r="M180" s="10" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -15203,22 +15203,22 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>81.75</v>
+        <v>82.05</v>
       </c>
       <c r="H181" t="n">
-        <v>81.343</v>
+        <v>81.41200000000001</v>
       </c>
       <c r="I181" t="n">
-        <v>80.66759999999999</v>
+        <v>80.68300000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>58.2</v>
+        <v>62.6</v>
       </c>
       <c r="K181" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="L181" t="n">
-        <v>-0.0538</v>
+        <v>-0.0174</v>
       </c>
       <c r="M181" s="10" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -15359,22 +15359,22 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>114.08</v>
+        <v>115.5101</v>
       </c>
       <c r="H183" t="n">
-        <v>115.4348</v>
+        <v>115.571</v>
       </c>
       <c r="I183" t="n">
-        <v>116.2074</v>
+        <v>116.236</v>
       </c>
       <c r="J183" t="n">
-        <v>44.6</v>
+        <v>49.5</v>
       </c>
       <c r="K183" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L183" t="n">
-        <v>-0.3249</v>
+        <v>-0.2336</v>
       </c>
       <c r="M183" s="10" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -15437,22 +15437,22 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>89.64</v>
+        <v>90.38</v>
       </c>
       <c r="H184" t="n">
-        <v>90.0288</v>
+        <v>90.0993</v>
       </c>
       <c r="I184" t="n">
-        <v>88.96339999999999</v>
+        <v>88.9782</v>
       </c>
       <c r="J184" t="n">
-        <v>48.1</v>
+        <v>54.6</v>
       </c>
       <c r="K184" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="L184" t="n">
-        <v>-0.2221</v>
+        <v>-0.1748</v>
       </c>
       <c r="M184" s="10" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -15515,22 +15515,22 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>78.39</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="H185" t="n">
-        <v>78.0104</v>
+        <v>78.04089999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>76.4682</v>
+        <v>76.4746</v>
       </c>
       <c r="J185" t="n">
-        <v>63</v>
+        <v>66.7</v>
       </c>
       <c r="K185" t="n">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
       <c r="L185" t="n">
-        <v>-0.1153</v>
+        <v>-0.0949</v>
       </c>
       <c r="M185" s="10" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -15565,7 +15565,7 @@
     </row>
     <row r="186">
       <c r="A186" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -15593,31 +15593,31 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>18.884</v>
+        <v>18.984</v>
       </c>
       <c r="H186" t="n">
-        <v>18.1537</v>
+        <v>18.2117</v>
       </c>
       <c r="I186" t="n">
-        <v>18.084</v>
+        <v>18.0972</v>
       </c>
       <c r="J186" t="n">
-        <v>66.5</v>
+        <v>69.5</v>
       </c>
       <c r="K186" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="L186" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="M186" s="12" t="inlineStr">
-        <is>
-          <t>L2 WATCH</t>
+        <v>0.1279</v>
+      </c>
+      <c r="M186" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -15671,22 +15671,22 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>39.865</v>
+        <v>40.145</v>
       </c>
       <c r="H187" t="n">
-        <v>39.6186</v>
+        <v>39.6453</v>
       </c>
       <c r="I187" t="n">
-        <v>39.2032</v>
+        <v>39.2088</v>
       </c>
       <c r="J187" t="n">
-        <v>55</v>
+        <v>58.7</v>
       </c>
       <c r="K187" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="L187" t="n">
-        <v>0.0395</v>
+        <v>0.0574</v>
       </c>
       <c r="M187" s="10" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -15749,22 +15749,22 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>52.57</v>
+        <v>52.85</v>
       </c>
       <c r="H188" t="n">
-        <v>52.9368</v>
+        <v>52.9633</v>
       </c>
       <c r="I188" t="n">
-        <v>52.4926</v>
+        <v>52.4982</v>
       </c>
       <c r="J188" t="n">
-        <v>43.7</v>
+        <v>49.5</v>
       </c>
       <c r="K188" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="L188" t="n">
-        <v>-0.1378</v>
+        <v>-0.1203</v>
       </c>
       <c r="M188" s="10" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -15827,22 +15827,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>8.448</v>
+        <v>8.443</v>
       </c>
       <c r="H189" t="n">
-        <v>8.445399999999999</v>
+        <v>8.444900000000001</v>
       </c>
       <c r="I189" t="n">
-        <v>8.349600000000001</v>
+        <v>8.349500000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="K189" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="L189" t="n">
-        <v>-0.0157</v>
+        <v>-0.016</v>
       </c>
       <c r="M189" s="10" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -15905,22 +15905,22 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>17.094</v>
+        <v>17.196</v>
       </c>
       <c r="H190" t="n">
-        <v>17.0792</v>
+        <v>17.0888</v>
       </c>
       <c r="I190" t="n">
-        <v>16.9027</v>
+        <v>16.9047</v>
       </c>
       <c r="J190" t="n">
-        <v>51.6</v>
+        <v>56</v>
       </c>
       <c r="K190" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L190" t="n">
-        <v>-0.0001</v>
+        <v>0.0063</v>
       </c>
       <c r="M190" s="10" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -15983,22 +15983,22 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>48.235</v>
+        <v>48.68</v>
       </c>
       <c r="H191" t="n">
-        <v>48.6768</v>
+        <v>48.7191</v>
       </c>
       <c r="I191" t="n">
-        <v>48.1979</v>
+        <v>48.2068</v>
       </c>
       <c r="J191" t="n">
-        <v>45.8</v>
+        <v>50.3</v>
       </c>
       <c r="K191" t="n">
-        <v>8.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="L191" t="n">
-        <v>-0.1067</v>
+        <v>-0.0786</v>
       </c>
       <c r="M191" s="10" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -16061,22 +16061,22 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>3.808</v>
+        <v>3.813</v>
       </c>
       <c r="H192" t="n">
-        <v>3.7665</v>
+        <v>3.767</v>
       </c>
       <c r="I192" t="n">
-        <v>3.7334</v>
+        <v>3.7335</v>
       </c>
       <c r="J192" t="n">
-        <v>57</v>
+        <v>57.7</v>
       </c>
       <c r="K192" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="L192" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="M192" s="12" t="inlineStr">
         <is>
@@ -16085,12 +16085,12 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>DE000A0Q4MJ7</t>
+          <t>GB00B15KXN58</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -16139,22 +16139,22 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>11.486</v>
+        <v>11.524</v>
       </c>
       <c r="H193" t="n">
-        <v>11.3141</v>
+        <v>11.296</v>
       </c>
       <c r="I193" t="n">
-        <v>10.9632</v>
+        <v>10.9398</v>
       </c>
       <c r="J193" t="n">
-        <v>61</v>
+        <v>62.9</v>
       </c>
       <c r="K193" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="L193" t="n">
-        <v>0.0156</v>
+        <v>0.0278</v>
       </c>
       <c r="M193" s="10" t="inlineStr">
         <is>
@@ -16163,12 +16163,12 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>DE000A0QLW44</t>
+          <t>GB00B15KY872</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -16217,22 +16217,22 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>10.36</v>
+        <v>10.366</v>
       </c>
       <c r="H194" t="n">
-        <v>10.1677</v>
+        <v>10.1683</v>
       </c>
       <c r="I194" t="n">
-        <v>9.4754</v>
+        <v>9.4755</v>
       </c>
       <c r="J194" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="K194" t="n">
-        <v>22.6</v>
+        <v>25.1</v>
       </c>
       <c r="L194" t="n">
-        <v>-0.0319</v>
+        <v>-0.0315</v>
       </c>
       <c r="M194" s="10" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -16295,22 +16295,22 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>26.83</v>
+        <v>27.035</v>
       </c>
       <c r="H195" t="n">
-        <v>27.469</v>
+        <v>27.4885</v>
       </c>
       <c r="I195" t="n">
-        <v>27.8999</v>
+        <v>27.904</v>
       </c>
       <c r="J195" t="n">
-        <v>41</v>
+        <v>43.5</v>
       </c>
       <c r="K195" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="L195" t="n">
-        <v>-0.0611</v>
+        <v>-0.048</v>
       </c>
       <c r="M195" s="10" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -16373,22 +16373,22 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>4.619</v>
+        <v>4.657</v>
       </c>
       <c r="H196" t="n">
-        <v>4.7526</v>
+        <v>4.754</v>
       </c>
       <c r="I196" t="n">
-        <v>4.8511</v>
+        <v>4.8514</v>
       </c>
       <c r="J196" t="n">
-        <v>24.5</v>
+        <v>33.7</v>
       </c>
       <c r="K196" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="L196" t="n">
-        <v>-0.0172</v>
+        <v>-0.0157</v>
       </c>
       <c r="M196" s="10" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -16451,22 +16451,22 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>84.26000000000001</v>
+        <v>84.22</v>
       </c>
       <c r="H197" t="n">
-        <v>85.69629999999999</v>
+        <v>85.7115</v>
       </c>
       <c r="I197" t="n">
-        <v>85.9927</v>
+        <v>85.99630000000001</v>
       </c>
       <c r="J197" t="n">
-        <v>37.5</v>
+        <v>36.2</v>
       </c>
       <c r="K197" t="n">
         <v>31.8</v>
       </c>
       <c r="L197" t="n">
-        <v>-0.353</v>
+        <v>-0.3475</v>
       </c>
       <c r="M197" s="10" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -16529,7 +16529,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>150.095</v>
+        <v>150.1069946289062</v>
       </c>
       <c r="H198" t="n">
         <v>149.1741</v>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -16607,22 +16607,22 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>141.03</v>
+        <v>141.1</v>
       </c>
       <c r="H199" t="n">
-        <v>141.1138</v>
+        <v>141.1196</v>
       </c>
       <c r="I199" t="n">
-        <v>141.1226</v>
+        <v>141.1238</v>
       </c>
       <c r="J199" t="n">
-        <v>45.3</v>
+        <v>49.1</v>
       </c>
       <c r="K199" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="L199" t="n">
-        <v>-0.0258</v>
+        <v>-0.0217</v>
       </c>
       <c r="M199" s="10" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -16685,22 +16685,22 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>157.48</v>
+        <v>159</v>
       </c>
       <c r="H200" t="n">
-        <v>157.5853</v>
+        <v>157.7297</v>
       </c>
       <c r="I200" t="n">
-        <v>155.7426</v>
+        <v>155.773</v>
       </c>
       <c r="J200" t="n">
-        <v>51.2</v>
+        <v>57.4</v>
       </c>
       <c r="K200" t="n">
-        <v>13.8</v>
+        <v>36.5</v>
       </c>
       <c r="L200" t="n">
-        <v>-0.2661</v>
+        <v>-0.17</v>
       </c>
       <c r="M200" s="10" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -16763,22 +16763,22 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>119.61</v>
+        <v>120.62</v>
       </c>
       <c r="H201" t="n">
-        <v>119.8616</v>
+        <v>119.9575</v>
       </c>
       <c r="I201" t="n">
-        <v>118.5611</v>
+        <v>118.5813</v>
       </c>
       <c r="J201" t="n">
-        <v>49.9</v>
+        <v>56.5</v>
       </c>
       <c r="K201" t="n">
-        <v>14.5</v>
+        <v>19.9</v>
       </c>
       <c r="L201" t="n">
-        <v>-0.2266</v>
+        <v>-0.1628</v>
       </c>
       <c r="M201" s="10" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -16841,22 +16841,22 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>366.86</v>
+        <v>369.46</v>
       </c>
       <c r="H202" t="n">
-        <v>367.1397</v>
+        <v>367.3865</v>
       </c>
       <c r="I202" t="n">
-        <v>354.0886</v>
+        <v>354.1406</v>
       </c>
       <c r="J202" t="n">
-        <v>51.9</v>
+        <v>54.1</v>
       </c>
       <c r="K202" t="n">
-        <v>20.3</v>
+        <v>24.9</v>
       </c>
       <c r="L202" t="n">
-        <v>-1.9259</v>
+        <v>-1.7623</v>
       </c>
       <c r="M202" s="10" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -16919,22 +16919,22 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>7.773</v>
+        <v>8.09</v>
       </c>
       <c r="H203" t="n">
-        <v>7.3428</v>
+        <v>7.373</v>
       </c>
       <c r="I203" t="n">
-        <v>6.6634</v>
+        <v>6.6697</v>
       </c>
       <c r="J203" t="n">
-        <v>66.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K203" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="L203" t="n">
-        <v>0.0389</v>
+        <v>0.0591</v>
       </c>
       <c r="M203" s="10" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -16997,22 +16997,22 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>30.56</v>
+        <v>30.48</v>
       </c>
       <c r="H204" t="n">
-        <v>29.6275</v>
+        <v>29.6198</v>
       </c>
       <c r="I204" t="n">
-        <v>28.5372</v>
+        <v>28.5356</v>
       </c>
       <c r="J204" t="n">
-        <v>69.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K204" t="n">
-        <v>26.3</v>
+        <v>28.8</v>
       </c>
       <c r="L204" t="n">
-        <v>0.0999</v>
+        <v>0.0946</v>
       </c>
       <c r="M204" s="10" t="inlineStr">
         <is>
@@ -17021,12 +17021,12 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>IE00BD6FVP32</t>
+          <t>IE00BD6FTQ80</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -17046,8 +17046,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="n">
-        <v>3</v>
+      <c r="A205" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -17075,31 +17075,31 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>123.7</v>
+        <v>125.66</v>
       </c>
       <c r="H205" t="n">
-        <v>123.6003</v>
+        <v>123.7869</v>
       </c>
       <c r="I205" t="n">
-        <v>122.5164</v>
+        <v>122.5556</v>
       </c>
       <c r="J205" t="n">
-        <v>51</v>
+        <v>56.2</v>
       </c>
       <c r="K205" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="L205" t="n">
-        <v>-0.0873</v>
-      </c>
-      <c r="M205" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
+        <v>0.0378</v>
+      </c>
+      <c r="M205" s="12" t="inlineStr">
+        <is>
+          <t>L2 WATCH</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -17153,22 +17153,22 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>37.955</v>
+        <v>38.69</v>
       </c>
       <c r="H206" t="n">
-        <v>39.2052</v>
+        <v>39.2751</v>
       </c>
       <c r="I206" t="n">
-        <v>39.1562</v>
+        <v>39.1709</v>
       </c>
       <c r="J206" t="n">
-        <v>42.8</v>
+        <v>47.1</v>
       </c>
       <c r="K206" t="n">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="L206" t="n">
-        <v>-0.2412</v>
+        <v>-0.1946</v>
       </c>
       <c r="M206" s="10" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -17231,22 +17231,22 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>9.353</v>
+        <v>9.536</v>
       </c>
       <c r="H207" t="n">
-        <v>9.4472</v>
+        <v>9.464700000000001</v>
       </c>
       <c r="I207" t="n">
-        <v>9.482100000000001</v>
+        <v>9.485799999999999</v>
       </c>
       <c r="J207" t="n">
-        <v>46.8</v>
+        <v>52.1</v>
       </c>
       <c r="K207" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="L207" t="n">
-        <v>-0.0213</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="M207" s="10" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -17309,22 +17309,22 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>8.617000000000001</v>
+        <v>8.763</v>
       </c>
       <c r="H208" t="n">
-        <v>8.794499999999999</v>
+        <v>8.808400000000001</v>
       </c>
       <c r="I208" t="n">
-        <v>9.196099999999999</v>
+        <v>9.199</v>
       </c>
       <c r="J208" t="n">
-        <v>39.1</v>
+        <v>45.1</v>
       </c>
       <c r="K208" t="n">
-        <v>24.1</v>
+        <v>23</v>
       </c>
       <c r="L208" t="n">
-        <v>0.0062</v>
+        <v>0.0156</v>
       </c>
       <c r="M208" s="10" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -17387,22 +17387,22 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>85.8925</v>
+        <v>86.6225</v>
       </c>
       <c r="H209" t="n">
-        <v>85.8867</v>
+        <v>85.9562</v>
       </c>
       <c r="I209" t="n">
-        <v>82.0097</v>
+        <v>82.0243</v>
       </c>
       <c r="J209" t="n">
-        <v>52.4</v>
+        <v>54.6</v>
       </c>
       <c r="K209" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="L209" t="n">
-        <v>-0.4402</v>
+        <v>-0.3936</v>
       </c>
       <c r="M209" s="10" t="inlineStr">
         <is>
@@ -17411,12 +17411,12 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>DE000A1RX996</t>
+          <t>IE00B4ND3602</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -17465,22 +17465,22 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>139.25</v>
+        <v>142.2</v>
       </c>
       <c r="H210" t="n">
-        <v>140.0082</v>
+        <v>140.2891</v>
       </c>
       <c r="I210" t="n">
-        <v>134.1894</v>
+        <v>134.2484</v>
       </c>
       <c r="J210" t="n">
-        <v>50.2</v>
+        <v>54.3</v>
       </c>
       <c r="K210" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="L210" t="n">
-        <v>-0.6744</v>
+        <v>-0.4861</v>
       </c>
       <c r="M210" s="10" t="inlineStr">
         <is>
@@ -17489,12 +17489,12 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>DE000A0N62E5</t>
+          <t>JE00B1VS2W53</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -17543,22 +17543,22 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>62.6</v>
+        <v>62.78</v>
       </c>
       <c r="H211" t="n">
-        <v>53.3935</v>
+        <v>52.9902</v>
       </c>
       <c r="I211" t="n">
-        <v>48.0007</v>
+        <v>47.9067</v>
       </c>
       <c r="J211" t="n">
-        <v>82.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K211" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="L211" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.8237</v>
       </c>
       <c r="M211" s="10" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-09-03 22:22</t>
+          <t>2026-09-04 09:46</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -17592,8 +17592,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="7" t="n">
-        <v>3</v>
+      <c r="A212" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -17621,31 +17621,31 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>59.14</v>
+        <v>62.17</v>
       </c>
       <c r="H212" t="n">
-        <v>58.3211</v>
+        <v>58.9638</v>
       </c>
       <c r="I212" t="n">
-        <v>51.6433</v>
+        <v>51.7861</v>
       </c>
       <c r="J212" t="n">
-        <v>56.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K212" t="n">
-        <v>34.3</v>
+        <v>37.7</v>
       </c>
       <c r="L212" t="n">
-        <v>-0.0234</v>
-      </c>
-      <c r="M212" s="10" t="i